--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22344427-D1AF-8147-96A1-6B89E9427385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{701F02A1-B03B-9D4B-B920-583079AE70D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4060" yWindow="3160" windowWidth="27240" windowHeight="16440" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
   </externalReferences>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="697">
   <si>
     <t>Household Name</t>
   </si>
@@ -2128,6 +2128,9 @@
   </si>
   <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000lQkx0YAC/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qehEnYAI/view</t>
   </si>
 </sst>
 </file>
@@ -8168,8 +8171,7 @@
     <col min="3" max="3" width="24.6640625" customWidth="1"/>
     <col min="4" max="4" width="22.1640625" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
-    <col min="6" max="6" width="84.33203125" customWidth="1"/>
-    <col min="7" max="7" width="45" customWidth="1"/>
+    <col min="6" max="7" width="84.33203125" customWidth="1"/>
     <col min="8" max="8" width="47.83203125" customWidth="1"/>
     <col min="9" max="9" width="47" customWidth="1"/>
   </cols>
@@ -8661,6 +8663,9 @@
       </c>
       <c r="F27" t="s">
         <v>117</v>
+      </c>
+      <c r="G27" t="s">
+        <v>696</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{701F02A1-B03B-9D4B-B920-583079AE70D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8A509E-4710-2F4D-8AD7-C4E636086E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4060" yWindow="3160" windowWidth="27240" windowHeight="16440" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="698">
   <si>
     <t>Household Name</t>
   </si>
@@ -2131,6 +2131,9 @@
   </si>
   <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qehEnYAI/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000topVtYAI/view</t>
   </si>
 </sst>
 </file>
@@ -11075,7 +11078,7 @@
         <v>692</v>
       </c>
       <c r="G168" t="s">
-        <v>340</v>
+        <v>697</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.2">

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B3C4B9-E5B4-9A48-B95E-857F045021E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE073FAD-450F-0A4B-AB22-EC2815E5F68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="3300" windowWidth="27240" windowHeight="16440" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
+    <workbookView xWindow="-34820" yWindow="2020" windowWidth="27240" windowHeight="16440" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
   <sheets>
     <sheet name="xlsx" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="995">
   <si>
     <t>Household Name</t>
   </si>
@@ -237,9 +237,6 @@
     <t>https://curebound.lightning.force.com/lightning/r/006QU00000p5Bn7YAE/view</t>
   </si>
   <si>
-    <t>Molly Elderedge + Manchester’s</t>
-  </si>
-  <si>
     <t>A19</t>
   </si>
   <si>
@@ -297,9 +294,6 @@
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000p56vRYAQ/view</t>
   </si>
   <si>
-    <t>Scott Thurman</t>
-  </si>
-  <si>
     <t>A17</t>
   </si>
   <si>
@@ -309,9 +303,6 @@
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000nZ0YsYAK/view</t>
   </si>
   <si>
-    <t>MacBaisey’s + Rastetter’s + Rubin’s</t>
-  </si>
-  <si>
     <t>A28</t>
   </si>
   <si>
@@ -324,9 +315,6 @@
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000pb4iRYAQ/view</t>
   </si>
   <si>
-    <t>Joanne Marks + Jim Sliverwood + Geier + Thomas's</t>
-  </si>
-  <si>
     <t>A25</t>
   </si>
   <si>
@@ -381,9 +369,6 @@
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000q67FPYAY/view</t>
   </si>
   <si>
-    <t>Shen's + Saripelli's</t>
-  </si>
-  <si>
     <t>A29</t>
   </si>
   <si>
@@ -1251,9 +1236,6 @@
     <t>x=17.03, y=63.29</t>
   </si>
   <si>
-    <t>(sponsor)</t>
-  </si>
-  <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000rDw2uYAC/view</t>
   </si>
   <si>
@@ -1422,9 +1404,6 @@
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000pboWjYAI/view</t>
   </si>
   <si>
-    <t>Cyrus K. Mirsaidi</t>
-  </si>
-  <si>
     <t>E74</t>
   </si>
   <si>
@@ -3028,6 +3007,21 @@
   </si>
   <si>
     <t>x=7.67, y=78.02</t>
+  </si>
+  <si>
+    <t>Manchester</t>
+  </si>
+  <si>
+    <t>Thurman + Doshay + Nagy</t>
+  </si>
+  <si>
+    <t>MacBaisey + Rastetter + Rubin</t>
+  </si>
+  <si>
+    <t>Joanne Marks + Jim Sliverwood + Geier + Thomas</t>
+  </si>
+  <si>
+    <t>Shen + Saripelli</t>
   </si>
 </sst>
 </file>
@@ -3116,7 +3110,17 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3497,7 +3501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7894B4-148E-174D-AE8B-E6DE441B89B0}">
-  <dimension ref="A1:I234"/>
+  <dimension ref="A1:I233"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="54.6640625" customWidth="1"/>
@@ -3835,43 +3839,43 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -3879,20 +3883,20 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -3900,20 +3904,20 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -3921,20 +3925,20 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -3942,20 +3946,20 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -3963,72 +3967,72 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>90</v>
+        <v>992</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>95</v>
+        <v>993</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -4036,20 +4040,20 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -4057,20 +4061,20 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -4078,43 +4082,43 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>114</v>
+        <v>994</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
@@ -4122,20 +4126,20 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -4143,20 +4147,20 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -4164,20 +4168,20 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -4185,20 +4189,20 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -4206,20 +4210,20 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -4227,20 +4231,20 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="4" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -4248,20 +4252,20 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
@@ -4269,43 +4273,43 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
@@ -4313,43 +4317,43 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="4" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -4357,16 +4361,16 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
@@ -4376,20 +4380,20 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="4" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -4400,16 +4404,16 @@
         <v>22</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -4418,16 +4422,16 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -4437,20 +4441,20 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -4458,20 +4462,20 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -4479,20 +4483,20 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -4500,20 +4504,20 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -4521,20 +4525,20 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
@@ -4542,20 +4546,20 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -4563,20 +4567,20 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -4584,20 +4588,20 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
@@ -4605,20 +4609,20 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
@@ -4626,22 +4630,22 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -4649,20 +4653,20 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
@@ -4670,20 +4674,20 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
@@ -4691,20 +4695,20 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
@@ -4712,20 +4716,20 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>739</v>
+        <v>691</v>
+      </c>
+      <c r="C57" t="s">
+        <v>732</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
@@ -4733,20 +4737,20 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
@@ -4754,20 +4758,20 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
@@ -4775,20 +4779,20 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
@@ -4796,20 +4800,20 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="4" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
@@ -4817,16 +4821,16 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
@@ -4836,16 +4840,16 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
@@ -4855,20 +4859,20 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
@@ -4876,13 +4880,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>12</v>
@@ -4895,20 +4899,20 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="4" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
@@ -4916,20 +4920,20 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="4" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
@@ -4937,20 +4941,20 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
@@ -4958,20 +4962,20 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
@@ -4979,20 +4983,20 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
@@ -5000,20 +5004,20 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
@@ -5021,20 +5025,20 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
@@ -5042,20 +5046,20 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="6" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
@@ -5063,20 +5067,20 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>292</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" s="6" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
@@ -5084,20 +5088,20 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
@@ -5105,22 +5109,22 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -5128,20 +5132,20 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
@@ -5149,20 +5153,20 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
@@ -5170,20 +5174,20 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="4" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
@@ -5191,20 +5195,20 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="4" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
@@ -5212,20 +5216,20 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
@@ -5233,20 +5237,20 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
@@ -5254,20 +5258,20 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -5275,20 +5279,20 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="4" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
@@ -5296,20 +5300,20 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="6" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
@@ -5317,20 +5321,20 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>336</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="6" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -5338,43 +5342,43 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="6" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -5382,20 +5386,20 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -5403,20 +5407,20 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="6" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -5424,20 +5428,20 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>354</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" s="6" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -5445,20 +5449,20 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="6" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -5466,20 +5470,20 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="6" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -5487,20 +5491,20 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="6" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -5508,20 +5512,20 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>362</v>
-      </c>
       <c r="C95" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="6" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -5529,20 +5533,20 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="6" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -5550,20 +5554,20 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="6" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
@@ -5571,20 +5575,20 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="6" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
@@ -5592,20 +5596,20 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="6" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
@@ -5613,20 +5617,20 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
@@ -5634,20 +5638,20 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="6" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
@@ -5655,20 +5659,20 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>383</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="6" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
@@ -5676,20 +5680,20 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="6" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -5697,20 +5701,20 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="6" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -5718,20 +5722,20 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>391</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" s="6" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -5739,20 +5743,20 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" s="6" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -5760,20 +5764,20 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>397</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" s="6" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
@@ -5781,20 +5785,20 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="4" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
@@ -5802,22 +5806,22 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="D109" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E109" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="C109" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>404</v>
-      </c>
       <c r="F109" s="6" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
@@ -5825,22 +5829,20 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="F110" s="6" t="s">
-        <v>405</v>
+        <v>159</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" s="4" t="s">
+        <v>679</v>
       </c>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
@@ -5848,20 +5850,20 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" s="4" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
@@ -5869,20 +5871,20 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="4" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
@@ -5890,34 +5892,32 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>415</v>
-      </c>
       <c r="C113" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>164</v>
+        <v>12</v>
       </c>
       <c r="E113" s="2"/>
-      <c r="F113" s="4" t="s">
-        <v>687</v>
-      </c>
+      <c r="F113" s="2"/>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>12</v>
@@ -5930,13 +5930,13 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C115" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>421</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>12</v>
@@ -5949,39 +5949,41 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>12</v>
+        <v>159</v>
       </c>
       <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
+      <c r="F116" s="4" t="s">
+        <v>681</v>
+      </c>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2" t="s">
         <v>424</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" s="4" t="s">
-        <v>688</v>
       </c>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
@@ -5989,20 +5991,20 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
@@ -6010,20 +6012,20 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E119" s="2"/>
-      <c r="F119" s="2" t="s">
-        <v>433</v>
+      <c r="F119" s="1" t="s">
+        <v>692</v>
       </c>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
@@ -6031,20 +6033,20 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="1" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
@@ -6052,20 +6054,20 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C121" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>438</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="1" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
@@ -6073,20 +6075,20 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E122" s="2"/>
-      <c r="F122" s="1" t="s">
-        <v>699</v>
+      <c r="F122" s="6" t="s">
+        <v>438</v>
       </c>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
@@ -6094,20 +6096,20 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="6" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
@@ -6115,20 +6117,20 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>445</v>
-      </c>
       <c r="C124" s="2" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="6" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
@@ -6136,20 +6138,20 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="6" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
@@ -6157,20 +6159,20 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="6" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
@@ -6178,20 +6180,20 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E127" s="2"/>
-      <c r="F127" s="6" t="s">
-        <v>444</v>
+      <c r="F127" s="2" t="s">
+        <v>450</v>
       </c>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
@@ -6199,20 +6201,20 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>455</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
@@ -6220,20 +6222,20 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
@@ -6241,20 +6243,20 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
@@ -6262,20 +6264,22 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E131" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="F131" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E131" s="2"/>
-      <c r="F131" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
@@ -6283,22 +6287,22 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="D132" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="C132" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>473</v>
+      <c r="F132" s="4" t="s">
+        <v>682</v>
       </c>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
@@ -6306,22 +6310,20 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E133" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="F133" s="4" t="s">
-        <v>689</v>
+      <c r="E133" s="2"/>
+      <c r="F133" s="1" t="s">
+        <v>693</v>
       </c>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
@@ -6329,20 +6331,22 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E134" s="2"/>
-      <c r="F134" s="1" t="s">
-        <v>700</v>
+      <c r="E134" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>477</v>
       </c>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
@@ -6350,22 +6354,20 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" s="2" t="s">
         <v>481</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="F135" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
@@ -6373,20 +6375,20 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
@@ -6394,20 +6396,22 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E137" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="F137" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E137" s="2"/>
-      <c r="F137" s="2" t="s">
-        <v>492</v>
       </c>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
@@ -6415,22 +6419,20 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C138" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="D138" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" s="2" t="s">
         <v>494</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>497</v>
       </c>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
@@ -6438,20 +6440,20 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
@@ -6459,20 +6461,22 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E140" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B140" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E140" s="2"/>
-      <c r="F140" s="2" t="s">
-        <v>505</v>
+      <c r="F140" s="4" t="s">
+        <v>683</v>
       </c>
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
@@ -6480,22 +6484,20 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>690</v>
       </c>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
@@ -6503,20 +6505,20 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
-        <v>510</v>
+        <v>18</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E142" s="2"/>
-      <c r="F142" s="2" t="s">
-        <v>513</v>
+      <c r="F142" s="4" t="s">
+        <v>684</v>
       </c>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
@@ -6527,17 +6529,17 @@
         <v>18</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" s="4" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
@@ -6548,17 +6550,17 @@
         <v>18</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" s="4" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
@@ -6566,20 +6568,22 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
-        <v>18</v>
+        <v>513</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E145" s="2"/>
-      <c r="F145" s="4" t="s">
-        <v>691</v>
+      <c r="E145" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="F145" s="6" t="s">
+        <v>517</v>
       </c>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
@@ -6587,22 +6591,22 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
@@ -6610,22 +6614,22 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="B147" s="2" t="s">
-        <v>525</v>
-      </c>
       <c r="C147" s="2" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
@@ -6633,22 +6637,20 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="F148" s="6" t="s">
-        <v>524</v>
+        <v>159</v>
+      </c>
+      <c r="E148" s="2"/>
+      <c r="F148" s="1" t="s">
+        <v>694</v>
       </c>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
@@ -6656,20 +6658,20 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>164</v>
+        <v>12</v>
       </c>
       <c r="E149" s="2"/>
-      <c r="F149" s="1" t="s">
-        <v>701</v>
+      <c r="F149" s="2" t="s">
+        <v>528</v>
       </c>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
@@ -6677,20 +6679,20 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>532</v>
+        <v>359</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E150" s="2"/>
-      <c r="F150" s="2" t="s">
-        <v>535</v>
+      <c r="F150" s="6" t="s">
+        <v>362</v>
       </c>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
@@ -6698,20 +6700,20 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
-        <v>364</v>
+        <v>531</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" s="6" t="s">
-        <v>367</v>
+        <v>534</v>
       </c>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
@@ -6719,20 +6721,20 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" s="6" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
@@ -6740,20 +6742,20 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>543</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" s="6" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
@@ -6761,20 +6763,20 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" s="6" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
@@ -6782,20 +6784,20 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" s="6" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
@@ -6803,20 +6805,20 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C156" s="2" t="s">
         <v>546</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" s="6" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
@@ -6824,20 +6826,20 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>546</v>
+        <v>381</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" s="6" t="s">
-        <v>549</v>
+        <v>384</v>
       </c>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
@@ -6845,20 +6847,20 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
-        <v>386</v>
+        <v>549</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" s="6" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
@@ -6866,20 +6868,20 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" s="6" t="s">
-        <v>389</v>
+        <v>554</v>
       </c>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
@@ -6887,20 +6889,20 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>556</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>560</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" s="6" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
@@ -6908,20 +6910,20 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E161" s="2"/>
-      <c r="F161" s="6" t="s">
-        <v>561</v>
+      <c r="F161" s="2" t="s">
+        <v>560</v>
       </c>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
@@ -6929,20 +6931,20 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
@@ -6950,20 +6952,22 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E163" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="F163" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E163" s="2"/>
-      <c r="F163" s="2" t="s">
-        <v>571</v>
       </c>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
@@ -6971,22 +6975,20 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
-        <v>572</v>
+        <v>344</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E164" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="F164" s="2" t="s">
-        <v>576</v>
+      <c r="E164" s="2"/>
+      <c r="F164" s="6" t="s">
+        <v>347</v>
       </c>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
@@ -6994,20 +6996,20 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" s="6" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
@@ -7015,20 +7017,20 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
-        <v>349</v>
+        <v>574</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>580</v>
+        <v>397</v>
+      </c>
+      <c r="C166" t="s">
+        <v>398</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E166" s="2"/>
-      <c r="F166" s="6" t="s">
-        <v>352</v>
+      <c r="F166" s="2" t="s">
+        <v>577</v>
       </c>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
@@ -7036,96 +7038,98 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
-        <v>581</v>
+        <v>170</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C167" s="2"/>
+        <v>575</v>
+      </c>
+      <c r="C167" t="s">
+        <v>576</v>
+      </c>
       <c r="D167" s="2" t="s">
-        <v>12</v>
+        <v>173</v>
       </c>
       <c r="E167" s="2"/>
-      <c r="F167" s="2" t="s">
-        <v>584</v>
-      </c>
+      <c r="F167" s="2"/>
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
       <c r="I167" s="2"/>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
-        <v>175</v>
+        <v>578</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="C168" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>695</v>
+      </c>
       <c r="D168" s="2" t="s">
-        <v>178</v>
+        <v>12</v>
       </c>
       <c r="E168" s="2"/>
-      <c r="F168" s="2"/>
-      <c r="G168" s="2"/>
+      <c r="F168" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>690</v>
+      </c>
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" s="2" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>12</v>
+        <v>159</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" s="4" t="s">
-        <v>692</v>
-      </c>
-      <c r="G169" s="1" t="s">
-        <v>697</v>
-      </c>
+        <v>686</v>
+      </c>
+      <c r="G169" s="2"/>
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>703</v>
+        <v>584</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>164</v>
+        <v>585</v>
       </c>
       <c r="E170" s="2"/>
-      <c r="F170" s="4" t="s">
-        <v>693</v>
-      </c>
+      <c r="F170" s="2"/>
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
       <c r="I170" s="2"/>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
@@ -7135,16 +7139,16 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="C172" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B172" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="D172" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
@@ -7154,16 +7158,16 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
@@ -7173,16 +7177,16 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
@@ -7192,16 +7196,16 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
@@ -7211,16 +7215,16 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
@@ -7230,16 +7234,16 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
@@ -7249,16 +7253,16 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
@@ -7268,16 +7272,16 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
@@ -7287,16 +7291,16 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
@@ -7306,16 +7310,16 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
@@ -7325,16 +7329,16 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
@@ -7344,16 +7348,16 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" s="2" t="s">
-        <v>589</v>
+        <v>697</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
@@ -7363,16 +7367,16 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
@@ -7382,16 +7386,16 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
-        <v>704</v>
+        <v>582</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>620</v>
+        <v>698</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
@@ -7401,16 +7405,16 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
@@ -7420,16 +7424,16 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
@@ -7439,16 +7443,16 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
@@ -7458,16 +7462,16 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
@@ -7477,16 +7481,16 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
@@ -7496,16 +7500,16 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
@@ -7515,16 +7519,16 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
@@ -7534,16 +7538,16 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" s="2"/>
@@ -7553,16 +7557,16 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E194" s="2"/>
       <c r="F194" s="2"/>
@@ -7572,16 +7576,16 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
@@ -7591,39 +7595,41 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
-        <v>589</v>
+        <v>625</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>592</v>
+        <v>159</v>
       </c>
       <c r="E196" s="2"/>
-      <c r="F196" s="2"/>
+      <c r="F196" s="2" t="s">
+        <v>627</v>
+      </c>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
       <c r="I196" s="2"/>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E197" s="2"/>
-      <c r="F197" s="2" t="s">
-        <v>634</v>
+      <c r="F197" s="4" t="s">
+        <v>687</v>
       </c>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
@@ -7631,20 +7637,20 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E198" s="2"/>
       <c r="F198" s="4" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
@@ -7652,37 +7658,35 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
-        <v>637</v>
+        <v>170</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E199" s="2"/>
-      <c r="F199" s="4" t="s">
-        <v>695</v>
-      </c>
+      <c r="F199" s="2"/>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
       <c r="I199" s="2"/>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
@@ -7692,16 +7696,16 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E201" s="2"/>
       <c r="F201" s="2"/>
@@ -7711,16 +7715,16 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
@@ -7730,16 +7734,16 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E203" s="2"/>
       <c r="F203" s="2"/>
@@ -7749,16 +7753,16 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>723</v>
+        <v>638</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E204" s="2"/>
       <c r="F204" s="2"/>
@@ -7768,16 +7772,16 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E205" s="2"/>
       <c r="F205" s="2"/>
@@ -7787,16 +7791,16 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E206" s="2"/>
       <c r="F206" s="2"/>
@@ -7806,16 +7810,16 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E207" s="2"/>
       <c r="F207" s="2"/>
@@ -7825,16 +7829,16 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E208" s="2"/>
       <c r="F208" s="2"/>
@@ -7844,16 +7848,16 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" s="2"/>
@@ -7863,16 +7867,16 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E210" s="2"/>
       <c r="F210" s="2"/>
@@ -7882,16 +7886,16 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" s="2"/>
@@ -7901,16 +7905,16 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" s="2"/>
@@ -7920,16 +7924,16 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A213" s="2" t="s">
-        <v>175</v>
+        <v>655</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>178</v>
+        <v>655</v>
       </c>
       <c r="E213" s="2"/>
       <c r="F213" s="2"/>
@@ -7939,16 +7943,16 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="E214" s="2"/>
       <c r="F214" s="2"/>
@@ -7958,16 +7962,16 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="E215" s="2"/>
       <c r="F215" s="2"/>
@@ -7977,16 +7981,16 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="B216" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="B216" s="2" t="s">
-        <v>667</v>
-      </c>
       <c r="C216" s="2" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="E216" s="2"/>
       <c r="F216" s="2"/>
@@ -7996,16 +8000,16 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
-        <v>662</v>
+        <v>582</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>662</v>
+        <v>585</v>
       </c>
       <c r="E217" s="2"/>
       <c r="F217" s="2"/>
@@ -8015,16 +8019,16 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E218" s="2"/>
       <c r="F218" s="2"/>
@@ -8034,16 +8038,16 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E219" s="2"/>
       <c r="F219" s="2"/>
@@ -8052,250 +8056,234 @@
       <c r="I219" s="2"/>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A220" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="E220" s="2"/>
-      <c r="F220" s="2"/>
-      <c r="G220" s="2"/>
-      <c r="H220" s="2"/>
-      <c r="I220" s="2"/>
+      <c r="A220" t="s">
+        <v>582</v>
+      </c>
+      <c r="B220" t="s">
+        <v>717</v>
+      </c>
+      <c r="C220" t="str">
+        <f>VLOOKUP(B220,Sheet1!A:B,2,FALSE)</f>
+        <v>x=9.25, y=80.82</v>
+      </c>
+      <c r="D220" t="s">
+        <v>585</v>
+      </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B221" t="s">
-        <v>724</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>740</v>
+        <v>718</v>
+      </c>
+      <c r="C221" t="str">
+        <f>VLOOKUP(B221,Sheet1!A:B,2,FALSE)</f>
+        <v>x=79.37, y=63.15</v>
       </c>
       <c r="D221" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B222" t="s">
-        <v>725</v>
-      </c>
-      <c r="C222" t="s">
-        <v>741</v>
+        <v>719</v>
+      </c>
+      <c r="C222" t="str">
+        <f>VLOOKUP(B222,Sheet1!A:B,2,FALSE)</f>
+        <v>x=26.03, y=86.14</v>
       </c>
       <c r="D222" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B223" t="s">
-        <v>726</v>
-      </c>
-      <c r="C223" t="s">
-        <v>742</v>
+        <v>720</v>
+      </c>
+      <c r="C223" t="str">
+        <f>VLOOKUP(B223,Sheet1!A:B,2,FALSE)</f>
+        <v>x=24.49, y=86.21</v>
       </c>
       <c r="D223" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B224" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="C224" t="str">
         <f>VLOOKUP(B224,Sheet1!A:B,2,FALSE)</f>
-        <v>x=24.49, y=86.21</v>
+        <v>x=67.22, y=86.14</v>
       </c>
       <c r="D224" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>589</v>
+        <v>170</v>
       </c>
       <c r="B225" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C225" t="str">
         <f>VLOOKUP(B225,Sheet1!A:B,2,FALSE)</f>
-        <v>x=67.22, y=86.14</v>
+        <v>x=10.90, y=63.07</v>
       </c>
       <c r="D225" t="s">
-        <v>592</v>
+        <v>173</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B226" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="C226" t="str">
         <f>VLOOKUP(B226,Sheet1!A:B,2,FALSE)</f>
-        <v>x=10.90, y=63.07</v>
+        <v>x=12.37, y=66.24</v>
       </c>
       <c r="D226" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B227" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="C227" t="str">
         <f>VLOOKUP(B227,Sheet1!A:B,2,FALSE)</f>
-        <v>x=12.37, y=66.24</v>
+        <v>x=10.79, y=66.31</v>
       </c>
       <c r="D227" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B228" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C228" t="str">
         <f>VLOOKUP(B228,Sheet1!A:B,2,FALSE)</f>
-        <v>x=10.79, y=66.31</v>
+        <v>x=38.14, y=94.04</v>
       </c>
       <c r="D228" t="s">
-        <v>178</v>
+        <v>173</v>
+      </c>
+      <c r="E228" t="s">
+        <v>726</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B229" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="C229" t="str">
         <f>VLOOKUP(B229,Sheet1!A:B,2,FALSE)</f>
-        <v>x=38.14, y=94.04</v>
+        <v>x=39.98, y=85.70</v>
       </c>
       <c r="D229" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E229" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A230" t="s">
-        <v>175</v>
+      <c r="A230" s="7" t="s">
+        <v>729</v>
       </c>
       <c r="B230" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="C230" t="str">
         <f>VLOOKUP(B230,Sheet1!A:B,2,FALSE)</f>
-        <v>x=39.98, y=85.70</v>
+        <v>x=68.76, y=86.28</v>
       </c>
       <c r="D230" t="s">
-        <v>178</v>
-      </c>
-      <c r="E230" t="s">
-        <v>735</v>
+        <v>585</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A231" s="7" t="s">
-        <v>736</v>
+      <c r="A231" t="s">
+        <v>582</v>
       </c>
       <c r="B231" t="s">
-        <v>737</v>
+        <v>721</v>
       </c>
       <c r="C231" t="str">
         <f>VLOOKUP(B231,Sheet1!A:B,2,FALSE)</f>
-        <v>x=68.76, y=86.28</v>
+        <v>x=67.22, y=86.14</v>
       </c>
       <c r="D231" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B232" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C232" t="str">
         <f>VLOOKUP(B232,Sheet1!A:B,2,FALSE)</f>
-        <v>x=67.22, y=86.14</v>
+        <v>x=71.99, y=86.35</v>
       </c>
       <c r="D232" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B233" t="s">
-        <v>738</v>
+        <v>718</v>
       </c>
       <c r="C233" t="str">
         <f>VLOOKUP(B233,Sheet1!A:B,2,FALSE)</f>
-        <v>x=71.99, y=86.35</v>
+        <v>x=79.37, y=63.15</v>
       </c>
       <c r="D233" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A234" t="s">
-        <v>589</v>
-      </c>
-      <c r="B234" t="s">
-        <v>725</v>
-      </c>
-      <c r="C234" t="str">
-        <f>VLOOKUP(B234,Sheet1!A:B,2,FALSE)</f>
-        <v>x=79.37, y=63.15</v>
-      </c>
-      <c r="D234" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G221:G1048576">
+  <conditionalFormatting sqref="G220:G1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="F16" r:id="rId1" xr:uid="{4C163042-8F5E-3D4F-B452-365982B83168}"/>
-    <hyperlink ref="F39" r:id="rId2" xr:uid="{8293602F-A51D-154A-B140-3E5A5814164B}"/>
-    <hyperlink ref="G169" r:id="rId3" xr:uid="{82236511-9499-BF47-9958-479B49885F8F}"/>
-    <hyperlink ref="F149" r:id="rId4" xr:uid="{7D4CF0E8-8FEC-7E47-9B63-24155BF788C4}"/>
-    <hyperlink ref="F134" r:id="rId5" xr:uid="{C971D10A-C024-DF40-8291-A11326D3B695}"/>
-    <hyperlink ref="F120" r:id="rId6" xr:uid="{9316BA32-0173-3B4C-9AC0-FD8A265D7311}"/>
-    <hyperlink ref="F121" r:id="rId7" xr:uid="{5461B8AF-9676-1447-937A-E7F9C44966D9}"/>
-    <hyperlink ref="F122" r:id="rId8" xr:uid="{68D7C769-E497-3A47-89CF-55E9EAB9E9EE}"/>
+    <hyperlink ref="F16" r:id="rId1" xr:uid="{07AF991F-F6C6-C44A-A751-5A2EA2944D41}"/>
+    <hyperlink ref="F39" r:id="rId2" xr:uid="{F041CF9A-13DD-624A-9B00-2D2AFA06DE44}"/>
+    <hyperlink ref="G168" r:id="rId3" xr:uid="{015B9B0A-F36B-434C-B71F-52D73CA54715}"/>
+    <hyperlink ref="F148" r:id="rId4" xr:uid="{B6CF26C8-F003-564C-91E1-424AA63AE620}"/>
+    <hyperlink ref="F133" r:id="rId5" xr:uid="{F16986EA-EEF8-E344-A461-8D16F1B0F343}"/>
+    <hyperlink ref="F119" r:id="rId6" xr:uid="{CABFB8E0-E217-3E47-A432-418BECF77264}"/>
+    <hyperlink ref="F120" r:id="rId7" xr:uid="{84CA1D64-C468-1049-94C5-C3897EF060BD}"/>
+    <hyperlink ref="F121" r:id="rId8" xr:uid="{042437EF-DB86-6F48-8CA6-C97CD720C3EB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8312,7 +8300,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
@@ -8328,18 +8316,18 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" t="s">
         <v>75</v>
-      </c>
-      <c r="B3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s">
         <v>79</v>
-      </c>
-      <c r="B4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -8352,50 +8340,50 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
         <v>83</v>
-      </c>
-      <c r="B6" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="B7" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="B8" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="B9" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B10" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="B11" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -8416,10 +8404,10 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="B14" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -8440,18 +8428,18 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B17" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -8464,10 +8452,10 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
         <v>67</v>
-      </c>
-      <c r="B20" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -8496,10 +8484,10 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" t="s">
         <v>71</v>
-      </c>
-      <c r="B24" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -8512,18 +8500,18 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -8536,26 +8524,26 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
@@ -8568,10 +8556,10 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -8584,2508 +8572,2508 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="B35" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B36" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B37" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B38" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B39" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="B40" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B41" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="B43" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B44" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="B45" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="B46" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B47" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B48" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B49" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B50" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B51" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B52" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B53" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B54" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B55" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B56" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B57" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B58" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B59" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B60" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="B61" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B62" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B63" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B64" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B65" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="B66" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="B67" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B68" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="B69" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B70" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B71" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B72" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B73" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="B74" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B75" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="B76" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="B77" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B78" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B79" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="B80" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B81" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="B82" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B83" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B84" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="B85" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="B86" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="B87" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="B88" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="B89" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="B90" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="B91" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="B92" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B93" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="B95" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="B96" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="B97" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="B98" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="B99" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="B100" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="B101" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="B102" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="B103" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="B104" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="B105" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="B106" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="B107" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="B108" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="B109" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="B110" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B111" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="B112" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="B113" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="B114" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="B115" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="B116" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B117" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="B118" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B119" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="B120" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="B121" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="B122" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="B123" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
       <c r="B124" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="B125" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="B126" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="B127" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B128" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="B129" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="B130" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>850</v>
+        <v>843</v>
       </c>
       <c r="B131" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="B132" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="B133" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="B134" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="B135" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="B136" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="B137" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B138" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="B139" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B140" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="B141" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="B142" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="B143" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="B144" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="B145" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="B146" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="B147" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B148" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B149" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B150" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="B151" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
       <c r="B152" t="s">
-        <v>877</v>
+        <v>870</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>878</v>
+        <v>871</v>
       </c>
       <c r="B153" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="B154" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
       <c r="B155" t="s">
-        <v>883</v>
+        <v>876</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="B156" t="s">
-        <v>885</v>
+        <v>878</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B157" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B158" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B159" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B160" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B161" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B162" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="B163" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B164" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>887</v>
+        <v>880</v>
       </c>
       <c r="B165" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B166" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B167" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="B168" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B169" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B170" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="B171" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B172" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="B173" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B174" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="B175" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B176" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B177" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="B178" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B179" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B180" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B181" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="B182" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B183" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B184" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B185" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B186" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B187" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="B188" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B189" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="B190" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B191" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="B192" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B193" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B194" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B195" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B196" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="B197" t="s">
-        <v>892</v>
+        <v>885</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="B198" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="B199" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="B200" t="s">
-        <v>894</v>
+        <v>887</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="B201" t="s">
-        <v>895</v>
+        <v>888</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="B202" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="B203" t="s">
-        <v>897</v>
+        <v>890</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>898</v>
+        <v>891</v>
       </c>
       <c r="B204" t="s">
-        <v>899</v>
+        <v>892</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="B205" t="s">
-        <v>900</v>
+        <v>893</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>901</v>
+        <v>894</v>
       </c>
       <c r="B206" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="B207" t="s">
-        <v>904</v>
+        <v>897</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>905</v>
+        <v>898</v>
       </c>
       <c r="B208" t="s">
-        <v>906</v>
+        <v>899</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B209" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="B210" t="s">
-        <v>908</v>
+        <v>901</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B211" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="B212" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="B213" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
       <c r="B214" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
       <c r="B215" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="B216" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="B217" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>919</v>
+        <v>912</v>
       </c>
       <c r="B218" t="s">
-        <v>920</v>
+        <v>913</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B219" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B220" t="s">
-        <v>922</v>
+        <v>915</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B221" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>923</v>
+        <v>916</v>
       </c>
       <c r="B222" t="s">
-        <v>924</v>
+        <v>917</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>925</v>
+        <v>918</v>
       </c>
       <c r="B223" t="s">
-        <v>926</v>
+        <v>919</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="B224" t="s">
-        <v>928</v>
+        <v>921</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>929</v>
+        <v>922</v>
       </c>
       <c r="B225" t="s">
-        <v>930</v>
+        <v>923</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>931</v>
+        <v>924</v>
       </c>
       <c r="B226" t="s">
-        <v>932</v>
+        <v>925</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>933</v>
+        <v>926</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>934</v>
+        <v>927</v>
       </c>
       <c r="B228" t="s">
-        <v>935</v>
+        <v>928</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="B229" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>936</v>
+        <v>929</v>
       </c>
       <c r="B230" t="s">
-        <v>937</v>
+        <v>930</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B231" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>938</v>
+        <v>931</v>
       </c>
       <c r="B232" t="s">
-        <v>939</v>
+        <v>932</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>940</v>
+        <v>933</v>
       </c>
       <c r="B233" t="s">
-        <v>941</v>
+        <v>934</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>942</v>
+        <v>935</v>
       </c>
       <c r="B234" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
       <c r="B235" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
       <c r="B236" t="s">
-        <v>947</v>
+        <v>940</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B237" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="B238" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B239" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B240" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="B241" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>948</v>
+        <v>941</v>
       </c>
       <c r="B242" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>949</v>
+        <v>942</v>
       </c>
       <c r="B243" t="s">
-        <v>950</v>
+        <v>943</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="B244" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>951</v>
+        <v>944</v>
       </c>
       <c r="B245" t="s">
-        <v>952</v>
+        <v>945</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>953</v>
+        <v>946</v>
       </c>
       <c r="B246" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B247" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B248" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B249" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="B250" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="B251" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>954</v>
+        <v>947</v>
       </c>
       <c r="B252" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="B253" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="B254" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>955</v>
+        <v>948</v>
       </c>
       <c r="B255" t="s">
-        <v>956</v>
+        <v>949</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="B256" t="s">
-        <v>957</v>
+        <v>950</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>958</v>
+        <v>951</v>
       </c>
       <c r="B257" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="B258" t="s">
-        <v>961</v>
+        <v>954</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="B259" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="B260" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="B261" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="B262" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="B263" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="B264" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="B265" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="B266" t="s">
-        <v>963</v>
+        <v>956</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
       <c r="B267" t="s">
-        <v>965</v>
+        <v>958</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="B268" t="s">
-        <v>966</v>
+        <v>959</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>967</v>
+        <v>960</v>
       </c>
       <c r="B269" t="s">
-        <v>968</v>
+        <v>961</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="B270" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="B271" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="B272" t="s">
-        <v>972</v>
+        <v>965</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="B273" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="B274" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="B275" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B276" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="B277" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="B278" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="B279" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="B280" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="B281" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="B282" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B283" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
       <c r="B284" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="B285" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>977</v>
+        <v>970</v>
       </c>
       <c r="B286" t="s">
-        <v>978</v>
+        <v>971</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="B287" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>979</v>
+        <v>972</v>
       </c>
       <c r="B288" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="B289" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B290" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="B291" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B292" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="B293" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="B294" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="B295" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="B296" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="B297" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="B298" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="B299" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="B300" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="B301" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="B302" t="s">
-        <v>986</v>
+        <v>979</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="B303" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="B304" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>989</v>
+        <v>982</v>
       </c>
       <c r="B305" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="B306" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="B307" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="B308" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="B309" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="B310" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="B311" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="B312" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="B313" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B314" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="B315" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="B316" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>993</v>
+        <v>986</v>
       </c>
       <c r="B317" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="B318" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="B319" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="B320" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="B321" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="B322" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B323" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="B324" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="B325" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="B326" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="B327" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="B328" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="B329" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="B330" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="B331" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="B332" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B333" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="B334" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="B335" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="B336" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="B337" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="B338" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="B339" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="B340" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="B341" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="B342" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="B343" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="B344" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B345" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="B346" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="B347" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="B348" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE073FAD-450F-0A4B-AB22-EC2815E5F68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66138E5-61B7-7744-A7AA-F866E6D5D88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-34820" yWindow="2020" windowWidth="27240" windowHeight="16440" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="995">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1826" uniqueCount="1003">
   <si>
     <t>Household Name</t>
   </si>
@@ -81,9 +81,6 @@
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000mWKCtYAO/view</t>
   </si>
   <si>
-    <t>Amy Koman</t>
-  </si>
-  <si>
     <t>A21</t>
   </si>
   <si>
@@ -138,9 +135,6 @@
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000mW63RYAS/view</t>
   </si>
   <si>
-    <t>Elisa Jaime</t>
-  </si>
-  <si>
     <t>A11</t>
   </si>
   <si>
@@ -150,9 +144,6 @@
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000mT0k9YAC/view</t>
   </si>
   <si>
-    <t>Amy Wood</t>
-  </si>
-  <si>
     <t>A24</t>
   </si>
   <si>
@@ -222,9 +213,6 @@
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000oiPfSYAU/view</t>
   </si>
   <si>
-    <t>Gary Levine + Larry Bloch</t>
-  </si>
-  <si>
     <t>A27</t>
   </si>
   <si>
@@ -546,9 +534,6 @@
     <t>x=35.21, y=65.88</t>
   </si>
   <si>
-    <t xml:space="preserve"> (Mike Cunningham)</t>
-  </si>
-  <si>
     <t>CB</t>
   </si>
   <si>
@@ -1245,9 +1230,6 @@
     <t>x=17.14, y=60.34</t>
   </si>
   <si>
-    <t>(purchase)</t>
-  </si>
-  <si>
     <t>Pacific Immunology</t>
   </si>
   <si>
@@ -1434,9 +1416,6 @@
     <t>x=15.38, y=80.53</t>
   </si>
   <si>
-    <t xml:space="preserve"> (now requesting E54 or near that area)</t>
-  </si>
-  <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000pdzeBYAQ/view</t>
   </si>
   <si>
@@ -1506,9 +1485,6 @@
     <t>x=76.21, y=71.70</t>
   </si>
   <si>
-    <t xml:space="preserve"> (would like to be on the right)</t>
-  </si>
-  <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qv4YqYAI/view</t>
   </si>
   <si>
@@ -1587,9 +1563,6 @@
     <t>x=15.49, y=86.21</t>
   </si>
   <si>
-    <t xml:space="preserve"> (Carla Taub)</t>
-  </si>
-  <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000rtSQ9YAM/view</t>
   </si>
   <si>
@@ -3022,6 +2995,57 @@
   </si>
   <si>
     <t>Shen + Saripelli</t>
+  </si>
+  <si>
+    <t>Amy + Bill Koman</t>
+  </si>
+  <si>
+    <t>x=50.55, y=55.39</t>
+  </si>
+  <si>
+    <t>Elisa Jaime + Lynda Kerr</t>
+  </si>
+  <si>
+    <t>Kerr Concert 2026 Tickets | Opportunity | Salesforce</t>
+  </si>
+  <si>
+    <t>Amy + Jim Wood</t>
+  </si>
+  <si>
+    <t>Gary Levine + Larry Bloch + Mitch Adler</t>
+  </si>
+  <si>
+    <t>Adler Concert 2026 Tickets | Opportunity | Salesforce</t>
+  </si>
+  <si>
+    <t>(Mike Cunningham)</t>
+  </si>
+  <si>
+    <t>Tafel Klaus Concert 2026 Tickets | Opportunity | Salesforce</t>
+  </si>
+  <si>
+    <t>x=56.90, y=93.53</t>
+  </si>
+  <si>
+    <t>(now requesting E54 or near that area)</t>
+  </si>
+  <si>
+    <t>(would like to be on the right)</t>
+  </si>
+  <si>
+    <t>(Carla Taub)</t>
+  </si>
+  <si>
+    <t>Theodora Polamalu</t>
+  </si>
+  <si>
+    <t>Sold Offline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Issue tickets to Michelle Kim at Michellekim2020@yahoo.com </t>
+  </si>
+  <si>
+    <t>Polamalu Concert 2026 Tickets | Opportunity | Salesforce</t>
   </si>
 </sst>
 </file>
@@ -3046,9 +3070,17 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -3056,17 +3088,13 @@
       <color rgb="FF467886"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3096,71 +3124,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3501,7 +3477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7894B4-148E-174D-AE8B-E6DE441B89B0}">
-  <dimension ref="A1:I233"/>
+  <dimension ref="A1:I234"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="54.6640625" customWidth="1"/>
@@ -3566,20 +3542,20 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -3587,20 +3563,20 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -3608,13 +3584,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>12</v>
@@ -3627,20 +3603,20 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>27</v>
+        <v>987</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -3648,20 +3624,20 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -3669,41 +3645,43 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>989</v>
+      </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>37</v>
+        <v>990</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -3711,20 +3689,20 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -3732,20 +3710,20 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -3753,20 +3731,20 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -3774,20 +3752,20 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -3795,20 +3773,20 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -3816,66 +3794,68 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>61</v>
+        <v>991</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H15" s="2"/>
+        <v>61</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>992</v>
+      </c>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>990</v>
+        <v>981</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="3" t="s">
-        <v>68</v>
+      <c r="F16" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -3883,20 +3863,20 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -3904,20 +3884,20 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -3925,20 +3905,20 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -3946,20 +3926,20 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>991</v>
+        <v>982</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -3967,72 +3947,72 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>992</v>
+        <v>983</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>993</v>
+        <v>984</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -4040,20 +4020,20 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -4061,20 +4041,20 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -4082,43 +4062,43 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>994</v>
+        <v>985</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
@@ -4126,20 +4106,20 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -4147,20 +4127,20 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -4168,20 +4148,20 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -4189,20 +4169,20 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -4210,20 +4190,20 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -4231,20 +4211,20 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E34" s="2"/>
-      <c r="F34" s="4" t="s">
-        <v>670</v>
+      <c r="F34" s="3" t="s">
+        <v>661</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -4252,20 +4232,20 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
@@ -4273,43 +4253,43 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
@@ -4317,43 +4297,43 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E38" s="2"/>
-      <c r="F38" s="4" t="s">
-        <v>671</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>155</v>
+      <c r="F38" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="F39" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -4361,16 +4341,16 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
@@ -4380,20 +4360,20 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E41" s="2"/>
-      <c r="F41" s="4" t="s">
-        <v>672</v>
+      <c r="F41" s="3" t="s">
+        <v>663</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -4401,19 +4381,19 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>169</v>
+        <v>993</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -4422,39 +4402,41 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>173</v>
+        <v>12</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
+      <c r="F43" s="1" t="s">
+        <v>994</v>
+      </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -4462,20 +4444,20 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -4483,20 +4465,20 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -4504,20 +4486,20 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -4525,20 +4507,20 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
@@ -4546,20 +4528,20 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -4567,20 +4549,20 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -4588,20 +4570,20 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
@@ -4609,20 +4591,20 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
@@ -4630,22 +4612,22 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -4653,20 +4635,20 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
@@ -4674,20 +4656,20 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
@@ -4695,20 +4677,20 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
@@ -4716,20 +4698,20 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="C57" t="s">
-        <v>732</v>
+        <v>682</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>723</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
@@ -4737,20 +4719,20 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
@@ -4758,20 +4740,20 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>235</v>
+        <v>995</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
@@ -4779,20 +4761,20 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
@@ -4800,20 +4782,20 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E61" s="2"/>
-      <c r="F61" s="4" t="s">
-        <v>673</v>
+      <c r="F61" s="3" t="s">
+        <v>664</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
@@ -4821,16 +4803,16 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
@@ -4840,16 +4822,16 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
@@ -4859,20 +4841,20 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
@@ -4880,13 +4862,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>12</v>
@@ -4899,20 +4881,20 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E66" s="2"/>
-      <c r="F66" s="4" t="s">
-        <v>674</v>
+      <c r="F66" s="3" t="s">
+        <v>665</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
@@ -4920,20 +4902,20 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E67" s="2"/>
-      <c r="F67" s="4" t="s">
-        <v>675</v>
+      <c r="F67" s="3" t="s">
+        <v>666</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
@@ -4941,20 +4923,20 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
@@ -4962,20 +4944,20 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>268</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
@@ -4983,20 +4965,20 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
@@ -5004,20 +4986,20 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
@@ -5025,20 +5007,20 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
@@ -5046,20 +5028,20 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E73" s="2"/>
-      <c r="F73" s="6" t="s">
-        <v>285</v>
+      <c r="F73" s="5" t="s">
+        <v>280</v>
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
@@ -5067,20 +5049,20 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>287</v>
-      </c>
       <c r="D74" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E74" s="2"/>
-      <c r="F74" s="6" t="s">
-        <v>285</v>
+      <c r="F74" s="5" t="s">
+        <v>280</v>
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
@@ -5088,20 +5070,20 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
@@ -5109,22 +5091,22 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -5132,20 +5114,20 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
@@ -5153,20 +5135,20 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
@@ -5174,20 +5156,20 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E79" s="2"/>
-      <c r="F79" s="4" t="s">
-        <v>676</v>
+      <c r="F79" s="3" t="s">
+        <v>667</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
@@ -5195,20 +5177,20 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E80" s="2"/>
-      <c r="F80" s="4" t="s">
-        <v>677</v>
+      <c r="F80" s="3" t="s">
+        <v>668</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
@@ -5216,20 +5198,20 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
@@ -5237,20 +5219,20 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
@@ -5258,20 +5240,20 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -5279,20 +5261,20 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E84" s="2"/>
-      <c r="F84" s="4" t="s">
-        <v>322</v>
+      <c r="F84" s="3" t="s">
+        <v>317</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
@@ -5300,20 +5282,20 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E85" s="2"/>
-      <c r="F85" s="6" t="s">
-        <v>329</v>
+      <c r="F85" s="5" t="s">
+        <v>324</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
@@ -5321,20 +5303,20 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>331</v>
-      </c>
       <c r="D86" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E86" s="2"/>
-      <c r="F86" s="6" t="s">
-        <v>329</v>
+      <c r="F86" s="5" t="s">
+        <v>324</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -5342,43 +5324,43 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E87" s="2"/>
-      <c r="F87" s="6" t="s">
-        <v>329</v>
+      <c r="F87" s="5" t="s">
+        <v>324</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -5386,20 +5368,20 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -5407,20 +5389,20 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E90" s="2"/>
-      <c r="F90" s="6" t="s">
-        <v>347</v>
+      <c r="F90" s="5" t="s">
+        <v>342</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -5428,20 +5410,20 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>349</v>
-      </c>
       <c r="D91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E91" s="2"/>
-      <c r="F91" s="6" t="s">
-        <v>347</v>
+      <c r="F91" s="5" t="s">
+        <v>342</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -5449,20 +5431,20 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E92" s="2"/>
-      <c r="F92" s="6" t="s">
-        <v>347</v>
+      <c r="F92" s="5" t="s">
+        <v>342</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -5470,20 +5452,20 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E93" s="2"/>
-      <c r="F93" s="6" t="s">
-        <v>347</v>
+      <c r="F93" s="5" t="s">
+        <v>342</v>
       </c>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -5491,20 +5473,20 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E94" s="2"/>
-      <c r="F94" s="6" t="s">
-        <v>347</v>
+      <c r="F94" s="5" t="s">
+        <v>342</v>
       </c>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -5512,20 +5494,20 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>357</v>
-      </c>
       <c r="C95" s="2" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E95" s="2"/>
-      <c r="F95" s="6" t="s">
-        <v>347</v>
+      <c r="F95" s="5" t="s">
+        <v>342</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -5533,20 +5515,20 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E96" s="2"/>
-      <c r="F96" s="6" t="s">
-        <v>362</v>
+      <c r="F96" s="5" t="s">
+        <v>357</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -5554,20 +5536,20 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E97" s="2"/>
-      <c r="F97" s="6" t="s">
-        <v>364</v>
+      <c r="F97" s="5" t="s">
+        <v>359</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
@@ -5575,20 +5557,20 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E98" s="2"/>
-      <c r="F98" s="6" t="s">
-        <v>364</v>
+      <c r="F98" s="5" t="s">
+        <v>359</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
@@ -5596,20 +5578,20 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>368</v>
-      </c>
       <c r="D99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E99" s="2"/>
-      <c r="F99" s="6" t="s">
-        <v>364</v>
+      <c r="F99" s="5" t="s">
+        <v>359</v>
       </c>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
@@ -5617,20 +5599,20 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
@@ -5638,20 +5620,20 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E101" s="2"/>
-      <c r="F101" s="6" t="s">
-        <v>376</v>
+      <c r="F101" s="5" t="s">
+        <v>371</v>
       </c>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
@@ -5659,20 +5641,20 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>378</v>
-      </c>
       <c r="D102" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E102" s="2"/>
-      <c r="F102" s="6" t="s">
-        <v>376</v>
+      <c r="F102" s="5" t="s">
+        <v>371</v>
       </c>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
@@ -5680,20 +5662,20 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E103" s="2"/>
-      <c r="F103" s="6" t="s">
-        <v>376</v>
+      <c r="F103" s="5" t="s">
+        <v>371</v>
       </c>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -5701,20 +5683,20 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E104" s="2"/>
-      <c r="F104" s="6" t="s">
-        <v>384</v>
+      <c r="F104" s="5" t="s">
+        <v>379</v>
       </c>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -5722,20 +5704,20 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>386</v>
-      </c>
       <c r="D105" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E105" s="2"/>
-      <c r="F105" s="6" t="s">
-        <v>384</v>
+      <c r="F105" s="5" t="s">
+        <v>379</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -5743,20 +5725,20 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E106" s="2"/>
-      <c r="F106" s="6" t="s">
-        <v>390</v>
+      <c r="F106" s="5" t="s">
+        <v>385</v>
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -5764,20 +5746,20 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>392</v>
-      </c>
       <c r="D107" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E107" s="2"/>
-      <c r="F107" s="6" t="s">
-        <v>390</v>
+      <c r="F107" s="5" t="s">
+        <v>385</v>
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
@@ -5785,20 +5767,20 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E108" s="2"/>
-      <c r="F108" s="4" t="s">
-        <v>678</v>
+      <c r="F108" s="3" t="s">
+        <v>669</v>
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
@@ -5806,22 +5788,20 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>401</v>
-      </c>
       <c r="D109" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="F109" s="6" t="s">
-        <v>399</v>
+        <v>155</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" s="5" t="s">
+        <v>394</v>
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
@@ -5829,20 +5809,20 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E110" s="2"/>
-      <c r="F110" s="4" t="s">
-        <v>679</v>
+      <c r="F110" s="3" t="s">
+        <v>670</v>
       </c>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
@@ -5850,20 +5830,20 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E111" s="2"/>
-      <c r="F111" s="4" t="s">
-        <v>680</v>
+      <c r="F111" s="3" t="s">
+        <v>671</v>
       </c>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
@@ -5871,20 +5851,20 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E112" s="2"/>
-      <c r="F112" s="4" t="s">
-        <v>680</v>
+      <c r="F112" s="3" t="s">
+        <v>671</v>
       </c>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
@@ -5892,13 +5872,13 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>12</v>
@@ -5911,13 +5891,13 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>12</v>
@@ -5930,13 +5910,13 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C115" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>417</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>12</v>
@@ -5949,20 +5929,20 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E116" s="2"/>
-      <c r="F116" s="4" t="s">
-        <v>681</v>
+      <c r="F116" s="3" t="s">
+        <v>672</v>
       </c>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
@@ -5970,20 +5950,20 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" s="2" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
@@ -5991,20 +5971,20 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
@@ -6012,20 +5992,20 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="1" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
@@ -6033,20 +6013,20 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="1" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
@@ -6054,20 +6034,20 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C121" s="2" t="s">
         <v>428</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>434</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="1" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
@@ -6075,20 +6055,20 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E122" s="2"/>
-      <c r="F122" s="6" t="s">
-        <v>438</v>
+      <c r="F122" s="5" t="s">
+        <v>432</v>
       </c>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
@@ -6096,20 +6076,20 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E123" s="2"/>
-      <c r="F123" s="6" t="s">
-        <v>438</v>
+      <c r="F123" s="5" t="s">
+        <v>432</v>
       </c>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
@@ -6117,20 +6097,20 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>441</v>
-      </c>
       <c r="C124" s="2" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E124" s="2"/>
-      <c r="F124" s="6" t="s">
-        <v>438</v>
+      <c r="F124" s="5" t="s">
+        <v>432</v>
       </c>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
@@ -6138,20 +6118,20 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E125" s="2"/>
-      <c r="F125" s="6" t="s">
-        <v>438</v>
+      <c r="F125" s="5" t="s">
+        <v>432</v>
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
@@ -6159,20 +6139,20 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E126" s="2"/>
-      <c r="F126" s="6" t="s">
-        <v>438</v>
+      <c r="F126" s="5" t="s">
+        <v>432</v>
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
@@ -6180,20 +6160,20 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
@@ -6201,20 +6181,20 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
@@ -6222,20 +6202,20 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" s="2" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
@@ -6243,20 +6223,20 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
@@ -6264,22 +6244,22 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>465</v>
+        <v>996</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
@@ -6287,22 +6267,22 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="F132" s="4" t="s">
-        <v>682</v>
+        <v>463</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>673</v>
       </c>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
@@ -6310,20 +6290,20 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="1" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
@@ -6331,22 +6311,22 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E134" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="F134" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>477</v>
       </c>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
@@ -6354,20 +6334,20 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
@@ -6375,20 +6355,20 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
@@ -6396,22 +6376,22 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>489</v>
+        <v>997</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
@@ -6419,20 +6399,20 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" s="2" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
@@ -6440,20 +6420,20 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" s="2" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
@@ -6461,22 +6441,22 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="F140" s="4" t="s">
-        <v>683</v>
+        <v>494</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>674</v>
       </c>
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
@@ -6484,20 +6464,20 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
@@ -6505,20 +6485,20 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E142" s="2"/>
-      <c r="F142" s="4" t="s">
-        <v>684</v>
+      <c r="F142" s="3" t="s">
+        <v>675</v>
       </c>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
@@ -6526,20 +6506,20 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E143" s="2"/>
-      <c r="F143" s="4" t="s">
-        <v>684</v>
+      <c r="F143" s="3" t="s">
+        <v>675</v>
       </c>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
@@ -6547,20 +6527,20 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E144" s="2"/>
-      <c r="F144" s="4" t="s">
-        <v>684</v>
+      <c r="F144" s="3" t="s">
+        <v>675</v>
       </c>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
@@ -6568,22 +6548,22 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="F145" s="6" t="s">
-        <v>517</v>
+        <v>998</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>508</v>
       </c>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
@@ -6591,22 +6571,22 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="F146" s="6" t="s">
-        <v>517</v>
+        <v>998</v>
+      </c>
+      <c r="F146" s="5" t="s">
+        <v>508</v>
       </c>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
@@ -6614,22 +6594,22 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="F147" s="6" t="s">
-        <v>517</v>
+        <v>998</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>508</v>
       </c>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
@@ -6637,20 +6617,20 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="1" t="s">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
@@ -6658,20 +6638,20 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
@@ -6679,20 +6659,20 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E150" s="2"/>
-      <c r="F150" s="6" t="s">
-        <v>362</v>
+      <c r="F150" s="5" t="s">
+        <v>357</v>
       </c>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
@@ -6700,20 +6680,20 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E151" s="2"/>
-      <c r="F151" s="6" t="s">
-        <v>534</v>
+      <c r="F151" s="5" t="s">
+        <v>525</v>
       </c>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
@@ -6721,20 +6701,20 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E152" s="2"/>
-      <c r="F152" s="6" t="s">
-        <v>534</v>
+      <c r="F152" s="5" t="s">
+        <v>525</v>
       </c>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
@@ -6742,20 +6722,20 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E153" s="2"/>
-      <c r="F153" s="6" t="s">
-        <v>534</v>
+      <c r="F153" s="5" t="s">
+        <v>525</v>
       </c>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
@@ -6763,20 +6743,20 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E154" s="2"/>
-      <c r="F154" s="6" t="s">
-        <v>542</v>
+      <c r="F154" s="5" t="s">
+        <v>533</v>
       </c>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
@@ -6784,20 +6764,20 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E155" s="2"/>
-      <c r="F155" s="6" t="s">
-        <v>542</v>
+      <c r="F155" s="5" t="s">
+        <v>533</v>
       </c>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
@@ -6805,20 +6785,20 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E156" s="2"/>
-      <c r="F156" s="6" t="s">
-        <v>542</v>
+      <c r="F156" s="5" t="s">
+        <v>533</v>
       </c>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
@@ -6826,20 +6806,20 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E157" s="2"/>
-      <c r="F157" s="6" t="s">
-        <v>384</v>
+      <c r="F157" s="5" t="s">
+        <v>379</v>
       </c>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
@@ -6847,20 +6827,20 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E158" s="2"/>
-      <c r="F158" s="6" t="s">
-        <v>384</v>
+      <c r="F158" s="5" t="s">
+        <v>379</v>
       </c>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
@@ -6868,20 +6848,20 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E159" s="2"/>
-      <c r="F159" s="6" t="s">
-        <v>554</v>
+      <c r="F159" s="5" t="s">
+        <v>545</v>
       </c>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
@@ -6889,20 +6869,20 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E160" s="2"/>
-      <c r="F160" s="6" t="s">
-        <v>554</v>
+      <c r="F160" s="5" t="s">
+        <v>545</v>
       </c>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
@@ -6910,20 +6890,20 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" s="2" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
@@ -6931,20 +6911,20 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" s="2" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
@@ -6952,22 +6932,22 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
@@ -6975,20 +6955,20 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E164" s="2"/>
-      <c r="F164" s="6" t="s">
-        <v>347</v>
+      <c r="F164" s="5" t="s">
+        <v>342</v>
       </c>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
@@ -6996,20 +6976,20 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E165" s="2"/>
-      <c r="F165" s="6" t="s">
-        <v>347</v>
+      <c r="F165" s="5" t="s">
+        <v>342</v>
       </c>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
@@ -7017,20 +6997,20 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="C166" t="s">
-        <v>398</v>
+        <v>392</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>393</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" s="2" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
@@ -7038,16 +7018,16 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="C167" t="s">
-        <v>576</v>
+        <v>566</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>567</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
@@ -7057,43 +7037,43 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E168" s="2"/>
-      <c r="F168" s="4" t="s">
-        <v>685</v>
+      <c r="F168" s="3" t="s">
+        <v>676</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" s="2" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E169" s="2"/>
-      <c r="F169" s="4" t="s">
-        <v>686</v>
+      <c r="F169" s="3" t="s">
+        <v>677</v>
       </c>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
@@ -7101,16 +7081,16 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" s="2"/>
@@ -7120,16 +7100,16 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
@@ -7139,16 +7119,16 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
@@ -7158,16 +7138,16 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="C173" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="B173" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>591</v>
-      </c>
       <c r="D173" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
@@ -7177,16 +7157,16 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
@@ -7196,16 +7176,16 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
@@ -7215,16 +7195,16 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
@@ -7234,16 +7214,16 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
@@ -7253,16 +7233,16 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
@@ -7272,16 +7252,16 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
@@ -7291,16 +7271,16 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
@@ -7310,16 +7290,16 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
@@ -7329,16 +7309,16 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
@@ -7348,16 +7328,16 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" s="2" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
@@ -7367,16 +7347,16 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
@@ -7386,16 +7366,16 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
@@ -7405,16 +7385,16 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
@@ -7424,16 +7404,16 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>700</v>
+        <v>691</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
@@ -7443,16 +7423,16 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
@@ -7462,16 +7442,16 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>702</v>
+        <v>693</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
@@ -7481,16 +7461,16 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
@@ -7500,16 +7480,16 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
@@ -7519,16 +7499,16 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
@@ -7538,16 +7518,16 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" s="2"/>
@@ -7557,16 +7537,16 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E194" s="2"/>
       <c r="F194" s="2"/>
@@ -7576,16 +7556,16 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
@@ -7595,20 +7575,20 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" s="2" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
@@ -7616,20 +7596,20 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E197" s="2"/>
-      <c r="F197" s="4" t="s">
-        <v>687</v>
+      <c r="F197" s="3" t="s">
+        <v>678</v>
       </c>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
@@ -7637,20 +7617,20 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E198" s="2"/>
-      <c r="F198" s="4" t="s">
-        <v>688</v>
+      <c r="F198" s="3" t="s">
+        <v>679</v>
       </c>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
@@ -7658,16 +7638,16 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E199" s="2"/>
       <c r="F199" s="2"/>
@@ -7677,16 +7657,16 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
@@ -7696,16 +7676,16 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E201" s="2"/>
       <c r="F201" s="2"/>
@@ -7715,16 +7695,16 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
@@ -7734,16 +7714,16 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E203" s="2"/>
       <c r="F203" s="2"/>
@@ -7753,16 +7733,16 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E204" s="2"/>
       <c r="F204" s="2"/>
@@ -7772,16 +7752,16 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E205" s="2"/>
       <c r="F205" s="2"/>
@@ -7791,16 +7771,16 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E206" s="2"/>
       <c r="F206" s="2"/>
@@ -7810,16 +7790,16 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E207" s="2"/>
       <c r="F207" s="2"/>
@@ -7829,16 +7809,16 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E208" s="2"/>
       <c r="F208" s="2"/>
@@ -7848,16 +7828,16 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" s="2"/>
@@ -7867,16 +7847,16 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E210" s="2"/>
       <c r="F210" s="2"/>
@@ -7886,16 +7866,16 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" s="2"/>
@@ -7905,16 +7885,16 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" s="2"/>
@@ -7924,16 +7904,16 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A213" s="2" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="E213" s="2"/>
       <c r="F213" s="2"/>
@@ -7943,16 +7923,16 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="E214" s="2"/>
       <c r="F214" s="2"/>
@@ -7962,16 +7942,16 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="E215" s="2"/>
       <c r="F215" s="2"/>
@@ -7981,16 +7961,16 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="E216" s="2"/>
       <c r="F216" s="2"/>
@@ -8000,16 +7980,16 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E217" s="2"/>
       <c r="F217" s="2"/>
@@ -8019,16 +7999,16 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E218" s="2"/>
       <c r="F218" s="2"/>
@@ -8038,16 +8018,16 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E219" s="2"/>
       <c r="F219" s="2"/>
@@ -8056,234 +8036,315 @@
       <c r="I219" s="2"/>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A220" t="s">
-        <v>582</v>
-      </c>
-      <c r="B220" t="s">
+      <c r="A220" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E220" s="2"/>
+      <c r="F220" s="2"/>
+      <c r="G220" s="2"/>
+      <c r="H220" s="2"/>
+      <c r="I220" s="2"/>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A221" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E221" s="2"/>
+      <c r="F221" s="2"/>
+      <c r="G221" s="2"/>
+      <c r="H221" s="2"/>
+      <c r="I221" s="2"/>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A222" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E222" s="2"/>
+      <c r="F222" s="2"/>
+      <c r="G222" s="2"/>
+      <c r="H222" s="2"/>
+      <c r="I222" s="2"/>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A223" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E223" s="2"/>
+      <c r="F223" s="2"/>
+      <c r="G223" s="2"/>
+      <c r="H223" s="2"/>
+      <c r="I223" s="2"/>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A224" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E224" s="2"/>
+      <c r="F224" s="2"/>
+      <c r="G224" s="2"/>
+      <c r="H224" s="2"/>
+      <c r="I224" s="2"/>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A225" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E225" s="2"/>
+      <c r="F225" s="2"/>
+      <c r="G225" s="2"/>
+      <c r="H225" s="2"/>
+      <c r="I225" s="2"/>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A226" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F226" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G226" s="2"/>
+      <c r="H226" s="2"/>
+      <c r="I226" s="2"/>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A227" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E227" s="2"/>
+      <c r="F227" s="2"/>
+      <c r="G227" s="2"/>
+      <c r="H227" s="2"/>
+      <c r="I227" s="2"/>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A228" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E228" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="C220" t="str">
-        <f>VLOOKUP(B220,Sheet1!A:B,2,FALSE)</f>
-        <v>x=9.25, y=80.82</v>
-      </c>
-      <c r="D220" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A221" t="s">
-        <v>582</v>
-      </c>
-      <c r="B221" t="s">
+      <c r="F228" s="2"/>
+      <c r="G228" s="2"/>
+      <c r="H228" s="2"/>
+      <c r="I228" s="2"/>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A229" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B229" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="C221" t="str">
-        <f>VLOOKUP(B221,Sheet1!A:B,2,FALSE)</f>
-        <v>x=79.37, y=63.15</v>
-      </c>
-      <c r="D221" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A222" t="s">
-        <v>582</v>
-      </c>
-      <c r="B222" t="s">
+      <c r="C229" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E229" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="C222" t="str">
-        <f>VLOOKUP(B222,Sheet1!A:B,2,FALSE)</f>
-        <v>x=26.03, y=86.14</v>
-      </c>
-      <c r="D222" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A223" t="s">
-        <v>582</v>
-      </c>
-      <c r="B223" t="s">
+      <c r="F229" s="2"/>
+      <c r="G229" s="2"/>
+      <c r="H229" s="2"/>
+      <c r="I229" s="2"/>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A230" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="C223" t="str">
-        <f>VLOOKUP(B223,Sheet1!A:B,2,FALSE)</f>
-        <v>x=24.49, y=86.21</v>
-      </c>
-      <c r="D223" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A224" t="s">
-        <v>582</v>
-      </c>
-      <c r="B224" t="s">
+      <c r="B230" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="C224" t="str">
-        <f>VLOOKUP(B224,Sheet1!A:B,2,FALSE)</f>
-        <v>x=67.22, y=86.14</v>
-      </c>
-      <c r="D224" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A225" t="s">
-        <v>170</v>
-      </c>
-      <c r="B225" t="s">
+      <c r="C230" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E230" s="2"/>
+      <c r="F230" s="2"/>
+      <c r="G230" s="2"/>
+      <c r="H230" s="2"/>
+      <c r="I230" s="2"/>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A231" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E231" s="2"/>
+      <c r="F231" s="2"/>
+      <c r="G231" s="2"/>
+      <c r="H231" s="2"/>
+      <c r="I231" s="2"/>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A232" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B232" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="C225" t="str">
-        <f>VLOOKUP(B225,Sheet1!A:B,2,FALSE)</f>
-        <v>x=10.90, y=63.07</v>
-      </c>
-      <c r="D225" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A226" t="s">
-        <v>170</v>
-      </c>
-      <c r="B226" t="s">
-        <v>723</v>
-      </c>
-      <c r="C226" t="str">
-        <f>VLOOKUP(B226,Sheet1!A:B,2,FALSE)</f>
-        <v>x=12.37, y=66.24</v>
-      </c>
-      <c r="D226" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A227" t="s">
-        <v>170</v>
-      </c>
-      <c r="B227" t="s">
-        <v>724</v>
-      </c>
-      <c r="C227" t="str">
-        <f>VLOOKUP(B227,Sheet1!A:B,2,FALSE)</f>
-        <v>x=10.79, y=66.31</v>
-      </c>
-      <c r="D227" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A228" t="s">
-        <v>170</v>
-      </c>
-      <c r="B228" t="s">
+      <c r="C232" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E232" s="2"/>
+      <c r="F232" s="2"/>
+      <c r="G232" s="2"/>
+      <c r="H232" s="2"/>
+      <c r="I232" s="2"/>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A233" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C233" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="C228" t="str">
-        <f>VLOOKUP(B228,Sheet1!A:B,2,FALSE)</f>
-        <v>x=38.14, y=94.04</v>
-      </c>
-      <c r="D228" t="s">
-        <v>173</v>
-      </c>
-      <c r="E228" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A229" t="s">
-        <v>170</v>
-      </c>
-      <c r="B229" t="s">
-        <v>727</v>
-      </c>
-      <c r="C229" t="str">
-        <f>VLOOKUP(B229,Sheet1!A:B,2,FALSE)</f>
-        <v>x=39.98, y=85.70</v>
-      </c>
-      <c r="D229" t="s">
-        <v>173</v>
-      </c>
-      <c r="E229" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A230" s="7" t="s">
-        <v>729</v>
-      </c>
-      <c r="B230" t="s">
-        <v>730</v>
-      </c>
-      <c r="C230" t="str">
-        <f>VLOOKUP(B230,Sheet1!A:B,2,FALSE)</f>
-        <v>x=68.76, y=86.28</v>
-      </c>
-      <c r="D230" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A231" t="s">
-        <v>582</v>
-      </c>
-      <c r="B231" t="s">
-        <v>721</v>
-      </c>
-      <c r="C231" t="str">
-        <f>VLOOKUP(B231,Sheet1!A:B,2,FALSE)</f>
-        <v>x=67.22, y=86.14</v>
-      </c>
-      <c r="D231" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A232" t="s">
-        <v>582</v>
-      </c>
-      <c r="B232" t="s">
-        <v>731</v>
-      </c>
-      <c r="C232" t="str">
-        <f>VLOOKUP(B232,Sheet1!A:B,2,FALSE)</f>
-        <v>x=71.99, y=86.35</v>
-      </c>
-      <c r="D232" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A233" t="s">
-        <v>582</v>
-      </c>
-      <c r="B233" t="s">
-        <v>718</v>
-      </c>
-      <c r="C233" t="str">
-        <f>VLOOKUP(B233,Sheet1!A:B,2,FALSE)</f>
-        <v>x=79.37, y=63.15</v>
-      </c>
-      <c r="D233" t="s">
-        <v>585</v>
-      </c>
+      <c r="D233" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E233" s="2"/>
+      <c r="F233" s="2"/>
+      <c r="G233" s="2"/>
+      <c r="H233" s="2"/>
+      <c r="I233" s="2"/>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A234" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E234" s="2"/>
+      <c r="F234" s="2"/>
+      <c r="G234" s="2"/>
+      <c r="H234" s="2"/>
+      <c r="I234" s="2"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G220:G1048576">
+  <conditionalFormatting sqref="G235:G1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="F16" r:id="rId1" xr:uid="{07AF991F-F6C6-C44A-A751-5A2EA2944D41}"/>
-    <hyperlink ref="F39" r:id="rId2" xr:uid="{F041CF9A-13DD-624A-9B00-2D2AFA06DE44}"/>
-    <hyperlink ref="G168" r:id="rId3" xr:uid="{015B9B0A-F36B-434C-B71F-52D73CA54715}"/>
-    <hyperlink ref="F148" r:id="rId4" xr:uid="{B6CF26C8-F003-564C-91E1-424AA63AE620}"/>
-    <hyperlink ref="F133" r:id="rId5" xr:uid="{F16986EA-EEF8-E344-A461-8D16F1B0F343}"/>
-    <hyperlink ref="F119" r:id="rId6" xr:uid="{CABFB8E0-E217-3E47-A432-418BECF77264}"/>
-    <hyperlink ref="F120" r:id="rId7" xr:uid="{84CA1D64-C468-1049-94C5-C3897EF060BD}"/>
-    <hyperlink ref="F121" r:id="rId8" xr:uid="{042437EF-DB86-6F48-8CA6-C97CD720C3EB}"/>
+    <hyperlink ref="G8" r:id="rId1" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u72eLYAQ/view" xr:uid="{65596CF7-BDB9-6A40-B030-1A20C6B98465}"/>
+    <hyperlink ref="H15" r:id="rId2" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000rvp8wYAA/view" xr:uid="{C5427ACB-FBA3-1E4E-889F-7B5EA77E8DBC}"/>
+    <hyperlink ref="F16" r:id="rId3" xr:uid="{9D963830-BAFA-644C-A644-5E8750DBB383}"/>
+    <hyperlink ref="F39" r:id="rId4" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000Q2enCYAR/view" xr:uid="{5222CFA8-43C4-FA43-BDDF-A929363493D2}"/>
+    <hyperlink ref="F43" r:id="rId5" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u9QkgYAE/view" xr:uid="{117D339F-73A8-3343-BDC7-646C679812A8}"/>
+    <hyperlink ref="F119" r:id="rId6" xr:uid="{8DCCDB3B-822D-C342-B115-0DE63B038623}"/>
+    <hyperlink ref="F120" r:id="rId7" xr:uid="{30DAE056-C7EB-9E4C-B1FE-4279CD7FEDD4}"/>
+    <hyperlink ref="F121" r:id="rId8" xr:uid="{57AAA8CA-E5D6-8C4E-A5D1-5243A96160CC}"/>
+    <hyperlink ref="F133" r:id="rId9" xr:uid="{8BFBED8D-BE27-AA4B-B2E7-08315E64B68C}"/>
+    <hyperlink ref="F148" r:id="rId10" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000s98yXYAQ/view" xr:uid="{BF94BAB4-0CE7-E645-BAD9-0BCA6B291B73}"/>
+    <hyperlink ref="G168" r:id="rId11" xr:uid="{6825F257-D41A-114A-88F7-20C2B22CF9C5}"/>
+    <hyperlink ref="F226" r:id="rId12" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u2DFRYA2/view" xr:uid="{F13A9300-ADB7-514D-9AB4-BDE540A31E7A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8300,7 +8361,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
@@ -8308,138 +8369,138 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
         <v>26</v>
-      </c>
-      <c r="B2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="B7" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="B8" t="s">
-        <v>740</v>
+        <v>731</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="B9" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="B10" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="B11" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
         <v>23</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>741</v>
+        <v>732</v>
       </c>
       <c r="B14" t="s">
-        <v>742</v>
+        <v>733</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
         <v>19</v>
-      </c>
-      <c r="B15" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B17" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -8452,2628 +8513,2628 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
         <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" t="s">
         <v>30</v>
-      </c>
-      <c r="B23" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B31" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
       <c r="B35" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B36" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B38" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B39" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
       <c r="B40" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B42" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
       <c r="B43" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B44" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="B45" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
       <c r="B46" t="s">
-        <v>751</v>
+        <v>742</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B47" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B48" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B49" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B50" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B51" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B52" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B53" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B54" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B55" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B56" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B57" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B58" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B59" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B60" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="B61" t="s">
-        <v>752</v>
+        <v>743</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B62" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B63" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B64" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B65" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
       <c r="B66" t="s">
-        <v>754</v>
+        <v>745</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="B67" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B68" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>755</v>
+        <v>746</v>
       </c>
       <c r="B69" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B70" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B71" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B72" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B73" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="B74" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B75" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
       <c r="B76" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="B77" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B78" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B79" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="B80" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B81" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B82" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B83" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B84" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="B85" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="B86" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="B87" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
       <c r="B88" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="B89" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="B90" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
       <c r="B91" t="s">
-        <v>778</v>
+        <v>769</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>779</v>
+        <v>770</v>
       </c>
       <c r="B92" t="s">
-        <v>780</v>
+        <v>771</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
       <c r="B93" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>784</v>
+        <v>775</v>
       </c>
       <c r="B95" t="s">
-        <v>785</v>
+        <v>776</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>786</v>
+        <v>777</v>
       </c>
       <c r="B96" t="s">
-        <v>787</v>
+        <v>778</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="B97" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
       <c r="B98" t="s">
-        <v>791</v>
+        <v>782</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>792</v>
+        <v>783</v>
       </c>
       <c r="B99" t="s">
-        <v>793</v>
+        <v>784</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>794</v>
+        <v>785</v>
       </c>
       <c r="B100" t="s">
-        <v>795</v>
+        <v>786</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>796</v>
+        <v>787</v>
       </c>
       <c r="B101" t="s">
-        <v>797</v>
+        <v>788</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>798</v>
+        <v>789</v>
       </c>
       <c r="B102" t="s">
-        <v>799</v>
+        <v>790</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>800</v>
+        <v>791</v>
       </c>
       <c r="B103" t="s">
-        <v>801</v>
+        <v>792</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>802</v>
+        <v>793</v>
       </c>
       <c r="B104" t="s">
-        <v>803</v>
+        <v>794</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="B105" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
       <c r="B106" t="s">
-        <v>807</v>
+        <v>798</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>808</v>
+        <v>799</v>
       </c>
       <c r="B107" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>810</v>
+        <v>801</v>
       </c>
       <c r="B108" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>812</v>
+        <v>803</v>
       </c>
       <c r="B109" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>814</v>
+        <v>805</v>
       </c>
       <c r="B110" t="s">
-        <v>815</v>
+        <v>806</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B111" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="B112" t="s">
-        <v>732</v>
+        <v>723</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
       <c r="B113" t="s">
-        <v>817</v>
+        <v>808</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
       <c r="B114" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="B115" t="s">
-        <v>821</v>
+        <v>812</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="B116" t="s">
-        <v>823</v>
+        <v>814</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>824</v>
+        <v>815</v>
       </c>
       <c r="B117" t="s">
-        <v>825</v>
+        <v>816</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>826</v>
+        <v>817</v>
       </c>
       <c r="B118" t="s">
-        <v>827</v>
+        <v>818</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B119" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>828</v>
+        <v>819</v>
       </c>
       <c r="B120" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
       <c r="B121" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>832</v>
+        <v>823</v>
       </c>
       <c r="B122" t="s">
-        <v>833</v>
+        <v>824</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>834</v>
+        <v>825</v>
       </c>
       <c r="B123" t="s">
-        <v>835</v>
+        <v>826</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>836</v>
+        <v>827</v>
       </c>
       <c r="B124" t="s">
-        <v>837</v>
+        <v>828</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>838</v>
+        <v>829</v>
       </c>
       <c r="B125" t="s">
-        <v>839</v>
+        <v>830</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>840</v>
+        <v>831</v>
       </c>
       <c r="B126" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
       <c r="B127" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B128" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="B129" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="B130" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
       <c r="B131" t="s">
-        <v>844</v>
+        <v>835</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
       <c r="B132" t="s">
-        <v>846</v>
+        <v>837</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>847</v>
+        <v>838</v>
       </c>
       <c r="B133" t="s">
-        <v>848</v>
+        <v>839</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>849</v>
+        <v>840</v>
       </c>
       <c r="B134" t="s">
-        <v>850</v>
+        <v>841</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>851</v>
+        <v>842</v>
       </c>
       <c r="B135" t="s">
-        <v>852</v>
+        <v>843</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="B136" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
       <c r="B137" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B138" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="B139" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B140" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>856</v>
+        <v>847</v>
       </c>
       <c r="B141" t="s">
-        <v>857</v>
+        <v>848</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>858</v>
+        <v>849</v>
       </c>
       <c r="B142" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
       <c r="B143" t="s">
-        <v>861</v>
+        <v>852</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="B144" t="s">
-        <v>863</v>
+        <v>854</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
       <c r="B145" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>866</v>
+        <v>857</v>
       </c>
       <c r="B146" t="s">
-        <v>867</v>
+        <v>858</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="B147" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B148" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B149" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B150" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="B151" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="B152" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="B153" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
       <c r="B154" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="B155" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="B156" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B157" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B158" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B159" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B160" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B161" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B162" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="B163" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B164" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
       <c r="B165" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B166" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B167" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="B168" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B169" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B170" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
       <c r="B171" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B172" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>882</v>
+        <v>873</v>
       </c>
       <c r="B173" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B174" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="B175" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B176" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B177" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>883</v>
+        <v>874</v>
       </c>
       <c r="B178" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B179" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B180" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B181" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="B182" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B183" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B184" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B185" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B186" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B187" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="B188" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B189" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="B190" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B191" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="B192" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B193" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B194" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B195" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B196" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>884</v>
+        <v>875</v>
       </c>
       <c r="B197" t="s">
-        <v>885</v>
+        <v>876</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
       <c r="B198" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="B199" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="B200" t="s">
-        <v>887</v>
+        <v>878</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="B201" t="s">
-        <v>888</v>
+        <v>879</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="B202" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>889</v>
+        <v>880</v>
       </c>
       <c r="B203" t="s">
-        <v>890</v>
+        <v>881</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>891</v>
+        <v>882</v>
       </c>
       <c r="B204" t="s">
-        <v>892</v>
+        <v>883</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
       <c r="B205" t="s">
-        <v>893</v>
+        <v>884</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="B206" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="B207" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="B208" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B209" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>900</v>
+        <v>891</v>
       </c>
       <c r="B210" t="s">
-        <v>901</v>
+        <v>892</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B211" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="B212" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>902</v>
+        <v>893</v>
       </c>
       <c r="B213" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="B214" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="B215" t="s">
-        <v>907</v>
+        <v>898</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="B216" t="s">
-        <v>909</v>
+        <v>900</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>910</v>
+        <v>901</v>
       </c>
       <c r="B217" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>912</v>
+        <v>903</v>
       </c>
       <c r="B218" t="s">
-        <v>913</v>
+        <v>904</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B219" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>914</v>
+        <v>905</v>
       </c>
       <c r="B220" t="s">
-        <v>915</v>
+        <v>906</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B221" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>916</v>
+        <v>907</v>
       </c>
       <c r="B222" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
       <c r="B223" t="s">
-        <v>919</v>
+        <v>910</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>920</v>
+        <v>911</v>
       </c>
       <c r="B224" t="s">
-        <v>921</v>
+        <v>912</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>922</v>
+        <v>913</v>
       </c>
       <c r="B225" t="s">
-        <v>923</v>
+        <v>914</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="B226" t="s">
-        <v>925</v>
+        <v>916</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>926</v>
+        <v>917</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>927</v>
+        <v>918</v>
       </c>
       <c r="B228" t="s">
-        <v>928</v>
+        <v>919</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="B229" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>929</v>
+        <v>920</v>
       </c>
       <c r="B230" t="s">
-        <v>930</v>
+        <v>921</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B231" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>931</v>
+        <v>922</v>
       </c>
       <c r="B232" t="s">
-        <v>932</v>
+        <v>923</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>933</v>
+        <v>924</v>
       </c>
       <c r="B233" t="s">
-        <v>934</v>
+        <v>925</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>935</v>
+        <v>926</v>
       </c>
       <c r="B234" t="s">
-        <v>936</v>
+        <v>927</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>937</v>
+        <v>928</v>
       </c>
       <c r="B235" t="s">
-        <v>938</v>
+        <v>929</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>939</v>
+        <v>930</v>
       </c>
       <c r="B236" t="s">
-        <v>940</v>
+        <v>931</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="B237" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B238" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B239" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="B240" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="B241" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>941</v>
+        <v>932</v>
       </c>
       <c r="B242" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>942</v>
+        <v>933</v>
       </c>
       <c r="B243" t="s">
-        <v>943</v>
+        <v>934</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="B244" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>944</v>
+        <v>935</v>
       </c>
       <c r="B245" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="B246" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B247" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B248" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B249" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B250" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="B251" t="s">
-        <v>700</v>
+        <v>691</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>947</v>
+        <v>938</v>
       </c>
       <c r="B252" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="B253" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="B254" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
       <c r="B255" t="s">
-        <v>949</v>
+        <v>940</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="B256" t="s">
-        <v>950</v>
+        <v>941</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>951</v>
+        <v>942</v>
       </c>
       <c r="B257" t="s">
-        <v>952</v>
+        <v>943</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>953</v>
+        <v>944</v>
       </c>
       <c r="B258" t="s">
-        <v>954</v>
+        <v>945</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B259" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="B260" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="B261" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B262" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="B263" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>955</v>
+        <v>946</v>
       </c>
       <c r="B264" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="B265" t="s">
-        <v>702</v>
+        <v>693</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
       <c r="B266" t="s">
-        <v>956</v>
+        <v>947</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>957</v>
+        <v>948</v>
       </c>
       <c r="B267" t="s">
-        <v>958</v>
+        <v>949</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
       <c r="B268" t="s">
-        <v>959</v>
+        <v>950</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>960</v>
+        <v>951</v>
       </c>
       <c r="B269" t="s">
-        <v>961</v>
+        <v>952</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>962</v>
+        <v>953</v>
       </c>
       <c r="B270" t="s">
-        <v>963</v>
+        <v>954</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B271" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>964</v>
+        <v>955</v>
       </c>
       <c r="B272" t="s">
-        <v>965</v>
+        <v>956</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="B273" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="B274" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="B275" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B276" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="B277" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="B278" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="B279" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="B280" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>966</v>
+        <v>957</v>
       </c>
       <c r="B281" t="s">
-        <v>967</v>
+        <v>958</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="B282" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="B283" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>968</v>
+        <v>959</v>
       </c>
       <c r="B284" t="s">
-        <v>969</v>
+        <v>960</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="B285" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>970</v>
+        <v>961</v>
       </c>
       <c r="B286" t="s">
-        <v>971</v>
+        <v>962</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="B287" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>972</v>
+        <v>963</v>
       </c>
       <c r="B288" t="s">
-        <v>973</v>
+        <v>964</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="B289" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B290" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="B291" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="B292" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>974</v>
+        <v>965</v>
       </c>
       <c r="B293" t="s">
-        <v>975</v>
+        <v>966</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="B294" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="B295" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="B296" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="B297" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="B298" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="B299" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>976</v>
+        <v>967</v>
       </c>
       <c r="B300" t="s">
-        <v>977</v>
+        <v>968</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="B301" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>978</v>
+        <v>969</v>
       </c>
       <c r="B302" t="s">
-        <v>979</v>
+        <v>970</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="B303" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="B304" t="s">
-        <v>981</v>
+        <v>972</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>982</v>
+        <v>973</v>
       </c>
       <c r="B305" t="s">
-        <v>983</v>
+        <v>974</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="B306" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="B307" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B308" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="B309" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B310" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="B311" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="B312" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="B313" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="B314" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="B315" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>984</v>
+        <v>975</v>
       </c>
       <c r="B316" t="s">
-        <v>985</v>
+        <v>976</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>986</v>
+        <v>977</v>
       </c>
       <c r="B317" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>988</v>
+        <v>979</v>
       </c>
       <c r="B318" t="s">
-        <v>989</v>
+        <v>980</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="B319" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="B320" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="B321" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="B322" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="B323" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="B324" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="B325" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="B326" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="B327" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="B328" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="B329" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
       <c r="B330" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="B331" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="B332" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B333" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="B334" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="B335" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="B336" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="B337" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="B338" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B339" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="B340" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B341" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="B342" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="B343" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="B344" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B345" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="B346" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="B347" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="B348" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66138E5-61B7-7744-A7AA-F866E6D5D88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D33769E8-74A5-224E-8449-7C5B67869E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-34820" yWindow="2020" windowWidth="27240" windowHeight="16440" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -3045,7 +3045,7 @@
     <t xml:space="preserve">Issue tickets to Michelle Kim at Michellekim2020@yahoo.com </t>
   </si>
   <si>
-    <t>Polamalu Concert 2026 Tickets | Opportunity | Salesforce</t>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u2DFRYA2/view</t>
   </si>
 </sst>
 </file>
@@ -8344,7 +8344,7 @@
     <hyperlink ref="F133" r:id="rId9" xr:uid="{8BFBED8D-BE27-AA4B-B2E7-08315E64B68C}"/>
     <hyperlink ref="F148" r:id="rId10" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000s98yXYAQ/view" xr:uid="{BF94BAB4-0CE7-E645-BAD9-0BCA6B291B73}"/>
     <hyperlink ref="G168" r:id="rId11" xr:uid="{6825F257-D41A-114A-88F7-20C2B22CF9C5}"/>
-    <hyperlink ref="F226" r:id="rId12" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u2DFRYA2/view" xr:uid="{F13A9300-ADB7-514D-9AB4-BDE540A31E7A}"/>
+    <hyperlink ref="F226" r:id="rId12" xr:uid="{F13A9300-ADB7-514D-9AB4-BDE540A31E7A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D33769E8-74A5-224E-8449-7C5B67869E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52CBE352-315F-C347-897A-DF0D01A33965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34820" yWindow="2020" windowWidth="27240" windowHeight="16440" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
+    <workbookView xWindow="2800" yWindow="1760" windowWidth="27240" windowHeight="16440" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
   <sheets>
     <sheet name="xlsx" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1826" uniqueCount="1003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1823" uniqueCount="1047">
   <si>
     <t>Household Name</t>
   </si>
@@ -1056,9 +1059,6 @@
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000spUGHYA2/view</t>
   </si>
   <si>
-    <t>Shannons’s to fill</t>
-  </si>
-  <si>
     <t>D55</t>
   </si>
   <si>
@@ -1638,9 +1638,6 @@
     <t>x=76.06, y=77.73</t>
   </si>
   <si>
-    <t>https://curebound.lightning.force.com/lightning/r/006QU00000pZi0uYAC/view</t>
-  </si>
-  <si>
     <t>E73</t>
   </si>
   <si>
@@ -3000,9 +2997,6 @@
     <t>Amy + Bill Koman</t>
   </si>
   <si>
-    <t>x=50.55, y=55.39</t>
-  </si>
-  <si>
     <t>Elisa Jaime + Lynda Kerr</t>
   </si>
   <si>
@@ -3018,24 +3012,9 @@
     <t>Adler Concert 2026 Tickets | Opportunity | Salesforce</t>
   </si>
   <si>
-    <t>(Mike Cunningham)</t>
-  </si>
-  <si>
     <t>Tafel Klaus Concert 2026 Tickets | Opportunity | Salesforce</t>
   </si>
   <si>
-    <t>x=56.90, y=93.53</t>
-  </si>
-  <si>
-    <t>(now requesting E54 or near that area)</t>
-  </si>
-  <si>
-    <t>(would like to be on the right)</t>
-  </si>
-  <si>
-    <t>(Carla Taub)</t>
-  </si>
-  <si>
     <t>Theodora Polamalu</t>
   </si>
   <si>
@@ -3046,6 +3025,162 @@
   </si>
   <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u2DFRYA2/view</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (Mike Cunningham)</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uLMDOYA4/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uKwXTYA0/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000rDyhPYAS/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uKvQ7YAK/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uLTZpYAO/view</t>
+  </si>
+  <si>
+    <t>Oppidan</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000tQVF0YAO/view</t>
+  </si>
+  <si>
+    <t>Shannon's to fill</t>
+  </si>
+  <si>
+    <t>Nevell</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u26ymYAA/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000pa30TYAQ/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uKruNYAS/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uLLu1YAG/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uLgX3YAK/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uKWrYYAW/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000pad3tYAA/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uMf2gYAC/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uLBgCYAW/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uLNcUYAW/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uLob4YAC/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uM4ZNYA0/view</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (now requesting E54 or near that area)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (would like to be on the right)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (Carla Taub)</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uLBMoYAO/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uLJU1YAO/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uKzS6YAK/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uLN9RYAW/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000pZi0uYAC/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uKuyhYAC/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uLIxlYAG/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uIzzIYAS/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uJn9iYAC/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uLhRVYA0/view</t>
+  </si>
+  <si>
+    <t>Largo Concrete</t>
+  </si>
+  <si>
+    <t>Jim Tkach</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u2Vx7YAE/view</t>
+  </si>
+  <si>
+    <t>ACSW</t>
+  </si>
+  <si>
+    <t>Tyler Musso</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u1lRKYAY/view</t>
+  </si>
+  <si>
+    <t>Lisa Stennes</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u0ydWYAQ/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u1zKXYAY/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u121MYAQ/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uJjEFYA0/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u1tJyYAI/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u1y8LYAQ/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u1a7gYAA/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u1oDrYAI/view</t>
+  </si>
+  <si>
+    <t>Michael Nall</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uL0fxYAC/view</t>
   </si>
 </sst>
 </file>
@@ -3070,17 +3205,9 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -3088,16 +3215,20 @@
       <color rgb="FF467886"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3108,6 +3239,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3124,19 +3261,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3158,6 +3308,2803 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="xlsx"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>Table Number</v>
+          </cell>
+          <cell r="B1" t="str">
+            <v>Coordinates</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>A1</v>
+          </cell>
+          <cell r="B2" t="str">
+            <v xml:space="preserve"> x=50.55, y=55.39</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>A2</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>x=41.23, y=55.46</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>A3</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>x=52.79, y=55.32</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>A4</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>x=39.02, y=55.46</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>A5</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>x=54.96, y=55.53</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>A6</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>x=36.75, y=55.53</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>A7</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>x=57.27, y=55.32</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>A8</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>x=34.47, y=55.39</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>A9</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>x=59.54, y=55.60</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>A10</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>x=32.27, y=55.39</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>A11</v>
+          </cell>
+          <cell r="B12" t="str">
+            <v>x=50.92, y=59.70</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>A12</v>
+          </cell>
+          <cell r="B13" t="str">
+            <v>x=40.97, y=59.84</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14" t="str">
+            <v>A13</v>
+          </cell>
+          <cell r="B14" t="str">
+            <v>x=53.23, y=59.70</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15" t="str">
+            <v>A14</v>
+          </cell>
+          <cell r="B15" t="str">
+            <v>x=38.58, y=59.77</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16" t="str">
+            <v>A15</v>
+          </cell>
+          <cell r="B16" t="str">
+            <v>x=50.95, y=64.08</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17" t="str">
+            <v>A16</v>
+          </cell>
+          <cell r="B17" t="str">
+            <v>x=40.90, y=64.15</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18" t="str">
+            <v>A17</v>
+          </cell>
+          <cell r="B18" t="str">
+            <v>x=53.08, y=64.15</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19" t="str">
+            <v>A18</v>
+          </cell>
+          <cell r="B19" t="str">
+            <v>x=38.66, y=64.30</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20" t="str">
+            <v>A19</v>
+          </cell>
+          <cell r="B20" t="str">
+            <v>x=50.92, y=68.39</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21" t="str">
+            <v>A20</v>
+          </cell>
+          <cell r="B21" t="str">
+            <v>x=40.93, y=68.46</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22" t="str">
+            <v>A21</v>
+          </cell>
+          <cell r="B22" t="str">
+            <v>x=53.12, y=68.53</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23" t="str">
+            <v>A22</v>
+          </cell>
+          <cell r="B23" t="str">
+            <v>x=38.69, y=68.39</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24" t="str">
+            <v>A23</v>
+          </cell>
+          <cell r="B24" t="str">
+            <v>x=50.95, y=72.84</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25" t="str">
+            <v>A24</v>
+          </cell>
+          <cell r="B25" t="str">
+            <v>x=40.93, y=72.77</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26" t="str">
+            <v>A25</v>
+          </cell>
+          <cell r="B26" t="str">
+            <v>x=53.05, y=72.70</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27" t="str">
+            <v>A26</v>
+          </cell>
+          <cell r="B27" t="str">
+            <v>x=38.58, y=72.63</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28" t="str">
+            <v>A27</v>
+          </cell>
+          <cell r="B28" t="str">
+            <v>x=51.03, y=77.23</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29" t="str">
+            <v>A28</v>
+          </cell>
+          <cell r="B29" t="str">
+            <v>x=40.90, y=77.59</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30" t="str">
+            <v>A29</v>
+          </cell>
+          <cell r="B30" t="str">
+            <v>x=53.27, y=77.30</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31" t="str">
+            <v>A30</v>
+          </cell>
+          <cell r="B31" t="str">
+            <v>x=38.73, y=77.30</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32" t="str">
+            <v>A31</v>
+          </cell>
+          <cell r="B32" t="str">
+            <v>x=50.84, y=81.68</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33" t="str">
+            <v>A32</v>
+          </cell>
+          <cell r="B33" t="str">
+            <v>x=40.82, y=81.82</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34" t="str">
+            <v>A33</v>
+          </cell>
+          <cell r="B34" t="str">
+            <v>x=53.16, y=81.68</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35" t="str">
+            <v>A34</v>
+          </cell>
+          <cell r="B35" t="str">
+            <v>x=38.66, y=81.75</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36" t="str">
+            <v>B1</v>
+          </cell>
+          <cell r="B36" t="str">
+            <v>x=46.04, y=82.47</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37" t="str">
+            <v>B2</v>
+          </cell>
+          <cell r="B37" t="str">
+            <v>x=43.65, y=82.26</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38" t="str">
+            <v>B3</v>
+          </cell>
+          <cell r="B38" t="str">
+            <v>x=48.02, y=82.33</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39" t="str">
+            <v>B4</v>
+          </cell>
+          <cell r="B39" t="str">
+            <v>x=44.27, y=85.85</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40" t="str">
+            <v>B5</v>
+          </cell>
+          <cell r="B40" t="str">
+            <v>x=47.61, y=85.85</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41" t="str">
+            <v>B6</v>
+          </cell>
+          <cell r="B41" t="str">
+            <v>x=42.18, y=85.85</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42" t="str">
+            <v>B7</v>
+          </cell>
+          <cell r="B42" t="str">
+            <v>x=49.52, y=85.78</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43" t="str">
+            <v>B8</v>
+          </cell>
+          <cell r="B43" t="str">
+            <v>x=39.98, y=85.70</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44" t="str">
+            <v>B9</v>
+          </cell>
+          <cell r="B44" t="str">
+            <v>x=51.54, y=85.78</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45" t="str">
+            <v>B10</v>
+          </cell>
+          <cell r="B45" t="str">
+            <v>x=38.11, y=85.70</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46" t="str">
+            <v>B11</v>
+          </cell>
+          <cell r="B46" t="str">
+            <v>x=53.63, y=85.78</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47" t="str">
+            <v>B12</v>
+          </cell>
+          <cell r="B47" t="str">
+            <v>x=44.16, y=89.73</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48" t="str">
+            <v>B13</v>
+          </cell>
+          <cell r="B48" t="str">
+            <v>x=47.50, y=89.80</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49" t="str">
+            <v>B14</v>
+          </cell>
+          <cell r="B49" t="str">
+            <v>x=42.14, y=89.87</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50" t="str">
+            <v>B15</v>
+          </cell>
+          <cell r="B50" t="str">
+            <v>x=49.49, y=89.94</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51" t="str">
+            <v>B16</v>
+          </cell>
+          <cell r="B51" t="str">
+            <v>x=40.12, y=89.87</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52" t="str">
+            <v>B17</v>
+          </cell>
+          <cell r="B52" t="str">
+            <v>x=51.54, y=89.87</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53" t="str">
+            <v>B18</v>
+          </cell>
+          <cell r="B53" t="str">
+            <v>x=38.07, y=89.80</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54" t="str">
+            <v>B19</v>
+          </cell>
+          <cell r="B54" t="str">
+            <v>x=53.67, y=89.80</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55" t="str">
+            <v>B20</v>
+          </cell>
+          <cell r="B55" t="str">
+            <v>x=44.20, y=93.68</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56" t="str">
+            <v>B21</v>
+          </cell>
+          <cell r="B56" t="str">
+            <v>x=47.47, y=93.75</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57" t="str">
+            <v>B22</v>
+          </cell>
+          <cell r="B57" t="str">
+            <v>x=42.18, y=93.75</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58" t="str">
+            <v>B23</v>
+          </cell>
+          <cell r="B58" t="str">
+            <v>x=49.67, y=93.68</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59" t="str">
+            <v>B24</v>
+          </cell>
+          <cell r="B59" t="str">
+            <v>x=40.05, y=93.75</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60" t="str">
+            <v>B25</v>
+          </cell>
+          <cell r="B60" t="str">
+            <v>x=51.58, y=93.75</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61" t="str">
+            <v>B26</v>
+          </cell>
+          <cell r="B61" t="str">
+            <v>x=38.14, y=94.04</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62" t="str">
+            <v>B27</v>
+          </cell>
+          <cell r="B62" t="str">
+            <v>x=53.63, y=93.82</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63" t="str">
+            <v>C1</v>
+          </cell>
+          <cell r="B63" t="str">
+            <v>x=56.57, y=61.93</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64" t="str">
+            <v>C2</v>
+          </cell>
+          <cell r="B64" t="str">
+            <v>x=35.06, y=61.85</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65" t="str">
+            <v>C3</v>
+          </cell>
+          <cell r="B65" t="str">
+            <v>x=58.77, y=62.14</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66" t="str">
+            <v>C4</v>
+          </cell>
+          <cell r="B66" t="str">
+            <v>x=33.00, y=62.00</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67" t="str">
+            <v>C5</v>
+          </cell>
+          <cell r="B67" t="str">
+            <v>x=60.72, y=62.07</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68" t="str">
+            <v>C6</v>
+          </cell>
+          <cell r="B68" t="str">
+            <v>x=30.98, y=62.07</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69" t="str">
+            <v>C7</v>
+          </cell>
+          <cell r="B69" t="str">
+            <v>x=62.85, y=62.07</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="A70" t="str">
+            <v>C8</v>
+          </cell>
+          <cell r="B70" t="str">
+            <v>x=28.85, y=62.07</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="A71" t="str">
+            <v>C9</v>
+          </cell>
+          <cell r="B71" t="str">
+            <v>x=56.61, y=66.38</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="A72" t="str">
+            <v>C10</v>
+          </cell>
+          <cell r="B72" t="str">
+            <v>x=35.21, y=65.88</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="A73" t="str">
+            <v>C11</v>
+          </cell>
+          <cell r="B73" t="str">
+            <v>x=58.66, y=66.16</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="A74" t="str">
+            <v>C12</v>
+          </cell>
+          <cell r="B74" t="str">
+            <v>x=33.04, y=66.31</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="A75" t="str">
+            <v>C13</v>
+          </cell>
+          <cell r="B75" t="str">
+            <v>x=60.72, y=66.09</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="A76" t="str">
+            <v>C14</v>
+          </cell>
+          <cell r="B76" t="str">
+            <v>x=30.98, y=66.16</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="A77" t="str">
+            <v>C15</v>
+          </cell>
+          <cell r="B77" t="str">
+            <v>x=62.70, y=66.09</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="A78" t="str">
+            <v>C16</v>
+          </cell>
+          <cell r="B78" t="str">
+            <v>x=28.82, y=66.16</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="A79" t="str">
+            <v>C17</v>
+          </cell>
+          <cell r="B79" t="str">
+            <v>x=56.64, y=69.97</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="A80" t="str">
+            <v>C18</v>
+          </cell>
+          <cell r="B80" t="str">
+            <v>x=35.10, y=69.76</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="A81" t="str">
+            <v>C19</v>
+          </cell>
+          <cell r="B81" t="str">
+            <v>x=58.74, y=69.97</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="A82" t="str">
+            <v>C20</v>
+          </cell>
+          <cell r="B82" t="str">
+            <v>x=33.08, y=69.97</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="A83" t="str">
+            <v>C21</v>
+          </cell>
+          <cell r="B83" t="str">
+            <v>x=60.83, y=69.97</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="A84" t="str">
+            <v>C22</v>
+          </cell>
+          <cell r="B84" t="str">
+            <v>x=30.91, y=69.83</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="A85" t="str">
+            <v>C23</v>
+          </cell>
+          <cell r="B85" t="str">
+            <v>x=62.81, y=69.90</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="A86" t="str">
+            <v>C24</v>
+          </cell>
+          <cell r="B86" t="str">
+            <v>x=28.93, y=69.90</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="A87" t="str">
+            <v>C25</v>
+          </cell>
+          <cell r="B87" t="str">
+            <v>x=56.68, y=77.80</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="A88" t="str">
+            <v>C26</v>
+          </cell>
+          <cell r="B88" t="str">
+            <v>x=35.06, y=77.66</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="A89" t="str">
+            <v>C27</v>
+          </cell>
+          <cell r="B89" t="str">
+            <v>x=58.66, y=77.73</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="A90" t="str">
+            <v>C28</v>
+          </cell>
+          <cell r="B90" t="str">
+            <v>x=33.08, y=77.80</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="A91" t="str">
+            <v>C29</v>
+          </cell>
+          <cell r="B91" t="str">
+            <v>x=60.72, y=77.80</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="A92" t="str">
+            <v>C30</v>
+          </cell>
+          <cell r="B92" t="str">
+            <v>x=30.95, y=77.73</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="A93" t="str">
+            <v>C31</v>
+          </cell>
+          <cell r="B93" t="str">
+            <v>x=62.78, y=77.59</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="A94" t="str">
+            <v>C32</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="A95" t="str">
+            <v>C33</v>
+          </cell>
+          <cell r="B95" t="str">
+            <v>x=56.68, y=81.68</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="A96" t="str">
+            <v>C34</v>
+          </cell>
+          <cell r="B96" t="str">
+            <v>x=35.02, y=81.82</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="A97" t="str">
+            <v>C35</v>
+          </cell>
+          <cell r="B97" t="str">
+            <v>x=58.70, y=81.97</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="A98" t="str">
+            <v>C36</v>
+          </cell>
+          <cell r="B98" t="str">
+            <v>x=33.04, y=81.75</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="A99" t="str">
+            <v>C37</v>
+          </cell>
+          <cell r="B99" t="str">
+            <v>x=60.68, y=81.75</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="A100" t="str">
+            <v>C38</v>
+          </cell>
+          <cell r="B100" t="str">
+            <v>x=30.95, y=81.97</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="A101" t="str">
+            <v>C39</v>
+          </cell>
+          <cell r="B101" t="str">
+            <v>x=62.78, y=81.82</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="A102" t="str">
+            <v>C40</v>
+          </cell>
+          <cell r="B102" t="str">
+            <v>x=28.96, y=81.75</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="A103" t="str">
+            <v>C41</v>
+          </cell>
+          <cell r="B103" t="str">
+            <v>x=56.61, y=85.78</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="A104" t="str">
+            <v>C42</v>
+          </cell>
+          <cell r="B104" t="str">
+            <v>x=35.13, y=85.78</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="A105" t="str">
+            <v>C43</v>
+          </cell>
+          <cell r="B105" t="str">
+            <v>x=58.70, y=85.78</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="A106" t="str">
+            <v>C44</v>
+          </cell>
+          <cell r="B106" t="str">
+            <v>x=32.93, y=85.92</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="A107" t="str">
+            <v>C45</v>
+          </cell>
+          <cell r="B107" t="str">
+            <v>x=60.65, y=85.63</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="A108" t="str">
+            <v>C46</v>
+          </cell>
+          <cell r="B108" t="str">
+            <v>x=30.95, y=85.85</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="A109" t="str">
+            <v>C47</v>
+          </cell>
+          <cell r="B109" t="str">
+            <v>x=62.81, y=85.85</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="A110" t="str">
+            <v>C48</v>
+          </cell>
+          <cell r="B110" t="str">
+            <v>x=28.93, y=85.85</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="A111" t="str">
+            <v>C49</v>
+          </cell>
+          <cell r="B111" t="str">
+            <v>x=56.64, y=89.73</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="A112" t="str">
+            <v>C50</v>
+          </cell>
+          <cell r="B112" t="str">
+            <v>x=35.06, y=89.58</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="A113" t="str">
+            <v>C51</v>
+          </cell>
+          <cell r="B113" t="str">
+            <v>x=58.74, y=89.73</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="A114" t="str">
+            <v>C52</v>
+          </cell>
+          <cell r="B114" t="str">
+            <v>x=32.97, y=89.80</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="A115" t="str">
+            <v>C53</v>
+          </cell>
+          <cell r="B115" t="str">
+            <v>x=60.76, y=89.73</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="A116" t="str">
+            <v>C54</v>
+          </cell>
+          <cell r="B116" t="str">
+            <v>x=31.06, y=89.87</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="A117" t="str">
+            <v>C55</v>
+          </cell>
+          <cell r="B117" t="str">
+            <v>x=62.70, y=89.73</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="A118" t="str">
+            <v>C56</v>
+          </cell>
+          <cell r="B118" t="str">
+            <v>x=28.93, y=89.66</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="A119" t="str">
+            <v>C57</v>
+          </cell>
+          <cell r="B119" t="str">
+            <v xml:space="preserve"> x=56.90, y=93.53</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="A120" t="str">
+            <v>C58</v>
+          </cell>
+          <cell r="B120" t="str">
+            <v>x=35.06, y=93.75</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="A121" t="str">
+            <v>C59</v>
+          </cell>
+          <cell r="B121" t="str">
+            <v>x=58.70, y=93.89</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="A122" t="str">
+            <v>C60</v>
+          </cell>
+          <cell r="B122" t="str">
+            <v>x=33.04, y=93.82</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="A123" t="str">
+            <v>C61</v>
+          </cell>
+          <cell r="B123" t="str">
+            <v>x=60.68, y=93.82</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="A124" t="str">
+            <v>C62</v>
+          </cell>
+          <cell r="B124" t="str">
+            <v>x=30.87, y=93.68</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="A125" t="str">
+            <v>C63</v>
+          </cell>
+          <cell r="B125" t="str">
+            <v>x=62.67, y=93.82</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="A126" t="str">
+            <v>C64</v>
+          </cell>
+          <cell r="B126" t="str">
+            <v>x=28.93, y=93.68</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="A127" t="str">
+            <v>D1</v>
+          </cell>
+          <cell r="B127" t="str">
+            <v>x=65.68, y=60.49</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="A128" t="str">
+            <v>D2</v>
+          </cell>
+          <cell r="B128" t="str">
+            <v>x=26.14, y=60.27</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="A129" t="str">
+            <v>D3</v>
+          </cell>
+          <cell r="B129" t="str">
+            <v>x=67.29, y=60.20</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="A130" t="str">
+            <v>D4</v>
+          </cell>
+          <cell r="B130" t="str">
+            <v>x=24.52, y=60.27</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="A131" t="str">
+            <v>D5</v>
+          </cell>
+          <cell r="B131" t="str">
+            <v>x=68.69, y=60.27</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="A132" t="str">
+            <v>D6</v>
+          </cell>
+          <cell r="B132" t="str">
+            <v>x=22.98, y=60.34</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="A133" t="str">
+            <v>D7</v>
+          </cell>
+          <cell r="B133" t="str">
+            <v>x=70.34, y=60.27</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="A134" t="str">
+            <v>D8</v>
+          </cell>
+          <cell r="B134" t="str">
+            <v>x=21.40, y=60.27</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="A135" t="str">
+            <v>D9</v>
+          </cell>
+          <cell r="B135" t="str">
+            <v>x=71.92, y=60.27</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="A136" t="str">
+            <v>D10</v>
+          </cell>
+          <cell r="B136" t="str">
+            <v>x=19.79, y=60.34</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="A137" t="str">
+            <v>D11</v>
+          </cell>
+          <cell r="B137" t="str">
+            <v>x=65.71, y=63.36</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="A138" t="str">
+            <v>D12</v>
+          </cell>
+          <cell r="B138" t="str">
+            <v>x=26.06, y=63.22</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="A139" t="str">
+            <v>D13</v>
+          </cell>
+          <cell r="B139" t="str">
+            <v>x=67.18, y=63.22</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="A140" t="str">
+            <v>D14</v>
+          </cell>
+          <cell r="B140" t="str">
+            <v>x=24.52, y=63.29</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="A141" t="str">
+            <v>D15</v>
+          </cell>
+          <cell r="B141" t="str">
+            <v>x=68.76, y=63.29</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="A142" t="str">
+            <v>D16</v>
+          </cell>
+          <cell r="B142" t="str">
+            <v>x=22.98, y=63.15</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="A143" t="str">
+            <v>D17</v>
+          </cell>
+          <cell r="B143" t="str">
+            <v>x=70.34, y=63.36</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="A144" t="str">
+            <v>D18</v>
+          </cell>
+          <cell r="B144" t="str">
+            <v>x=21.37, y=63.36</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="A145" t="str">
+            <v>D19</v>
+          </cell>
+          <cell r="B145" t="str">
+            <v>x=71.88, y=63.29</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="A146" t="str">
+            <v>D20</v>
+          </cell>
+          <cell r="B146" t="str">
+            <v>x=19.79, y=63.36</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="A147" t="str">
+            <v>D21</v>
+          </cell>
+          <cell r="B147" t="str">
+            <v>x=65.57, y=66.38</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="A148" t="str">
+            <v>D22</v>
+          </cell>
+          <cell r="B148" t="str">
+            <v>x=26.10, y=66.09</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="A149" t="str">
+            <v>D23</v>
+          </cell>
+          <cell r="B149" t="str">
+            <v>x=67.22, y=66.38</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="A150" t="str">
+            <v>D24</v>
+          </cell>
+          <cell r="B150" t="str">
+            <v>x=24.49, y=66.38</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="A151" t="str">
+            <v>D25</v>
+          </cell>
+          <cell r="B151" t="str">
+            <v>x=68.69, y=66.31</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="A152" t="str">
+            <v>D26</v>
+          </cell>
+          <cell r="B152" t="str">
+            <v>x=22.91, y=66.38</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="A153" t="str">
+            <v>D27</v>
+          </cell>
+          <cell r="B153" t="str">
+            <v>x=70.30, y=66.31</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="A154" t="str">
+            <v>D28</v>
+          </cell>
+          <cell r="B154" t="str">
+            <v>x=21.33, y=66.31</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="A155" t="str">
+            <v>D29</v>
+          </cell>
+          <cell r="B155" t="str">
+            <v>x=71.88, y=66.38</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="A156" t="str">
+            <v>D30</v>
+          </cell>
+          <cell r="B156" t="str">
+            <v>x=19.75, y=66.31</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="A157" t="str">
+            <v>D31</v>
+          </cell>
+          <cell r="B157" t="str">
+            <v>x=65.60, y=71.91</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="A158" t="str">
+            <v>D32</v>
+          </cell>
+          <cell r="B158" t="str">
+            <v>x=26.03, y=71.77</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="A159" t="str">
+            <v>D33</v>
+          </cell>
+          <cell r="B159" t="str">
+            <v>x=67.25, y=72.05</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="A160" t="str">
+            <v>D34</v>
+          </cell>
+          <cell r="B160" t="str">
+            <v>x=24.49, y=71.77</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="A161" t="str">
+            <v>D35</v>
+          </cell>
+          <cell r="B161" t="str">
+            <v>x=68.80, y=71.77</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="A162" t="str">
+            <v>D36</v>
+          </cell>
+          <cell r="B162" t="str">
+            <v>x=22.87, y=71.98</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="A163" t="str">
+            <v>D37</v>
+          </cell>
+          <cell r="B163" t="str">
+            <v>x=70.37, y=71.62</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="A164" t="str">
+            <v>D38</v>
+          </cell>
+          <cell r="B164" t="str">
+            <v>x=21.40, y=71.84</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="A165" t="str">
+            <v>D39</v>
+          </cell>
+          <cell r="B165" t="str">
+            <v>x=71.84, y=71.62</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="A166" t="str">
+            <v>D40</v>
+          </cell>
+          <cell r="B166" t="str">
+            <v>x=19.75, y=71.55</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="A167" t="str">
+            <v>D41</v>
+          </cell>
+          <cell r="B167" t="str">
+            <v>x=65.64, y=74.86</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="A168" t="str">
+            <v>D42</v>
+          </cell>
+          <cell r="B168" t="str">
+            <v>x=26.03, y=74.78</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="A169" t="str">
+            <v>D43</v>
+          </cell>
+          <cell r="B169" t="str">
+            <v>x=67.25, y=74.78</v>
+          </cell>
+        </row>
+        <row r="170">
+          <cell r="A170" t="str">
+            <v>D44</v>
+          </cell>
+          <cell r="B170" t="str">
+            <v>x=24.52, y=74.78</v>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="A171" t="str">
+            <v>D45</v>
+          </cell>
+          <cell r="B171" t="str">
+            <v>x=68.72, y=74.78</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="A172" t="str">
+            <v>D46</v>
+          </cell>
+          <cell r="B172" t="str">
+            <v>x=22.91, y=74.93</v>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="A173" t="str">
+            <v>D47</v>
+          </cell>
+          <cell r="B173" t="str">
+            <v>x=70.30, y=74.86</v>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="A174" t="str">
+            <v>D48</v>
+          </cell>
+          <cell r="B174" t="str">
+            <v>x=21.37, y=74.64</v>
+          </cell>
+        </row>
+        <row r="175">
+          <cell r="A175" t="str">
+            <v>D49</v>
+          </cell>
+          <cell r="B175" t="str">
+            <v>x=71.92, y=74.71</v>
+          </cell>
+        </row>
+        <row r="176">
+          <cell r="A176" t="str">
+            <v>D50</v>
+          </cell>
+          <cell r="B176" t="str">
+            <v>x=19.79, y=74.64</v>
+          </cell>
+        </row>
+        <row r="177">
+          <cell r="A177" t="str">
+            <v>D51</v>
+          </cell>
+          <cell r="B177" t="str">
+            <v>x=65.68, y=77.66</v>
+          </cell>
+        </row>
+        <row r="178">
+          <cell r="A178" t="str">
+            <v>D52</v>
+          </cell>
+          <cell r="B178" t="str">
+            <v>x=26.10, y=77.73</v>
+          </cell>
+        </row>
+        <row r="179">
+          <cell r="A179" t="str">
+            <v>D53</v>
+          </cell>
+          <cell r="B179" t="str">
+            <v>x=67.14, y=77.73</v>
+          </cell>
+        </row>
+        <row r="180">
+          <cell r="A180" t="str">
+            <v>D54</v>
+          </cell>
+          <cell r="B180" t="str">
+            <v>x=24.52, y=77.80</v>
+          </cell>
+        </row>
+        <row r="181">
+          <cell r="A181" t="str">
+            <v>D55</v>
+          </cell>
+          <cell r="B181" t="str">
+            <v>x=68.72, y=77.80</v>
+          </cell>
+        </row>
+        <row r="182">
+          <cell r="A182" t="str">
+            <v>D56</v>
+          </cell>
+          <cell r="B182" t="str">
+            <v>x=22.91, y=77.80</v>
+          </cell>
+        </row>
+        <row r="183">
+          <cell r="A183" t="str">
+            <v>D57</v>
+          </cell>
+          <cell r="B183" t="str">
+            <v>x=70.30, y=77.73</v>
+          </cell>
+        </row>
+        <row r="184">
+          <cell r="A184" t="str">
+            <v>D58</v>
+          </cell>
+          <cell r="B184" t="str">
+            <v>x=21.44, y=77.87</v>
+          </cell>
+        </row>
+        <row r="185">
+          <cell r="A185" t="str">
+            <v>D59</v>
+          </cell>
+          <cell r="B185" t="str">
+            <v>x=71.92, y=77.66</v>
+          </cell>
+        </row>
+        <row r="186">
+          <cell r="A186" t="str">
+            <v>D60</v>
+          </cell>
+          <cell r="B186" t="str">
+            <v>x=19.82, y=77.80</v>
+          </cell>
+        </row>
+        <row r="187">
+          <cell r="A187" t="str">
+            <v>D61</v>
+          </cell>
+          <cell r="B187" t="str">
+            <v>x=65.60, y=80.82</v>
+          </cell>
+        </row>
+        <row r="188">
+          <cell r="A188" t="str">
+            <v>D62</v>
+          </cell>
+          <cell r="B188" t="str">
+            <v>x=26.03, y=80.96</v>
+          </cell>
+        </row>
+        <row r="189">
+          <cell r="A189" t="str">
+            <v>D63</v>
+          </cell>
+          <cell r="B189" t="str">
+            <v>x=67.18, y=80.68</v>
+          </cell>
+        </row>
+        <row r="190">
+          <cell r="A190" t="str">
+            <v>D64</v>
+          </cell>
+          <cell r="B190" t="str">
+            <v>x=24.45, y=80.82</v>
+          </cell>
+        </row>
+        <row r="191">
+          <cell r="A191" t="str">
+            <v>D65</v>
+          </cell>
+          <cell r="B191" t="str">
+            <v>x=68.76, y=80.75</v>
+          </cell>
+        </row>
+        <row r="192">
+          <cell r="A192" t="str">
+            <v>D66</v>
+          </cell>
+          <cell r="B192" t="str">
+            <v>x=22.83, y=80.89</v>
+          </cell>
+        </row>
+        <row r="193">
+          <cell r="A193" t="str">
+            <v>D67</v>
+          </cell>
+          <cell r="B193" t="str">
+            <v>x=70.34, y=80.89</v>
+          </cell>
+        </row>
+        <row r="194">
+          <cell r="A194" t="str">
+            <v>D68</v>
+          </cell>
+          <cell r="B194" t="str">
+            <v>x=21.33, y=80.75</v>
+          </cell>
+        </row>
+        <row r="195">
+          <cell r="A195" t="str">
+            <v>D69</v>
+          </cell>
+          <cell r="B195" t="str">
+            <v>x=71.99, y=80.82</v>
+          </cell>
+        </row>
+        <row r="196">
+          <cell r="A196" t="str">
+            <v>D70</v>
+          </cell>
+          <cell r="B196" t="str">
+            <v>x=19.71, y=80.75</v>
+          </cell>
+        </row>
+        <row r="197">
+          <cell r="A197" t="str">
+            <v>D71</v>
+          </cell>
+          <cell r="B197" t="str">
+            <v>x=65.71, y=85.92</v>
+          </cell>
+        </row>
+        <row r="198">
+          <cell r="A198" t="str">
+            <v>D72</v>
+          </cell>
+          <cell r="B198" t="str">
+            <v>x=26.03, y=86.14</v>
+          </cell>
+        </row>
+        <row r="199">
+          <cell r="A199" t="str">
+            <v>D73</v>
+          </cell>
+          <cell r="B199" t="str">
+            <v>x=67.22, y=86.14</v>
+          </cell>
+        </row>
+        <row r="200">
+          <cell r="A200" t="str">
+            <v>D74</v>
+          </cell>
+          <cell r="B200" t="str">
+            <v>x=24.49, y=86.21</v>
+          </cell>
+        </row>
+        <row r="201">
+          <cell r="A201" t="str">
+            <v>D75</v>
+          </cell>
+          <cell r="B201" t="str">
+            <v>x=68.76, y=86.28</v>
+          </cell>
+        </row>
+        <row r="202">
+          <cell r="A202" t="str">
+            <v>D76</v>
+          </cell>
+          <cell r="B202" t="str">
+            <v>x=23.05, y=86.14</v>
+          </cell>
+        </row>
+        <row r="203">
+          <cell r="A203" t="str">
+            <v>D77</v>
+          </cell>
+          <cell r="B203" t="str">
+            <v>x=70.63, y=86.21</v>
+          </cell>
+        </row>
+        <row r="204">
+          <cell r="A204" t="str">
+            <v>D78</v>
+          </cell>
+          <cell r="B204" t="str">
+            <v>x=21.40, y=86.14</v>
+          </cell>
+        </row>
+        <row r="205">
+          <cell r="A205" t="str">
+            <v>D79</v>
+          </cell>
+          <cell r="B205" t="str">
+            <v>x=71.99, y=86.35</v>
+          </cell>
+        </row>
+        <row r="206">
+          <cell r="A206" t="str">
+            <v>D80</v>
+          </cell>
+          <cell r="B206" t="str">
+            <v>x=19.86, y=86.06</v>
+          </cell>
+        </row>
+        <row r="207">
+          <cell r="A207" t="str">
+            <v>D81</v>
+          </cell>
+          <cell r="B207" t="str">
+            <v>x=65.71, y=89.30</v>
+          </cell>
+        </row>
+        <row r="208">
+          <cell r="A208" t="str">
+            <v>D82</v>
+          </cell>
+          <cell r="B208" t="str">
+            <v>x=26.06, y=89.22</v>
+          </cell>
+        </row>
+        <row r="209">
+          <cell r="A209" t="str">
+            <v>D83</v>
+          </cell>
+          <cell r="B209" t="str">
+            <v>x=67.14, y=89.15</v>
+          </cell>
+        </row>
+        <row r="210">
+          <cell r="A210" t="str">
+            <v>D84</v>
+          </cell>
+          <cell r="B210" t="str">
+            <v>x=24.45, y=89.22</v>
+          </cell>
+        </row>
+        <row r="211">
+          <cell r="A211" t="str">
+            <v>D85</v>
+          </cell>
+          <cell r="B211" t="str">
+            <v>x=68.80, y=88.94</v>
+          </cell>
+        </row>
+        <row r="212">
+          <cell r="A212" t="str">
+            <v>D86</v>
+          </cell>
+          <cell r="B212" t="str">
+            <v>x=22.94, y=89.30</v>
+          </cell>
+        </row>
+        <row r="213">
+          <cell r="A213" t="str">
+            <v>D87</v>
+          </cell>
+          <cell r="B213" t="str">
+            <v>x=70.30, y=89.15</v>
+          </cell>
+        </row>
+        <row r="214">
+          <cell r="A214" t="str">
+            <v>D88</v>
+          </cell>
+          <cell r="B214" t="str">
+            <v>x=21.37, y=89.01</v>
+          </cell>
+        </row>
+        <row r="215">
+          <cell r="A215" t="str">
+            <v>D89</v>
+          </cell>
+          <cell r="B215" t="str">
+            <v>x=71.95, y=89.51</v>
+          </cell>
+        </row>
+        <row r="216">
+          <cell r="A216" t="str">
+            <v>D90</v>
+          </cell>
+          <cell r="B216" t="str">
+            <v>x=19.79, y=89.08</v>
+          </cell>
+        </row>
+        <row r="217">
+          <cell r="A217" t="str">
+            <v>D91</v>
+          </cell>
+          <cell r="B217" t="str">
+            <v>x=65.64, y=92.24</v>
+          </cell>
+        </row>
+        <row r="218">
+          <cell r="A218" t="str">
+            <v>D92</v>
+          </cell>
+          <cell r="B218" t="str">
+            <v>x=25.95, y=92.31</v>
+          </cell>
+        </row>
+        <row r="219">
+          <cell r="A219" t="str">
+            <v>D93</v>
+          </cell>
+          <cell r="B219" t="str">
+            <v>x=67.18, y=92.24</v>
+          </cell>
+        </row>
+        <row r="220">
+          <cell r="A220" t="str">
+            <v>D94</v>
+          </cell>
+          <cell r="B220" t="str">
+            <v>x=24.49, y=92.24</v>
+          </cell>
+        </row>
+        <row r="221">
+          <cell r="A221" t="str">
+            <v>D95</v>
+          </cell>
+          <cell r="B221" t="str">
+            <v>x=68.76, y=92.24</v>
+          </cell>
+        </row>
+        <row r="222">
+          <cell r="A222" t="str">
+            <v>D96</v>
+          </cell>
+          <cell r="B222" t="str">
+            <v>x=22.91, y=92.24</v>
+          </cell>
+        </row>
+        <row r="223">
+          <cell r="A223" t="str">
+            <v>D97</v>
+          </cell>
+          <cell r="B223" t="str">
+            <v>x=70.26, y=92.24</v>
+          </cell>
+        </row>
+        <row r="224">
+          <cell r="A224" t="str">
+            <v>D98</v>
+          </cell>
+          <cell r="B224" t="str">
+            <v>x=21.26, y=92.24</v>
+          </cell>
+        </row>
+        <row r="225">
+          <cell r="A225" t="str">
+            <v>D99</v>
+          </cell>
+          <cell r="B225" t="str">
+            <v>x=71.88, y=92.39</v>
+          </cell>
+        </row>
+        <row r="226">
+          <cell r="A226" t="str">
+            <v>D100</v>
+          </cell>
+          <cell r="B226" t="str">
+            <v>x=19.82, y=92.24</v>
+          </cell>
+        </row>
+        <row r="227">
+          <cell r="A227" t="str">
+            <v>D101</v>
+          </cell>
+        </row>
+        <row r="228">
+          <cell r="A228" t="str">
+            <v>D102</v>
+          </cell>
+          <cell r="B228" t="str">
+            <v>x=26.06, y=95.33</v>
+          </cell>
+        </row>
+        <row r="229">
+          <cell r="A229" t="str">
+            <v>D103</v>
+          </cell>
+          <cell r="B229" t="str">
+            <v>x=67.29, y=95.26</v>
+          </cell>
+        </row>
+        <row r="230">
+          <cell r="A230" t="str">
+            <v>D104</v>
+          </cell>
+          <cell r="B230" t="str">
+            <v>x=24.45, y=95.40</v>
+          </cell>
+        </row>
+        <row r="231">
+          <cell r="A231" t="str">
+            <v>D105</v>
+          </cell>
+          <cell r="B231" t="str">
+            <v>x=68.76, y=95.33</v>
+          </cell>
+        </row>
+        <row r="232">
+          <cell r="A232" t="str">
+            <v>D106</v>
+          </cell>
+          <cell r="B232" t="str">
+            <v>x=22.94, y=95.40</v>
+          </cell>
+        </row>
+        <row r="233">
+          <cell r="A233" t="str">
+            <v>D107</v>
+          </cell>
+          <cell r="B233" t="str">
+            <v>x=70.30, y=95.47</v>
+          </cell>
+        </row>
+        <row r="234">
+          <cell r="A234" t="str">
+            <v>D108</v>
+          </cell>
+          <cell r="B234" t="str">
+            <v>x=21.37, y=95.33</v>
+          </cell>
+        </row>
+        <row r="235">
+          <cell r="A235" t="str">
+            <v>D109</v>
+          </cell>
+          <cell r="B235" t="str">
+            <v>x=71.92, y=95.40</v>
+          </cell>
+        </row>
+        <row r="236">
+          <cell r="A236" t="str">
+            <v>D110</v>
+          </cell>
+          <cell r="B236" t="str">
+            <v>x=19.86, y=95.33</v>
+          </cell>
+        </row>
+        <row r="237">
+          <cell r="A237" t="str">
+            <v>E1</v>
+          </cell>
+          <cell r="B237" t="str">
+            <v>x=74.60, y=60.20</v>
+          </cell>
+        </row>
+        <row r="238">
+          <cell r="A238" t="str">
+            <v>E2</v>
+          </cell>
+          <cell r="B238" t="str">
+            <v>x=17.14, y=60.34</v>
+          </cell>
+        </row>
+        <row r="239">
+          <cell r="A239" t="str">
+            <v>E3</v>
+          </cell>
+          <cell r="B239" t="str">
+            <v>x=76.17, y=60.13</v>
+          </cell>
+        </row>
+        <row r="240">
+          <cell r="A240" t="str">
+            <v>E4</v>
+          </cell>
+          <cell r="B240" t="str">
+            <v>x=15.49, y=60.42</v>
+          </cell>
+        </row>
+        <row r="241">
+          <cell r="A241" t="str">
+            <v>E5</v>
+          </cell>
+          <cell r="B241" t="str">
+            <v>x=77.72, y=60.13</v>
+          </cell>
+        </row>
+        <row r="242">
+          <cell r="A242" t="str">
+            <v>E6</v>
+          </cell>
+          <cell r="B242" t="str">
+            <v>x=13.95, y=60.06</v>
+          </cell>
+        </row>
+        <row r="243">
+          <cell r="A243" t="str">
+            <v>E7</v>
+          </cell>
+          <cell r="B243" t="str">
+            <v>x=79.37, y=60.27</v>
+          </cell>
+        </row>
+        <row r="244">
+          <cell r="A244" t="str">
+            <v>E8</v>
+          </cell>
+          <cell r="B244" t="str">
+            <v>x=12.44, y=60.20</v>
+          </cell>
+        </row>
+        <row r="245">
+          <cell r="A245" t="str">
+            <v>E9</v>
+          </cell>
+          <cell r="B245" t="str">
+            <v>x=80.91, y=60.20</v>
+          </cell>
+        </row>
+        <row r="246">
+          <cell r="A246" t="str">
+            <v>E10</v>
+          </cell>
+          <cell r="B246" t="str">
+            <v>x=10.83, y=60.20</v>
+          </cell>
+        </row>
+        <row r="247">
+          <cell r="A247" t="str">
+            <v>E11</v>
+          </cell>
+          <cell r="B247" t="str">
+            <v>x=74.56, y=63.36</v>
+          </cell>
+        </row>
+        <row r="248">
+          <cell r="A248" t="str">
+            <v>E12</v>
+          </cell>
+          <cell r="B248" t="str">
+            <v>x=17.03, y=63.29</v>
+          </cell>
+        </row>
+        <row r="249">
+          <cell r="A249" t="str">
+            <v>E13</v>
+          </cell>
+          <cell r="B249" t="str">
+            <v>x=76.17, y=63.07</v>
+          </cell>
+        </row>
+        <row r="250">
+          <cell r="A250" t="str">
+            <v>E14</v>
+          </cell>
+          <cell r="B250" t="str">
+            <v>x=15.53, y=63.29</v>
+          </cell>
+        </row>
+        <row r="251">
+          <cell r="A251" t="str">
+            <v>E15</v>
+          </cell>
+          <cell r="B251" t="str">
+            <v>x=77.72, y=63.29</v>
+          </cell>
+        </row>
+        <row r="252">
+          <cell r="A252" t="str">
+            <v>E16</v>
+          </cell>
+          <cell r="B252" t="str">
+            <v>x=13.95, y=63.22</v>
+          </cell>
+        </row>
+        <row r="253">
+          <cell r="A253" t="str">
+            <v>E17</v>
+          </cell>
+          <cell r="B253" t="str">
+            <v>x=79.37, y=63.15</v>
+          </cell>
+        </row>
+        <row r="254">
+          <cell r="A254" t="str">
+            <v>E18</v>
+          </cell>
+          <cell r="B254" t="str">
+            <v>x=12.56, y=63.36</v>
+          </cell>
+        </row>
+        <row r="255">
+          <cell r="A255" t="str">
+            <v>E19</v>
+          </cell>
+          <cell r="B255" t="str">
+            <v>x=80.95, y=63.22</v>
+          </cell>
+        </row>
+        <row r="256">
+          <cell r="A256" t="str">
+            <v>E20</v>
+          </cell>
+          <cell r="B256" t="str">
+            <v>x=10.90, y=63.07</v>
+          </cell>
+        </row>
+        <row r="257">
+          <cell r="A257" t="str">
+            <v>E21</v>
+          </cell>
+          <cell r="B257" t="str">
+            <v>x=82.42, y=63.29</v>
+          </cell>
+        </row>
+        <row r="258">
+          <cell r="A258" t="str">
+            <v>E22</v>
+          </cell>
+          <cell r="B258" t="str">
+            <v>x=9.25, y=63.07</v>
+          </cell>
+        </row>
+        <row r="259">
+          <cell r="A259" t="str">
+            <v>E23</v>
+          </cell>
+          <cell r="B259" t="str">
+            <v>x=74.60, y=66.16</v>
+          </cell>
+        </row>
+        <row r="260">
+          <cell r="A260" t="str">
+            <v>E24</v>
+          </cell>
+          <cell r="B260" t="str">
+            <v>x=17.07, y=66.45</v>
+          </cell>
+        </row>
+        <row r="261">
+          <cell r="A261" t="str">
+            <v>E25</v>
+          </cell>
+          <cell r="B261" t="str">
+            <v>x=76.17, y=66.31</v>
+          </cell>
+        </row>
+        <row r="262">
+          <cell r="A262" t="str">
+            <v>E26</v>
+          </cell>
+          <cell r="B262" t="str">
+            <v>x=15.57, y=66.31</v>
+          </cell>
+        </row>
+        <row r="263">
+          <cell r="A263" t="str">
+            <v>E27</v>
+          </cell>
+          <cell r="B263" t="str">
+            <v>x=77.64, y=66.45</v>
+          </cell>
+        </row>
+        <row r="264">
+          <cell r="A264" t="str">
+            <v>E28</v>
+          </cell>
+          <cell r="B264" t="str">
+            <v>x=13.95, y=66.09</v>
+          </cell>
+        </row>
+        <row r="265">
+          <cell r="A265" t="str">
+            <v>E29</v>
+          </cell>
+          <cell r="B265" t="str">
+            <v>x=79.30, y=66.38</v>
+          </cell>
+        </row>
+        <row r="266">
+          <cell r="A266" t="str">
+            <v>E30</v>
+          </cell>
+          <cell r="B266" t="str">
+            <v>x=12.37, y=66.24</v>
+          </cell>
+        </row>
+        <row r="267">
+          <cell r="A267" t="str">
+            <v>E31</v>
+          </cell>
+          <cell r="B267" t="str">
+            <v>x=80.95, y=66.31</v>
+          </cell>
+        </row>
+        <row r="268">
+          <cell r="A268" t="str">
+            <v>E32</v>
+          </cell>
+          <cell r="B268" t="str">
+            <v>x=10.79, y=66.31</v>
+          </cell>
+        </row>
+        <row r="269">
+          <cell r="A269" t="str">
+            <v>E33</v>
+          </cell>
+          <cell r="B269" t="str">
+            <v>x=82.42, y=66.24</v>
+          </cell>
+        </row>
+        <row r="270">
+          <cell r="A270" t="str">
+            <v>E34</v>
+          </cell>
+          <cell r="B270" t="str">
+            <v>x=9.36, y=66.24</v>
+          </cell>
+        </row>
+        <row r="271">
+          <cell r="A271" t="str">
+            <v>E35</v>
+          </cell>
+          <cell r="B271" t="str">
+            <v>x=74.52, y=71.70</v>
+          </cell>
+        </row>
+        <row r="272">
+          <cell r="A272" t="str">
+            <v>E36</v>
+          </cell>
+          <cell r="B272" t="str">
+            <v>x=7.97, y=66.52</v>
+          </cell>
+        </row>
+        <row r="273">
+          <cell r="A273" t="str">
+            <v>E37</v>
+          </cell>
+          <cell r="B273" t="str">
+            <v>x=76.21, y=71.70</v>
+          </cell>
+        </row>
+        <row r="274">
+          <cell r="A274" t="str">
+            <v>E38</v>
+          </cell>
+          <cell r="B274" t="str">
+            <v>x=17.14, y=71.77</v>
+          </cell>
+        </row>
+        <row r="275">
+          <cell r="A275" t="str">
+            <v>E39</v>
+          </cell>
+          <cell r="B275" t="str">
+            <v>x=77.83, y=71.70</v>
+          </cell>
+        </row>
+        <row r="276">
+          <cell r="A276" t="str">
+            <v>E40</v>
+          </cell>
+          <cell r="B276" t="str">
+            <v>x=15.60, y=71.48</v>
+          </cell>
+        </row>
+        <row r="277">
+          <cell r="A277" t="str">
+            <v>E41</v>
+          </cell>
+          <cell r="B277" t="str">
+            <v>x=79.26, y=71.77</v>
+          </cell>
+        </row>
+        <row r="278">
+          <cell r="A278" t="str">
+            <v>E42</v>
+          </cell>
+          <cell r="B278" t="str">
+            <v>x=13.84, y=71.70</v>
+          </cell>
+        </row>
+        <row r="279">
+          <cell r="A279" t="str">
+            <v>E43</v>
+          </cell>
+          <cell r="B279" t="str">
+            <v>x=81.02, y=71.55</v>
+          </cell>
+        </row>
+        <row r="280">
+          <cell r="A280" t="str">
+            <v>E44</v>
+          </cell>
+          <cell r="B280" t="str">
+            <v>x=12.41, y=71.55</v>
+          </cell>
+        </row>
+        <row r="281">
+          <cell r="A281" t="str">
+            <v>E45</v>
+          </cell>
+          <cell r="B281" t="str">
+            <v>x=82.53, y=71.41</v>
+          </cell>
+        </row>
+        <row r="282">
+          <cell r="A282" t="str">
+            <v>E46</v>
+          </cell>
+          <cell r="B282" t="str">
+            <v>x=10.83, y=71.62</v>
+          </cell>
+        </row>
+        <row r="283">
+          <cell r="A283" t="str">
+            <v>E47</v>
+          </cell>
+          <cell r="B283" t="str">
+            <v>x=74.67, y=74.64</v>
+          </cell>
+        </row>
+        <row r="284">
+          <cell r="A284" t="str">
+            <v>E48</v>
+          </cell>
+          <cell r="B284" t="str">
+            <v>x=9.32, y=71.70</v>
+          </cell>
+        </row>
+        <row r="285">
+          <cell r="A285" t="str">
+            <v>E49</v>
+          </cell>
+          <cell r="B285" t="str">
+            <v>x=76.17, y=74.71</v>
+          </cell>
+        </row>
+        <row r="286">
+          <cell r="A286" t="str">
+            <v>E50</v>
+          </cell>
+          <cell r="B286" t="str">
+            <v>x=7.78, y=71.70</v>
+          </cell>
+        </row>
+        <row r="287">
+          <cell r="A287" t="str">
+            <v>E51</v>
+          </cell>
+          <cell r="B287" t="str">
+            <v>x=77.75, y=74.64</v>
+          </cell>
+        </row>
+        <row r="288">
+          <cell r="A288" t="str">
+            <v>E52</v>
+          </cell>
+          <cell r="B288" t="str">
+            <v>x=6.09, y=71.62</v>
+          </cell>
+        </row>
+        <row r="289">
+          <cell r="A289" t="str">
+            <v>E53</v>
+          </cell>
+          <cell r="B289" t="str">
+            <v>x=79.30, y=74.78</v>
+          </cell>
+        </row>
+        <row r="290">
+          <cell r="A290" t="str">
+            <v>E54</v>
+          </cell>
+          <cell r="B290" t="str">
+            <v>x=17.03, y=74.78</v>
+          </cell>
+        </row>
+        <row r="291">
+          <cell r="A291" t="str">
+            <v>E55</v>
+          </cell>
+          <cell r="B291" t="str">
+            <v>x=80.87, y=74.64</v>
+          </cell>
+        </row>
+        <row r="292">
+          <cell r="A292" t="str">
+            <v>E56</v>
+          </cell>
+          <cell r="B292" t="str">
+            <v>x=15.64, y=74.78</v>
+          </cell>
+        </row>
+        <row r="293">
+          <cell r="A293" t="str">
+            <v>E57</v>
+          </cell>
+          <cell r="B293" t="str">
+            <v>x=82.42, y=74.64</v>
+          </cell>
+        </row>
+        <row r="294">
+          <cell r="A294" t="str">
+            <v>E58</v>
+          </cell>
+          <cell r="B294" t="str">
+            <v>x=13.99, y=74.78</v>
+          </cell>
+        </row>
+        <row r="295">
+          <cell r="A295" t="str">
+            <v>E59</v>
+          </cell>
+          <cell r="B295" t="str">
+            <v>x=74.71, y=78.02</v>
+          </cell>
+        </row>
+        <row r="296">
+          <cell r="A296" t="str">
+            <v>E60</v>
+          </cell>
+          <cell r="B296" t="str">
+            <v>x=12.44, y=74.86</v>
+          </cell>
+        </row>
+        <row r="297">
+          <cell r="A297" t="str">
+            <v>E61</v>
+          </cell>
+          <cell r="B297" t="str">
+            <v>x=76.06, y=77.73</v>
+          </cell>
+        </row>
+        <row r="298">
+          <cell r="A298" t="str">
+            <v>E62</v>
+          </cell>
+          <cell r="B298" t="str">
+            <v>x=10.90, y=74.86</v>
+          </cell>
+        </row>
+        <row r="299">
+          <cell r="A299" t="str">
+            <v>E63</v>
+          </cell>
+          <cell r="B299" t="str">
+            <v>x=77.79, y=77.95</v>
+          </cell>
+        </row>
+        <row r="300">
+          <cell r="A300" t="str">
+            <v>E64</v>
+          </cell>
+          <cell r="B300" t="str">
+            <v>x=9.25, y=74.78</v>
+          </cell>
+        </row>
+        <row r="301">
+          <cell r="A301" t="str">
+            <v>E65</v>
+          </cell>
+          <cell r="B301" t="str">
+            <v>x=79.30, y=77.66</v>
+          </cell>
+        </row>
+        <row r="302">
+          <cell r="A302" t="str">
+            <v>E66</v>
+          </cell>
+          <cell r="B302" t="str">
+            <v>x=7.78, y=74.78</v>
+          </cell>
+        </row>
+        <row r="303">
+          <cell r="A303" t="str">
+            <v>E67</v>
+          </cell>
+          <cell r="B303" t="str">
+            <v>x=80.84, y=77.73</v>
+          </cell>
+        </row>
+        <row r="304">
+          <cell r="A304" t="str">
+            <v>E68</v>
+          </cell>
+          <cell r="B304" t="str">
+            <v>x=6.13, y=74.50</v>
+          </cell>
+        </row>
+        <row r="305">
+          <cell r="A305" t="str">
+            <v>E69</v>
+          </cell>
+          <cell r="B305" t="str">
+            <v>x=82.34, y=77.80</v>
+          </cell>
+        </row>
+        <row r="306">
+          <cell r="A306" t="str">
+            <v>E70</v>
+          </cell>
+          <cell r="B306" t="str">
+            <v>x=17.11, y=77.80</v>
+          </cell>
+        </row>
+        <row r="307">
+          <cell r="A307" t="str">
+            <v>E71</v>
+          </cell>
+          <cell r="B307" t="str">
+            <v>x=74.67, y=80.82</v>
+          </cell>
+        </row>
+        <row r="308">
+          <cell r="A308" t="str">
+            <v>E72</v>
+          </cell>
+          <cell r="B308" t="str">
+            <v>x=15.53, y=77.87</v>
+          </cell>
+        </row>
+        <row r="309">
+          <cell r="A309" t="str">
+            <v>E73</v>
+          </cell>
+          <cell r="B309" t="str">
+            <v>x=76.21, y=80.82</v>
+          </cell>
+        </row>
+        <row r="310">
+          <cell r="A310" t="str">
+            <v>E74</v>
+          </cell>
+          <cell r="B310" t="str">
+            <v>x=13.99, y=77.80</v>
+          </cell>
+        </row>
+        <row r="311">
+          <cell r="A311" t="str">
+            <v>E75</v>
+          </cell>
+          <cell r="B311" t="str">
+            <v>x=77.83, y=80.60</v>
+          </cell>
+        </row>
+        <row r="312">
+          <cell r="A312" t="str">
+            <v>E76</v>
+          </cell>
+          <cell r="B312" t="str">
+            <v>x=12.41, y=77.80</v>
+          </cell>
+        </row>
+        <row r="313">
+          <cell r="A313" t="str">
+            <v>E77</v>
+          </cell>
+          <cell r="B313" t="str">
+            <v>x=79.33, y=80.89</v>
+          </cell>
+        </row>
+        <row r="314">
+          <cell r="A314" t="str">
+            <v>E78</v>
+          </cell>
+          <cell r="B314" t="str">
+            <v>x=10.98, y=77.73</v>
+          </cell>
+        </row>
+        <row r="315">
+          <cell r="A315" t="str">
+            <v>E79</v>
+          </cell>
+          <cell r="B315" t="str">
+            <v>x=80.80, y=80.96</v>
+          </cell>
+        </row>
+        <row r="316">
+          <cell r="A316" t="str">
+            <v>E80</v>
+          </cell>
+          <cell r="B316" t="str">
+            <v>x=9.32, y=77.80</v>
+          </cell>
+        </row>
+        <row r="317">
+          <cell r="A317" t="str">
+            <v>E81</v>
+          </cell>
+          <cell r="B317" t="str">
+            <v>x=82.34, y=80.75</v>
+          </cell>
+        </row>
+        <row r="318">
+          <cell r="A318" t="str">
+            <v>E82</v>
+          </cell>
+          <cell r="B318" t="str">
+            <v>x=7.67, y=78.02</v>
+          </cell>
+        </row>
+        <row r="319">
+          <cell r="A319" t="str">
+            <v>E83</v>
+          </cell>
+          <cell r="B319" t="str">
+            <v>x=74.56, y=86.14</v>
+          </cell>
+        </row>
+        <row r="320">
+          <cell r="A320" t="str">
+            <v>E84</v>
+          </cell>
+          <cell r="B320" t="str">
+            <v>x=17.07, y=80.75</v>
+          </cell>
+        </row>
+        <row r="321">
+          <cell r="A321" t="str">
+            <v>E85</v>
+          </cell>
+          <cell r="B321" t="str">
+            <v>x=76.28, y=86.14</v>
+          </cell>
+        </row>
+        <row r="322">
+          <cell r="A322" t="str">
+            <v>E86</v>
+          </cell>
+          <cell r="B322" t="str">
+            <v>x=15.38, y=80.53</v>
+          </cell>
+        </row>
+        <row r="323">
+          <cell r="A323" t="str">
+            <v>E87</v>
+          </cell>
+          <cell r="B323" t="str">
+            <v>x=77.57, y=85.99</v>
+          </cell>
+        </row>
+        <row r="324">
+          <cell r="A324" t="str">
+            <v>E88</v>
+          </cell>
+          <cell r="B324" t="str">
+            <v>x=13.95, y=80.68</v>
+          </cell>
+        </row>
+        <row r="325">
+          <cell r="A325" t="str">
+            <v>E89</v>
+          </cell>
+          <cell r="B325" t="str">
+            <v>x=79.33, y=86.06</v>
+          </cell>
+        </row>
+        <row r="326">
+          <cell r="A326" t="str">
+            <v>E90</v>
+          </cell>
+          <cell r="B326" t="str">
+            <v>x=12.48, y=80.60</v>
+          </cell>
+        </row>
+        <row r="327">
+          <cell r="A327" t="str">
+            <v>E91</v>
+          </cell>
+          <cell r="B327" t="str">
+            <v>x=80.87, y=85.99</v>
+          </cell>
+        </row>
+        <row r="328">
+          <cell r="A328" t="str">
+            <v>E92</v>
+          </cell>
+          <cell r="B328" t="str">
+            <v>x=10.94, y=80.96</v>
+          </cell>
+        </row>
+        <row r="329">
+          <cell r="A329" t="str">
+            <v>E93</v>
+          </cell>
+          <cell r="B329" t="str">
+            <v>x=74.63, y=89.22</v>
+          </cell>
+        </row>
+        <row r="330">
+          <cell r="A330" t="str">
+            <v>E94</v>
+          </cell>
+          <cell r="B330" t="str">
+            <v>x=9.25, y=80.82</v>
+          </cell>
+        </row>
+        <row r="331">
+          <cell r="A331" t="str">
+            <v>E95</v>
+          </cell>
+          <cell r="B331" t="str">
+            <v>x=76.21, y=89.22</v>
+          </cell>
+        </row>
+        <row r="332">
+          <cell r="A332" t="str">
+            <v>E96</v>
+          </cell>
+          <cell r="B332" t="str">
+            <v>x=17.18, y=86.06</v>
+          </cell>
+        </row>
+        <row r="333">
+          <cell r="A333" t="str">
+            <v>E97</v>
+          </cell>
+          <cell r="B333" t="str">
+            <v>x=77.83, y=89.15</v>
+          </cell>
+        </row>
+        <row r="334">
+          <cell r="A334" t="str">
+            <v>E98</v>
+          </cell>
+          <cell r="B334" t="str">
+            <v>x=15.49, y=86.21</v>
+          </cell>
+        </row>
+        <row r="335">
+          <cell r="A335" t="str">
+            <v>E99</v>
+          </cell>
+          <cell r="B335" t="str">
+            <v>x=79.33, y=89.08</v>
+          </cell>
+        </row>
+        <row r="336">
+          <cell r="A336" t="str">
+            <v>E100</v>
+          </cell>
+          <cell r="B336" t="str">
+            <v>x=13.88, y=85.78</v>
+          </cell>
+        </row>
+        <row r="337">
+          <cell r="A337" t="str">
+            <v>E101</v>
+          </cell>
+          <cell r="B337" t="str">
+            <v>x=74.67, y=92.17</v>
+          </cell>
+        </row>
+        <row r="338">
+          <cell r="A338" t="str">
+            <v>E102</v>
+          </cell>
+          <cell r="B338" t="str">
+            <v>x=12.48, y=86.06</v>
+          </cell>
+        </row>
+        <row r="339">
+          <cell r="A339" t="str">
+            <v>E103</v>
+          </cell>
+          <cell r="B339" t="str">
+            <v>x=76.25, y=92.24</v>
+          </cell>
+        </row>
+        <row r="340">
+          <cell r="A340" t="str">
+            <v>E104</v>
+          </cell>
+          <cell r="B340" t="str">
+            <v>x=17.03, y=89.15</v>
+          </cell>
+        </row>
+        <row r="341">
+          <cell r="A341" t="str">
+            <v>E105</v>
+          </cell>
+          <cell r="B341" t="str">
+            <v>x=77.75, y=92.10</v>
+          </cell>
+        </row>
+        <row r="342">
+          <cell r="A342" t="str">
+            <v>E106</v>
+          </cell>
+          <cell r="B342" t="str">
+            <v>x=15.53, y=89.22</v>
+          </cell>
+        </row>
+        <row r="343">
+          <cell r="A343" t="str">
+            <v>E107</v>
+          </cell>
+          <cell r="B343" t="str">
+            <v>x=74.52, y=95.26</v>
+          </cell>
+        </row>
+        <row r="344">
+          <cell r="A344" t="str">
+            <v>E108</v>
+          </cell>
+          <cell r="B344" t="str">
+            <v>x=13.95, y=89.01</v>
+          </cell>
+        </row>
+        <row r="345">
+          <cell r="A345" t="str">
+            <v>E109</v>
+          </cell>
+          <cell r="B345" t="str">
+            <v>x=76.17, y=95.33</v>
+          </cell>
+        </row>
+        <row r="346">
+          <cell r="A346" t="str">
+            <v>E110</v>
+          </cell>
+          <cell r="B346" t="str">
+            <v>x=17.07, y=92.31</v>
+          </cell>
+        </row>
+        <row r="347">
+          <cell r="A347" t="str">
+            <v>E112</v>
+          </cell>
+          <cell r="B347" t="str">
+            <v>x=15.53, y=92.17</v>
+          </cell>
+        </row>
+        <row r="348">
+          <cell r="A348" t="str">
+            <v>E114</v>
+          </cell>
+          <cell r="B348" t="str">
+            <v>x=17.14, y=95.33</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3478,12 +6425,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7894B4-148E-174D-AE8B-E6DE441B89B0}">
   <dimension ref="A1:I234"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="54.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11"/>
-    <col min="3" max="4" width="24.6640625" customWidth="1"/>
-    <col min="5" max="5" width="22.1640625" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" customWidth="1"/>
     <col min="6" max="6" width="89.1640625" customWidth="1"/>
     <col min="7" max="7" width="84.33203125" customWidth="1"/>
     <col min="8" max="8" width="45" customWidth="1"/>
@@ -3542,7 +6489,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>14</v>
@@ -3609,7 +6556,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>987</v>
+        <v>26</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>12</v>
@@ -3645,7 +6592,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>32</v>
@@ -3661,14 +6608,14 @@
         <v>34</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>35</v>
@@ -3794,7 +6741,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>58</v>
@@ -3813,13 +6760,13 @@
         <v>61</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>62</v>
@@ -3831,7 +6778,7 @@
         <v>12</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G16" s="2" t="s">
@@ -3926,7 +6873,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>81</v>
@@ -3947,7 +6894,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>84</v>
@@ -3972,7 +6919,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>88</v>
@@ -4062,7 +7009,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>106</v>
@@ -4078,7 +7025,7 @@
         <v>108</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -4223,8 +7170,8 @@
         <v>12</v>
       </c>
       <c r="E34" s="2"/>
-      <c r="F34" s="3" t="s">
-        <v>661</v>
+      <c r="F34" s="4" t="s">
+        <v>659</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -4309,10 +7256,10 @@
         <v>12</v>
       </c>
       <c r="E38" s="2"/>
-      <c r="F38" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="G38" s="4" t="s">
+      <c r="F38" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="G38" s="5" t="s">
         <v>151</v>
       </c>
       <c r="H38" s="2"/>
@@ -4332,7 +7279,7 @@
         <v>155</v>
       </c>
       <c r="E39" s="2"/>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="3" t="s">
         <v>156</v>
       </c>
       <c r="G39" s="2"/>
@@ -4372,8 +7319,8 @@
         <v>155</v>
       </c>
       <c r="E41" s="2"/>
-      <c r="F41" s="3" t="s">
-        <v>663</v>
+      <c r="F41" s="4" t="s">
+        <v>661</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -4393,7 +7340,7 @@
         <v>12</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -4415,7 +7362,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="1" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -4701,10 +7648,10 @@
         <v>220</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>723</v>
+        <v>680</v>
+      </c>
+      <c r="C57" t="s">
+        <v>721</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>12</v>
@@ -4746,7 +7693,7 @@
         <v>229</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>995</v>
+        <v>230</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>12</v>
@@ -4794,8 +7741,8 @@
         <v>155</v>
       </c>
       <c r="E61" s="2"/>
-      <c r="F61" s="3" t="s">
-        <v>664</v>
+      <c r="F61" s="4" t="s">
+        <v>662</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
@@ -4893,8 +7840,8 @@
         <v>155</v>
       </c>
       <c r="E66" s="2"/>
-      <c r="F66" s="3" t="s">
-        <v>665</v>
+      <c r="F66" s="4" t="s">
+        <v>663</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
@@ -4914,8 +7861,8 @@
         <v>155</v>
       </c>
       <c r="E67" s="2"/>
-      <c r="F67" s="3" t="s">
-        <v>666</v>
+      <c r="F67" s="4" t="s">
+        <v>664</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
@@ -5040,7 +7987,7 @@
         <v>12</v>
       </c>
       <c r="E73" s="2"/>
-      <c r="F73" s="5" t="s">
+      <c r="F73" s="6" t="s">
         <v>280</v>
       </c>
       <c r="G73" s="2"/>
@@ -5061,8 +8008,8 @@
         <v>12</v>
       </c>
       <c r="E74" s="2"/>
-      <c r="F74" s="5" t="s">
-        <v>280</v>
+      <c r="F74" s="6" t="s">
+        <v>996</v>
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
@@ -5168,8 +8115,8 @@
         <v>155</v>
       </c>
       <c r="E79" s="2"/>
-      <c r="F79" s="3" t="s">
-        <v>667</v>
+      <c r="F79" s="4" t="s">
+        <v>665</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
@@ -5189,8 +8136,8 @@
         <v>155</v>
       </c>
       <c r="E80" s="2"/>
-      <c r="F80" s="3" t="s">
-        <v>668</v>
+      <c r="F80" s="4" t="s">
+        <v>666</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
@@ -5273,7 +8220,7 @@
         <v>12</v>
       </c>
       <c r="E84" s="2"/>
-      <c r="F84" s="3" t="s">
+      <c r="F84" s="4" t="s">
         <v>317</v>
       </c>
       <c r="G84" s="2"/>
@@ -5294,7 +8241,7 @@
         <v>12</v>
       </c>
       <c r="E85" s="2"/>
-      <c r="F85" s="5" t="s">
+      <c r="F85" s="6" t="s">
         <v>324</v>
       </c>
       <c r="G85" s="2"/>
@@ -5315,8 +8262,8 @@
         <v>12</v>
       </c>
       <c r="E86" s="2"/>
-      <c r="F86" s="5" t="s">
-        <v>324</v>
+      <c r="F86" s="6" t="s">
+        <v>997</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -5336,10 +8283,10 @@
         <v>12</v>
       </c>
       <c r="E87" s="2"/>
-      <c r="F87" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G87" s="2" t="s">
+      <c r="F87" s="6" t="s">
+        <v>998</v>
+      </c>
+      <c r="G87" s="5" t="s">
         <v>330</v>
       </c>
       <c r="H87" s="2"/>
@@ -5389,20 +8336,20 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B90" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="C90" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="D90" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" s="6" t="s">
         <v>341</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" s="5" t="s">
-        <v>342</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -5410,20 +8357,20 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>344</v>
-      </c>
       <c r="D91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E91" s="2"/>
-      <c r="F91" s="5" t="s">
-        <v>342</v>
+      <c r="F91" s="6" t="s">
+        <v>999</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -5431,20 +8378,20 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B92" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>346</v>
-      </c>
       <c r="D92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E92" s="2"/>
-      <c r="F92" s="5" t="s">
-        <v>342</v>
+      <c r="F92" s="6" t="s">
+        <v>1000</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -5452,20 +8399,20 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="C93" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C93" s="2" t="s">
-        <v>349</v>
-      </c>
       <c r="D93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E93" s="2"/>
-      <c r="F93" s="5" t="s">
-        <v>342</v>
+      <c r="F93" s="6" t="s">
+        <v>1002</v>
       </c>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -5473,20 +8420,20 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>347</v>
+        <v>1003</v>
       </c>
       <c r="B94" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>351</v>
-      </c>
       <c r="D94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E94" s="2"/>
-      <c r="F94" s="5" t="s">
-        <v>342</v>
+      <c r="F94" s="7" t="s">
+        <v>341</v>
       </c>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -5494,20 +8441,20 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>347</v>
+        <v>1004</v>
       </c>
       <c r="B95" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>353</v>
-      </c>
       <c r="D95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E95" s="2"/>
-      <c r="F95" s="5" t="s">
-        <v>342</v>
+      <c r="F95" s="6" t="s">
+        <v>1005</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -5515,20 +8462,20 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="C96" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C96" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="D96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E96" s="2"/>
-      <c r="F96" s="5" t="s">
-        <v>357</v>
+      <c r="F96" s="6" t="s">
+        <v>1006</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -5536,7 +8483,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>221</v>
@@ -5548,8 +8495,8 @@
         <v>12</v>
       </c>
       <c r="E97" s="2"/>
-      <c r="F97" s="5" t="s">
-        <v>359</v>
+      <c r="F97" s="6" t="s">
+        <v>358</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
@@ -5557,20 +8504,20 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B98" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>361</v>
-      </c>
       <c r="D98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E98" s="2"/>
-      <c r="F98" s="5" t="s">
-        <v>359</v>
+      <c r="F98" s="6" t="s">
+        <v>1007</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
@@ -5578,20 +8525,20 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B99" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="C99" s="2" t="s">
-        <v>363</v>
-      </c>
       <c r="D99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E99" s="2"/>
-      <c r="F99" s="5" t="s">
-        <v>359</v>
+      <c r="F99" s="6" t="s">
+        <v>1008</v>
       </c>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
@@ -5599,20 +8546,20 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="C100" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>366</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
@@ -5620,20 +8567,20 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="C101" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="C101" s="2" t="s">
-        <v>370</v>
-      </c>
       <c r="D101" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E101" s="2"/>
-      <c r="F101" s="5" t="s">
-        <v>371</v>
+      <c r="F101" s="6" t="s">
+        <v>1009</v>
       </c>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
@@ -5641,20 +8588,20 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>373</v>
-      </c>
       <c r="D102" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E102" s="2"/>
-      <c r="F102" s="5" t="s">
-        <v>371</v>
+      <c r="F102" s="6" t="s">
+        <v>1010</v>
       </c>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
@@ -5662,20 +8609,20 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B103" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>375</v>
-      </c>
       <c r="D103" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E103" s="2"/>
-      <c r="F103" s="5" t="s">
-        <v>371</v>
+      <c r="F103" s="6" t="s">
+        <v>370</v>
       </c>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -5683,20 +8630,20 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="C104" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="D104" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" s="6" t="s">
         <v>378</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" s="5" t="s">
-        <v>379</v>
       </c>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -5704,20 +8651,20 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B105" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="D105" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E105" s="2"/>
-      <c r="F105" s="5" t="s">
-        <v>379</v>
+      <c r="F105" s="6" t="s">
+        <v>1011</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -5725,20 +8672,20 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="C106" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="D106" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" s="6" t="s">
         <v>384</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" s="5" t="s">
-        <v>385</v>
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -5746,20 +8693,20 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B107" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="C107" s="2" t="s">
-        <v>387</v>
-      </c>
       <c r="D107" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E107" s="2"/>
-      <c r="F107" s="5" t="s">
-        <v>385</v>
+      <c r="F107" s="6" t="s">
+        <v>1012</v>
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
@@ -5767,20 +8714,20 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="C108" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>390</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E108" s="2"/>
-      <c r="F108" s="3" t="s">
-        <v>669</v>
+      <c r="F108" s="4" t="s">
+        <v>667</v>
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
@@ -5788,20 +8735,20 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B109" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>396</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E109" s="2"/>
-      <c r="F109" s="5" t="s">
-        <v>394</v>
+      <c r="F109" s="7" t="s">
+        <v>393</v>
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
@@ -5809,20 +8756,20 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="C110" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E110" s="2"/>
-      <c r="F110" s="3" t="s">
-        <v>670</v>
+      <c r="F110" s="4" t="s">
+        <v>668</v>
       </c>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
@@ -5830,20 +8777,20 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="C111" s="2" t="s">
         <v>401</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>402</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E111" s="2"/>
-      <c r="F111" s="3" t="s">
-        <v>671</v>
+      <c r="F111" s="4" t="s">
+        <v>669</v>
       </c>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
@@ -5851,20 +8798,20 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B112" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>403</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>404</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E112" s="2"/>
-      <c r="F112" s="3" t="s">
-        <v>671</v>
+      <c r="F112" s="4" t="s">
+        <v>669</v>
       </c>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
@@ -5872,13 +8819,13 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="C113" s="2" t="s">
         <v>406</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>407</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>12</v>
@@ -5891,13 +8838,13 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B114" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>408</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>409</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>12</v>
@@ -5910,13 +8857,13 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B115" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C115" s="2" t="s">
         <v>410</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>411</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>12</v>
@@ -5929,20 +8876,20 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="C116" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E116" s="2"/>
-      <c r="F116" s="3" t="s">
-        <v>672</v>
+      <c r="F116" s="4" t="s">
+        <v>670</v>
       </c>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
@@ -5950,20 +8897,20 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B117" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="C117" s="2" t="s">
         <v>416</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>417</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
@@ -5971,20 +8918,20 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B118" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C118" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
@@ -5992,20 +8939,20 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="C119" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>424</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
@@ -6013,20 +8960,20 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B120" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C120" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>426</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
@@ -6034,20 +8981,20 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B121" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C121" s="2" t="s">
         <v>427</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>428</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
@@ -6055,20 +9002,20 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="C122" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="D122" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" s="6" t="s">
         <v>431</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" s="5" t="s">
-        <v>432</v>
       </c>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
@@ -6076,20 +9023,20 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B123" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C123" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="C123" s="2" t="s">
-        <v>434</v>
-      </c>
       <c r="D123" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E123" s="2"/>
-      <c r="F123" s="5" t="s">
-        <v>432</v>
+      <c r="F123" s="6" t="s">
+        <v>1013</v>
       </c>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
@@ -6097,20 +9044,20 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B124" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C124" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="C124" s="2" t="s">
-        <v>436</v>
-      </c>
       <c r="D124" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E124" s="2"/>
-      <c r="F124" s="5" t="s">
-        <v>432</v>
+      <c r="F124" s="6" t="s">
+        <v>1014</v>
       </c>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
@@ -6118,20 +9065,20 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B125" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="C125" s="2" t="s">
-        <v>438</v>
-      </c>
       <c r="D125" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E125" s="2"/>
-      <c r="F125" s="5" t="s">
-        <v>432</v>
+      <c r="F125" s="6" t="s">
+        <v>1015</v>
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
@@ -6139,20 +9086,20 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B126" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="C126" s="2" t="s">
-        <v>440</v>
-      </c>
       <c r="D126" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E126" s="2"/>
-      <c r="F126" s="5" t="s">
-        <v>432</v>
+      <c r="F126" s="6" t="s">
+        <v>1016</v>
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
@@ -6160,20 +9107,20 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="C127" s="2" t="s">
         <v>442</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>443</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
@@ -6181,20 +9128,20 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="C128" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>447</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
@@ -6202,20 +9149,20 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B129" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C129" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
@@ -6223,20 +9170,20 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B130" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="C130" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
@@ -6244,22 +9191,22 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="C131" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="D131" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F131" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>996</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>459</v>
       </c>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
@@ -6267,22 +9214,22 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B132" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="C132" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="D132" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D132" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="F132" s="3" t="s">
-        <v>673</v>
+      <c r="F132" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
@@ -6290,20 +9237,20 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B133" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="C133" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>466</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
@@ -6311,22 +9258,22 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="C134" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="D134" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="F134" s="2" t="s">
         <v>469</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>470</v>
       </c>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
@@ -6334,20 +9281,20 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B135" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="C135" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>473</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
@@ -6355,20 +9302,20 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B136" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="C136" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>477</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
@@ -6376,22 +9323,22 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B137" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="C137" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="C137" s="2" t="s">
+      <c r="D137" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F137" s="2" t="s">
         <v>481</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>997</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>482</v>
       </c>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
@@ -6399,20 +9346,20 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="C138" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
@@ -6420,20 +9367,20 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B139" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="C139" s="2" t="s">
         <v>488</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>489</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
@@ -6441,22 +9388,22 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="C140" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="D140" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E140" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="D140" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="F140" s="3" t="s">
-        <v>674</v>
+      <c r="F140" s="4" t="s">
+        <v>672</v>
       </c>
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
@@ -6464,20 +9411,20 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="C141" s="2" t="s">
         <v>496</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>497</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
@@ -6488,17 +9435,17 @@
         <v>17</v>
       </c>
       <c r="B142" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="C142" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="C142" s="2" t="s">
-        <v>500</v>
-      </c>
       <c r="D142" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E142" s="2"/>
-      <c r="F142" s="3" t="s">
-        <v>675</v>
+      <c r="F142" s="4" t="s">
+        <v>673</v>
       </c>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
@@ -6509,17 +9456,17 @@
         <v>17</v>
       </c>
       <c r="B143" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C143" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="C143" s="2" t="s">
-        <v>502</v>
-      </c>
       <c r="D143" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E143" s="2"/>
-      <c r="F143" s="3" t="s">
-        <v>675</v>
+      <c r="F143" s="4" t="s">
+        <v>673</v>
       </c>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
@@ -6530,17 +9477,17 @@
         <v>17</v>
       </c>
       <c r="B144" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C144" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="C144" s="2" t="s">
-        <v>504</v>
-      </c>
       <c r="D144" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E144" s="2"/>
-      <c r="F144" s="3" t="s">
-        <v>675</v>
+      <c r="F144" s="4" t="s">
+        <v>673</v>
       </c>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
@@ -6548,22 +9495,22 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="C145" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="D145" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F145" s="6" t="s">
         <v>507</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>508</v>
       </c>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
@@ -6571,22 +9518,22 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B146" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="C146" s="2" t="s">
-        <v>510</v>
-      </c>
       <c r="D146" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>508</v>
+        <v>1019</v>
+      </c>
+      <c r="F146" s="6" t="s">
+        <v>1020</v>
       </c>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
@@ -6594,22 +9541,22 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B147" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="C147" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="C147" s="2" t="s">
-        <v>512</v>
-      </c>
       <c r="D147" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>508</v>
+        <v>1019</v>
+      </c>
+      <c r="F147" s="6" t="s">
+        <v>1021</v>
       </c>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
@@ -6617,20 +9564,20 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="B148" s="2" t="s">
+      <c r="C148" s="2" t="s">
         <v>514</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>515</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
@@ -6638,20 +9585,20 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B149" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="C149" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>518</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
@@ -6659,20 +9606,20 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B150" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="C150" s="2" t="s">
-        <v>521</v>
-      </c>
       <c r="D150" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E150" s="2"/>
-      <c r="F150" s="5" t="s">
-        <v>357</v>
+      <c r="F150" s="6" t="s">
+        <v>356</v>
       </c>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
@@ -6680,20 +9627,20 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="C151" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="D151" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E151" s="2"/>
+      <c r="F151" s="6" t="s">
         <v>524</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E151" s="2"/>
-      <c r="F151" s="5" t="s">
-        <v>525</v>
       </c>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
@@ -6701,20 +9648,20 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B152" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="2" t="s">
-        <v>527</v>
-      </c>
       <c r="D152" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E152" s="2"/>
-      <c r="F152" s="5" t="s">
-        <v>525</v>
+      <c r="F152" s="6" t="s">
+        <v>1022</v>
       </c>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
@@ -6722,20 +9669,20 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B153" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="C153" s="2" t="s">
-        <v>529</v>
-      </c>
       <c r="D153" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E153" s="2"/>
-      <c r="F153" s="5" t="s">
-        <v>525</v>
+      <c r="F153" s="6" t="s">
+        <v>1023</v>
       </c>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
@@ -6743,20 +9690,20 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="C154" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="C154" s="2" t="s">
-        <v>532</v>
-      </c>
       <c r="D154" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E154" s="2"/>
-      <c r="F154" s="5" t="s">
-        <v>533</v>
+      <c r="F154" s="6" t="s">
+        <v>1024</v>
       </c>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
@@ -6764,20 +9711,20 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E155" s="2"/>
-      <c r="F155" s="5" t="s">
-        <v>533</v>
+      <c r="F155" s="6" t="s">
+        <v>1025</v>
       </c>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
@@ -6785,20 +9732,20 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E156" s="2"/>
-      <c r="F156" s="5" t="s">
-        <v>533</v>
+      <c r="F156" s="6" t="s">
+        <v>1026</v>
       </c>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
@@ -6806,20 +9753,20 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E157" s="2"/>
-      <c r="F157" s="5" t="s">
-        <v>379</v>
+      <c r="F157" s="6" t="s">
+        <v>1027</v>
       </c>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
@@ -6827,20 +9774,20 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="B158" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>542</v>
-      </c>
       <c r="D158" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E158" s="2"/>
-      <c r="F158" s="5" t="s">
-        <v>379</v>
+      <c r="F158" s="6" t="s">
+        <v>543</v>
       </c>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
@@ -6848,20 +9795,20 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E159" s="2"/>
-      <c r="F159" s="5" t="s">
-        <v>545</v>
+      <c r="F159" s="6" t="s">
+        <v>1028</v>
       </c>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
@@ -6869,20 +9816,20 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E160" s="2"/>
-      <c r="F160" s="5" t="s">
-        <v>545</v>
+      <c r="F160" s="6" t="s">
+        <v>1029</v>
       </c>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
@@ -6890,20 +9837,20 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>548</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>550</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
@@ -6911,20 +9858,20 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>554</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
@@ -6932,22 +9879,22 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="C163" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="D163" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E163" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="F163" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E163" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="F163" s="2" t="s">
-        <v>560</v>
       </c>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
@@ -6955,20 +9902,22 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
-        <v>339</v>
+        <v>1030</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E164" s="2"/>
-      <c r="F164" s="5" t="s">
-        <v>342</v>
+      <c r="E164" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F164" s="6" t="s">
+        <v>1032</v>
       </c>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
@@ -6976,20 +9925,22 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
-        <v>339</v>
+        <v>1033</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E165" s="2"/>
-      <c r="F165" s="5" t="s">
-        <v>342</v>
+      <c r="E165" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F165" s="6" t="s">
+        <v>1035</v>
       </c>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
@@ -6997,20 +9948,20 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B166" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C166" t="s">
         <v>392</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>393</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
@@ -7018,62 +9969,70 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
-        <v>165</v>
+        <v>1036</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
+      </c>
+      <c r="C167" t="s">
+        <v>565</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>168</v>
+        <v>992</v>
       </c>
       <c r="E167" s="2"/>
-      <c r="F167" s="2"/>
-      <c r="G167" s="2"/>
-      <c r="H167" s="2"/>
-      <c r="I167" s="2"/>
+      <c r="F167" s="6" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H167" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I167" s="1" t="s">
+        <v>1040</v>
+      </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E168" s="2"/>
-      <c r="F168" s="3" t="s">
-        <v>676</v>
+      <c r="F168" s="4" t="s">
+        <v>674</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E169" s="2"/>
-      <c r="F169" s="3" t="s">
-        <v>677</v>
+      <c r="F169" s="4" t="s">
+        <v>675</v>
       </c>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
@@ -7081,16 +10040,16 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="C170" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="B170" s="2" t="s">
+      <c r="D170" s="2" t="s">
         <v>574</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>576</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" s="2"/>
@@ -7100,16 +10059,16 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
@@ -7119,16 +10078,16 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
@@ -7138,16 +10097,16 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
@@ -7157,16 +10116,16 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
@@ -7176,16 +10135,16 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
@@ -7195,16 +10154,16 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
@@ -7214,16 +10173,16 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
@@ -7233,16 +10192,16 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
@@ -7252,16 +10211,16 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
@@ -7271,16 +10230,16 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
@@ -7290,16 +10249,16 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
@@ -7309,16 +10268,16 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
@@ -7328,16 +10287,16 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
@@ -7347,16 +10306,16 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
@@ -7366,16 +10325,16 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
@@ -7385,16 +10344,16 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
@@ -7404,16 +10363,16 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
@@ -7423,16 +10382,16 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
@@ -7442,16 +10401,16 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
@@ -7461,16 +10420,16 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
@@ -7480,16 +10439,16 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
@@ -7499,16 +10458,16 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
@@ -7518,16 +10477,16 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" s="2"/>
@@ -7537,16 +10496,16 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E194" s="2"/>
       <c r="F194" s="2"/>
@@ -7556,16 +10515,16 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
@@ -7575,20 +10534,20 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
@@ -7596,20 +10555,20 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E197" s="2"/>
-      <c r="F197" s="3" t="s">
-        <v>678</v>
+      <c r="F197" s="4" t="s">
+        <v>676</v>
       </c>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
@@ -7617,20 +10576,20 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E198" s="2"/>
-      <c r="F198" s="3" t="s">
-        <v>679</v>
+      <c r="F198" s="4" t="s">
+        <v>677</v>
       </c>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
@@ -7638,32 +10597,40 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
-        <v>165</v>
+        <v>1036</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>168</v>
+        <v>992</v>
       </c>
       <c r="E199" s="2"/>
-      <c r="F199" s="2"/>
-      <c r="G199" s="2"/>
-      <c r="H199" s="2"/>
-      <c r="I199" s="2"/>
+      <c r="F199" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H199" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="I199" s="1" t="s">
+        <v>1044</v>
+      </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
         <v>165</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>168</v>
@@ -7679,10 +10646,10 @@
         <v>165</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>168</v>
@@ -7698,10 +10665,10 @@
         <v>165</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>168</v>
@@ -7717,10 +10684,10 @@
         <v>165</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>168</v>
@@ -7736,10 +10703,10 @@
         <v>165</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>168</v>
@@ -7755,10 +10722,10 @@
         <v>165</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>168</v>
@@ -7774,10 +10741,10 @@
         <v>165</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>168</v>
@@ -7793,10 +10760,10 @@
         <v>165</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>168</v>
@@ -7812,10 +10779,10 @@
         <v>165</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>168</v>
@@ -7831,10 +10798,10 @@
         <v>165</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>168</v>
@@ -7850,10 +10817,10 @@
         <v>165</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>168</v>
@@ -7869,10 +10836,10 @@
         <v>165</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>168</v>
@@ -7888,10 +10855,10 @@
         <v>165</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>168</v>
@@ -7904,16 +10871,16 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A213" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="C213" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B213" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>648</v>
-      </c>
       <c r="D213" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E213" s="2"/>
       <c r="F213" s="2"/>
@@ -7923,16 +10890,16 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E214" s="2"/>
       <c r="F214" s="2"/>
@@ -7942,16 +10909,16 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E215" s="2"/>
       <c r="F215" s="2"/>
@@ -7961,16 +10928,16 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E216" s="2"/>
       <c r="F216" s="2"/>
@@ -7980,16 +10947,16 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E217" s="2"/>
       <c r="F217" s="2"/>
@@ -7999,16 +10966,16 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E218" s="2"/>
       <c r="F218" s="2"/>
@@ -8018,16 +10985,16 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E219" s="2"/>
       <c r="F219" s="2"/>
@@ -8036,315 +11003,312 @@
       <c r="I219" s="2"/>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A220" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="B220" s="2" t="s">
+      <c r="A220" t="s">
+        <v>571</v>
+      </c>
+      <c r="B220" t="s">
+        <v>706</v>
+      </c>
+      <c r="C220" t="str">
+        <f>VLOOKUP(B220,[1]Sheet1!A:B,2,FALSE)</f>
+        <v>x=9.25, y=80.82</v>
+      </c>
+      <c r="D220" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>571</v>
+      </c>
+      <c r="B221" t="s">
+        <v>707</v>
+      </c>
+      <c r="C221" t="str">
+        <f>VLOOKUP(B221,[1]Sheet1!A:B,2,FALSE)</f>
+        <v>x=79.37, y=63.15</v>
+      </c>
+      <c r="D221" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
+        <v>571</v>
+      </c>
+      <c r="B222" t="s">
         <v>708</v>
       </c>
-      <c r="C220" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E220" s="2"/>
-      <c r="F220" s="2"/>
-      <c r="G220" s="2"/>
-      <c r="H220" s="2"/>
-      <c r="I220" s="2"/>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A221" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="B221" s="2" t="s">
+      <c r="C222" t="str">
+        <f>VLOOKUP(B222,[1]Sheet1!A:B,2,FALSE)</f>
+        <v>x=26.03, y=86.14</v>
+      </c>
+      <c r="D222" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>571</v>
+      </c>
+      <c r="B223" t="s">
         <v>709</v>
       </c>
-      <c r="C221" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="D221" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E221" s="2"/>
-      <c r="F221" s="2"/>
-      <c r="G221" s="2"/>
-      <c r="H221" s="2"/>
-      <c r="I221" s="2"/>
-    </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A222" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="B222" s="2" t="s">
+      <c r="C223" t="str">
+        <f>VLOOKUP(B223,[1]Sheet1!A:B,2,FALSE)</f>
+        <v>x=24.49, y=86.21</v>
+      </c>
+      <c r="D223" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>571</v>
+      </c>
+      <c r="B224" t="s">
         <v>710</v>
       </c>
-      <c r="C222" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="D222" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E222" s="2"/>
-      <c r="F222" s="2"/>
-      <c r="G222" s="2"/>
-      <c r="H222" s="2"/>
-      <c r="I222" s="2"/>
-    </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A223" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="B223" s="2" t="s">
+      <c r="C224" t="str">
+        <f>VLOOKUP(B224,[1]Sheet1!A:B,2,FALSE)</f>
+        <v>x=67.22, y=86.14</v>
+      </c>
+      <c r="D224" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B225" t="s">
         <v>711</v>
       </c>
-      <c r="C223" s="2" t="s">
-        <v>878</v>
-      </c>
-      <c r="D223" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E223" s="2"/>
-      <c r="F223" s="2"/>
-      <c r="G223" s="2"/>
-      <c r="H223" s="2"/>
-      <c r="I223" s="2"/>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A224" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="B224" s="2" t="s">
+      <c r="C225" t="str">
+        <f>VLOOKUP(B225,[1]Sheet1!A:B,2,FALSE)</f>
+        <v>x=10.90, y=63.07</v>
+      </c>
+      <c r="D225" t="s">
+        <v>992</v>
+      </c>
+      <c r="F225" s="1" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>991</v>
+      </c>
+      <c r="B226" t="s">
         <v>712</v>
       </c>
-      <c r="C224" s="2" t="s">
-        <v>877</v>
-      </c>
-      <c r="D224" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E224" s="2"/>
-      <c r="F224" s="2"/>
-      <c r="G224" s="2"/>
-      <c r="H224" s="2"/>
-      <c r="I224" s="2"/>
-    </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A225" s="2" t="s">
+      <c r="C226" t="str">
+        <f>VLOOKUP(B226,[1]Sheet1!A:B,2,FALSE)</f>
+        <v>x=12.37, y=66.24</v>
+      </c>
+      <c r="D226" t="s">
+        <v>992</v>
+      </c>
+      <c r="E226" t="s">
+        <v>993</v>
+      </c>
+      <c r="F226" s="1" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
         <v>165</v>
       </c>
-      <c r="B225" s="2" t="s">
+      <c r="B227" t="s">
         <v>713</v>
       </c>
-      <c r="C225" s="2" t="s">
-        <v>941</v>
-      </c>
-      <c r="D225" s="2" t="s">
+      <c r="C227" t="str">
+        <f>VLOOKUP(B227,[1]Sheet1!A:B,2,FALSE)</f>
+        <v>x=10.79, y=66.31</v>
+      </c>
+      <c r="D227" t="s">
         <v>168</v>
       </c>
-      <c r="E225" s="2"/>
-      <c r="F225" s="2"/>
-      <c r="G225" s="2"/>
-      <c r="H225" s="2"/>
-      <c r="I225" s="2"/>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A226" s="2" t="s">
-        <v>999</v>
-      </c>
-      <c r="B226" s="2" t="s">
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A228" t="s">
+        <v>165</v>
+      </c>
+      <c r="B228" t="s">
         <v>714</v>
       </c>
-      <c r="C226" s="2" t="s">
-        <v>947</v>
-      </c>
-      <c r="D226" s="2" t="s">
-        <v>1000</v>
-      </c>
-      <c r="E226" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F226" s="1" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G226" s="2"/>
-      <c r="H226" s="2"/>
-      <c r="I226" s="2"/>
-    </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A227" s="2" t="s">
+      <c r="C228" t="str">
+        <f>VLOOKUP(B228,[1]Sheet1!A:B,2,FALSE)</f>
+        <v>x=38.14, y=94.04</v>
+      </c>
+      <c r="D228" t="s">
+        <v>168</v>
+      </c>
+      <c r="E228" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A229" t="s">
         <v>165</v>
       </c>
-      <c r="B227" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>950</v>
-      </c>
-      <c r="D227" s="2" t="s">
+      <c r="B229" t="s">
+        <v>716</v>
+      </c>
+      <c r="C229" t="str">
+        <f>VLOOKUP(B229,[1]Sheet1!A:B,2,FALSE)</f>
+        <v>x=39.98, y=85.70</v>
+      </c>
+      <c r="D229" t="s">
         <v>168</v>
       </c>
-      <c r="E227" s="2"/>
-      <c r="F227" s="2"/>
-      <c r="G227" s="2"/>
-      <c r="H227" s="2"/>
-      <c r="I227" s="2"/>
-    </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A228" s="2" t="s">
+      <c r="E229" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A230" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="B230" t="s">
+        <v>719</v>
+      </c>
+      <c r="C230" t="str">
+        <f>VLOOKUP(B230,[1]Sheet1!A:B,2,FALSE)</f>
+        <v>x=68.76, y=86.28</v>
+      </c>
+      <c r="D230" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
+        <v>571</v>
+      </c>
+      <c r="B231" t="s">
+        <v>710</v>
+      </c>
+      <c r="C231" t="str">
+        <f>VLOOKUP(B231,[1]Sheet1!A:B,2,FALSE)</f>
+        <v>x=67.22, y=86.14</v>
+      </c>
+      <c r="D231" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A232" t="s">
+        <v>571</v>
+      </c>
+      <c r="B232" t="s">
+        <v>720</v>
+      </c>
+      <c r="C232" t="str">
+        <f>VLOOKUP(B232,[1]Sheet1!A:B,2,FALSE)</f>
+        <v>x=71.99, y=86.35</v>
+      </c>
+      <c r="D232" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A233" t="s">
+        <v>571</v>
+      </c>
+      <c r="B233" t="s">
+        <v>707</v>
+      </c>
+      <c r="C233" t="str">
+        <f>VLOOKUP(B233,[1]Sheet1!A:B,2,FALSE)</f>
+        <v>x=79.37, y=63.15</v>
+      </c>
+      <c r="D233" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
         <v>165</v>
       </c>
-      <c r="B228" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="D228" s="2" t="s">
+      <c r="B234" t="s">
+        <v>873</v>
+      </c>
+      <c r="C234" t="s">
+        <v>874</v>
+      </c>
+      <c r="D234" t="s">
         <v>168</v>
       </c>
-      <c r="E228" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="F228" s="2"/>
-      <c r="G228" s="2"/>
-      <c r="H228" s="2"/>
-      <c r="I228" s="2"/>
-    </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A229" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B229" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="D229" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E229" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="F229" s="2"/>
-      <c r="G229" s="2"/>
-      <c r="H229" s="2"/>
-      <c r="I229" s="2"/>
-    </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A230" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="D230" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E230" s="2"/>
-      <c r="F230" s="2"/>
-      <c r="G230" s="2"/>
-      <c r="H230" s="2"/>
-      <c r="I230" s="2"/>
-    </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A231" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>877</v>
-      </c>
-      <c r="D231" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E231" s="2"/>
-      <c r="F231" s="2"/>
-      <c r="G231" s="2"/>
-      <c r="H231" s="2"/>
-      <c r="I231" s="2"/>
-    </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A232" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>884</v>
-      </c>
-      <c r="D232" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E232" s="2"/>
-      <c r="F232" s="2"/>
-      <c r="G232" s="2"/>
-      <c r="H232" s="2"/>
-      <c r="I232" s="2"/>
-    </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A233" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="D233" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E233" s="2"/>
-      <c r="F233" s="2"/>
-      <c r="G233" s="2"/>
-      <c r="H233" s="2"/>
-      <c r="I233" s="2"/>
-    </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A234" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>875</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="D234" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E234" s="2"/>
-      <c r="F234" s="2"/>
-      <c r="G234" s="2"/>
-      <c r="H234" s="2"/>
-      <c r="I234" s="2"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G235:G1048576">
+  <conditionalFormatting sqref="G220:G1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="G8" r:id="rId1" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u72eLYAQ/view" xr:uid="{65596CF7-BDB9-6A40-B030-1A20C6B98465}"/>
-    <hyperlink ref="H15" r:id="rId2" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000rvp8wYAA/view" xr:uid="{C5427ACB-FBA3-1E4E-889F-7B5EA77E8DBC}"/>
-    <hyperlink ref="F16" r:id="rId3" xr:uid="{9D963830-BAFA-644C-A644-5E8750DBB383}"/>
-    <hyperlink ref="F39" r:id="rId4" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000Q2enCYAR/view" xr:uid="{5222CFA8-43C4-FA43-BDDF-A929363493D2}"/>
-    <hyperlink ref="F43" r:id="rId5" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u9QkgYAE/view" xr:uid="{117D339F-73A8-3343-BDC7-646C679812A8}"/>
-    <hyperlink ref="F119" r:id="rId6" xr:uid="{8DCCDB3B-822D-C342-B115-0DE63B038623}"/>
-    <hyperlink ref="F120" r:id="rId7" xr:uid="{30DAE056-C7EB-9E4C-B1FE-4279CD7FEDD4}"/>
-    <hyperlink ref="F121" r:id="rId8" xr:uid="{57AAA8CA-E5D6-8C4E-A5D1-5243A96160CC}"/>
-    <hyperlink ref="F133" r:id="rId9" xr:uid="{8BFBED8D-BE27-AA4B-B2E7-08315E64B68C}"/>
-    <hyperlink ref="F148" r:id="rId10" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000s98yXYAQ/view" xr:uid="{BF94BAB4-0CE7-E645-BAD9-0BCA6B291B73}"/>
-    <hyperlink ref="G168" r:id="rId11" xr:uid="{6825F257-D41A-114A-88F7-20C2B22CF9C5}"/>
-    <hyperlink ref="F226" r:id="rId12" xr:uid="{F13A9300-ADB7-514D-9AB4-BDE540A31E7A}"/>
+    <hyperlink ref="F16" r:id="rId1" xr:uid="{20B66D1F-5514-1641-96D3-7AB0045B18B7}"/>
+    <hyperlink ref="F39" r:id="rId2" xr:uid="{8DCA624B-AF25-3C43-A31D-350DD0BA2F7A}"/>
+    <hyperlink ref="G168" r:id="rId3" xr:uid="{818D38FB-8179-B949-BB5C-6FF5F8BED354}"/>
+    <hyperlink ref="F148" r:id="rId4" xr:uid="{11ED83F1-61AC-E647-AEAF-FC9229AD21EB}"/>
+    <hyperlink ref="F133" r:id="rId5" xr:uid="{A5E55A53-4CB8-924E-9E48-9A9E26F05AC7}"/>
+    <hyperlink ref="F119" r:id="rId6" xr:uid="{E2231DB0-C9E3-7240-B073-4E388C91C900}"/>
+    <hyperlink ref="F120" r:id="rId7" xr:uid="{ED191C20-AAB6-6D4C-9225-21BE4963C152}"/>
+    <hyperlink ref="F121" r:id="rId8" xr:uid="{199C0745-BD7F-1941-9DAF-5CDAFAD15F8A}"/>
+    <hyperlink ref="H15" r:id="rId9" xr:uid="{79F6D4E4-559C-4549-AC04-6148955629DA}"/>
+    <hyperlink ref="G8" r:id="rId10" xr:uid="{4DA14941-F63E-5241-A8E4-1DD0EC4B17C4}"/>
+    <hyperlink ref="F43" r:id="rId11" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u9QkgYAE/view" xr:uid="{273571A2-75A3-864E-BE91-320E10E4429E}"/>
+    <hyperlink ref="F226" r:id="rId12" xr:uid="{8EBC30FF-50CD-B94D-9390-728D2373EF06}"/>
+    <hyperlink ref="F225" r:id="rId13" xr:uid="{57EC2AD1-85F5-D842-B10A-E8970F9A7B38}"/>
+    <hyperlink ref="F199" r:id="rId14" xr:uid="{D3B3D373-DE7D-DD4A-90C8-E301E07A3C5F}"/>
+    <hyperlink ref="G199" r:id="rId15" xr:uid="{86269759-79E0-3C4B-95FF-5E3FA8228AD6}"/>
+    <hyperlink ref="H199" r:id="rId16" xr:uid="{9DDF838C-21F9-9847-A914-1274205D0A02}"/>
+    <hyperlink ref="I199" r:id="rId17" xr:uid="{E02F7DFE-805F-674C-84D5-6CB7AF9DC227}"/>
+    <hyperlink ref="F167" r:id="rId18" xr:uid="{40AF881D-2DBC-F144-9CDD-B7725C2955B0}"/>
+    <hyperlink ref="G167" r:id="rId19" xr:uid="{23355997-DC56-A040-A8D2-145B7E1744F0}"/>
+    <hyperlink ref="H167" r:id="rId20" xr:uid="{FA039E2F-0E2A-EF4A-AC04-2663407D2681}"/>
+    <hyperlink ref="I167" r:id="rId21" xr:uid="{0453D391-8DF5-4F4C-A845-C89C47C3B15A}"/>
+    <hyperlink ref="F145" r:id="rId22" xr:uid="{23A223E9-E940-5F40-93B3-BC41D89A37DC}"/>
+    <hyperlink ref="F146" r:id="rId23" xr:uid="{F8C1804C-F4C6-0B46-93B6-78F5FA0027B0}"/>
+    <hyperlink ref="F147" r:id="rId24" xr:uid="{C80A734A-60DB-5547-A4FB-6611F96359CD}"/>
+    <hyperlink ref="F73" r:id="rId25" xr:uid="{064F0BC5-0EBC-5445-81AB-054623DF910D}"/>
+    <hyperlink ref="F74" r:id="rId26" xr:uid="{EEFD37F7-0FC7-AA49-BAB1-43CC8349AB4A}"/>
+    <hyperlink ref="F85" r:id="rId27" xr:uid="{99D56DD4-A6F3-184B-9CD8-15A0D9941AFE}"/>
+    <hyperlink ref="F86" r:id="rId28" xr:uid="{6BDB2AE8-B783-5D40-A215-9D1156A44B2F}"/>
+    <hyperlink ref="F87" r:id="rId29" xr:uid="{58DA2BCA-912B-8A4C-B13D-B0892CA4D745}"/>
+    <hyperlink ref="F90" r:id="rId30" xr:uid="{12CA4843-7B9F-2C4E-9C2E-810B4588D96F}"/>
+    <hyperlink ref="F91" r:id="rId31" xr:uid="{BE962A5C-674C-ED43-97F8-C6EFAA294EED}"/>
+    <hyperlink ref="F92" r:id="rId32" xr:uid="{F0FF85A7-19D2-0441-BA37-776623F900E8}"/>
+    <hyperlink ref="F93" r:id="rId33" xr:uid="{BA657F8B-3359-0645-8CC1-A098CE015027}"/>
+    <hyperlink ref="F95" r:id="rId34" xr:uid="{CC217EFC-E739-3A42-864E-D420CAF80764}"/>
+    <hyperlink ref="F150" r:id="rId35" xr:uid="{7AF7228B-E539-D940-B4B8-4862293FC789}"/>
+    <hyperlink ref="F96" r:id="rId36" xr:uid="{0A59ADD1-266E-F241-B900-9DE0C8426D04}"/>
+    <hyperlink ref="F97" r:id="rId37" xr:uid="{81AC3CD9-861E-9B4B-9690-4D5D2168E871}"/>
+    <hyperlink ref="F98" r:id="rId38" xr:uid="{3EB2F645-7D1A-A348-B77D-8985860F059A}"/>
+    <hyperlink ref="F99" r:id="rId39" xr:uid="{57919F5B-765D-184F-9A0A-5598DD10580E}"/>
+    <hyperlink ref="F101" r:id="rId40" xr:uid="{FA82F43C-3FBA-1B46-9075-9ECD10253685}"/>
+    <hyperlink ref="F102" r:id="rId41" xr:uid="{29AFCC58-BCA7-A942-8F6D-DEA826267A2E}"/>
+    <hyperlink ref="F103" r:id="rId42" xr:uid="{5813434F-99BF-3F44-840D-B2409B85F6C0}"/>
+    <hyperlink ref="F104" r:id="rId43" xr:uid="{FE404FCA-9A69-144E-8932-37404BC78AED}"/>
+    <hyperlink ref="F105" r:id="rId44" xr:uid="{22E4F622-9A62-6C4D-AC03-400BAD4E6427}"/>
+    <hyperlink ref="F157" r:id="rId45" xr:uid="{D04779D6-A774-F14D-B338-562D2406F561}"/>
+    <hyperlink ref="F164" r:id="rId46" xr:uid="{BAE06E74-C4ED-2E4A-80EC-F47D577DC14D}"/>
+    <hyperlink ref="F165" r:id="rId47" xr:uid="{BC335D08-D650-E040-953E-9B73D03D730F}"/>
+    <hyperlink ref="F106" r:id="rId48" xr:uid="{C3028E67-D32F-4148-9DFE-DDE425B3C7E4}"/>
+    <hyperlink ref="F107" r:id="rId49" xr:uid="{1F978071-A0C6-A547-AE4C-ECCEFB65113E}"/>
+    <hyperlink ref="F122" r:id="rId50" xr:uid="{3FCC90C2-2D87-0B48-B38C-7ADEC6B7E10B}"/>
+    <hyperlink ref="F123" r:id="rId51" xr:uid="{95EF836E-1BAC-0548-9B7D-E131E21A525A}"/>
+    <hyperlink ref="F124" r:id="rId52" xr:uid="{45DD9E3A-60A4-A548-BD04-79170D35B7F1}"/>
+    <hyperlink ref="F125" r:id="rId53" xr:uid="{DE773A1F-C62E-344E-89D4-E1D79CEC7E20}"/>
+    <hyperlink ref="F126" r:id="rId54" xr:uid="{347EB156-DBD0-2645-A1C6-85E4992610DD}"/>
+    <hyperlink ref="F151" r:id="rId55" xr:uid="{06503851-6386-D24E-A732-FF3D80EDE26E}"/>
+    <hyperlink ref="F152" r:id="rId56" xr:uid="{8E178F25-9C87-F34F-922F-C15FF52535BF}"/>
+    <hyperlink ref="F153" r:id="rId57" xr:uid="{2CE4D433-AD62-D347-BB18-C5C360BDFE5C}"/>
+    <hyperlink ref="F154" r:id="rId58" xr:uid="{D4C1DD6E-600E-D240-BBFE-1230FB9E5862}"/>
+    <hyperlink ref="F155" r:id="rId59" xr:uid="{B2869912-09FA-654C-B29E-8D3CC0A57AF7}"/>
+    <hyperlink ref="F156" r:id="rId60" xr:uid="{1DF36AB9-0BDE-284C-BD89-D8FF05AB05F0}"/>
+    <hyperlink ref="F158" r:id="rId61" xr:uid="{3DA55A82-A5EE-7445-A6B6-588EED61A52D}"/>
+    <hyperlink ref="F159" r:id="rId62" xr:uid="{AE87EB9B-02F1-274C-9F06-E58F99CCB2CE}"/>
+    <hyperlink ref="F160" r:id="rId63" xr:uid="{9E15451E-EF0F-4940-B63D-AFD0436CD599}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8361,7 +11325,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
@@ -8409,42 +11373,42 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B7" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B8" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B9" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B10" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B11" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -8465,10 +11429,10 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B14" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -8633,10 +11597,10 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B35" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
@@ -8673,10 +11637,10 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B40" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
@@ -8697,10 +11661,10 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B43" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
@@ -8713,18 +11677,18 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B45" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B46" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
@@ -8841,10 +11805,10 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B61" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
@@ -8881,18 +11845,18 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B66" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B67" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
@@ -8905,10 +11869,10 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B69" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
@@ -8945,10 +11909,10 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B74" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
@@ -8961,18 +11925,18 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B76" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B77" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
@@ -8993,10 +11957,10 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B80" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
@@ -9009,10 +11973,10 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B82" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
@@ -9033,207 +11997,207 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B85" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B86" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B87" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B88" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B89" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B90" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B91" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B92" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B93" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B95" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B96" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B97" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B98" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B99" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B100" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B101" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B102" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B103" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B104" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B105" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B106" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B107" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B108" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B109" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B110" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
@@ -9246,58 +12210,58 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B112" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B113" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B114" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B115" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B116" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B117" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B118" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
@@ -9310,66 +12274,66 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B120" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B121" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B122" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B123" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B124" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B125" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B126" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B127" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
@@ -9382,74 +12346,74 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B129" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B130" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B131" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B132" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B133" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B134" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B135" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B136" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B137" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
@@ -9462,10 +12426,10 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B139" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
@@ -9478,58 +12442,58 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B141" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B142" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B143" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B144" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B145" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B146" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B147" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
@@ -9558,50 +12522,50 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B151" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B152" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B153" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B154" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B155" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B156" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
@@ -9646,42 +12610,42 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
+        <v>364</v>
+      </c>
+      <c r="B162" t="s">
         <v>365</v>
-      </c>
-      <c r="B162" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B163" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
+        <v>385</v>
+      </c>
+      <c r="B164" t="s">
         <v>386</v>
-      </c>
-      <c r="B164" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B165" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
+        <v>354</v>
+      </c>
+      <c r="B166" t="s">
         <v>355</v>
-      </c>
-      <c r="B166" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
@@ -9694,10 +12658,10 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B168" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
@@ -9718,10 +12682,10 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B171" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
@@ -9734,26 +12698,26 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B173" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
+        <v>382</v>
+      </c>
+      <c r="B174" t="s">
         <v>383</v>
-      </c>
-      <c r="B174" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B175" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
@@ -9774,10 +12738,10 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B178" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
@@ -9798,50 +12762,50 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
+        <v>339</v>
+      </c>
+      <c r="B181" t="s">
         <v>340</v>
-      </c>
-      <c r="B181" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B182" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
+        <v>344</v>
+      </c>
+      <c r="B183" t="s">
         <v>345</v>
-      </c>
-      <c r="B183" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
+        <v>361</v>
+      </c>
+      <c r="B184" t="s">
         <v>362</v>
-      </c>
-      <c r="B184" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
+        <v>349</v>
+      </c>
+      <c r="B185" t="s">
         <v>350</v>
-      </c>
-      <c r="B185" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
+        <v>359</v>
+      </c>
+      <c r="B186" t="s">
         <v>360</v>
-      </c>
-      <c r="B186" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
@@ -9854,10 +12818,10 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B188" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
@@ -9870,154 +12834,154 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B190" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
+        <v>342</v>
+      </c>
+      <c r="B191" t="s">
         <v>343</v>
-      </c>
-      <c r="B191" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B192" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
+        <v>347</v>
+      </c>
+      <c r="B193" t="s">
         <v>348</v>
-      </c>
-      <c r="B193" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
+        <v>376</v>
+      </c>
+      <c r="B194" t="s">
         <v>377</v>
-      </c>
-      <c r="B194" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
+        <v>351</v>
+      </c>
+      <c r="B195" t="s">
         <v>352</v>
-      </c>
-      <c r="B195" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
+        <v>379</v>
+      </c>
+      <c r="B196" t="s">
         <v>380</v>
-      </c>
-      <c r="B196" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B197" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B198" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B199" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B200" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B201" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B202" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B203" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B204" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B205" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B206" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B207" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B208" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
@@ -10030,167 +12994,167 @@
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B210" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
+        <v>368</v>
+      </c>
+      <c r="B211" t="s">
         <v>369</v>
-      </c>
-      <c r="B211" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B212" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B213" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B214" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B215" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B216" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B217" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B218" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
+        <v>371</v>
+      </c>
+      <c r="B219" t="s">
         <v>372</v>
-      </c>
-      <c r="B219" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B220" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
+        <v>373</v>
+      </c>
+      <c r="B221" t="s">
         <v>374</v>
-      </c>
-      <c r="B221" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B222" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B223" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B224" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B225" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B226" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B228" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B229" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B230" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
@@ -10203,938 +13167,938 @@
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B232" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B233" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B234" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B235" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B236" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
+        <v>412</v>
+      </c>
+      <c r="B237" t="s">
         <v>413</v>
-      </c>
-      <c r="B237" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
+        <v>394</v>
+      </c>
+      <c r="B238" t="s">
         <v>395</v>
-      </c>
-      <c r="B238" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
+        <v>405</v>
+      </c>
+      <c r="B239" t="s">
         <v>406</v>
-      </c>
-      <c r="B239" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
+        <v>445</v>
+      </c>
+      <c r="B240" t="s">
         <v>446</v>
-      </c>
-      <c r="B240" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B241" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B242" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B243" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B244" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B245" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B246" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
+        <v>388</v>
+      </c>
+      <c r="B247" t="s">
         <v>389</v>
-      </c>
-      <c r="B247" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
+        <v>391</v>
+      </c>
+      <c r="B248" t="s">
         <v>392</v>
-      </c>
-      <c r="B248" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
+        <v>407</v>
+      </c>
+      <c r="B249" t="s">
         <v>408</v>
-      </c>
-      <c r="B249" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
+        <v>400</v>
+      </c>
+      <c r="B250" t="s">
         <v>401</v>
-      </c>
-      <c r="B250" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B251" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B252" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B253" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B254" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B255" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B256" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B257" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B258" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
+        <v>397</v>
+      </c>
+      <c r="B259" t="s">
         <v>398</v>
-      </c>
-      <c r="B259" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
+        <v>487</v>
+      </c>
+      <c r="B260" t="s">
         <v>488</v>
-      </c>
-      <c r="B260" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
+        <v>409</v>
+      </c>
+      <c r="B261" t="s">
         <v>410</v>
-      </c>
-      <c r="B261" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
+        <v>402</v>
+      </c>
+      <c r="B262" t="s">
         <v>403</v>
-      </c>
-      <c r="B262" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B263" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B264" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B265" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B266" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B267" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B268" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B269" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B270" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
+        <v>418</v>
+      </c>
+      <c r="B271" t="s">
         <v>419</v>
-      </c>
-      <c r="B271" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B272" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
+        <v>479</v>
+      </c>
+      <c r="B273" t="s">
         <v>480</v>
-      </c>
-      <c r="B273" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
+        <v>519</v>
+      </c>
+      <c r="B274" t="s">
         <v>520</v>
-      </c>
-      <c r="B274" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
+        <v>441</v>
+      </c>
+      <c r="B275" t="s">
         <v>442</v>
-      </c>
-      <c r="B275" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
+        <v>426</v>
+      </c>
+      <c r="B276" t="s">
         <v>427</v>
-      </c>
-      <c r="B276" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
+        <v>491</v>
+      </c>
+      <c r="B277" t="s">
         <v>492</v>
-      </c>
-      <c r="B277" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B278" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
+        <v>516</v>
+      </c>
+      <c r="B279" t="s">
         <v>517</v>
-      </c>
-      <c r="B279" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B280" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B281" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B282" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
+        <v>415</v>
+      </c>
+      <c r="B283" t="s">
         <v>416</v>
-      </c>
-      <c r="B283" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B284" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
+        <v>522</v>
+      </c>
+      <c r="B285" t="s">
         <v>523</v>
-      </c>
-      <c r="B285" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B286" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
+        <v>525</v>
+      </c>
+      <c r="B287" t="s">
         <v>526</v>
-      </c>
-      <c r="B287" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B288" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B289" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
+        <v>422</v>
+      </c>
+      <c r="B290" t="s">
         <v>423</v>
-      </c>
-      <c r="B290" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
+        <v>513</v>
+      </c>
+      <c r="B291" t="s">
         <v>514</v>
-      </c>
-      <c r="B291" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
+        <v>424</v>
+      </c>
+      <c r="B292" t="s">
         <v>425</v>
-      </c>
-      <c r="B292" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B293" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B294" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B295" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
+        <v>498</v>
+      </c>
+      <c r="B296" t="s">
         <v>499</v>
-      </c>
-      <c r="B296" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
+        <v>530</v>
+      </c>
+      <c r="B297" t="s">
         <v>531</v>
-      </c>
-      <c r="B297" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
+        <v>502</v>
+      </c>
+      <c r="B298" t="s">
         <v>503</v>
-      </c>
-      <c r="B298" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
+        <v>527</v>
+      </c>
+      <c r="B299" t="s">
         <v>528</v>
-      </c>
-      <c r="B299" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B300" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B301" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B302" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B303" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B304" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B305" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
+        <v>460</v>
+      </c>
+      <c r="B306" t="s">
         <v>461</v>
-      </c>
-      <c r="B306" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B307" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
+        <v>452</v>
+      </c>
+      <c r="B308" t="s">
         <v>453</v>
-      </c>
-      <c r="B308" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B309" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
+        <v>448</v>
+      </c>
+      <c r="B310" t="s">
         <v>449</v>
-      </c>
-      <c r="B310" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B311" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
+        <v>500</v>
+      </c>
+      <c r="B312" t="s">
         <v>501</v>
-      </c>
-      <c r="B312" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B313" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
+        <v>475</v>
+      </c>
+      <c r="B314" t="s">
         <v>476</v>
-      </c>
-      <c r="B314" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B315" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B316" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B317" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B318" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B319" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B320" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B321" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
+        <v>456</v>
+      </c>
+      <c r="B322" t="s">
         <v>457</v>
-      </c>
-      <c r="B322" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
+        <v>429</v>
+      </c>
+      <c r="B323" t="s">
         <v>430</v>
-      </c>
-      <c r="B323" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B324" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
+        <v>483</v>
+      </c>
+      <c r="B325" t="s">
         <v>484</v>
-      </c>
-      <c r="B325" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B326" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B327" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
+        <v>495</v>
+      </c>
+      <c r="B328" t="s">
         <v>496</v>
-      </c>
-      <c r="B328" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B329" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B330" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B331" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B332" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
+        <v>432</v>
+      </c>
+      <c r="B333" t="s">
         <v>433</v>
-      </c>
-      <c r="B333" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
+        <v>505</v>
+      </c>
+      <c r="B334" t="s">
         <v>506</v>
-      </c>
-      <c r="B334" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
+        <v>471</v>
+      </c>
+      <c r="B335" t="s">
         <v>472</v>
-      </c>
-      <c r="B335" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
+        <v>464</v>
+      </c>
+      <c r="B336" t="s">
         <v>465</v>
-      </c>
-      <c r="B336" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B337" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B338" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
+        <v>438</v>
+      </c>
+      <c r="B339" t="s">
         <v>439</v>
-      </c>
-      <c r="B339" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B340" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
+        <v>434</v>
+      </c>
+      <c r="B341" t="s">
         <v>435</v>
-      </c>
-      <c r="B341" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
+        <v>508</v>
+      </c>
+      <c r="B342" t="s">
         <v>509</v>
-      </c>
-      <c r="B342" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B343" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
+        <v>467</v>
+      </c>
+      <c r="B344" t="s">
         <v>468</v>
-      </c>
-      <c r="B344" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
+        <v>436</v>
+      </c>
+      <c r="B345" t="s">
         <v>437</v>
-      </c>
-      <c r="B345" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B346" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
+        <v>510</v>
+      </c>
+      <c r="B347" t="s">
         <v>511</v>
-      </c>
-      <c r="B347" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B348" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
   </sheetData>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FDA6DEC-402A-A84E-B312-332D6F2E3511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88419E85-6E46-8242-9B1C-E18FCE4D7E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2780" yWindow="1760" windowWidth="27240" windowHeight="16440" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1842" uniqueCount="1053">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1842" uniqueCount="1052">
   <si>
     <t>Household Name</t>
   </si>
@@ -3186,16 +3186,13 @@
     <t>Todd Christian (Illumina)</t>
   </si>
   <si>
-    <t>Christian Concert 2026 Tickets | Opportunity | Salesforce</t>
-  </si>
-  <si>
     <t>San Diego Biomed</t>
   </si>
   <si>
     <t>Additionally purchased table</t>
   </si>
   <si>
-    <t>San Diego Biomedical Concert 2026 Tickets | Opportunity | Salesforce</t>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uJkzpYAC/view</t>
   </si>
 </sst>
 </file>
@@ -8391,7 +8388,7 @@
       </c>
       <c r="E228" s="3"/>
       <c r="F228" s="1" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="G228" s="3"/>
       <c r="H228" s="3"/>
@@ -8515,7 +8512,7 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>837</v>
@@ -8527,10 +8524,10 @@
         <v>168</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>1052</v>
+        <v>391</v>
       </c>
       <c r="G235" s="3"/>
       <c r="H235" s="3"/>
@@ -8677,8 +8674,8 @@
     <hyperlink ref="I199" r:id="rId63" xr:uid="{F22BA3C7-AF46-734F-B794-63EDB1C464F2}"/>
     <hyperlink ref="F225" r:id="rId64" xr:uid="{EBE8A84F-7758-B643-B6C8-2F914C73F877}"/>
     <hyperlink ref="F226" r:id="rId65" xr:uid="{F46B40A5-400F-8143-A9E8-E880E9EC381D}"/>
-    <hyperlink ref="F228" r:id="rId66" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uJkzpYAC/view" xr:uid="{42235C5A-3531-CA40-88C6-28FBF478ECEB}"/>
-    <hyperlink ref="F235" r:id="rId67" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000rDw2uYAC/view" xr:uid="{D43EE19D-AFBE-234B-9089-CBB823EA7E10}"/>
+    <hyperlink ref="F235" r:id="rId66" xr:uid="{A244B320-AB44-FA4F-B729-59E47E5DF2B0}"/>
+    <hyperlink ref="F228" r:id="rId67" xr:uid="{74A4A6AC-04FA-874F-B8D7-4A69A07AD06D}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C514481F-3876-DD4B-AD2F-0BFBC7D28563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080947AE-18DC-874F-B697-1A9DADF66F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="1840" windowWidth="29820" windowHeight="19560" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
+    <workbookView xWindow="2140" yWindow="1840" windowWidth="29820" windowHeight="19560" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
   <sheets>
     <sheet name="xlsx" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1842" uniqueCount="1056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1842" uniqueCount="1055">
   <si>
     <t>Household Name</t>
   </si>
@@ -507,9 +507,6 @@
     <t>Sponsor Hold</t>
   </si>
   <si>
-    <t>Clayco Construction $125000 Sponsorship 6/1/2026 | Opportunity | Salesforce</t>
-  </si>
-  <si>
     <t>Trott</t>
   </si>
   <si>
@@ -2979,21 +2976,12 @@
     <t>Elisa Jaime + Lynda Kerr</t>
   </si>
   <si>
-    <t>Kerr Concert 2026 Tickets | Opportunity | Salesforce</t>
-  </si>
-  <si>
     <t>Amy + Jim Wood</t>
   </si>
   <si>
     <t>Gary Levine + Larry Bloch + Mitch Adler</t>
   </si>
   <si>
-    <t>Adler Concert 2026 Tickets | Opportunity | Salesforce</t>
-  </si>
-  <si>
-    <t>Tafel Klaus Concert 2026 Tickets | Opportunity | Salesforce</t>
-  </si>
-  <si>
     <t>Theodora Polamalu</t>
   </si>
   <si>
@@ -3162,15 +3150,9 @@
     <t>Amy Myers</t>
   </si>
   <si>
-    <t>Socol Concert 2026 Tickets | Opportunity | Salesforce</t>
-  </si>
-  <si>
     <t>Vickey Syage</t>
   </si>
   <si>
-    <t>Whittington Concert 2026 Tickets | Opportunity | Salesforce</t>
-  </si>
-  <si>
     <t>(now requesting E54 or near that area)</t>
   </si>
   <si>
@@ -3195,16 +3177,31 @@
     <t>Mary Ellen Aviano</t>
   </si>
   <si>
-    <t>Aviano Concert 2026 Tickets | Opportunity | Salesforce</t>
-  </si>
-  <si>
     <t>Stephanie Smith</t>
   </si>
   <si>
     <t>Donating to cancer fighters</t>
   </si>
   <si>
-    <t>Justin and Stephanie Smith and Friends Household | Account | Salesforce</t>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u72eLYAQ/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000rvp8wYAA/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000Q2enCYAR/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u9QkgYAE/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uXDB9YAO/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uutEVYAY/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Account/0014W00002W8eYDQAZ/view</t>
   </si>
 </sst>
 </file>
@@ -3644,6 +3641,8 @@
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="5" max="5" width="58.33203125" customWidth="1"/>
+    <col min="6" max="6" width="84.6640625" customWidth="1"/>
+    <col min="7" max="7" width="77.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -3698,7 +3697,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>14</v>
@@ -3765,7 +3764,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>12</v>
@@ -3801,7 +3800,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>32</v>
@@ -3817,14 +3816,14 @@
         <v>34</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>980</v>
+        <v>1048</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>35</v>
@@ -3950,7 +3949,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>58</v>
@@ -3969,13 +3968,13 @@
         <v>61</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>983</v>
+        <v>1049</v>
       </c>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>62</v>
@@ -4082,7 +4081,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>81</v>
@@ -4103,7 +4102,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>84</v>
@@ -4128,7 +4127,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>88</v>
@@ -4218,7 +4217,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>106</v>
@@ -4234,7 +4233,7 @@
         <v>108</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -4380,7 +4379,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -4466,7 +4465,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>151</v>
@@ -4489,7 +4488,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="1" t="s">
-        <v>156</v>
+        <v>1050</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -4497,13 +4496,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>155</v>
@@ -4516,20 +4515,20 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -4540,16 +4539,16 @@
         <v>21</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="D42" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="2"/>
@@ -4561,17 +4560,17 @@
         <v>50</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="1" t="s">
-        <v>984</v>
+        <v>1051</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -4579,20 +4578,20 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -4600,20 +4599,20 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -4621,20 +4620,20 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -4642,20 +4641,20 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -4663,20 +4662,20 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
@@ -4684,20 +4683,20 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -4705,20 +4704,20 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -4726,20 +4725,20 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
@@ -4747,20 +4746,20 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>201</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
@@ -4768,22 +4767,22 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="D53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E53" s="2" t="s">
+      <c r="F53" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -4791,20 +4790,20 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C54" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
@@ -4812,20 +4811,20 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>214</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
@@ -4833,20 +4832,20 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
@@ -4854,20 +4853,20 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
@@ -4875,20 +4874,20 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C58" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
@@ -4896,20 +4895,20 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>229</v>
-      </c>
       <c r="C59" s="2" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
@@ -4917,20 +4916,20 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>233</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>234</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
@@ -4938,20 +4937,20 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="C61" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
@@ -4959,13 +4958,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>241</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>155</v>
@@ -4978,13 +4977,13 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="C63" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>155</v>
@@ -4997,20 +4996,20 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="C64" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
@@ -5018,13 +5017,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="C65" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>251</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>12</v>
@@ -5037,20 +5036,20 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="C66" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
@@ -5058,20 +5057,20 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="C67" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
@@ -5079,20 +5078,20 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
@@ -5100,20 +5099,20 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
@@ -5121,20 +5120,20 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="C70" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
@@ -5142,20 +5141,20 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="C71" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>271</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
@@ -5163,20 +5162,20 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
@@ -5184,20 +5183,20 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
@@ -5205,20 +5204,20 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B74" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" s="5" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
@@ -5226,20 +5225,20 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="C75" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
@@ -5247,22 +5246,22 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B76" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="C76" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="D76" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D76" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E76" s="2" t="s">
+      <c r="F76" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -5270,20 +5269,20 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="C77" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>294</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
@@ -5291,20 +5290,20 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="C78" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
@@ -5312,20 +5311,20 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
@@ -5333,20 +5332,20 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="C80" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>305</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
@@ -5354,20 +5353,20 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="5" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
@@ -5375,16 +5374,16 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B82" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>311</v>
-      </c>
       <c r="D82" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E82" s="7"/>
       <c r="F82" s="7"/>
@@ -5394,20 +5393,20 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="C83" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>314</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="1" t="s">
-        <v>1041</v>
+        <v>314</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -5415,20 +5414,20 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="C84" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>318</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
@@ -5436,20 +5435,20 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="C85" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>321</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
@@ -5457,20 +5456,20 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>324</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="5" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -5478,43 +5477,43 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="C87" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>327</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="5" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="C88" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -5522,20 +5521,20 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="C89" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>335</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -5543,20 +5542,20 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B90" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -5564,20 +5563,20 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>341</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" s="5" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -5585,20 +5584,20 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B92" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>343</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="5" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -5606,20 +5605,20 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="B93" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>346</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="5" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -5627,20 +5626,20 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="B94" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>348</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -5648,20 +5647,20 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B95" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>350</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="5" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -5669,20 +5668,20 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="C96" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>353</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="5" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -5690,20 +5689,20 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B97" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
@@ -5711,20 +5710,20 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B98" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>358</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="5" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
@@ -5732,20 +5731,20 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B99" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>360</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="5" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
@@ -5753,20 +5752,20 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="C100" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
@@ -5774,20 +5773,20 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B101" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
@@ -5795,20 +5794,20 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="5" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
@@ -5816,20 +5815,20 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B103" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>372</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -5837,20 +5836,20 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="C104" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>375</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -5858,20 +5857,20 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B105" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" s="5" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -5879,20 +5878,20 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="C106" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -5900,20 +5899,20 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B107" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>384</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" s="5" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
@@ -5921,20 +5920,20 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="C108" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>387</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
@@ -5942,20 +5941,20 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B109" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>393</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
@@ -5963,20 +5962,20 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="C110" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>396</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
@@ -5984,20 +5983,20 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="C111" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
@@ -6005,20 +6004,20 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B112" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>401</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
@@ -6026,13 +6025,13 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="C113" s="2" t="s">
         <v>403</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>404</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>12</v>
@@ -6045,13 +6044,13 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B114" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>12</v>
@@ -6064,13 +6063,13 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B115" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C115" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>408</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>12</v>
@@ -6083,20 +6082,20 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="B116" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C116" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" s="1" t="s">
-        <v>1043</v>
+        <v>1052</v>
       </c>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
@@ -6104,20 +6103,20 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B117" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="C117" s="2" t="s">
         <v>412</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>413</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
@@ -6125,20 +6124,20 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B118" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C118" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>416</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
@@ -6146,20 +6145,20 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="C119" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
@@ -6167,20 +6166,20 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B120" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C120" s="2" t="s">
         <v>421</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>422</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
@@ -6188,20 +6187,20 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B121" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C121" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>424</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
@@ -6209,20 +6208,20 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="C122" s="2" t="s">
         <v>426</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>427</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
@@ -6230,20 +6229,20 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B123" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C123" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>430</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="5" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
@@ -6251,20 +6250,20 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B124" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C124" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>432</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="5" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
@@ -6272,20 +6271,20 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B125" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>434</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="5" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
@@ -6293,20 +6292,20 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B126" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="5" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
@@ -6314,20 +6313,20 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="C127" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>439</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
@@ -6335,20 +6334,20 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="C128" s="2" t="s">
         <v>442</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>443</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
@@ -6356,20 +6355,20 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B129" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C129" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>446</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
@@ -6377,20 +6376,20 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B130" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="C130" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
@@ -6398,22 +6397,22 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="C131" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="D131" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F131" s="2" t="s">
         <v>454</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>1044</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>455</v>
       </c>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
@@ -6421,22 +6420,22 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B132" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="C132" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="D132" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="D132" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>459</v>
-      </c>
       <c r="F132" s="3" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
@@ -6444,20 +6443,20 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B133" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="C133" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
@@ -6465,22 +6464,22 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="C134" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="D134" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="F134" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>466</v>
       </c>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
@@ -6488,20 +6487,20 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B135" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="C135" s="2" t="s">
         <v>468</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>469</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
@@ -6509,20 +6508,20 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B136" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="C136" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>473</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
@@ -6530,22 +6529,22 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B137" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="C137" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="C137" s="2" t="s">
+      <c r="D137" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F137" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
@@ -6553,20 +6552,20 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="C138" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
@@ -6574,20 +6573,20 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B139" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="C139" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
@@ -6595,22 +6594,22 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="C140" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="D140" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E140" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="D140" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>490</v>
-      </c>
       <c r="F140" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
@@ -6618,20 +6617,20 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="C141" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>493</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
@@ -6642,17 +6641,17 @@
         <v>17</v>
       </c>
       <c r="B142" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C142" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
@@ -6663,17 +6662,17 @@
         <v>17</v>
       </c>
       <c r="B143" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C143" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>498</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
@@ -6684,17 +6683,17 @@
         <v>17</v>
       </c>
       <c r="B144" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="C144" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
@@ -6702,22 +6701,22 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="C145" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="D145" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F145" s="5" t="s">
         <v>503</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>504</v>
       </c>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
@@ -6725,22 +6724,22 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B146" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="C146" s="2" t="s">
-        <v>506</v>
-      </c>
       <c r="D146" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
@@ -6748,22 +6747,22 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B147" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C147" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="C147" s="2" t="s">
-        <v>508</v>
-      </c>
       <c r="D147" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
@@ -6771,20 +6770,20 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="B148" s="2" t="s">
+      <c r="C148" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
@@ -6792,20 +6791,20 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B149" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="C149" s="2" t="s">
         <v>513</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>514</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
@@ -6813,20 +6812,20 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B150" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>517</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
@@ -6834,20 +6833,20 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="C151" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>520</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
@@ -6855,20 +6854,20 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B152" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>522</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>523</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" s="5" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
@@ -6876,20 +6875,20 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B153" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>524</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>525</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" s="5" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
@@ -6897,20 +6896,20 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="C154" s="2" t="s">
         <v>527</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>528</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" s="5" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
@@ -6918,20 +6917,20 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B155" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>529</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>530</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" s="5" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
@@ -6939,20 +6938,20 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B156" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C156" s="2" t="s">
         <v>531</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>532</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" s="5" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
@@ -6960,20 +6959,20 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B157" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="C157" s="2" t="s">
         <v>533</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>534</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" s="5" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
@@ -6981,20 +6980,20 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B158" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="B158" s="2" t="s">
+      <c r="C158" s="2" t="s">
         <v>536</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>537</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" s="5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
@@ -7002,20 +7001,20 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B159" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>539</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" s="5" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
@@ -7023,20 +7022,20 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B160" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>541</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>542</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" s="5" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
@@ -7044,20 +7043,20 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B161" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="B161" s="2" t="s">
+      <c r="C161" s="2" t="s">
         <v>544</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>545</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
@@ -7065,20 +7064,20 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B162" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="B162" s="2" t="s">
+      <c r="C162" s="2" t="s">
         <v>548</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>549</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
@@ -7086,22 +7085,22 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B163" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="C163" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="D163" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E163" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="D163" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E163" s="2" t="s">
+      <c r="F163" s="2" t="s">
         <v>554</v>
-      </c>
-      <c r="F163" s="2" t="s">
-        <v>555</v>
       </c>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
@@ -7109,22 +7108,22 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="B164" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="C164" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="C164" s="2" t="s">
-        <v>557</v>
-      </c>
       <c r="D164" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
@@ -7132,22 +7131,22 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="B165" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C165" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="C165" s="2" t="s">
-        <v>559</v>
-      </c>
       <c r="D165" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
@@ -7155,20 +7154,20 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B166" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C166" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>390</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
@@ -7176,70 +7175,70 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="B167" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="C167" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="C167" s="2" t="s">
-        <v>562</v>
-      </c>
       <c r="D167" s="2" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" s="5" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B168" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="B168" s="2" t="s">
-        <v>565</v>
-      </c>
       <c r="C168" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" s="3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B169" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="B169" s="2" t="s">
-        <v>567</v>
-      </c>
       <c r="C169" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" s="3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
@@ -7247,16 +7246,16 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B170" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="B170" s="2" t="s">
+      <c r="C170" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="C170" s="2" t="s">
+      <c r="D170" s="2" t="s">
         <v>570</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>571</v>
       </c>
       <c r="E170" s="7"/>
       <c r="F170" s="7"/>
@@ -7266,16 +7265,16 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B171" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C171" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="C171" s="2" t="s">
-        <v>573</v>
-      </c>
       <c r="D171" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E171" s="7"/>
       <c r="F171" s="7"/>
@@ -7285,16 +7284,16 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B172" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="C172" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="C172" s="2" t="s">
-        <v>575</v>
-      </c>
       <c r="D172" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E172" s="7"/>
       <c r="F172" s="7"/>
@@ -7304,16 +7303,16 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B173" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C173" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="C173" s="2" t="s">
-        <v>577</v>
-      </c>
       <c r="D173" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E173" s="7"/>
       <c r="F173" s="7"/>
@@ -7323,16 +7322,16 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B174" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="C174" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="C174" s="2" t="s">
-        <v>579</v>
-      </c>
       <c r="D174" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E174" s="7"/>
       <c r="F174" s="7"/>
@@ -7342,16 +7341,16 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B175" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="C175" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="C175" s="2" t="s">
-        <v>581</v>
-      </c>
       <c r="D175" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E175" s="7"/>
       <c r="F175" s="7"/>
@@ -7361,16 +7360,16 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B176" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="C176" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="C176" s="2" t="s">
-        <v>583</v>
-      </c>
       <c r="D176" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E176" s="7"/>
       <c r="F176" s="7"/>
@@ -7380,16 +7379,16 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B177" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C177" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="C177" s="2" t="s">
-        <v>585</v>
-      </c>
       <c r="D177" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E177" s="7"/>
       <c r="F177" s="7"/>
@@ -7399,16 +7398,16 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B178" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="C178" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="C178" s="2" t="s">
-        <v>587</v>
-      </c>
       <c r="D178" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E178" s="7"/>
       <c r="F178" s="7"/>
@@ -7418,16 +7417,16 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B179" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="C179" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="C179" s="2" t="s">
-        <v>589</v>
-      </c>
       <c r="D179" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E179" s="7"/>
       <c r="F179" s="7"/>
@@ -7437,16 +7436,16 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B180" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="C180" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="C180" s="2" t="s">
-        <v>591</v>
-      </c>
       <c r="D180" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E180" s="7"/>
       <c r="F180" s="7"/>
@@ -7456,16 +7455,16 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B181" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="C181" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="C181" s="2" t="s">
-        <v>593</v>
-      </c>
       <c r="D181" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E181" s="7"/>
       <c r="F181" s="7"/>
@@ -7475,16 +7474,16 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B182" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="C182" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="C182" s="2" t="s">
-        <v>595</v>
-      </c>
       <c r="D182" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E182" s="7"/>
       <c r="F182" s="7"/>
@@ -7494,16 +7493,16 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B183" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="C183" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="C183" s="2" t="s">
-        <v>597</v>
-      </c>
       <c r="D183" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E183" s="7"/>
       <c r="F183" s="7"/>
@@ -7513,16 +7512,16 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B184" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="C184" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="C184" s="2" t="s">
-        <v>599</v>
-      </c>
       <c r="D184" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E184" s="7"/>
       <c r="F184" s="7"/>
@@ -7532,16 +7531,16 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E185" s="7"/>
       <c r="F185" s="7"/>
@@ -7551,16 +7550,16 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E186" s="7"/>
       <c r="F186" s="7"/>
@@ -7570,16 +7569,16 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E187" s="7"/>
       <c r="F187" s="7"/>
@@ -7589,16 +7588,16 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E188" s="7"/>
       <c r="F188" s="7"/>
@@ -7608,16 +7607,16 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E189" s="7"/>
       <c r="F189" s="7"/>
@@ -7627,16 +7626,16 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E190" s="7"/>
       <c r="F190" s="7"/>
@@ -7646,16 +7645,16 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E191" s="7"/>
       <c r="F191" s="7"/>
@@ -7665,16 +7664,16 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E192" s="7"/>
       <c r="F192" s="7"/>
@@ -7684,16 +7683,16 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E193" s="7"/>
       <c r="F193" s="7"/>
@@ -7703,16 +7702,16 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E194" s="7"/>
       <c r="F194" s="7"/>
@@ -7722,16 +7721,16 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E195" s="7"/>
       <c r="F195" s="7"/>
@@ -7741,20 +7740,20 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B196" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="B196" s="2" t="s">
-        <v>612</v>
-      </c>
       <c r="C196" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
@@ -7762,20 +7761,20 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B197" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B197" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="C197" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E197" s="2"/>
       <c r="F197" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
@@ -7783,20 +7782,20 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B198" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="B198" s="2" t="s">
-        <v>617</v>
-      </c>
       <c r="C198" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E198" s="2"/>
       <c r="F198" s="3" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
@@ -7804,43 +7803,43 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="E199" s="2"/>
       <c r="F199" s="5" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E200" s="7"/>
       <c r="F200" s="7"/>
@@ -7850,20 +7849,20 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="E201" s="2"/>
       <c r="F201" s="1" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
@@ -7871,16 +7870,16 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E202" s="7"/>
       <c r="F202" s="7"/>
@@ -7890,16 +7889,16 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E203" s="7"/>
       <c r="F203" s="7"/>
@@ -7909,16 +7908,16 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B204" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="C204" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="C204" s="2" t="s">
-        <v>624</v>
-      </c>
       <c r="D204" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E204" s="7"/>
       <c r="F204" s="7"/>
@@ -7928,16 +7927,16 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B205" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="C205" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="C205" s="2" t="s">
-        <v>626</v>
-      </c>
       <c r="D205" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E205" s="7"/>
       <c r="F205" s="7"/>
@@ -7947,16 +7946,16 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B206" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C206" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="C206" s="2" t="s">
-        <v>628</v>
-      </c>
       <c r="D206" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E206" s="7"/>
       <c r="F206" s="7"/>
@@ -7966,16 +7965,16 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B207" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C207" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="C207" s="2" t="s">
-        <v>630</v>
-      </c>
       <c r="D207" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E207" s="7"/>
       <c r="F207" s="7"/>
@@ -7985,16 +7984,16 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B208" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C208" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="C208" s="2" t="s">
-        <v>632</v>
-      </c>
       <c r="D208" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E208" s="7"/>
       <c r="F208" s="7"/>
@@ -8004,16 +8003,16 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B209" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="C209" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="C209" s="2" t="s">
-        <v>634</v>
-      </c>
       <c r="D209" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E209" s="7"/>
       <c r="F209" s="7"/>
@@ -8023,16 +8022,16 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B210" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="C210" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="C210" s="2" t="s">
-        <v>636</v>
-      </c>
       <c r="D210" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E210" s="7"/>
       <c r="F210" s="7"/>
@@ -8042,16 +8041,16 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B211" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="C211" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="C211" s="2" t="s">
-        <v>638</v>
-      </c>
       <c r="D211" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E211" s="7"/>
       <c r="F211" s="7"/>
@@ -8061,16 +8060,16 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B212" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="C212" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="C212" s="2" t="s">
-        <v>640</v>
-      </c>
       <c r="D212" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E212" s="7"/>
       <c r="F212" s="7"/>
@@ -8080,16 +8079,16 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A213" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="B213" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="B213" s="2" t="s">
+      <c r="C213" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="C213" s="2" t="s">
-        <v>643</v>
-      </c>
       <c r="D213" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E213" s="7"/>
       <c r="F213" s="7"/>
@@ -8099,16 +8098,16 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B214" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="C214" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="C214" s="2" t="s">
-        <v>645</v>
-      </c>
       <c r="D214" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E214" s="7"/>
       <c r="F214" s="7"/>
@@ -8118,16 +8117,16 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B215" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="C215" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="C215" s="2" t="s">
-        <v>647</v>
-      </c>
       <c r="D215" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E215" s="7"/>
       <c r="F215" s="7"/>
@@ -8137,16 +8136,16 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B216" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="C216" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="C216" s="2" t="s">
-        <v>649</v>
-      </c>
       <c r="D216" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E216" s="7"/>
       <c r="F216" s="7"/>
@@ -8156,16 +8155,16 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B217" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="C217" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C217" s="2" t="s">
-        <v>651</v>
-      </c>
       <c r="D217" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E217" s="7"/>
       <c r="F217" s="7"/>
@@ -8175,16 +8174,16 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B218" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="C218" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="C218" s="2" t="s">
-        <v>653</v>
-      </c>
       <c r="D218" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E218" s="7"/>
       <c r="F218" s="7"/>
@@ -8194,16 +8193,16 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B219" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="C219" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="C219" s="2" t="s">
-        <v>655</v>
-      </c>
       <c r="D219" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E219" s="7"/>
       <c r="F219" s="7"/>
@@ -8213,16 +8212,16 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E220" s="7"/>
       <c r="F220" s="7"/>
@@ -8232,16 +8231,16 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E221" s="7"/>
       <c r="F221" s="7"/>
@@ -8251,16 +8250,16 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E222" s="7"/>
       <c r="F222" s="7"/>
@@ -8270,16 +8269,16 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E223" s="7"/>
       <c r="F223" s="7"/>
@@ -8289,16 +8288,16 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E224" s="7"/>
       <c r="F224" s="7"/>
@@ -8308,20 +8307,20 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" s="2" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="E225" s="2"/>
       <c r="F225" s="1" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
@@ -8329,22 +8328,22 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
@@ -8352,22 +8351,22 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" s="2" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="E227" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F227" s="1" t="s">
         <v>1054</v>
-      </c>
-      <c r="F227" s="1" t="s">
-        <v>1055</v>
       </c>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
@@ -8375,20 +8374,20 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="E228" s="2"/>
       <c r="F228" s="1" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
@@ -8397,10 +8396,10 @@
     <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229" s="2"/>
       <c r="B229" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D229" s="2"/>
       <c r="E229" s="7"/>
@@ -8411,16 +8410,16 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="B230" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="B230" s="2" t="s">
-        <v>713</v>
-      </c>
       <c r="C230" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E230" s="7"/>
       <c r="F230" s="7"/>
@@ -8430,16 +8429,16 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E231" s="7"/>
       <c r="F231" s="7"/>
@@ -8449,16 +8448,16 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E232" s="7"/>
       <c r="F232" s="7"/>
@@ -8468,16 +8467,16 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E233" s="7"/>
       <c r="F233" s="7"/>
@@ -8487,16 +8486,16 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B234" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="C234" s="2" t="s">
         <v>867</v>
       </c>
-      <c r="C234" s="2" t="s">
-        <v>868</v>
-      </c>
       <c r="D234" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E234" s="7"/>
       <c r="F234" s="7"/>
@@ -8506,22 +8505,22 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="2" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="B235" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="C235" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="C235" s="2" t="s">
-        <v>837</v>
-      </c>
       <c r="D235" s="2" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G235" s="2"/>
       <c r="H235" s="2"/>
@@ -8598,75 +8597,67 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G8" r:id="rId1" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u72eLYAQ/view" xr:uid="{08BA72A6-6835-8948-9100-21D0F9CAE38F}"/>
-    <hyperlink ref="H15" r:id="rId2" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000rvp8wYAA/view" xr:uid="{65C4FF31-A81E-344C-B9D7-06BBC95A1ECE}"/>
-    <hyperlink ref="F16" r:id="rId3" xr:uid="{4D83744C-709D-1C41-BA5E-BD2AE84E9412}"/>
-    <hyperlink ref="F39" r:id="rId4" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000Q2enCYAR/view" xr:uid="{9528373A-3D1B-304A-9579-0C3C0BC7B6AE}"/>
-    <hyperlink ref="F43" r:id="rId5" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u9QkgYAE/view" xr:uid="{85A6A25D-D438-6446-A617-E81B6D86849D}"/>
-    <hyperlink ref="F73" r:id="rId6" xr:uid="{E171D32A-9215-BC46-80D0-A79887E19E01}"/>
-    <hyperlink ref="F74" r:id="rId7" xr:uid="{9DF0B287-4625-CB48-801B-9E764F127A83}"/>
-    <hyperlink ref="F81" r:id="rId8" xr:uid="{FB164A30-A480-E143-8EA5-3998C45CB0D7}"/>
-    <hyperlink ref="F83" r:id="rId9" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{26DEFE91-F6FD-9B41-98AC-752A24E75E50}"/>
-    <hyperlink ref="F85" r:id="rId10" xr:uid="{AF0BFBD2-717C-FC4A-B33B-2D3C915AEB0D}"/>
-    <hyperlink ref="F86" r:id="rId11" xr:uid="{DE9BE6D6-A787-AA4D-B623-F01F084CE0B0}"/>
-    <hyperlink ref="F87" r:id="rId12" xr:uid="{19BA1FCC-1651-F144-9744-891570D1AA16}"/>
-    <hyperlink ref="F90" r:id="rId13" xr:uid="{B9A95435-246B-A94E-872F-C0D9B761A68B}"/>
-    <hyperlink ref="F91" r:id="rId14" xr:uid="{BA90320D-30CD-BE45-A3D1-DF54D2914E7A}"/>
-    <hyperlink ref="F92" r:id="rId15" xr:uid="{39E85E5F-728A-D742-AF01-0103FD12A971}"/>
-    <hyperlink ref="F93" r:id="rId16" xr:uid="{E4C380DC-FA3A-FC4F-B31F-D630BDD1C2F1}"/>
-    <hyperlink ref="F95" r:id="rId17" xr:uid="{F6111BC4-3075-1B45-A641-B65694F66E75}"/>
-    <hyperlink ref="F96" r:id="rId18" xr:uid="{BC04F785-48C5-2148-8E4D-98BDBDAA39A2}"/>
-    <hyperlink ref="F97" r:id="rId19" xr:uid="{707FB250-4006-6540-B5F2-7FA6B4D84AE1}"/>
-    <hyperlink ref="F98" r:id="rId20" xr:uid="{43AAD2B6-AD8E-DB4A-92F2-CB1FDC1AB0B8}"/>
-    <hyperlink ref="F99" r:id="rId21" xr:uid="{6B651F64-6FB9-6C48-B73B-D73AFA70E755}"/>
-    <hyperlink ref="F102" r:id="rId22" xr:uid="{C271DA1A-7EC9-C945-8E50-1E1DA3B913AF}"/>
-    <hyperlink ref="F103" r:id="rId23" xr:uid="{9A9983EC-9BD1-3548-87FB-A024F49EAD34}"/>
-    <hyperlink ref="F104" r:id="rId24" xr:uid="{D9253CE1-9F79-2449-AE00-75EC5FEF656A}"/>
-    <hyperlink ref="F105" r:id="rId25" xr:uid="{783D53D8-C4E8-A04D-B065-D3E480E850CC}"/>
-    <hyperlink ref="F106" r:id="rId26" xr:uid="{473D8204-2057-454C-AA07-27706272F915}"/>
-    <hyperlink ref="F107" r:id="rId27" xr:uid="{45DB696E-0B53-9940-9B1F-6F1C06EBF3F5}"/>
-    <hyperlink ref="F116" r:id="rId28" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uXDB9YAO/view" xr:uid="{B7603362-0752-0145-A740-02BBA291C491}"/>
-    <hyperlink ref="F119" r:id="rId29" xr:uid="{E56A32FA-602E-0146-B178-82687404DCEF}"/>
-    <hyperlink ref="F120" r:id="rId30" xr:uid="{041F1990-725F-F046-88DB-493F97A5760C}"/>
-    <hyperlink ref="F121" r:id="rId31" xr:uid="{E985503A-375A-3949-B95B-6BB03BAEAA01}"/>
-    <hyperlink ref="F122" r:id="rId32" xr:uid="{5A05BB01-A4D7-844D-80BE-89B2BA678BB0}"/>
-    <hyperlink ref="F123" r:id="rId33" xr:uid="{0B7F59E8-F289-B046-91BB-4F579E1CE558}"/>
-    <hyperlink ref="F124" r:id="rId34" xr:uid="{712F2B88-BDB0-E241-8E6D-451D262C6986}"/>
-    <hyperlink ref="F125" r:id="rId35" xr:uid="{86EF9220-27E0-1B42-B7E9-86744EAB0414}"/>
-    <hyperlink ref="F126" r:id="rId36" xr:uid="{ED57DC6C-6767-BE44-81D9-CF0A118CD0FE}"/>
-    <hyperlink ref="F133" r:id="rId37" xr:uid="{FEC8FACE-5A6E-C542-921E-2B157967AE85}"/>
-    <hyperlink ref="F145" r:id="rId38" xr:uid="{B9EE879B-229E-6741-9EE9-FBC67A23C348}"/>
-    <hyperlink ref="F146" r:id="rId39" xr:uid="{1E0EFBFE-053F-594C-9C10-1948BC7B9488}"/>
-    <hyperlink ref="F147" r:id="rId40" xr:uid="{D2D91943-D9F1-6342-9C2D-2F12A2A7D78F}"/>
-    <hyperlink ref="F148" r:id="rId41" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000s98yXYAQ/view" xr:uid="{E9D56349-9509-1A4D-9171-4F7104D11BA2}"/>
-    <hyperlink ref="F150" r:id="rId42" xr:uid="{9D81EB20-48E6-5A48-A6C7-F60F9DA8CBC1}"/>
-    <hyperlink ref="F151" r:id="rId43" xr:uid="{0EAF5AAB-C472-4E48-8C56-A3010416A213}"/>
-    <hyperlink ref="F152" r:id="rId44" xr:uid="{A6D2A713-186B-7940-B2C1-452735DC1441}"/>
-    <hyperlink ref="F153" r:id="rId45" xr:uid="{205067C4-9448-4F4F-9382-E4CF81BF5C06}"/>
-    <hyperlink ref="F154" r:id="rId46" xr:uid="{8E8ABFF6-D633-1341-A264-D9FCF4CECFE9}"/>
-    <hyperlink ref="F155" r:id="rId47" xr:uid="{BF78F0CE-B457-EA46-861E-06BD16FBD826}"/>
-    <hyperlink ref="F156" r:id="rId48" xr:uid="{C95D0D85-F640-BF4A-A84B-F07379198FFC}"/>
-    <hyperlink ref="F157" r:id="rId49" xr:uid="{D187263F-7347-3D41-A079-AD1579C398AD}"/>
-    <hyperlink ref="F158" r:id="rId50" xr:uid="{7791C319-5E9C-D248-8A81-7E299181536A}"/>
-    <hyperlink ref="F159" r:id="rId51" xr:uid="{E1ECCA8A-A61E-694F-B805-60F3AB6BFB50}"/>
-    <hyperlink ref="F160" r:id="rId52" xr:uid="{35B90A27-BD5A-9345-A8E7-7310FD6FBF20}"/>
-    <hyperlink ref="F164" r:id="rId53" xr:uid="{5DD3122C-5356-0844-B949-EF3C2DA4F343}"/>
-    <hyperlink ref="F165" r:id="rId54" xr:uid="{ED14609D-7B09-FE49-BE61-E9D9ADF3CFF7}"/>
-    <hyperlink ref="F167" r:id="rId55" xr:uid="{C5459565-305A-B545-83F2-2D5B3A1BAA7E}"/>
-    <hyperlink ref="G167" r:id="rId56" xr:uid="{BC0E9968-30CE-6A4D-BE19-A697EB2281FD}"/>
-    <hyperlink ref="H167" r:id="rId57" xr:uid="{06C543E1-8ECD-E349-B0AD-B573A44B4707}"/>
-    <hyperlink ref="I167" r:id="rId58" xr:uid="{B30DB557-A160-E641-8A7B-EC549B0188BE}"/>
-    <hyperlink ref="G168" r:id="rId59" xr:uid="{66A435B9-4B78-1347-B463-EEC74E39AEF8}"/>
-    <hyperlink ref="F199" r:id="rId60" xr:uid="{4494705E-34E4-C640-BC43-4ABE8BC739DD}"/>
-    <hyperlink ref="G199" r:id="rId61" xr:uid="{46D613B4-D756-0B44-B65A-D03E92803F8D}"/>
-    <hyperlink ref="H199" r:id="rId62" xr:uid="{E3E72607-F906-0A4C-B2CE-4C7931127AB2}"/>
-    <hyperlink ref="I199" r:id="rId63" xr:uid="{FEBE9D2E-D687-E548-B5DF-74901ECAF388}"/>
-    <hyperlink ref="F201" r:id="rId64" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uutEVYAY/view" xr:uid="{42746A26-EE7E-334B-ACE4-1E6052F28630}"/>
-    <hyperlink ref="F225" r:id="rId65" xr:uid="{8C0A64F8-8B65-FD46-B2C3-2691D27116E8}"/>
-    <hyperlink ref="F226" r:id="rId66" xr:uid="{49C8B99B-F637-E946-9D77-EF29843A88C2}"/>
-    <hyperlink ref="F227" r:id="rId67" display="https://curebound.lightning.force.com/lightning/r/Account/0014W00002W8eYDQAZ/view" xr:uid="{DB0D26CE-2E20-344C-BC1C-DB630D85FF04}"/>
-    <hyperlink ref="F228" r:id="rId68" xr:uid="{E0F44330-36E5-534E-8633-A00A60FB7629}"/>
-    <hyperlink ref="F235" r:id="rId69" xr:uid="{6EADA4E6-6752-C04A-8B4C-6E546ABF6A75}"/>
+    <hyperlink ref="F16" r:id="rId1" xr:uid="{4D83744C-709D-1C41-BA5E-BD2AE84E9412}"/>
+    <hyperlink ref="F73" r:id="rId2" xr:uid="{E171D32A-9215-BC46-80D0-A79887E19E01}"/>
+    <hyperlink ref="F74" r:id="rId3" xr:uid="{9DF0B287-4625-CB48-801B-9E764F127A83}"/>
+    <hyperlink ref="F81" r:id="rId4" xr:uid="{FB164A30-A480-E143-8EA5-3998C45CB0D7}"/>
+    <hyperlink ref="F85" r:id="rId5" xr:uid="{AF0BFBD2-717C-FC4A-B33B-2D3C915AEB0D}"/>
+    <hyperlink ref="F86" r:id="rId6" xr:uid="{DE9BE6D6-A787-AA4D-B623-F01F084CE0B0}"/>
+    <hyperlink ref="F87" r:id="rId7" xr:uid="{19BA1FCC-1651-F144-9744-891570D1AA16}"/>
+    <hyperlink ref="F90" r:id="rId8" xr:uid="{B9A95435-246B-A94E-872F-C0D9B761A68B}"/>
+    <hyperlink ref="F91" r:id="rId9" xr:uid="{BA90320D-30CD-BE45-A3D1-DF54D2914E7A}"/>
+    <hyperlink ref="F92" r:id="rId10" xr:uid="{39E85E5F-728A-D742-AF01-0103FD12A971}"/>
+    <hyperlink ref="F93" r:id="rId11" xr:uid="{E4C380DC-FA3A-FC4F-B31F-D630BDD1C2F1}"/>
+    <hyperlink ref="F95" r:id="rId12" xr:uid="{F6111BC4-3075-1B45-A641-B65694F66E75}"/>
+    <hyperlink ref="F96" r:id="rId13" xr:uid="{BC04F785-48C5-2148-8E4D-98BDBDAA39A2}"/>
+    <hyperlink ref="F97" r:id="rId14" xr:uid="{707FB250-4006-6540-B5F2-7FA6B4D84AE1}"/>
+    <hyperlink ref="F98" r:id="rId15" xr:uid="{43AAD2B6-AD8E-DB4A-92F2-CB1FDC1AB0B8}"/>
+    <hyperlink ref="F99" r:id="rId16" xr:uid="{6B651F64-6FB9-6C48-B73B-D73AFA70E755}"/>
+    <hyperlink ref="F102" r:id="rId17" xr:uid="{C271DA1A-7EC9-C945-8E50-1E1DA3B913AF}"/>
+    <hyperlink ref="F103" r:id="rId18" xr:uid="{9A9983EC-9BD1-3548-87FB-A024F49EAD34}"/>
+    <hyperlink ref="F104" r:id="rId19" xr:uid="{D9253CE1-9F79-2449-AE00-75EC5FEF656A}"/>
+    <hyperlink ref="F105" r:id="rId20" xr:uid="{783D53D8-C4E8-A04D-B065-D3E480E850CC}"/>
+    <hyperlink ref="F106" r:id="rId21" xr:uid="{473D8204-2057-454C-AA07-27706272F915}"/>
+    <hyperlink ref="F107" r:id="rId22" xr:uid="{45DB696E-0B53-9940-9B1F-6F1C06EBF3F5}"/>
+    <hyperlink ref="F119" r:id="rId23" xr:uid="{E56A32FA-602E-0146-B178-82687404DCEF}"/>
+    <hyperlink ref="F120" r:id="rId24" xr:uid="{041F1990-725F-F046-88DB-493F97A5760C}"/>
+    <hyperlink ref="F121" r:id="rId25" xr:uid="{E985503A-375A-3949-B95B-6BB03BAEAA01}"/>
+    <hyperlink ref="F122" r:id="rId26" xr:uid="{5A05BB01-A4D7-844D-80BE-89B2BA678BB0}"/>
+    <hyperlink ref="F123" r:id="rId27" xr:uid="{0B7F59E8-F289-B046-91BB-4F579E1CE558}"/>
+    <hyperlink ref="F124" r:id="rId28" xr:uid="{712F2B88-BDB0-E241-8E6D-451D262C6986}"/>
+    <hyperlink ref="F125" r:id="rId29" xr:uid="{86EF9220-27E0-1B42-B7E9-86744EAB0414}"/>
+    <hyperlink ref="F126" r:id="rId30" xr:uid="{ED57DC6C-6767-BE44-81D9-CF0A118CD0FE}"/>
+    <hyperlink ref="F133" r:id="rId31" xr:uid="{FEC8FACE-5A6E-C542-921E-2B157967AE85}"/>
+    <hyperlink ref="F145" r:id="rId32" xr:uid="{B9EE879B-229E-6741-9EE9-FBC67A23C348}"/>
+    <hyperlink ref="F146" r:id="rId33" xr:uid="{1E0EFBFE-053F-594C-9C10-1948BC7B9488}"/>
+    <hyperlink ref="F147" r:id="rId34" xr:uid="{D2D91943-D9F1-6342-9C2D-2F12A2A7D78F}"/>
+    <hyperlink ref="F148" r:id="rId35" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000s98yXYAQ/view" xr:uid="{E9D56349-9509-1A4D-9171-4F7104D11BA2}"/>
+    <hyperlink ref="F150" r:id="rId36" xr:uid="{9D81EB20-48E6-5A48-A6C7-F60F9DA8CBC1}"/>
+    <hyperlink ref="F151" r:id="rId37" xr:uid="{0EAF5AAB-C472-4E48-8C56-A3010416A213}"/>
+    <hyperlink ref="F152" r:id="rId38" xr:uid="{A6D2A713-186B-7940-B2C1-452735DC1441}"/>
+    <hyperlink ref="F153" r:id="rId39" xr:uid="{205067C4-9448-4F4F-9382-E4CF81BF5C06}"/>
+    <hyperlink ref="F154" r:id="rId40" xr:uid="{8E8ABFF6-D633-1341-A264-D9FCF4CECFE9}"/>
+    <hyperlink ref="F155" r:id="rId41" xr:uid="{BF78F0CE-B457-EA46-861E-06BD16FBD826}"/>
+    <hyperlink ref="F156" r:id="rId42" xr:uid="{C95D0D85-F640-BF4A-A84B-F07379198FFC}"/>
+    <hyperlink ref="F157" r:id="rId43" xr:uid="{D187263F-7347-3D41-A079-AD1579C398AD}"/>
+    <hyperlink ref="F158" r:id="rId44" xr:uid="{7791C319-5E9C-D248-8A81-7E299181536A}"/>
+    <hyperlink ref="F159" r:id="rId45" xr:uid="{E1ECCA8A-A61E-694F-B805-60F3AB6BFB50}"/>
+    <hyperlink ref="F160" r:id="rId46" xr:uid="{35B90A27-BD5A-9345-A8E7-7310FD6FBF20}"/>
+    <hyperlink ref="F164" r:id="rId47" xr:uid="{5DD3122C-5356-0844-B949-EF3C2DA4F343}"/>
+    <hyperlink ref="F165" r:id="rId48" xr:uid="{ED14609D-7B09-FE49-BE61-E9D9ADF3CFF7}"/>
+    <hyperlink ref="F167" r:id="rId49" xr:uid="{C5459565-305A-B545-83F2-2D5B3A1BAA7E}"/>
+    <hyperlink ref="G167" r:id="rId50" xr:uid="{BC0E9968-30CE-6A4D-BE19-A697EB2281FD}"/>
+    <hyperlink ref="H167" r:id="rId51" xr:uid="{06C543E1-8ECD-E349-B0AD-B573A44B4707}"/>
+    <hyperlink ref="I167" r:id="rId52" xr:uid="{B30DB557-A160-E641-8A7B-EC549B0188BE}"/>
+    <hyperlink ref="G168" r:id="rId53" xr:uid="{66A435B9-4B78-1347-B463-EEC74E39AEF8}"/>
+    <hyperlink ref="F199" r:id="rId54" xr:uid="{4494705E-34E4-C640-BC43-4ABE8BC739DD}"/>
+    <hyperlink ref="G199" r:id="rId55" xr:uid="{46D613B4-D756-0B44-B65A-D03E92803F8D}"/>
+    <hyperlink ref="H199" r:id="rId56" xr:uid="{E3E72607-F906-0A4C-B2CE-4C7931127AB2}"/>
+    <hyperlink ref="I199" r:id="rId57" xr:uid="{FEBE9D2E-D687-E548-B5DF-74901ECAF388}"/>
+    <hyperlink ref="F225" r:id="rId58" xr:uid="{8C0A64F8-8B65-FD46-B2C3-2691D27116E8}"/>
+    <hyperlink ref="F226" r:id="rId59" xr:uid="{49C8B99B-F637-E946-9D77-EF29843A88C2}"/>
+    <hyperlink ref="F228" r:id="rId60" xr:uid="{E0F44330-36E5-534E-8633-A00A60FB7629}"/>
+    <hyperlink ref="F235" r:id="rId61" xr:uid="{6EADA4E6-6752-C04A-8B4C-6E546ABF6A75}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8683,7 +8674,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
@@ -8731,42 +8722,42 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>719</v>
+      </c>
+      <c r="B7" t="s">
         <v>720</v>
-      </c>
-      <c r="B7" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>721</v>
+      </c>
+      <c r="B8" t="s">
         <v>722</v>
-      </c>
-      <c r="B8" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B9" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>645</v>
+      </c>
+      <c r="B10" t="s">
         <v>646</v>
-      </c>
-      <c r="B10" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>641</v>
+      </c>
+      <c r="B11" t="s">
         <v>642</v>
-      </c>
-      <c r="B11" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -8787,10 +8778,10 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>723</v>
+      </c>
+      <c r="B14" t="s">
         <v>724</v>
-      </c>
-      <c r="B14" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -8955,10 +8946,10 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
+        <v>725</v>
+      </c>
+      <c r="B35" t="s">
         <v>726</v>
-      </c>
-      <c r="B35" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
@@ -8995,10 +8986,10 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>727</v>
+      </c>
+      <c r="B40" t="s">
         <v>728</v>
-      </c>
-      <c r="B40" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
@@ -9019,10 +9010,10 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B43" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
@@ -9035,154 +9026,154 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
+        <v>730</v>
+      </c>
+      <c r="B45" t="s">
         <v>731</v>
-      </c>
-      <c r="B45" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>732</v>
+      </c>
+      <c r="B46" t="s">
         <v>733</v>
-      </c>
-      <c r="B46" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>169</v>
+      </c>
+      <c r="B47" t="s">
         <v>170</v>
-      </c>
-      <c r="B47" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>172</v>
+      </c>
+      <c r="B48" t="s">
         <v>173</v>
-      </c>
-      <c r="B48" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>175</v>
+      </c>
+      <c r="B49" t="s">
         <v>176</v>
-      </c>
-      <c r="B49" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>183</v>
+      </c>
+      <c r="B50" t="s">
         <v>184</v>
-      </c>
-      <c r="B50" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>179</v>
+      </c>
+      <c r="B51" t="s">
         <v>180</v>
-      </c>
-      <c r="B51" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>232</v>
+      </c>
+      <c r="B52" t="s">
         <v>233</v>
-      </c>
-      <c r="B52" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>191</v>
+      </c>
+      <c r="B53" t="s">
         <v>192</v>
-      </c>
-      <c r="B53" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>245</v>
+      </c>
+      <c r="B54" t="s">
         <v>246</v>
-      </c>
-      <c r="B54" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>187</v>
+      </c>
+      <c r="B55" t="s">
         <v>188</v>
-      </c>
-      <c r="B55" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
+        <v>195</v>
+      </c>
+      <c r="B56" t="s">
         <v>196</v>
-      </c>
-      <c r="B56" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
+        <v>249</v>
+      </c>
+      <c r="B57" t="s">
         <v>250</v>
-      </c>
-      <c r="B57" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>203</v>
+      </c>
+      <c r="B58" t="s">
         <v>204</v>
-      </c>
-      <c r="B58" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
+        <v>199</v>
+      </c>
+      <c r="B59" t="s">
         <v>200</v>
-      </c>
-      <c r="B59" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>208</v>
+      </c>
+      <c r="B60" t="s">
         <v>209</v>
-      </c>
-      <c r="B60" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B61" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
+        <v>216</v>
+      </c>
+      <c r="B62" t="s">
         <v>217</v>
-      </c>
-      <c r="B62" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>165</v>
+      </c>
+      <c r="B63" t="s">
         <v>166</v>
-      </c>
-      <c r="B63" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
@@ -9195,50 +9186,50 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
+        <v>160</v>
+      </c>
+      <c r="B65" t="s">
         <v>161</v>
-      </c>
-      <c r="B65" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
+        <v>735</v>
+      </c>
+      <c r="B66" t="s">
         <v>736</v>
-      </c>
-      <c r="B66" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B67" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
+        <v>255</v>
+      </c>
+      <c r="B68" t="s">
         <v>256</v>
-      </c>
-      <c r="B68" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
+        <v>737</v>
+      </c>
+      <c r="B69" t="s">
         <v>738</v>
-      </c>
-      <c r="B69" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
+        <v>242</v>
+      </c>
+      <c r="B70" t="s">
         <v>243</v>
-      </c>
-      <c r="B70" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
@@ -9251,10 +9242,10 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
+        <v>162</v>
+      </c>
+      <c r="B72" t="s">
         <v>163</v>
-      </c>
-      <c r="B72" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
@@ -9267,42 +9258,42 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
+        <v>739</v>
+      </c>
+      <c r="B74" t="s">
         <v>740</v>
-      </c>
-      <c r="B74" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
+        <v>236</v>
+      </c>
+      <c r="B75" t="s">
         <v>237</v>
-      </c>
-      <c r="B75" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
+        <v>741</v>
+      </c>
+      <c r="B76" t="s">
         <v>742</v>
-      </c>
-      <c r="B76" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
+        <v>743</v>
+      </c>
+      <c r="B77" t="s">
         <v>744</v>
-      </c>
-      <c r="B77" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
+        <v>239</v>
+      </c>
+      <c r="B78" t="s">
         <v>240</v>
-      </c>
-      <c r="B78" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
@@ -9315,2148 +9306,2148 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
+        <v>745</v>
+      </c>
+      <c r="B80" t="s">
         <v>746</v>
-      </c>
-      <c r="B80" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
+        <v>157</v>
+      </c>
+      <c r="B81" t="s">
         <v>158</v>
-      </c>
-      <c r="B81" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
+        <v>747</v>
+      </c>
+      <c r="B82" t="s">
         <v>748</v>
-      </c>
-      <c r="B82" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
+        <v>252</v>
+      </c>
+      <c r="B83" t="s">
         <v>253</v>
-      </c>
-      <c r="B83" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
+        <v>224</v>
+      </c>
+      <c r="B84" t="s">
         <v>225</v>
-      </c>
-      <c r="B84" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
+        <v>749</v>
+      </c>
+      <c r="B85" t="s">
         <v>750</v>
-      </c>
-      <c r="B85" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B86" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
+        <v>751</v>
+      </c>
+      <c r="B87" t="s">
         <v>752</v>
-      </c>
-      <c r="B87" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
+        <v>753</v>
+      </c>
+      <c r="B88" t="s">
         <v>754</v>
-      </c>
-      <c r="B88" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
+        <v>755</v>
+      </c>
+      <c r="B89" t="s">
         <v>756</v>
-      </c>
-      <c r="B89" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
+        <v>757</v>
+      </c>
+      <c r="B90" t="s">
         <v>758</v>
-      </c>
-      <c r="B90" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
+        <v>759</v>
+      </c>
+      <c r="B91" t="s">
         <v>760</v>
-      </c>
-      <c r="B91" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
+        <v>761</v>
+      </c>
+      <c r="B92" t="s">
         <v>762</v>
-      </c>
-      <c r="B92" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
+        <v>763</v>
+      </c>
+      <c r="B93" t="s">
         <v>764</v>
-      </c>
-      <c r="B93" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
+        <v>766</v>
+      </c>
+      <c r="B95" t="s">
         <v>767</v>
-      </c>
-      <c r="B95" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
+        <v>768</v>
+      </c>
+      <c r="B96" t="s">
         <v>769</v>
-      </c>
-      <c r="B96" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
+        <v>770</v>
+      </c>
+      <c r="B97" t="s">
         <v>771</v>
-      </c>
-      <c r="B97" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
+        <v>772</v>
+      </c>
+      <c r="B98" t="s">
         <v>773</v>
-      </c>
-      <c r="B98" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
+        <v>774</v>
+      </c>
+      <c r="B99" t="s">
         <v>775</v>
-      </c>
-      <c r="B99" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
+        <v>776</v>
+      </c>
+      <c r="B100" t="s">
         <v>777</v>
-      </c>
-      <c r="B100" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
+        <v>778</v>
+      </c>
+      <c r="B101" t="s">
         <v>779</v>
-      </c>
-      <c r="B101" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
+        <v>780</v>
+      </c>
+      <c r="B102" t="s">
         <v>781</v>
-      </c>
-      <c r="B102" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
+        <v>782</v>
+      </c>
+      <c r="B103" t="s">
         <v>783</v>
-      </c>
-      <c r="B103" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
+        <v>784</v>
+      </c>
+      <c r="B104" t="s">
         <v>785</v>
-      </c>
-      <c r="B104" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
+        <v>786</v>
+      </c>
+      <c r="B105" t="s">
         <v>787</v>
-      </c>
-      <c r="B105" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
+        <v>788</v>
+      </c>
+      <c r="B106" t="s">
         <v>789</v>
-      </c>
-      <c r="B106" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
+        <v>790</v>
+      </c>
+      <c r="B107" t="s">
         <v>791</v>
-      </c>
-      <c r="B107" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
+        <v>792</v>
+      </c>
+      <c r="B108" t="s">
         <v>793</v>
-      </c>
-      <c r="B108" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
+        <v>794</v>
+      </c>
+      <c r="B109" t="s">
         <v>795</v>
-      </c>
-      <c r="B109" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
+        <v>796</v>
+      </c>
+      <c r="B110" t="s">
         <v>797</v>
-      </c>
-      <c r="B110" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
+        <v>212</v>
+      </c>
+      <c r="B111" t="s">
         <v>213</v>
-      </c>
-      <c r="B111" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B112" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
+        <v>798</v>
+      </c>
+      <c r="B113" t="s">
         <v>799</v>
-      </c>
-      <c r="B113" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
+        <v>800</v>
+      </c>
+      <c r="B114" t="s">
         <v>801</v>
-      </c>
-      <c r="B114" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
+        <v>802</v>
+      </c>
+      <c r="B115" t="s">
         <v>803</v>
-      </c>
-      <c r="B115" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
+        <v>804</v>
+      </c>
+      <c r="B116" t="s">
         <v>805</v>
-      </c>
-      <c r="B116" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
+        <v>806</v>
+      </c>
+      <c r="B117" t="s">
         <v>807</v>
-      </c>
-      <c r="B117" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
+        <v>808</v>
+      </c>
+      <c r="B118" t="s">
         <v>809</v>
-      </c>
-      <c r="B118" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
+        <v>228</v>
+      </c>
+      <c r="B119" t="s">
         <v>229</v>
-      </c>
-      <c r="B119" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
+        <v>810</v>
+      </c>
+      <c r="B120" t="s">
         <v>811</v>
-      </c>
-      <c r="B120" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
+        <v>812</v>
+      </c>
+      <c r="B121" t="s">
         <v>813</v>
-      </c>
-      <c r="B121" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
+        <v>814</v>
+      </c>
+      <c r="B122" t="s">
         <v>815</v>
-      </c>
-      <c r="B122" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
+        <v>816</v>
+      </c>
+      <c r="B123" t="s">
         <v>817</v>
-      </c>
-      <c r="B123" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
+        <v>818</v>
+      </c>
+      <c r="B124" t="s">
         <v>819</v>
-      </c>
-      <c r="B124" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
+        <v>820</v>
+      </c>
+      <c r="B125" t="s">
         <v>821</v>
-      </c>
-      <c r="B125" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
+        <v>822</v>
+      </c>
+      <c r="B126" t="s">
         <v>823</v>
-      </c>
-      <c r="B126" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B127" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
+        <v>283</v>
+      </c>
+      <c r="B128" t="s">
         <v>284</v>
-      </c>
-      <c r="B128" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B129" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B130" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
+        <v>825</v>
+      </c>
+      <c r="B131" t="s">
         <v>826</v>
-      </c>
-      <c r="B131" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
+        <v>827</v>
+      </c>
+      <c r="B132" t="s">
         <v>828</v>
-      </c>
-      <c r="B132" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
+        <v>829</v>
+      </c>
+      <c r="B133" t="s">
         <v>830</v>
-      </c>
-      <c r="B133" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
+        <v>831</v>
+      </c>
+      <c r="B134" t="s">
         <v>832</v>
-      </c>
-      <c r="B134" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
+        <v>833</v>
+      </c>
+      <c r="B135" t="s">
         <v>834</v>
-      </c>
-      <c r="B135" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
+        <v>835</v>
+      </c>
+      <c r="B136" t="s">
         <v>836</v>
-      </c>
-      <c r="B136" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B137" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
+        <v>258</v>
+      </c>
+      <c r="B138" t="s">
         <v>259</v>
-      </c>
-      <c r="B138" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B139" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
+        <v>303</v>
+      </c>
+      <c r="B140" t="s">
         <v>304</v>
-      </c>
-      <c r="B140" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
+        <v>838</v>
+      </c>
+      <c r="B141" t="s">
         <v>839</v>
-      </c>
-      <c r="B141" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
+        <v>840</v>
+      </c>
+      <c r="B142" t="s">
         <v>841</v>
-      </c>
-      <c r="B142" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
+        <v>842</v>
+      </c>
+      <c r="B143" t="s">
         <v>843</v>
-      </c>
-      <c r="B143" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
+        <v>844</v>
+      </c>
+      <c r="B144" t="s">
         <v>845</v>
-      </c>
-      <c r="B144" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
+        <v>846</v>
+      </c>
+      <c r="B145" t="s">
         <v>847</v>
-      </c>
-      <c r="B145" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
+        <v>848</v>
+      </c>
+      <c r="B146" t="s">
         <v>849</v>
-      </c>
-      <c r="B146" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B147" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
+        <v>261</v>
+      </c>
+      <c r="B148" t="s">
         <v>262</v>
-      </c>
-      <c r="B148" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
+        <v>300</v>
+      </c>
+      <c r="B149" t="s">
         <v>301</v>
-      </c>
-      <c r="B149" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
+        <v>296</v>
+      </c>
+      <c r="B150" t="s">
         <v>297</v>
-      </c>
-      <c r="B150" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B151" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
+        <v>851</v>
+      </c>
+      <c r="B152" t="s">
         <v>852</v>
-      </c>
-      <c r="B152" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
+        <v>853</v>
+      </c>
+      <c r="B153" t="s">
         <v>854</v>
-      </c>
-      <c r="B153" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
+        <v>855</v>
+      </c>
+      <c r="B154" t="s">
         <v>856</v>
-      </c>
-      <c r="B154" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
+        <v>857</v>
+      </c>
+      <c r="B155" t="s">
         <v>858</v>
-      </c>
-      <c r="B155" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
+        <v>859</v>
+      </c>
+      <c r="B156" t="s">
         <v>860</v>
-      </c>
-      <c r="B156" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
+        <v>273</v>
+      </c>
+      <c r="B157" t="s">
         <v>274</v>
-      </c>
-      <c r="B157" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
+        <v>265</v>
+      </c>
+      <c r="B158" t="s">
         <v>266</v>
-      </c>
-      <c r="B158" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
+        <v>319</v>
+      </c>
+      <c r="B159" t="s">
         <v>320</v>
-      </c>
-      <c r="B159" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
+        <v>292</v>
+      </c>
+      <c r="B160" t="s">
         <v>293</v>
-      </c>
-      <c r="B160" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
+        <v>329</v>
+      </c>
+      <c r="B161" t="s">
         <v>330</v>
-      </c>
-      <c r="B161" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
+        <v>361</v>
+      </c>
+      <c r="B162" t="s">
         <v>362</v>
-      </c>
-      <c r="B162" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B163" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
+        <v>382</v>
+      </c>
+      <c r="B164" t="s">
         <v>383</v>
-      </c>
-      <c r="B164" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B165" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
+        <v>351</v>
+      </c>
+      <c r="B166" t="s">
         <v>352</v>
-      </c>
-      <c r="B166" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
+        <v>277</v>
+      </c>
+      <c r="B167" t="s">
         <v>278</v>
-      </c>
-      <c r="B167" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
+        <v>649</v>
+      </c>
+      <c r="B168" t="s">
         <v>650</v>
-      </c>
-      <c r="B168" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
+        <v>322</v>
+      </c>
+      <c r="B169" t="s">
         <v>323</v>
-      </c>
-      <c r="B169" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
+        <v>287</v>
+      </c>
+      <c r="B170" t="s">
         <v>288</v>
-      </c>
-      <c r="B170" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B171" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
+        <v>312</v>
+      </c>
+      <c r="B172" t="s">
         <v>313</v>
-      </c>
-      <c r="B172" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B173" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
+        <v>379</v>
+      </c>
+      <c r="B174" t="s">
         <v>380</v>
-      </c>
-      <c r="B174" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
+        <v>638</v>
+      </c>
+      <c r="B175" t="s">
         <v>639</v>
-      </c>
-      <c r="B175" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
+        <v>220</v>
+      </c>
+      <c r="B176" t="s">
         <v>221</v>
-      </c>
-      <c r="B176" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
+        <v>280</v>
+      </c>
+      <c r="B177" t="s">
         <v>281</v>
-      </c>
-      <c r="B177" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B178" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
+        <v>325</v>
+      </c>
+      <c r="B179" t="s">
         <v>326</v>
-      </c>
-      <c r="B179" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
+        <v>333</v>
+      </c>
+      <c r="B180" t="s">
         <v>334</v>
-      </c>
-      <c r="B180" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
+        <v>336</v>
+      </c>
+      <c r="B181" t="s">
         <v>337</v>
-      </c>
-      <c r="B181" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
+        <v>628</v>
+      </c>
+      <c r="B182" t="s">
         <v>629</v>
-      </c>
-      <c r="B182" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
+        <v>341</v>
+      </c>
+      <c r="B183" t="s">
         <v>342</v>
-      </c>
-      <c r="B183" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
+        <v>358</v>
+      </c>
+      <c r="B184" t="s">
         <v>359</v>
-      </c>
-      <c r="B184" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
+        <v>346</v>
+      </c>
+      <c r="B185" t="s">
         <v>347</v>
-      </c>
-      <c r="B185" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
+        <v>356</v>
+      </c>
+      <c r="B186" t="s">
         <v>357</v>
-      </c>
-      <c r="B186" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
+        <v>269</v>
+      </c>
+      <c r="B187" t="s">
         <v>270</v>
-      </c>
-      <c r="B187" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
+        <v>651</v>
+      </c>
+      <c r="B188" t="s">
         <v>652</v>
-      </c>
-      <c r="B188" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
+        <v>309</v>
+      </c>
+      <c r="B189" t="s">
         <v>310</v>
-      </c>
-      <c r="B189" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B190" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
+        <v>339</v>
+      </c>
+      <c r="B191" t="s">
         <v>340</v>
-      </c>
-      <c r="B191" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B192" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
+        <v>344</v>
+      </c>
+      <c r="B193" t="s">
         <v>345</v>
-      </c>
-      <c r="B193" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
+        <v>373</v>
+      </c>
+      <c r="B194" t="s">
         <v>374</v>
-      </c>
-      <c r="B194" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
+        <v>348</v>
+      </c>
+      <c r="B195" t="s">
         <v>349</v>
-      </c>
-      <c r="B195" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
+        <v>376</v>
+      </c>
+      <c r="B196" t="s">
         <v>377</v>
-      </c>
-      <c r="B196" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
+        <v>866</v>
+      </c>
+      <c r="B197" t="s">
         <v>867</v>
-      </c>
-      <c r="B197" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B198" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B199" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B200" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B201" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
+        <v>595</v>
+      </c>
+      <c r="B202" t="s">
         <v>596</v>
-      </c>
-      <c r="B202" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
+        <v>871</v>
+      </c>
+      <c r="B203" t="s">
         <v>872</v>
-      </c>
-      <c r="B203" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
+        <v>873</v>
+      </c>
+      <c r="B204" t="s">
         <v>874</v>
-      </c>
-      <c r="B204" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B205" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
+        <v>876</v>
+      </c>
+      <c r="B206" t="s">
         <v>877</v>
-      </c>
-      <c r="B206" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
+        <v>878</v>
+      </c>
+      <c r="B207" t="s">
         <v>879</v>
-      </c>
-      <c r="B207" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
+        <v>880</v>
+      </c>
+      <c r="B208" t="s">
         <v>881</v>
-      </c>
-      <c r="B208" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
+        <v>316</v>
+      </c>
+      <c r="B209" t="s">
         <v>317</v>
-      </c>
-      <c r="B209" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
+        <v>882</v>
+      </c>
+      <c r="B210" t="s">
         <v>883</v>
-      </c>
-      <c r="B210" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
+        <v>365</v>
+      </c>
+      <c r="B211" t="s">
         <v>366</v>
-      </c>
-      <c r="B211" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
+        <v>597</v>
+      </c>
+      <c r="B212" t="s">
         <v>598</v>
-      </c>
-      <c r="B212" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
+        <v>884</v>
+      </c>
+      <c r="B213" t="s">
         <v>885</v>
-      </c>
-      <c r="B213" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
+        <v>886</v>
+      </c>
+      <c r="B214" t="s">
         <v>887</v>
-      </c>
-      <c r="B214" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
+        <v>888</v>
+      </c>
+      <c r="B215" t="s">
         <v>889</v>
-      </c>
-      <c r="B215" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
+        <v>890</v>
+      </c>
+      <c r="B216" t="s">
         <v>891</v>
-      </c>
-      <c r="B216" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
+        <v>892</v>
+      </c>
+      <c r="B217" t="s">
         <v>893</v>
-      </c>
-      <c r="B217" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
+        <v>894</v>
+      </c>
+      <c r="B218" t="s">
         <v>895</v>
-      </c>
-      <c r="B218" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
+        <v>368</v>
+      </c>
+      <c r="B219" t="s">
         <v>369</v>
-      </c>
-      <c r="B219" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
+        <v>896</v>
+      </c>
+      <c r="B220" t="s">
         <v>897</v>
-      </c>
-      <c r="B220" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
+        <v>370</v>
+      </c>
+      <c r="B221" t="s">
         <v>371</v>
-      </c>
-      <c r="B221" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
+        <v>898</v>
+      </c>
+      <c r="B222" t="s">
         <v>899</v>
-      </c>
-      <c r="B222" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
+        <v>900</v>
+      </c>
+      <c r="B223" t="s">
         <v>901</v>
-      </c>
-      <c r="B223" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
+        <v>902</v>
+      </c>
+      <c r="B224" t="s">
         <v>903</v>
-      </c>
-      <c r="B224" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
+        <v>904</v>
+      </c>
+      <c r="B225" t="s">
         <v>905</v>
-      </c>
-      <c r="B225" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
+        <v>906</v>
+      </c>
+      <c r="B226" t="s">
         <v>907</v>
-      </c>
-      <c r="B226" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
+        <v>909</v>
+      </c>
+      <c r="B228" t="s">
         <v>910</v>
-      </c>
-      <c r="B228" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
+        <v>643</v>
+      </c>
+      <c r="B229" t="s">
         <v>644</v>
-      </c>
-      <c r="B229" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
+        <v>911</v>
+      </c>
+      <c r="B230" t="s">
         <v>912</v>
-      </c>
-      <c r="B230" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
+        <v>306</v>
+      </c>
+      <c r="B231" t="s">
         <v>307</v>
-      </c>
-      <c r="B231" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
+        <v>913</v>
+      </c>
+      <c r="B232" t="s">
         <v>914</v>
-      </c>
-      <c r="B232" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
+        <v>915</v>
+      </c>
+      <c r="B233" t="s">
         <v>916</v>
-      </c>
-      <c r="B233" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
+        <v>917</v>
+      </c>
+      <c r="B234" t="s">
         <v>918</v>
-      </c>
-      <c r="B234" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
+        <v>919</v>
+      </c>
+      <c r="B235" t="s">
         <v>920</v>
-      </c>
-      <c r="B235" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
+        <v>921</v>
+      </c>
+      <c r="B236" t="s">
         <v>922</v>
-      </c>
-      <c r="B236" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
+        <v>408</v>
+      </c>
+      <c r="B237" t="s">
         <v>409</v>
-      </c>
-      <c r="B237" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
+        <v>391</v>
+      </c>
+      <c r="B238" t="s">
         <v>392</v>
-      </c>
-      <c r="B238" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
+        <v>402</v>
+      </c>
+      <c r="B239" t="s">
         <v>403</v>
-      </c>
-      <c r="B239" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
+        <v>441</v>
+      </c>
+      <c r="B240" t="s">
         <v>442</v>
-      </c>
-      <c r="B240" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B241" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B242" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
+        <v>924</v>
+      </c>
+      <c r="B243" t="s">
         <v>925</v>
-      </c>
-      <c r="B243" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B244" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
+        <v>926</v>
+      </c>
+      <c r="B245" t="s">
         <v>927</v>
-      </c>
-      <c r="B245" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B246" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
+        <v>385</v>
+      </c>
+      <c r="B247" t="s">
         <v>386</v>
-      </c>
-      <c r="B247" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
+        <v>388</v>
+      </c>
+      <c r="B248" t="s">
         <v>389</v>
-      </c>
-      <c r="B248" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
+        <v>404</v>
+      </c>
+      <c r="B249" t="s">
         <v>405</v>
-      </c>
-      <c r="B249" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
+        <v>397</v>
+      </c>
+      <c r="B250" t="s">
         <v>398</v>
-      </c>
-      <c r="B250" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B251" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B252" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B253" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
+        <v>560</v>
+      </c>
+      <c r="B254" t="s">
         <v>561</v>
-      </c>
-      <c r="B254" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
+        <v>930</v>
+      </c>
+      <c r="B255" t="s">
         <v>931</v>
-      </c>
-      <c r="B255" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B256" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
+        <v>933</v>
+      </c>
+      <c r="B257" t="s">
         <v>934</v>
-      </c>
-      <c r="B257" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
+        <v>935</v>
+      </c>
+      <c r="B258" t="s">
         <v>936</v>
-      </c>
-      <c r="B258" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
+        <v>394</v>
+      </c>
+      <c r="B259" t="s">
         <v>395</v>
-      </c>
-      <c r="B259" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
+        <v>483</v>
+      </c>
+      <c r="B260" t="s">
         <v>484</v>
-      </c>
-      <c r="B260" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
+        <v>406</v>
+      </c>
+      <c r="B261" t="s">
         <v>407</v>
-      </c>
-      <c r="B261" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
+        <v>399</v>
+      </c>
+      <c r="B262" t="s">
         <v>400</v>
-      </c>
-      <c r="B262" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B263" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B264" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B265" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B266" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
+        <v>939</v>
+      </c>
+      <c r="B267" t="s">
         <v>940</v>
-      </c>
-      <c r="B267" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B268" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
+        <v>942</v>
+      </c>
+      <c r="B269" t="s">
         <v>943</v>
-      </c>
-      <c r="B269" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
+        <v>944</v>
+      </c>
+      <c r="B270" t="s">
         <v>945</v>
-      </c>
-      <c r="B270" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
+        <v>414</v>
+      </c>
+      <c r="B271" t="s">
         <v>415</v>
-      </c>
-      <c r="B271" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
+        <v>946</v>
+      </c>
+      <c r="B272" t="s">
         <v>947</v>
-      </c>
-      <c r="B272" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
+        <v>475</v>
+      </c>
+      <c r="B273" t="s">
         <v>476</v>
-      </c>
-      <c r="B273" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
+        <v>515</v>
+      </c>
+      <c r="B274" t="s">
         <v>516</v>
-      </c>
-      <c r="B274" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
+        <v>437</v>
+      </c>
+      <c r="B275" t="s">
         <v>438</v>
-      </c>
-      <c r="B275" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
+        <v>422</v>
+      </c>
+      <c r="B276" t="s">
         <v>423</v>
-      </c>
-      <c r="B276" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
+        <v>487</v>
+      </c>
+      <c r="B277" t="s">
         <v>488</v>
-      </c>
-      <c r="B277" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
+        <v>581</v>
+      </c>
+      <c r="B278" t="s">
         <v>582</v>
-      </c>
-      <c r="B278" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
+        <v>512</v>
+      </c>
+      <c r="B279" t="s">
         <v>513</v>
-      </c>
-      <c r="B279" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
+        <v>579</v>
+      </c>
+      <c r="B280" t="s">
         <v>580</v>
-      </c>
-      <c r="B280" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
+        <v>948</v>
+      </c>
+      <c r="B281" t="s">
         <v>949</v>
-      </c>
-      <c r="B281" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
+        <v>577</v>
+      </c>
+      <c r="B282" t="s">
         <v>578</v>
-      </c>
-      <c r="B282" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
+        <v>411</v>
+      </c>
+      <c r="B283" t="s">
         <v>412</v>
-      </c>
-      <c r="B283" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
+        <v>950</v>
+      </c>
+      <c r="B284" t="s">
         <v>951</v>
-      </c>
-      <c r="B284" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
+        <v>518</v>
+      </c>
+      <c r="B285" t="s">
         <v>519</v>
-      </c>
-      <c r="B285" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
+        <v>952</v>
+      </c>
+      <c r="B286" t="s">
         <v>953</v>
-      </c>
-      <c r="B286" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
+        <v>521</v>
+      </c>
+      <c r="B287" t="s">
         <v>522</v>
-      </c>
-      <c r="B287" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
+        <v>954</v>
+      </c>
+      <c r="B288" t="s">
         <v>955</v>
-      </c>
-      <c r="B288" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
+        <v>547</v>
+      </c>
+      <c r="B289" t="s">
         <v>548</v>
-      </c>
-      <c r="B289" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
+        <v>418</v>
+      </c>
+      <c r="B290" t="s">
         <v>419</v>
-      </c>
-      <c r="B290" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
+        <v>509</v>
+      </c>
+      <c r="B291" t="s">
         <v>510</v>
-      </c>
-      <c r="B291" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
+        <v>420</v>
+      </c>
+      <c r="B292" t="s">
         <v>421</v>
-      </c>
-      <c r="B292" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
+        <v>956</v>
+      </c>
+      <c r="B293" t="s">
         <v>957</v>
-      </c>
-      <c r="B293" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
+        <v>653</v>
+      </c>
+      <c r="B294" t="s">
         <v>654</v>
-      </c>
-      <c r="B294" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
+        <v>555</v>
+      </c>
+      <c r="B295" t="s">
         <v>556</v>
-      </c>
-      <c r="B295" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
+        <v>494</v>
+      </c>
+      <c r="B296" t="s">
         <v>495</v>
-      </c>
-      <c r="B296" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
+        <v>526</v>
+      </c>
+      <c r="B297" t="s">
         <v>527</v>
-      </c>
-      <c r="B297" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
+        <v>498</v>
+      </c>
+      <c r="B298" t="s">
         <v>499</v>
-      </c>
-      <c r="B298" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
+        <v>523</v>
+      </c>
+      <c r="B299" t="s">
         <v>524</v>
-      </c>
-      <c r="B299" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
+        <v>958</v>
+      </c>
+      <c r="B300" t="s">
         <v>959</v>
-      </c>
-      <c r="B300" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
+        <v>535</v>
+      </c>
+      <c r="B301" t="s">
         <v>536</v>
-      </c>
-      <c r="B301" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
+        <v>960</v>
+      </c>
+      <c r="B302" t="s">
         <v>961</v>
-      </c>
-      <c r="B302" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
+        <v>543</v>
+      </c>
+      <c r="B303" t="s">
         <v>544</v>
-      </c>
-      <c r="B303" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
+        <v>962</v>
+      </c>
+      <c r="B304" t="s">
         <v>963</v>
-      </c>
-      <c r="B304" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
+        <v>964</v>
+      </c>
+      <c r="B305" t="s">
         <v>965</v>
-      </c>
-      <c r="B305" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
+        <v>456</v>
+      </c>
+      <c r="B306" t="s">
         <v>457</v>
-      </c>
-      <c r="B306" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
+        <v>557</v>
+      </c>
+      <c r="B307" t="s">
         <v>558</v>
-      </c>
-      <c r="B307" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
+        <v>448</v>
+      </c>
+      <c r="B308" t="s">
         <v>449</v>
-      </c>
-      <c r="B308" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
+        <v>528</v>
+      </c>
+      <c r="B309" t="s">
         <v>529</v>
-      </c>
-      <c r="B309" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
+        <v>444</v>
+      </c>
+      <c r="B310" t="s">
         <v>445</v>
-      </c>
-      <c r="B310" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
+        <v>530</v>
+      </c>
+      <c r="B311" t="s">
         <v>531</v>
-      </c>
-      <c r="B311" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
+        <v>496</v>
+      </c>
+      <c r="B312" t="s">
         <v>497</v>
-      </c>
-      <c r="B312" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
+        <v>537</v>
+      </c>
+      <c r="B313" t="s">
         <v>538</v>
-      </c>
-      <c r="B313" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
+        <v>471</v>
+      </c>
+      <c r="B314" t="s">
         <v>472</v>
-      </c>
-      <c r="B314" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
+        <v>540</v>
+      </c>
+      <c r="B315" t="s">
         <v>541</v>
-      </c>
-      <c r="B315" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
+        <v>966</v>
+      </c>
+      <c r="B316" t="s">
         <v>967</v>
-      </c>
-      <c r="B316" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
+        <v>968</v>
+      </c>
+      <c r="B317" t="s">
         <v>969</v>
-      </c>
-      <c r="B317" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
+        <v>970</v>
+      </c>
+      <c r="B318" t="s">
         <v>971</v>
-      </c>
-      <c r="B318" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
+        <v>551</v>
+      </c>
+      <c r="B319" t="s">
         <v>552</v>
-      </c>
-      <c r="B319" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
+        <v>532</v>
+      </c>
+      <c r="B320" t="s">
         <v>533</v>
-      </c>
-      <c r="B320" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B321" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
+        <v>452</v>
+      </c>
+      <c r="B322" t="s">
         <v>453</v>
-      </c>
-      <c r="B322" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
+        <v>425</v>
+      </c>
+      <c r="B323" t="s">
         <v>426</v>
-      </c>
-      <c r="B323" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B324" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
+        <v>479</v>
+      </c>
+      <c r="B325" t="s">
         <v>480</v>
-      </c>
-      <c r="B325" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
+        <v>583</v>
+      </c>
+      <c r="B326" t="s">
         <v>584</v>
-      </c>
-      <c r="B326" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B327" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
+        <v>491</v>
+      </c>
+      <c r="B328" t="s">
         <v>492</v>
-      </c>
-      <c r="B328" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B329" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B330" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B331" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
+        <v>587</v>
+      </c>
+      <c r="B332" t="s">
         <v>588</v>
-      </c>
-      <c r="B332" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
+        <v>428</v>
+      </c>
+      <c r="B333" t="s">
         <v>429</v>
-      </c>
-      <c r="B333" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
+        <v>501</v>
+      </c>
+      <c r="B334" t="s">
         <v>502</v>
-      </c>
-      <c r="B334" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
+        <v>467</v>
+      </c>
+      <c r="B335" t="s">
         <v>468</v>
-      </c>
-      <c r="B335" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
+        <v>460</v>
+      </c>
+      <c r="B336" t="s">
         <v>461</v>
-      </c>
-      <c r="B336" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B337" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
+        <v>585</v>
+      </c>
+      <c r="B338" t="s">
         <v>586</v>
-      </c>
-      <c r="B338" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
+        <v>434</v>
+      </c>
+      <c r="B339" t="s">
         <v>435</v>
-      </c>
-      <c r="B339" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
+        <v>589</v>
+      </c>
+      <c r="B340" t="s">
         <v>590</v>
-      </c>
-      <c r="B340" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
+        <v>430</v>
+      </c>
+      <c r="B341" t="s">
         <v>431</v>
-      </c>
-      <c r="B341" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
+        <v>504</v>
+      </c>
+      <c r="B342" t="s">
         <v>505</v>
-      </c>
-      <c r="B342" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B343" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
+        <v>463</v>
+      </c>
+      <c r="B344" t="s">
         <v>464</v>
-      </c>
-      <c r="B344" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
+        <v>432</v>
+      </c>
+      <c r="B345" t="s">
         <v>433</v>
-      </c>
-      <c r="B345" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
+        <v>593</v>
+      </c>
+      <c r="B346" t="s">
         <v>594</v>
-      </c>
-      <c r="B346" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
+        <v>506</v>
+      </c>
+      <c r="B347" t="s">
         <v>507</v>
-      </c>
-      <c r="B347" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
+        <v>591</v>
+      </c>
+      <c r="B348" t="s">
         <v>592</v>
-      </c>
-      <c r="B348" t="s">
-        <v>593</v>
       </c>
     </row>
   </sheetData>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080947AE-18DC-874F-B697-1A9DADF66F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0826D3-E829-A545-A63E-EDF65A576E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2140" yWindow="1840" windowWidth="29820" windowHeight="19560" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="33380" windowHeight="21580" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
   <sheets>
     <sheet name="xlsx" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1842" uniqueCount="1055">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1840" uniqueCount="1055">
   <si>
     <t>Household Name</t>
   </si>
@@ -3640,6 +3640,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="58.33203125" customWidth="1"/>
     <col min="6" max="6" width="84.6640625" customWidth="1"/>
     <col min="7" max="7" width="77.1640625" customWidth="1"/>
@@ -8395,12 +8397,8 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229" s="2"/>
-      <c r="B229" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>729</v>
-      </c>
+      <c r="B229" s="2"/>
+      <c r="C229" s="2"/>
       <c r="D229" s="2"/>
       <c r="E229" s="7"/>
       <c r="F229" s="7"/>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0826D3-E829-A545-A63E-EDF65A576E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA01B39-F3AC-3A4C-9AD4-C0DAB839547D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33380" windowHeight="21580" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1840" uniqueCount="1055">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="1055">
   <si>
     <t>Household Name</t>
   </si>
@@ -507,6 +507,9 @@
     <t>Sponsor Hold</t>
   </si>
   <si>
+    <t>Clayco Construction $125000 Sponsorship 6/1/2026 | Opportunity | Salesforce</t>
+  </si>
+  <si>
     <t>Trott</t>
   </si>
   <si>
@@ -1572,9 +1575,6 @@
     <t>x=80.87, y=74.64</t>
   </si>
   <si>
-    <t>Cheryl Anderson</t>
-  </si>
-  <si>
     <t>E43</t>
   </si>
   <si>
@@ -2976,12 +2976,21 @@
     <t>Elisa Jaime + Lynda Kerr</t>
   </si>
   <si>
+    <t>Kerr Concert 2026 Tickets | Opportunity | Salesforce</t>
+  </si>
+  <si>
     <t>Amy + Jim Wood</t>
   </si>
   <si>
     <t>Gary Levine + Larry Bloch + Mitch Adler</t>
   </si>
   <si>
+    <t>Adler Concert 2026 Tickets | Opportunity | Salesforce</t>
+  </si>
+  <si>
+    <t>Tafel Klaus Concert 2026 Tickets | Opportunity | Salesforce</t>
+  </si>
+  <si>
     <t>Theodora Polamalu</t>
   </si>
   <si>
@@ -3150,9 +3159,15 @@
     <t>Amy Myers</t>
   </si>
   <si>
+    <t>Socol Concert 2026 Tickets | Opportunity | Salesforce</t>
+  </si>
+  <si>
     <t>Vickey Syage</t>
   </si>
   <si>
+    <t>Whittington Concert 2026 Tickets | Opportunity | Salesforce</t>
+  </si>
+  <si>
     <t>(now requesting E54 or near that area)</t>
   </si>
   <si>
@@ -3174,34 +3189,19 @@
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uJkzpYAC/view</t>
   </si>
   <si>
-    <t>Mary Ellen Aviano</t>
-  </si>
-  <si>
     <t>Stephanie Smith</t>
   </si>
   <si>
     <t>Donating to cancer fighters</t>
   </si>
   <si>
-    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u72eLYAQ/view</t>
-  </si>
-  <si>
-    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000rvp8wYAA/view</t>
-  </si>
-  <si>
-    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000Q2enCYAR/view</t>
-  </si>
-  <si>
-    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u9QkgYAE/view</t>
-  </si>
-  <si>
-    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uXDB9YAO/view</t>
-  </si>
-  <si>
-    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uutEVYAY/view</t>
-  </si>
-  <si>
-    <t>https://curebound.lightning.force.com/lightning/r/Account/0014W00002W8eYDQAZ/view</t>
+    <t>Justin and Stephanie Smith and Friends Household | Account | Salesforce</t>
+  </si>
+  <si>
+    <t>Cheryl Anderson &amp; Randy Brooks</t>
+  </si>
+  <si>
+    <t>Brooks Concert 2026 Tickets | Opportunity | Salesforce</t>
   </si>
 </sst>
 </file>
@@ -3259,24 +3259,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3292,15 +3280,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3636,15 +3623,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7894B4-148E-174D-AE8B-E6DE441B89B0}">
-  <dimension ref="A1:I235"/>
+  <dimension ref="A1:I237"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="58.33203125" customWidth="1"/>
-    <col min="6" max="6" width="84.6640625" customWidth="1"/>
-    <col min="7" max="7" width="77.1640625" customWidth="1"/>
+    <col min="1" max="9" width="60.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -3752,8 +3734,8 @@
       <c r="D5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -3766,7 +3748,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>12</v>
@@ -3818,14 +3800,14 @@
         <v>34</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>1048</v>
+        <v>979</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>35</v>
@@ -3951,7 +3933,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>58</v>
@@ -3970,7 +3952,7 @@
         <v>61</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>1049</v>
+        <v>982</v>
       </c>
       <c r="I15" s="2"/>
     </row>
@@ -4490,7 +4472,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="1" t="s">
-        <v>1050</v>
+        <v>156</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -4498,32 +4480,32 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>155</v>
@@ -4541,18 +4523,18 @@
         <v>21</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E42" s="7" t="s">
-        <v>1034</v>
-      </c>
-      <c r="F42" s="7"/>
+      <c r="E42" s="5" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F42" s="5"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
@@ -4562,17 +4544,17 @@
         <v>50</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="1" t="s">
-        <v>1051</v>
+        <v>983</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -4580,20 +4562,20 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -4601,20 +4583,20 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -4622,20 +4604,20 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -4643,20 +4625,20 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -4664,20 +4646,20 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
@@ -4685,20 +4667,20 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -4706,20 +4688,20 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -4727,20 +4709,20 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
@@ -4748,20 +4730,20 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
@@ -4769,22 +4751,22 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -4792,20 +4774,20 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
@@ -4813,20 +4795,20 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
@@ -4834,20 +4816,20 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
@@ -4855,7 +4837,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>675</v>
@@ -4868,7 +4850,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
@@ -4876,20 +4858,20 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
@@ -4897,20 +4879,20 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
@@ -4918,20 +4900,20 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
@@ -4939,13 +4921,13 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>155</v>
@@ -4960,58 +4942,58 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
@@ -5019,32 +5001,32 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>155</v>
@@ -5059,13 +5041,13 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>155</v>
@@ -5080,20 +5062,20 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
@@ -5101,20 +5083,20 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
@@ -5122,20 +5104,20 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
@@ -5143,20 +5125,20 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
@@ -5164,20 +5146,20 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
@@ -5185,20 +5167,20 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E73" s="2"/>
-      <c r="F73" s="5" t="s">
-        <v>279</v>
+      <c r="F73" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
@@ -5206,20 +5188,20 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E74" s="2"/>
-      <c r="F74" s="5" t="s">
-        <v>985</v>
+      <c r="F74" s="1" t="s">
+        <v>988</v>
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
@@ -5227,20 +5209,20 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
@@ -5248,22 +5230,22 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -5271,20 +5253,20 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
@@ -5292,20 +5274,20 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
@@ -5313,13 +5295,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>155</v>
@@ -5334,13 +5316,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>155</v>
@@ -5355,20 +5337,20 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E81" s="2"/>
-      <c r="F81" s="5" t="s">
-        <v>998</v>
+      <c r="F81" s="1" t="s">
+        <v>1001</v>
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
@@ -5376,39 +5358,39 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
+        <v>168</v>
+      </c>
+      <c r="E82" s="5"/>
+      <c r="F82" s="5"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="1" t="s">
-        <v>314</v>
+        <v>1040</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -5416,20 +5398,20 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
@@ -5437,20 +5419,20 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E85" s="2"/>
-      <c r="F85" s="5" t="s">
-        <v>321</v>
+      <c r="F85" s="1" t="s">
+        <v>322</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
@@ -5458,20 +5440,20 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E86" s="2"/>
-      <c r="F86" s="5" t="s">
-        <v>986</v>
+      <c r="F86" s="1" t="s">
+        <v>989</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -5479,43 +5461,43 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E87" s="2"/>
-      <c r="F87" s="5" t="s">
-        <v>987</v>
+      <c r="F87" s="1" t="s">
+        <v>990</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -5523,20 +5505,20 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -5544,20 +5526,20 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E90" s="2"/>
-      <c r="F90" s="5" t="s">
-        <v>338</v>
+      <c r="F90" s="1" t="s">
+        <v>339</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -5565,20 +5547,20 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E91" s="2"/>
-      <c r="F91" s="5" t="s">
-        <v>988</v>
+      <c r="F91" s="1" t="s">
+        <v>991</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -5586,20 +5568,20 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>342</v>
-      </c>
       <c r="D92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E92" s="2"/>
-      <c r="F92" s="5" t="s">
-        <v>989</v>
+      <c r="F92" s="1" t="s">
+        <v>992</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -5607,20 +5589,20 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E93" s="2"/>
-      <c r="F93" s="5" t="s">
-        <v>991</v>
+      <c r="F93" s="1" t="s">
+        <v>994</v>
       </c>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -5628,20 +5610,20 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -5649,20 +5631,20 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E95" s="2"/>
-      <c r="F95" s="5" t="s">
-        <v>994</v>
+      <c r="F95" s="1" t="s">
+        <v>997</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -5670,20 +5652,20 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E96" s="2"/>
-      <c r="F96" s="5" t="s">
-        <v>995</v>
+      <c r="F96" s="1" t="s">
+        <v>998</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -5691,20 +5673,20 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E97" s="2"/>
-      <c r="F97" s="5" t="s">
-        <v>355</v>
+      <c r="F97" s="1" t="s">
+        <v>356</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
@@ -5712,20 +5694,20 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E98" s="2"/>
-      <c r="F98" s="5" t="s">
-        <v>996</v>
+      <c r="F98" s="1" t="s">
+        <v>999</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
@@ -5733,20 +5715,20 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E99" s="2"/>
-      <c r="F99" s="5" t="s">
-        <v>997</v>
+      <c r="F99" s="1" t="s">
+        <v>1000</v>
       </c>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
@@ -5754,20 +5736,20 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
@@ -5775,20 +5757,20 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
@@ -5796,20 +5778,20 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E102" s="2"/>
-      <c r="F102" s="5" t="s">
-        <v>999</v>
+      <c r="F102" s="1" t="s">
+        <v>1002</v>
       </c>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
@@ -5817,20 +5799,20 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E103" s="2"/>
-      <c r="F103" s="5" t="s">
-        <v>367</v>
+      <c r="F103" s="1" t="s">
+        <v>368</v>
       </c>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -5838,20 +5820,20 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E104" s="2"/>
-      <c r="F104" s="5" t="s">
-        <v>375</v>
+      <c r="F104" s="1" t="s">
+        <v>376</v>
       </c>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -5859,20 +5841,20 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E105" s="2"/>
-      <c r="F105" s="5" t="s">
-        <v>1000</v>
+      <c r="F105" s="1" t="s">
+        <v>1003</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -5880,20 +5862,20 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E106" s="2"/>
-      <c r="F106" s="5" t="s">
-        <v>381</v>
+      <c r="F106" s="1" t="s">
+        <v>382</v>
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -5901,20 +5883,20 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E107" s="2"/>
-      <c r="F107" s="5" t="s">
-        <v>1001</v>
+      <c r="F107" s="1" t="s">
+        <v>1004</v>
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
@@ -5922,13 +5904,13 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>155</v>
@@ -5943,20 +5925,20 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
@@ -5964,13 +5946,13 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>155</v>
@@ -5985,13 +5967,13 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>155</v>
@@ -6006,13 +5988,13 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>155</v>
@@ -6027,77 +6009,77 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E113" s="7"/>
-      <c r="F113" s="7"/>
+      <c r="E113" s="5"/>
+      <c r="F113" s="5"/>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E114" s="7"/>
-      <c r="F114" s="7"/>
+      <c r="E114" s="5"/>
+      <c r="F114" s="5"/>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E115" s="7"/>
-      <c r="F115" s="7"/>
+      <c r="E115" s="5"/>
+      <c r="F115" s="5"/>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" s="1" t="s">
-        <v>1052</v>
+        <v>1042</v>
       </c>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
@@ -6105,20 +6087,20 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
@@ -6126,20 +6108,20 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
@@ -6147,13 +6129,13 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>12</v>
@@ -6168,13 +6150,13 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>12</v>
@@ -6189,13 +6171,13 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>12</v>
@@ -6210,20 +6192,20 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E122" s="2"/>
-      <c r="F122" s="5" t="s">
-        <v>427</v>
+      <c r="F122" s="1" t="s">
+        <v>428</v>
       </c>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
@@ -6231,20 +6213,20 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E123" s="2"/>
-      <c r="F123" s="5" t="s">
-        <v>1002</v>
+      <c r="F123" s="1" t="s">
+        <v>1005</v>
       </c>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
@@ -6252,20 +6234,20 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E124" s="2"/>
-      <c r="F124" s="5" t="s">
-        <v>1003</v>
+      <c r="F124" s="1" t="s">
+        <v>1006</v>
       </c>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
@@ -6273,20 +6255,20 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E125" s="2"/>
-      <c r="F125" s="5" t="s">
-        <v>1004</v>
+      <c r="F125" s="1" t="s">
+        <v>1007</v>
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
@@ -6294,20 +6276,20 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E126" s="2"/>
-      <c r="F126" s="5" t="s">
-        <v>1005</v>
+      <c r="F126" s="1" t="s">
+        <v>1008</v>
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
@@ -6315,20 +6297,20 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
@@ -6336,20 +6318,20 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
@@ -6357,20 +6339,20 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
@@ -6378,20 +6360,20 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
@@ -6399,22 +6381,22 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
@@ -6422,19 +6404,19 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>666</v>
@@ -6445,13 +6427,13 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>12</v>
@@ -6466,22 +6448,22 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
@@ -6489,20 +6471,20 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
@@ -6510,20 +6492,20 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
@@ -6531,22 +6513,22 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
@@ -6554,20 +6536,20 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
@@ -6575,20 +6557,20 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
@@ -6596,19 +6578,19 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>667</v>
@@ -6619,20 +6601,20 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
@@ -6643,10 +6625,10 @@
         <v>17</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>12</v>
@@ -6664,10 +6646,10 @@
         <v>17</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>12</v>
@@ -6685,10 +6667,10 @@
         <v>17</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>12</v>
@@ -6703,22 +6685,22 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>503</v>
+        <v>1045</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>504</v>
       </c>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
@@ -6726,22 +6708,22 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>1006</v>
+        <v>1045</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>1009</v>
       </c>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
@@ -6749,22 +6731,22 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>1007</v>
+        <v>1045</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>1010</v>
       </c>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
@@ -6772,13 +6754,13 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>155</v>
@@ -6793,7 +6775,7 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
-        <v>511</v>
+        <v>1053</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>512</v>
@@ -6808,13 +6790,15 @@
       <c r="F149" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="G149" s="2"/>
+      <c r="G149" s="1" t="s">
+        <v>1054</v>
+      </c>
       <c r="H149" s="2"/>
       <c r="I149" s="2"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>515</v>
@@ -6826,8 +6810,8 @@
         <v>12</v>
       </c>
       <c r="E150" s="2"/>
-      <c r="F150" s="5" t="s">
-        <v>353</v>
+      <c r="F150" s="1" t="s">
+        <v>354</v>
       </c>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
@@ -6847,7 +6831,7 @@
         <v>12</v>
       </c>
       <c r="E151" s="2"/>
-      <c r="F151" s="5" t="s">
+      <c r="F151" s="1" t="s">
         <v>520</v>
       </c>
       <c r="G151" s="2"/>
@@ -6868,8 +6852,8 @@
         <v>12</v>
       </c>
       <c r="E152" s="2"/>
-      <c r="F152" s="5" t="s">
-        <v>1008</v>
+      <c r="F152" s="1" t="s">
+        <v>1011</v>
       </c>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
@@ -6889,8 +6873,8 @@
         <v>12</v>
       </c>
       <c r="E153" s="2"/>
-      <c r="F153" s="5" t="s">
-        <v>1009</v>
+      <c r="F153" s="1" t="s">
+        <v>1012</v>
       </c>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
@@ -6910,8 +6894,8 @@
         <v>12</v>
       </c>
       <c r="E154" s="2"/>
-      <c r="F154" s="5" t="s">
-        <v>1010</v>
+      <c r="F154" s="1" t="s">
+        <v>1013</v>
       </c>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
@@ -6931,8 +6915,8 @@
         <v>12</v>
       </c>
       <c r="E155" s="2"/>
-      <c r="F155" s="5" t="s">
-        <v>1011</v>
+      <c r="F155" s="1" t="s">
+        <v>1014</v>
       </c>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
@@ -6952,8 +6936,8 @@
         <v>12</v>
       </c>
       <c r="E156" s="2"/>
-      <c r="F156" s="5" t="s">
-        <v>1012</v>
+      <c r="F156" s="1" t="s">
+        <v>1015</v>
       </c>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
@@ -6961,7 +6945,7 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>532</v>
@@ -6973,8 +6957,8 @@
         <v>12</v>
       </c>
       <c r="E157" s="2"/>
-      <c r="F157" s="5" t="s">
-        <v>1013</v>
+      <c r="F157" s="1" t="s">
+        <v>1016</v>
       </c>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
@@ -6994,7 +6978,7 @@
         <v>12</v>
       </c>
       <c r="E158" s="2"/>
-      <c r="F158" s="5" t="s">
+      <c r="F158" s="1" t="s">
         <v>539</v>
       </c>
       <c r="G158" s="2"/>
@@ -7015,8 +6999,8 @@
         <v>12</v>
       </c>
       <c r="E159" s="2"/>
-      <c r="F159" s="5" t="s">
-        <v>1014</v>
+      <c r="F159" s="1" t="s">
+        <v>1017</v>
       </c>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
@@ -7036,8 +7020,8 @@
         <v>12</v>
       </c>
       <c r="E160" s="2"/>
-      <c r="F160" s="5" t="s">
-        <v>1015</v>
+      <c r="F160" s="1" t="s">
+        <v>1018</v>
       </c>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
@@ -7110,7 +7094,7 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>555</v>
@@ -7122,10 +7106,10 @@
         <v>12</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>1017</v>
-      </c>
-      <c r="F164" s="5" t="s">
-        <v>1018</v>
+        <v>1020</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>1021</v>
       </c>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
@@ -7133,7 +7117,7 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>557</v>
@@ -7145,10 +7129,10 @@
         <v>12</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>1020</v>
-      </c>
-      <c r="F165" s="5" t="s">
-        <v>1021</v>
+        <v>1023</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>1024</v>
       </c>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
@@ -7159,10 +7143,10 @@
         <v>559</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>12</v>
@@ -7177,7 +7161,7 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>560</v>
@@ -7186,20 +7170,20 @@
         <v>561</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E167" s="2"/>
-      <c r="F167" s="5" t="s">
-        <v>1023</v>
+      <c r="F167" s="1" t="s">
+        <v>1026</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.2">
@@ -7259,8 +7243,8 @@
       <c r="D170" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E170" s="7"/>
-      <c r="F170" s="7"/>
+      <c r="E170" s="5"/>
+      <c r="F170" s="5"/>
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
       <c r="I170" s="2"/>
@@ -7278,8 +7262,8 @@
       <c r="D171" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E171" s="7"/>
-      <c r="F171" s="7"/>
+      <c r="E171" s="5"/>
+      <c r="F171" s="5"/>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
       <c r="I171" s="2"/>
@@ -7297,8 +7281,8 @@
       <c r="D172" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E172" s="7"/>
-      <c r="F172" s="7"/>
+      <c r="E172" s="5"/>
+      <c r="F172" s="5"/>
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
       <c r="I172" s="2"/>
@@ -7316,8 +7300,8 @@
       <c r="D173" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E173" s="7"/>
-      <c r="F173" s="7"/>
+      <c r="E173" s="5"/>
+      <c r="F173" s="5"/>
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
       <c r="I173" s="2"/>
@@ -7335,8 +7319,8 @@
       <c r="D174" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E174" s="7"/>
-      <c r="F174" s="7"/>
+      <c r="E174" s="5"/>
+      <c r="F174" s="5"/>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
       <c r="I174" s="2"/>
@@ -7354,8 +7338,8 @@
       <c r="D175" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E175" s="7"/>
-      <c r="F175" s="7"/>
+      <c r="E175" s="5"/>
+      <c r="F175" s="5"/>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
       <c r="I175" s="2"/>
@@ -7373,8 +7357,8 @@
       <c r="D176" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E176" s="7"/>
-      <c r="F176" s="7"/>
+      <c r="E176" s="5"/>
+      <c r="F176" s="5"/>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
       <c r="I176" s="2"/>
@@ -7392,8 +7376,8 @@
       <c r="D177" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E177" s="7"/>
-      <c r="F177" s="7"/>
+      <c r="E177" s="5"/>
+      <c r="F177" s="5"/>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
       <c r="I177" s="2"/>
@@ -7411,8 +7395,8 @@
       <c r="D178" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E178" s="7"/>
-      <c r="F178" s="7"/>
+      <c r="E178" s="5"/>
+      <c r="F178" s="5"/>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
       <c r="I178" s="2"/>
@@ -7430,8 +7414,8 @@
       <c r="D179" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E179" s="7"/>
-      <c r="F179" s="7"/>
+      <c r="E179" s="5"/>
+      <c r="F179" s="5"/>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
       <c r="I179" s="2"/>
@@ -7449,8 +7433,8 @@
       <c r="D180" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E180" s="7"/>
-      <c r="F180" s="7"/>
+      <c r="E180" s="5"/>
+      <c r="F180" s="5"/>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
       <c r="I180" s="2"/>
@@ -7468,8 +7452,8 @@
       <c r="D181" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E181" s="7"/>
-      <c r="F181" s="7"/>
+      <c r="E181" s="5"/>
+      <c r="F181" s="5"/>
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
       <c r="I181" s="2"/>
@@ -7487,8 +7471,8 @@
       <c r="D182" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E182" s="7"/>
-      <c r="F182" s="7"/>
+      <c r="E182" s="5"/>
+      <c r="F182" s="5"/>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
       <c r="I182" s="2"/>
@@ -7506,8 +7490,8 @@
       <c r="D183" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E183" s="7"/>
-      <c r="F183" s="7"/>
+      <c r="E183" s="5"/>
+      <c r="F183" s="5"/>
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
       <c r="I183" s="2"/>
@@ -7525,8 +7509,8 @@
       <c r="D184" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E184" s="7"/>
-      <c r="F184" s="7"/>
+      <c r="E184" s="5"/>
+      <c r="F184" s="5"/>
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
       <c r="I184" s="2"/>
@@ -7544,8 +7528,8 @@
       <c r="D185" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E185" s="7"/>
-      <c r="F185" s="7"/>
+      <c r="E185" s="5"/>
+      <c r="F185" s="5"/>
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
       <c r="I185" s="2"/>
@@ -7563,8 +7547,8 @@
       <c r="D186" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E186" s="7"/>
-      <c r="F186" s="7"/>
+      <c r="E186" s="5"/>
+      <c r="F186" s="5"/>
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
       <c r="I186" s="2"/>
@@ -7582,8 +7566,8 @@
       <c r="D187" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E187" s="7"/>
-      <c r="F187" s="7"/>
+      <c r="E187" s="5"/>
+      <c r="F187" s="5"/>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
       <c r="I187" s="2"/>
@@ -7601,8 +7585,8 @@
       <c r="D188" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E188" s="7"/>
-      <c r="F188" s="7"/>
+      <c r="E188" s="5"/>
+      <c r="F188" s="5"/>
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
       <c r="I188" s="2"/>
@@ -7620,8 +7604,8 @@
       <c r="D189" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E189" s="7"/>
-      <c r="F189" s="7"/>
+      <c r="E189" s="5"/>
+      <c r="F189" s="5"/>
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
       <c r="I189" s="2"/>
@@ -7639,8 +7623,8 @@
       <c r="D190" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E190" s="7"/>
-      <c r="F190" s="7"/>
+      <c r="E190" s="5"/>
+      <c r="F190" s="5"/>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
       <c r="I190" s="2"/>
@@ -7658,8 +7642,8 @@
       <c r="D191" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E191" s="7"/>
-      <c r="F191" s="7"/>
+      <c r="E191" s="5"/>
+      <c r="F191" s="5"/>
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
       <c r="I191" s="2"/>
@@ -7677,8 +7661,8 @@
       <c r="D192" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E192" s="7"/>
-      <c r="F192" s="7"/>
+      <c r="E192" s="5"/>
+      <c r="F192" s="5"/>
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
       <c r="I192" s="2"/>
@@ -7696,8 +7680,8 @@
       <c r="D193" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E193" s="7"/>
-      <c r="F193" s="7"/>
+      <c r="E193" s="5"/>
+      <c r="F193" s="5"/>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
       <c r="I193" s="2"/>
@@ -7715,8 +7699,8 @@
       <c r="D194" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E194" s="7"/>
-      <c r="F194" s="7"/>
+      <c r="E194" s="5"/>
+      <c r="F194" s="5"/>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
       <c r="I194" s="2"/>
@@ -7734,8 +7718,8 @@
       <c r="D195" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E195" s="7"/>
-      <c r="F195" s="7"/>
+      <c r="E195" s="5"/>
+      <c r="F195" s="5"/>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
       <c r="I195" s="2"/>
@@ -7751,7 +7735,7 @@
         <v>693</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" s="2" t="s">
@@ -7805,7 +7789,7 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>617</v>
@@ -7814,25 +7798,25 @@
         <v>696</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E199" s="2"/>
-      <c r="F199" s="5" t="s">
-        <v>1027</v>
+      <c r="F199" s="1" t="s">
+        <v>1030</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>618</v>
@@ -7841,17 +7825,17 @@
         <v>697</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E200" s="7"/>
-      <c r="F200" s="7"/>
+        <v>168</v>
+      </c>
+      <c r="E200" s="5"/>
+      <c r="F200" s="5"/>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
       <c r="I200" s="2"/>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
-        <v>1045</v>
+        <v>165</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>619</v>
@@ -7860,19 +7844,17 @@
         <v>698</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>982</v>
-      </c>
-      <c r="E201" s="2"/>
-      <c r="F201" s="1" t="s">
-        <v>1053</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="E201" s="5"/>
+      <c r="F201" s="5"/>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
       <c r="I201" s="2"/>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>620</v>
@@ -7881,17 +7863,17 @@
         <v>699</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E202" s="7"/>
-      <c r="F202" s="7"/>
+        <v>168</v>
+      </c>
+      <c r="E202" s="5"/>
+      <c r="F202" s="5"/>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
       <c r="I202" s="2"/>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>621</v>
@@ -7900,17 +7882,17 @@
         <v>700</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E203" s="7"/>
-      <c r="F203" s="7"/>
+        <v>168</v>
+      </c>
+      <c r="E203" s="5"/>
+      <c r="F203" s="5"/>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
       <c r="I203" s="2"/>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>622</v>
@@ -7919,17 +7901,17 @@
         <v>623</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E204" s="7"/>
-      <c r="F204" s="7"/>
+        <v>168</v>
+      </c>
+      <c r="E204" s="5"/>
+      <c r="F204" s="5"/>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
       <c r="I204" s="2"/>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>624</v>
@@ -7938,17 +7920,17 @@
         <v>625</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E205" s="7"/>
-      <c r="F205" s="7"/>
+        <v>168</v>
+      </c>
+      <c r="E205" s="5"/>
+      <c r="F205" s="5"/>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
       <c r="I205" s="2"/>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>626</v>
@@ -7957,17 +7939,17 @@
         <v>627</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E206" s="7"/>
-      <c r="F206" s="7"/>
+        <v>168</v>
+      </c>
+      <c r="E206" s="5"/>
+      <c r="F206" s="5"/>
       <c r="G206" s="2"/>
       <c r="H206" s="2"/>
       <c r="I206" s="2"/>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>628</v>
@@ -7976,17 +7958,17 @@
         <v>629</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E207" s="7"/>
-      <c r="F207" s="7"/>
+        <v>168</v>
+      </c>
+      <c r="E207" s="5"/>
+      <c r="F207" s="5"/>
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
       <c r="I207" s="2"/>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>630</v>
@@ -7995,17 +7977,17 @@
         <v>631</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E208" s="7"/>
-      <c r="F208" s="7"/>
+        <v>168</v>
+      </c>
+      <c r="E208" s="5"/>
+      <c r="F208" s="5"/>
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
       <c r="I208" s="2"/>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>632</v>
@@ -8014,17 +7996,17 @@
         <v>633</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E209" s="7"/>
-      <c r="F209" s="7"/>
+        <v>168</v>
+      </c>
+      <c r="E209" s="5"/>
+      <c r="F209" s="5"/>
       <c r="G209" s="2"/>
       <c r="H209" s="2"/>
       <c r="I209" s="2"/>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>634</v>
@@ -8033,17 +8015,17 @@
         <v>635</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E210" s="7"/>
-      <c r="F210" s="7"/>
+        <v>168</v>
+      </c>
+      <c r="E210" s="5"/>
+      <c r="F210" s="5"/>
       <c r="G210" s="2"/>
       <c r="H210" s="2"/>
       <c r="I210" s="2"/>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>636</v>
@@ -8052,17 +8034,17 @@
         <v>637</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E211" s="7"/>
-      <c r="F211" s="7"/>
+        <v>168</v>
+      </c>
+      <c r="E211" s="5"/>
+      <c r="F211" s="5"/>
       <c r="G211" s="2"/>
       <c r="H211" s="2"/>
       <c r="I211" s="2"/>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>638</v>
@@ -8071,10 +8053,10 @@
         <v>639</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E212" s="7"/>
-      <c r="F212" s="7"/>
+        <v>168</v>
+      </c>
+      <c r="E212" s="5"/>
+      <c r="F212" s="5"/>
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
       <c r="I212" s="2"/>
@@ -8092,8 +8074,8 @@
       <c r="D213" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="E213" s="7"/>
-      <c r="F213" s="7"/>
+      <c r="E213" s="5"/>
+      <c r="F213" s="5"/>
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
       <c r="I213" s="2"/>
@@ -8111,8 +8093,8 @@
       <c r="D214" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="E214" s="7"/>
-      <c r="F214" s="7"/>
+      <c r="E214" s="5"/>
+      <c r="F214" s="5"/>
       <c r="G214" s="2"/>
       <c r="H214" s="2"/>
       <c r="I214" s="2"/>
@@ -8130,8 +8112,8 @@
       <c r="D215" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="E215" s="7"/>
-      <c r="F215" s="7"/>
+      <c r="E215" s="5"/>
+      <c r="F215" s="5"/>
       <c r="G215" s="2"/>
       <c r="H215" s="2"/>
       <c r="I215" s="2"/>
@@ -8149,8 +8131,8 @@
       <c r="D216" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="E216" s="7"/>
-      <c r="F216" s="7"/>
+      <c r="E216" s="5"/>
+      <c r="F216" s="5"/>
       <c r="G216" s="2"/>
       <c r="H216" s="2"/>
       <c r="I216" s="2"/>
@@ -8168,8 +8150,8 @@
       <c r="D217" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E217" s="7"/>
-      <c r="F217" s="7"/>
+      <c r="E217" s="5"/>
+      <c r="F217" s="5"/>
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
       <c r="I217" s="2"/>
@@ -8187,8 +8169,8 @@
       <c r="D218" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E218" s="7"/>
-      <c r="F218" s="7"/>
+      <c r="E218" s="5"/>
+      <c r="F218" s="5"/>
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
       <c r="I218" s="2"/>
@@ -8206,8 +8188,8 @@
       <c r="D219" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E219" s="7"/>
-      <c r="F219" s="7"/>
+      <c r="E219" s="5"/>
+      <c r="F219" s="5"/>
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
       <c r="I219" s="2"/>
@@ -8225,8 +8207,8 @@
       <c r="D220" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E220" s="7"/>
-      <c r="F220" s="7"/>
+      <c r="E220" s="5"/>
+      <c r="F220" s="5"/>
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
       <c r="I220" s="2"/>
@@ -8244,8 +8226,8 @@
       <c r="D221" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E221" s="7"/>
-      <c r="F221" s="7"/>
+      <c r="E221" s="5"/>
+      <c r="F221" s="5"/>
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
       <c r="I221" s="2"/>
@@ -8263,8 +8245,8 @@
       <c r="D222" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E222" s="7"/>
-      <c r="F222" s="7"/>
+      <c r="E222" s="5"/>
+      <c r="F222" s="5"/>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
       <c r="I222" s="2"/>
@@ -8282,8 +8264,8 @@
       <c r="D223" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E223" s="7"/>
-      <c r="F223" s="7"/>
+      <c r="E223" s="5"/>
+      <c r="F223" s="5"/>
       <c r="G223" s="2"/>
       <c r="H223" s="2"/>
       <c r="I223" s="2"/>
@@ -8301,15 +8283,15 @@
       <c r="D224" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E224" s="7"/>
-      <c r="F224" s="7"/>
+      <c r="E224" s="5"/>
+      <c r="F224" s="5"/>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
       <c r="I224" s="2"/>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" s="2" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>706</v>
@@ -8318,11 +8300,11 @@
         <v>932</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E225" s="2"/>
       <c r="F225" s="1" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
@@ -8330,7 +8312,7 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>707</v>
@@ -8339,13 +8321,13 @@
         <v>938</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
@@ -8353,7 +8335,7 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" s="2" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>708</v>
@@ -8362,13 +8344,13 @@
         <v>941</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
@@ -8376,7 +8358,7 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
-        <v>1041</v>
+        <v>1046</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>709</v>
@@ -8385,11 +8367,11 @@
         <v>734</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E228" s="2"/>
       <c r="F228" s="1" t="s">
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
@@ -8400,8 +8382,8 @@
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
       <c r="D229" s="2"/>
-      <c r="E229" s="7"/>
-      <c r="F229" s="7"/>
+      <c r="E229" s="5"/>
+      <c r="F229" s="5"/>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
       <c r="I229" s="2"/>
@@ -8419,8 +8401,8 @@
       <c r="D230" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E230" s="7"/>
-      <c r="F230" s="7"/>
+      <c r="E230" s="5"/>
+      <c r="F230" s="5"/>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
       <c r="I230" s="2"/>
@@ -8438,8 +8420,8 @@
       <c r="D231" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E231" s="7"/>
-      <c r="F231" s="7"/>
+      <c r="E231" s="5"/>
+      <c r="F231" s="5"/>
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
       <c r="I231" s="2"/>
@@ -8457,8 +8439,8 @@
       <c r="D232" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E232" s="7"/>
-      <c r="F232" s="7"/>
+      <c r="E232" s="5"/>
+      <c r="F232" s="5"/>
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
       <c r="I232" s="2"/>
@@ -8476,15 +8458,15 @@
       <c r="D233" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E233" s="7"/>
-      <c r="F233" s="7"/>
+      <c r="E233" s="5"/>
+      <c r="F233" s="5"/>
       <c r="G233" s="2"/>
       <c r="H233" s="2"/>
       <c r="I233" s="2"/>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>866</v>
@@ -8493,17 +8475,17 @@
         <v>867</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E234" s="7"/>
-      <c r="F234" s="7"/>
+        <v>168</v>
+      </c>
+      <c r="E234" s="5"/>
+      <c r="F234" s="5"/>
       <c r="G234" s="2"/>
       <c r="H234" s="2"/>
       <c r="I234" s="2"/>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="2" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>835</v>
@@ -8512,22 +8494,62 @@
         <v>836</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G235" s="2"/>
       <c r="H235" s="2"/>
       <c r="I235" s="2"/>
     </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A236" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E236" s="5"/>
+      <c r="F236" s="5"/>
+      <c r="G236" s="2"/>
+      <c r="H236" s="2"/>
+      <c r="I236" s="2"/>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A237" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E237" s="5"/>
+      <c r="F237" s="5"/>
+      <c r="G237" s="2"/>
+      <c r="H237" s="2"/>
+      <c r="I237" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="69">
     <mergeCell ref="E233:F233"/>
     <mergeCell ref="E234:F234"/>
+    <mergeCell ref="E236:F236"/>
+    <mergeCell ref="E237:F237"/>
     <mergeCell ref="E224:F224"/>
     <mergeCell ref="E229:F229"/>
     <mergeCell ref="E230:F230"/>
@@ -8552,6 +8574,7 @@
     <mergeCell ref="E210:F210"/>
     <mergeCell ref="E211:F211"/>
     <mergeCell ref="E200:F200"/>
+    <mergeCell ref="E201:F201"/>
     <mergeCell ref="E202:F202"/>
     <mergeCell ref="E203:F203"/>
     <mergeCell ref="E204:F204"/>
@@ -8595,67 +8618,75 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F16" r:id="rId1" xr:uid="{4D83744C-709D-1C41-BA5E-BD2AE84E9412}"/>
-    <hyperlink ref="F73" r:id="rId2" xr:uid="{E171D32A-9215-BC46-80D0-A79887E19E01}"/>
-    <hyperlink ref="F74" r:id="rId3" xr:uid="{9DF0B287-4625-CB48-801B-9E764F127A83}"/>
-    <hyperlink ref="F81" r:id="rId4" xr:uid="{FB164A30-A480-E143-8EA5-3998C45CB0D7}"/>
-    <hyperlink ref="F85" r:id="rId5" xr:uid="{AF0BFBD2-717C-FC4A-B33B-2D3C915AEB0D}"/>
-    <hyperlink ref="F86" r:id="rId6" xr:uid="{DE9BE6D6-A787-AA4D-B623-F01F084CE0B0}"/>
-    <hyperlink ref="F87" r:id="rId7" xr:uid="{19BA1FCC-1651-F144-9744-891570D1AA16}"/>
-    <hyperlink ref="F90" r:id="rId8" xr:uid="{B9A95435-246B-A94E-872F-C0D9B761A68B}"/>
-    <hyperlink ref="F91" r:id="rId9" xr:uid="{BA90320D-30CD-BE45-A3D1-DF54D2914E7A}"/>
-    <hyperlink ref="F92" r:id="rId10" xr:uid="{39E85E5F-728A-D742-AF01-0103FD12A971}"/>
-    <hyperlink ref="F93" r:id="rId11" xr:uid="{E4C380DC-FA3A-FC4F-B31F-D630BDD1C2F1}"/>
-    <hyperlink ref="F95" r:id="rId12" xr:uid="{F6111BC4-3075-1B45-A641-B65694F66E75}"/>
-    <hyperlink ref="F96" r:id="rId13" xr:uid="{BC04F785-48C5-2148-8E4D-98BDBDAA39A2}"/>
-    <hyperlink ref="F97" r:id="rId14" xr:uid="{707FB250-4006-6540-B5F2-7FA6B4D84AE1}"/>
-    <hyperlink ref="F98" r:id="rId15" xr:uid="{43AAD2B6-AD8E-DB4A-92F2-CB1FDC1AB0B8}"/>
-    <hyperlink ref="F99" r:id="rId16" xr:uid="{6B651F64-6FB9-6C48-B73B-D73AFA70E755}"/>
-    <hyperlink ref="F102" r:id="rId17" xr:uid="{C271DA1A-7EC9-C945-8E50-1E1DA3B913AF}"/>
-    <hyperlink ref="F103" r:id="rId18" xr:uid="{9A9983EC-9BD1-3548-87FB-A024F49EAD34}"/>
-    <hyperlink ref="F104" r:id="rId19" xr:uid="{D9253CE1-9F79-2449-AE00-75EC5FEF656A}"/>
-    <hyperlink ref="F105" r:id="rId20" xr:uid="{783D53D8-C4E8-A04D-B065-D3E480E850CC}"/>
-    <hyperlink ref="F106" r:id="rId21" xr:uid="{473D8204-2057-454C-AA07-27706272F915}"/>
-    <hyperlink ref="F107" r:id="rId22" xr:uid="{45DB696E-0B53-9940-9B1F-6F1C06EBF3F5}"/>
-    <hyperlink ref="F119" r:id="rId23" xr:uid="{E56A32FA-602E-0146-B178-82687404DCEF}"/>
-    <hyperlink ref="F120" r:id="rId24" xr:uid="{041F1990-725F-F046-88DB-493F97A5760C}"/>
-    <hyperlink ref="F121" r:id="rId25" xr:uid="{E985503A-375A-3949-B95B-6BB03BAEAA01}"/>
-    <hyperlink ref="F122" r:id="rId26" xr:uid="{5A05BB01-A4D7-844D-80BE-89B2BA678BB0}"/>
-    <hyperlink ref="F123" r:id="rId27" xr:uid="{0B7F59E8-F289-B046-91BB-4F579E1CE558}"/>
-    <hyperlink ref="F124" r:id="rId28" xr:uid="{712F2B88-BDB0-E241-8E6D-451D262C6986}"/>
-    <hyperlink ref="F125" r:id="rId29" xr:uid="{86EF9220-27E0-1B42-B7E9-86744EAB0414}"/>
-    <hyperlink ref="F126" r:id="rId30" xr:uid="{ED57DC6C-6767-BE44-81D9-CF0A118CD0FE}"/>
-    <hyperlink ref="F133" r:id="rId31" xr:uid="{FEC8FACE-5A6E-C542-921E-2B157967AE85}"/>
-    <hyperlink ref="F145" r:id="rId32" xr:uid="{B9EE879B-229E-6741-9EE9-FBC67A23C348}"/>
-    <hyperlink ref="F146" r:id="rId33" xr:uid="{1E0EFBFE-053F-594C-9C10-1948BC7B9488}"/>
-    <hyperlink ref="F147" r:id="rId34" xr:uid="{D2D91943-D9F1-6342-9C2D-2F12A2A7D78F}"/>
-    <hyperlink ref="F148" r:id="rId35" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000s98yXYAQ/view" xr:uid="{E9D56349-9509-1A4D-9171-4F7104D11BA2}"/>
-    <hyperlink ref="F150" r:id="rId36" xr:uid="{9D81EB20-48E6-5A48-A6C7-F60F9DA8CBC1}"/>
-    <hyperlink ref="F151" r:id="rId37" xr:uid="{0EAF5AAB-C472-4E48-8C56-A3010416A213}"/>
-    <hyperlink ref="F152" r:id="rId38" xr:uid="{A6D2A713-186B-7940-B2C1-452735DC1441}"/>
-    <hyperlink ref="F153" r:id="rId39" xr:uid="{205067C4-9448-4F4F-9382-E4CF81BF5C06}"/>
-    <hyperlink ref="F154" r:id="rId40" xr:uid="{8E8ABFF6-D633-1341-A264-D9FCF4CECFE9}"/>
-    <hyperlink ref="F155" r:id="rId41" xr:uid="{BF78F0CE-B457-EA46-861E-06BD16FBD826}"/>
-    <hyperlink ref="F156" r:id="rId42" xr:uid="{C95D0D85-F640-BF4A-A84B-F07379198FFC}"/>
-    <hyperlink ref="F157" r:id="rId43" xr:uid="{D187263F-7347-3D41-A079-AD1579C398AD}"/>
-    <hyperlink ref="F158" r:id="rId44" xr:uid="{7791C319-5E9C-D248-8A81-7E299181536A}"/>
-    <hyperlink ref="F159" r:id="rId45" xr:uid="{E1ECCA8A-A61E-694F-B805-60F3AB6BFB50}"/>
-    <hyperlink ref="F160" r:id="rId46" xr:uid="{35B90A27-BD5A-9345-A8E7-7310FD6FBF20}"/>
-    <hyperlink ref="F164" r:id="rId47" xr:uid="{5DD3122C-5356-0844-B949-EF3C2DA4F343}"/>
-    <hyperlink ref="F165" r:id="rId48" xr:uid="{ED14609D-7B09-FE49-BE61-E9D9ADF3CFF7}"/>
-    <hyperlink ref="F167" r:id="rId49" xr:uid="{C5459565-305A-B545-83F2-2D5B3A1BAA7E}"/>
-    <hyperlink ref="G167" r:id="rId50" xr:uid="{BC0E9968-30CE-6A4D-BE19-A697EB2281FD}"/>
-    <hyperlink ref="H167" r:id="rId51" xr:uid="{06C543E1-8ECD-E349-B0AD-B573A44B4707}"/>
-    <hyperlink ref="I167" r:id="rId52" xr:uid="{B30DB557-A160-E641-8A7B-EC549B0188BE}"/>
-    <hyperlink ref="G168" r:id="rId53" xr:uid="{66A435B9-4B78-1347-B463-EEC74E39AEF8}"/>
-    <hyperlink ref="F199" r:id="rId54" xr:uid="{4494705E-34E4-C640-BC43-4ABE8BC739DD}"/>
-    <hyperlink ref="G199" r:id="rId55" xr:uid="{46D613B4-D756-0B44-B65A-D03E92803F8D}"/>
-    <hyperlink ref="H199" r:id="rId56" xr:uid="{E3E72607-F906-0A4C-B2CE-4C7931127AB2}"/>
-    <hyperlink ref="I199" r:id="rId57" xr:uid="{FEBE9D2E-D687-E548-B5DF-74901ECAF388}"/>
-    <hyperlink ref="F225" r:id="rId58" xr:uid="{8C0A64F8-8B65-FD46-B2C3-2691D27116E8}"/>
-    <hyperlink ref="F226" r:id="rId59" xr:uid="{49C8B99B-F637-E946-9D77-EF29843A88C2}"/>
-    <hyperlink ref="F228" r:id="rId60" xr:uid="{E0F44330-36E5-534E-8633-A00A60FB7629}"/>
-    <hyperlink ref="F235" r:id="rId61" xr:uid="{6EADA4E6-6752-C04A-8B4C-6E546ABF6A75}"/>
+    <hyperlink ref="G8" r:id="rId1" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u72eLYAQ/view" xr:uid="{D3441ED5-BCF2-844F-844E-86893A853D5C}"/>
+    <hyperlink ref="H15" r:id="rId2" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000rvp8wYAA/view" xr:uid="{1E34D697-A595-AC4C-9A12-D9EAC9831E5F}"/>
+    <hyperlink ref="F16" r:id="rId3" xr:uid="{4C7F8145-BD86-B94C-A5FA-944B0846E8EC}"/>
+    <hyperlink ref="F39" r:id="rId4" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000Q2enCYAR/view" xr:uid="{7B193E22-F2F4-984F-9FE8-B637E37CE128}"/>
+    <hyperlink ref="F43" r:id="rId5" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u9QkgYAE/view" xr:uid="{57433578-9471-5240-8562-63DE207C1E3B}"/>
+    <hyperlink ref="F73" r:id="rId6" xr:uid="{7C9DDC73-3AA5-7840-B37F-5DACA8C6087B}"/>
+    <hyperlink ref="F74" r:id="rId7" xr:uid="{D6A64E6C-55F2-AD41-999A-7DFE92034190}"/>
+    <hyperlink ref="F81" r:id="rId8" xr:uid="{FFDE54F5-ABD6-0C47-A626-F828F6AAE386}"/>
+    <hyperlink ref="F83" r:id="rId9" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{E5B8BE52-B838-0241-BA3E-2B16297615E5}"/>
+    <hyperlink ref="F85" r:id="rId10" xr:uid="{55E1EBE6-8BF8-914F-9328-5636698C019E}"/>
+    <hyperlink ref="F86" r:id="rId11" xr:uid="{265765DB-81CB-3844-AEEE-52154148A425}"/>
+    <hyperlink ref="F87" r:id="rId12" xr:uid="{83FB02AE-A5BD-5841-A0E8-E938C6A8F6B2}"/>
+    <hyperlink ref="F90" r:id="rId13" xr:uid="{DC02162B-37B2-F142-AE3E-9DBF69E2C840}"/>
+    <hyperlink ref="F91" r:id="rId14" xr:uid="{F45AE381-6913-8647-A3EB-D640115FA0D0}"/>
+    <hyperlink ref="F92" r:id="rId15" xr:uid="{78A743F6-7DA6-374C-A3EB-0EF27193E538}"/>
+    <hyperlink ref="F93" r:id="rId16" xr:uid="{82FA811E-605E-6148-97C1-96CFDA2A27A6}"/>
+    <hyperlink ref="F95" r:id="rId17" xr:uid="{B0C9954D-D6CB-6944-80C5-5E6A9C473B3B}"/>
+    <hyperlink ref="F96" r:id="rId18" xr:uid="{48E3A21D-CC84-8E40-BE0E-B871EC7D0496}"/>
+    <hyperlink ref="F97" r:id="rId19" xr:uid="{FAE882D7-FD54-D246-8E0D-42F215667125}"/>
+    <hyperlink ref="F98" r:id="rId20" xr:uid="{D8287F0E-E866-AA4F-A597-0FBAFAF94B08}"/>
+    <hyperlink ref="F99" r:id="rId21" xr:uid="{DE997DA4-3140-3949-A78F-5763EDFF052D}"/>
+    <hyperlink ref="F102" r:id="rId22" xr:uid="{2C08F2C7-B056-1D4E-95A8-D0CC52D64EDD}"/>
+    <hyperlink ref="F103" r:id="rId23" xr:uid="{5CE9DD97-A1AB-A94D-AD38-F4167F06A003}"/>
+    <hyperlink ref="F104" r:id="rId24" xr:uid="{D2224D19-7CA4-9A46-9668-3D24CAB8DDAA}"/>
+    <hyperlink ref="F105" r:id="rId25" xr:uid="{4889BB5A-EC6B-454B-9FA2-186C9C82876F}"/>
+    <hyperlink ref="F106" r:id="rId26" xr:uid="{500B64BE-B459-8045-A6A9-6963AE8340A5}"/>
+    <hyperlink ref="F107" r:id="rId27" xr:uid="{2F0FEEE1-0CA2-1547-95A9-538AA7F71601}"/>
+    <hyperlink ref="F116" r:id="rId28" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uXDB9YAO/view" xr:uid="{6773B690-35FE-0644-A201-5BEC863AB1EC}"/>
+    <hyperlink ref="F119" r:id="rId29" xr:uid="{C65A2F58-EDD5-774E-91DE-E2B56567127D}"/>
+    <hyperlink ref="F120" r:id="rId30" xr:uid="{6F74A9E0-3854-FA45-BBA2-FD514CA1DC21}"/>
+    <hyperlink ref="F121" r:id="rId31" xr:uid="{7C198BF8-6FC7-364C-9FF4-D292A5671756}"/>
+    <hyperlink ref="F122" r:id="rId32" xr:uid="{1A824135-D09B-524B-9E5B-A777931E5A2D}"/>
+    <hyperlink ref="F123" r:id="rId33" xr:uid="{3ED28AFE-2E26-E845-9067-91A449261D67}"/>
+    <hyperlink ref="F124" r:id="rId34" xr:uid="{973DD18F-59D6-E249-B4C0-80B079103823}"/>
+    <hyperlink ref="F125" r:id="rId35" xr:uid="{B9F6918B-2CFA-8441-AAF3-A7CC7DEDB441}"/>
+    <hyperlink ref="F126" r:id="rId36" xr:uid="{FF6A4EE7-E184-D949-9FE9-17792665426F}"/>
+    <hyperlink ref="F133" r:id="rId37" xr:uid="{D57FECAA-9276-3643-B005-F7AB7BAB1E99}"/>
+    <hyperlink ref="F145" r:id="rId38" xr:uid="{2FAD485E-19C9-A240-89F9-4AA97C4B56E6}"/>
+    <hyperlink ref="F146" r:id="rId39" xr:uid="{58A034F0-66F9-C34F-8327-A5256B68EEFF}"/>
+    <hyperlink ref="F147" r:id="rId40" xr:uid="{6BECD366-6F41-FA41-9B82-6F68ED2AD1DF}"/>
+    <hyperlink ref="F148" r:id="rId41" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000s98yXYAQ/view" xr:uid="{B9CFCA7A-67CE-FC4F-80FD-A1FFB430048F}"/>
+    <hyperlink ref="G149" r:id="rId42" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vDa6VYAS/view" xr:uid="{B2B64DA8-BAA5-A548-A3B0-99C2B2703DA0}"/>
+    <hyperlink ref="F150" r:id="rId43" xr:uid="{157D611B-BA15-E641-97F8-D9607805F67E}"/>
+    <hyperlink ref="F151" r:id="rId44" xr:uid="{E4DC1C5A-7194-5B49-90F8-85FA0726EC39}"/>
+    <hyperlink ref="F152" r:id="rId45" xr:uid="{9F08D383-F79A-8744-AC72-AF6DAD84A62E}"/>
+    <hyperlink ref="F153" r:id="rId46" xr:uid="{F3C90E3A-E7B8-A240-8CC7-C16AAA6567C0}"/>
+    <hyperlink ref="F154" r:id="rId47" xr:uid="{3F544506-DDE9-D24A-937B-A348194494D4}"/>
+    <hyperlink ref="F155" r:id="rId48" xr:uid="{B76A963C-E273-754E-8562-CEC32804C7F6}"/>
+    <hyperlink ref="F156" r:id="rId49" xr:uid="{46B7F455-3F2E-BF40-9AF7-7633BAC81EF0}"/>
+    <hyperlink ref="F157" r:id="rId50" xr:uid="{FC627278-EFE9-C340-AB30-E920B3195A28}"/>
+    <hyperlink ref="F158" r:id="rId51" xr:uid="{5EDE7466-8391-5C47-ACCD-F7033B0346E9}"/>
+    <hyperlink ref="F159" r:id="rId52" xr:uid="{E2096B9B-D633-7745-94B1-2F158CACC3FA}"/>
+    <hyperlink ref="F160" r:id="rId53" xr:uid="{98A67CA7-2172-8940-93F8-84D96DE10C5A}"/>
+    <hyperlink ref="F164" r:id="rId54" xr:uid="{B5989662-DD64-4943-A176-C4A9D7C3DA94}"/>
+    <hyperlink ref="F165" r:id="rId55" xr:uid="{879F7869-B8FB-CC41-8C58-B2C8950D048B}"/>
+    <hyperlink ref="F167" r:id="rId56" xr:uid="{FC337A7E-A49F-7543-9281-827FE6AAAC37}"/>
+    <hyperlink ref="G167" r:id="rId57" xr:uid="{21176141-BD70-BE4E-AD28-6FC000AAE738}"/>
+    <hyperlink ref="H167" r:id="rId58" xr:uid="{30A15A8D-7AA1-9747-B49C-9DB4E573264D}"/>
+    <hyperlink ref="I167" r:id="rId59" xr:uid="{1A9CBB84-CF6A-994A-9A2C-90A122995B7F}"/>
+    <hyperlink ref="G168" r:id="rId60" xr:uid="{A591C193-E171-1E4B-8246-C7E765F50660}"/>
+    <hyperlink ref="F199" r:id="rId61" xr:uid="{A5D4F92F-7A8B-E449-A2D2-4CBE608B1FC8}"/>
+    <hyperlink ref="G199" r:id="rId62" xr:uid="{D802EF13-355D-CC4E-AEE8-EE367A33FFDA}"/>
+    <hyperlink ref="H199" r:id="rId63" xr:uid="{262FD7D7-F22C-B542-BF7D-217E9F23203B}"/>
+    <hyperlink ref="I199" r:id="rId64" xr:uid="{62EFA2FE-C4BD-C443-8892-0F1AFE28D589}"/>
+    <hyperlink ref="F225" r:id="rId65" xr:uid="{70B86A88-F489-9E44-B5E9-278B6BBE2C9F}"/>
+    <hyperlink ref="F226" r:id="rId66" xr:uid="{91FB41BF-FB7F-4C4B-84BB-ECE1BFAAABFC}"/>
+    <hyperlink ref="F227" r:id="rId67" display="https://curebound.lightning.force.com/lightning/r/Account/0014W00002W8eYDQAZ/view" xr:uid="{94B6116C-2E97-5944-9405-63AFC44D7284}"/>
+    <hyperlink ref="F228" r:id="rId68" xr:uid="{AF6DB760-2F55-8F4D-B80D-03159B2D6CB0}"/>
+    <hyperlink ref="F235" r:id="rId69" xr:uid="{41F1C20C-DD22-C34C-AF57-5509D2AE290F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9040,114 +9071,114 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B48" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B49" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B51" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B52" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B53" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B54" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B55" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B56" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B57" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B58" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B59" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B60" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
@@ -9160,18 +9191,18 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B62" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B63" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
@@ -9184,10 +9215,10 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B65" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
@@ -9208,10 +9239,10 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B68" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
@@ -9224,10 +9255,10 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B70" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
@@ -9240,10 +9271,10 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B72" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
@@ -9264,10 +9295,10 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B75" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
@@ -9288,10 +9319,10 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B78" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
@@ -9312,10 +9343,10 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B81" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
@@ -9328,18 +9359,18 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B83" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B84" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
@@ -9549,10 +9580,10 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B111" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
@@ -9613,10 +9644,10 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B119" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
@@ -9685,10 +9716,10 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B128" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
@@ -9765,10 +9796,10 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B138" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
@@ -9781,10 +9812,10 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B140" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
@@ -9845,26 +9876,26 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B149" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B150" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
@@ -9917,50 +9948,50 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B157" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B158" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B159" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B160" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B161" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B162" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
@@ -9973,10 +10004,10 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B164" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
@@ -9989,18 +10020,18 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B166" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B167" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
@@ -10013,18 +10044,18 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B169" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B170" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
@@ -10037,10 +10068,10 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B172" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
@@ -10053,10 +10084,10 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B174" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
@@ -10069,18 +10100,18 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B176" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B177" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
@@ -10093,26 +10124,26 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B179" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B180" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
@@ -10125,42 +10156,42 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B183" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B184" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B185" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B186" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B187" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
@@ -10173,10 +10204,10 @@
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B189" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
@@ -10189,10 +10220,10 @@
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B191" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
@@ -10205,34 +10236,34 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B193" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B194" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B195" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B196" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
@@ -10333,10 +10364,10 @@
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B209" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
@@ -10349,10 +10380,10 @@
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B211" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
@@ -10413,10 +10444,10 @@
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B219" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
@@ -10429,10 +10460,10 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B221" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
@@ -10506,10 +10537,10 @@
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B231" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
@@ -10554,34 +10585,34 @@
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B237" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B238" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B239" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B240" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
@@ -10634,34 +10665,34 @@
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B247" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B248" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B249" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B250" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
@@ -10730,34 +10761,34 @@
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B259" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B260" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B261" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B262" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
@@ -10826,10 +10857,10 @@
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B271" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.2">
@@ -10842,10 +10873,10 @@
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B273" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.2">
@@ -10858,26 +10889,26 @@
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B275" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B276" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B277" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
@@ -10922,10 +10953,10 @@
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B283" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.2">
@@ -10978,26 +11009,26 @@
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B290" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B291" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B292" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
@@ -11026,10 +11057,10 @@
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B296" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
@@ -11042,10 +11073,10 @@
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B298" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
@@ -11106,10 +11137,10 @@
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B306" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.2">
@@ -11122,10 +11153,10 @@
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B308" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.2">
@@ -11138,10 +11169,10 @@
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B310" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.2">
@@ -11154,10 +11185,10 @@
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B312" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.2">
@@ -11170,10 +11201,10 @@
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B314" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.2">
@@ -11234,18 +11265,18 @@
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B322" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B323" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
@@ -11258,10 +11289,10 @@
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B325" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.2">
@@ -11282,10 +11313,10 @@
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B328" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.2">
@@ -11322,34 +11353,34 @@
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B333" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B334" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B335" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B336" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.2">
@@ -11370,10 +11401,10 @@
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B339" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.2">
@@ -11386,18 +11417,18 @@
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B341" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B342" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.2">
@@ -11410,18 +11441,18 @@
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B344" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B345" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.2">
@@ -11434,10 +11465,10 @@
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B347" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.2">

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA01B39-F3AC-3A4C-9AD4-C0DAB839547D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AA2076F-FB4C-7144-9437-8FDA4F6FFECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="33380" windowHeight="21580" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
+    <workbookView xWindow="3980" yWindow="1480" windowWidth="29160" windowHeight="20060" activeTab="1" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
   <sheets>
     <sheet name="xlsx" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="1055">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1858" uniqueCount="1058">
   <si>
     <t>Household Name</t>
   </si>
@@ -507,9 +508,6 @@
     <t>Sponsor Hold</t>
   </si>
   <si>
-    <t>Clayco Construction $125000 Sponsorship 6/1/2026 | Opportunity | Salesforce</t>
-  </si>
-  <si>
     <t>Trott</t>
   </si>
   <si>
@@ -2073,9 +2071,6 @@
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qvw9RYAQ/view</t>
   </si>
   <si>
-    <t>Ranch &amp; Coast Magazine Advertising CFC26 Sponsorship 1/16/2026 | Opportunity | Salesforce</t>
-  </si>
-  <si>
     <t>x=13.95, y=80.68</t>
   </si>
   <si>
@@ -2976,21 +2971,12 @@
     <t>Elisa Jaime + Lynda Kerr</t>
   </si>
   <si>
-    <t>Kerr Concert 2026 Tickets | Opportunity | Salesforce</t>
-  </si>
-  <si>
     <t>Amy + Jim Wood</t>
   </si>
   <si>
     <t>Gary Levine + Larry Bloch + Mitch Adler</t>
   </si>
   <si>
-    <t>Adler Concert 2026 Tickets | Opportunity | Salesforce</t>
-  </si>
-  <si>
-    <t>Tafel Klaus Concert 2026 Tickets | Opportunity | Salesforce</t>
-  </si>
-  <si>
     <t>Theodora Polamalu</t>
   </si>
   <si>
@@ -3165,9 +3151,6 @@
     <t>Vickey Syage</t>
   </si>
   <si>
-    <t>Whittington Concert 2026 Tickets | Opportunity | Salesforce</t>
-  </si>
-  <si>
     <t>(now requesting E54 or near that area)</t>
   </si>
   <si>
@@ -3195,13 +3178,40 @@
     <t>Donating to cancer fighters</t>
   </si>
   <si>
-    <t>Justin and Stephanie Smith and Friends Household | Account | Salesforce</t>
-  </si>
-  <si>
     <t>Cheryl Anderson &amp; Randy Brooks</t>
   </si>
   <si>
-    <t>Brooks Concert 2026 Tickets | Opportunity | Salesforce</t>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u72eLYAQ/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000rvp8wYAA/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000Q2enCYAR/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u9QkgYAE/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uXDB9YAO/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vDa6VYAS/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Account/0014W00002W8eYDQAZ/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000s98yXYAQ/view</t>
+  </si>
+  <si>
+    <t>Potentially Second Table for Cheryl Anderson</t>
+  </si>
+  <si>
+    <t>Debby &amp; Hal Jacobs</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uKciSYAS/view</t>
   </si>
 </sst>
 </file>
@@ -3280,13 +3290,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -3623,10 +3632,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7894B4-148E-174D-AE8B-E6DE441B89B0}">
-  <dimension ref="A1:I237"/>
+  <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{496ADA21-09B7-4646-B59A-A38257810680}">
+  <dimension ref="A1:I239"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="9" width="60.33203125" customWidth="1"/>
+    <col min="5" max="5" width="66.1640625" customWidth="1"/>
+    <col min="6" max="6" width="87.6640625" customWidth="1"/>
+    <col min="7" max="7" width="75.1640625" customWidth="1"/>
+    <col min="8" max="8" width="42.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -3681,7 +3703,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>14</v>
@@ -3734,8 +3756,8 @@
       <c r="D5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -3748,7 +3770,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>12</v>
@@ -3784,7 +3806,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>32</v>
@@ -3800,14 +3822,14 @@
         <v>34</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>979</v>
+        <v>1047</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>35</v>
@@ -3933,7 +3955,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>58</v>
@@ -3952,13 +3974,13 @@
         <v>61</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>982</v>
+        <v>1048</v>
       </c>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>62</v>
@@ -4065,7 +4087,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>81</v>
@@ -4086,7 +4108,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>84</v>
@@ -4111,7 +4133,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>88</v>
@@ -4201,7 +4223,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>106</v>
@@ -4217,7 +4239,7 @@
         <v>108</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -4363,7 +4385,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -4449,7 +4471,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>151</v>
@@ -4472,7 +4494,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="1" t="s">
-        <v>156</v>
+        <v>1049</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -4480,39 +4502,39 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -4523,18 +4545,18 @@
         <v>21</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="D42" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F42" s="5"/>
+      <c r="E42" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
@@ -4544,17 +4566,17 @@
         <v>50</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="1" t="s">
-        <v>983</v>
+        <v>1050</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -4562,20 +4584,20 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -4583,20 +4605,20 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -4604,20 +4626,20 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -4625,20 +4647,20 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -4646,20 +4668,20 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
@@ -4667,20 +4689,20 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -4688,20 +4710,20 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -4709,20 +4731,20 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
@@ -4730,20 +4752,20 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>201</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
@@ -4751,22 +4773,22 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="D53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E53" s="2" t="s">
+      <c r="F53" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -4774,20 +4796,20 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C54" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
@@ -4795,20 +4817,20 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>214</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
@@ -4816,20 +4838,20 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
@@ -4837,20 +4859,20 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
@@ -4858,20 +4880,20 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C58" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
@@ -4879,20 +4901,20 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>229</v>
-      </c>
       <c r="C59" s="2" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
@@ -4900,20 +4922,20 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>233</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>234</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
@@ -4921,20 +4943,20 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="C61" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
@@ -4942,58 +4964,58 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>241</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="C63" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="C64" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
@@ -5001,39 +5023,39 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="C65" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>251</v>
-      </c>
       <c r="D65" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="C66" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
@@ -5041,20 +5063,20 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="C67" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
@@ -5062,20 +5084,20 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
@@ -5083,20 +5105,20 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
@@ -5104,20 +5126,20 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="C70" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
@@ -5125,20 +5147,20 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="C71" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>271</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
@@ -5146,20 +5168,20 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
@@ -5167,20 +5189,20 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
@@ -5188,20 +5210,20 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B74" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" s="1" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
@@ -5209,20 +5231,20 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="C75" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
@@ -5230,22 +5252,22 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B76" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="C76" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="D76" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D76" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E76" s="2" t="s">
+      <c r="F76" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -5253,20 +5275,20 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="C77" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>294</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
@@ -5274,20 +5296,20 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="C78" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
@@ -5295,20 +5317,20 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
@@ -5316,20 +5338,20 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="C80" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>305</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
@@ -5337,20 +5359,20 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="1" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
@@ -5358,39 +5380,39 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B82" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>311</v>
-      </c>
       <c r="D82" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="C83" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>314</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="1" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -5398,20 +5420,20 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="C84" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>318</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
@@ -5419,20 +5441,20 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="C85" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>321</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
@@ -5440,20 +5462,20 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>324</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="1" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -5461,43 +5483,43 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="C87" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>327</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="1" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="C88" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -5505,20 +5527,20 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="C89" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>335</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -5526,20 +5548,20 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B90" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -5547,20 +5569,20 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>341</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" s="1" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -5568,20 +5590,20 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B92" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>343</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="1" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -5589,20 +5611,20 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="B93" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>346</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="1" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -5610,20 +5632,20 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="B94" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>348</v>
-      </c>
       <c r="D94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E94" s="2"/>
-      <c r="F94" s="6" t="s">
-        <v>339</v>
+      <c r="F94" s="5" t="s">
+        <v>338</v>
       </c>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -5631,20 +5653,20 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="B95" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>350</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="1" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -5652,20 +5674,20 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="C96" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>353</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="1" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -5673,20 +5695,20 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B97" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
@@ -5694,20 +5716,20 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B98" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>358</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="1" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
@@ -5715,20 +5737,20 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B99" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>360</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="1" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
@@ -5736,20 +5758,20 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="C100" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
@@ -5757,20 +5779,20 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B101" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
@@ -5778,20 +5800,20 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="1" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
@@ -5799,20 +5821,20 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B103" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>372</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -5820,20 +5842,20 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="C104" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>375</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -5841,20 +5863,20 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B105" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" s="1" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -5862,20 +5884,20 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="C106" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -5883,20 +5905,20 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B107" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>384</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" s="1" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
@@ -5904,20 +5926,20 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="C108" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>387</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
@@ -5925,20 +5947,20 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B109" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>393</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E109" s="2"/>
-      <c r="F109" s="6" t="s">
-        <v>391</v>
+      <c r="F109" s="5" t="s">
+        <v>390</v>
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
@@ -5946,20 +5968,20 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="C110" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>396</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
@@ -5967,20 +5989,20 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="C111" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
@@ -5988,20 +6010,20 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B112" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>401</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
@@ -6009,77 +6031,77 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="C113" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="C113" s="2" t="s">
-        <v>404</v>
-      </c>
       <c r="D113" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E113" s="5"/>
-      <c r="F113" s="5"/>
+      <c r="E113" s="2"/>
+      <c r="F113" s="2"/>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B114" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C114" s="2" t="s">
-        <v>406</v>
-      </c>
       <c r="D114" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E114" s="5"/>
-      <c r="F114" s="5"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B115" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C115" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>408</v>
-      </c>
       <c r="D115" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E115" s="5"/>
-      <c r="F115" s="5"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="B116" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C116" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" s="1" t="s">
-        <v>1042</v>
+        <v>1051</v>
       </c>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
@@ -6087,20 +6109,20 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B117" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="C117" s="2" t="s">
         <v>412</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>413</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
@@ -6108,20 +6130,20 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B118" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C118" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>416</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
@@ -6129,20 +6151,20 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="C119" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
@@ -6150,20 +6172,20 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B120" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C120" s="2" t="s">
         <v>421</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>422</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
@@ -6171,20 +6193,20 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B121" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C121" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>424</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
@@ -6192,20 +6214,20 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="C122" s="2" t="s">
         <v>426</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>427</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
@@ -6213,20 +6235,20 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B123" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C123" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>430</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="1" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
@@ -6234,20 +6256,20 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B124" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C124" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>432</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="1" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
@@ -6255,20 +6277,20 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B125" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>434</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="1" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
@@ -6276,20 +6298,20 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B126" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="1" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
@@ -6297,20 +6319,20 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="C127" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>439</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
@@ -6318,20 +6340,20 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="C128" s="2" t="s">
         <v>442</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>443</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
@@ -6339,20 +6361,20 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B129" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C129" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>446</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
@@ -6360,20 +6382,20 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B130" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="C130" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
@@ -6381,22 +6403,22 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="C131" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="D131" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F131" s="2" t="s">
         <v>454</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>1043</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>455</v>
       </c>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
@@ -6404,22 +6426,22 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B132" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="C132" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="D132" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="D132" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>459</v>
-      </c>
       <c r="F132" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
@@ -6427,20 +6449,20 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B133" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="C133" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
@@ -6448,22 +6470,22 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="C134" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="D134" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="F134" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>466</v>
       </c>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
@@ -6471,20 +6493,20 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B135" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="C135" s="2" t="s">
         <v>468</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>469</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
@@ -6492,20 +6514,20 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B136" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="C136" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>473</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
@@ -6513,22 +6535,22 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B137" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="C137" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="C137" s="2" t="s">
+      <c r="D137" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F137" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>1044</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
@@ -6536,20 +6558,20 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="C138" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
@@ -6557,20 +6579,20 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B139" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="C139" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
@@ -6578,22 +6600,22 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="C140" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="D140" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E140" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="D140" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>490</v>
-      </c>
       <c r="F140" s="3" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
@@ -6601,20 +6623,20 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="C141" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>493</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
@@ -6625,17 +6647,17 @@
         <v>17</v>
       </c>
       <c r="B142" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C142" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
@@ -6646,17 +6668,17 @@
         <v>17</v>
       </c>
       <c r="B143" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C143" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>498</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
@@ -6667,17 +6689,17 @@
         <v>17</v>
       </c>
       <c r="B144" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="C144" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
@@ -6685,22 +6707,22 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="C145" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="D145" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F145" s="1" t="s">
         <v>503</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
@@ -6708,22 +6730,22 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B146" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="C146" s="2" t="s">
-        <v>506</v>
-      </c>
       <c r="D146" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
@@ -6731,22 +6753,22 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B147" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C147" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="C147" s="2" t="s">
-        <v>508</v>
-      </c>
       <c r="D147" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
@@ -6754,64 +6776,64 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
-        <v>509</v>
+        <v>1046</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="E148" s="2"/>
-      <c r="F148" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="G148" s="2"/>
+      <c r="F148" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>1052</v>
+      </c>
       <c r="H148" s="2"/>
       <c r="I148" s="2"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
-        <v>1053</v>
+        <v>350</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E149" s="2"/>
-      <c r="F149" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>1054</v>
-      </c>
+      <c r="F149" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G149" s="2"/>
       <c r="H149" s="2"/>
       <c r="I149" s="2"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>351</v>
+        <v>516</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" s="1" t="s">
-        <v>354</v>
+        <v>519</v>
       </c>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
@@ -6819,20 +6841,20 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" s="1" t="s">
-        <v>520</v>
+        <v>1006</v>
       </c>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
@@ -6840,20 +6862,20 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" s="1" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
@@ -6861,20 +6883,20 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" s="1" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
@@ -6882,20 +6904,20 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" s="1" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
@@ -6903,20 +6925,20 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" s="1" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
@@ -6924,20 +6946,20 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" s="1" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
@@ -6945,20 +6967,20 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>373</v>
+        <v>533</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" s="1" t="s">
-        <v>1016</v>
+        <v>538</v>
       </c>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
@@ -6966,20 +6988,20 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" s="1" t="s">
-        <v>539</v>
+        <v>1012</v>
       </c>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
@@ -6987,20 +7009,20 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" s="1" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
@@ -7008,20 +7030,20 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E160" s="2"/>
-      <c r="F160" s="1" t="s">
-        <v>1018</v>
+      <c r="F160" s="2" t="s">
+        <v>544</v>
       </c>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
@@ -7029,20 +7051,20 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
@@ -7050,20 +7072,22 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E162" s="2"/>
+      <c r="E162" s="2" t="s">
+        <v>552</v>
+      </c>
       <c r="F162" s="2" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
@@ -7071,22 +7095,22 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
-        <v>550</v>
+        <v>1014</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="F163" s="2" t="s">
-        <v>554</v>
+        <v>1015</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>1016</v>
       </c>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
@@ -7094,22 +7118,22 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F164" s="1" t="s">
         <v>1019</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E164" s="2" t="s">
-        <v>1020</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>1021</v>
       </c>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
@@ -7117,22 +7141,20 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
-        <v>1022</v>
+        <v>558</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>557</v>
+        <v>388</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>558</v>
+        <v>389</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E165" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F165" s="1" t="s">
-        <v>1024</v>
+      <c r="E165" s="2"/>
+      <c r="F165" s="2" t="s">
+        <v>561</v>
       </c>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
@@ -7140,606 +7162,606 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B166" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="B166" s="2" t="s">
-        <v>389</v>
-      </c>
       <c r="C166" s="2" t="s">
-        <v>390</v>
+        <v>560</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>12</v>
+        <v>980</v>
       </c>
       <c r="E166" s="2"/>
-      <c r="F166" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="G166" s="2"/>
-      <c r="H166" s="2"/>
-      <c r="I166" s="2"/>
+      <c r="F166" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H166" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I166" s="1" t="s">
+        <v>1024</v>
+      </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
-        <v>1025</v>
+        <v>562</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>561</v>
+        <v>677</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>985</v>
+        <v>12</v>
       </c>
       <c r="E167" s="2"/>
-      <c r="F167" s="1" t="s">
-        <v>1026</v>
+      <c r="F167" s="3" t="s">
+        <v>668</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="H167" s="1" t="s">
-        <v>1028</v>
-      </c>
-      <c r="I167" s="1" t="s">
-        <v>1029</v>
-      </c>
+        <v>673</v>
+      </c>
+      <c r="H167" s="2"/>
+      <c r="I167" s="2"/>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="G168" s="1" t="s">
-        <v>674</v>
-      </c>
+      <c r="G168" s="2"/>
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>680</v>
+        <v>568</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>155</v>
+        <v>569</v>
       </c>
       <c r="E169" s="2"/>
-      <c r="F169" s="3" t="s">
-        <v>670</v>
-      </c>
+      <c r="F169" s="2"/>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C170" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="D170" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="D170" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E170" s="5"/>
-      <c r="F170" s="5"/>
+      <c r="E170" s="2"/>
+      <c r="F170" s="2"/>
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
       <c r="I170" s="2"/>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E171" s="5"/>
-      <c r="F171" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E171" s="2"/>
+      <c r="F171" s="2"/>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
       <c r="I171" s="2"/>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E172" s="5"/>
-      <c r="F172" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E172" s="2"/>
+      <c r="F172" s="2"/>
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
       <c r="I172" s="2"/>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E173" s="5"/>
-      <c r="F173" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E173" s="2"/>
+      <c r="F173" s="2"/>
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
       <c r="I173" s="2"/>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E174" s="5"/>
-      <c r="F174" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E174" s="2"/>
+      <c r="F174" s="2"/>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
       <c r="I174" s="2"/>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E175" s="5"/>
-      <c r="F175" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E175" s="2"/>
+      <c r="F175" s="2"/>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
       <c r="I175" s="2"/>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E176" s="5"/>
-      <c r="F176" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E176" s="2"/>
+      <c r="F176" s="2"/>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
       <c r="I176" s="2"/>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E177" s="5"/>
-      <c r="F177" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E177" s="2"/>
+      <c r="F177" s="2"/>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
       <c r="I177" s="2"/>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E178" s="5"/>
-      <c r="F178" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E178" s="2"/>
+      <c r="F178" s="2"/>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
       <c r="I178" s="2"/>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E179" s="5"/>
-      <c r="F179" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E179" s="2"/>
+      <c r="F179" s="2"/>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
       <c r="I179" s="2"/>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E180" s="5"/>
-      <c r="F180" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E180" s="2"/>
+      <c r="F180" s="2"/>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
       <c r="I180" s="2"/>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E181" s="5"/>
-      <c r="F181" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E181" s="2"/>
+      <c r="F181" s="2"/>
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
       <c r="I181" s="2"/>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
-        <v>567</v>
+        <v>679</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E182" s="5"/>
-      <c r="F182" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E182" s="2"/>
+      <c r="F182" s="2"/>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
       <c r="I182" s="2"/>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E183" s="5"/>
-      <c r="F183" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E183" s="2"/>
+      <c r="F183" s="2"/>
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
       <c r="I183" s="2"/>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
-        <v>681</v>
+        <v>566</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>598</v>
+        <v>680</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E184" s="5"/>
-      <c r="F184" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E184" s="2"/>
+      <c r="F184" s="2"/>
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
       <c r="I184" s="2"/>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>599</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E185" s="5"/>
-      <c r="F185" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E185" s="2"/>
+      <c r="F185" s="2"/>
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
       <c r="I185" s="2"/>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>600</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E186" s="5"/>
-      <c r="F186" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E186" s="2"/>
+      <c r="F186" s="2"/>
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
       <c r="I186" s="2"/>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>601</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E187" s="5"/>
-      <c r="F187" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E187" s="2"/>
+      <c r="F187" s="2"/>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
       <c r="I187" s="2"/>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>602</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E188" s="5"/>
-      <c r="F188" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E188" s="2"/>
+      <c r="F188" s="2"/>
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
       <c r="I188" s="2"/>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>603</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E189" s="5"/>
-      <c r="F189" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E189" s="2"/>
+      <c r="F189" s="2"/>
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
       <c r="I189" s="2"/>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>604</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E190" s="5"/>
-      <c r="F190" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E190" s="2"/>
+      <c r="F190" s="2"/>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
       <c r="I190" s="2"/>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>605</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E191" s="5"/>
-      <c r="F191" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E191" s="2"/>
+      <c r="F191" s="2"/>
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
       <c r="I191" s="2"/>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>606</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E192" s="5"/>
-      <c r="F192" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E192" s="2"/>
+      <c r="F192" s="2"/>
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
       <c r="I192" s="2"/>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>607</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E193" s="5"/>
-      <c r="F193" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E193" s="2"/>
+      <c r="F193" s="2"/>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
       <c r="I193" s="2"/>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>608</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E194" s="5"/>
-      <c r="F194" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E194" s="2"/>
+      <c r="F194" s="2"/>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
       <c r="I194" s="2"/>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
-        <v>567</v>
+        <v>609</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E195" s="5"/>
-      <c r="F195" s="5"/>
+        <v>980</v>
+      </c>
+      <c r="E195" s="2"/>
+      <c r="F195" s="2" t="s">
+        <v>611</v>
+      </c>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
       <c r="I195" s="2"/>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>985</v>
+        <v>155</v>
       </c>
       <c r="E196" s="2"/>
-      <c r="F196" s="2" t="s">
-        <v>612</v>
+      <c r="F196" s="3" t="s">
+        <v>670</v>
       </c>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
@@ -7747,13 +7769,13 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>155</v>
@@ -7768,543 +7790,545 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
-        <v>615</v>
+        <v>1020</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>616</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>155</v>
+        <v>980</v>
       </c>
       <c r="E198" s="2"/>
-      <c r="F198" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="G198" s="2"/>
-      <c r="H198" s="2"/>
-      <c r="I198" s="2"/>
+      <c r="F198" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H198" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="I198" s="1" t="s">
+        <v>1028</v>
+      </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
-        <v>1025</v>
+        <v>164</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>617</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>985</v>
+        <v>167</v>
       </c>
       <c r="E199" s="2"/>
-      <c r="F199" s="1" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G199" s="1" t="s">
-        <v>1031</v>
-      </c>
-      <c r="H199" s="1" t="s">
-        <v>1032</v>
-      </c>
-      <c r="I199" s="1" t="s">
-        <v>1033</v>
-      </c>
+      <c r="F199" s="2"/>
+      <c r="G199" s="2"/>
+      <c r="H199" s="2"/>
+      <c r="I199" s="2"/>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>618</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E200" s="5"/>
-      <c r="F200" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="E200" s="2"/>
+      <c r="F200" s="3"/>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
       <c r="I200" s="2"/>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>619</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E201" s="5"/>
-      <c r="F201" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="E201" s="2"/>
+      <c r="F201" s="2"/>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
       <c r="I201" s="2"/>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>620</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E202" s="5"/>
-      <c r="F202" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="E202" s="2"/>
+      <c r="F202" s="2"/>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
       <c r="I202" s="2"/>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>621</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>700</v>
+        <v>622</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E203" s="5"/>
-      <c r="F203" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="E203" s="2"/>
+      <c r="F203" s="2"/>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
       <c r="I203" s="2"/>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E204" s="5"/>
-      <c r="F204" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="E204" s="2"/>
+      <c r="F204" s="2"/>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
       <c r="I204" s="2"/>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E205" s="5"/>
-      <c r="F205" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="E205" s="2"/>
+      <c r="F205" s="2"/>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
       <c r="I205" s="2"/>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E206" s="5"/>
-      <c r="F206" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="E206" s="2"/>
+      <c r="F206" s="2"/>
       <c r="G206" s="2"/>
       <c r="H206" s="2"/>
       <c r="I206" s="2"/>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E207" s="5"/>
-      <c r="F207" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="E207" s="2"/>
+      <c r="F207" s="2"/>
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
       <c r="I207" s="2"/>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E208" s="5"/>
-      <c r="F208" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="E208" s="2"/>
+      <c r="F208" s="2"/>
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
       <c r="I208" s="2"/>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E209" s="5"/>
-      <c r="F209" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="E209" s="2"/>
+      <c r="F209" s="2"/>
       <c r="G209" s="2"/>
       <c r="H209" s="2"/>
       <c r="I209" s="2"/>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E210" s="5"/>
-      <c r="F210" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="E210" s="2"/>
+      <c r="F210" s="2"/>
       <c r="G210" s="2"/>
       <c r="H210" s="2"/>
       <c r="I210" s="2"/>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E211" s="5"/>
-      <c r="F211" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="E211" s="2"/>
+      <c r="F211" s="2"/>
       <c r="G211" s="2"/>
       <c r="H211" s="2"/>
       <c r="I211" s="2"/>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
-        <v>165</v>
+        <v>639</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C212" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D212" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="D212" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E212" s="5"/>
-      <c r="F212" s="5"/>
+      <c r="E212" s="2"/>
+      <c r="F212" s="2"/>
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
       <c r="I212" s="2"/>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A213" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="E213" s="5"/>
-      <c r="F213" s="5"/>
+        <v>639</v>
+      </c>
+      <c r="E213" s="2"/>
+      <c r="F213" s="2"/>
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
       <c r="I213" s="2"/>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="E214" s="5"/>
-      <c r="F214" s="5"/>
+        <v>639</v>
+      </c>
+      <c r="E214" s="2"/>
+      <c r="F214" s="2"/>
       <c r="G214" s="2"/>
       <c r="H214" s="2"/>
       <c r="I214" s="2"/>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="E215" s="5"/>
-      <c r="F215" s="5"/>
+        <v>639</v>
+      </c>
+      <c r="E215" s="2"/>
+      <c r="F215" s="2"/>
       <c r="G215" s="2"/>
       <c r="H215" s="2"/>
       <c r="I215" s="2"/>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
-        <v>640</v>
+        <v>566</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="E216" s="5"/>
-      <c r="F216" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E216" s="2"/>
+      <c r="F216" s="2"/>
       <c r="G216" s="2"/>
       <c r="H216" s="2"/>
       <c r="I216" s="2"/>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E217" s="5"/>
-      <c r="F217" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E217" s="2"/>
+      <c r="F217" s="2"/>
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
       <c r="I217" s="2"/>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E218" s="5"/>
-      <c r="F218" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E218" s="2"/>
+      <c r="F218" s="2"/>
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
       <c r="I218" s="2"/>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>653</v>
+        <v>699</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>654</v>
+        <v>713</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E219" s="5"/>
-      <c r="F219" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E219" s="2"/>
+      <c r="F219" s="2"/>
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
       <c r="I219" s="2"/>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E220" s="5"/>
-      <c r="F220" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E220" s="2"/>
+      <c r="F220" s="2"/>
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
       <c r="I220" s="2"/>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E221" s="5"/>
-      <c r="F221" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E221" s="2"/>
+      <c r="F221" s="2"/>
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
       <c r="I221" s="2"/>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>717</v>
+        <v>867</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E222" s="5"/>
-      <c r="F222" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E222" s="2"/>
+      <c r="F222" s="2"/>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
       <c r="I222" s="2"/>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E223" s="5"/>
-      <c r="F223" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E223" s="2"/>
+      <c r="F223" s="2"/>
       <c r="G223" s="2"/>
       <c r="H223" s="2"/>
       <c r="I223" s="2"/>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
-        <v>567</v>
+        <v>1029</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>868</v>
+        <v>930</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E224" s="5"/>
-      <c r="F224" s="5"/>
+        <v>980</v>
+      </c>
+      <c r="E224" s="2"/>
+      <c r="F224" s="1" t="s">
+        <v>1030</v>
+      </c>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
       <c r="I224" s="2"/>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" s="2" t="s">
-        <v>1034</v>
+        <v>979</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>985</v>
-      </c>
-      <c r="E225" s="2"/>
+        <v>980</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>981</v>
+      </c>
       <c r="F225" s="1" t="s">
-        <v>1035</v>
+        <v>982</v>
       </c>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
@@ -8312,22 +8336,22 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
-        <v>984</v>
+        <v>1044</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>986</v>
+        <v>1045</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>987</v>
+        <v>1053</v>
       </c>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
@@ -8335,22 +8359,20 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" s="2" t="s">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>941</v>
+        <v>732</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>985</v>
-      </c>
-      <c r="E227" s="2" t="s">
-        <v>1051</v>
-      </c>
+        <v>980</v>
+      </c>
+      <c r="E227" s="2"/>
       <c r="F227" s="1" t="s">
-        <v>1052</v>
+        <v>1043</v>
       </c>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
@@ -8358,341 +8380,312 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
-        <v>1046</v>
+        <v>709</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>734</v>
+        <v>868</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>985</v>
+        <v>569</v>
       </c>
       <c r="E228" s="2"/>
-      <c r="F228" s="1" t="s">
-        <v>1049</v>
-      </c>
+      <c r="F228" s="2"/>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
       <c r="I228" s="2"/>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A229" s="2"/>
-      <c r="B229" s="2"/>
-      <c r="C229" s="2"/>
-      <c r="D229" s="2"/>
-      <c r="E229" s="5"/>
-      <c r="F229" s="5"/>
+      <c r="A229" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E229" s="2"/>
+      <c r="F229" s="2"/>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
       <c r="I229" s="2"/>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B230" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="B230" s="2" t="s">
-        <v>712</v>
-      </c>
       <c r="C230" s="2" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E230" s="5"/>
-      <c r="F230" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E230" s="2"/>
+      <c r="F230" s="2"/>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
       <c r="I230" s="2"/>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>868</v>
+        <v>714</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E231" s="5"/>
-      <c r="F231" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E231" s="2"/>
+      <c r="F231" s="2"/>
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
       <c r="I231" s="2"/>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
-        <v>567</v>
+        <v>164</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>713</v>
+        <v>864</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>875</v>
+        <v>865</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E232" s="5"/>
-      <c r="F232" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="E232" s="2"/>
+      <c r="F232" s="2"/>
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
       <c r="I232" s="2"/>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" s="2" t="s">
-        <v>567</v>
+        <v>1041</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>702</v>
+        <v>833</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>716</v>
+        <v>834</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E233" s="5"/>
-      <c r="F233" s="5"/>
+        <v>980</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F233" s="1" t="s">
+        <v>390</v>
+      </c>
       <c r="G233" s="2"/>
       <c r="H233" s="2"/>
       <c r="I233" s="2"/>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" s="2" t="s">
-        <v>165</v>
+        <v>566</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>866</v>
+        <v>878</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>867</v>
+        <v>879</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E234" s="5"/>
-      <c r="F234" s="5"/>
+        <v>569</v>
+      </c>
+      <c r="E234" s="2"/>
+      <c r="F234" s="2"/>
       <c r="G234" s="2"/>
       <c r="H234" s="2"/>
       <c r="I234" s="2"/>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="2" t="s">
-        <v>1047</v>
+        <v>566</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>835</v>
+        <v>922</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>836</v>
+        <v>923</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>985</v>
-      </c>
-      <c r="E235" s="2" t="s">
-        <v>1048</v>
-      </c>
-      <c r="F235" s="1" t="s">
-        <v>391</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="E235" s="2"/>
+      <c r="F235" s="2"/>
       <c r="G235" s="2"/>
       <c r="H235" s="2"/>
       <c r="I235" s="2"/>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
-        <v>567</v>
+        <v>508</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>880</v>
+        <v>937</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>881</v>
+        <v>938</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E236" s="5"/>
-      <c r="F236" s="5"/>
+        <v>155</v>
+      </c>
+      <c r="E236" s="2"/>
+      <c r="F236" s="1" t="s">
+        <v>1054</v>
+      </c>
       <c r="G236" s="2"/>
       <c r="H236" s="2"/>
       <c r="I236" s="2"/>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
-        <v>567</v>
+        <v>164</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>924</v>
+        <v>509</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>925</v>
+        <v>510</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E237" s="5"/>
-      <c r="F237" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F237" s="2"/>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
       <c r="I237" s="2"/>
     </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A238" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="E238" s="2"/>
+      <c r="F238" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G238" s="2"/>
+      <c r="H238" s="2"/>
+      <c r="I238" s="2"/>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A239" s="2"/>
+      <c r="B239" s="2"/>
+      <c r="C239" s="2"/>
+      <c r="D239" s="2"/>
+      <c r="E239" s="2"/>
+      <c r="F239" s="2"/>
+      <c r="G239" s="2"/>
+      <c r="H239" s="2"/>
+      <c r="I239" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="69">
-    <mergeCell ref="E233:F233"/>
-    <mergeCell ref="E234:F234"/>
-    <mergeCell ref="E236:F236"/>
-    <mergeCell ref="E237:F237"/>
-    <mergeCell ref="E224:F224"/>
-    <mergeCell ref="E229:F229"/>
-    <mergeCell ref="E230:F230"/>
-    <mergeCell ref="E231:F231"/>
-    <mergeCell ref="E232:F232"/>
-    <mergeCell ref="E218:F218"/>
-    <mergeCell ref="E219:F219"/>
-    <mergeCell ref="E220:F220"/>
-    <mergeCell ref="E221:F221"/>
-    <mergeCell ref="E222:F222"/>
-    <mergeCell ref="E223:F223"/>
-    <mergeCell ref="E212:F212"/>
-    <mergeCell ref="E213:F213"/>
-    <mergeCell ref="E214:F214"/>
-    <mergeCell ref="E215:F215"/>
-    <mergeCell ref="E216:F216"/>
-    <mergeCell ref="E217:F217"/>
-    <mergeCell ref="E206:F206"/>
-    <mergeCell ref="E207:F207"/>
-    <mergeCell ref="E208:F208"/>
-    <mergeCell ref="E209:F209"/>
-    <mergeCell ref="E210:F210"/>
-    <mergeCell ref="E211:F211"/>
-    <mergeCell ref="E200:F200"/>
-    <mergeCell ref="E201:F201"/>
-    <mergeCell ref="E202:F202"/>
-    <mergeCell ref="E203:F203"/>
-    <mergeCell ref="E204:F204"/>
-    <mergeCell ref="E205:F205"/>
-    <mergeCell ref="E190:F190"/>
-    <mergeCell ref="E191:F191"/>
-    <mergeCell ref="E192:F192"/>
-    <mergeCell ref="E193:F193"/>
-    <mergeCell ref="E194:F194"/>
-    <mergeCell ref="E195:F195"/>
-    <mergeCell ref="E184:F184"/>
-    <mergeCell ref="E185:F185"/>
-    <mergeCell ref="E186:F186"/>
-    <mergeCell ref="E187:F187"/>
-    <mergeCell ref="E188:F188"/>
-    <mergeCell ref="E189:F189"/>
-    <mergeCell ref="E178:F178"/>
-    <mergeCell ref="E179:F179"/>
-    <mergeCell ref="E180:F180"/>
-    <mergeCell ref="E181:F181"/>
-    <mergeCell ref="E182:F182"/>
-    <mergeCell ref="E183:F183"/>
-    <mergeCell ref="E172:F172"/>
-    <mergeCell ref="E173:F173"/>
-    <mergeCell ref="E174:F174"/>
-    <mergeCell ref="E175:F175"/>
-    <mergeCell ref="E176:F176"/>
-    <mergeCell ref="E177:F177"/>
-    <mergeCell ref="E82:F82"/>
-    <mergeCell ref="E113:F113"/>
-    <mergeCell ref="E114:F114"/>
-    <mergeCell ref="E115:F115"/>
-    <mergeCell ref="E170:F170"/>
-    <mergeCell ref="E171:F171"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="E65:F65"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G8" r:id="rId1" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u72eLYAQ/view" xr:uid="{D3441ED5-BCF2-844F-844E-86893A853D5C}"/>
-    <hyperlink ref="H15" r:id="rId2" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000rvp8wYAA/view" xr:uid="{1E34D697-A595-AC4C-9A12-D9EAC9831E5F}"/>
-    <hyperlink ref="F16" r:id="rId3" xr:uid="{4C7F8145-BD86-B94C-A5FA-944B0846E8EC}"/>
-    <hyperlink ref="F39" r:id="rId4" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000Q2enCYAR/view" xr:uid="{7B193E22-F2F4-984F-9FE8-B637E37CE128}"/>
-    <hyperlink ref="F43" r:id="rId5" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000u9QkgYAE/view" xr:uid="{57433578-9471-5240-8562-63DE207C1E3B}"/>
-    <hyperlink ref="F73" r:id="rId6" xr:uid="{7C9DDC73-3AA5-7840-B37F-5DACA8C6087B}"/>
-    <hyperlink ref="F74" r:id="rId7" xr:uid="{D6A64E6C-55F2-AD41-999A-7DFE92034190}"/>
-    <hyperlink ref="F81" r:id="rId8" xr:uid="{FFDE54F5-ABD6-0C47-A626-F828F6AAE386}"/>
-    <hyperlink ref="F83" r:id="rId9" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{E5B8BE52-B838-0241-BA3E-2B16297615E5}"/>
-    <hyperlink ref="F85" r:id="rId10" xr:uid="{55E1EBE6-8BF8-914F-9328-5636698C019E}"/>
-    <hyperlink ref="F86" r:id="rId11" xr:uid="{265765DB-81CB-3844-AEEE-52154148A425}"/>
-    <hyperlink ref="F87" r:id="rId12" xr:uid="{83FB02AE-A5BD-5841-A0E8-E938C6A8F6B2}"/>
-    <hyperlink ref="F90" r:id="rId13" xr:uid="{DC02162B-37B2-F142-AE3E-9DBF69E2C840}"/>
-    <hyperlink ref="F91" r:id="rId14" xr:uid="{F45AE381-6913-8647-A3EB-D640115FA0D0}"/>
-    <hyperlink ref="F92" r:id="rId15" xr:uid="{78A743F6-7DA6-374C-A3EB-0EF27193E538}"/>
-    <hyperlink ref="F93" r:id="rId16" xr:uid="{82FA811E-605E-6148-97C1-96CFDA2A27A6}"/>
-    <hyperlink ref="F95" r:id="rId17" xr:uid="{B0C9954D-D6CB-6944-80C5-5E6A9C473B3B}"/>
-    <hyperlink ref="F96" r:id="rId18" xr:uid="{48E3A21D-CC84-8E40-BE0E-B871EC7D0496}"/>
-    <hyperlink ref="F97" r:id="rId19" xr:uid="{FAE882D7-FD54-D246-8E0D-42F215667125}"/>
-    <hyperlink ref="F98" r:id="rId20" xr:uid="{D8287F0E-E866-AA4F-A597-0FBAFAF94B08}"/>
-    <hyperlink ref="F99" r:id="rId21" xr:uid="{DE997DA4-3140-3949-A78F-5763EDFF052D}"/>
-    <hyperlink ref="F102" r:id="rId22" xr:uid="{2C08F2C7-B056-1D4E-95A8-D0CC52D64EDD}"/>
-    <hyperlink ref="F103" r:id="rId23" xr:uid="{5CE9DD97-A1AB-A94D-AD38-F4167F06A003}"/>
-    <hyperlink ref="F104" r:id="rId24" xr:uid="{D2224D19-7CA4-9A46-9668-3D24CAB8DDAA}"/>
-    <hyperlink ref="F105" r:id="rId25" xr:uid="{4889BB5A-EC6B-454B-9FA2-186C9C82876F}"/>
-    <hyperlink ref="F106" r:id="rId26" xr:uid="{500B64BE-B459-8045-A6A9-6963AE8340A5}"/>
-    <hyperlink ref="F107" r:id="rId27" xr:uid="{2F0FEEE1-0CA2-1547-95A9-538AA7F71601}"/>
-    <hyperlink ref="F116" r:id="rId28" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uXDB9YAO/view" xr:uid="{6773B690-35FE-0644-A201-5BEC863AB1EC}"/>
-    <hyperlink ref="F119" r:id="rId29" xr:uid="{C65A2F58-EDD5-774E-91DE-E2B56567127D}"/>
-    <hyperlink ref="F120" r:id="rId30" xr:uid="{6F74A9E0-3854-FA45-BBA2-FD514CA1DC21}"/>
-    <hyperlink ref="F121" r:id="rId31" xr:uid="{7C198BF8-6FC7-364C-9FF4-D292A5671756}"/>
-    <hyperlink ref="F122" r:id="rId32" xr:uid="{1A824135-D09B-524B-9E5B-A777931E5A2D}"/>
-    <hyperlink ref="F123" r:id="rId33" xr:uid="{3ED28AFE-2E26-E845-9067-91A449261D67}"/>
-    <hyperlink ref="F124" r:id="rId34" xr:uid="{973DD18F-59D6-E249-B4C0-80B079103823}"/>
-    <hyperlink ref="F125" r:id="rId35" xr:uid="{B9F6918B-2CFA-8441-AAF3-A7CC7DEDB441}"/>
-    <hyperlink ref="F126" r:id="rId36" xr:uid="{FF6A4EE7-E184-D949-9FE9-17792665426F}"/>
-    <hyperlink ref="F133" r:id="rId37" xr:uid="{D57FECAA-9276-3643-B005-F7AB7BAB1E99}"/>
-    <hyperlink ref="F145" r:id="rId38" xr:uid="{2FAD485E-19C9-A240-89F9-4AA97C4B56E6}"/>
-    <hyperlink ref="F146" r:id="rId39" xr:uid="{58A034F0-66F9-C34F-8327-A5256B68EEFF}"/>
-    <hyperlink ref="F147" r:id="rId40" xr:uid="{6BECD366-6F41-FA41-9B82-6F68ED2AD1DF}"/>
-    <hyperlink ref="F148" r:id="rId41" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000s98yXYAQ/view" xr:uid="{B9CFCA7A-67CE-FC4F-80FD-A1FFB430048F}"/>
-    <hyperlink ref="G149" r:id="rId42" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vDa6VYAS/view" xr:uid="{B2B64DA8-BAA5-A548-A3B0-99C2B2703DA0}"/>
-    <hyperlink ref="F150" r:id="rId43" xr:uid="{157D611B-BA15-E641-97F8-D9607805F67E}"/>
-    <hyperlink ref="F151" r:id="rId44" xr:uid="{E4DC1C5A-7194-5B49-90F8-85FA0726EC39}"/>
-    <hyperlink ref="F152" r:id="rId45" xr:uid="{9F08D383-F79A-8744-AC72-AF6DAD84A62E}"/>
-    <hyperlink ref="F153" r:id="rId46" xr:uid="{F3C90E3A-E7B8-A240-8CC7-C16AAA6567C0}"/>
-    <hyperlink ref="F154" r:id="rId47" xr:uid="{3F544506-DDE9-D24A-937B-A348194494D4}"/>
-    <hyperlink ref="F155" r:id="rId48" xr:uid="{B76A963C-E273-754E-8562-CEC32804C7F6}"/>
-    <hyperlink ref="F156" r:id="rId49" xr:uid="{46B7F455-3F2E-BF40-9AF7-7633BAC81EF0}"/>
-    <hyperlink ref="F157" r:id="rId50" xr:uid="{FC627278-EFE9-C340-AB30-E920B3195A28}"/>
-    <hyperlink ref="F158" r:id="rId51" xr:uid="{5EDE7466-8391-5C47-ACCD-F7033B0346E9}"/>
-    <hyperlink ref="F159" r:id="rId52" xr:uid="{E2096B9B-D633-7745-94B1-2F158CACC3FA}"/>
-    <hyperlink ref="F160" r:id="rId53" xr:uid="{98A67CA7-2172-8940-93F8-84D96DE10C5A}"/>
-    <hyperlink ref="F164" r:id="rId54" xr:uid="{B5989662-DD64-4943-A176-C4A9D7C3DA94}"/>
-    <hyperlink ref="F165" r:id="rId55" xr:uid="{879F7869-B8FB-CC41-8C58-B2C8950D048B}"/>
-    <hyperlink ref="F167" r:id="rId56" xr:uid="{FC337A7E-A49F-7543-9281-827FE6AAAC37}"/>
-    <hyperlink ref="G167" r:id="rId57" xr:uid="{21176141-BD70-BE4E-AD28-6FC000AAE738}"/>
-    <hyperlink ref="H167" r:id="rId58" xr:uid="{30A15A8D-7AA1-9747-B49C-9DB4E573264D}"/>
-    <hyperlink ref="I167" r:id="rId59" xr:uid="{1A9CBB84-CF6A-994A-9A2C-90A122995B7F}"/>
-    <hyperlink ref="G168" r:id="rId60" xr:uid="{A591C193-E171-1E4B-8246-C7E765F50660}"/>
-    <hyperlink ref="F199" r:id="rId61" xr:uid="{A5D4F92F-7A8B-E449-A2D2-4CBE608B1FC8}"/>
-    <hyperlink ref="G199" r:id="rId62" xr:uid="{D802EF13-355D-CC4E-AEE8-EE367A33FFDA}"/>
-    <hyperlink ref="H199" r:id="rId63" xr:uid="{262FD7D7-F22C-B542-BF7D-217E9F23203B}"/>
-    <hyperlink ref="I199" r:id="rId64" xr:uid="{62EFA2FE-C4BD-C443-8892-0F1AFE28D589}"/>
-    <hyperlink ref="F225" r:id="rId65" xr:uid="{70B86A88-F489-9E44-B5E9-278B6BBE2C9F}"/>
-    <hyperlink ref="F226" r:id="rId66" xr:uid="{91FB41BF-FB7F-4C4B-84BB-ECE1BFAAABFC}"/>
-    <hyperlink ref="F227" r:id="rId67" display="https://curebound.lightning.force.com/lightning/r/Account/0014W00002W8eYDQAZ/view" xr:uid="{94B6116C-2E97-5944-9405-63AFC44D7284}"/>
-    <hyperlink ref="F228" r:id="rId68" xr:uid="{AF6DB760-2F55-8F4D-B80D-03159B2D6CB0}"/>
-    <hyperlink ref="F235" r:id="rId69" xr:uid="{41F1C20C-DD22-C34C-AF57-5509D2AE290F}"/>
+    <hyperlink ref="G8" r:id="rId1" xr:uid="{94AD40EF-9540-ED45-A6C6-8E5DC035795D}"/>
+    <hyperlink ref="H15" r:id="rId2" xr:uid="{ACD433A6-4234-BC44-BD87-13DD6682F41B}"/>
+    <hyperlink ref="F16" r:id="rId3" xr:uid="{4A378492-8636-C946-BE37-F0EE6AB59933}"/>
+    <hyperlink ref="F39" r:id="rId4" xr:uid="{02B130CF-5F04-8F4C-B5D9-AB1A4C1785BE}"/>
+    <hyperlink ref="F43" r:id="rId5" xr:uid="{93586513-8B24-6549-AAEA-8ABBF32F95FB}"/>
+    <hyperlink ref="F73" r:id="rId6" xr:uid="{D9BCCCA2-915D-E24E-8666-6BB444AA4781}"/>
+    <hyperlink ref="F74" r:id="rId7" xr:uid="{4B618E87-52DD-A546-900F-B5D16BB2FC53}"/>
+    <hyperlink ref="F81" r:id="rId8" xr:uid="{A090C2BF-F5FD-2647-8D46-BFDB614472C0}"/>
+    <hyperlink ref="F83" r:id="rId9" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{8036DC3B-3948-1848-8765-8C3109BBC2AB}"/>
+    <hyperlink ref="F85" r:id="rId10" xr:uid="{96A36E13-FE0D-4745-9F90-E435AAADD5D7}"/>
+    <hyperlink ref="F86" r:id="rId11" xr:uid="{35199DB8-0551-F349-8BCC-479B5F5D689C}"/>
+    <hyperlink ref="F87" r:id="rId12" xr:uid="{5BE3FC93-5505-DB43-A96C-65BF0C36A0EB}"/>
+    <hyperlink ref="F90" r:id="rId13" xr:uid="{2CD2F937-4BCD-D44C-8E2D-407033F4984C}"/>
+    <hyperlink ref="F91" r:id="rId14" xr:uid="{5356F0C7-54EA-C84A-94CE-9DF3DC723DE5}"/>
+    <hyperlink ref="F92" r:id="rId15" xr:uid="{48A472F0-E433-544E-8EA7-0BE255DF92F1}"/>
+    <hyperlink ref="F93" r:id="rId16" xr:uid="{44F44A01-DCE9-F345-AC4D-4D9390900CF6}"/>
+    <hyperlink ref="F95" r:id="rId17" xr:uid="{95CF1CAA-F28A-A848-82C4-2C0AF9915C3C}"/>
+    <hyperlink ref="F96" r:id="rId18" xr:uid="{151DBD30-3F92-464A-9FB9-636E8ACD6053}"/>
+    <hyperlink ref="F97" r:id="rId19" xr:uid="{B6C1817D-3637-CB46-8479-9A2C2E901FC8}"/>
+    <hyperlink ref="F98" r:id="rId20" xr:uid="{B2121D7A-5B34-6F4D-914E-A47493750366}"/>
+    <hyperlink ref="F99" r:id="rId21" xr:uid="{78761F2C-7E06-BF45-A9F1-6CE5B29979BD}"/>
+    <hyperlink ref="F102" r:id="rId22" xr:uid="{B59B3BCB-7CCA-0340-A727-D929838226AC}"/>
+    <hyperlink ref="F103" r:id="rId23" xr:uid="{85CFED38-4585-6542-91AF-8E5B975F8988}"/>
+    <hyperlink ref="F104" r:id="rId24" xr:uid="{6FD2373B-FBFF-8447-8DDD-457CE0741412}"/>
+    <hyperlink ref="F105" r:id="rId25" xr:uid="{CAB19658-2A90-844C-BA8B-194C30F745F8}"/>
+    <hyperlink ref="F106" r:id="rId26" xr:uid="{21B39643-AD6F-1B4D-A596-D7ED67BFDF48}"/>
+    <hyperlink ref="F107" r:id="rId27" xr:uid="{DE8274A8-9FA1-2C41-BDC7-E2B730893E58}"/>
+    <hyperlink ref="F116" r:id="rId28" xr:uid="{FE47D459-CAF8-3B4D-B664-B3843E23FF69}"/>
+    <hyperlink ref="F119" r:id="rId29" xr:uid="{28C58097-53E2-434C-8AA9-295D877D0F14}"/>
+    <hyperlink ref="F120" r:id="rId30" xr:uid="{225CDD90-10C3-3E46-A300-C59F5D708B82}"/>
+    <hyperlink ref="F121" r:id="rId31" xr:uid="{B396FF89-CBD8-F445-94DF-4D7057E90EF2}"/>
+    <hyperlink ref="F122" r:id="rId32" xr:uid="{5CD477E5-22F9-4547-A2A6-BB3D9116AB74}"/>
+    <hyperlink ref="F123" r:id="rId33" xr:uid="{6845C127-9A1C-B54A-B329-64800FD34E80}"/>
+    <hyperlink ref="F124" r:id="rId34" xr:uid="{B521712B-00C3-514F-9660-CCFCDA06DF53}"/>
+    <hyperlink ref="F125" r:id="rId35" xr:uid="{B6D49427-2E82-294F-B771-7306FB2F2F21}"/>
+    <hyperlink ref="F126" r:id="rId36" xr:uid="{F4C8F2B0-49DF-B540-9A28-10AA14EE46F8}"/>
+    <hyperlink ref="F133" r:id="rId37" xr:uid="{B48D4B4C-DE7A-DC4E-9F1C-49AB272959C7}"/>
+    <hyperlink ref="F145" r:id="rId38" xr:uid="{8A7D450D-33F3-3F4E-899E-3ED48BC7AAA2}"/>
+    <hyperlink ref="F146" r:id="rId39" xr:uid="{BC605A5D-FFA8-C043-996E-6C0583EB1CA3}"/>
+    <hyperlink ref="F147" r:id="rId40" xr:uid="{99D06EE2-0038-7B44-A45C-89DB27AE7F72}"/>
+    <hyperlink ref="G148" r:id="rId41" xr:uid="{9E3C1D4F-C2E8-C34D-8DFF-68600F21E664}"/>
+    <hyperlink ref="F149" r:id="rId42" xr:uid="{510DC778-7054-4148-8CBD-8BF7AEF38939}"/>
+    <hyperlink ref="F150" r:id="rId43" xr:uid="{318D2D62-8A82-7C44-ACA3-87AAB7208C70}"/>
+    <hyperlink ref="F151" r:id="rId44" xr:uid="{279CBC26-C674-8347-8859-024A9292328A}"/>
+    <hyperlink ref="F152" r:id="rId45" xr:uid="{660551C1-24FD-1245-BA1A-B6CFCA972166}"/>
+    <hyperlink ref="F153" r:id="rId46" xr:uid="{301416E6-CC87-6244-8127-6FEBAAF2F29B}"/>
+    <hyperlink ref="F154" r:id="rId47" xr:uid="{7A3AFC16-93F3-5140-9110-D1D572E40D7F}"/>
+    <hyperlink ref="F155" r:id="rId48" xr:uid="{1A32FC08-A520-7E4B-B25C-202C7FC38E90}"/>
+    <hyperlink ref="F156" r:id="rId49" xr:uid="{BD136DFB-53A7-2947-8E78-ACC2C5B3C27F}"/>
+    <hyperlink ref="F157" r:id="rId50" xr:uid="{D5ABAE57-E5A3-7C41-B9AC-D661299E7A8A}"/>
+    <hyperlink ref="F158" r:id="rId51" xr:uid="{4C3AB3C6-21E9-4F4B-9491-08001C0AD2C8}"/>
+    <hyperlink ref="F159" r:id="rId52" xr:uid="{BDB034D0-D2D3-C445-B552-49467B5BCE83}"/>
+    <hyperlink ref="F163" r:id="rId53" xr:uid="{0E20FDF3-E8F0-7941-B7BC-6AE9F1DEC256}"/>
+    <hyperlink ref="F164" r:id="rId54" xr:uid="{8BFD11A0-87C9-A54B-B2BE-6BD93F1DBA30}"/>
+    <hyperlink ref="F166" r:id="rId55" xr:uid="{5776A445-E2BE-3E4A-9499-8240F0CBFFA4}"/>
+    <hyperlink ref="G166" r:id="rId56" xr:uid="{F7182AD7-9FF0-0A48-959F-5E0E2CB30FE5}"/>
+    <hyperlink ref="H166" r:id="rId57" xr:uid="{B4BA0651-042C-724B-B4D0-192C765F51E1}"/>
+    <hyperlink ref="I166" r:id="rId58" xr:uid="{99A49A4D-A255-E848-8646-693CDFFB12F8}"/>
+    <hyperlink ref="G167" r:id="rId59" xr:uid="{4F670899-7BFE-6D40-83EA-4265C3960161}"/>
+    <hyperlink ref="F198" r:id="rId60" xr:uid="{580580A4-0A61-FF42-920D-1E09EFE7D876}"/>
+    <hyperlink ref="G198" r:id="rId61" xr:uid="{241B62FF-EE0E-5E46-A73C-671431B1B6EE}"/>
+    <hyperlink ref="H198" r:id="rId62" xr:uid="{DB071AF4-751A-9E47-84A0-69C407496D3F}"/>
+    <hyperlink ref="I198" r:id="rId63" xr:uid="{B86715D2-6F5F-E44F-B6AE-26E9D5009DCF}"/>
+    <hyperlink ref="F224" r:id="rId64" xr:uid="{FFD16E37-16EE-DC46-AFC2-E3C270C29A53}"/>
+    <hyperlink ref="F225" r:id="rId65" xr:uid="{B37E013A-F9C9-7844-AE37-91653867C57F}"/>
+    <hyperlink ref="F226" r:id="rId66" xr:uid="{2FF5DD5C-DBA2-DA45-9263-D839D4ED41BE}"/>
+    <hyperlink ref="F227" r:id="rId67" xr:uid="{6A8BAC88-17B8-684D-B266-9CC0CA5067DC}"/>
+    <hyperlink ref="F233" r:id="rId68" xr:uid="{E7B9314A-EB55-BA48-AF70-18CC16F1DB52}"/>
+    <hyperlink ref="F236" r:id="rId69" xr:uid="{A0062744-9716-6845-85A6-8DC252A5EB64}"/>
+    <hyperlink ref="F238" r:id="rId70" xr:uid="{B614A598-E6A8-A74F-A481-A0CE0952B109}"/>
   </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FD4C2A1-B27E-E843-AC87-689F52865EF9}">
   <dimension ref="A1:B348"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -8703,7 +8696,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
@@ -8751,42 +8744,42 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B7" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B8" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B9" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>644</v>
+      </c>
+      <c r="B10" t="s">
         <v>645</v>
-      </c>
-      <c r="B10" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>640</v>
+      </c>
+      <c r="B11" t="s">
         <v>641</v>
-      </c>
-      <c r="B11" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -8807,10 +8800,10 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B14" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -8975,10 +8968,10 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B35" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
@@ -9015,10 +9008,10 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B40" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
@@ -9039,10 +9032,10 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B43" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
@@ -9055,154 +9048,154 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B45" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B46" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>169</v>
+      </c>
+      <c r="B47" t="s">
         <v>170</v>
-      </c>
-      <c r="B47" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>172</v>
+      </c>
+      <c r="B48" t="s">
         <v>173</v>
-      </c>
-      <c r="B48" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>175</v>
+      </c>
+      <c r="B49" t="s">
         <v>176</v>
-      </c>
-      <c r="B49" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>183</v>
+      </c>
+      <c r="B50" t="s">
         <v>184</v>
-      </c>
-      <c r="B50" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>179</v>
+      </c>
+      <c r="B51" t="s">
         <v>180</v>
-      </c>
-      <c r="B51" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>232</v>
+      </c>
+      <c r="B52" t="s">
         <v>233</v>
-      </c>
-      <c r="B52" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>191</v>
+      </c>
+      <c r="B53" t="s">
         <v>192</v>
-      </c>
-      <c r="B53" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>245</v>
+      </c>
+      <c r="B54" t="s">
         <v>246</v>
-      </c>
-      <c r="B54" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>187</v>
+      </c>
+      <c r="B55" t="s">
         <v>188</v>
-      </c>
-      <c r="B55" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
+        <v>195</v>
+      </c>
+      <c r="B56" t="s">
         <v>196</v>
-      </c>
-      <c r="B56" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
+        <v>249</v>
+      </c>
+      <c r="B57" t="s">
         <v>250</v>
-      </c>
-      <c r="B57" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>203</v>
+      </c>
+      <c r="B58" t="s">
         <v>204</v>
-      </c>
-      <c r="B58" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
+        <v>199</v>
+      </c>
+      <c r="B59" t="s">
         <v>200</v>
-      </c>
-      <c r="B59" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>208</v>
+      </c>
+      <c r="B60" t="s">
         <v>209</v>
-      </c>
-      <c r="B60" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B61" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
+        <v>216</v>
+      </c>
+      <c r="B62" t="s">
         <v>217</v>
-      </c>
-      <c r="B62" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>165</v>
+      </c>
+      <c r="B63" t="s">
         <v>166</v>
-      </c>
-      <c r="B63" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
@@ -9215,50 +9208,50 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
+        <v>160</v>
+      </c>
+      <c r="B65" t="s">
         <v>161</v>
-      </c>
-      <c r="B65" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B66" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B67" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
+        <v>255</v>
+      </c>
+      <c r="B68" t="s">
         <v>256</v>
-      </c>
-      <c r="B68" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B69" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
+        <v>242</v>
+      </c>
+      <c r="B70" t="s">
         <v>243</v>
-      </c>
-      <c r="B70" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
@@ -9271,10 +9264,10 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
+        <v>162</v>
+      </c>
+      <c r="B72" t="s">
         <v>163</v>
-      </c>
-      <c r="B72" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
@@ -9287,42 +9280,42 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B74" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
+        <v>236</v>
+      </c>
+      <c r="B75" t="s">
         <v>237</v>
-      </c>
-      <c r="B75" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B76" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B77" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
+        <v>239</v>
+      </c>
+      <c r="B78" t="s">
         <v>240</v>
-      </c>
-      <c r="B78" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
@@ -9335,2148 +9328,2148 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B80" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
+        <v>157</v>
+      </c>
+      <c r="B81" t="s">
         <v>158</v>
-      </c>
-      <c r="B81" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B82" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
+        <v>252</v>
+      </c>
+      <c r="B83" t="s">
         <v>253</v>
-      </c>
-      <c r="B83" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
+        <v>224</v>
+      </c>
+      <c r="B84" t="s">
         <v>225</v>
-      </c>
-      <c r="B84" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B85" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B86" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B87" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B88" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B89" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B90" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B91" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B92" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B93" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B95" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B96" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B97" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B98" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B99" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B100" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B101" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B102" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B103" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B104" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B105" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B106" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B107" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B108" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B109" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B110" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
+        <v>212</v>
+      </c>
+      <c r="B111" t="s">
         <v>213</v>
-      </c>
-      <c r="B111" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B112" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B113" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B114" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B115" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B116" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B117" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B118" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
+        <v>228</v>
+      </c>
+      <c r="B119" t="s">
         <v>229</v>
-      </c>
-      <c r="B119" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B120" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B121" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B122" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B123" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B124" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B125" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B126" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B127" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
+        <v>283</v>
+      </c>
+      <c r="B128" t="s">
         <v>284</v>
-      </c>
-      <c r="B128" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B129" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B130" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B131" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B132" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B133" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B134" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B135" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B136" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B137" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
+        <v>258</v>
+      </c>
+      <c r="B138" t="s">
         <v>259</v>
-      </c>
-      <c r="B138" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B139" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
+        <v>303</v>
+      </c>
+      <c r="B140" t="s">
         <v>304</v>
-      </c>
-      <c r="B140" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B141" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B142" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B143" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B144" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B145" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B146" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B147" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
+        <v>261</v>
+      </c>
+      <c r="B148" t="s">
         <v>262</v>
-      </c>
-      <c r="B148" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
+        <v>300</v>
+      </c>
+      <c r="B149" t="s">
         <v>301</v>
-      </c>
-      <c r="B149" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
+        <v>296</v>
+      </c>
+      <c r="B150" t="s">
         <v>297</v>
-      </c>
-      <c r="B150" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B151" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B152" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B153" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B154" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B155" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B156" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
+        <v>273</v>
+      </c>
+      <c r="B157" t="s">
         <v>274</v>
-      </c>
-      <c r="B157" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
+        <v>265</v>
+      </c>
+      <c r="B158" t="s">
         <v>266</v>
-      </c>
-      <c r="B158" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
+        <v>319</v>
+      </c>
+      <c r="B159" t="s">
         <v>320</v>
-      </c>
-      <c r="B159" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
+        <v>292</v>
+      </c>
+      <c r="B160" t="s">
         <v>293</v>
-      </c>
-      <c r="B160" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
+        <v>329</v>
+      </c>
+      <c r="B161" t="s">
         <v>330</v>
-      </c>
-      <c r="B161" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
+        <v>361</v>
+      </c>
+      <c r="B162" t="s">
         <v>362</v>
-      </c>
-      <c r="B162" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B163" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
+        <v>382</v>
+      </c>
+      <c r="B164" t="s">
         <v>383</v>
-      </c>
-      <c r="B164" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B165" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
+        <v>351</v>
+      </c>
+      <c r="B166" t="s">
         <v>352</v>
-      </c>
-      <c r="B166" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
+        <v>277</v>
+      </c>
+      <c r="B167" t="s">
         <v>278</v>
-      </c>
-      <c r="B167" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
+        <v>648</v>
+      </c>
+      <c r="B168" t="s">
         <v>649</v>
-      </c>
-      <c r="B168" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
+        <v>322</v>
+      </c>
+      <c r="B169" t="s">
         <v>323</v>
-      </c>
-      <c r="B169" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
+        <v>287</v>
+      </c>
+      <c r="B170" t="s">
         <v>288</v>
-      </c>
-      <c r="B170" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B171" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
+        <v>312</v>
+      </c>
+      <c r="B172" t="s">
         <v>313</v>
-      </c>
-      <c r="B172" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B173" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
+        <v>379</v>
+      </c>
+      <c r="B174" t="s">
         <v>380</v>
-      </c>
-      <c r="B174" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
+        <v>637</v>
+      </c>
+      <c r="B175" t="s">
         <v>638</v>
-      </c>
-      <c r="B175" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
+        <v>220</v>
+      </c>
+      <c r="B176" t="s">
         <v>221</v>
-      </c>
-      <c r="B176" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
+        <v>280</v>
+      </c>
+      <c r="B177" t="s">
         <v>281</v>
-      </c>
-      <c r="B177" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B178" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
+        <v>325</v>
+      </c>
+      <c r="B179" t="s">
         <v>326</v>
-      </c>
-      <c r="B179" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
+        <v>333</v>
+      </c>
+      <c r="B180" t="s">
         <v>334</v>
-      </c>
-      <c r="B180" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
+        <v>336</v>
+      </c>
+      <c r="B181" t="s">
         <v>337</v>
-      </c>
-      <c r="B181" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
+        <v>627</v>
+      </c>
+      <c r="B182" t="s">
         <v>628</v>
-      </c>
-      <c r="B182" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
+        <v>341</v>
+      </c>
+      <c r="B183" t="s">
         <v>342</v>
-      </c>
-      <c r="B183" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
+        <v>358</v>
+      </c>
+      <c r="B184" t="s">
         <v>359</v>
-      </c>
-      <c r="B184" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
+        <v>346</v>
+      </c>
+      <c r="B185" t="s">
         <v>347</v>
-      </c>
-      <c r="B185" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
+        <v>356</v>
+      </c>
+      <c r="B186" t="s">
         <v>357</v>
-      </c>
-      <c r="B186" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
+        <v>269</v>
+      </c>
+      <c r="B187" t="s">
         <v>270</v>
-      </c>
-      <c r="B187" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
+        <v>650</v>
+      </c>
+      <c r="B188" t="s">
         <v>651</v>
-      </c>
-      <c r="B188" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
+        <v>309</v>
+      </c>
+      <c r="B189" t="s">
         <v>310</v>
-      </c>
-      <c r="B189" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B190" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
+        <v>339</v>
+      </c>
+      <c r="B191" t="s">
         <v>340</v>
-      </c>
-      <c r="B191" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B192" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
+        <v>344</v>
+      </c>
+      <c r="B193" t="s">
         <v>345</v>
-      </c>
-      <c r="B193" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
+        <v>373</v>
+      </c>
+      <c r="B194" t="s">
         <v>374</v>
-      </c>
-      <c r="B194" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
+        <v>348</v>
+      </c>
+      <c r="B195" t="s">
         <v>349</v>
-      </c>
-      <c r="B195" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
+        <v>376</v>
+      </c>
+      <c r="B196" t="s">
         <v>377</v>
-      </c>
-      <c r="B196" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B197" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B198" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B199" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B200" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B201" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
+        <v>594</v>
+      </c>
+      <c r="B202" t="s">
         <v>595</v>
-      </c>
-      <c r="B202" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B203" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B204" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B205" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B206" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B207" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B208" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
+        <v>316</v>
+      </c>
+      <c r="B209" t="s">
         <v>317</v>
-      </c>
-      <c r="B209" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B210" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
+        <v>365</v>
+      </c>
+      <c r="B211" t="s">
         <v>366</v>
-      </c>
-      <c r="B211" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
+        <v>596</v>
+      </c>
+      <c r="B212" t="s">
         <v>597</v>
-      </c>
-      <c r="B212" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B213" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B214" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B215" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B216" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B217" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B218" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
+        <v>368</v>
+      </c>
+      <c r="B219" t="s">
         <v>369</v>
-      </c>
-      <c r="B219" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B220" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
+        <v>370</v>
+      </c>
+      <c r="B221" t="s">
         <v>371</v>
-      </c>
-      <c r="B221" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B222" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B223" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B224" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B225" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B226" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B228" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
+        <v>642</v>
+      </c>
+      <c r="B229" t="s">
         <v>643</v>
-      </c>
-      <c r="B229" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B230" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
+        <v>306</v>
+      </c>
+      <c r="B231" t="s">
         <v>307</v>
-      </c>
-      <c r="B231" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B232" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B233" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B234" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B235" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B236" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
+        <v>408</v>
+      </c>
+      <c r="B237" t="s">
         <v>409</v>
-      </c>
-      <c r="B237" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
+        <v>391</v>
+      </c>
+      <c r="B238" t="s">
         <v>392</v>
-      </c>
-      <c r="B238" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
+        <v>402</v>
+      </c>
+      <c r="B239" t="s">
         <v>403</v>
-      </c>
-      <c r="B239" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
+        <v>441</v>
+      </c>
+      <c r="B240" t="s">
         <v>442</v>
-      </c>
-      <c r="B240" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B241" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B242" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B243" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B244" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B245" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B246" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
+        <v>385</v>
+      </c>
+      <c r="B247" t="s">
         <v>386</v>
-      </c>
-      <c r="B247" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
+        <v>388</v>
+      </c>
+      <c r="B248" t="s">
         <v>389</v>
-      </c>
-      <c r="B248" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
+        <v>404</v>
+      </c>
+      <c r="B249" t="s">
         <v>405</v>
-      </c>
-      <c r="B249" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
+        <v>397</v>
+      </c>
+      <c r="B250" t="s">
         <v>398</v>
-      </c>
-      <c r="B250" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B251" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B252" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B253" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
+        <v>559</v>
+      </c>
+      <c r="B254" t="s">
         <v>560</v>
-      </c>
-      <c r="B254" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B255" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B256" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B257" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B258" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
+        <v>394</v>
+      </c>
+      <c r="B259" t="s">
         <v>395</v>
-      </c>
-      <c r="B259" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
+        <v>483</v>
+      </c>
+      <c r="B260" t="s">
         <v>484</v>
-      </c>
-      <c r="B260" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
+        <v>406</v>
+      </c>
+      <c r="B261" t="s">
         <v>407</v>
-      </c>
-      <c r="B261" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
+        <v>399</v>
+      </c>
+      <c r="B262" t="s">
         <v>400</v>
-      </c>
-      <c r="B262" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B263" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B264" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B265" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B266" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B267" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B268" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B269" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B270" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
+        <v>414</v>
+      </c>
+      <c r="B271" t="s">
         <v>415</v>
-      </c>
-      <c r="B271" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B272" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
+        <v>475</v>
+      </c>
+      <c r="B273" t="s">
         <v>476</v>
-      </c>
-      <c r="B273" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
+        <v>514</v>
+      </c>
+      <c r="B274" t="s">
         <v>515</v>
-      </c>
-      <c r="B274" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
+        <v>437</v>
+      </c>
+      <c r="B275" t="s">
         <v>438</v>
-      </c>
-      <c r="B275" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
+        <v>422</v>
+      </c>
+      <c r="B276" t="s">
         <v>423</v>
-      </c>
-      <c r="B276" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
+        <v>487</v>
+      </c>
+      <c r="B277" t="s">
         <v>488</v>
-      </c>
-      <c r="B277" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
+        <v>580</v>
+      </c>
+      <c r="B278" t="s">
         <v>581</v>
-      </c>
-      <c r="B278" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
+        <v>511</v>
+      </c>
+      <c r="B279" t="s">
         <v>512</v>
-      </c>
-      <c r="B279" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
+        <v>578</v>
+      </c>
+      <c r="B280" t="s">
         <v>579</v>
-      </c>
-      <c r="B280" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B281" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
+        <v>576</v>
+      </c>
+      <c r="B282" t="s">
         <v>577</v>
-      </c>
-      <c r="B282" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
+        <v>411</v>
+      </c>
+      <c r="B283" t="s">
         <v>412</v>
-      </c>
-      <c r="B283" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B284" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
+        <v>517</v>
+      </c>
+      <c r="B285" t="s">
         <v>518</v>
-      </c>
-      <c r="B285" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B286" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
+        <v>520</v>
+      </c>
+      <c r="B287" t="s">
         <v>521</v>
-      </c>
-      <c r="B287" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B288" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
+        <v>546</v>
+      </c>
+      <c r="B289" t="s">
         <v>547</v>
-      </c>
-      <c r="B289" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
+        <v>418</v>
+      </c>
+      <c r="B290" t="s">
         <v>419</v>
-      </c>
-      <c r="B290" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
+        <v>509</v>
+      </c>
+      <c r="B291" t="s">
         <v>510</v>
-      </c>
-      <c r="B291" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
+        <v>420</v>
+      </c>
+      <c r="B292" t="s">
         <v>421</v>
-      </c>
-      <c r="B292" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="B293" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
+        <v>652</v>
+      </c>
+      <c r="B294" t="s">
         <v>653</v>
-      </c>
-      <c r="B294" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
+        <v>554</v>
+      </c>
+      <c r="B295" t="s">
         <v>555</v>
-      </c>
-      <c r="B295" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
+        <v>494</v>
+      </c>
+      <c r="B296" t="s">
         <v>495</v>
-      </c>
-      <c r="B296" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
+        <v>525</v>
+      </c>
+      <c r="B297" t="s">
         <v>526</v>
-      </c>
-      <c r="B297" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
+        <v>498</v>
+      </c>
+      <c r="B298" t="s">
         <v>499</v>
-      </c>
-      <c r="B298" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
+        <v>522</v>
+      </c>
+      <c r="B299" t="s">
         <v>523</v>
-      </c>
-      <c r="B299" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B300" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
+        <v>534</v>
+      </c>
+      <c r="B301" t="s">
         <v>535</v>
-      </c>
-      <c r="B301" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B302" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
+        <v>542</v>
+      </c>
+      <c r="B303" t="s">
         <v>543</v>
-      </c>
-      <c r="B303" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B304" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B305" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
+        <v>456</v>
+      </c>
+      <c r="B306" t="s">
         <v>457</v>
-      </c>
-      <c r="B306" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
+        <v>556</v>
+      </c>
+      <c r="B307" t="s">
         <v>557</v>
-      </c>
-      <c r="B307" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
+        <v>448</v>
+      </c>
+      <c r="B308" t="s">
         <v>449</v>
-      </c>
-      <c r="B308" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
+        <v>527</v>
+      </c>
+      <c r="B309" t="s">
         <v>528</v>
-      </c>
-      <c r="B309" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
+        <v>444</v>
+      </c>
+      <c r="B310" t="s">
         <v>445</v>
-      </c>
-      <c r="B310" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
+        <v>529</v>
+      </c>
+      <c r="B311" t="s">
         <v>530</v>
-      </c>
-      <c r="B311" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
+        <v>496</v>
+      </c>
+      <c r="B312" t="s">
         <v>497</v>
-      </c>
-      <c r="B312" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
+        <v>536</v>
+      </c>
+      <c r="B313" t="s">
         <v>537</v>
-      </c>
-      <c r="B313" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
+        <v>471</v>
+      </c>
+      <c r="B314" t="s">
         <v>472</v>
-      </c>
-      <c r="B314" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
+        <v>539</v>
+      </c>
+      <c r="B315" t="s">
         <v>540</v>
-      </c>
-      <c r="B315" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B316" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B317" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B318" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
+        <v>550</v>
+      </c>
+      <c r="B319" t="s">
         <v>551</v>
-      </c>
-      <c r="B319" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
+        <v>531</v>
+      </c>
+      <c r="B320" t="s">
         <v>532</v>
-      </c>
-      <c r="B320" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B321" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
+        <v>452</v>
+      </c>
+      <c r="B322" t="s">
         <v>453</v>
-      </c>
-      <c r="B322" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
+        <v>425</v>
+      </c>
+      <c r="B323" t="s">
         <v>426</v>
-      </c>
-      <c r="B323" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B324" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
+        <v>479</v>
+      </c>
+      <c r="B325" t="s">
         <v>480</v>
-      </c>
-      <c r="B325" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
+        <v>582</v>
+      </c>
+      <c r="B326" t="s">
         <v>583</v>
-      </c>
-      <c r="B326" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B327" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
+        <v>491</v>
+      </c>
+      <c r="B328" t="s">
         <v>492</v>
-      </c>
-      <c r="B328" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B329" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B330" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B331" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
+        <v>586</v>
+      </c>
+      <c r="B332" t="s">
         <v>587</v>
-      </c>
-      <c r="B332" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
+        <v>428</v>
+      </c>
+      <c r="B333" t="s">
         <v>429</v>
-      </c>
-      <c r="B333" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
+        <v>501</v>
+      </c>
+      <c r="B334" t="s">
         <v>502</v>
-      </c>
-      <c r="B334" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
+        <v>467</v>
+      </c>
+      <c r="B335" t="s">
         <v>468</v>
-      </c>
-      <c r="B335" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
+        <v>460</v>
+      </c>
+      <c r="B336" t="s">
         <v>461</v>
-      </c>
-      <c r="B336" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B337" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
+        <v>584</v>
+      </c>
+      <c r="B338" t="s">
         <v>585</v>
-      </c>
-      <c r="B338" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
+        <v>434</v>
+      </c>
+      <c r="B339" t="s">
         <v>435</v>
-      </c>
-      <c r="B339" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
+        <v>588</v>
+      </c>
+      <c r="B340" t="s">
         <v>589</v>
-      </c>
-      <c r="B340" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
+        <v>430</v>
+      </c>
+      <c r="B341" t="s">
         <v>431</v>
-      </c>
-      <c r="B341" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
+        <v>504</v>
+      </c>
+      <c r="B342" t="s">
         <v>505</v>
-      </c>
-      <c r="B342" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B343" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
+        <v>463</v>
+      </c>
+      <c r="B344" t="s">
         <v>464</v>
-      </c>
-      <c r="B344" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
+        <v>432</v>
+      </c>
+      <c r="B345" t="s">
         <v>433</v>
-      </c>
-      <c r="B345" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
+        <v>592</v>
+      </c>
+      <c r="B346" t="s">
         <v>593</v>
-      </c>
-      <c r="B346" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
+        <v>506</v>
+      </c>
+      <c r="B347" t="s">
         <v>507</v>
-      </c>
-      <c r="B347" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
+        <v>590</v>
+      </c>
+      <c r="B348" t="s">
         <v>591</v>
-      </c>
-      <c r="B348" t="s">
-        <v>592</v>
       </c>
     </row>
   </sheetData>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AA2076F-FB4C-7144-9437-8FDA4F6FFECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA08DD43-E75C-AC43-ADD8-A06CC9F5DBF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3980" yWindow="1480" windowWidth="29160" windowHeight="20060" activeTab="1" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="33380" windowHeight="21580" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
   <sheets>
     <sheet name="xlsx" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1858" uniqueCount="1058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3022" uniqueCount="1058">
   <si>
     <t>Household Name</t>
   </si>
@@ -3632,10 +3632,5048 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7894B4-148E-174D-AE8B-E6DE441B89B0}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:I239"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="4" width="10.83203125"/>
+    <col min="5" max="5" width="66.1640625" customWidth="1"/>
+    <col min="6" max="6" width="87.6640625" customWidth="1"/>
+    <col min="7" max="7" width="75.1640625" customWidth="1"/>
+    <col min="8" max="8" width="42.33203125" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A70" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A71" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A75" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A76" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A77" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A78" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A79" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A80" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A81" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A82" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A83" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A84" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A85" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A86" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A87" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A88" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A89" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A90" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A91" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A92" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A93" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A94" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A95" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A96" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A97" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A98" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A99" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A100" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A101" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A102" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A103" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+      <c r="I103" s="2"/>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A104" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A105" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+      <c r="I105" s="2"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A106" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+      <c r="I106" s="2"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A107" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
+      <c r="I107" s="2"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A108" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2"/>
+      <c r="I108" s="2"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A109" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2"/>
+      <c r="I109" s="2"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A110" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
+      <c r="I110" s="2"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A111" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="G111" s="2"/>
+      <c r="H111" s="2"/>
+      <c r="I111" s="2"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A112" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="G112" s="2"/>
+      <c r="H112" s="2"/>
+      <c r="I112" s="2"/>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A113" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" s="2"/>
+      <c r="G113" s="2"/>
+      <c r="H113" s="2"/>
+      <c r="I113" s="2"/>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A114" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="2"/>
+      <c r="H114" s="2"/>
+      <c r="I114" s="2"/>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A115" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
+      <c r="G115" s="2"/>
+      <c r="H115" s="2"/>
+      <c r="I115" s="2"/>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A116" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G116" s="2"/>
+      <c r="H116" s="2"/>
+      <c r="I116" s="2"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A117" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="G117" s="2"/>
+      <c r="H117" s="2"/>
+      <c r="I117" s="2"/>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A118" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="G118" s="2"/>
+      <c r="H118" s="2"/>
+      <c r="I118" s="2"/>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A119" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="G119" s="2"/>
+      <c r="H119" s="2"/>
+      <c r="I119" s="2"/>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A120" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="G120" s="2"/>
+      <c r="H120" s="2"/>
+      <c r="I120" s="2"/>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A121" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="G121" s="2"/>
+      <c r="H121" s="2"/>
+      <c r="I121" s="2"/>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A122" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="G122" s="2"/>
+      <c r="H122" s="2"/>
+      <c r="I122" s="2"/>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A123" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G123" s="2"/>
+      <c r="H123" s="2"/>
+      <c r="I123" s="2"/>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A124" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G124" s="2"/>
+      <c r="H124" s="2"/>
+      <c r="I124" s="2"/>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A125" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G125" s="2"/>
+      <c r="H125" s="2"/>
+      <c r="I125" s="2"/>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A126" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G126" s="2"/>
+      <c r="H126" s="2"/>
+      <c r="I126" s="2"/>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A127" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="G127" s="2"/>
+      <c r="H127" s="2"/>
+      <c r="I127" s="2"/>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A128" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="G128" s="2"/>
+      <c r="H128" s="2"/>
+      <c r="I128" s="2"/>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A129" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="G129" s="2"/>
+      <c r="H129" s="2"/>
+      <c r="I129" s="2"/>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A130" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="G130" s="2"/>
+      <c r="H130" s="2"/>
+      <c r="I130" s="2"/>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A131" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="G131" s="2"/>
+      <c r="H131" s="2"/>
+      <c r="I131" s="2"/>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A132" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="G132" s="2"/>
+      <c r="H132" s="2"/>
+      <c r="I132" s="2"/>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A133" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="G133" s="2"/>
+      <c r="H133" s="2"/>
+      <c r="I133" s="2"/>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A134" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="G134" s="2"/>
+      <c r="H134" s="2"/>
+      <c r="I134" s="2"/>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A135" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="G135" s="2"/>
+      <c r="H135" s="2"/>
+      <c r="I135" s="2"/>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A136" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="G136" s="2"/>
+      <c r="H136" s="2"/>
+      <c r="I136" s="2"/>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A137" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="G137" s="2"/>
+      <c r="H137" s="2"/>
+      <c r="I137" s="2"/>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A138" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="G138" s="2"/>
+      <c r="H138" s="2"/>
+      <c r="I138" s="2"/>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A139" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="G139" s="2"/>
+      <c r="H139" s="2"/>
+      <c r="I139" s="2"/>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A140" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="G140" s="2"/>
+      <c r="H140" s="2"/>
+      <c r="I140" s="2"/>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A141" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="G141" s="2"/>
+      <c r="H141" s="2"/>
+      <c r="I141" s="2"/>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A142" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="G142" s="2"/>
+      <c r="H142" s="2"/>
+      <c r="I142" s="2"/>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A143" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E143" s="2"/>
+      <c r="F143" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="G143" s="2"/>
+      <c r="H143" s="2"/>
+      <c r="I143" s="2"/>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A144" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="G144" s="2"/>
+      <c r="H144" s="2"/>
+      <c r="I144" s="2"/>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A145" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="G145" s="2"/>
+      <c r="H145" s="2"/>
+      <c r="I145" s="2"/>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A146" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G146" s="2"/>
+      <c r="H146" s="2"/>
+      <c r="I146" s="2"/>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A147" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G147" s="2"/>
+      <c r="H147" s="2"/>
+      <c r="I147" s="2"/>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A148" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E148" s="2"/>
+      <c r="F148" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="H148" s="2"/>
+      <c r="I148" s="2"/>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A149" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E149" s="2"/>
+      <c r="F149" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G149" s="2"/>
+      <c r="H149" s="2"/>
+      <c r="I149" s="2"/>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A150" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E150" s="2"/>
+      <c r="F150" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="G150" s="2"/>
+      <c r="H150" s="2"/>
+      <c r="I150" s="2"/>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A151" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E151" s="2"/>
+      <c r="F151" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G151" s="2"/>
+      <c r="H151" s="2"/>
+      <c r="I151" s="2"/>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A152" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G152" s="2"/>
+      <c r="H152" s="2"/>
+      <c r="I152" s="2"/>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A153" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E153" s="2"/>
+      <c r="F153" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G153" s="2"/>
+      <c r="H153" s="2"/>
+      <c r="I153" s="2"/>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A154" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E154" s="2"/>
+      <c r="F154" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G154" s="2"/>
+      <c r="H154" s="2"/>
+      <c r="I154" s="2"/>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A155" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E155" s="2"/>
+      <c r="F155" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G155" s="2"/>
+      <c r="H155" s="2"/>
+      <c r="I155" s="2"/>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A156" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E156" s="2"/>
+      <c r="F156" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G156" s="2"/>
+      <c r="H156" s="2"/>
+      <c r="I156" s="2"/>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A157" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E157" s="2"/>
+      <c r="F157" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="G157" s="2"/>
+      <c r="H157" s="2"/>
+      <c r="I157" s="2"/>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A158" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E158" s="2"/>
+      <c r="F158" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G158" s="2"/>
+      <c r="H158" s="2"/>
+      <c r="I158" s="2"/>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A159" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E159" s="2"/>
+      <c r="F159" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G159" s="2"/>
+      <c r="H159" s="2"/>
+      <c r="I159" s="2"/>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A160" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E160" s="2"/>
+      <c r="F160" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="G160" s="2"/>
+      <c r="H160" s="2"/>
+      <c r="I160" s="2"/>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A161" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E161" s="2"/>
+      <c r="F161" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="G161" s="2"/>
+      <c r="H161" s="2"/>
+      <c r="I161" s="2"/>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A162" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="G162" s="2"/>
+      <c r="H162" s="2"/>
+      <c r="I162" s="2"/>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A163" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G163" s="2"/>
+      <c r="H163" s="2"/>
+      <c r="I163" s="2"/>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A164" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G164" s="2"/>
+      <c r="H164" s="2"/>
+      <c r="I164" s="2"/>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A165" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E165" s="2"/>
+      <c r="F165" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="G165" s="2"/>
+      <c r="H165" s="2"/>
+      <c r="I165" s="2"/>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A166" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="E166" s="2"/>
+      <c r="F166" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H166" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I166" s="1" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A167" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E167" s="2"/>
+      <c r="F167" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="H167" s="2"/>
+      <c r="I167" s="2"/>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A168" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E168" s="2"/>
+      <c r="F168" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="G168" s="2"/>
+      <c r="H168" s="2"/>
+      <c r="I168" s="2"/>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A169" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E169" s="2"/>
+      <c r="F169" s="2"/>
+      <c r="G169" s="2"/>
+      <c r="H169" s="2"/>
+      <c r="I169" s="2"/>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A170" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E170" s="2"/>
+      <c r="F170" s="2"/>
+      <c r="G170" s="2"/>
+      <c r="H170" s="2"/>
+      <c r="I170" s="2"/>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A171" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E171" s="2"/>
+      <c r="F171" s="2"/>
+      <c r="G171" s="2"/>
+      <c r="H171" s="2"/>
+      <c r="I171" s="2"/>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A172" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E172" s="2"/>
+      <c r="F172" s="2"/>
+      <c r="G172" s="2"/>
+      <c r="H172" s="2"/>
+      <c r="I172" s="2"/>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A173" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E173" s="2"/>
+      <c r="F173" s="2"/>
+      <c r="G173" s="2"/>
+      <c r="H173" s="2"/>
+      <c r="I173" s="2"/>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A174" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E174" s="2"/>
+      <c r="F174" s="2"/>
+      <c r="G174" s="2"/>
+      <c r="H174" s="2"/>
+      <c r="I174" s="2"/>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A175" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E175" s="2"/>
+      <c r="F175" s="2"/>
+      <c r="G175" s="2"/>
+      <c r="H175" s="2"/>
+      <c r="I175" s="2"/>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A176" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E176" s="2"/>
+      <c r="F176" s="2"/>
+      <c r="G176" s="2"/>
+      <c r="H176" s="2"/>
+      <c r="I176" s="2"/>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A177" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E177" s="2"/>
+      <c r="F177" s="2"/>
+      <c r="G177" s="2"/>
+      <c r="H177" s="2"/>
+      <c r="I177" s="2"/>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A178" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E178" s="2"/>
+      <c r="F178" s="2"/>
+      <c r="G178" s="2"/>
+      <c r="H178" s="2"/>
+      <c r="I178" s="2"/>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A179" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E179" s="2"/>
+      <c r="F179" s="2"/>
+      <c r="G179" s="2"/>
+      <c r="H179" s="2"/>
+      <c r="I179" s="2"/>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A180" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E180" s="2"/>
+      <c r="F180" s="2"/>
+      <c r="G180" s="2"/>
+      <c r="H180" s="2"/>
+      <c r="I180" s="2"/>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A181" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E181" s="2"/>
+      <c r="F181" s="2"/>
+      <c r="G181" s="2"/>
+      <c r="H181" s="2"/>
+      <c r="I181" s="2"/>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A182" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E182" s="2"/>
+      <c r="F182" s="2"/>
+      <c r="G182" s="2"/>
+      <c r="H182" s="2"/>
+      <c r="I182" s="2"/>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A183" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E183" s="2"/>
+      <c r="F183" s="2"/>
+      <c r="G183" s="2"/>
+      <c r="H183" s="2"/>
+      <c r="I183" s="2"/>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A184" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E184" s="2"/>
+      <c r="F184" s="2"/>
+      <c r="G184" s="2"/>
+      <c r="H184" s="2"/>
+      <c r="I184" s="2"/>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A185" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E185" s="2"/>
+      <c r="F185" s="2"/>
+      <c r="G185" s="2"/>
+      <c r="H185" s="2"/>
+      <c r="I185" s="2"/>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A186" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E186" s="2"/>
+      <c r="F186" s="2"/>
+      <c r="G186" s="2"/>
+      <c r="H186" s="2"/>
+      <c r="I186" s="2"/>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A187" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E187" s="2"/>
+      <c r="F187" s="2"/>
+      <c r="G187" s="2"/>
+      <c r="H187" s="2"/>
+      <c r="I187" s="2"/>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A188" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E188" s="2"/>
+      <c r="F188" s="2"/>
+      <c r="G188" s="2"/>
+      <c r="H188" s="2"/>
+      <c r="I188" s="2"/>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A189" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E189" s="2"/>
+      <c r="F189" s="2"/>
+      <c r="G189" s="2"/>
+      <c r="H189" s="2"/>
+      <c r="I189" s="2"/>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A190" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E190" s="2"/>
+      <c r="F190" s="2"/>
+      <c r="G190" s="2"/>
+      <c r="H190" s="2"/>
+      <c r="I190" s="2"/>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A191" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E191" s="2"/>
+      <c r="F191" s="2"/>
+      <c r="G191" s="2"/>
+      <c r="H191" s="2"/>
+      <c r="I191" s="2"/>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A192" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E192" s="2"/>
+      <c r="F192" s="2"/>
+      <c r="G192" s="2"/>
+      <c r="H192" s="2"/>
+      <c r="I192" s="2"/>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A193" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E193" s="2"/>
+      <c r="F193" s="2"/>
+      <c r="G193" s="2"/>
+      <c r="H193" s="2"/>
+      <c r="I193" s="2"/>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A194" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E194" s="2"/>
+      <c r="F194" s="2"/>
+      <c r="G194" s="2"/>
+      <c r="H194" s="2"/>
+      <c r="I194" s="2"/>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A195" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="E195" s="2"/>
+      <c r="F195" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="G195" s="2"/>
+      <c r="H195" s="2"/>
+      <c r="I195" s="2"/>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A196" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E196" s="2"/>
+      <c r="F196" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="G196" s="2"/>
+      <c r="H196" s="2"/>
+      <c r="I196" s="2"/>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A197" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E197" s="2"/>
+      <c r="F197" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="G197" s="2"/>
+      <c r="H197" s="2"/>
+      <c r="I197" s="2"/>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A198" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="E198" s="2"/>
+      <c r="F198" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H198" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="I198" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A199" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E199" s="2"/>
+      <c r="F199" s="2"/>
+      <c r="G199" s="2"/>
+      <c r="H199" s="2"/>
+      <c r="I199" s="2"/>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A200" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E200" s="2"/>
+      <c r="F200" s="3"/>
+      <c r="G200" s="2"/>
+      <c r="H200" s="2"/>
+      <c r="I200" s="2"/>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A201" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E201" s="2"/>
+      <c r="F201" s="2"/>
+      <c r="G201" s="2"/>
+      <c r="H201" s="2"/>
+      <c r="I201" s="2"/>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A202" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E202" s="2"/>
+      <c r="F202" s="2"/>
+      <c r="G202" s="2"/>
+      <c r="H202" s="2"/>
+      <c r="I202" s="2"/>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A203" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E203" s="2"/>
+      <c r="F203" s="2"/>
+      <c r="G203" s="2"/>
+      <c r="H203" s="2"/>
+      <c r="I203" s="2"/>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A204" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E204" s="2"/>
+      <c r="F204" s="2"/>
+      <c r="G204" s="2"/>
+      <c r="H204" s="2"/>
+      <c r="I204" s="2"/>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A205" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E205" s="2"/>
+      <c r="F205" s="2"/>
+      <c r="G205" s="2"/>
+      <c r="H205" s="2"/>
+      <c r="I205" s="2"/>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A206" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E206" s="2"/>
+      <c r="F206" s="2"/>
+      <c r="G206" s="2"/>
+      <c r="H206" s="2"/>
+      <c r="I206" s="2"/>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A207" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E207" s="2"/>
+      <c r="F207" s="2"/>
+      <c r="G207" s="2"/>
+      <c r="H207" s="2"/>
+      <c r="I207" s="2"/>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A208" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E208" s="2"/>
+      <c r="F208" s="2"/>
+      <c r="G208" s="2"/>
+      <c r="H208" s="2"/>
+      <c r="I208" s="2"/>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A209" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E209" s="2"/>
+      <c r="F209" s="2"/>
+      <c r="G209" s="2"/>
+      <c r="H209" s="2"/>
+      <c r="I209" s="2"/>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A210" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E210" s="2"/>
+      <c r="F210" s="2"/>
+      <c r="G210" s="2"/>
+      <c r="H210" s="2"/>
+      <c r="I210" s="2"/>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A211" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E211" s="2"/>
+      <c r="F211" s="2"/>
+      <c r="G211" s="2"/>
+      <c r="H211" s="2"/>
+      <c r="I211" s="2"/>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A212" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E212" s="2"/>
+      <c r="F212" s="2"/>
+      <c r="G212" s="2"/>
+      <c r="H212" s="2"/>
+      <c r="I212" s="2"/>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A213" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E213" s="2"/>
+      <c r="F213" s="2"/>
+      <c r="G213" s="2"/>
+      <c r="H213" s="2"/>
+      <c r="I213" s="2"/>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A214" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E214" s="2"/>
+      <c r="F214" s="2"/>
+      <c r="G214" s="2"/>
+      <c r="H214" s="2"/>
+      <c r="I214" s="2"/>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A215" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E215" s="2"/>
+      <c r="F215" s="2"/>
+      <c r="G215" s="2"/>
+      <c r="H215" s="2"/>
+      <c r="I215" s="2"/>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A216" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E216" s="2"/>
+      <c r="F216" s="2"/>
+      <c r="G216" s="2"/>
+      <c r="H216" s="2"/>
+      <c r="I216" s="2"/>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A217" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E217" s="2"/>
+      <c r="F217" s="2"/>
+      <c r="G217" s="2"/>
+      <c r="H217" s="2"/>
+      <c r="I217" s="2"/>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A218" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E218" s="2"/>
+      <c r="F218" s="2"/>
+      <c r="G218" s="2"/>
+      <c r="H218" s="2"/>
+      <c r="I218" s="2"/>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A219" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E219" s="2"/>
+      <c r="F219" s="2"/>
+      <c r="G219" s="2"/>
+      <c r="H219" s="2"/>
+      <c r="I219" s="2"/>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A220" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E220" s="2"/>
+      <c r="F220" s="2"/>
+      <c r="G220" s="2"/>
+      <c r="H220" s="2"/>
+      <c r="I220" s="2"/>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A221" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E221" s="2"/>
+      <c r="F221" s="2"/>
+      <c r="G221" s="2"/>
+      <c r="H221" s="2"/>
+      <c r="I221" s="2"/>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A222" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E222" s="2"/>
+      <c r="F222" s="2"/>
+      <c r="G222" s="2"/>
+      <c r="H222" s="2"/>
+      <c r="I222" s="2"/>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A223" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E223" s="2"/>
+      <c r="F223" s="2"/>
+      <c r="G223" s="2"/>
+      <c r="H223" s="2"/>
+      <c r="I223" s="2"/>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A224" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="E224" s="2"/>
+      <c r="F224" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G224" s="2"/>
+      <c r="H224" s="2"/>
+      <c r="I224" s="2"/>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A225" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="F225" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="G225" s="2"/>
+      <c r="H225" s="2"/>
+      <c r="I225" s="2"/>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A226" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F226" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G226" s="2"/>
+      <c r="H226" s="2"/>
+      <c r="I226" s="2"/>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A227" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="E227" s="2"/>
+      <c r="F227" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G227" s="2"/>
+      <c r="H227" s="2"/>
+      <c r="I227" s="2"/>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A228" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E228" s="2"/>
+      <c r="F228" s="2"/>
+      <c r="G228" s="2"/>
+      <c r="H228" s="2"/>
+      <c r="I228" s="2"/>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A229" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E229" s="2"/>
+      <c r="F229" s="2"/>
+      <c r="G229" s="2"/>
+      <c r="H229" s="2"/>
+      <c r="I229" s="2"/>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A230" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E230" s="2"/>
+      <c r="F230" s="2"/>
+      <c r="G230" s="2"/>
+      <c r="H230" s="2"/>
+      <c r="I230" s="2"/>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A231" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E231" s="2"/>
+      <c r="F231" s="2"/>
+      <c r="G231" s="2"/>
+      <c r="H231" s="2"/>
+      <c r="I231" s="2"/>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A232" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E232" s="2"/>
+      <c r="F232" s="2"/>
+      <c r="G232" s="2"/>
+      <c r="H232" s="2"/>
+      <c r="I232" s="2"/>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A233" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F233" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G233" s="2"/>
+      <c r="H233" s="2"/>
+      <c r="I233" s="2"/>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A234" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E234" s="2"/>
+      <c r="F234" s="2"/>
+      <c r="G234" s="2"/>
+      <c r="H234" s="2"/>
+      <c r="I234" s="2"/>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A235" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E235" s="2"/>
+      <c r="F235" s="2"/>
+      <c r="G235" s="2"/>
+      <c r="H235" s="2"/>
+      <c r="I235" s="2"/>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A236" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E236" s="2"/>
+      <c r="F236" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G236" s="2"/>
+      <c r="H236" s="2"/>
+      <c r="I236" s="2"/>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A237" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F237" s="2"/>
+      <c r="G237" s="2"/>
+      <c r="H237" s="2"/>
+      <c r="I237" s="2"/>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A238" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="E238" s="2"/>
+      <c r="F238" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G238" s="2"/>
+      <c r="H238" s="2"/>
+      <c r="I238" s="2"/>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A239" s="2"/>
+      <c r="B239" s="2"/>
+      <c r="C239" s="2"/>
+      <c r="D239" s="2"/>
+      <c r="E239" s="2"/>
+      <c r="F239" s="2"/>
+      <c r="G239" s="2"/>
+      <c r="H239" s="2"/>
+      <c r="I239" s="2"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="G8" r:id="rId1" xr:uid="{159BBC56-6422-9440-AF19-D0D4FED23536}"/>
+    <hyperlink ref="H15" r:id="rId2" xr:uid="{56F38695-667D-724F-BCF6-2911ACBBC8A3}"/>
+    <hyperlink ref="F16" r:id="rId3" xr:uid="{D25EFC87-D403-B142-9530-FAC877D5EB24}"/>
+    <hyperlink ref="F39" r:id="rId4" xr:uid="{6C79E68C-1A30-E046-AF00-5509A69B6430}"/>
+    <hyperlink ref="F43" r:id="rId5" xr:uid="{106A51D7-6D7A-634D-83A7-7B2F8EC4A2FB}"/>
+    <hyperlink ref="F73" r:id="rId6" xr:uid="{9B2B9A01-153E-1347-A08A-3C2B202802CC}"/>
+    <hyperlink ref="F74" r:id="rId7" xr:uid="{81213DBF-60B1-3448-A211-E3A8A524FAE3}"/>
+    <hyperlink ref="F81" r:id="rId8" xr:uid="{48DC187C-9249-0B47-BD1D-AA577A330AFB}"/>
+    <hyperlink ref="F83" r:id="rId9" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{2D5A5F35-4E93-9845-BC8A-66E0F335DF14}"/>
+    <hyperlink ref="F85" r:id="rId10" xr:uid="{6A27D4F9-0B5D-694F-8F8B-CAB34DC24494}"/>
+    <hyperlink ref="F86" r:id="rId11" xr:uid="{FED3349A-FD93-A94D-8FBF-BC4719F8429F}"/>
+    <hyperlink ref="F87" r:id="rId12" xr:uid="{B2510302-61AB-C540-A96F-71D6304E36D6}"/>
+    <hyperlink ref="F90" r:id="rId13" xr:uid="{E719D4EC-2984-714F-B628-A6BC01B5940C}"/>
+    <hyperlink ref="F91" r:id="rId14" xr:uid="{8E6BC122-C900-C84E-BD06-3F38CF07BED9}"/>
+    <hyperlink ref="F92" r:id="rId15" xr:uid="{49A5D607-661A-7542-A2CD-A5E4C2865F1D}"/>
+    <hyperlink ref="F93" r:id="rId16" xr:uid="{FE02C46B-48A8-8B4D-9FB7-794B8B38B7E9}"/>
+    <hyperlink ref="F95" r:id="rId17" xr:uid="{CF4DB45D-DF52-004E-9527-D94CB223062B}"/>
+    <hyperlink ref="F96" r:id="rId18" xr:uid="{94D55428-A9F0-E444-86B5-6E50C081DBFE}"/>
+    <hyperlink ref="F97" r:id="rId19" xr:uid="{6149307E-9D5F-9E47-9E57-5A981178E542}"/>
+    <hyperlink ref="F98" r:id="rId20" xr:uid="{852D472A-7B92-2C4F-891D-E8845048EC81}"/>
+    <hyperlink ref="F99" r:id="rId21" xr:uid="{C7C7097B-80B7-3B41-8B0C-A72D1B5EE3E2}"/>
+    <hyperlink ref="F102" r:id="rId22" xr:uid="{2CDEAA2D-1415-E64B-AC77-86C969E1CB00}"/>
+    <hyperlink ref="F103" r:id="rId23" xr:uid="{DD257F06-8688-3E44-AA77-395C481A6688}"/>
+    <hyperlink ref="F104" r:id="rId24" xr:uid="{4FDBE0E7-D8EA-D84C-A78B-CD65BF1F9354}"/>
+    <hyperlink ref="F105" r:id="rId25" xr:uid="{148C7D17-449B-FE4C-9AB1-2E4FCA8DBED2}"/>
+    <hyperlink ref="F106" r:id="rId26" xr:uid="{9C5F4DDB-E941-1D49-B74B-D9CD7F39CF17}"/>
+    <hyperlink ref="F107" r:id="rId27" xr:uid="{938E2E55-10B6-C344-8A4D-39A03C6129A3}"/>
+    <hyperlink ref="F116" r:id="rId28" xr:uid="{22A547F8-EDD8-F945-A781-64FB122DA983}"/>
+    <hyperlink ref="F119" r:id="rId29" xr:uid="{D543C927-E079-3B4F-ADA0-29851C881A33}"/>
+    <hyperlink ref="F120" r:id="rId30" xr:uid="{D5E1CE96-06E4-2A4C-B2F6-89A25BF79909}"/>
+    <hyperlink ref="F121" r:id="rId31" xr:uid="{114A7B3C-1092-D843-9AC5-BF80E4E0D043}"/>
+    <hyperlink ref="F122" r:id="rId32" xr:uid="{08C3E9F1-E327-1E4A-81CA-F90564189D2B}"/>
+    <hyperlink ref="F123" r:id="rId33" xr:uid="{EEB9B3CF-E3C3-5C44-AB26-E6CCED689413}"/>
+    <hyperlink ref="F124" r:id="rId34" xr:uid="{278D82BB-F204-4E41-A5D2-42C246C2C5F6}"/>
+    <hyperlink ref="F125" r:id="rId35" xr:uid="{9A56AD7A-8DC2-1B4C-B777-7D42244F4D39}"/>
+    <hyperlink ref="F126" r:id="rId36" xr:uid="{A281555C-7C27-DB47-BC08-26D8AD78348E}"/>
+    <hyperlink ref="F133" r:id="rId37" xr:uid="{2F8E0855-90E5-204F-9521-4FC206125599}"/>
+    <hyperlink ref="F145" r:id="rId38" xr:uid="{386838AF-35D3-0C49-AA80-3E13CF5B763B}"/>
+    <hyperlink ref="F146" r:id="rId39" xr:uid="{2A54DB1C-D0D5-1A46-B5B4-2AB3EA25BFD0}"/>
+    <hyperlink ref="F147" r:id="rId40" xr:uid="{629AECC2-B440-5840-93BE-63654BCA2188}"/>
+    <hyperlink ref="G148" r:id="rId41" xr:uid="{0C60883E-E3F2-F443-8FA7-2BD961B72E6F}"/>
+    <hyperlink ref="F149" r:id="rId42" xr:uid="{A05E9319-E2CD-6F4C-A2F6-789D39CE0686}"/>
+    <hyperlink ref="F150" r:id="rId43" xr:uid="{22935E0A-9D44-B54E-9D73-78917652534C}"/>
+    <hyperlink ref="F151" r:id="rId44" xr:uid="{2FB9AF62-D718-8144-9B35-7B77D2BE032B}"/>
+    <hyperlink ref="F152" r:id="rId45" xr:uid="{4E5EFDDA-6883-BF46-9E94-D893494F0F03}"/>
+    <hyperlink ref="F153" r:id="rId46" xr:uid="{83EF0E15-DAD3-2247-8FA2-D7D2E3F0D476}"/>
+    <hyperlink ref="F154" r:id="rId47" xr:uid="{12293028-0860-7B43-AE47-C899F71780FE}"/>
+    <hyperlink ref="F155" r:id="rId48" xr:uid="{13C473DC-2BE8-9747-9940-9621B4D8401D}"/>
+    <hyperlink ref="F156" r:id="rId49" xr:uid="{CC242625-9DEE-9145-8AEC-B442B2117990}"/>
+    <hyperlink ref="F157" r:id="rId50" xr:uid="{C0175F66-06C0-7344-8D20-E2BCDBA1AC97}"/>
+    <hyperlink ref="F158" r:id="rId51" xr:uid="{C907CADD-A43D-5545-B215-F1105030E680}"/>
+    <hyperlink ref="F159" r:id="rId52" xr:uid="{C681EA47-E54B-B34A-B611-F048C453763A}"/>
+    <hyperlink ref="F163" r:id="rId53" xr:uid="{2D048A3B-EE7C-604D-97BC-51B069433511}"/>
+    <hyperlink ref="F164" r:id="rId54" xr:uid="{E3C5F5B5-5535-ED4F-ACA0-6F36390F26CE}"/>
+    <hyperlink ref="F166" r:id="rId55" xr:uid="{42C15DAA-F574-EA43-8847-50AEC943B030}"/>
+    <hyperlink ref="G166" r:id="rId56" xr:uid="{854723C1-43C2-B249-95DE-F73D593B39D5}"/>
+    <hyperlink ref="H166" r:id="rId57" xr:uid="{654F1329-8EC9-084A-87AA-4871C7006B37}"/>
+    <hyperlink ref="I166" r:id="rId58" xr:uid="{C8DB336E-F896-724C-8B08-FB28BD0B86EF}"/>
+    <hyperlink ref="G167" r:id="rId59" xr:uid="{806C5B21-9EBE-F54D-96D0-962331F4FC7D}"/>
+    <hyperlink ref="F198" r:id="rId60" xr:uid="{0BE899F9-B63C-6F49-A85C-026E93E6D75D}"/>
+    <hyperlink ref="G198" r:id="rId61" xr:uid="{867F0619-DB83-4F42-AB0F-1EB115FE6428}"/>
+    <hyperlink ref="H198" r:id="rId62" xr:uid="{57A2339F-7161-F646-A1CC-5A0018A28691}"/>
+    <hyperlink ref="I198" r:id="rId63" xr:uid="{B33161BA-5CD1-3D46-876E-8E8CBC111EF0}"/>
+    <hyperlink ref="F224" r:id="rId64" xr:uid="{239CD0E2-06EC-0C46-B91D-EB396EFC8717}"/>
+    <hyperlink ref="F225" r:id="rId65" xr:uid="{37F5520A-0B94-9749-8BCF-2D7DA9A8CA43}"/>
+    <hyperlink ref="F226" r:id="rId66" xr:uid="{4767BB22-415D-054C-A5B7-2163FB542DFA}"/>
+    <hyperlink ref="F227" r:id="rId67" xr:uid="{D252C2E7-F024-D94A-857C-D62CEEE78395}"/>
+    <hyperlink ref="F233" r:id="rId68" xr:uid="{579C86E0-10EF-1C41-9289-A3B287B3DE21}"/>
+    <hyperlink ref="F236" r:id="rId69" xr:uid="{9CE98C5A-B57A-CD48-968B-FF0B87FB4D70}"/>
+    <hyperlink ref="F238" r:id="rId70" xr:uid="{12E46609-D4CE-1D47-A3A4-3A16B1014403}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA08DD43-E75C-AC43-ADD8-A06CC9F5DBF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F219698D-EC15-6A45-96FD-6A961A544ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33380" windowHeight="21580" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3022" uniqueCount="1058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3024" uniqueCount="1067">
   <si>
     <t>Household Name</t>
   </si>
@@ -3212,6 +3212,33 @@
   </si>
   <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uKciSYAS/view</t>
+  </si>
+  <si>
+    <t>HOLD - Trott</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CB </t>
+  </si>
+  <si>
+    <t>Curebound Hold</t>
+  </si>
+  <si>
+    <t>Hold for Emi Stech</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vTNtIYAW/view</t>
+  </si>
+  <si>
+    <t>Casa Dragones &amp; BRAND</t>
+  </si>
+  <si>
+    <t>2 tickets each</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uCpUlYAK/view</t>
   </si>
 </sst>
 </file>
@@ -3632,15 +3659,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7894B4-148E-174D-AE8B-E6DE441B89B0}">
-  <dimension ref="A1:I239"/>
+  <dimension ref="A1:I238"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="4" width="10.83203125"/>
-    <col min="5" max="5" width="66.1640625" customWidth="1"/>
-    <col min="6" max="6" width="87.6640625" customWidth="1"/>
-    <col min="7" max="7" width="75.1640625" customWidth="1"/>
-    <col min="8" max="8" width="42.33203125" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125"/>
+    <col min="5" max="5" width="37.1640625" customWidth="1"/>
+    <col min="6" max="6" width="92.1640625" customWidth="1"/>
+    <col min="7" max="7" width="57.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -4494,7 +4518,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>156</v>
+        <v>1058</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>157</v>
@@ -4503,7 +4527,7 @@
         <v>158</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
@@ -4513,7 +4537,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>160</v>
@@ -4522,12 +4546,10 @@
         <v>161</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="E41" s="2"/>
-      <c r="F41" s="3" t="s">
-        <v>656</v>
-      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
@@ -5055,20 +5077,20 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="E67" s="2"/>
-      <c r="F67" s="3" t="s">
-        <v>659</v>
+      <c r="F67" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
@@ -5079,17 +5101,17 @@
         <v>257</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
@@ -5097,20 +5119,20 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
@@ -5118,20 +5140,20 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
@@ -5139,20 +5161,20 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
@@ -5160,20 +5182,20 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E72" s="2"/>
-      <c r="F72" s="2" t="s">
-        <v>275</v>
+      <c r="F72" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
@@ -5184,17 +5206,17 @@
         <v>276</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="1" t="s">
-        <v>279</v>
+        <v>983</v>
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
@@ -5202,20 +5224,20 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E74" s="2"/>
-      <c r="F74" s="1" t="s">
-        <v>983</v>
+      <c r="F74" s="2" t="s">
+        <v>285</v>
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
@@ -5223,20 +5245,22 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E75" s="2"/>
+      <c r="E75" s="2" t="s">
+        <v>289</v>
+      </c>
       <c r="F75" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
@@ -5244,22 +5268,20 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>289</v>
-      </c>
+      <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -5267,20 +5289,20 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
@@ -5288,20 +5310,20 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="E78" s="2"/>
-      <c r="F78" s="2" t="s">
-        <v>298</v>
+      <c r="F78" s="3" t="s">
+        <v>660</v>
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
@@ -5309,20 +5331,20 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
@@ -5330,20 +5352,20 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>302</v>
+        <v>1034</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="E80" s="2"/>
-      <c r="F80" s="3" t="s">
-        <v>661</v>
+      <c r="F80" s="1" t="s">
+        <v>996</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
@@ -5351,60 +5373,60 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>1034</v>
+        <v>164</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>12</v>
+        <v>167</v>
       </c>
       <c r="E81" s="2"/>
-      <c r="F81" s="1" t="s">
-        <v>996</v>
-      </c>
+      <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>164</v>
+        <v>311</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>167</v>
+        <v>12</v>
       </c>
       <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
+      <c r="F82" s="1" t="s">
+        <v>1035</v>
+      </c>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E83" s="2"/>
-      <c r="F83" s="1" t="s">
-        <v>1035</v>
+      <c r="F83" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -5412,20 +5434,20 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E84" s="2"/>
-      <c r="F84" s="3" t="s">
-        <v>314</v>
+      <c r="F84" s="1" t="s">
+        <v>321</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
@@ -5436,17 +5458,17 @@
         <v>318</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="1" t="s">
-        <v>321</v>
+        <v>984</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
@@ -5454,64 +5476,64 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="1" t="s">
-        <v>984</v>
-      </c>
-      <c r="G86" s="2"/>
+        <v>985</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>327</v>
+      </c>
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E87" s="2"/>
-      <c r="F87" s="1" t="s">
-        <v>985</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>327</v>
-      </c>
+      <c r="F87" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -5519,20 +5541,20 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E89" s="2"/>
-      <c r="F89" s="2" t="s">
-        <v>335</v>
+      <c r="F89" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -5543,17 +5565,17 @@
         <v>343</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="1" t="s">
-        <v>338</v>
+        <v>986</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -5564,17 +5586,17 @@
         <v>343</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -5582,20 +5604,20 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>343</v>
+        <v>988</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="1" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -5603,20 +5625,20 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E93" s="2"/>
-      <c r="F93" s="1" t="s">
-        <v>989</v>
+      <c r="F93" s="5" t="s">
+        <v>338</v>
       </c>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -5624,20 +5646,20 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E94" s="2"/>
-      <c r="F94" s="5" t="s">
-        <v>338</v>
+      <c r="F94" s="1" t="s">
+        <v>992</v>
       </c>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -5645,20 +5667,20 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>991</v>
+        <v>350</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="1" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -5666,20 +5688,20 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>351</v>
+        <v>220</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>352</v>
+        <v>221</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="1" t="s">
-        <v>993</v>
+        <v>355</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -5690,17 +5712,17 @@
         <v>354</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>220</v>
+        <v>356</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>221</v>
+        <v>357</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="1" t="s">
-        <v>355</v>
+        <v>994</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
@@ -5711,17 +5733,17 @@
         <v>354</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
@@ -5729,20 +5751,20 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E99" s="2"/>
-      <c r="F99" s="1" t="s">
-        <v>995</v>
+      <c r="F99" s="2" t="s">
+        <v>363</v>
       </c>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
@@ -5750,20 +5772,20 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>360</v>
+        <v>305</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
-        <v>363</v>
+        <v>308</v>
       </c>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
@@ -5771,20 +5793,20 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>305</v>
+        <v>364</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E101" s="2"/>
-      <c r="F101" s="2" t="s">
-        <v>308</v>
+      <c r="F101" s="1" t="s">
+        <v>997</v>
       </c>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
@@ -5795,17 +5817,17 @@
         <v>364</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="1" t="s">
-        <v>997</v>
+        <v>367</v>
       </c>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
@@ -5813,20 +5835,20 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="1" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -5837,17 +5859,17 @@
         <v>372</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="1" t="s">
-        <v>375</v>
+        <v>998</v>
       </c>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -5855,20 +5877,20 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" s="1" t="s">
-        <v>998</v>
+        <v>381</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -5879,17 +5901,17 @@
         <v>378</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" s="1" t="s">
-        <v>381</v>
+        <v>999</v>
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -5897,20 +5919,20 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="E107" s="2"/>
-      <c r="F107" s="1" t="s">
-        <v>999</v>
+      <c r="F107" s="3" t="s">
+        <v>662</v>
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
@@ -5918,20 +5940,20 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E108" s="2"/>
-      <c r="F108" s="3" t="s">
-        <v>662</v>
+      <c r="F108" s="5" t="s">
+        <v>390</v>
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
@@ -5939,20 +5961,20 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E109" s="2"/>
-      <c r="F109" s="5" t="s">
-        <v>390</v>
+      <c r="F109" s="3" t="s">
+        <v>663</v>
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
@@ -5960,20 +5982,20 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" s="3" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
@@ -5984,10 +6006,10 @@
         <v>396</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>155</v>
@@ -6002,21 +6024,19 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="E112" s="2"/>
-      <c r="F112" s="3" t="s">
-        <v>664</v>
-      </c>
+      <c r="F112" s="2"/>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
@@ -6026,10 +6046,10 @@
         <v>401</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>12</v>
@@ -6045,10 +6065,10 @@
         <v>401</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>12</v>
@@ -6061,39 +6081,41 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>401</v>
+        <v>1036</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E115" s="2"/>
-      <c r="F115" s="2"/>
+      <c r="F115" s="1" t="s">
+        <v>1051</v>
+      </c>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>1036</v>
+        <v>410</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E116" s="2"/>
-      <c r="F116" s="1" t="s">
-        <v>1051</v>
+      <c r="F116" s="2" t="s">
+        <v>413</v>
       </c>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
@@ -6104,17 +6126,17 @@
         <v>410</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
@@ -6122,20 +6144,20 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E118" s="2"/>
-      <c r="F118" s="2" t="s">
-        <v>416</v>
+      <c r="F118" s="1" t="s">
+        <v>675</v>
       </c>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
@@ -6146,10 +6168,10 @@
         <v>417</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>12</v>
@@ -6167,10 +6189,10 @@
         <v>417</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>12</v>
@@ -6185,20 +6207,20 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="1" t="s">
-        <v>675</v>
+        <v>427</v>
       </c>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
@@ -6209,17 +6231,17 @@
         <v>424</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="1" t="s">
-        <v>427</v>
+        <v>1000</v>
       </c>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
@@ -6230,17 +6252,17 @@
         <v>424</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
@@ -6251,17 +6273,17 @@
         <v>424</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
@@ -6272,17 +6294,17 @@
         <v>424</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="1" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
@@ -6290,20 +6312,20 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E126" s="2"/>
-      <c r="F126" s="1" t="s">
-        <v>1003</v>
+      <c r="F126" s="2" t="s">
+        <v>439</v>
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
@@ -6311,20 +6333,20 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
@@ -6332,20 +6354,20 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
@@ -6356,17 +6378,17 @@
         <v>447</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
@@ -6374,20 +6396,22 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E130" s="2"/>
+      <c r="E130" s="2" t="s">
+        <v>1037</v>
+      </c>
       <c r="F130" s="2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
@@ -6395,22 +6419,22 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>665</v>
       </c>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
@@ -6418,22 +6442,20 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E132" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="F132" s="3" t="s">
-        <v>665</v>
+      <c r="E132" s="2"/>
+      <c r="F132" s="1" t="s">
+        <v>676</v>
       </c>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
@@ -6441,20 +6463,22 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E133" s="2"/>
-      <c r="F133" s="1" t="s">
-        <v>676</v>
+      <c r="E133" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>465</v>
       </c>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
@@ -6462,22 +6486,20 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E134" s="2" t="s">
-        <v>458</v>
-      </c>
+      <c r="E134" s="2"/>
       <c r="F134" s="2" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
@@ -6485,20 +6507,20 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
@@ -6506,20 +6528,22 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E136" s="2"/>
+      <c r="E136" s="2" t="s">
+        <v>1038</v>
+      </c>
       <c r="F136" s="2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
@@ -6527,22 +6551,20 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E137" s="2" t="s">
-        <v>1038</v>
-      </c>
+      <c r="E137" s="2"/>
       <c r="F137" s="2" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
@@ -6550,20 +6572,20 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" s="2" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
@@ -6571,20 +6593,22 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E139" s="2"/>
-      <c r="F139" s="2" t="s">
-        <v>485</v>
+      <c r="E139" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>666</v>
       </c>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
@@ -6592,22 +6616,20 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E140" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="F140" s="3" t="s">
-        <v>666</v>
+      <c r="E140" s="2"/>
+      <c r="F140" s="2" t="s">
+        <v>493</v>
       </c>
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
@@ -6615,20 +6637,20 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
-        <v>490</v>
+        <v>17</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E141" s="2"/>
-      <c r="F141" s="2" t="s">
-        <v>493</v>
+      <c r="F141" s="3" t="s">
+        <v>667</v>
       </c>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
@@ -6639,10 +6661,10 @@
         <v>17</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>12</v>
@@ -6660,10 +6682,10 @@
         <v>17</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>12</v>
@@ -6678,20 +6700,22 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
-        <v>17</v>
+        <v>500</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E144" s="2"/>
-      <c r="F144" s="3" t="s">
-        <v>667</v>
+      <c r="E144" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>503</v>
       </c>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
@@ -6702,10 +6726,10 @@
         <v>500</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>12</v>
@@ -6714,7 +6738,7 @@
         <v>1039</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>503</v>
+        <v>1004</v>
       </c>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
@@ -6725,10 +6749,10 @@
         <v>500</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>12</v>
@@ -6737,7 +6761,7 @@
         <v>1039</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
@@ -6745,66 +6769,64 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>500</v>
+        <v>1046</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E147" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>1005</v>
-      </c>
-      <c r="G147" s="2"/>
+      <c r="E147" s="2"/>
+      <c r="F147" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>1052</v>
+      </c>
       <c r="H147" s="2"/>
       <c r="I147" s="2"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
-        <v>1046</v>
+        <v>350</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E148" s="2"/>
-      <c r="F148" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>1052</v>
-      </c>
+      <c r="F148" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G148" s="2"/>
       <c r="H148" s="2"/>
       <c r="I148" s="2"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
-        <v>350</v>
+        <v>516</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="1" t="s">
-        <v>353</v>
+        <v>519</v>
       </c>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
@@ -6815,17 +6837,17 @@
         <v>516</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" s="1" t="s">
-        <v>519</v>
+        <v>1006</v>
       </c>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
@@ -6836,17 +6858,17 @@
         <v>516</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
@@ -6854,20 +6876,20 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
@@ -6878,17 +6900,17 @@
         <v>524</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
@@ -6899,17 +6921,17 @@
         <v>524</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" s="1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
@@ -6917,20 +6939,20 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
-        <v>524</v>
+        <v>372</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
@@ -6938,20 +6960,20 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
-        <v>372</v>
+        <v>533</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" s="1" t="s">
-        <v>1011</v>
+        <v>538</v>
       </c>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
@@ -6962,17 +6984,17 @@
         <v>533</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" s="1" t="s">
-        <v>538</v>
+        <v>1012</v>
       </c>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
@@ -6983,17 +7005,17 @@
         <v>533</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
@@ -7001,20 +7023,20 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E159" s="2"/>
-      <c r="F159" s="1" t="s">
-        <v>1013</v>
+      <c r="F159" s="2" t="s">
+        <v>544</v>
       </c>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
@@ -7022,20 +7044,20 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" s="2" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
@@ -7043,20 +7065,22 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E161" s="2"/>
+      <c r="E161" s="2" t="s">
+        <v>552</v>
+      </c>
       <c r="F161" s="2" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
@@ -7064,22 +7088,22 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
-        <v>549</v>
+        <v>1014</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="F162" s="2" t="s">
-        <v>553</v>
+        <v>1015</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>1016</v>
       </c>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
@@ -7087,22 +7111,22 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
@@ -7110,22 +7134,20 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
-        <v>1017</v>
+        <v>558</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>556</v>
+        <v>388</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>557</v>
+        <v>389</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E164" s="2" t="s">
-        <v>1018</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>1019</v>
+      <c r="E164" s="2"/>
+      <c r="F164" s="2" t="s">
+        <v>561</v>
       </c>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
@@ -7133,92 +7155,90 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
-        <v>558</v>
+        <v>1020</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>388</v>
+        <v>559</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>389</v>
+        <v>560</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>12</v>
+        <v>980</v>
       </c>
       <c r="E165" s="2"/>
-      <c r="F165" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="G165" s="2"/>
-      <c r="H165" s="2"/>
-      <c r="I165" s="2"/>
+      <c r="F165" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H165" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>1024</v>
+      </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
-        <v>1020</v>
+        <v>562</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>560</v>
+        <v>677</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>980</v>
+        <v>12</v>
       </c>
       <c r="E166" s="2"/>
-      <c r="F166" s="1" t="s">
-        <v>1021</v>
+      <c r="F166" s="3" t="s">
+        <v>668</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>1022</v>
-      </c>
-      <c r="H166" s="1" t="s">
-        <v>1023</v>
-      </c>
-      <c r="I166" s="1" t="s">
-        <v>1024</v>
-      </c>
+        <v>673</v>
+      </c>
+      <c r="H166" s="2"/>
+      <c r="I166" s="2"/>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="G167" s="1" t="s">
-        <v>673</v>
-      </c>
+        <v>669</v>
+      </c>
+      <c r="G167" s="2"/>
       <c r="H167" s="2"/>
       <c r="I167" s="2"/>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>678</v>
+        <v>568</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>155</v>
+        <v>569</v>
       </c>
       <c r="E168" s="2"/>
-      <c r="F168" s="3" t="s">
-        <v>669</v>
-      </c>
+      <c r="F168" s="2"/>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
@@ -7228,10 +7248,10 @@
         <v>566</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>569</v>
@@ -7247,10 +7267,10 @@
         <v>566</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>569</v>
@@ -7266,10 +7286,10 @@
         <v>566</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>569</v>
@@ -7285,10 +7305,10 @@
         <v>566</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>569</v>
@@ -7304,10 +7324,10 @@
         <v>566</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>569</v>
@@ -7323,10 +7343,10 @@
         <v>566</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>569</v>
@@ -7342,10 +7362,10 @@
         <v>566</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>569</v>
@@ -7361,10 +7381,10 @@
         <v>566</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>569</v>
@@ -7380,10 +7400,10 @@
         <v>566</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>569</v>
@@ -7399,10 +7419,10 @@
         <v>566</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>569</v>
@@ -7418,10 +7438,10 @@
         <v>566</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>569</v>
@@ -7437,10 +7457,10 @@
         <v>566</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>569</v>
@@ -7453,13 +7473,13 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
-        <v>566</v>
+        <v>679</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>569</v>
@@ -7475,10 +7495,10 @@
         <v>679</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>569</v>
@@ -7491,13 +7511,13 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" s="2" t="s">
-        <v>679</v>
+        <v>566</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>597</v>
+        <v>680</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>569</v>
@@ -7513,10 +7533,10 @@
         <v>566</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>569</v>
@@ -7532,10 +7552,10 @@
         <v>566</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>569</v>
@@ -7551,10 +7571,10 @@
         <v>566</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>569</v>
@@ -7570,10 +7590,10 @@
         <v>566</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>569</v>
@@ -7589,10 +7609,10 @@
         <v>566</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>569</v>
@@ -7608,10 +7628,10 @@
         <v>566</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>569</v>
@@ -7627,10 +7647,10 @@
         <v>566</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>569</v>
@@ -7646,10 +7666,10 @@
         <v>566</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>569</v>
@@ -7665,10 +7685,10 @@
         <v>566</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>569</v>
@@ -7684,10 +7704,10 @@
         <v>566</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>569</v>
@@ -7700,39 +7720,43 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
-        <v>566</v>
+        <v>1059</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>608</v>
+        <v>757</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="E194" s="2"/>
-      <c r="F194" s="2"/>
+        <v>1060</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>1062</v>
+      </c>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
       <c r="I194" s="2"/>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>980</v>
+        <v>155</v>
       </c>
       <c r="E195" s="2"/>
-      <c r="F195" s="2" t="s">
-        <v>611</v>
+      <c r="F195" s="3" t="s">
+        <v>670</v>
       </c>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
@@ -7740,20 +7764,20 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" s="3" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
@@ -7761,67 +7785,65 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
-        <v>614</v>
+        <v>1020</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>155</v>
+        <v>980</v>
       </c>
       <c r="E197" s="2"/>
-      <c r="F197" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="G197" s="2"/>
-      <c r="H197" s="2"/>
-      <c r="I197" s="2"/>
+      <c r="F197" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G197" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H197" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="I197" s="1" t="s">
+        <v>1028</v>
+      </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
-        <v>1020</v>
+        <v>164</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>980</v>
+        <v>167</v>
       </c>
       <c r="E198" s="2"/>
-      <c r="F198" s="1" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G198" s="1" t="s">
-        <v>1026</v>
-      </c>
-      <c r="H198" s="1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="I198" s="1" t="s">
-        <v>1028</v>
-      </c>
+      <c r="F198" s="2"/>
+      <c r="G198" s="2"/>
+      <c r="H198" s="2"/>
+      <c r="I198" s="2"/>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
         <v>164</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E199" s="2"/>
-      <c r="F199" s="2"/>
+      <c r="F199" s="3"/>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
       <c r="I199" s="2"/>
@@ -7831,16 +7853,16 @@
         <v>164</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E200" s="2"/>
-      <c r="F200" s="3"/>
+      <c r="F200" s="2"/>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
       <c r="I200" s="2"/>
@@ -7850,10 +7872,10 @@
         <v>164</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>167</v>
@@ -7869,10 +7891,10 @@
         <v>164</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>698</v>
+        <v>622</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>167</v>
@@ -7888,10 +7910,10 @@
         <v>164</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>167</v>
@@ -7904,20 +7926,26 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
-        <v>164</v>
+        <v>1063</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E204" s="2"/>
-      <c r="F204" s="2"/>
-      <c r="G204" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>1065</v>
+      </c>
       <c r="H204" s="2"/>
       <c r="I204" s="2"/>
     </row>
@@ -7926,10 +7954,10 @@
         <v>164</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>167</v>
@@ -7945,10 +7973,10 @@
         <v>164</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>167</v>
@@ -7964,10 +7992,10 @@
         <v>164</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>167</v>
@@ -7983,10 +8011,10 @@
         <v>164</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>167</v>
@@ -8002,10 +8030,10 @@
         <v>164</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>167</v>
@@ -8021,10 +8049,10 @@
         <v>164</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>167</v>
@@ -8037,16 +8065,16 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
-        <v>164</v>
+        <v>639</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>167</v>
+        <v>639</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" s="2"/>
@@ -8059,10 +8087,10 @@
         <v>639</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>639</v>
@@ -8078,10 +8106,10 @@
         <v>639</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>639</v>
@@ -8097,10 +8125,10 @@
         <v>639</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>639</v>
@@ -8113,16 +8141,16 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
-        <v>639</v>
+        <v>566</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>639</v>
+        <v>569</v>
       </c>
       <c r="E215" s="2"/>
       <c r="F215" s="2"/>
@@ -8135,10 +8163,10 @@
         <v>566</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>569</v>
@@ -8154,10 +8182,10 @@
         <v>566</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>569</v>
@@ -8173,10 +8201,10 @@
         <v>566</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>652</v>
+        <v>699</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>653</v>
+        <v>713</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>569</v>
@@ -8192,10 +8220,10 @@
         <v>566</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>569</v>
@@ -8211,10 +8239,10 @@
         <v>566</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>569</v>
@@ -8230,10 +8258,10 @@
         <v>566</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>715</v>
+        <v>867</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>569</v>
@@ -8249,10 +8277,10 @@
         <v>566</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>569</v>
@@ -8265,39 +8293,43 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" s="2" t="s">
-        <v>566</v>
+        <v>1029</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>866</v>
+        <v>930</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>569</v>
+        <v>980</v>
       </c>
       <c r="E223" s="2"/>
-      <c r="F223" s="2"/>
+      <c r="F223" s="1" t="s">
+        <v>1030</v>
+      </c>
       <c r="G223" s="2"/>
       <c r="H223" s="2"/>
       <c r="I223" s="2"/>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
-        <v>1029</v>
+        <v>979</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="E224" s="2"/>
+      <c r="E224" s="2" t="s">
+        <v>981</v>
+      </c>
       <c r="F224" s="1" t="s">
-        <v>1030</v>
+        <v>982</v>
       </c>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
@@ -8305,22 +8337,22 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" s="2" t="s">
-        <v>979</v>
+        <v>1044</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>980</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>981</v>
+        <v>1045</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>982</v>
+        <v>1053</v>
       </c>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
@@ -8328,22 +8360,20 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>939</v>
+        <v>732</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="E226" s="2" t="s">
-        <v>1045</v>
-      </c>
+      <c r="E226" s="2"/>
       <c r="F226" s="1" t="s">
-        <v>1053</v>
+        <v>1043</v>
       </c>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
@@ -8351,34 +8381,32 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" s="2" t="s">
-        <v>1040</v>
+        <v>709</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>732</v>
+        <v>868</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>980</v>
+        <v>569</v>
       </c>
       <c r="E227" s="2"/>
-      <c r="F227" s="1" t="s">
-        <v>1043</v>
-      </c>
+      <c r="F227" s="2"/>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
       <c r="I227" s="2"/>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
-        <v>709</v>
+        <v>566</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>569</v>
@@ -8394,10 +8422,10 @@
         <v>566</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>569</v>
@@ -8413,10 +8441,10 @@
         <v>566</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>873</v>
+        <v>714</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>569</v>
@@ -8429,16 +8457,16 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" s="2" t="s">
-        <v>566</v>
+        <v>164</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>700</v>
+        <v>864</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>714</v>
+        <v>865</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>569</v>
+        <v>167</v>
       </c>
       <c r="E231" s="2"/>
       <c r="F231" s="2"/>
@@ -8448,42 +8476,42 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
-        <v>164</v>
+        <v>1041</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>864</v>
+        <v>833</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>865</v>
+        <v>834</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E232" s="2"/>
-      <c r="F232" s="2"/>
+        <v>980</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F232" s="1" t="s">
+        <v>390</v>
+      </c>
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
       <c r="I232" s="2"/>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" s="2" t="s">
-        <v>1041</v>
+        <v>566</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>833</v>
+        <v>878</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>834</v>
+        <v>879</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>980</v>
-      </c>
-      <c r="E233" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F233" s="1" t="s">
-        <v>390</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="E233" s="2"/>
+      <c r="F233" s="2"/>
       <c r="G233" s="2"/>
       <c r="H233" s="2"/>
       <c r="I233" s="2"/>
@@ -8493,10 +8521,10 @@
         <v>566</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>878</v>
+        <v>922</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>879</v>
+        <v>923</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>569</v>
@@ -8509,170 +8537,160 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="2" t="s">
-        <v>566</v>
+        <v>508</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>922</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>923</v>
+        <v>937</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>938</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>569</v>
+        <v>155</v>
       </c>
       <c r="E235" s="2"/>
-      <c r="F235" s="2"/>
+      <c r="F235" s="1" t="s">
+        <v>1054</v>
+      </c>
       <c r="G235" s="2"/>
       <c r="H235" s="2"/>
       <c r="I235" s="2"/>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
-        <v>508</v>
+        <v>164</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>937</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>938</v>
+        <v>509</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>510</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E236" s="2"/>
-      <c r="F236" s="1" t="s">
-        <v>1054</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F236" s="2"/>
       <c r="G236" s="2"/>
       <c r="H236" s="2"/>
       <c r="I236" s="2"/>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
-        <v>164</v>
+        <v>1056</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>510</v>
+        <v>739</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>740</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E237" s="2" t="s">
-        <v>1055</v>
-      </c>
-      <c r="F237" s="2"/>
+        <v>980</v>
+      </c>
+      <c r="E237" s="2"/>
+      <c r="F237" s="1" t="s">
+        <v>1057</v>
+      </c>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
       <c r="I237" s="2"/>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
-        <v>1056</v>
+        <v>609</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>740</v>
-      </c>
+        <v>759</v>
+      </c>
+      <c r="C238" s="2"/>
       <c r="D238" s="2" t="s">
         <v>980</v>
       </c>
       <c r="E238" s="2"/>
-      <c r="F238" s="1" t="s">
-        <v>1057</v>
+      <c r="F238" s="2" t="s">
+        <v>611</v>
       </c>
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
       <c r="I238" s="2"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A239" s="2"/>
-      <c r="B239" s="2"/>
-      <c r="C239" s="2"/>
-      <c r="D239" s="2"/>
-      <c r="E239" s="2"/>
-      <c r="F239" s="2"/>
-      <c r="G239" s="2"/>
-      <c r="H239" s="2"/>
-      <c r="I239" s="2"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G8" r:id="rId1" xr:uid="{159BBC56-6422-9440-AF19-D0D4FED23536}"/>
-    <hyperlink ref="H15" r:id="rId2" xr:uid="{56F38695-667D-724F-BCF6-2911ACBBC8A3}"/>
-    <hyperlink ref="F16" r:id="rId3" xr:uid="{D25EFC87-D403-B142-9530-FAC877D5EB24}"/>
-    <hyperlink ref="F39" r:id="rId4" xr:uid="{6C79E68C-1A30-E046-AF00-5509A69B6430}"/>
-    <hyperlink ref="F43" r:id="rId5" xr:uid="{106A51D7-6D7A-634D-83A7-7B2F8EC4A2FB}"/>
-    <hyperlink ref="F73" r:id="rId6" xr:uid="{9B2B9A01-153E-1347-A08A-3C2B202802CC}"/>
-    <hyperlink ref="F74" r:id="rId7" xr:uid="{81213DBF-60B1-3448-A211-E3A8A524FAE3}"/>
-    <hyperlink ref="F81" r:id="rId8" xr:uid="{48DC187C-9249-0B47-BD1D-AA577A330AFB}"/>
-    <hyperlink ref="F83" r:id="rId9" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{2D5A5F35-4E93-9845-BC8A-66E0F335DF14}"/>
-    <hyperlink ref="F85" r:id="rId10" xr:uid="{6A27D4F9-0B5D-694F-8F8B-CAB34DC24494}"/>
-    <hyperlink ref="F86" r:id="rId11" xr:uid="{FED3349A-FD93-A94D-8FBF-BC4719F8429F}"/>
-    <hyperlink ref="F87" r:id="rId12" xr:uid="{B2510302-61AB-C540-A96F-71D6304E36D6}"/>
-    <hyperlink ref="F90" r:id="rId13" xr:uid="{E719D4EC-2984-714F-B628-A6BC01B5940C}"/>
-    <hyperlink ref="F91" r:id="rId14" xr:uid="{8E6BC122-C900-C84E-BD06-3F38CF07BED9}"/>
-    <hyperlink ref="F92" r:id="rId15" xr:uid="{49A5D607-661A-7542-A2CD-A5E4C2865F1D}"/>
-    <hyperlink ref="F93" r:id="rId16" xr:uid="{FE02C46B-48A8-8B4D-9FB7-794B8B38B7E9}"/>
-    <hyperlink ref="F95" r:id="rId17" xr:uid="{CF4DB45D-DF52-004E-9527-D94CB223062B}"/>
-    <hyperlink ref="F96" r:id="rId18" xr:uid="{94D55428-A9F0-E444-86B5-6E50C081DBFE}"/>
-    <hyperlink ref="F97" r:id="rId19" xr:uid="{6149307E-9D5F-9E47-9E57-5A981178E542}"/>
-    <hyperlink ref="F98" r:id="rId20" xr:uid="{852D472A-7B92-2C4F-891D-E8845048EC81}"/>
-    <hyperlink ref="F99" r:id="rId21" xr:uid="{C7C7097B-80B7-3B41-8B0C-A72D1B5EE3E2}"/>
-    <hyperlink ref="F102" r:id="rId22" xr:uid="{2CDEAA2D-1415-E64B-AC77-86C969E1CB00}"/>
-    <hyperlink ref="F103" r:id="rId23" xr:uid="{DD257F06-8688-3E44-AA77-395C481A6688}"/>
-    <hyperlink ref="F104" r:id="rId24" xr:uid="{4FDBE0E7-D8EA-D84C-A78B-CD65BF1F9354}"/>
-    <hyperlink ref="F105" r:id="rId25" xr:uid="{148C7D17-449B-FE4C-9AB1-2E4FCA8DBED2}"/>
-    <hyperlink ref="F106" r:id="rId26" xr:uid="{9C5F4DDB-E941-1D49-B74B-D9CD7F39CF17}"/>
-    <hyperlink ref="F107" r:id="rId27" xr:uid="{938E2E55-10B6-C344-8A4D-39A03C6129A3}"/>
-    <hyperlink ref="F116" r:id="rId28" xr:uid="{22A547F8-EDD8-F945-A781-64FB122DA983}"/>
-    <hyperlink ref="F119" r:id="rId29" xr:uid="{D543C927-E079-3B4F-ADA0-29851C881A33}"/>
-    <hyperlink ref="F120" r:id="rId30" xr:uid="{D5E1CE96-06E4-2A4C-B2F6-89A25BF79909}"/>
-    <hyperlink ref="F121" r:id="rId31" xr:uid="{114A7B3C-1092-D843-9AC5-BF80E4E0D043}"/>
-    <hyperlink ref="F122" r:id="rId32" xr:uid="{08C3E9F1-E327-1E4A-81CA-F90564189D2B}"/>
-    <hyperlink ref="F123" r:id="rId33" xr:uid="{EEB9B3CF-E3C3-5C44-AB26-E6CCED689413}"/>
-    <hyperlink ref="F124" r:id="rId34" xr:uid="{278D82BB-F204-4E41-A5D2-42C246C2C5F6}"/>
-    <hyperlink ref="F125" r:id="rId35" xr:uid="{9A56AD7A-8DC2-1B4C-B777-7D42244F4D39}"/>
-    <hyperlink ref="F126" r:id="rId36" xr:uid="{A281555C-7C27-DB47-BC08-26D8AD78348E}"/>
-    <hyperlink ref="F133" r:id="rId37" xr:uid="{2F8E0855-90E5-204F-9521-4FC206125599}"/>
-    <hyperlink ref="F145" r:id="rId38" xr:uid="{386838AF-35D3-0C49-AA80-3E13CF5B763B}"/>
-    <hyperlink ref="F146" r:id="rId39" xr:uid="{2A54DB1C-D0D5-1A46-B5B4-2AB3EA25BFD0}"/>
-    <hyperlink ref="F147" r:id="rId40" xr:uid="{629AECC2-B440-5840-93BE-63654BCA2188}"/>
-    <hyperlink ref="G148" r:id="rId41" xr:uid="{0C60883E-E3F2-F443-8FA7-2BD961B72E6F}"/>
-    <hyperlink ref="F149" r:id="rId42" xr:uid="{A05E9319-E2CD-6F4C-A2F6-789D39CE0686}"/>
-    <hyperlink ref="F150" r:id="rId43" xr:uid="{22935E0A-9D44-B54E-9D73-78917652534C}"/>
-    <hyperlink ref="F151" r:id="rId44" xr:uid="{2FB9AF62-D718-8144-9B35-7B77D2BE032B}"/>
-    <hyperlink ref="F152" r:id="rId45" xr:uid="{4E5EFDDA-6883-BF46-9E94-D893494F0F03}"/>
-    <hyperlink ref="F153" r:id="rId46" xr:uid="{83EF0E15-DAD3-2247-8FA2-D7D2E3F0D476}"/>
-    <hyperlink ref="F154" r:id="rId47" xr:uid="{12293028-0860-7B43-AE47-C899F71780FE}"/>
-    <hyperlink ref="F155" r:id="rId48" xr:uid="{13C473DC-2BE8-9747-9940-9621B4D8401D}"/>
-    <hyperlink ref="F156" r:id="rId49" xr:uid="{CC242625-9DEE-9145-8AEC-B442B2117990}"/>
-    <hyperlink ref="F157" r:id="rId50" xr:uid="{C0175F66-06C0-7344-8D20-E2BCDBA1AC97}"/>
-    <hyperlink ref="F158" r:id="rId51" xr:uid="{C907CADD-A43D-5545-B215-F1105030E680}"/>
-    <hyperlink ref="F159" r:id="rId52" xr:uid="{C681EA47-E54B-B34A-B611-F048C453763A}"/>
-    <hyperlink ref="F163" r:id="rId53" xr:uid="{2D048A3B-EE7C-604D-97BC-51B069433511}"/>
-    <hyperlink ref="F164" r:id="rId54" xr:uid="{E3C5F5B5-5535-ED4F-ACA0-6F36390F26CE}"/>
-    <hyperlink ref="F166" r:id="rId55" xr:uid="{42C15DAA-F574-EA43-8847-50AEC943B030}"/>
-    <hyperlink ref="G166" r:id="rId56" xr:uid="{854723C1-43C2-B249-95DE-F73D593B39D5}"/>
-    <hyperlink ref="H166" r:id="rId57" xr:uid="{654F1329-8EC9-084A-87AA-4871C7006B37}"/>
-    <hyperlink ref="I166" r:id="rId58" xr:uid="{C8DB336E-F896-724C-8B08-FB28BD0B86EF}"/>
-    <hyperlink ref="G167" r:id="rId59" xr:uid="{806C5B21-9EBE-F54D-96D0-962331F4FC7D}"/>
-    <hyperlink ref="F198" r:id="rId60" xr:uid="{0BE899F9-B63C-6F49-A85C-026E93E6D75D}"/>
-    <hyperlink ref="G198" r:id="rId61" xr:uid="{867F0619-DB83-4F42-AB0F-1EB115FE6428}"/>
-    <hyperlink ref="H198" r:id="rId62" xr:uid="{57A2339F-7161-F646-A1CC-5A0018A28691}"/>
-    <hyperlink ref="I198" r:id="rId63" xr:uid="{B33161BA-5CD1-3D46-876E-8E8CBC111EF0}"/>
-    <hyperlink ref="F224" r:id="rId64" xr:uid="{239CD0E2-06EC-0C46-B91D-EB396EFC8717}"/>
-    <hyperlink ref="F225" r:id="rId65" xr:uid="{37F5520A-0B94-9749-8BCF-2D7DA9A8CA43}"/>
-    <hyperlink ref="F226" r:id="rId66" xr:uid="{4767BB22-415D-054C-A5B7-2163FB542DFA}"/>
-    <hyperlink ref="F227" r:id="rId67" xr:uid="{D252C2E7-F024-D94A-857C-D62CEEE78395}"/>
-    <hyperlink ref="F233" r:id="rId68" xr:uid="{579C86E0-10EF-1C41-9289-A3B287B3DE21}"/>
-    <hyperlink ref="F236" r:id="rId69" xr:uid="{9CE98C5A-B57A-CD48-968B-FF0B87FB4D70}"/>
-    <hyperlink ref="F238" r:id="rId70" xr:uid="{12E46609-D4CE-1D47-A3A4-3A16B1014403}"/>
+    <hyperlink ref="G8" r:id="rId1" xr:uid="{25AF4313-A10C-CC44-90B4-E990EC0A412E}"/>
+    <hyperlink ref="H15" r:id="rId2" xr:uid="{51A31803-543B-F042-9D3B-3679DAAD568B}"/>
+    <hyperlink ref="F16" r:id="rId3" xr:uid="{727A9275-2686-7442-889C-51AC386F1E1C}"/>
+    <hyperlink ref="F39" r:id="rId4" xr:uid="{946E6E45-8186-3541-886A-5F97268B0D55}"/>
+    <hyperlink ref="F43" r:id="rId5" xr:uid="{A59E0C26-A9AF-3E4B-B859-68F268FF095E}"/>
+    <hyperlink ref="F72" r:id="rId6" xr:uid="{9F06EEB6-24ED-0B41-AAD5-3B58C61D3753}"/>
+    <hyperlink ref="F73" r:id="rId7" xr:uid="{B264B08C-A11A-3642-9876-67380148607A}"/>
+    <hyperlink ref="F80" r:id="rId8" xr:uid="{7BA9C228-B8FF-124F-A3C0-B1242837DCD4}"/>
+    <hyperlink ref="F82" r:id="rId9" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{1A23E2DD-ECEF-8545-A2EA-50C524623C68}"/>
+    <hyperlink ref="F84" r:id="rId10" xr:uid="{27272D8E-9955-644E-987F-78DD8A12785D}"/>
+    <hyperlink ref="F85" r:id="rId11" xr:uid="{E454762E-A6B7-B348-B3AC-92B681F86DE9}"/>
+    <hyperlink ref="F86" r:id="rId12" xr:uid="{CE1D4FF0-3A8B-D840-AD87-D9FA20EE0436}"/>
+    <hyperlink ref="F89" r:id="rId13" xr:uid="{7F309EA1-BEC4-0942-91DD-F7A627A58309}"/>
+    <hyperlink ref="F90" r:id="rId14" xr:uid="{F323FB20-E48F-484A-9E78-8DEC1C94ED6F}"/>
+    <hyperlink ref="F91" r:id="rId15" xr:uid="{5D0EC6CF-2624-D94F-B41A-A76F16F64672}"/>
+    <hyperlink ref="F92" r:id="rId16" xr:uid="{8FA0089C-5A75-A24C-A7C8-B9C5A9B7FB90}"/>
+    <hyperlink ref="F94" r:id="rId17" xr:uid="{51306C15-98D3-C24B-BFBA-D448E75D938F}"/>
+    <hyperlink ref="F95" r:id="rId18" xr:uid="{3D131800-3647-C54B-BF62-63308F8DEFF2}"/>
+    <hyperlink ref="F96" r:id="rId19" xr:uid="{F8B5CF5B-F74C-984A-B9BB-F168B2A81C30}"/>
+    <hyperlink ref="F97" r:id="rId20" xr:uid="{61DB6CF4-6BE1-164C-B688-D48489CD849C}"/>
+    <hyperlink ref="F98" r:id="rId21" xr:uid="{FF279C77-D811-4147-9443-313C3D652445}"/>
+    <hyperlink ref="F101" r:id="rId22" xr:uid="{1562B38D-55AF-0447-A6CA-90C633C5DF93}"/>
+    <hyperlink ref="F102" r:id="rId23" xr:uid="{97186E08-E23D-3B4C-B4CB-6FA60909F879}"/>
+    <hyperlink ref="F103" r:id="rId24" xr:uid="{07152449-8858-B146-BC2A-51333DE87428}"/>
+    <hyperlink ref="F104" r:id="rId25" xr:uid="{DC9FEB7F-3927-5B4D-A0C8-C75010454532}"/>
+    <hyperlink ref="F105" r:id="rId26" xr:uid="{B05A2A41-D255-1D47-AA29-3691C522D4CB}"/>
+    <hyperlink ref="F106" r:id="rId27" xr:uid="{23EB7CD8-1BE5-E842-BBCD-87DDCCFE533A}"/>
+    <hyperlink ref="F115" r:id="rId28" xr:uid="{C46D599E-9B9B-8844-A23B-93CB7D2B4B08}"/>
+    <hyperlink ref="F118" r:id="rId29" xr:uid="{514669EC-937B-FF45-AE80-BD6FD3563A84}"/>
+    <hyperlink ref="F119" r:id="rId30" xr:uid="{1C0DCFC0-629E-6D42-9305-1385FF261DBF}"/>
+    <hyperlink ref="F120" r:id="rId31" xr:uid="{891D149D-C8ED-A047-A45C-AFEE682B486D}"/>
+    <hyperlink ref="F121" r:id="rId32" xr:uid="{2F4A4A9F-D29E-964B-BB60-51CF9DA1FBF1}"/>
+    <hyperlink ref="F122" r:id="rId33" xr:uid="{55149644-FFEB-694B-9276-F370358DEDEF}"/>
+    <hyperlink ref="F123" r:id="rId34" xr:uid="{727ACD72-BC2C-4545-818C-B6ED0631246A}"/>
+    <hyperlink ref="F124" r:id="rId35" xr:uid="{2D048B74-3A09-874C-A0E1-16B6DA6616FC}"/>
+    <hyperlink ref="F125" r:id="rId36" xr:uid="{17C2D1B1-C30F-0441-B2AF-6818DABD15E2}"/>
+    <hyperlink ref="F132" r:id="rId37" xr:uid="{49A9D9BF-28FC-AA47-8767-77B8FB3DE84C}"/>
+    <hyperlink ref="F144" r:id="rId38" xr:uid="{5ECE135C-C299-D043-B29D-5D384B6BAFD0}"/>
+    <hyperlink ref="F145" r:id="rId39" xr:uid="{FBCD15B4-F8B2-AD46-AD24-488362DBFC2F}"/>
+    <hyperlink ref="F146" r:id="rId40" xr:uid="{D7C026FC-2F71-B640-92C7-84C7671CF836}"/>
+    <hyperlink ref="G147" r:id="rId41" xr:uid="{B8167462-222D-694C-8D68-72AF06240D37}"/>
+    <hyperlink ref="F148" r:id="rId42" xr:uid="{94A4DE90-9E53-5144-9A26-528898893071}"/>
+    <hyperlink ref="F149" r:id="rId43" xr:uid="{013401D3-964F-694A-AF7D-8B7F6483B9D0}"/>
+    <hyperlink ref="F150" r:id="rId44" xr:uid="{827A3F42-8866-CE44-9982-289976C7C848}"/>
+    <hyperlink ref="F151" r:id="rId45" xr:uid="{F49BCEC7-DBDB-F142-914C-8B3D58BA7263}"/>
+    <hyperlink ref="F152" r:id="rId46" xr:uid="{E0354966-3D34-8D4D-B6B9-6E1C684309B4}"/>
+    <hyperlink ref="F153" r:id="rId47" xr:uid="{97790F6C-B24E-5843-A6E7-EC143F51DD0C}"/>
+    <hyperlink ref="F154" r:id="rId48" xr:uid="{78086053-FF36-7E4E-B13D-616800656A97}"/>
+    <hyperlink ref="F155" r:id="rId49" xr:uid="{0640B3C7-2257-EA46-B04F-35DF98D40F89}"/>
+    <hyperlink ref="F156" r:id="rId50" xr:uid="{E0365EC4-A3EC-014F-B6F7-C67407A86FE6}"/>
+    <hyperlink ref="F157" r:id="rId51" xr:uid="{0B503E60-43B7-1940-835F-693A5BCBDC9C}"/>
+    <hyperlink ref="F158" r:id="rId52" xr:uid="{3C1BD9B7-FCBE-694C-AB73-68D9437AFCD5}"/>
+    <hyperlink ref="F162" r:id="rId53" xr:uid="{F3103CF5-9386-3F4C-9B5C-448C4989EEE5}"/>
+    <hyperlink ref="F163" r:id="rId54" xr:uid="{DB3AC30F-17B7-A446-BCD7-31DEE64B9DE3}"/>
+    <hyperlink ref="F165" r:id="rId55" xr:uid="{293EEC14-0D45-FB42-9063-2FB3E0C6E772}"/>
+    <hyperlink ref="G165" r:id="rId56" xr:uid="{88B5EFA3-2E98-2149-97C1-106AAEC4BDA7}"/>
+    <hyperlink ref="H165" r:id="rId57" xr:uid="{C2974DB9-A2DB-0942-ABFB-3DF04EE25343}"/>
+    <hyperlink ref="I165" r:id="rId58" xr:uid="{D557C465-84D9-804B-8754-932DB7D88925}"/>
+    <hyperlink ref="G166" r:id="rId59" xr:uid="{9BAF91E2-9CF6-5C4E-BA73-998B00F8B236}"/>
+    <hyperlink ref="F194" r:id="rId60" xr:uid="{95C34E5D-989E-7940-A09F-BEF48B7FB87D}"/>
+    <hyperlink ref="F197" r:id="rId61" xr:uid="{02A422C3-79A4-5C46-A0E9-174F3E919621}"/>
+    <hyperlink ref="G197" r:id="rId62" xr:uid="{62E91E89-3BC5-3145-AE91-35DC0B71EF44}"/>
+    <hyperlink ref="H197" r:id="rId63" xr:uid="{F7DC09BE-D493-464F-863B-C7A5B3C94A52}"/>
+    <hyperlink ref="I197" r:id="rId64" xr:uid="{DFB622B9-64B7-5445-860E-4E3F4E516667}"/>
+    <hyperlink ref="F223" r:id="rId65" xr:uid="{CD99FCD6-1338-F744-B98F-4746DF49B204}"/>
+    <hyperlink ref="F224" r:id="rId66" xr:uid="{B14C9C4A-888B-BE46-97C7-C80AF3B0439D}"/>
+    <hyperlink ref="F225" r:id="rId67" xr:uid="{1DC108ED-0A20-084F-88C0-C534FD38D676}"/>
+    <hyperlink ref="F226" r:id="rId68" xr:uid="{48508E57-5996-4944-8979-C214C91F96A7}"/>
+    <hyperlink ref="F232" r:id="rId69" xr:uid="{4C74D948-EA69-2744-9948-518521BBE1A4}"/>
+    <hyperlink ref="F235" r:id="rId70" xr:uid="{F9AF1FA6-B598-B144-8ACD-02DB70DCD80A}"/>
+    <hyperlink ref="F237" r:id="rId71" xr:uid="{7BE8A8EB-C78E-F54D-BFB0-80BEED0E6466}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F219698D-EC15-6A45-96FD-6A961A544ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E184E2-56EE-3F47-BB51-D7A688C6397A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33380" windowHeight="21580" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3024" uniqueCount="1067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3025" uniqueCount="1067">
   <si>
     <t>Household Name</t>
   </si>
@@ -8605,7 +8605,9 @@
       <c r="B238" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="C238" s="2"/>
+      <c r="C238" s="2" t="s">
+        <v>760</v>
+      </c>
       <c r="D238" s="2" t="s">
         <v>980</v>
       </c>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E184E2-56EE-3F47-BB51-D7A688C6397A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8CA27C-B8BD-0244-A5FE-B3677D97DAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33380" windowHeight="21580" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -7726,7 +7726,7 @@
         <v>757</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>691</v>
+        <v>758</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>1060</v>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8CA27C-B8BD-0244-A5FE-B3677D97DAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45145E94-B215-B942-B257-82E1C9F72AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33380" windowHeight="21580" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3025" uniqueCount="1067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3028" uniqueCount="1068">
   <si>
     <t>Household Name</t>
   </si>
@@ -3235,17 +3235,20 @@
     <t>2 tickets each</t>
   </si>
   <si>
-    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view</t>
+    <t>Brand Napa Valley $ Sponsorship 5/7/2026 | Opportunity | Salesforce</t>
   </si>
   <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uCpUlYAK/view</t>
+  </si>
+  <si>
+    <t>Chopard</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3295,6 +3298,12 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3317,13 +3326,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3659,12 +3669,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7894B4-148E-174D-AE8B-E6DE441B89B0}">
-  <dimension ref="A1:I238"/>
+  <dimension ref="A1:I240"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="37.1640625" customWidth="1"/>
-    <col min="6" max="6" width="92.1640625" customWidth="1"/>
-    <col min="7" max="7" width="57.83203125" customWidth="1"/>
+    <col min="1" max="10" width="31.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -8537,62 +8545,62 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="2" t="s">
-        <v>508</v>
+        <v>164</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>937</v>
+        <v>509</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>938</v>
+        <v>510</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E235" s="2"/>
-      <c r="F235" s="1" t="s">
-        <v>1054</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F235" s="2"/>
       <c r="G235" s="2"/>
       <c r="H235" s="2"/>
       <c r="I235" s="2"/>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
-        <v>164</v>
+        <v>1056</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>509</v>
+        <v>739</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>510</v>
+        <v>740</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E236" s="2" t="s">
-        <v>1055</v>
-      </c>
-      <c r="F236" s="2"/>
+        <v>980</v>
+      </c>
+      <c r="E236" s="2"/>
+      <c r="F236" s="1" t="s">
+        <v>1057</v>
+      </c>
       <c r="G236" s="2"/>
       <c r="H236" s="2"/>
       <c r="I236" s="2"/>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
-        <v>1056</v>
+        <v>609</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="C237" s="4" t="s">
-        <v>740</v>
+        <v>759</v>
+      </c>
+      <c r="C237" s="6" t="s">
+        <v>760</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>980</v>
       </c>
       <c r="E237" s="2"/>
-      <c r="F237" s="1" t="s">
-        <v>1057</v>
+      <c r="F237" s="2" t="s">
+        <v>611</v>
       </c>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
@@ -8600,99 +8608,130 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
-        <v>609</v>
+        <v>1067</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>760</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C238" s="2"/>
       <c r="D238" s="2" t="s">
-        <v>980</v>
+        <v>155</v>
       </c>
       <c r="E238" s="2"/>
-      <c r="F238" s="2" t="s">
-        <v>611</v>
+      <c r="F238" s="1" t="s">
+        <v>659</v>
       </c>
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
       <c r="I238" s="2"/>
     </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A239" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C239" s="4"/>
+      <c r="D239" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E239" s="2"/>
+      <c r="F239" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G239" s="2"/>
+      <c r="H239" s="2"/>
+      <c r="I239" s="2"/>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A240" s="2"/>
+      <c r="B240" s="2"/>
+      <c r="C240" s="2"/>
+      <c r="D240" s="2"/>
+      <c r="E240" s="2"/>
+      <c r="F240" s="2"/>
+      <c r="G240" s="2"/>
+      <c r="H240" s="2"/>
+      <c r="I240" s="2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G8" r:id="rId1" xr:uid="{25AF4313-A10C-CC44-90B4-E990EC0A412E}"/>
-    <hyperlink ref="H15" r:id="rId2" xr:uid="{51A31803-543B-F042-9D3B-3679DAAD568B}"/>
-    <hyperlink ref="F16" r:id="rId3" xr:uid="{727A9275-2686-7442-889C-51AC386F1E1C}"/>
-    <hyperlink ref="F39" r:id="rId4" xr:uid="{946E6E45-8186-3541-886A-5F97268B0D55}"/>
-    <hyperlink ref="F43" r:id="rId5" xr:uid="{A59E0C26-A9AF-3E4B-B859-68F268FF095E}"/>
-    <hyperlink ref="F72" r:id="rId6" xr:uid="{9F06EEB6-24ED-0B41-AAD5-3B58C61D3753}"/>
-    <hyperlink ref="F73" r:id="rId7" xr:uid="{B264B08C-A11A-3642-9876-67380148607A}"/>
-    <hyperlink ref="F80" r:id="rId8" xr:uid="{7BA9C228-B8FF-124F-A3C0-B1242837DCD4}"/>
-    <hyperlink ref="F82" r:id="rId9" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{1A23E2DD-ECEF-8545-A2EA-50C524623C68}"/>
-    <hyperlink ref="F84" r:id="rId10" xr:uid="{27272D8E-9955-644E-987F-78DD8A12785D}"/>
-    <hyperlink ref="F85" r:id="rId11" xr:uid="{E454762E-A6B7-B348-B3AC-92B681F86DE9}"/>
-    <hyperlink ref="F86" r:id="rId12" xr:uid="{CE1D4FF0-3A8B-D840-AD87-D9FA20EE0436}"/>
-    <hyperlink ref="F89" r:id="rId13" xr:uid="{7F309EA1-BEC4-0942-91DD-F7A627A58309}"/>
-    <hyperlink ref="F90" r:id="rId14" xr:uid="{F323FB20-E48F-484A-9E78-8DEC1C94ED6F}"/>
-    <hyperlink ref="F91" r:id="rId15" xr:uid="{5D0EC6CF-2624-D94F-B41A-A76F16F64672}"/>
-    <hyperlink ref="F92" r:id="rId16" xr:uid="{8FA0089C-5A75-A24C-A7C8-B9C5A9B7FB90}"/>
-    <hyperlink ref="F94" r:id="rId17" xr:uid="{51306C15-98D3-C24B-BFBA-D448E75D938F}"/>
-    <hyperlink ref="F95" r:id="rId18" xr:uid="{3D131800-3647-C54B-BF62-63308F8DEFF2}"/>
-    <hyperlink ref="F96" r:id="rId19" xr:uid="{F8B5CF5B-F74C-984A-B9BB-F168B2A81C30}"/>
-    <hyperlink ref="F97" r:id="rId20" xr:uid="{61DB6CF4-6BE1-164C-B688-D48489CD849C}"/>
-    <hyperlink ref="F98" r:id="rId21" xr:uid="{FF279C77-D811-4147-9443-313C3D652445}"/>
-    <hyperlink ref="F101" r:id="rId22" xr:uid="{1562B38D-55AF-0447-A6CA-90C633C5DF93}"/>
-    <hyperlink ref="F102" r:id="rId23" xr:uid="{97186E08-E23D-3B4C-B4CB-6FA60909F879}"/>
-    <hyperlink ref="F103" r:id="rId24" xr:uid="{07152449-8858-B146-BC2A-51333DE87428}"/>
-    <hyperlink ref="F104" r:id="rId25" xr:uid="{DC9FEB7F-3927-5B4D-A0C8-C75010454532}"/>
-    <hyperlink ref="F105" r:id="rId26" xr:uid="{B05A2A41-D255-1D47-AA29-3691C522D4CB}"/>
-    <hyperlink ref="F106" r:id="rId27" xr:uid="{23EB7CD8-1BE5-E842-BBCD-87DDCCFE533A}"/>
-    <hyperlink ref="F115" r:id="rId28" xr:uid="{C46D599E-9B9B-8844-A23B-93CB7D2B4B08}"/>
-    <hyperlink ref="F118" r:id="rId29" xr:uid="{514669EC-937B-FF45-AE80-BD6FD3563A84}"/>
-    <hyperlink ref="F119" r:id="rId30" xr:uid="{1C0DCFC0-629E-6D42-9305-1385FF261DBF}"/>
-    <hyperlink ref="F120" r:id="rId31" xr:uid="{891D149D-C8ED-A047-A45C-AFEE682B486D}"/>
-    <hyperlink ref="F121" r:id="rId32" xr:uid="{2F4A4A9F-D29E-964B-BB60-51CF9DA1FBF1}"/>
-    <hyperlink ref="F122" r:id="rId33" xr:uid="{55149644-FFEB-694B-9276-F370358DEDEF}"/>
-    <hyperlink ref="F123" r:id="rId34" xr:uid="{727ACD72-BC2C-4545-818C-B6ED0631246A}"/>
-    <hyperlink ref="F124" r:id="rId35" xr:uid="{2D048B74-3A09-874C-A0E1-16B6DA6616FC}"/>
-    <hyperlink ref="F125" r:id="rId36" xr:uid="{17C2D1B1-C30F-0441-B2AF-6818DABD15E2}"/>
-    <hyperlink ref="F132" r:id="rId37" xr:uid="{49A9D9BF-28FC-AA47-8767-77B8FB3DE84C}"/>
-    <hyperlink ref="F144" r:id="rId38" xr:uid="{5ECE135C-C299-D043-B29D-5D384B6BAFD0}"/>
-    <hyperlink ref="F145" r:id="rId39" xr:uid="{FBCD15B4-F8B2-AD46-AD24-488362DBFC2F}"/>
-    <hyperlink ref="F146" r:id="rId40" xr:uid="{D7C026FC-2F71-B640-92C7-84C7671CF836}"/>
-    <hyperlink ref="G147" r:id="rId41" xr:uid="{B8167462-222D-694C-8D68-72AF06240D37}"/>
-    <hyperlink ref="F148" r:id="rId42" xr:uid="{94A4DE90-9E53-5144-9A26-528898893071}"/>
-    <hyperlink ref="F149" r:id="rId43" xr:uid="{013401D3-964F-694A-AF7D-8B7F6483B9D0}"/>
-    <hyperlink ref="F150" r:id="rId44" xr:uid="{827A3F42-8866-CE44-9982-289976C7C848}"/>
-    <hyperlink ref="F151" r:id="rId45" xr:uid="{F49BCEC7-DBDB-F142-914C-8B3D58BA7263}"/>
-    <hyperlink ref="F152" r:id="rId46" xr:uid="{E0354966-3D34-8D4D-B6B9-6E1C684309B4}"/>
-    <hyperlink ref="F153" r:id="rId47" xr:uid="{97790F6C-B24E-5843-A6E7-EC143F51DD0C}"/>
-    <hyperlink ref="F154" r:id="rId48" xr:uid="{78086053-FF36-7E4E-B13D-616800656A97}"/>
-    <hyperlink ref="F155" r:id="rId49" xr:uid="{0640B3C7-2257-EA46-B04F-35DF98D40F89}"/>
-    <hyperlink ref="F156" r:id="rId50" xr:uid="{E0365EC4-A3EC-014F-B6F7-C67407A86FE6}"/>
-    <hyperlink ref="F157" r:id="rId51" xr:uid="{0B503E60-43B7-1940-835F-693A5BCBDC9C}"/>
-    <hyperlink ref="F158" r:id="rId52" xr:uid="{3C1BD9B7-FCBE-694C-AB73-68D9437AFCD5}"/>
-    <hyperlink ref="F162" r:id="rId53" xr:uid="{F3103CF5-9386-3F4C-9B5C-448C4989EEE5}"/>
-    <hyperlink ref="F163" r:id="rId54" xr:uid="{DB3AC30F-17B7-A446-BCD7-31DEE64B9DE3}"/>
-    <hyperlink ref="F165" r:id="rId55" xr:uid="{293EEC14-0D45-FB42-9063-2FB3E0C6E772}"/>
-    <hyperlink ref="G165" r:id="rId56" xr:uid="{88B5EFA3-2E98-2149-97C1-106AAEC4BDA7}"/>
-    <hyperlink ref="H165" r:id="rId57" xr:uid="{C2974DB9-A2DB-0942-ABFB-3DF04EE25343}"/>
-    <hyperlink ref="I165" r:id="rId58" xr:uid="{D557C465-84D9-804B-8754-932DB7D88925}"/>
-    <hyperlink ref="G166" r:id="rId59" xr:uid="{9BAF91E2-9CF6-5C4E-BA73-998B00F8B236}"/>
-    <hyperlink ref="F194" r:id="rId60" xr:uid="{95C34E5D-989E-7940-A09F-BEF48B7FB87D}"/>
-    <hyperlink ref="F197" r:id="rId61" xr:uid="{02A422C3-79A4-5C46-A0E9-174F3E919621}"/>
-    <hyperlink ref="G197" r:id="rId62" xr:uid="{62E91E89-3BC5-3145-AE91-35DC0B71EF44}"/>
-    <hyperlink ref="H197" r:id="rId63" xr:uid="{F7DC09BE-D493-464F-863B-C7A5B3C94A52}"/>
-    <hyperlink ref="I197" r:id="rId64" xr:uid="{DFB622B9-64B7-5445-860E-4E3F4E516667}"/>
-    <hyperlink ref="F223" r:id="rId65" xr:uid="{CD99FCD6-1338-F744-B98F-4746DF49B204}"/>
-    <hyperlink ref="F224" r:id="rId66" xr:uid="{B14C9C4A-888B-BE46-97C7-C80AF3B0439D}"/>
-    <hyperlink ref="F225" r:id="rId67" xr:uid="{1DC108ED-0A20-084F-88C0-C534FD38D676}"/>
-    <hyperlink ref="F226" r:id="rId68" xr:uid="{48508E57-5996-4944-8979-C214C91F96A7}"/>
-    <hyperlink ref="F232" r:id="rId69" xr:uid="{4C74D948-EA69-2744-9948-518521BBE1A4}"/>
-    <hyperlink ref="F235" r:id="rId70" xr:uid="{F9AF1FA6-B598-B144-8ACD-02DB70DCD80A}"/>
-    <hyperlink ref="F237" r:id="rId71" xr:uid="{7BE8A8EB-C78E-F54D-BFB0-80BEED0E6466}"/>
+    <hyperlink ref="G8" r:id="rId1" xr:uid="{0683D9D2-E449-D14E-A74D-0DB016EBB052}"/>
+    <hyperlink ref="H15" r:id="rId2" xr:uid="{C064B916-8698-9F40-B06E-2C592D364D34}"/>
+    <hyperlink ref="F16" r:id="rId3" xr:uid="{2F8D750D-C0AA-B64F-ADAE-15C4152E029D}"/>
+    <hyperlink ref="F39" r:id="rId4" xr:uid="{2F32A917-1D80-E545-9382-C607A2444003}"/>
+    <hyperlink ref="F43" r:id="rId5" xr:uid="{9C987C36-0066-894B-98F1-92EF9F6E8AA6}"/>
+    <hyperlink ref="F72" r:id="rId6" xr:uid="{0B5EA83E-5115-4B4A-B03A-60D95DC171F8}"/>
+    <hyperlink ref="F73" r:id="rId7" xr:uid="{4B28D6A5-1E35-1146-BC90-94AA12238D76}"/>
+    <hyperlink ref="F80" r:id="rId8" xr:uid="{22514270-4364-6B42-A790-B7971176B467}"/>
+    <hyperlink ref="F82" r:id="rId9" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{78047D3D-F110-784B-8F9F-C8658E6828FF}"/>
+    <hyperlink ref="F84" r:id="rId10" xr:uid="{87F82FE0-588E-DC49-A4DA-A4E4B80DEDA7}"/>
+    <hyperlink ref="F85" r:id="rId11" xr:uid="{5D4B3A60-D84D-234C-BF63-797B6D2C11A3}"/>
+    <hyperlink ref="F86" r:id="rId12" xr:uid="{320672D6-3A49-7144-A9B0-99E2897B70A6}"/>
+    <hyperlink ref="F89" r:id="rId13" xr:uid="{F2906274-9EF0-B047-BED8-BBE7C39510D1}"/>
+    <hyperlink ref="F90" r:id="rId14" xr:uid="{A56BE9F4-82D4-204A-AA33-E4958ECEC498}"/>
+    <hyperlink ref="F91" r:id="rId15" xr:uid="{11ED5116-2C55-A841-9828-2A4654F92AC8}"/>
+    <hyperlink ref="F92" r:id="rId16" xr:uid="{BEBFDF24-8751-1A41-9147-E2C953CFDBAE}"/>
+    <hyperlink ref="F94" r:id="rId17" xr:uid="{1E5C3452-AD2B-554B-8E81-8B321160E184}"/>
+    <hyperlink ref="F95" r:id="rId18" xr:uid="{38019B70-E174-A54F-9611-8471729E6B13}"/>
+    <hyperlink ref="F96" r:id="rId19" xr:uid="{C2330617-7CD6-A34C-901F-CC9393D8C2F9}"/>
+    <hyperlink ref="F97" r:id="rId20" xr:uid="{3CAD21A6-E921-9C4E-A862-2AF811FFE9EC}"/>
+    <hyperlink ref="F98" r:id="rId21" xr:uid="{7F59135C-6174-D548-94CC-B1B9A9187267}"/>
+    <hyperlink ref="F101" r:id="rId22" xr:uid="{D6EB6267-FC12-C444-9921-E73DE6836EC3}"/>
+    <hyperlink ref="F102" r:id="rId23" xr:uid="{0935F4F5-396A-EC40-BFC3-E5D318CDAE77}"/>
+    <hyperlink ref="F103" r:id="rId24" xr:uid="{2A7B762A-8F2A-E543-8456-D303C1572F4C}"/>
+    <hyperlink ref="F104" r:id="rId25" xr:uid="{2E5B3B20-CD26-A847-8491-A1FB5FE0E477}"/>
+    <hyperlink ref="F105" r:id="rId26" xr:uid="{243B62D3-5E2A-4549-A595-3AC6D3C8E90C}"/>
+    <hyperlink ref="F106" r:id="rId27" xr:uid="{043113E1-FE50-6546-BB31-ACB9444E1102}"/>
+    <hyperlink ref="F115" r:id="rId28" xr:uid="{E45EF3E2-25E5-1243-9324-EDFC24D03084}"/>
+    <hyperlink ref="F118" r:id="rId29" xr:uid="{43EFA958-C592-4E4C-9EF0-22E552EAABED}"/>
+    <hyperlink ref="F119" r:id="rId30" xr:uid="{B4692FAD-C9AA-CC45-A5FD-8C2ADD56353B}"/>
+    <hyperlink ref="F120" r:id="rId31" xr:uid="{29ADFB9B-CAC4-464D-B71A-8908A431D3BE}"/>
+    <hyperlink ref="F121" r:id="rId32" xr:uid="{3AB01097-9FE4-4444-A720-A967A50DFC16}"/>
+    <hyperlink ref="F122" r:id="rId33" xr:uid="{03CD05A9-969B-1F46-B39E-A2A22C06782E}"/>
+    <hyperlink ref="F123" r:id="rId34" xr:uid="{6610C6DE-A67B-694A-B81A-0C01C720FD49}"/>
+    <hyperlink ref="F124" r:id="rId35" xr:uid="{F3E51191-D2B0-F442-AE09-D6C3DACBB080}"/>
+    <hyperlink ref="F125" r:id="rId36" xr:uid="{D26FEFE1-716E-494A-A8F4-47A5E8EAE9AC}"/>
+    <hyperlink ref="F132" r:id="rId37" xr:uid="{D6A5DF21-9B11-7643-A9AB-688C86374D54}"/>
+    <hyperlink ref="F144" r:id="rId38" xr:uid="{FE6B260E-C5FD-B544-9FE6-BB070AC76BAC}"/>
+    <hyperlink ref="F145" r:id="rId39" xr:uid="{533D6A3C-2ED6-7D4D-A05C-253DFB9389EF}"/>
+    <hyperlink ref="F146" r:id="rId40" xr:uid="{37010ECC-A790-CE41-9AF1-9F2CF301B4CD}"/>
+    <hyperlink ref="G147" r:id="rId41" xr:uid="{27835BD6-FEB3-F846-95A5-30FE8261681D}"/>
+    <hyperlink ref="F148" r:id="rId42" xr:uid="{6D5EFC6A-47D8-BD4C-8CC6-A82DEE812A6B}"/>
+    <hyperlink ref="F149" r:id="rId43" xr:uid="{B32D2699-53DE-7B40-9DF3-9AA3AC25487B}"/>
+    <hyperlink ref="F150" r:id="rId44" xr:uid="{CF678504-1C6F-3C49-921A-757AE6D690F0}"/>
+    <hyperlink ref="F151" r:id="rId45" xr:uid="{14E2D30C-5621-8848-896A-D174AC72A30D}"/>
+    <hyperlink ref="F152" r:id="rId46" xr:uid="{5B7161A8-D04C-C04A-9154-4DE2BC49300F}"/>
+    <hyperlink ref="F153" r:id="rId47" xr:uid="{DE82C0C9-3777-3A45-ABF0-0D3B389DE9BF}"/>
+    <hyperlink ref="F154" r:id="rId48" xr:uid="{2991DC46-849B-984D-82D4-C9BA46965400}"/>
+    <hyperlink ref="F155" r:id="rId49" xr:uid="{7C158869-62D0-914E-B9AB-86E29C04AD92}"/>
+    <hyperlink ref="F156" r:id="rId50" xr:uid="{3303754A-9602-0B40-B591-8078B1F2F400}"/>
+    <hyperlink ref="F157" r:id="rId51" xr:uid="{58A58969-37C9-0C42-A889-70098A0FBE9D}"/>
+    <hyperlink ref="F158" r:id="rId52" xr:uid="{AF69F823-E536-F247-8E7B-6CFD11089A8A}"/>
+    <hyperlink ref="F162" r:id="rId53" xr:uid="{F31366DF-5211-F04D-A3E3-415D74F495B2}"/>
+    <hyperlink ref="F163" r:id="rId54" xr:uid="{E6ABB46E-002B-C94C-9249-F6F982A00EA2}"/>
+    <hyperlink ref="F165" r:id="rId55" xr:uid="{C0AB3CFE-0911-B14F-808A-20B4FA975FE9}"/>
+    <hyperlink ref="G165" r:id="rId56" xr:uid="{85BC2734-BAD4-5242-8942-022D6A8A0AB9}"/>
+    <hyperlink ref="H165" r:id="rId57" xr:uid="{62C652A1-E606-A542-A8C1-1855C5659D31}"/>
+    <hyperlink ref="I165" r:id="rId58" xr:uid="{A1F9D4B1-0098-8743-B801-C97D1A6FBF84}"/>
+    <hyperlink ref="G166" r:id="rId59" xr:uid="{2562845C-6CD3-7B42-9B31-205713D8E2E0}"/>
+    <hyperlink ref="F194" r:id="rId60" xr:uid="{0D836360-7CB7-344A-9819-A95E0857CEF9}"/>
+    <hyperlink ref="F197" r:id="rId61" xr:uid="{FEAA8EC6-0BB7-0B49-86B1-1FDB70D4D0ED}"/>
+    <hyperlink ref="G197" r:id="rId62" xr:uid="{B96528EE-11C9-224A-8BC8-444B55371645}"/>
+    <hyperlink ref="H197" r:id="rId63" xr:uid="{A3464ECD-516F-1A40-935A-F1BBC86ABFC2}"/>
+    <hyperlink ref="I197" r:id="rId64" xr:uid="{42DBFFDE-D897-2A41-AB5C-D670CB0A7174}"/>
+    <hyperlink ref="F204" r:id="rId65" xr:uid="{597F03BA-8CD2-AF44-8000-E2256EFD75D4}"/>
+    <hyperlink ref="G204" r:id="rId66" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view" xr:uid="{4745DF9D-2D6F-F446-BDEB-E60DD029CC76}"/>
+    <hyperlink ref="F223" r:id="rId67" xr:uid="{FC10816C-2792-4445-A1D5-E7A3FCA5BCFA}"/>
+    <hyperlink ref="F224" r:id="rId68" xr:uid="{21356ED0-4038-A64B-B5C7-F1A5ECBD6B4F}"/>
+    <hyperlink ref="F225" r:id="rId69" xr:uid="{C98B9432-0B63-6C4B-A95F-958236A82FD7}"/>
+    <hyperlink ref="F226" r:id="rId70" xr:uid="{97F6673B-F524-A74F-BDE6-AD3D0795AC67}"/>
+    <hyperlink ref="F232" r:id="rId71" xr:uid="{2C6C9B8B-F83A-8C41-8CBF-97CCC040B769}"/>
+    <hyperlink ref="F236" r:id="rId72" xr:uid="{5A81C910-9073-D34C-B683-DF512DEB8CA2}"/>
+    <hyperlink ref="F238" r:id="rId73" xr:uid="{A5272048-42B7-0F40-89B5-1A1DB1873DCC}"/>
+    <hyperlink ref="F239" r:id="rId74" xr:uid="{71988E24-3B2F-7845-8475-D8DDB1F8F397}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45145E94-B215-B942-B257-82E1C9F72AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9880C3B-5A85-2D42-BE5C-395295CE1560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="33380" windowHeight="21580" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
+    <workbookView xWindow="-20" yWindow="1760" windowWidth="33380" windowHeight="21580" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
   <sheets>
     <sheet name="xlsx" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3028" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3033" uniqueCount="1068">
   <si>
     <t>Household Name</t>
   </si>
@@ -8613,7 +8613,9 @@
       <c r="B238" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C238" s="2"/>
+      <c r="C238" s="2" t="s">
+        <v>256</v>
+      </c>
       <c r="D238" s="2" t="s">
         <v>155</v>
       </c>
@@ -8632,7 +8634,9 @@
       <c r="B239" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="C239" s="4"/>
+      <c r="C239" s="4" t="s">
+        <v>634</v>
+      </c>
       <c r="D239" s="2" t="s">
         <v>155</v>
       </c>
@@ -8645,10 +8649,16 @@
       <c r="I239" s="2"/>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A240" s="2"/>
-      <c r="B240" s="2"/>
+      <c r="A240" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>937</v>
+      </c>
       <c r="C240" s="2"/>
-      <c r="D240" s="2"/>
+      <c r="D240" s="2" t="s">
+        <v>167</v>
+      </c>
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9880C3B-5A85-2D42-BE5C-395295CE1560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108B3554-537F-4D4E-8AFE-A7F97E78A69D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20" yWindow="1760" windowWidth="33380" windowHeight="21580" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3033" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3034" uniqueCount="1069">
   <si>
     <t>Household Name</t>
   </si>
@@ -3242,13 +3242,16 @@
   </si>
   <si>
     <t>Chopard</t>
+  </si>
+  <si>
+    <t>"x=80.95, y=66.31</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3304,6 +3307,12 @@
       <name val="Menlo"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3326,7 +3335,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3334,6 +3343,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -8655,7 +8665,9 @@
       <c r="B240" s="2" t="s">
         <v>937</v>
       </c>
-      <c r="C240" s="2"/>
+      <c r="C240" s="7" t="s">
+        <v>1068</v>
+      </c>
       <c r="D240" s="2" t="s">
         <v>167</v>
       </c>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108B3554-537F-4D4E-8AFE-A7F97E78A69D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6428CC3B-7DD2-F147-802A-BFC40032139D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20" yWindow="1760" windowWidth="33380" windowHeight="21580" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3034" uniqueCount="1069">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3034" uniqueCount="1068">
   <si>
     <t>Household Name</t>
   </si>
@@ -3242,9 +3242,6 @@
   </si>
   <si>
     <t>Chopard</t>
-  </si>
-  <si>
-    <t>"x=80.95, y=66.31</t>
   </si>
 </sst>
 </file>
@@ -8666,7 +8663,7 @@
         <v>937</v>
       </c>
       <c r="C240" s="7" t="s">
-        <v>1068</v>
+        <v>938</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>167</v>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6428CC3B-7DD2-F147-802A-BFC40032139D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F95B8B8-CCA7-934D-819D-4E59504174C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="1760" windowWidth="33380" windowHeight="21580" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
+    <workbookView xWindow="-31960" yWindow="500" windowWidth="33380" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
   <sheets>
     <sheet name="xlsx" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3034" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3035" uniqueCount="1075">
   <si>
     <t>Household Name</t>
   </si>
@@ -3242,13 +3242,34 @@
   </si>
   <si>
     <t>Chopard</t>
+  </si>
+  <si>
+    <t>Half Jennifer Ledfors/Half Sold Online</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000w7PJfYAM/view</t>
+  </si>
+  <si>
+    <t>Chuck Reiter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sold Offline </t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000w8AGvYAM/view</t>
+  </si>
+  <si>
+    <t>Potential table for Manchester Grand Hyatt</t>
+  </si>
+  <si>
+    <t>Larry Paulson</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3304,12 +3325,6 @@
       <name val="Menlo"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3332,7 +3347,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3340,7 +3355,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3678,9 +3692,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7894B4-148E-174D-AE8B-E6DE441B89B0}">
   <dimension ref="A1:I240"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="10" width="31.6640625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
@@ -8396,7 +8407,7 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" s="2" t="s">
-        <v>709</v>
+        <v>1068</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>710</v>
@@ -8408,7 +8419,9 @@
         <v>569</v>
       </c>
       <c r="E227" s="2"/>
-      <c r="F227" s="2"/>
+      <c r="F227" s="1" t="s">
+        <v>1069</v>
+      </c>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
       <c r="I227" s="2"/>
@@ -8552,7 +8565,7 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="2" t="s">
-        <v>164</v>
+        <v>1070</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>509</v>
@@ -8561,32 +8574,32 @@
         <v>510</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E235" s="2" t="s">
-        <v>1055</v>
-      </c>
-      <c r="F235" s="2"/>
+        <v>1071</v>
+      </c>
+      <c r="E235" s="2"/>
+      <c r="F235" s="1" t="s">
+        <v>1072</v>
+      </c>
       <c r="G235" s="2"/>
       <c r="H235" s="2"/>
       <c r="I235" s="2"/>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
-        <v>1056</v>
+        <v>609</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="C236" s="4" t="s">
-        <v>740</v>
+        <v>759</v>
+      </c>
+      <c r="C236" s="6" t="s">
+        <v>760</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>980</v>
       </c>
       <c r="E236" s="2"/>
-      <c r="F236" s="1" t="s">
-        <v>1057</v>
+      <c r="F236" s="2" t="s">
+        <v>611</v>
       </c>
       <c r="G236" s="2"/>
       <c r="H236" s="2"/>
@@ -8594,20 +8607,20 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
-        <v>609</v>
+        <v>1067</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="C237" s="6" t="s">
-        <v>760</v>
+        <v>255</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>256</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>980</v>
+        <v>155</v>
       </c>
       <c r="E237" s="2"/>
-      <c r="F237" s="2" t="s">
-        <v>611</v>
+      <c r="F237" s="1" t="s">
+        <v>659</v>
       </c>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
@@ -8615,20 +8628,20 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
-        <v>1067</v>
+        <v>508</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>256</v>
+        <v>633</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>634</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E238" s="2"/>
       <c r="F238" s="1" t="s">
-        <v>659</v>
+        <v>1054</v>
       </c>
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
@@ -8636,37 +8649,37 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A239" s="2" t="s">
-        <v>508</v>
+        <v>164</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="C239" s="4" t="s">
-        <v>634</v>
+        <v>937</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>938</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E239" s="2"/>
-      <c r="F239" s="1" t="s">
-        <v>1054</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F239" s="2"/>
       <c r="G239" s="2"/>
       <c r="H239" s="2"/>
       <c r="I239" s="2"/>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
-        <v>164</v>
+        <v>1074</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>937</v>
-      </c>
-      <c r="C240" s="7" t="s">
-        <v>938</v>
+        <v>966</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>967</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>167</v>
+        <v>1071</v>
       </c>
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
@@ -8677,80 +8690,81 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G8" r:id="rId1" xr:uid="{0683D9D2-E449-D14E-A74D-0DB016EBB052}"/>
-    <hyperlink ref="H15" r:id="rId2" xr:uid="{C064B916-8698-9F40-B06E-2C592D364D34}"/>
-    <hyperlink ref="F16" r:id="rId3" xr:uid="{2F8D750D-C0AA-B64F-ADAE-15C4152E029D}"/>
-    <hyperlink ref="F39" r:id="rId4" xr:uid="{2F32A917-1D80-E545-9382-C607A2444003}"/>
-    <hyperlink ref="F43" r:id="rId5" xr:uid="{9C987C36-0066-894B-98F1-92EF9F6E8AA6}"/>
-    <hyperlink ref="F72" r:id="rId6" xr:uid="{0B5EA83E-5115-4B4A-B03A-60D95DC171F8}"/>
-    <hyperlink ref="F73" r:id="rId7" xr:uid="{4B28D6A5-1E35-1146-BC90-94AA12238D76}"/>
-    <hyperlink ref="F80" r:id="rId8" xr:uid="{22514270-4364-6B42-A790-B7971176B467}"/>
-    <hyperlink ref="F82" r:id="rId9" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{78047D3D-F110-784B-8F9F-C8658E6828FF}"/>
-    <hyperlink ref="F84" r:id="rId10" xr:uid="{87F82FE0-588E-DC49-A4DA-A4E4B80DEDA7}"/>
-    <hyperlink ref="F85" r:id="rId11" xr:uid="{5D4B3A60-D84D-234C-BF63-797B6D2C11A3}"/>
-    <hyperlink ref="F86" r:id="rId12" xr:uid="{320672D6-3A49-7144-A9B0-99E2897B70A6}"/>
-    <hyperlink ref="F89" r:id="rId13" xr:uid="{F2906274-9EF0-B047-BED8-BBE7C39510D1}"/>
-    <hyperlink ref="F90" r:id="rId14" xr:uid="{A56BE9F4-82D4-204A-AA33-E4958ECEC498}"/>
-    <hyperlink ref="F91" r:id="rId15" xr:uid="{11ED5116-2C55-A841-9828-2A4654F92AC8}"/>
-    <hyperlink ref="F92" r:id="rId16" xr:uid="{BEBFDF24-8751-1A41-9147-E2C953CFDBAE}"/>
-    <hyperlink ref="F94" r:id="rId17" xr:uid="{1E5C3452-AD2B-554B-8E81-8B321160E184}"/>
-    <hyperlink ref="F95" r:id="rId18" xr:uid="{38019B70-E174-A54F-9611-8471729E6B13}"/>
-    <hyperlink ref="F96" r:id="rId19" xr:uid="{C2330617-7CD6-A34C-901F-CC9393D8C2F9}"/>
-    <hyperlink ref="F97" r:id="rId20" xr:uid="{3CAD21A6-E921-9C4E-A862-2AF811FFE9EC}"/>
-    <hyperlink ref="F98" r:id="rId21" xr:uid="{7F59135C-6174-D548-94CC-B1B9A9187267}"/>
-    <hyperlink ref="F101" r:id="rId22" xr:uid="{D6EB6267-FC12-C444-9921-E73DE6836EC3}"/>
-    <hyperlink ref="F102" r:id="rId23" xr:uid="{0935F4F5-396A-EC40-BFC3-E5D318CDAE77}"/>
-    <hyperlink ref="F103" r:id="rId24" xr:uid="{2A7B762A-8F2A-E543-8456-D303C1572F4C}"/>
-    <hyperlink ref="F104" r:id="rId25" xr:uid="{2E5B3B20-CD26-A847-8491-A1FB5FE0E477}"/>
-    <hyperlink ref="F105" r:id="rId26" xr:uid="{243B62D3-5E2A-4549-A595-3AC6D3C8E90C}"/>
-    <hyperlink ref="F106" r:id="rId27" xr:uid="{043113E1-FE50-6546-BB31-ACB9444E1102}"/>
-    <hyperlink ref="F115" r:id="rId28" xr:uid="{E45EF3E2-25E5-1243-9324-EDFC24D03084}"/>
-    <hyperlink ref="F118" r:id="rId29" xr:uid="{43EFA958-C592-4E4C-9EF0-22E552EAABED}"/>
-    <hyperlink ref="F119" r:id="rId30" xr:uid="{B4692FAD-C9AA-CC45-A5FD-8C2ADD56353B}"/>
-    <hyperlink ref="F120" r:id="rId31" xr:uid="{29ADFB9B-CAC4-464D-B71A-8908A431D3BE}"/>
-    <hyperlink ref="F121" r:id="rId32" xr:uid="{3AB01097-9FE4-4444-A720-A967A50DFC16}"/>
-    <hyperlink ref="F122" r:id="rId33" xr:uid="{03CD05A9-969B-1F46-B39E-A2A22C06782E}"/>
-    <hyperlink ref="F123" r:id="rId34" xr:uid="{6610C6DE-A67B-694A-B81A-0C01C720FD49}"/>
-    <hyperlink ref="F124" r:id="rId35" xr:uid="{F3E51191-D2B0-F442-AE09-D6C3DACBB080}"/>
-    <hyperlink ref="F125" r:id="rId36" xr:uid="{D26FEFE1-716E-494A-A8F4-47A5E8EAE9AC}"/>
-    <hyperlink ref="F132" r:id="rId37" xr:uid="{D6A5DF21-9B11-7643-A9AB-688C86374D54}"/>
-    <hyperlink ref="F144" r:id="rId38" xr:uid="{FE6B260E-C5FD-B544-9FE6-BB070AC76BAC}"/>
-    <hyperlink ref="F145" r:id="rId39" xr:uid="{533D6A3C-2ED6-7D4D-A05C-253DFB9389EF}"/>
-    <hyperlink ref="F146" r:id="rId40" xr:uid="{37010ECC-A790-CE41-9AF1-9F2CF301B4CD}"/>
-    <hyperlink ref="G147" r:id="rId41" xr:uid="{27835BD6-FEB3-F846-95A5-30FE8261681D}"/>
-    <hyperlink ref="F148" r:id="rId42" xr:uid="{6D5EFC6A-47D8-BD4C-8CC6-A82DEE812A6B}"/>
-    <hyperlink ref="F149" r:id="rId43" xr:uid="{B32D2699-53DE-7B40-9DF3-9AA3AC25487B}"/>
-    <hyperlink ref="F150" r:id="rId44" xr:uid="{CF678504-1C6F-3C49-921A-757AE6D690F0}"/>
-    <hyperlink ref="F151" r:id="rId45" xr:uid="{14E2D30C-5621-8848-896A-D174AC72A30D}"/>
-    <hyperlink ref="F152" r:id="rId46" xr:uid="{5B7161A8-D04C-C04A-9154-4DE2BC49300F}"/>
-    <hyperlink ref="F153" r:id="rId47" xr:uid="{DE82C0C9-3777-3A45-ABF0-0D3B389DE9BF}"/>
-    <hyperlink ref="F154" r:id="rId48" xr:uid="{2991DC46-849B-984D-82D4-C9BA46965400}"/>
-    <hyperlink ref="F155" r:id="rId49" xr:uid="{7C158869-62D0-914E-B9AB-86E29C04AD92}"/>
-    <hyperlink ref="F156" r:id="rId50" xr:uid="{3303754A-9602-0B40-B591-8078B1F2F400}"/>
-    <hyperlink ref="F157" r:id="rId51" xr:uid="{58A58969-37C9-0C42-A889-70098A0FBE9D}"/>
-    <hyperlink ref="F158" r:id="rId52" xr:uid="{AF69F823-E536-F247-8E7B-6CFD11089A8A}"/>
-    <hyperlink ref="F162" r:id="rId53" xr:uid="{F31366DF-5211-F04D-A3E3-415D74F495B2}"/>
-    <hyperlink ref="F163" r:id="rId54" xr:uid="{E6ABB46E-002B-C94C-9249-F6F982A00EA2}"/>
-    <hyperlink ref="F165" r:id="rId55" xr:uid="{C0AB3CFE-0911-B14F-808A-20B4FA975FE9}"/>
-    <hyperlink ref="G165" r:id="rId56" xr:uid="{85BC2734-BAD4-5242-8942-022D6A8A0AB9}"/>
-    <hyperlink ref="H165" r:id="rId57" xr:uid="{62C652A1-E606-A542-A8C1-1855C5659D31}"/>
-    <hyperlink ref="I165" r:id="rId58" xr:uid="{A1F9D4B1-0098-8743-B801-C97D1A6FBF84}"/>
-    <hyperlink ref="G166" r:id="rId59" xr:uid="{2562845C-6CD3-7B42-9B31-205713D8E2E0}"/>
-    <hyperlink ref="F194" r:id="rId60" xr:uid="{0D836360-7CB7-344A-9819-A95E0857CEF9}"/>
-    <hyperlink ref="F197" r:id="rId61" xr:uid="{FEAA8EC6-0BB7-0B49-86B1-1FDB70D4D0ED}"/>
-    <hyperlink ref="G197" r:id="rId62" xr:uid="{B96528EE-11C9-224A-8BC8-444B55371645}"/>
-    <hyperlink ref="H197" r:id="rId63" xr:uid="{A3464ECD-516F-1A40-935A-F1BBC86ABFC2}"/>
-    <hyperlink ref="I197" r:id="rId64" xr:uid="{42DBFFDE-D897-2A41-AB5C-D670CB0A7174}"/>
-    <hyperlink ref="F204" r:id="rId65" xr:uid="{597F03BA-8CD2-AF44-8000-E2256EFD75D4}"/>
-    <hyperlink ref="G204" r:id="rId66" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view" xr:uid="{4745DF9D-2D6F-F446-BDEB-E60DD029CC76}"/>
-    <hyperlink ref="F223" r:id="rId67" xr:uid="{FC10816C-2792-4445-A1D5-E7A3FCA5BCFA}"/>
-    <hyperlink ref="F224" r:id="rId68" xr:uid="{21356ED0-4038-A64B-B5C7-F1A5ECBD6B4F}"/>
-    <hyperlink ref="F225" r:id="rId69" xr:uid="{C98B9432-0B63-6C4B-A95F-958236A82FD7}"/>
-    <hyperlink ref="F226" r:id="rId70" xr:uid="{97F6673B-F524-A74F-BDE6-AD3D0795AC67}"/>
-    <hyperlink ref="F232" r:id="rId71" xr:uid="{2C6C9B8B-F83A-8C41-8CBF-97CCC040B769}"/>
-    <hyperlink ref="F236" r:id="rId72" xr:uid="{5A81C910-9073-D34C-B683-DF512DEB8CA2}"/>
-    <hyperlink ref="F238" r:id="rId73" xr:uid="{A5272048-42B7-0F40-89B5-1A1DB1873DCC}"/>
-    <hyperlink ref="F239" r:id="rId74" xr:uid="{71988E24-3B2F-7845-8475-D8DDB1F8F397}"/>
+    <hyperlink ref="G8" r:id="rId1" xr:uid="{2932D1B6-661C-5F40-B265-3BC4F5CD1008}"/>
+    <hyperlink ref="H15" r:id="rId2" xr:uid="{8F5C5A8C-5138-2D42-B505-E69D8A18F003}"/>
+    <hyperlink ref="F16" r:id="rId3" xr:uid="{233E4743-9821-D241-B8E2-94574290B130}"/>
+    <hyperlink ref="F39" r:id="rId4" xr:uid="{E34DE3EB-648C-634D-A11D-45EB0531A0B7}"/>
+    <hyperlink ref="F43" r:id="rId5" xr:uid="{5935EF36-5BCB-C844-A838-6FC8B17DC2C0}"/>
+    <hyperlink ref="F72" r:id="rId6" xr:uid="{39C52E2D-EA08-314A-A66B-37A2A6BF9F43}"/>
+    <hyperlink ref="F73" r:id="rId7" xr:uid="{E4263635-9BEB-064D-ACB3-CD1EBDEB9760}"/>
+    <hyperlink ref="F80" r:id="rId8" xr:uid="{1323A638-EA84-5542-A2C8-946BA17FF0E9}"/>
+    <hyperlink ref="F82" r:id="rId9" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{853EA4A9-CBB6-4E4C-9E54-0EAAD100618F}"/>
+    <hyperlink ref="F84" r:id="rId10" xr:uid="{78ADACEA-162A-AD40-A042-419F4CF99535}"/>
+    <hyperlink ref="F85" r:id="rId11" xr:uid="{75EFC3C6-07FE-344F-B4EA-5D3909DE40BC}"/>
+    <hyperlink ref="F86" r:id="rId12" xr:uid="{27683132-A8AF-5247-A967-C443DF6DCFF5}"/>
+    <hyperlink ref="F89" r:id="rId13" xr:uid="{2413FBE6-3F8B-BC46-A117-B48B956795BF}"/>
+    <hyperlink ref="F90" r:id="rId14" xr:uid="{8A3FFAD5-FEE6-2647-85AA-444E492768F2}"/>
+    <hyperlink ref="F91" r:id="rId15" xr:uid="{EA26F55A-A5D9-FD4A-919F-8A6AA3BF6EE2}"/>
+    <hyperlink ref="F92" r:id="rId16" xr:uid="{A1453476-301C-C744-8BE8-6159CC12A28F}"/>
+    <hyperlink ref="F94" r:id="rId17" xr:uid="{B4691709-F57C-3847-BC92-4CBE18BBEAC3}"/>
+    <hyperlink ref="F95" r:id="rId18" xr:uid="{6F580915-2F83-9F4B-9D88-FE7F0009C12B}"/>
+    <hyperlink ref="F96" r:id="rId19" xr:uid="{5403847D-4AA7-5D43-9202-364E74F8532E}"/>
+    <hyperlink ref="F97" r:id="rId20" xr:uid="{6F647556-D97C-DB44-94FA-EBEE011E2AF9}"/>
+    <hyperlink ref="F98" r:id="rId21" xr:uid="{62B25751-CE43-C24E-A5A5-9784EBA68CDF}"/>
+    <hyperlink ref="F101" r:id="rId22" xr:uid="{C0876EF9-8F89-0447-9087-E5BDFAA7649E}"/>
+    <hyperlink ref="F102" r:id="rId23" xr:uid="{685368E1-0C61-DD45-A16F-12C3EFBB65D3}"/>
+    <hyperlink ref="F103" r:id="rId24" xr:uid="{56FB0824-E1D2-924E-BFB4-F256A82954C5}"/>
+    <hyperlink ref="F104" r:id="rId25" xr:uid="{1CAE6B36-217A-D54C-901C-4D9304C87FB3}"/>
+    <hyperlink ref="F105" r:id="rId26" xr:uid="{7D68FE21-BDEF-6E41-84B6-DA2FED37AE55}"/>
+    <hyperlink ref="F106" r:id="rId27" xr:uid="{25EC621F-EAA5-DF46-BA55-BB331DB2C0E0}"/>
+    <hyperlink ref="F115" r:id="rId28" xr:uid="{E6520685-884E-674D-A8BF-6DFADF29E4B7}"/>
+    <hyperlink ref="F118" r:id="rId29" xr:uid="{AED1BBAB-2EE9-A34A-8658-54325E847BE4}"/>
+    <hyperlink ref="F119" r:id="rId30" xr:uid="{6C3428F0-B9EB-FE42-8A83-ECDE991246A4}"/>
+    <hyperlink ref="F120" r:id="rId31" xr:uid="{5C082370-FE0E-A845-81C6-E57CA0B2AC31}"/>
+    <hyperlink ref="F121" r:id="rId32" xr:uid="{F1BA6C59-329C-424B-9C5D-C06D66422F67}"/>
+    <hyperlink ref="F122" r:id="rId33" xr:uid="{5C6AE1D5-B268-FA4E-AA07-6BBA6618D3B5}"/>
+    <hyperlink ref="F123" r:id="rId34" xr:uid="{0AF7C7E0-8614-E545-82C8-E387E283E3D8}"/>
+    <hyperlink ref="F124" r:id="rId35" xr:uid="{8135E5B9-73FC-4247-95E1-46817E719060}"/>
+    <hyperlink ref="F125" r:id="rId36" xr:uid="{AEDF7AD3-51D4-E24C-A16A-A5B6823CA710}"/>
+    <hyperlink ref="F132" r:id="rId37" xr:uid="{F9CCF84C-105D-C147-B0F5-0FC626F86232}"/>
+    <hyperlink ref="F144" r:id="rId38" xr:uid="{9F56E444-3186-2640-AE54-18E2E0337921}"/>
+    <hyperlink ref="F145" r:id="rId39" xr:uid="{9F8DE241-823A-6A43-8D19-D6A74FF71D06}"/>
+    <hyperlink ref="F146" r:id="rId40" xr:uid="{F88012CF-099E-9A4E-A044-E7FB2BB316F9}"/>
+    <hyperlink ref="G147" r:id="rId41" xr:uid="{D95F43EB-6B40-FC4F-B7E7-773F0107C9F2}"/>
+    <hyperlink ref="F148" r:id="rId42" xr:uid="{FBE4D094-BBBA-364A-8783-77CE18E43CA6}"/>
+    <hyperlink ref="F149" r:id="rId43" xr:uid="{2FCF1D71-D0E2-AF45-ABE1-B239A521F1C3}"/>
+    <hyperlink ref="F150" r:id="rId44" xr:uid="{0AC9ED99-8F4C-1640-AD0E-4D3A3C4CB582}"/>
+    <hyperlink ref="F151" r:id="rId45" xr:uid="{C2B21F85-31C0-D844-AEA5-20745CA02E81}"/>
+    <hyperlink ref="F152" r:id="rId46" xr:uid="{3E4CC3C5-AB57-C64A-9BBC-6D7890B621D8}"/>
+    <hyperlink ref="F153" r:id="rId47" xr:uid="{BCEB96DD-6D3C-DC47-9BFA-74DA04010AC2}"/>
+    <hyperlink ref="F154" r:id="rId48" xr:uid="{989C9EE2-FB41-7447-9A85-43952BF28808}"/>
+    <hyperlink ref="F155" r:id="rId49" xr:uid="{2C43C957-E757-814D-A781-EF707C3E729C}"/>
+    <hyperlink ref="F156" r:id="rId50" xr:uid="{80368C8C-958A-1247-96A1-D1931C91C8ED}"/>
+    <hyperlink ref="F157" r:id="rId51" xr:uid="{D43EFAFC-B80A-764E-AB1E-4F68A1C83A34}"/>
+    <hyperlink ref="F158" r:id="rId52" xr:uid="{F93D30C0-AF80-BF4E-9998-AAA0555BE610}"/>
+    <hyperlink ref="F162" r:id="rId53" xr:uid="{935FBEB3-F568-B946-8382-8760B533DE18}"/>
+    <hyperlink ref="F163" r:id="rId54" xr:uid="{FB9585BC-AC11-0048-B1BF-4834DADFF5CD}"/>
+    <hyperlink ref="F165" r:id="rId55" xr:uid="{80BA2A6C-9A84-A245-BF7E-F23B62D720C3}"/>
+    <hyperlink ref="G165" r:id="rId56" xr:uid="{2633E504-8DE9-FD48-8EC9-CE227B47E9C8}"/>
+    <hyperlink ref="H165" r:id="rId57" xr:uid="{E6FC7D29-F318-C347-B277-6773C33CE5C3}"/>
+    <hyperlink ref="I165" r:id="rId58" xr:uid="{1B3C46BD-ACFB-2B49-A1F4-C70452A81C44}"/>
+    <hyperlink ref="G166" r:id="rId59" xr:uid="{2E674B67-D122-FD4D-A38E-6572D762DEE2}"/>
+    <hyperlink ref="F194" r:id="rId60" xr:uid="{0E6A3A97-EAAD-B945-BC4E-894F4031033C}"/>
+    <hyperlink ref="F197" r:id="rId61" xr:uid="{4DD84577-46C4-8D44-9CC4-2B272E4D7DE8}"/>
+    <hyperlink ref="G197" r:id="rId62" xr:uid="{1E41FD75-7CE1-5B43-AA03-AF57B1C6A1C4}"/>
+    <hyperlink ref="H197" r:id="rId63" xr:uid="{BC56EB69-4EDC-2B49-A92A-A8A7CC9E741E}"/>
+    <hyperlink ref="I197" r:id="rId64" xr:uid="{E1A6BF86-913A-4F4E-9383-78E7A540E229}"/>
+    <hyperlink ref="F204" r:id="rId65" xr:uid="{FAAE404B-6FC8-8149-B05E-36D5FD1E7D94}"/>
+    <hyperlink ref="G204" r:id="rId66" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view" xr:uid="{AB70E365-8FF3-1845-939C-FD71EF80CBEF}"/>
+    <hyperlink ref="F223" r:id="rId67" xr:uid="{CA0C2990-28FB-0242-B8FE-9A961F4A76ED}"/>
+    <hyperlink ref="F224" r:id="rId68" xr:uid="{D12B7FEF-BA87-524C-84C5-C9B385861F03}"/>
+    <hyperlink ref="F225" r:id="rId69" xr:uid="{A04501DB-6BA1-6D46-AEB5-2B1922FE2E70}"/>
+    <hyperlink ref="F226" r:id="rId70" xr:uid="{6CCC038E-FB87-194D-98F2-5A804C20620D}"/>
+    <hyperlink ref="F227" r:id="rId71" xr:uid="{A0192599-9C3D-E844-852D-65BD6750D087}"/>
+    <hyperlink ref="F232" r:id="rId72" xr:uid="{332A61BD-7A47-8944-91EF-96703A216FFA}"/>
+    <hyperlink ref="F235" r:id="rId73" xr:uid="{E685A72C-1B8F-3140-A9B9-1F00551E02D8}"/>
+    <hyperlink ref="F237" r:id="rId74" xr:uid="{654E6580-A237-C54E-923F-25D803E58A74}"/>
+    <hyperlink ref="F238" r:id="rId75" xr:uid="{AE6F1EDE-66E0-AE4F-9A4F-131E16BD5015}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F95B8B8-CCA7-934D-819D-4E59504174C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B739C87C-89BB-5B4E-B0CD-2AE0D0ADFAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31960" yWindow="500" windowWidth="33380" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="33380" windowHeight="21580" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
   <sheets>
     <sheet name="xlsx" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3035" uniqueCount="1075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3047" uniqueCount="1075">
   <si>
     <t>Household Name</t>
   </si>
@@ -3326,12 +3326,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3347,7 +3353,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3355,6 +3361,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3690,7 +3697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7894B4-148E-174D-AE8B-E6DE441B89B0}">
-  <dimension ref="A1:I240"/>
+  <dimension ref="A1:I243"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -8036,7 +8043,7 @@
       <c r="A208" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B208" s="2" t="s">
+      <c r="B208" s="7" t="s">
         <v>633</v>
       </c>
       <c r="C208" s="2" t="s">
@@ -8245,7 +8252,7 @@
       <c r="A219" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="B219" s="2" t="s">
+      <c r="B219" s="7" t="s">
         <v>700</v>
       </c>
       <c r="C219" s="2" t="s">
@@ -8302,7 +8309,7 @@
       <c r="A222" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="B222" s="2" t="s">
+      <c r="B222" s="7" t="s">
         <v>703</v>
       </c>
       <c r="C222" s="2" t="s">
@@ -8430,7 +8437,7 @@
       <c r="A228" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="B228" s="2" t="s">
+      <c r="B228" s="7" t="s">
         <v>703</v>
       </c>
       <c r="C228" s="2" t="s">
@@ -8468,7 +8475,7 @@
       <c r="A230" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="B230" s="2" t="s">
+      <c r="B230" s="7" t="s">
         <v>700</v>
       </c>
       <c r="C230" s="2" t="s">
@@ -8630,7 +8637,7 @@
       <c r="A238" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B238" s="2" t="s">
+      <c r="B238" s="7" t="s">
         <v>633</v>
       </c>
       <c r="C238" s="4" t="s">
@@ -8687,84 +8694,141 @@
       <c r="H240" s="2"/>
       <c r="I240" s="2"/>
     </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A241" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E241" s="2"/>
+      <c r="F241" s="2"/>
+      <c r="G241" s="2"/>
+      <c r="H241" s="2"/>
+      <c r="I241" s="2"/>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A242" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E242" s="2"/>
+      <c r="F242" s="2"/>
+      <c r="G242" s="2"/>
+      <c r="H242" s="2"/>
+      <c r="I242" s="2"/>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A243" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E243" s="2"/>
+      <c r="F243" s="2"/>
+      <c r="G243" s="2"/>
+      <c r="H243" s="2"/>
+      <c r="I243" s="2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G8" r:id="rId1" xr:uid="{2932D1B6-661C-5F40-B265-3BC4F5CD1008}"/>
-    <hyperlink ref="H15" r:id="rId2" xr:uid="{8F5C5A8C-5138-2D42-B505-E69D8A18F003}"/>
-    <hyperlink ref="F16" r:id="rId3" xr:uid="{233E4743-9821-D241-B8E2-94574290B130}"/>
-    <hyperlink ref="F39" r:id="rId4" xr:uid="{E34DE3EB-648C-634D-A11D-45EB0531A0B7}"/>
-    <hyperlink ref="F43" r:id="rId5" xr:uid="{5935EF36-5BCB-C844-A838-6FC8B17DC2C0}"/>
-    <hyperlink ref="F72" r:id="rId6" xr:uid="{39C52E2D-EA08-314A-A66B-37A2A6BF9F43}"/>
-    <hyperlink ref="F73" r:id="rId7" xr:uid="{E4263635-9BEB-064D-ACB3-CD1EBDEB9760}"/>
-    <hyperlink ref="F80" r:id="rId8" xr:uid="{1323A638-EA84-5542-A2C8-946BA17FF0E9}"/>
-    <hyperlink ref="F82" r:id="rId9" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{853EA4A9-CBB6-4E4C-9E54-0EAAD100618F}"/>
-    <hyperlink ref="F84" r:id="rId10" xr:uid="{78ADACEA-162A-AD40-A042-419F4CF99535}"/>
-    <hyperlink ref="F85" r:id="rId11" xr:uid="{75EFC3C6-07FE-344F-B4EA-5D3909DE40BC}"/>
-    <hyperlink ref="F86" r:id="rId12" xr:uid="{27683132-A8AF-5247-A967-C443DF6DCFF5}"/>
-    <hyperlink ref="F89" r:id="rId13" xr:uid="{2413FBE6-3F8B-BC46-A117-B48B956795BF}"/>
-    <hyperlink ref="F90" r:id="rId14" xr:uid="{8A3FFAD5-FEE6-2647-85AA-444E492768F2}"/>
-    <hyperlink ref="F91" r:id="rId15" xr:uid="{EA26F55A-A5D9-FD4A-919F-8A6AA3BF6EE2}"/>
-    <hyperlink ref="F92" r:id="rId16" xr:uid="{A1453476-301C-C744-8BE8-6159CC12A28F}"/>
-    <hyperlink ref="F94" r:id="rId17" xr:uid="{B4691709-F57C-3847-BC92-4CBE18BBEAC3}"/>
-    <hyperlink ref="F95" r:id="rId18" xr:uid="{6F580915-2F83-9F4B-9D88-FE7F0009C12B}"/>
-    <hyperlink ref="F96" r:id="rId19" xr:uid="{5403847D-4AA7-5D43-9202-364E74F8532E}"/>
-    <hyperlink ref="F97" r:id="rId20" xr:uid="{6F647556-D97C-DB44-94FA-EBEE011E2AF9}"/>
-    <hyperlink ref="F98" r:id="rId21" xr:uid="{62B25751-CE43-C24E-A5A5-9784EBA68CDF}"/>
-    <hyperlink ref="F101" r:id="rId22" xr:uid="{C0876EF9-8F89-0447-9087-E5BDFAA7649E}"/>
-    <hyperlink ref="F102" r:id="rId23" xr:uid="{685368E1-0C61-DD45-A16F-12C3EFBB65D3}"/>
-    <hyperlink ref="F103" r:id="rId24" xr:uid="{56FB0824-E1D2-924E-BFB4-F256A82954C5}"/>
-    <hyperlink ref="F104" r:id="rId25" xr:uid="{1CAE6B36-217A-D54C-901C-4D9304C87FB3}"/>
-    <hyperlink ref="F105" r:id="rId26" xr:uid="{7D68FE21-BDEF-6E41-84B6-DA2FED37AE55}"/>
-    <hyperlink ref="F106" r:id="rId27" xr:uid="{25EC621F-EAA5-DF46-BA55-BB331DB2C0E0}"/>
-    <hyperlink ref="F115" r:id="rId28" xr:uid="{E6520685-884E-674D-A8BF-6DFADF29E4B7}"/>
-    <hyperlink ref="F118" r:id="rId29" xr:uid="{AED1BBAB-2EE9-A34A-8658-54325E847BE4}"/>
-    <hyperlink ref="F119" r:id="rId30" xr:uid="{6C3428F0-B9EB-FE42-8A83-ECDE991246A4}"/>
-    <hyperlink ref="F120" r:id="rId31" xr:uid="{5C082370-FE0E-A845-81C6-E57CA0B2AC31}"/>
-    <hyperlink ref="F121" r:id="rId32" xr:uid="{F1BA6C59-329C-424B-9C5D-C06D66422F67}"/>
-    <hyperlink ref="F122" r:id="rId33" xr:uid="{5C6AE1D5-B268-FA4E-AA07-6BBA6618D3B5}"/>
-    <hyperlink ref="F123" r:id="rId34" xr:uid="{0AF7C7E0-8614-E545-82C8-E387E283E3D8}"/>
-    <hyperlink ref="F124" r:id="rId35" xr:uid="{8135E5B9-73FC-4247-95E1-46817E719060}"/>
-    <hyperlink ref="F125" r:id="rId36" xr:uid="{AEDF7AD3-51D4-E24C-A16A-A5B6823CA710}"/>
-    <hyperlink ref="F132" r:id="rId37" xr:uid="{F9CCF84C-105D-C147-B0F5-0FC626F86232}"/>
-    <hyperlink ref="F144" r:id="rId38" xr:uid="{9F56E444-3186-2640-AE54-18E2E0337921}"/>
-    <hyperlink ref="F145" r:id="rId39" xr:uid="{9F8DE241-823A-6A43-8D19-D6A74FF71D06}"/>
-    <hyperlink ref="F146" r:id="rId40" xr:uid="{F88012CF-099E-9A4E-A044-E7FB2BB316F9}"/>
-    <hyperlink ref="G147" r:id="rId41" xr:uid="{D95F43EB-6B40-FC4F-B7E7-773F0107C9F2}"/>
-    <hyperlink ref="F148" r:id="rId42" xr:uid="{FBE4D094-BBBA-364A-8783-77CE18E43CA6}"/>
-    <hyperlink ref="F149" r:id="rId43" xr:uid="{2FCF1D71-D0E2-AF45-ABE1-B239A521F1C3}"/>
-    <hyperlink ref="F150" r:id="rId44" xr:uid="{0AC9ED99-8F4C-1640-AD0E-4D3A3C4CB582}"/>
-    <hyperlink ref="F151" r:id="rId45" xr:uid="{C2B21F85-31C0-D844-AEA5-20745CA02E81}"/>
-    <hyperlink ref="F152" r:id="rId46" xr:uid="{3E4CC3C5-AB57-C64A-9BBC-6D7890B621D8}"/>
-    <hyperlink ref="F153" r:id="rId47" xr:uid="{BCEB96DD-6D3C-DC47-9BFA-74DA04010AC2}"/>
-    <hyperlink ref="F154" r:id="rId48" xr:uid="{989C9EE2-FB41-7447-9A85-43952BF28808}"/>
-    <hyperlink ref="F155" r:id="rId49" xr:uid="{2C43C957-E757-814D-A781-EF707C3E729C}"/>
-    <hyperlink ref="F156" r:id="rId50" xr:uid="{80368C8C-958A-1247-96A1-D1931C91C8ED}"/>
-    <hyperlink ref="F157" r:id="rId51" xr:uid="{D43EFAFC-B80A-764E-AB1E-4F68A1C83A34}"/>
-    <hyperlink ref="F158" r:id="rId52" xr:uid="{F93D30C0-AF80-BF4E-9998-AAA0555BE610}"/>
-    <hyperlink ref="F162" r:id="rId53" xr:uid="{935FBEB3-F568-B946-8382-8760B533DE18}"/>
-    <hyperlink ref="F163" r:id="rId54" xr:uid="{FB9585BC-AC11-0048-B1BF-4834DADFF5CD}"/>
-    <hyperlink ref="F165" r:id="rId55" xr:uid="{80BA2A6C-9A84-A245-BF7E-F23B62D720C3}"/>
-    <hyperlink ref="G165" r:id="rId56" xr:uid="{2633E504-8DE9-FD48-8EC9-CE227B47E9C8}"/>
-    <hyperlink ref="H165" r:id="rId57" xr:uid="{E6FC7D29-F318-C347-B277-6773C33CE5C3}"/>
-    <hyperlink ref="I165" r:id="rId58" xr:uid="{1B3C46BD-ACFB-2B49-A1F4-C70452A81C44}"/>
-    <hyperlink ref="G166" r:id="rId59" xr:uid="{2E674B67-D122-FD4D-A38E-6572D762DEE2}"/>
-    <hyperlink ref="F194" r:id="rId60" xr:uid="{0E6A3A97-EAAD-B945-BC4E-894F4031033C}"/>
-    <hyperlink ref="F197" r:id="rId61" xr:uid="{4DD84577-46C4-8D44-9CC4-2B272E4D7DE8}"/>
-    <hyperlink ref="G197" r:id="rId62" xr:uid="{1E41FD75-7CE1-5B43-AA03-AF57B1C6A1C4}"/>
-    <hyperlink ref="H197" r:id="rId63" xr:uid="{BC56EB69-4EDC-2B49-A92A-A8A7CC9E741E}"/>
-    <hyperlink ref="I197" r:id="rId64" xr:uid="{E1A6BF86-913A-4F4E-9383-78E7A540E229}"/>
-    <hyperlink ref="F204" r:id="rId65" xr:uid="{FAAE404B-6FC8-8149-B05E-36D5FD1E7D94}"/>
-    <hyperlink ref="G204" r:id="rId66" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view" xr:uid="{AB70E365-8FF3-1845-939C-FD71EF80CBEF}"/>
-    <hyperlink ref="F223" r:id="rId67" xr:uid="{CA0C2990-28FB-0242-B8FE-9A961F4A76ED}"/>
-    <hyperlink ref="F224" r:id="rId68" xr:uid="{D12B7FEF-BA87-524C-84C5-C9B385861F03}"/>
-    <hyperlink ref="F225" r:id="rId69" xr:uid="{A04501DB-6BA1-6D46-AEB5-2B1922FE2E70}"/>
-    <hyperlink ref="F226" r:id="rId70" xr:uid="{6CCC038E-FB87-194D-98F2-5A804C20620D}"/>
-    <hyperlink ref="F227" r:id="rId71" xr:uid="{A0192599-9C3D-E844-852D-65BD6750D087}"/>
-    <hyperlink ref="F232" r:id="rId72" xr:uid="{332A61BD-7A47-8944-91EF-96703A216FFA}"/>
-    <hyperlink ref="F235" r:id="rId73" xr:uid="{E685A72C-1B8F-3140-A9B9-1F00551E02D8}"/>
-    <hyperlink ref="F237" r:id="rId74" xr:uid="{654E6580-A237-C54E-923F-25D803E58A74}"/>
-    <hyperlink ref="F238" r:id="rId75" xr:uid="{AE6F1EDE-66E0-AE4F-9A4F-131E16BD5015}"/>
+    <hyperlink ref="G8" r:id="rId1" xr:uid="{7D7394D5-D1AE-E549-B6C3-6A3912A06463}"/>
+    <hyperlink ref="H15" r:id="rId2" xr:uid="{CBDA9453-A3F4-2E40-A36D-98F3497B6237}"/>
+    <hyperlink ref="F16" r:id="rId3" xr:uid="{3AD1FAB8-1FEE-5746-B1D9-666485AC4719}"/>
+    <hyperlink ref="F39" r:id="rId4" xr:uid="{930BBC19-8A23-884C-BAC6-55428F51F08B}"/>
+    <hyperlink ref="F43" r:id="rId5" xr:uid="{08A897AA-1429-B848-BD85-CAFF80F82047}"/>
+    <hyperlink ref="F72" r:id="rId6" xr:uid="{1E762ED8-F5F2-4643-8059-51898D6EB062}"/>
+    <hyperlink ref="F73" r:id="rId7" xr:uid="{BED25232-F326-7A48-91FB-DFAE8FEDEACE}"/>
+    <hyperlink ref="F80" r:id="rId8" xr:uid="{CA98360F-381E-3341-91E3-7BFA8B2CE344}"/>
+    <hyperlink ref="F82" r:id="rId9" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{83B0A671-D365-7E48-8C39-BB3BCF8E3361}"/>
+    <hyperlink ref="F84" r:id="rId10" xr:uid="{6D8567A4-73D6-0245-BA73-443FD10841A8}"/>
+    <hyperlink ref="F85" r:id="rId11" xr:uid="{38A8B3BA-EF93-E642-BE81-4262664EFD1D}"/>
+    <hyperlink ref="F86" r:id="rId12" xr:uid="{D13EFC6F-D1C9-DE45-A160-5321B542E14A}"/>
+    <hyperlink ref="F89" r:id="rId13" xr:uid="{20A88789-C6EA-DB4F-8CD1-9ABCC7B99304}"/>
+    <hyperlink ref="F90" r:id="rId14" xr:uid="{DE1F5746-2B36-0E41-A922-78F6F556402F}"/>
+    <hyperlink ref="F91" r:id="rId15" xr:uid="{3DBFF586-230E-8F46-A2FD-9B549EFB836B}"/>
+    <hyperlink ref="F92" r:id="rId16" xr:uid="{D8FAFAB9-2B6D-9F4A-96CB-2DEF2734825A}"/>
+    <hyperlink ref="F94" r:id="rId17" xr:uid="{E5BF390A-5DEC-5C45-9663-348D95274D08}"/>
+    <hyperlink ref="F95" r:id="rId18" xr:uid="{2734AAE0-F47E-0940-A015-2F2DA0115E5A}"/>
+    <hyperlink ref="F96" r:id="rId19" xr:uid="{2C24B646-A8DB-DB43-9C0B-402B3C134C66}"/>
+    <hyperlink ref="F97" r:id="rId20" xr:uid="{EC20CEC7-4A51-594E-A612-A25142275E6C}"/>
+    <hyperlink ref="F98" r:id="rId21" xr:uid="{D73B0BD7-0C49-2F48-8E44-D5504CEC4103}"/>
+    <hyperlink ref="F101" r:id="rId22" xr:uid="{594FF819-9ADB-AE42-8D31-86274A171D61}"/>
+    <hyperlink ref="F102" r:id="rId23" xr:uid="{45C180CF-68C1-0641-B275-8B35A3D509A4}"/>
+    <hyperlink ref="F103" r:id="rId24" xr:uid="{3F1103D5-C892-484E-AFE6-82C1A5018D60}"/>
+    <hyperlink ref="F104" r:id="rId25" xr:uid="{ACB8DEDA-2F3C-8B4E-BB85-1B2895438F26}"/>
+    <hyperlink ref="F105" r:id="rId26" xr:uid="{6749E19E-CC8E-4E41-85C6-3ED7F5A05826}"/>
+    <hyperlink ref="F106" r:id="rId27" xr:uid="{23C74D4D-9043-ED48-8275-3F1D21B86751}"/>
+    <hyperlink ref="F115" r:id="rId28" xr:uid="{89727F48-4C69-AC4A-8C98-D8F1ACD701FA}"/>
+    <hyperlink ref="F118" r:id="rId29" xr:uid="{239A9B1C-48FE-DF42-B72C-0B8259869513}"/>
+    <hyperlink ref="F119" r:id="rId30" xr:uid="{8D96DC35-E0C2-9B4E-B660-E6135FB25461}"/>
+    <hyperlink ref="F120" r:id="rId31" xr:uid="{8BED97A1-9FEB-994D-9DBB-06042243E5BA}"/>
+    <hyperlink ref="F121" r:id="rId32" xr:uid="{5D7526E1-5416-6540-BB44-36D37BCB74F7}"/>
+    <hyperlink ref="F122" r:id="rId33" xr:uid="{2C4F7C32-C605-8344-8EE8-EC24E9CF6CFE}"/>
+    <hyperlink ref="F123" r:id="rId34" xr:uid="{5A774304-5E3D-9D48-AEE4-8DD82169D761}"/>
+    <hyperlink ref="F124" r:id="rId35" xr:uid="{214ECA77-A55C-C744-9934-97619FCC9F1D}"/>
+    <hyperlink ref="F125" r:id="rId36" xr:uid="{703CED4C-39E6-8745-ADDF-C1E70D5D4EF3}"/>
+    <hyperlink ref="F132" r:id="rId37" xr:uid="{CDC9084E-DCC1-F946-A5EF-2348A8900572}"/>
+    <hyperlink ref="F144" r:id="rId38" xr:uid="{886415A6-B40C-754A-ADC4-5026B9D84B75}"/>
+    <hyperlink ref="F145" r:id="rId39" xr:uid="{0FFEE8B3-F671-7844-93F6-B9711848CCB5}"/>
+    <hyperlink ref="F146" r:id="rId40" xr:uid="{8D874B1F-9612-D049-8A12-18A10EE40BD7}"/>
+    <hyperlink ref="G147" r:id="rId41" xr:uid="{18BCCA4F-ABC3-4E47-AA3B-8AAADE59EDC4}"/>
+    <hyperlink ref="F148" r:id="rId42" xr:uid="{A930A36B-2033-5343-B093-F2A948C6F140}"/>
+    <hyperlink ref="F149" r:id="rId43" xr:uid="{1CFD8438-039B-F445-AB19-C3955CF63E11}"/>
+    <hyperlink ref="F150" r:id="rId44" xr:uid="{4FB44645-DD18-6547-A824-A55B53F7A3E5}"/>
+    <hyperlink ref="F151" r:id="rId45" xr:uid="{E936DC15-5C40-4242-BD0E-9D8B0DD95D96}"/>
+    <hyperlink ref="F152" r:id="rId46" xr:uid="{95DE8B8D-A214-F345-8DE9-DE417C1A9CCB}"/>
+    <hyperlink ref="F153" r:id="rId47" xr:uid="{2544C65D-D133-2844-88A8-710D7CEBA353}"/>
+    <hyperlink ref="F154" r:id="rId48" xr:uid="{CC7C2B81-1C89-334D-85A0-215A67A25C90}"/>
+    <hyperlink ref="F155" r:id="rId49" xr:uid="{4C6D28FC-5DDB-2644-99BC-3ED114561B94}"/>
+    <hyperlink ref="F156" r:id="rId50" xr:uid="{2299459D-74B2-EE43-9938-9838EE991A0C}"/>
+    <hyperlink ref="F157" r:id="rId51" xr:uid="{8E034FA7-BD4C-C34C-9A2E-D63093EE0B4A}"/>
+    <hyperlink ref="F158" r:id="rId52" xr:uid="{423AE3EE-3515-F141-B250-6BEF884E2684}"/>
+    <hyperlink ref="F162" r:id="rId53" xr:uid="{BF9AC7AC-6DCC-BD49-BBB6-88EFD18F4BEB}"/>
+    <hyperlink ref="F163" r:id="rId54" xr:uid="{19CFED2A-8869-7E4F-A60C-47C5395F5EA6}"/>
+    <hyperlink ref="F165" r:id="rId55" xr:uid="{258E7532-D6DF-6348-8BB5-389179AD2364}"/>
+    <hyperlink ref="G165" r:id="rId56" xr:uid="{672D7234-1864-844A-A490-E859FEDFB5BD}"/>
+    <hyperlink ref="H165" r:id="rId57" xr:uid="{6A460D40-376E-664B-BEF5-2CD6EE3697A9}"/>
+    <hyperlink ref="I165" r:id="rId58" xr:uid="{6ED882E7-6629-3341-BE6E-FB81156384D0}"/>
+    <hyperlink ref="G166" r:id="rId59" xr:uid="{0270F66F-BCD1-4A4E-B6E9-188E77475D0E}"/>
+    <hyperlink ref="F194" r:id="rId60" xr:uid="{1CC4E0E1-2FB8-9C42-A25D-042E382A7D72}"/>
+    <hyperlink ref="F197" r:id="rId61" xr:uid="{F3F6A072-8FA0-C84C-AE18-0ED9D211772E}"/>
+    <hyperlink ref="G197" r:id="rId62" xr:uid="{9769C8D5-6858-E441-8BC2-E0A3BF5CEB2D}"/>
+    <hyperlink ref="H197" r:id="rId63" xr:uid="{6D6812CA-CC97-C940-B715-1216873B5C0E}"/>
+    <hyperlink ref="I197" r:id="rId64" xr:uid="{CB21346F-FC5A-D047-93B6-65C21D3F2F5A}"/>
+    <hyperlink ref="F204" r:id="rId65" xr:uid="{66DE1A70-9677-104A-84AA-BE756909ADDE}"/>
+    <hyperlink ref="G204" r:id="rId66" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view" xr:uid="{9A0868B0-B140-4747-BB00-9FD254CB54AF}"/>
+    <hyperlink ref="F223" r:id="rId67" xr:uid="{E85BB3D7-42AA-9C44-A2AA-F6A4E4E8F4CF}"/>
+    <hyperlink ref="F224" r:id="rId68" xr:uid="{E40739EA-D796-8C4C-9E58-8BD78FF9561D}"/>
+    <hyperlink ref="F225" r:id="rId69" xr:uid="{6C28465D-AD68-6443-AF11-C2D215239D57}"/>
+    <hyperlink ref="F226" r:id="rId70" xr:uid="{99CA16CD-ECC9-2141-B60E-385241567031}"/>
+    <hyperlink ref="F227" r:id="rId71" xr:uid="{4F722BC3-27E9-2644-B58F-01358637CDC7}"/>
+    <hyperlink ref="F232" r:id="rId72" xr:uid="{5B9E928D-6517-EB4C-BE06-6C3B79140ADD}"/>
+    <hyperlink ref="F235" r:id="rId73" xr:uid="{A60EF5DF-C57D-FA41-8182-BF4A41FE8F4A}"/>
+    <hyperlink ref="F237" r:id="rId74" xr:uid="{1A8310D8-CD15-FA40-8A41-BD9870C268C4}"/>
+    <hyperlink ref="F238" r:id="rId75" xr:uid="{72BEDB06-EC8D-AA49-8188-0D6628C4DD34}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B739C87C-89BB-5B4E-B0CD-2AE0D0ADFAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1230F2E4-3DA5-3E41-A3C5-0D22391191F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33380" windowHeight="21580" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3047" uniqueCount="1075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3059" uniqueCount="1082">
   <si>
     <t>Household Name</t>
   </si>
@@ -3263,6 +3263,27 @@
   </si>
   <si>
     <t>Larry Paulson</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000wYVO9YAO/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000wYVw1YAG/view</t>
+  </si>
+  <si>
+    <t>Ommid Asbaghi</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000wXRHlYAO/view</t>
+  </si>
+  <si>
+    <t>Kathy Stumm</t>
+  </si>
+  <si>
+    <t>four way split</t>
+  </si>
+  <si>
+    <t xml:space="preserve">potential table for Ommid's friend </t>
   </si>
 </sst>
 </file>
@@ -3697,8 +3718,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7894B4-148E-174D-AE8B-E6DE441B89B0}">
-  <dimension ref="A1:I243"/>
+  <dimension ref="A1:I246"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="10" width="32.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
@@ -3806,7 +3830,9 @@
         <v>12</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="F5" s="1" t="s">
+        <v>1075</v>
+      </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -4603,7 +4629,9 @@
       <c r="E42" s="2" t="s">
         <v>1032</v>
       </c>
-      <c r="F42" s="2"/>
+      <c r="F42" s="1" t="s">
+        <v>1076</v>
+      </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
@@ -5364,7 +5392,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>302</v>
+        <v>164</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>303</v>
@@ -5373,12 +5401,10 @@
         <v>304</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="E79" s="2"/>
-      <c r="F79" s="3" t="s">
-        <v>661</v>
-      </c>
+      <c r="F79" s="3"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
@@ -6345,7 +6371,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>436</v>
+        <v>1077</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>437</v>
@@ -6357,8 +6383,8 @@
         <v>12</v>
       </c>
       <c r="E126" s="2"/>
-      <c r="F126" s="2" t="s">
-        <v>439</v>
+      <c r="F126" s="1" t="s">
+        <v>1078</v>
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
@@ -6626,7 +6652,7 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>487</v>
@@ -6637,11 +6663,9 @@
       <c r="D139" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E139" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="F139" s="3" t="s">
-        <v>666</v>
+      <c r="E139" s="2"/>
+      <c r="F139" s="1" t="s">
+        <v>493</v>
       </c>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
@@ -6649,7 +6673,7 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
-        <v>490</v>
+        <v>1079</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>491</v>
@@ -6660,9 +6684,11 @@
       <c r="D140" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E140" s="2"/>
-      <c r="F140" s="2" t="s">
-        <v>493</v>
+      <c r="E140" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>666</v>
       </c>
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
@@ -7776,7 +7802,7 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
-        <v>612</v>
+        <v>164</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>613</v>
@@ -7785,12 +7811,10 @@
         <v>692</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>155</v>
+        <v>1060</v>
       </c>
       <c r="E195" s="2"/>
-      <c r="F195" s="3" t="s">
-        <v>670</v>
-      </c>
+      <c r="F195" s="3"/>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
       <c r="I195" s="2"/>
@@ -8751,84 +8775,156 @@
       <c r="H243" s="2"/>
       <c r="I243" s="2"/>
     </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A244" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="C244" s="2" t="str">
+        <f>VLOOKUP(B244,Sheet1!A:B,2,FALSE)</f>
+        <v>x=9.25, y=74.78</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E244" s="2"/>
+      <c r="F244" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="G244" s="2"/>
+      <c r="H244" s="2"/>
+      <c r="I244" s="2"/>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A245" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="C245" s="2" t="str">
+        <f>VLOOKUP(B245,Sheet1!A:B,2,FALSE)</f>
+        <v>x=9.32, y=77.80</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F245" s="2"/>
+      <c r="G245" s="2"/>
+      <c r="H245" s="2"/>
+      <c r="I245" s="2"/>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A246" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="C246" s="2" t="str">
+        <f>VLOOKUP(B246,Sheet1!A:B,2,FALSE)</f>
+        <v>x=7.67, y=78.02</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F246" s="2"/>
+      <c r="G246" s="2"/>
+      <c r="H246" s="2"/>
+      <c r="I246" s="2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G8" r:id="rId1" xr:uid="{7D7394D5-D1AE-E549-B6C3-6A3912A06463}"/>
-    <hyperlink ref="H15" r:id="rId2" xr:uid="{CBDA9453-A3F4-2E40-A36D-98F3497B6237}"/>
-    <hyperlink ref="F16" r:id="rId3" xr:uid="{3AD1FAB8-1FEE-5746-B1D9-666485AC4719}"/>
-    <hyperlink ref="F39" r:id="rId4" xr:uid="{930BBC19-8A23-884C-BAC6-55428F51F08B}"/>
-    <hyperlink ref="F43" r:id="rId5" xr:uid="{08A897AA-1429-B848-BD85-CAFF80F82047}"/>
-    <hyperlink ref="F72" r:id="rId6" xr:uid="{1E762ED8-F5F2-4643-8059-51898D6EB062}"/>
-    <hyperlink ref="F73" r:id="rId7" xr:uid="{BED25232-F326-7A48-91FB-DFAE8FEDEACE}"/>
-    <hyperlink ref="F80" r:id="rId8" xr:uid="{CA98360F-381E-3341-91E3-7BFA8B2CE344}"/>
-    <hyperlink ref="F82" r:id="rId9" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{83B0A671-D365-7E48-8C39-BB3BCF8E3361}"/>
-    <hyperlink ref="F84" r:id="rId10" xr:uid="{6D8567A4-73D6-0245-BA73-443FD10841A8}"/>
-    <hyperlink ref="F85" r:id="rId11" xr:uid="{38A8B3BA-EF93-E642-BE81-4262664EFD1D}"/>
-    <hyperlink ref="F86" r:id="rId12" xr:uid="{D13EFC6F-D1C9-DE45-A160-5321B542E14A}"/>
-    <hyperlink ref="F89" r:id="rId13" xr:uid="{20A88789-C6EA-DB4F-8CD1-9ABCC7B99304}"/>
-    <hyperlink ref="F90" r:id="rId14" xr:uid="{DE1F5746-2B36-0E41-A922-78F6F556402F}"/>
-    <hyperlink ref="F91" r:id="rId15" xr:uid="{3DBFF586-230E-8F46-A2FD-9B549EFB836B}"/>
-    <hyperlink ref="F92" r:id="rId16" xr:uid="{D8FAFAB9-2B6D-9F4A-96CB-2DEF2734825A}"/>
-    <hyperlink ref="F94" r:id="rId17" xr:uid="{E5BF390A-5DEC-5C45-9663-348D95274D08}"/>
-    <hyperlink ref="F95" r:id="rId18" xr:uid="{2734AAE0-F47E-0940-A015-2F2DA0115E5A}"/>
-    <hyperlink ref="F96" r:id="rId19" xr:uid="{2C24B646-A8DB-DB43-9C0B-402B3C134C66}"/>
-    <hyperlink ref="F97" r:id="rId20" xr:uid="{EC20CEC7-4A51-594E-A612-A25142275E6C}"/>
-    <hyperlink ref="F98" r:id="rId21" xr:uid="{D73B0BD7-0C49-2F48-8E44-D5504CEC4103}"/>
-    <hyperlink ref="F101" r:id="rId22" xr:uid="{594FF819-9ADB-AE42-8D31-86274A171D61}"/>
-    <hyperlink ref="F102" r:id="rId23" xr:uid="{45C180CF-68C1-0641-B275-8B35A3D509A4}"/>
-    <hyperlink ref="F103" r:id="rId24" xr:uid="{3F1103D5-C892-484E-AFE6-82C1A5018D60}"/>
-    <hyperlink ref="F104" r:id="rId25" xr:uid="{ACB8DEDA-2F3C-8B4E-BB85-1B2895438F26}"/>
-    <hyperlink ref="F105" r:id="rId26" xr:uid="{6749E19E-CC8E-4E41-85C6-3ED7F5A05826}"/>
-    <hyperlink ref="F106" r:id="rId27" xr:uid="{23C74D4D-9043-ED48-8275-3F1D21B86751}"/>
-    <hyperlink ref="F115" r:id="rId28" xr:uid="{89727F48-4C69-AC4A-8C98-D8F1ACD701FA}"/>
-    <hyperlink ref="F118" r:id="rId29" xr:uid="{239A9B1C-48FE-DF42-B72C-0B8259869513}"/>
-    <hyperlink ref="F119" r:id="rId30" xr:uid="{8D96DC35-E0C2-9B4E-B660-E6135FB25461}"/>
-    <hyperlink ref="F120" r:id="rId31" xr:uid="{8BED97A1-9FEB-994D-9DBB-06042243E5BA}"/>
-    <hyperlink ref="F121" r:id="rId32" xr:uid="{5D7526E1-5416-6540-BB44-36D37BCB74F7}"/>
-    <hyperlink ref="F122" r:id="rId33" xr:uid="{2C4F7C32-C605-8344-8EE8-EC24E9CF6CFE}"/>
-    <hyperlink ref="F123" r:id="rId34" xr:uid="{5A774304-5E3D-9D48-AEE4-8DD82169D761}"/>
-    <hyperlink ref="F124" r:id="rId35" xr:uid="{214ECA77-A55C-C744-9934-97619FCC9F1D}"/>
-    <hyperlink ref="F125" r:id="rId36" xr:uid="{703CED4C-39E6-8745-ADDF-C1E70D5D4EF3}"/>
-    <hyperlink ref="F132" r:id="rId37" xr:uid="{CDC9084E-DCC1-F946-A5EF-2348A8900572}"/>
-    <hyperlink ref="F144" r:id="rId38" xr:uid="{886415A6-B40C-754A-ADC4-5026B9D84B75}"/>
-    <hyperlink ref="F145" r:id="rId39" xr:uid="{0FFEE8B3-F671-7844-93F6-B9711848CCB5}"/>
-    <hyperlink ref="F146" r:id="rId40" xr:uid="{8D874B1F-9612-D049-8A12-18A10EE40BD7}"/>
-    <hyperlink ref="G147" r:id="rId41" xr:uid="{18BCCA4F-ABC3-4E47-AA3B-8AAADE59EDC4}"/>
-    <hyperlink ref="F148" r:id="rId42" xr:uid="{A930A36B-2033-5343-B093-F2A948C6F140}"/>
-    <hyperlink ref="F149" r:id="rId43" xr:uid="{1CFD8438-039B-F445-AB19-C3955CF63E11}"/>
-    <hyperlink ref="F150" r:id="rId44" xr:uid="{4FB44645-DD18-6547-A824-A55B53F7A3E5}"/>
-    <hyperlink ref="F151" r:id="rId45" xr:uid="{E936DC15-5C40-4242-BD0E-9D8B0DD95D96}"/>
-    <hyperlink ref="F152" r:id="rId46" xr:uid="{95DE8B8D-A214-F345-8DE9-DE417C1A9CCB}"/>
-    <hyperlink ref="F153" r:id="rId47" xr:uid="{2544C65D-D133-2844-88A8-710D7CEBA353}"/>
-    <hyperlink ref="F154" r:id="rId48" xr:uid="{CC7C2B81-1C89-334D-85A0-215A67A25C90}"/>
-    <hyperlink ref="F155" r:id="rId49" xr:uid="{4C6D28FC-5DDB-2644-99BC-3ED114561B94}"/>
-    <hyperlink ref="F156" r:id="rId50" xr:uid="{2299459D-74B2-EE43-9938-9838EE991A0C}"/>
-    <hyperlink ref="F157" r:id="rId51" xr:uid="{8E034FA7-BD4C-C34C-9A2E-D63093EE0B4A}"/>
-    <hyperlink ref="F158" r:id="rId52" xr:uid="{423AE3EE-3515-F141-B250-6BEF884E2684}"/>
-    <hyperlink ref="F162" r:id="rId53" xr:uid="{BF9AC7AC-6DCC-BD49-BBB6-88EFD18F4BEB}"/>
-    <hyperlink ref="F163" r:id="rId54" xr:uid="{19CFED2A-8869-7E4F-A60C-47C5395F5EA6}"/>
-    <hyperlink ref="F165" r:id="rId55" xr:uid="{258E7532-D6DF-6348-8BB5-389179AD2364}"/>
-    <hyperlink ref="G165" r:id="rId56" xr:uid="{672D7234-1864-844A-A490-E859FEDFB5BD}"/>
-    <hyperlink ref="H165" r:id="rId57" xr:uid="{6A460D40-376E-664B-BEF5-2CD6EE3697A9}"/>
-    <hyperlink ref="I165" r:id="rId58" xr:uid="{6ED882E7-6629-3341-BE6E-FB81156384D0}"/>
-    <hyperlink ref="G166" r:id="rId59" xr:uid="{0270F66F-BCD1-4A4E-B6E9-188E77475D0E}"/>
-    <hyperlink ref="F194" r:id="rId60" xr:uid="{1CC4E0E1-2FB8-9C42-A25D-042E382A7D72}"/>
-    <hyperlink ref="F197" r:id="rId61" xr:uid="{F3F6A072-8FA0-C84C-AE18-0ED9D211772E}"/>
-    <hyperlink ref="G197" r:id="rId62" xr:uid="{9769C8D5-6858-E441-8BC2-E0A3BF5CEB2D}"/>
-    <hyperlink ref="H197" r:id="rId63" xr:uid="{6D6812CA-CC97-C940-B715-1216873B5C0E}"/>
-    <hyperlink ref="I197" r:id="rId64" xr:uid="{CB21346F-FC5A-D047-93B6-65C21D3F2F5A}"/>
-    <hyperlink ref="F204" r:id="rId65" xr:uid="{66DE1A70-9677-104A-84AA-BE756909ADDE}"/>
-    <hyperlink ref="G204" r:id="rId66" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view" xr:uid="{9A0868B0-B140-4747-BB00-9FD254CB54AF}"/>
-    <hyperlink ref="F223" r:id="rId67" xr:uid="{E85BB3D7-42AA-9C44-A2AA-F6A4E4E8F4CF}"/>
-    <hyperlink ref="F224" r:id="rId68" xr:uid="{E40739EA-D796-8C4C-9E58-8BD78FF9561D}"/>
-    <hyperlink ref="F225" r:id="rId69" xr:uid="{6C28465D-AD68-6443-AF11-C2D215239D57}"/>
-    <hyperlink ref="F226" r:id="rId70" xr:uid="{99CA16CD-ECC9-2141-B60E-385241567031}"/>
-    <hyperlink ref="F227" r:id="rId71" xr:uid="{4F722BC3-27E9-2644-B58F-01358637CDC7}"/>
-    <hyperlink ref="F232" r:id="rId72" xr:uid="{5B9E928D-6517-EB4C-BE06-6C3B79140ADD}"/>
-    <hyperlink ref="F235" r:id="rId73" xr:uid="{A60EF5DF-C57D-FA41-8182-BF4A41FE8F4A}"/>
-    <hyperlink ref="F237" r:id="rId74" xr:uid="{1A8310D8-CD15-FA40-8A41-BD9870C268C4}"/>
-    <hyperlink ref="F238" r:id="rId75" xr:uid="{72BEDB06-EC8D-AA49-8188-0D6628C4DD34}"/>
+    <hyperlink ref="F5" r:id="rId1" xr:uid="{04D1AAB8-7064-B342-A2A8-7D68F9EEDBD5}"/>
+    <hyperlink ref="G8" r:id="rId2" xr:uid="{74935FD3-25E6-A543-A4C2-61606314AB50}"/>
+    <hyperlink ref="H15" r:id="rId3" xr:uid="{39AAF570-D82E-C543-96E5-98B4752C6606}"/>
+    <hyperlink ref="F16" r:id="rId4" xr:uid="{E10E3C3B-2870-5143-AE84-66AB5A9BCA74}"/>
+    <hyperlink ref="F39" r:id="rId5" xr:uid="{221FD613-8565-F747-9D6E-29A50DFDA338}"/>
+    <hyperlink ref="F42" r:id="rId6" xr:uid="{A09A4399-DF80-0049-A538-ADB701D8A81F}"/>
+    <hyperlink ref="F43" r:id="rId7" xr:uid="{D423B1E5-93C1-0144-91E4-288571590CF6}"/>
+    <hyperlink ref="F72" r:id="rId8" xr:uid="{A736A96C-3F40-6F47-8406-F53034A35495}"/>
+    <hyperlink ref="F73" r:id="rId9" xr:uid="{DF5C3B71-A913-0342-9792-D356739654CC}"/>
+    <hyperlink ref="F80" r:id="rId10" xr:uid="{CEEEE699-C521-1544-80C5-5947E50C9E84}"/>
+    <hyperlink ref="F82" r:id="rId11" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{EBE9F826-9477-7147-BC60-4AB46936CF6B}"/>
+    <hyperlink ref="F84" r:id="rId12" xr:uid="{0075C90C-49BC-3046-A98B-173888D3FE64}"/>
+    <hyperlink ref="F85" r:id="rId13" xr:uid="{D8967545-60D2-6748-AC17-D1CF60147E77}"/>
+    <hyperlink ref="F86" r:id="rId14" xr:uid="{BAF26269-D00B-D344-A557-87B802B9D0EC}"/>
+    <hyperlink ref="F89" r:id="rId15" xr:uid="{EB68DA6F-491D-2F4C-90F6-D5C05DEDF4E1}"/>
+    <hyperlink ref="F90" r:id="rId16" xr:uid="{D50E0A94-7719-1F42-BF9E-3AFFF20B621A}"/>
+    <hyperlink ref="F91" r:id="rId17" xr:uid="{FDEF68A8-393A-5943-9C54-577C4E68FF03}"/>
+    <hyperlink ref="F92" r:id="rId18" xr:uid="{A73080BA-FC8E-A244-AC9C-E7E35924F47D}"/>
+    <hyperlink ref="F94" r:id="rId19" xr:uid="{E6FE7450-5CD0-8041-A74F-BFD8AD6139F1}"/>
+    <hyperlink ref="F95" r:id="rId20" xr:uid="{C2D93D7B-E957-AB44-8869-01D925FFD54D}"/>
+    <hyperlink ref="F96" r:id="rId21" xr:uid="{38FF751B-4DE5-7F41-8046-62414D85A6A0}"/>
+    <hyperlink ref="F97" r:id="rId22" xr:uid="{556D7434-1DD6-F94D-949A-42408CD12D14}"/>
+    <hyperlink ref="F98" r:id="rId23" xr:uid="{CE2EA120-8EBB-0649-A3EB-6B74703ADC3C}"/>
+    <hyperlink ref="F101" r:id="rId24" xr:uid="{67112478-1E9F-7847-9714-A8B7357AC7A3}"/>
+    <hyperlink ref="F102" r:id="rId25" xr:uid="{BB728625-5137-FD40-A992-30CA4D44BD41}"/>
+    <hyperlink ref="F103" r:id="rId26" xr:uid="{6B183599-6418-4246-A0A3-B8DC1182EC19}"/>
+    <hyperlink ref="F104" r:id="rId27" xr:uid="{A0FC70F7-EBE3-F24D-A73E-B1597044BC6B}"/>
+    <hyperlink ref="F105" r:id="rId28" xr:uid="{BED39D68-A395-0241-9B11-37BE2D1B2CE2}"/>
+    <hyperlink ref="F106" r:id="rId29" xr:uid="{7A360B15-F743-6346-9729-D391C1A79CBE}"/>
+    <hyperlink ref="F115" r:id="rId30" xr:uid="{F5A3DE4F-8C8D-D249-A6CE-61049BABA1E0}"/>
+    <hyperlink ref="F118" r:id="rId31" xr:uid="{B49D86E2-B143-D748-BBA6-9AF298CEF98E}"/>
+    <hyperlink ref="F119" r:id="rId32" xr:uid="{3DAB9712-9CC2-154D-8283-19F5BAA14176}"/>
+    <hyperlink ref="F120" r:id="rId33" xr:uid="{744332C6-03C7-6A48-A6B7-252A346F0C41}"/>
+    <hyperlink ref="F121" r:id="rId34" xr:uid="{1417FC18-B1B0-254B-8923-6AB5B38E5A3F}"/>
+    <hyperlink ref="F122" r:id="rId35" xr:uid="{AD142301-0E08-4F43-8149-B9E934084C91}"/>
+    <hyperlink ref="F123" r:id="rId36" xr:uid="{2127BB67-CF80-A94B-A338-4D38A85701D9}"/>
+    <hyperlink ref="F124" r:id="rId37" xr:uid="{61F33741-03D7-7F4B-9103-C90EC87F3A82}"/>
+    <hyperlink ref="F125" r:id="rId38" xr:uid="{2B3ECD1B-0206-E449-A31C-34DE40AF7358}"/>
+    <hyperlink ref="F126" r:id="rId39" xr:uid="{BBAC3D50-2089-0C41-B3A2-5C2C1AAF0544}"/>
+    <hyperlink ref="F132" r:id="rId40" xr:uid="{AEB65F31-41AA-2148-AC69-394839F7E90C}"/>
+    <hyperlink ref="F139" r:id="rId41" xr:uid="{DE0347F6-76D7-C240-A4A7-779301A46C25}"/>
+    <hyperlink ref="F140" r:id="rId42" xr:uid="{9AF4A68A-99DC-F34A-935C-F2D897C843EE}"/>
+    <hyperlink ref="F144" r:id="rId43" xr:uid="{77C12965-63B7-CD45-BF89-23555996D07D}"/>
+    <hyperlink ref="F145" r:id="rId44" xr:uid="{02CBD596-CEDB-D442-AC7D-A0BA679ACB06}"/>
+    <hyperlink ref="F146" r:id="rId45" xr:uid="{BEE9088F-3D2C-A84B-B9B7-5B0450826FAB}"/>
+    <hyperlink ref="G147" r:id="rId46" xr:uid="{9F32E378-2E90-154B-9E27-36ACE72B8C7C}"/>
+    <hyperlink ref="F148" r:id="rId47" xr:uid="{BB8DFB0A-CB63-E249-A00B-6CCA5B11A8B1}"/>
+    <hyperlink ref="F149" r:id="rId48" xr:uid="{792A8708-49A1-8A49-9705-1B45E58A90DD}"/>
+    <hyperlink ref="F150" r:id="rId49" xr:uid="{35CBE119-889D-B14D-AF9C-E9D1E8A7BD6B}"/>
+    <hyperlink ref="F151" r:id="rId50" xr:uid="{92190858-BBBF-CC4E-8459-DEC388D54FBF}"/>
+    <hyperlink ref="F152" r:id="rId51" xr:uid="{CC6991DD-676B-AF41-9F34-ABF0F5293854}"/>
+    <hyperlink ref="F153" r:id="rId52" xr:uid="{44F865A9-229A-7B45-BB39-1A109D55CC71}"/>
+    <hyperlink ref="F154" r:id="rId53" xr:uid="{7DD2C92C-ABFA-0541-8E4D-10C68533D00E}"/>
+    <hyperlink ref="F155" r:id="rId54" xr:uid="{E7F9A324-D987-E54A-8C25-7694ACFE0A63}"/>
+    <hyperlink ref="F156" r:id="rId55" xr:uid="{4CE3613B-9104-9E4B-9E16-3B3CD00553EF}"/>
+    <hyperlink ref="F157" r:id="rId56" xr:uid="{FADF0A12-4A83-FE43-A188-FD06EA450115}"/>
+    <hyperlink ref="F158" r:id="rId57" xr:uid="{4012B00D-6984-E249-A6A7-9C00462E4980}"/>
+    <hyperlink ref="F162" r:id="rId58" xr:uid="{92616819-DF77-E745-AC19-6F91C3D7D9C8}"/>
+    <hyperlink ref="F163" r:id="rId59" xr:uid="{109C6B6E-F3F7-4941-AC9F-AEF6C711FA4A}"/>
+    <hyperlink ref="F165" r:id="rId60" xr:uid="{1AF7C07A-7294-2343-8406-22621D8D7C83}"/>
+    <hyperlink ref="G165" r:id="rId61" xr:uid="{20B24F04-580E-694A-94B9-0C7EE6DF9C60}"/>
+    <hyperlink ref="H165" r:id="rId62" xr:uid="{7E4E117C-A2DE-6344-9B1A-490E8CFF1203}"/>
+    <hyperlink ref="I165" r:id="rId63" xr:uid="{A460BBAD-A3C6-5D45-9692-6B48F54EC8B5}"/>
+    <hyperlink ref="G166" r:id="rId64" xr:uid="{A0814516-B4A9-8B49-BA1C-EA6B5B57FE11}"/>
+    <hyperlink ref="F194" r:id="rId65" xr:uid="{EAC55C19-DB8E-784F-B88C-0428DD81A7F8}"/>
+    <hyperlink ref="F197" r:id="rId66" xr:uid="{8CB4FBE6-57C0-B047-AAFD-9F3CD83FFD10}"/>
+    <hyperlink ref="G197" r:id="rId67" xr:uid="{FFCAA1D8-DDC3-6047-806C-F1FAC89C13D8}"/>
+    <hyperlink ref="H197" r:id="rId68" xr:uid="{D9FFA116-1E10-CB4A-A4D3-ADB8F9CB4544}"/>
+    <hyperlink ref="I197" r:id="rId69" xr:uid="{411043A8-358E-9848-9049-CCF4376F8EAE}"/>
+    <hyperlink ref="F204" r:id="rId70" xr:uid="{3A0149AD-FAE7-3344-B872-DABB988B8ED5}"/>
+    <hyperlink ref="G204" r:id="rId71" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view" xr:uid="{1C038C8A-4FED-2340-8337-4E6AAEBE6BB9}"/>
+    <hyperlink ref="F223" r:id="rId72" xr:uid="{8081E488-C6B9-AB40-99E3-1047D6BB28F8}"/>
+    <hyperlink ref="F224" r:id="rId73" xr:uid="{770BF84C-CF2B-8443-A426-158B3280BFB0}"/>
+    <hyperlink ref="F225" r:id="rId74" xr:uid="{A3909524-39C9-3640-8A86-3CB029647F17}"/>
+    <hyperlink ref="F226" r:id="rId75" xr:uid="{C5749CE7-A198-8144-8B57-9FE1918DD33D}"/>
+    <hyperlink ref="F227" r:id="rId76" xr:uid="{1DD65324-EB2A-7543-BF9C-73CB9FA93084}"/>
+    <hyperlink ref="F232" r:id="rId77" xr:uid="{F692241B-B08A-EF4B-856F-D79FE35D9528}"/>
+    <hyperlink ref="F235" r:id="rId78" xr:uid="{2B3077BE-507F-034E-AE81-2A0B02F26ADD}"/>
+    <hyperlink ref="F237" r:id="rId79" xr:uid="{2BA2AFE5-3289-C845-93C0-794D9FE59DC9}"/>
+    <hyperlink ref="F238" r:id="rId80" xr:uid="{C50A8610-C713-E044-81B8-614764342D66}"/>
+    <hyperlink ref="F244" r:id="rId81" xr:uid="{3A6C7766-F20C-3448-A34B-C50FCC2F91F8}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1230F2E4-3DA5-3E41-A3C5-0D22391191F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118F691A-04DF-AA43-B897-CC32CACAF7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33380" windowHeight="21580" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3059" uniqueCount="1082">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3062" uniqueCount="1087">
   <si>
     <t>Household Name</t>
   </si>
@@ -3284,13 +3284,28 @@
   </si>
   <si>
     <t xml:space="preserve">potential table for Ommid's friend </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1/2 Maryellen Aviano 1/2 Online</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uutEVYAY/view</t>
+  </si>
+  <si>
+    <t>1/2 Eileen Zismer 1/2 CB</t>
+  </si>
+  <si>
+    <t>1/2 Eileen Zismer &amp; 1/2 CB inventory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E9 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3346,6 +3361,19 @@
       <name val="Menlo"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -3374,7 +3402,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3383,6 +3411,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3718,10 +3749,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7894B4-148E-174D-AE8B-E6DE441B89B0}">
-  <dimension ref="A1:I246"/>
+  <dimension ref="A1:I248"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="10" width="32.83203125" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -4098,9 +4129,7 @@
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>69</v>
-      </c>
+      <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
         <v>70</v>
       </c>
@@ -4111,9 +4140,7 @@
         <v>12</v>
       </c>
       <c r="E18" s="2"/>
-      <c r="F18" s="2" t="s">
-        <v>72</v>
-      </c>
+      <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -7532,7 +7559,7 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
-        <v>679</v>
+        <v>1082</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>594</v>
@@ -7541,17 +7568,19 @@
         <v>595</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>569</v>
+        <v>12</v>
       </c>
       <c r="E181" s="2"/>
-      <c r="F181" s="2"/>
+      <c r="F181" s="1" t="s">
+        <v>1083</v>
+      </c>
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
       <c r="I181" s="2"/>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A182" s="2" t="s">
-        <v>679</v>
+      <c r="A182" s="8">
+        <v>46024</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>596</v>
@@ -7811,7 +7840,7 @@
         <v>692</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>1060</v>
+        <v>167</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" s="3"/>
@@ -7964,7 +7993,7 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
-        <v>164</v>
+        <v>1059</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>623</v>
@@ -7975,7 +8004,7 @@
       <c r="D203" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E203" s="2"/>
+      <c r="E203" s="9"/>
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
@@ -8516,7 +8545,7 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" s="2" t="s">
-        <v>164</v>
+        <v>1084</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>864</v>
@@ -8525,9 +8554,11 @@
         <v>865</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E231" s="2"/>
+        <v>1071</v>
+      </c>
+      <c r="E231" s="10" t="s">
+        <v>1085</v>
+      </c>
       <c r="F231" s="2"/>
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
@@ -8782,10 +8813,7 @@
       <c r="B244" s="2" t="s">
         <v>956</v>
       </c>
-      <c r="C244" s="2" t="str">
-        <f>VLOOKUP(B244,Sheet1!A:B,2,FALSE)</f>
-        <v>x=9.25, y=74.78</v>
-      </c>
+      <c r="C244" s="2"/>
       <c r="D244" s="2" t="s">
         <v>1071</v>
       </c>
@@ -8804,10 +8832,7 @@
       <c r="B245" s="2" t="s">
         <v>964</v>
       </c>
-      <c r="C245" s="2" t="str">
-        <f>VLOOKUP(B245,Sheet1!A:B,2,FALSE)</f>
-        <v>x=9.32, y=77.80</v>
-      </c>
+      <c r="C245" s="2"/>
       <c r="D245" s="2" t="s">
         <v>167</v>
       </c>
@@ -8826,10 +8851,7 @@
       <c r="B246" s="2" t="s">
         <v>968</v>
       </c>
-      <c r="C246" s="2" t="str">
-        <f>VLOOKUP(B246,Sheet1!A:B,2,FALSE)</f>
-        <v>x=7.67, y=78.02</v>
-      </c>
+      <c r="C246" s="2"/>
       <c r="D246" s="2" t="s">
         <v>167</v>
       </c>
@@ -8841,90 +8863,121 @@
       <c r="H246" s="2"/>
       <c r="I246" s="2"/>
     </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A247" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="C247" s="2"/>
+      <c r="D247" s="2"/>
+      <c r="E247" s="2"/>
+      <c r="F247" s="2"/>
+      <c r="G247" s="2"/>
+      <c r="H247" s="2"/>
+      <c r="I247" s="2"/>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A248" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C248" s="2"/>
+      <c r="D248" s="2"/>
+      <c r="E248" s="2"/>
+      <c r="F248" s="2"/>
+      <c r="G248" s="2"/>
+      <c r="H248" s="2"/>
+      <c r="I248" s="2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F5" r:id="rId1" xr:uid="{04D1AAB8-7064-B342-A2A8-7D68F9EEDBD5}"/>
-    <hyperlink ref="G8" r:id="rId2" xr:uid="{74935FD3-25E6-A543-A4C2-61606314AB50}"/>
-    <hyperlink ref="H15" r:id="rId3" xr:uid="{39AAF570-D82E-C543-96E5-98B4752C6606}"/>
-    <hyperlink ref="F16" r:id="rId4" xr:uid="{E10E3C3B-2870-5143-AE84-66AB5A9BCA74}"/>
-    <hyperlink ref="F39" r:id="rId5" xr:uid="{221FD613-8565-F747-9D6E-29A50DFDA338}"/>
-    <hyperlink ref="F42" r:id="rId6" xr:uid="{A09A4399-DF80-0049-A538-ADB701D8A81F}"/>
-    <hyperlink ref="F43" r:id="rId7" xr:uid="{D423B1E5-93C1-0144-91E4-288571590CF6}"/>
-    <hyperlink ref="F72" r:id="rId8" xr:uid="{A736A96C-3F40-6F47-8406-F53034A35495}"/>
-    <hyperlink ref="F73" r:id="rId9" xr:uid="{DF5C3B71-A913-0342-9792-D356739654CC}"/>
-    <hyperlink ref="F80" r:id="rId10" xr:uid="{CEEEE699-C521-1544-80C5-5947E50C9E84}"/>
-    <hyperlink ref="F82" r:id="rId11" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{EBE9F826-9477-7147-BC60-4AB46936CF6B}"/>
-    <hyperlink ref="F84" r:id="rId12" xr:uid="{0075C90C-49BC-3046-A98B-173888D3FE64}"/>
-    <hyperlink ref="F85" r:id="rId13" xr:uid="{D8967545-60D2-6748-AC17-D1CF60147E77}"/>
-    <hyperlink ref="F86" r:id="rId14" xr:uid="{BAF26269-D00B-D344-A557-87B802B9D0EC}"/>
-    <hyperlink ref="F89" r:id="rId15" xr:uid="{EB68DA6F-491D-2F4C-90F6-D5C05DEDF4E1}"/>
-    <hyperlink ref="F90" r:id="rId16" xr:uid="{D50E0A94-7719-1F42-BF9E-3AFFF20B621A}"/>
-    <hyperlink ref="F91" r:id="rId17" xr:uid="{FDEF68A8-393A-5943-9C54-577C4E68FF03}"/>
-    <hyperlink ref="F92" r:id="rId18" xr:uid="{A73080BA-FC8E-A244-AC9C-E7E35924F47D}"/>
-    <hyperlink ref="F94" r:id="rId19" xr:uid="{E6FE7450-5CD0-8041-A74F-BFD8AD6139F1}"/>
-    <hyperlink ref="F95" r:id="rId20" xr:uid="{C2D93D7B-E957-AB44-8869-01D925FFD54D}"/>
-    <hyperlink ref="F96" r:id="rId21" xr:uid="{38FF751B-4DE5-7F41-8046-62414D85A6A0}"/>
-    <hyperlink ref="F97" r:id="rId22" xr:uid="{556D7434-1DD6-F94D-949A-42408CD12D14}"/>
-    <hyperlink ref="F98" r:id="rId23" xr:uid="{CE2EA120-8EBB-0649-A3EB-6B74703ADC3C}"/>
-    <hyperlink ref="F101" r:id="rId24" xr:uid="{67112478-1E9F-7847-9714-A8B7357AC7A3}"/>
-    <hyperlink ref="F102" r:id="rId25" xr:uid="{BB728625-5137-FD40-A992-30CA4D44BD41}"/>
-    <hyperlink ref="F103" r:id="rId26" xr:uid="{6B183599-6418-4246-A0A3-B8DC1182EC19}"/>
-    <hyperlink ref="F104" r:id="rId27" xr:uid="{A0FC70F7-EBE3-F24D-A73E-B1597044BC6B}"/>
-    <hyperlink ref="F105" r:id="rId28" xr:uid="{BED39D68-A395-0241-9B11-37BE2D1B2CE2}"/>
-    <hyperlink ref="F106" r:id="rId29" xr:uid="{7A360B15-F743-6346-9729-D391C1A79CBE}"/>
-    <hyperlink ref="F115" r:id="rId30" xr:uid="{F5A3DE4F-8C8D-D249-A6CE-61049BABA1E0}"/>
-    <hyperlink ref="F118" r:id="rId31" xr:uid="{B49D86E2-B143-D748-BBA6-9AF298CEF98E}"/>
-    <hyperlink ref="F119" r:id="rId32" xr:uid="{3DAB9712-9CC2-154D-8283-19F5BAA14176}"/>
-    <hyperlink ref="F120" r:id="rId33" xr:uid="{744332C6-03C7-6A48-A6B7-252A346F0C41}"/>
-    <hyperlink ref="F121" r:id="rId34" xr:uid="{1417FC18-B1B0-254B-8923-6AB5B38E5A3F}"/>
-    <hyperlink ref="F122" r:id="rId35" xr:uid="{AD142301-0E08-4F43-8149-B9E934084C91}"/>
-    <hyperlink ref="F123" r:id="rId36" xr:uid="{2127BB67-CF80-A94B-A338-4D38A85701D9}"/>
-    <hyperlink ref="F124" r:id="rId37" xr:uid="{61F33741-03D7-7F4B-9103-C90EC87F3A82}"/>
-    <hyperlink ref="F125" r:id="rId38" xr:uid="{2B3ECD1B-0206-E449-A31C-34DE40AF7358}"/>
-    <hyperlink ref="F126" r:id="rId39" xr:uid="{BBAC3D50-2089-0C41-B3A2-5C2C1AAF0544}"/>
-    <hyperlink ref="F132" r:id="rId40" xr:uid="{AEB65F31-41AA-2148-AC69-394839F7E90C}"/>
-    <hyperlink ref="F139" r:id="rId41" xr:uid="{DE0347F6-76D7-C240-A4A7-779301A46C25}"/>
-    <hyperlink ref="F140" r:id="rId42" xr:uid="{9AF4A68A-99DC-F34A-935C-F2D897C843EE}"/>
-    <hyperlink ref="F144" r:id="rId43" xr:uid="{77C12965-63B7-CD45-BF89-23555996D07D}"/>
-    <hyperlink ref="F145" r:id="rId44" xr:uid="{02CBD596-CEDB-D442-AC7D-A0BA679ACB06}"/>
-    <hyperlink ref="F146" r:id="rId45" xr:uid="{BEE9088F-3D2C-A84B-B9B7-5B0450826FAB}"/>
-    <hyperlink ref="G147" r:id="rId46" xr:uid="{9F32E378-2E90-154B-9E27-36ACE72B8C7C}"/>
-    <hyperlink ref="F148" r:id="rId47" xr:uid="{BB8DFB0A-CB63-E249-A00B-6CCA5B11A8B1}"/>
-    <hyperlink ref="F149" r:id="rId48" xr:uid="{792A8708-49A1-8A49-9705-1B45E58A90DD}"/>
-    <hyperlink ref="F150" r:id="rId49" xr:uid="{35CBE119-889D-B14D-AF9C-E9D1E8A7BD6B}"/>
-    <hyperlink ref="F151" r:id="rId50" xr:uid="{92190858-BBBF-CC4E-8459-DEC388D54FBF}"/>
-    <hyperlink ref="F152" r:id="rId51" xr:uid="{CC6991DD-676B-AF41-9F34-ABF0F5293854}"/>
-    <hyperlink ref="F153" r:id="rId52" xr:uid="{44F865A9-229A-7B45-BB39-1A109D55CC71}"/>
-    <hyperlink ref="F154" r:id="rId53" xr:uid="{7DD2C92C-ABFA-0541-8E4D-10C68533D00E}"/>
-    <hyperlink ref="F155" r:id="rId54" xr:uid="{E7F9A324-D987-E54A-8C25-7694ACFE0A63}"/>
-    <hyperlink ref="F156" r:id="rId55" xr:uid="{4CE3613B-9104-9E4B-9E16-3B3CD00553EF}"/>
-    <hyperlink ref="F157" r:id="rId56" xr:uid="{FADF0A12-4A83-FE43-A188-FD06EA450115}"/>
-    <hyperlink ref="F158" r:id="rId57" xr:uid="{4012B00D-6984-E249-A6A7-9C00462E4980}"/>
-    <hyperlink ref="F162" r:id="rId58" xr:uid="{92616819-DF77-E745-AC19-6F91C3D7D9C8}"/>
-    <hyperlink ref="F163" r:id="rId59" xr:uid="{109C6B6E-F3F7-4941-AC9F-AEF6C711FA4A}"/>
-    <hyperlink ref="F165" r:id="rId60" xr:uid="{1AF7C07A-7294-2343-8406-22621D8D7C83}"/>
-    <hyperlink ref="G165" r:id="rId61" xr:uid="{20B24F04-580E-694A-94B9-0C7EE6DF9C60}"/>
-    <hyperlink ref="H165" r:id="rId62" xr:uid="{7E4E117C-A2DE-6344-9B1A-490E8CFF1203}"/>
-    <hyperlink ref="I165" r:id="rId63" xr:uid="{A460BBAD-A3C6-5D45-9692-6B48F54EC8B5}"/>
-    <hyperlink ref="G166" r:id="rId64" xr:uid="{A0814516-B4A9-8B49-BA1C-EA6B5B57FE11}"/>
-    <hyperlink ref="F194" r:id="rId65" xr:uid="{EAC55C19-DB8E-784F-B88C-0428DD81A7F8}"/>
-    <hyperlink ref="F197" r:id="rId66" xr:uid="{8CB4FBE6-57C0-B047-AAFD-9F3CD83FFD10}"/>
-    <hyperlink ref="G197" r:id="rId67" xr:uid="{FFCAA1D8-DDC3-6047-806C-F1FAC89C13D8}"/>
-    <hyperlink ref="H197" r:id="rId68" xr:uid="{D9FFA116-1E10-CB4A-A4D3-ADB8F9CB4544}"/>
-    <hyperlink ref="I197" r:id="rId69" xr:uid="{411043A8-358E-9848-9049-CCF4376F8EAE}"/>
-    <hyperlink ref="F204" r:id="rId70" xr:uid="{3A0149AD-FAE7-3344-B872-DABB988B8ED5}"/>
-    <hyperlink ref="G204" r:id="rId71" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view" xr:uid="{1C038C8A-4FED-2340-8337-4E6AAEBE6BB9}"/>
-    <hyperlink ref="F223" r:id="rId72" xr:uid="{8081E488-C6B9-AB40-99E3-1047D6BB28F8}"/>
-    <hyperlink ref="F224" r:id="rId73" xr:uid="{770BF84C-CF2B-8443-A426-158B3280BFB0}"/>
-    <hyperlink ref="F225" r:id="rId74" xr:uid="{A3909524-39C9-3640-8A86-3CB029647F17}"/>
-    <hyperlink ref="F226" r:id="rId75" xr:uid="{C5749CE7-A198-8144-8B57-9FE1918DD33D}"/>
-    <hyperlink ref="F227" r:id="rId76" xr:uid="{1DD65324-EB2A-7543-BF9C-73CB9FA93084}"/>
-    <hyperlink ref="F232" r:id="rId77" xr:uid="{F692241B-B08A-EF4B-856F-D79FE35D9528}"/>
-    <hyperlink ref="F235" r:id="rId78" xr:uid="{2B3077BE-507F-034E-AE81-2A0B02F26ADD}"/>
-    <hyperlink ref="F237" r:id="rId79" xr:uid="{2BA2AFE5-3289-C845-93C0-794D9FE59DC9}"/>
-    <hyperlink ref="F238" r:id="rId80" xr:uid="{C50A8610-C713-E044-81B8-614764342D66}"/>
-    <hyperlink ref="F244" r:id="rId81" xr:uid="{3A6C7766-F20C-3448-A34B-C50FCC2F91F8}"/>
+    <hyperlink ref="F5" r:id="rId1" xr:uid="{C9E8B679-DCEF-3E42-ABCB-BFEBF50167F9}"/>
+    <hyperlink ref="G8" r:id="rId2" xr:uid="{6B85D203-378C-EF4D-91B9-119DC026F3E8}"/>
+    <hyperlink ref="H15" r:id="rId3" xr:uid="{BE271FBA-E7D3-1B4E-997A-B46C6FFF8A28}"/>
+    <hyperlink ref="F16" r:id="rId4" xr:uid="{5EB059E4-1518-A54E-9011-16B3A6B9249F}"/>
+    <hyperlink ref="F39" r:id="rId5" xr:uid="{105DCE1E-6854-7246-82CC-3EFB481EAB4D}"/>
+    <hyperlink ref="F42" r:id="rId6" xr:uid="{3980170F-D1DF-FA43-A8D4-D1538E3F0248}"/>
+    <hyperlink ref="F43" r:id="rId7" xr:uid="{0B398506-EA14-9B4B-9846-856DF287B1BB}"/>
+    <hyperlink ref="F72" r:id="rId8" xr:uid="{FA465637-D96C-B049-94D5-2375320F8BF1}"/>
+    <hyperlink ref="F73" r:id="rId9" xr:uid="{45935F14-C3A2-EE48-B7C3-F6BE5EA27761}"/>
+    <hyperlink ref="F80" r:id="rId10" xr:uid="{B9F4B4B2-DD08-5D46-A5FD-F3D2C58B8D1B}"/>
+    <hyperlink ref="F82" r:id="rId11" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{6D40418B-C8FB-5C40-BCC1-54177EE04362}"/>
+    <hyperlink ref="F84" r:id="rId12" xr:uid="{59708C19-515B-C64A-9CC2-C7737CF9101D}"/>
+    <hyperlink ref="F85" r:id="rId13" xr:uid="{C0E661FF-2471-C444-AFA1-E67B91403C67}"/>
+    <hyperlink ref="F86" r:id="rId14" xr:uid="{5F782FC3-7ADE-F949-87F7-C500516CC61C}"/>
+    <hyperlink ref="F89" r:id="rId15" xr:uid="{9220AFC0-F027-8E47-8C5D-81035610A2D8}"/>
+    <hyperlink ref="F90" r:id="rId16" xr:uid="{6A8F6FC6-D4F9-3D40-B805-43F28743296D}"/>
+    <hyperlink ref="F91" r:id="rId17" xr:uid="{A0E7FE6C-9675-EA4D-B484-E708DFBABF93}"/>
+    <hyperlink ref="F92" r:id="rId18" xr:uid="{4855D83A-F4D3-D24E-B84F-EC0FF461E655}"/>
+    <hyperlink ref="F94" r:id="rId19" xr:uid="{4E8DDFA3-FE78-CB45-894D-141462FDA895}"/>
+    <hyperlink ref="F95" r:id="rId20" xr:uid="{689BFAAA-8F0E-0C4E-9C22-B29ED77EAF21}"/>
+    <hyperlink ref="F96" r:id="rId21" xr:uid="{B03E1714-A0E5-6840-87E4-626033744D9D}"/>
+    <hyperlink ref="F97" r:id="rId22" xr:uid="{C001EC90-D588-914D-B4CE-EA8F9524F001}"/>
+    <hyperlink ref="F98" r:id="rId23" xr:uid="{51E81B59-495F-1A4B-8DCD-4F0FB0F5F740}"/>
+    <hyperlink ref="F101" r:id="rId24" xr:uid="{69F44087-21F1-444B-BC92-BEDDCB6BAF31}"/>
+    <hyperlink ref="F102" r:id="rId25" xr:uid="{A1C0FEE7-104A-0146-BC92-B8097B6C3EEF}"/>
+    <hyperlink ref="F103" r:id="rId26" xr:uid="{6FE89437-B508-0B4C-AAD7-E2D46D4CD3D9}"/>
+    <hyperlink ref="F104" r:id="rId27" xr:uid="{189A0DB8-012A-384E-98A2-04DE2084D5D3}"/>
+    <hyperlink ref="F105" r:id="rId28" xr:uid="{0635A1BB-B6B3-CB4E-A7A2-351FCE023FE7}"/>
+    <hyperlink ref="F106" r:id="rId29" xr:uid="{A0B6605F-B37F-434A-8AEA-F0CB46055E22}"/>
+    <hyperlink ref="F115" r:id="rId30" xr:uid="{2EF8DF20-0EF7-4840-AC38-29C64AF5C186}"/>
+    <hyperlink ref="F118" r:id="rId31" xr:uid="{A0262EA2-DC6E-884F-80C7-303FD637A859}"/>
+    <hyperlink ref="F119" r:id="rId32" xr:uid="{049853C1-729D-9C4B-949D-FEBAE26B26D5}"/>
+    <hyperlink ref="F120" r:id="rId33" xr:uid="{59BE7560-AEC1-B64A-8B50-03D6A552F07B}"/>
+    <hyperlink ref="F121" r:id="rId34" xr:uid="{C0F51B2A-45E7-6D41-8232-DA7205EB12FB}"/>
+    <hyperlink ref="F122" r:id="rId35" xr:uid="{BF651D05-F02D-E948-B8A9-22260259738B}"/>
+    <hyperlink ref="F123" r:id="rId36" xr:uid="{DB9E6789-F281-994D-9D56-47AA19BB7556}"/>
+    <hyperlink ref="F124" r:id="rId37" xr:uid="{96A190E9-3569-5144-80C1-CEA7D46BEFDB}"/>
+    <hyperlink ref="F125" r:id="rId38" xr:uid="{F764D9D3-F1DB-5749-B1B9-5315EE113BA4}"/>
+    <hyperlink ref="F126" r:id="rId39" xr:uid="{4694032A-E86D-6145-B19F-5FE9D178BB31}"/>
+    <hyperlink ref="F132" r:id="rId40" xr:uid="{59C34E12-49FD-B942-941E-33BE339D3439}"/>
+    <hyperlink ref="F139" r:id="rId41" xr:uid="{FD8D5E73-41AD-8046-955C-15233A75A9DC}"/>
+    <hyperlink ref="F140" r:id="rId42" xr:uid="{3385E6D0-CBA5-A042-99FF-FBFBE2F24306}"/>
+    <hyperlink ref="F144" r:id="rId43" xr:uid="{63F018E8-0392-E24B-B1A6-89ED2C52F00B}"/>
+    <hyperlink ref="F145" r:id="rId44" xr:uid="{08A2D2CE-A6C4-FC45-8AE2-17B323D018A6}"/>
+    <hyperlink ref="F146" r:id="rId45" xr:uid="{17BB58AA-7748-F247-A3AA-ECA5F25C4258}"/>
+    <hyperlink ref="G147" r:id="rId46" xr:uid="{628E2625-F1D2-DC45-BB00-92D5029F1D08}"/>
+    <hyperlink ref="F148" r:id="rId47" xr:uid="{6CFE1148-9296-3643-90DE-DFAEB57BC570}"/>
+    <hyperlink ref="F149" r:id="rId48" xr:uid="{D54D40F4-8961-3348-BF74-74736CCB022E}"/>
+    <hyperlink ref="F150" r:id="rId49" xr:uid="{6848736E-2B5C-9E4D-9EAF-AD5565B47669}"/>
+    <hyperlink ref="F151" r:id="rId50" xr:uid="{D84EB54A-6097-D648-92A5-5F3BAFF86CEA}"/>
+    <hyperlink ref="F152" r:id="rId51" xr:uid="{FD4E266A-815E-BC4A-861C-189DB85BA33A}"/>
+    <hyperlink ref="F153" r:id="rId52" xr:uid="{A2A0EA72-886A-9748-BE4C-C9C26D9DAD7C}"/>
+    <hyperlink ref="F154" r:id="rId53" xr:uid="{BE24F46F-AFE5-A14D-8ECE-2632A5ADE785}"/>
+    <hyperlink ref="F155" r:id="rId54" xr:uid="{854A2A4C-C908-FB43-85DD-352E51E1CAAD}"/>
+    <hyperlink ref="F156" r:id="rId55" xr:uid="{44BD2531-CDA8-F846-AD24-E2918F203277}"/>
+    <hyperlink ref="F157" r:id="rId56" xr:uid="{27F84449-7FAE-2549-97FD-33B7C531AE93}"/>
+    <hyperlink ref="F158" r:id="rId57" xr:uid="{7866B05B-87CA-094D-B73F-0A39A87FECAC}"/>
+    <hyperlink ref="F162" r:id="rId58" xr:uid="{FC0E72F2-F249-0240-B20D-8C5D0CA7C643}"/>
+    <hyperlink ref="F163" r:id="rId59" xr:uid="{0B9FA73B-9B8D-1643-8DEF-416E2B692694}"/>
+    <hyperlink ref="F165" r:id="rId60" xr:uid="{E45AB9BA-6376-DE4C-A3FA-32BA6546F516}"/>
+    <hyperlink ref="G165" r:id="rId61" xr:uid="{64FC7EE6-2E66-3748-976A-BE443F559B9C}"/>
+    <hyperlink ref="H165" r:id="rId62" xr:uid="{321D0DB5-E98D-CF41-A801-E8B7BFF09756}"/>
+    <hyperlink ref="I165" r:id="rId63" xr:uid="{FBA7510A-B20B-1F4E-B5B5-196E1A54C85F}"/>
+    <hyperlink ref="G166" r:id="rId64" xr:uid="{A6CF9215-BFC1-5043-A4EA-EF18123960B9}"/>
+    <hyperlink ref="F181" r:id="rId65" xr:uid="{17CCB66F-91D5-5E42-8770-FEA1371E346A}"/>
+    <hyperlink ref="F194" r:id="rId66" xr:uid="{1861960A-55A4-0249-B9DC-774FEFF441E2}"/>
+    <hyperlink ref="F197" r:id="rId67" xr:uid="{7B579B5A-985A-7D4D-BBC4-1401A261A7BC}"/>
+    <hyperlink ref="G197" r:id="rId68" xr:uid="{743AEE0D-D8B7-9146-A9A6-32FB9591B58D}"/>
+    <hyperlink ref="H197" r:id="rId69" xr:uid="{579AFDDA-539F-B541-B791-E62167568FDC}"/>
+    <hyperlink ref="I197" r:id="rId70" xr:uid="{2711D5EB-3959-ED49-BBAE-F4FC4BAFBC57}"/>
+    <hyperlink ref="F204" r:id="rId71" xr:uid="{09E204B8-2078-204B-9825-CBD106A65014}"/>
+    <hyperlink ref="G204" r:id="rId72" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view" xr:uid="{BB66E76C-2D49-F845-995B-32E33B962EBA}"/>
+    <hyperlink ref="F223" r:id="rId73" xr:uid="{99EF46DF-D91D-874B-9D6E-8FCBE58F05C7}"/>
+    <hyperlink ref="F224" r:id="rId74" xr:uid="{980A4C4E-9C30-7146-9332-598508B6B67F}"/>
+    <hyperlink ref="F225" r:id="rId75" xr:uid="{1D2CA386-3A8B-3247-938F-440847E13D23}"/>
+    <hyperlink ref="F226" r:id="rId76" xr:uid="{15A4F16A-31C9-1948-A6EE-B321367E4D03}"/>
+    <hyperlink ref="F227" r:id="rId77" xr:uid="{2D745C0F-6406-C948-9BDB-1EF51C0CF6A7}"/>
+    <hyperlink ref="F232" r:id="rId78" xr:uid="{E638AB9A-C220-984B-B7C5-1F942C99283B}"/>
+    <hyperlink ref="F235" r:id="rId79" xr:uid="{DDFC1201-2B33-9346-B27C-EFA753D505D9}"/>
+    <hyperlink ref="F237" r:id="rId80" xr:uid="{98FAF202-06A9-3543-AD0A-305D677787E0}"/>
+    <hyperlink ref="F238" r:id="rId81" xr:uid="{A584D741-8D46-B349-A945-AB1D2EB0F2E7}"/>
+    <hyperlink ref="F244" r:id="rId82" xr:uid="{49E513AF-3F9C-A943-BE28-188CC71E9067}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118F691A-04DF-AA43-B897-CC32CACAF7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2A3704-4B48-A746-B87D-2122AE0FFA49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="33380" windowHeight="21580" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
+    <workbookView xWindow="-36940" yWindow="-540" windowWidth="33380" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
   <sheets>
     <sheet name="xlsx" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3062" uniqueCount="1087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3067" uniqueCount="1087">
   <si>
     <t>Household Name</t>
   </si>
@@ -3752,6 +3752,7 @@
   <dimension ref="A1:I248"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="3" max="3" width="23.5" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8813,7 +8814,9 @@
       <c r="B244" s="2" t="s">
         <v>956</v>
       </c>
-      <c r="C244" s="2"/>
+      <c r="C244" s="2" t="s">
+        <v>957</v>
+      </c>
       <c r="D244" s="2" t="s">
         <v>1071</v>
       </c>
@@ -8832,7 +8835,9 @@
       <c r="B245" s="2" t="s">
         <v>964</v>
       </c>
-      <c r="C245" s="2"/>
+      <c r="C245" s="2" t="s">
+        <v>965</v>
+      </c>
       <c r="D245" s="2" t="s">
         <v>167</v>
       </c>
@@ -8851,7 +8856,9 @@
       <c r="B246" s="2" t="s">
         <v>968</v>
       </c>
-      <c r="C246" s="2"/>
+      <c r="C246" s="2" t="s">
+        <v>969</v>
+      </c>
       <c r="D246" s="2" t="s">
         <v>167</v>
       </c>
@@ -8870,7 +8877,9 @@
       <c r="B247" s="2" t="s">
         <v>928</v>
       </c>
-      <c r="C247" s="2"/>
+      <c r="C247" s="2" t="s">
+        <v>929</v>
+      </c>
       <c r="D247" s="2"/>
       <c r="E247" s="2"/>
       <c r="F247" s="2"/>
@@ -8885,7 +8894,9 @@
       <c r="B248" s="2" t="s">
         <v>1086</v>
       </c>
-      <c r="C248" s="2"/>
+      <c r="C248" s="2" t="s">
+        <v>925</v>
+      </c>
       <c r="D248" s="2"/>
       <c r="E248" s="2"/>
       <c r="F248" s="2"/>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2A3704-4B48-A746-B87D-2122AE0FFA49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2940F7D7-3266-B143-AB41-3B0177E81272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-36940" yWindow="-540" windowWidth="33380" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3067" uniqueCount="1087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3069" uniqueCount="1087">
   <si>
     <t>Household Name</t>
   </si>
@@ -3753,6 +3753,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="23.5" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8880,7 +8881,9 @@
       <c r="C247" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="D247" s="2"/>
+      <c r="D247" s="2" t="s">
+        <v>167</v>
+      </c>
       <c r="E247" s="2"/>
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
@@ -8897,7 +8900,9 @@
       <c r="C248" s="2" t="s">
         <v>925</v>
       </c>
-      <c r="D248" s="2"/>
+      <c r="D248" s="2" t="s">
+        <v>167</v>
+      </c>
       <c r="E248" s="2"/>
       <c r="F248" s="2"/>
       <c r="G248" s="2"/>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2940F7D7-3266-B143-AB41-3B0177E81272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B884D47-DDE6-ED4F-B7B6-612342DB9BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-36940" yWindow="-540" windowWidth="33380" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3069" uniqueCount="1087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3066" uniqueCount="1087">
   <si>
     <t>Household Name</t>
   </si>
@@ -3749,7 +3749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7894B4-148E-174D-AE8B-E6DE441B89B0}">
-  <dimension ref="A1:I248"/>
+  <dimension ref="A1:I247"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="23.5" customWidth="1"/>
@@ -4131,38 +4131,42 @@
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="B18" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+      <c r="F18" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -4170,20 +4174,20 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>77</v>
+        <v>971</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -4191,93 +4195,93 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G21" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
+      <c r="I21" s="2" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H22" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="I22" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>973</v>
+        <v>94</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>93</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -4285,20 +4289,20 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -4306,64 +4310,64 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>102</v>
+        <v>974</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G26" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>672</v>
+      </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>974</v>
+        <v>109</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>672</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
@@ -4371,20 +4375,20 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -4392,20 +4396,20 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -4413,20 +4417,20 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -4434,20 +4438,20 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -4455,20 +4459,20 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E33" s="2"/>
-      <c r="F33" s="2" t="s">
-        <v>132</v>
+      <c r="F33" s="3" t="s">
+        <v>654</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -4476,20 +4480,20 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E34" s="2"/>
-      <c r="F34" s="3" t="s">
-        <v>654</v>
+      <c r="F34" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -4497,169 +4501,169 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G35" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>143</v>
+      </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>143</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E37" s="2"/>
-      <c r="F37" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G37" s="2"/>
+      <c r="F37" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>151</v>
+      </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="E38" s="2"/>
-      <c r="F38" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>151</v>
-      </c>
+      <c r="F38" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>152</v>
+        <v>1058</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="E39" s="2"/>
-      <c r="F39" s="1" t="s">
-        <v>1049</v>
-      </c>
+      <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>1058</v>
+        <v>164</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>12</v>
+        <v>167</v>
       </c>
       <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
+      <c r="F40" s="3"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>1076</v>
+      </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>1032</v>
-      </c>
+      <c r="E42" s="2"/>
       <c r="F42" s="1" t="s">
-        <v>1076</v>
+        <v>1050</v>
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
@@ -4667,20 +4671,20 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>50</v>
+        <v>168</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="1" t="s">
-        <v>1050</v>
+      <c r="F43" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -4691,17 +4695,17 @@
         <v>168</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -4712,17 +4716,17 @@
         <v>168</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -4730,20 +4734,20 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -4751,20 +4755,20 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -4772,20 +4776,20 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
@@ -4793,20 +4797,20 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -4814,20 +4818,20 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -4835,20 +4839,20 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
@@ -4856,20 +4860,22 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E52" s="2"/>
+      <c r="E52" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="F52" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
@@ -4877,22 +4883,20 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>205</v>
-      </c>
+      <c r="E53" s="2"/>
       <c r="F53" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -4900,20 +4904,20 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
@@ -4921,20 +4925,20 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
@@ -4942,20 +4946,20 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>216</v>
+        <v>674</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>217</v>
+        <v>712</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
@@ -4963,20 +4967,20 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>674</v>
+        <v>224</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>712</v>
+        <v>225</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
@@ -4984,20 +4988,20 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>225</v>
+        <v>1033</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
@@ -5005,20 +5009,20 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1033</v>
+        <v>233</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
@@ -5026,20 +5030,20 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="E60" s="2"/>
-      <c r="F60" s="2" t="s">
-        <v>234</v>
+      <c r="F60" s="3" t="s">
+        <v>657</v>
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
@@ -5047,34 +5051,32 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E61" s="2"/>
-      <c r="F61" s="3" t="s">
-        <v>657</v>
-      </c>
+      <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>155</v>
@@ -5087,79 +5089,81 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
+      <c r="F63" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E64" s="2"/>
-      <c r="F64" s="2" t="s">
-        <v>247</v>
-      </c>
+      <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
+      <c r="F65" s="3" t="s">
+        <v>658</v>
+      </c>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="E66" s="2"/>
-      <c r="F66" s="3" t="s">
-        <v>658</v>
+      <c r="F66" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
@@ -5170,17 +5174,17 @@
         <v>257</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
@@ -5188,20 +5192,20 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
@@ -5209,20 +5213,20 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
@@ -5230,20 +5234,20 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
@@ -5251,20 +5255,20 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E71" s="2"/>
-      <c r="F71" s="2" t="s">
-        <v>275</v>
+      <c r="F71" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
@@ -5275,17 +5279,17 @@
         <v>276</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="1" t="s">
-        <v>279</v>
+        <v>983</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
@@ -5293,20 +5297,20 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E73" s="2"/>
-      <c r="F73" s="1" t="s">
-        <v>983</v>
+      <c r="F73" s="2" t="s">
+        <v>285</v>
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
@@ -5314,20 +5318,22 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E74" s="2"/>
+      <c r="E74" s="2" t="s">
+        <v>289</v>
+      </c>
       <c r="F74" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
@@ -5335,22 +5341,20 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>289</v>
-      </c>
+      <c r="E75" s="2"/>
       <c r="F75" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
@@ -5358,20 +5362,20 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -5379,20 +5383,20 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="E77" s="2"/>
-      <c r="F77" s="2" t="s">
-        <v>298</v>
+      <c r="F77" s="3" t="s">
+        <v>660</v>
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
@@ -5400,100 +5404,100 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>299</v>
+        <v>164</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="E78" s="2"/>
-      <c r="F78" s="3" t="s">
-        <v>660</v>
-      </c>
+      <c r="F78" s="3"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>164</v>
+        <v>1034</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>167</v>
+        <v>12</v>
       </c>
       <c r="E79" s="2"/>
-      <c r="F79" s="3"/>
+      <c r="F79" s="1" t="s">
+        <v>996</v>
+      </c>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>1034</v>
+        <v>164</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>12</v>
+        <v>167</v>
       </c>
       <c r="E80" s="2"/>
-      <c r="F80" s="1" t="s">
-        <v>996</v>
-      </c>
+      <c r="F80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>164</v>
+        <v>311</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>167</v>
+        <v>12</v>
       </c>
       <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
+      <c r="F81" s="1" t="s">
+        <v>1035</v>
+      </c>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E82" s="2"/>
-      <c r="F82" s="1" t="s">
-        <v>1035</v>
+      <c r="F82" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
@@ -5501,20 +5505,20 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E83" s="2"/>
-      <c r="F83" s="3" t="s">
-        <v>314</v>
+      <c r="F83" s="1" t="s">
+        <v>321</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -5525,17 +5529,17 @@
         <v>318</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="1" t="s">
-        <v>321</v>
+        <v>984</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
@@ -5543,64 +5547,64 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="1" t="s">
-        <v>984</v>
-      </c>
-      <c r="G85" s="2"/>
+        <v>985</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>327</v>
+      </c>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E86" s="2"/>
-      <c r="F86" s="1" t="s">
-        <v>985</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>327</v>
-      </c>
+      <c r="F86" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
@@ -5608,20 +5612,20 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E88" s="2"/>
-      <c r="F88" s="2" t="s">
-        <v>335</v>
+      <c r="F88" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -5632,17 +5636,17 @@
         <v>343</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="1" t="s">
-        <v>338</v>
+        <v>986</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -5653,17 +5657,17 @@
         <v>343</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -5671,20 +5675,20 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>343</v>
+        <v>988</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" s="1" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -5692,20 +5696,20 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E92" s="2"/>
-      <c r="F92" s="1" t="s">
-        <v>989</v>
+      <c r="F92" s="5" t="s">
+        <v>338</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -5713,20 +5717,20 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E93" s="2"/>
-      <c r="F93" s="5" t="s">
-        <v>338</v>
+      <c r="F93" s="1" t="s">
+        <v>992</v>
       </c>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -5734,20 +5738,20 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>991</v>
+        <v>350</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="1" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -5755,20 +5759,20 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>351</v>
+        <v>220</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>352</v>
+        <v>221</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="1" t="s">
-        <v>993</v>
+        <v>355</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -5779,17 +5783,17 @@
         <v>354</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>220</v>
+        <v>356</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>221</v>
+        <v>357</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="1" t="s">
-        <v>355</v>
+        <v>994</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -5800,17 +5804,17 @@
         <v>354</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
@@ -5818,20 +5822,20 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E98" s="2"/>
-      <c r="F98" s="1" t="s">
-        <v>995</v>
+      <c r="F98" s="2" t="s">
+        <v>363</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
@@ -5839,20 +5843,20 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>360</v>
+        <v>305</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2" t="s">
-        <v>363</v>
+        <v>308</v>
       </c>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
@@ -5860,20 +5864,20 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>305</v>
+        <v>364</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E100" s="2"/>
-      <c r="F100" s="2" t="s">
-        <v>308</v>
+      <c r="F100" s="1" t="s">
+        <v>997</v>
       </c>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
@@ -5884,17 +5888,17 @@
         <v>364</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="1" t="s">
-        <v>997</v>
+        <v>367</v>
       </c>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
@@ -5902,20 +5906,20 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="1" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
@@ -5926,17 +5930,17 @@
         <v>372</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="1" t="s">
-        <v>375</v>
+        <v>998</v>
       </c>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -5944,20 +5948,20 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="1" t="s">
-        <v>998</v>
+        <v>381</v>
       </c>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -5968,17 +5972,17 @@
         <v>378</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" s="1" t="s">
-        <v>381</v>
+        <v>999</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -5986,20 +5990,20 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="E106" s="2"/>
-      <c r="F106" s="1" t="s">
-        <v>999</v>
+      <c r="F106" s="3" t="s">
+        <v>662</v>
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -6007,20 +6011,20 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E107" s="2"/>
-      <c r="F107" s="3" t="s">
-        <v>662</v>
+      <c r="F107" s="5" t="s">
+        <v>390</v>
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
@@ -6028,20 +6032,20 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E108" s="2"/>
-      <c r="F108" s="5" t="s">
-        <v>390</v>
+      <c r="F108" s="3" t="s">
+        <v>663</v>
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
@@ -6049,20 +6053,20 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="3" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
@@ -6073,10 +6077,10 @@
         <v>396</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>155</v>
@@ -6091,21 +6095,19 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="E111" s="2"/>
-      <c r="F111" s="3" t="s">
-        <v>664</v>
-      </c>
+      <c r="F111" s="2"/>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
@@ -6115,10 +6117,10 @@
         <v>401</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>12</v>
@@ -6134,10 +6136,10 @@
         <v>401</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>12</v>
@@ -6150,39 +6152,41 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>401</v>
+        <v>1036</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E114" s="2"/>
-      <c r="F114" s="2"/>
+      <c r="F114" s="1" t="s">
+        <v>1051</v>
+      </c>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>1036</v>
+        <v>410</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E115" s="2"/>
-      <c r="F115" s="1" t="s">
-        <v>1051</v>
+      <c r="F115" s="2" t="s">
+        <v>413</v>
       </c>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
@@ -6193,17 +6197,17 @@
         <v>410</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
@@ -6211,20 +6215,20 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E117" s="2"/>
-      <c r="F117" s="2" t="s">
-        <v>416</v>
+      <c r="F117" s="1" t="s">
+        <v>675</v>
       </c>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
@@ -6235,10 +6239,10 @@
         <v>417</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>12</v>
@@ -6256,10 +6260,10 @@
         <v>417</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>12</v>
@@ -6274,20 +6278,20 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="1" t="s">
-        <v>675</v>
+        <v>427</v>
       </c>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
@@ -6298,17 +6302,17 @@
         <v>424</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="1" t="s">
-        <v>427</v>
+        <v>1000</v>
       </c>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
@@ -6319,17 +6323,17 @@
         <v>424</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
@@ -6340,17 +6344,17 @@
         <v>424</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
@@ -6361,17 +6365,17 @@
         <v>424</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="1" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
@@ -6379,20 +6383,20 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>424</v>
+        <v>1077</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="1" t="s">
-        <v>1003</v>
+        <v>1078</v>
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
@@ -6400,20 +6404,20 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>1077</v>
+        <v>440</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E126" s="2"/>
-      <c r="F126" s="1" t="s">
-        <v>1078</v>
+      <c r="F126" s="2" t="s">
+        <v>443</v>
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
@@ -6421,20 +6425,20 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
@@ -6445,17 +6449,17 @@
         <v>447</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
@@ -6463,20 +6467,22 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E129" s="2"/>
+      <c r="E129" s="2" t="s">
+        <v>1037</v>
+      </c>
       <c r="F129" s="2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
@@ -6484,22 +6490,22 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F130" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>665</v>
       </c>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
@@ -6507,22 +6513,20 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E131" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="F131" s="3" t="s">
-        <v>665</v>
+      <c r="E131" s="2"/>
+      <c r="F131" s="1" t="s">
+        <v>676</v>
       </c>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
@@ -6530,20 +6534,22 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E132" s="2"/>
-      <c r="F132" s="1" t="s">
-        <v>676</v>
+      <c r="E132" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>465</v>
       </c>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
@@ -6551,22 +6557,20 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E133" s="2" t="s">
-        <v>458</v>
-      </c>
+      <c r="E133" s="2"/>
       <c r="F133" s="2" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
@@ -6574,20 +6578,20 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
@@ -6595,20 +6599,22 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E135" s="2"/>
+      <c r="E135" s="2" t="s">
+        <v>1038</v>
+      </c>
       <c r="F135" s="2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
@@ -6616,22 +6622,20 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E136" s="2" t="s">
-        <v>1038</v>
-      </c>
+      <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
@@ -6639,20 +6643,20 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" s="2" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
@@ -6660,20 +6664,20 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E138" s="2"/>
-      <c r="F138" s="2" t="s">
-        <v>485</v>
+      <c r="F138" s="1" t="s">
+        <v>493</v>
       </c>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
@@ -6681,20 +6685,22 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
-        <v>490</v>
+        <v>1079</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E139" s="2"/>
+      <c r="E139" s="2" t="s">
+        <v>1080</v>
+      </c>
       <c r="F139" s="1" t="s">
-        <v>493</v>
+        <v>666</v>
       </c>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
@@ -6702,22 +6708,20 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
-        <v>1079</v>
+        <v>17</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E140" s="2" t="s">
-        <v>1080</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>666</v>
+      <c r="E140" s="2"/>
+      <c r="F140" s="3" t="s">
+        <v>667</v>
       </c>
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
@@ -6728,10 +6732,10 @@
         <v>17</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>12</v>
@@ -6749,10 +6753,10 @@
         <v>17</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>12</v>
@@ -6767,20 +6771,22 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
-        <v>17</v>
+        <v>500</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E143" s="2"/>
-      <c r="F143" s="3" t="s">
-        <v>667</v>
+      <c r="E143" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>503</v>
       </c>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
@@ -6791,10 +6797,10 @@
         <v>500</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>12</v>
@@ -6803,7 +6809,7 @@
         <v>1039</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>503</v>
+        <v>1004</v>
       </c>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
@@ -6814,10 +6820,10 @@
         <v>500</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>12</v>
@@ -6826,7 +6832,7 @@
         <v>1039</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
@@ -6834,66 +6840,64 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>500</v>
+        <v>1046</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E146" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>1005</v>
-      </c>
-      <c r="G146" s="2"/>
+      <c r="E146" s="2"/>
+      <c r="F146" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>1052</v>
+      </c>
       <c r="H146" s="2"/>
       <c r="I146" s="2"/>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>1046</v>
+        <v>350</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E147" s="2"/>
-      <c r="F147" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>1052</v>
-      </c>
+      <c r="F147" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G147" s="2"/>
       <c r="H147" s="2"/>
       <c r="I147" s="2"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
-        <v>350</v>
+        <v>516</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="1" t="s">
-        <v>353</v>
+        <v>519</v>
       </c>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
@@ -6904,17 +6908,17 @@
         <v>516</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="1" t="s">
-        <v>519</v>
+        <v>1006</v>
       </c>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
@@ -6925,17 +6929,17 @@
         <v>516</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
@@ -6943,20 +6947,20 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
@@ -6967,17 +6971,17 @@
         <v>524</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
@@ -6988,17 +6992,17 @@
         <v>524</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" s="1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
@@ -7006,20 +7010,20 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
-        <v>524</v>
+        <v>372</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
@@ -7027,20 +7031,20 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
-        <v>372</v>
+        <v>533</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" s="1" t="s">
-        <v>1011</v>
+        <v>538</v>
       </c>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
@@ -7051,17 +7055,17 @@
         <v>533</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" s="1" t="s">
-        <v>538</v>
+        <v>1012</v>
       </c>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
@@ -7072,17 +7076,17 @@
         <v>533</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
@@ -7090,20 +7094,20 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E158" s="2"/>
-      <c r="F158" s="1" t="s">
-        <v>1013</v>
+      <c r="F158" s="2" t="s">
+        <v>544</v>
       </c>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
@@ -7111,20 +7115,20 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" s="2" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
@@ -7132,20 +7136,22 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E160" s="2"/>
+      <c r="E160" s="2" t="s">
+        <v>552</v>
+      </c>
       <c r="F160" s="2" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
@@ -7153,22 +7159,22 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
-        <v>549</v>
+        <v>1014</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="F161" s="2" t="s">
-        <v>553</v>
+        <v>1015</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>1016</v>
       </c>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
@@ -7176,22 +7182,22 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
@@ -7199,22 +7205,20 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
-        <v>1017</v>
+        <v>558</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>556</v>
+        <v>388</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>557</v>
+        <v>389</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E163" s="2" t="s">
-        <v>1018</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>1019</v>
+      <c r="E163" s="2"/>
+      <c r="F163" s="2" t="s">
+        <v>561</v>
       </c>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
@@ -7222,92 +7226,90 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
-        <v>558</v>
+        <v>1020</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>388</v>
+        <v>559</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>389</v>
+        <v>560</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>12</v>
+        <v>980</v>
       </c>
       <c r="E164" s="2"/>
-      <c r="F164" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="G164" s="2"/>
-      <c r="H164" s="2"/>
-      <c r="I164" s="2"/>
+      <c r="F164" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>1024</v>
+      </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
-        <v>1020</v>
+        <v>562</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>560</v>
+        <v>677</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>980</v>
+        <v>12</v>
       </c>
       <c r="E165" s="2"/>
-      <c r="F165" s="1" t="s">
-        <v>1021</v>
+      <c r="F165" s="3" t="s">
+        <v>668</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>1022</v>
-      </c>
-      <c r="H165" s="1" t="s">
-        <v>1023</v>
-      </c>
-      <c r="I165" s="1" t="s">
-        <v>1024</v>
-      </c>
+        <v>673</v>
+      </c>
+      <c r="H165" s="2"/>
+      <c r="I165" s="2"/>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="G166" s="1" t="s">
-        <v>673</v>
-      </c>
+        <v>669</v>
+      </c>
+      <c r="G166" s="2"/>
       <c r="H166" s="2"/>
       <c r="I166" s="2"/>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>678</v>
+        <v>568</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>155</v>
+        <v>569</v>
       </c>
       <c r="E167" s="2"/>
-      <c r="F167" s="3" t="s">
-        <v>669</v>
-      </c>
+      <c r="F167" s="2"/>
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
       <c r="I167" s="2"/>
@@ -7317,10 +7319,10 @@
         <v>566</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>569</v>
@@ -7336,10 +7338,10 @@
         <v>566</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>569</v>
@@ -7355,10 +7357,10 @@
         <v>566</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>569</v>
@@ -7374,10 +7376,10 @@
         <v>566</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>569</v>
@@ -7393,10 +7395,10 @@
         <v>566</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>569</v>
@@ -7412,10 +7414,10 @@
         <v>566</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>569</v>
@@ -7431,10 +7433,10 @@
         <v>566</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>569</v>
@@ -7450,10 +7452,10 @@
         <v>566</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>569</v>
@@ -7469,10 +7471,10 @@
         <v>566</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>569</v>
@@ -7488,10 +7490,10 @@
         <v>566</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>569</v>
@@ -7507,10 +7509,10 @@
         <v>566</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>569</v>
@@ -7526,10 +7528,10 @@
         <v>566</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>569</v>
@@ -7542,53 +7544,53 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
-        <v>566</v>
+        <v>1082</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>569</v>
+        <v>12</v>
       </c>
       <c r="E180" s="2"/>
-      <c r="F180" s="2"/>
+      <c r="F180" s="1" t="s">
+        <v>1083</v>
+      </c>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
       <c r="I180" s="2"/>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A181" s="2" t="s">
-        <v>1082</v>
+      <c r="A181" s="8">
+        <v>46024</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>12</v>
+        <v>569</v>
       </c>
       <c r="E181" s="2"/>
-      <c r="F181" s="1" t="s">
-        <v>1083</v>
-      </c>
+      <c r="F181" s="2"/>
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
       <c r="I181" s="2"/>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A182" s="8">
-        <v>46024</v>
+      <c r="A182" s="2" t="s">
+        <v>566</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>597</v>
+        <v>680</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>569</v>
@@ -7604,10 +7606,10 @@
         <v>566</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>569</v>
@@ -7623,10 +7625,10 @@
         <v>566</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>569</v>
@@ -7642,10 +7644,10 @@
         <v>566</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>569</v>
@@ -7661,10 +7663,10 @@
         <v>566</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>569</v>
@@ -7680,10 +7682,10 @@
         <v>566</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>569</v>
@@ -7699,10 +7701,10 @@
         <v>566</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>569</v>
@@ -7718,10 +7720,10 @@
         <v>566</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>569</v>
@@ -7737,10 +7739,10 @@
         <v>566</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>569</v>
@@ -7756,10 +7758,10 @@
         <v>566</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>569</v>
@@ -7775,10 +7777,10 @@
         <v>566</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>569</v>
@@ -7791,128 +7793,128 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" s="2" t="s">
-        <v>566</v>
+        <v>1059</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>608</v>
+        <v>757</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>690</v>
+        <v>758</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="E193" s="2"/>
-      <c r="F193" s="2"/>
+        <v>1060</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>1062</v>
+      </c>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
       <c r="I193" s="2"/>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
-        <v>1059</v>
+        <v>164</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>757</v>
+        <v>613</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>758</v>
+        <v>692</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>1060</v>
-      </c>
-      <c r="E194" s="2" t="s">
-        <v>1061</v>
-      </c>
-      <c r="F194" s="1" t="s">
-        <v>1062</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="E194" s="2"/>
+      <c r="F194" s="3"/>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
       <c r="I194" s="2"/>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
-        <v>164</v>
+        <v>614</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="E195" s="2"/>
-      <c r="F195" s="3"/>
+      <c r="F195" s="3" t="s">
+        <v>671</v>
+      </c>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
       <c r="I195" s="2"/>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
-        <v>614</v>
+        <v>1020</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>155</v>
+        <v>980</v>
       </c>
       <c r="E196" s="2"/>
-      <c r="F196" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="G196" s="2"/>
-      <c r="H196" s="2"/>
-      <c r="I196" s="2"/>
+      <c r="F196" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H196" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="I196" s="1" t="s">
+        <v>1028</v>
+      </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
-        <v>1020</v>
+        <v>164</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>980</v>
+        <v>167</v>
       </c>
       <c r="E197" s="2"/>
-      <c r="F197" s="1" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G197" s="1" t="s">
-        <v>1026</v>
-      </c>
-      <c r="H197" s="1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="I197" s="1" t="s">
-        <v>1028</v>
-      </c>
+      <c r="F197" s="2"/>
+      <c r="G197" s="2"/>
+      <c r="H197" s="2"/>
+      <c r="I197" s="2"/>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
         <v>164</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E198" s="2"/>
-      <c r="F198" s="2"/>
+      <c r="F198" s="3"/>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
       <c r="I198" s="2"/>
@@ -7922,16 +7924,16 @@
         <v>164</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E199" s="2"/>
-      <c r="F199" s="3"/>
+      <c r="F199" s="2"/>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
       <c r="I199" s="2"/>
@@ -7941,10 +7943,10 @@
         <v>164</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>167</v>
@@ -7960,10 +7962,10 @@
         <v>164</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>698</v>
+        <v>622</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>167</v>
@@ -7976,18 +7978,18 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
-        <v>164</v>
+        <v>1059</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E202" s="2"/>
+      <c r="E202" s="9"/>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
@@ -7995,45 +7997,45 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E203" s="9"/>
-      <c r="F203" s="2"/>
-      <c r="G203" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>1065</v>
+      </c>
       <c r="H203" s="2"/>
       <c r="I203" s="2"/>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
-        <v>1063</v>
+        <v>164</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E204" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="F204" s="1" t="s">
-        <v>1066</v>
-      </c>
-      <c r="G204" s="1" t="s">
-        <v>1065</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="E204" s="2"/>
+      <c r="F204" s="2"/>
+      <c r="G204" s="2"/>
       <c r="H204" s="2"/>
       <c r="I204" s="2"/>
     </row>
@@ -8042,10 +8044,10 @@
         <v>164</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>167</v>
@@ -8061,10 +8063,10 @@
         <v>164</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>167</v>
@@ -8079,11 +8081,11 @@
       <c r="A207" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B207" s="2" t="s">
-        <v>631</v>
+      <c r="B207" s="7" t="s">
+        <v>633</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>167</v>
@@ -8098,11 +8100,11 @@
       <c r="A208" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B208" s="7" t="s">
-        <v>633</v>
+      <c r="B208" s="2" t="s">
+        <v>635</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>167</v>
@@ -8118,10 +8120,10 @@
         <v>164</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>167</v>
@@ -8134,16 +8136,16 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
-        <v>164</v>
+        <v>639</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>167</v>
+        <v>639</v>
       </c>
       <c r="E210" s="2"/>
       <c r="F210" s="2"/>
@@ -8156,10 +8158,10 @@
         <v>639</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>639</v>
@@ -8175,10 +8177,10 @@
         <v>639</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>639</v>
@@ -8194,10 +8196,10 @@
         <v>639</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>639</v>
@@ -8210,16 +8212,16 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
-        <v>639</v>
+        <v>566</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>639</v>
+        <v>569</v>
       </c>
       <c r="E214" s="2"/>
       <c r="F214" s="2"/>
@@ -8232,10 +8234,10 @@
         <v>566</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>569</v>
@@ -8251,10 +8253,10 @@
         <v>566</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>569</v>
@@ -8270,10 +8272,10 @@
         <v>566</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>652</v>
+        <v>699</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>653</v>
+        <v>713</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>569</v>
@@ -8288,11 +8290,11 @@
       <c r="A218" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="B218" s="2" t="s">
-        <v>699</v>
+      <c r="B218" s="7" t="s">
+        <v>700</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>569</v>
@@ -8307,11 +8309,11 @@
       <c r="A219" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="B219" s="7" t="s">
-        <v>700</v>
+      <c r="B219" s="2" t="s">
+        <v>701</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>569</v>
@@ -8327,10 +8329,10 @@
         <v>566</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>715</v>
+        <v>867</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>569</v>
@@ -8345,11 +8347,11 @@
       <c r="A221" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="B221" s="2" t="s">
-        <v>702</v>
+      <c r="B221" s="7" t="s">
+        <v>703</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>569</v>
@@ -8362,39 +8364,43 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="B222" s="7" t="s">
-        <v>703</v>
+        <v>1029</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>704</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>866</v>
+        <v>930</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>569</v>
+        <v>980</v>
       </c>
       <c r="E222" s="2"/>
-      <c r="F222" s="2"/>
+      <c r="F222" s="1" t="s">
+        <v>1030</v>
+      </c>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
       <c r="I222" s="2"/>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" s="2" t="s">
-        <v>1029</v>
+        <v>979</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="E223" s="2"/>
+      <c r="E223" s="2" t="s">
+        <v>981</v>
+      </c>
       <c r="F223" s="1" t="s">
-        <v>1030</v>
+        <v>982</v>
       </c>
       <c r="G223" s="2"/>
       <c r="H223" s="2"/>
@@ -8402,22 +8408,22 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
-        <v>979</v>
+        <v>1044</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>980</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>981</v>
+        <v>1045</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>982</v>
+        <v>1053</v>
       </c>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
@@ -8425,22 +8431,20 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" s="2" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>939</v>
+        <v>732</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="E225" s="2" t="s">
-        <v>1045</v>
-      </c>
+      <c r="E225" s="2"/>
       <c r="F225" s="1" t="s">
-        <v>1053</v>
+        <v>1043</v>
       </c>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
@@ -8448,20 +8452,20 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
-        <v>1040</v>
+        <v>1068</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>732</v>
+        <v>868</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>980</v>
+        <v>569</v>
       </c>
       <c r="E226" s="2"/>
       <c r="F226" s="1" t="s">
-        <v>1043</v>
+        <v>1069</v>
       </c>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
@@ -8469,21 +8473,19 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" s="2" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>710</v>
+        <v>566</v>
+      </c>
+      <c r="B227" s="7" t="s">
+        <v>703</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>569</v>
       </c>
       <c r="E227" s="2"/>
-      <c r="F227" s="1" t="s">
-        <v>1069</v>
-      </c>
+      <c r="F227" s="2"/>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
       <c r="I227" s="2"/>
@@ -8492,11 +8494,11 @@
       <c r="A228" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="B228" s="7" t="s">
-        <v>703</v>
+      <c r="B228" s="2" t="s">
+        <v>711</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>569</v>
@@ -8511,11 +8513,11 @@
       <c r="A229" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="B229" s="2" t="s">
-        <v>711</v>
+      <c r="B229" s="7" t="s">
+        <v>700</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>873</v>
+        <v>714</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>569</v>
@@ -8528,18 +8530,20 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="B230" s="7" t="s">
-        <v>700</v>
+        <v>1084</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>864</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>714</v>
+        <v>865</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="E230" s="2"/>
+        <v>1071</v>
+      </c>
+      <c r="E230" s="10" t="s">
+        <v>1085</v>
+      </c>
       <c r="F230" s="2"/>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
@@ -8547,44 +8551,42 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" s="2" t="s">
-        <v>1084</v>
+        <v>1041</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>864</v>
+        <v>833</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>865</v>
+        <v>834</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E231" s="10" t="s">
-        <v>1085</v>
-      </c>
-      <c r="F231" s="2"/>
+        <v>980</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F231" s="1" t="s">
+        <v>390</v>
+      </c>
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
       <c r="I231" s="2"/>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
-        <v>1041</v>
+        <v>566</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>833</v>
+        <v>878</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>834</v>
+        <v>879</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>980</v>
-      </c>
-      <c r="E232" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F232" s="1" t="s">
-        <v>390</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="E232" s="2"/>
+      <c r="F232" s="2"/>
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
       <c r="I232" s="2"/>
@@ -8594,10 +8596,10 @@
         <v>566</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>878</v>
+        <v>922</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>879</v>
+        <v>923</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>569</v>
@@ -8610,39 +8612,41 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" s="2" t="s">
-        <v>566</v>
+        <v>1070</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>922</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>923</v>
+        <v>509</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>510</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>569</v>
+        <v>1071</v>
       </c>
       <c r="E234" s="2"/>
-      <c r="F234" s="2"/>
+      <c r="F234" s="1" t="s">
+        <v>1072</v>
+      </c>
       <c r="G234" s="2"/>
       <c r="H234" s="2"/>
       <c r="I234" s="2"/>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="2" t="s">
-        <v>1070</v>
+        <v>609</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="C235" s="4" t="s">
-        <v>510</v>
+        <v>759</v>
+      </c>
+      <c r="C235" s="6" t="s">
+        <v>760</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>1071</v>
+        <v>980</v>
       </c>
       <c r="E235" s="2"/>
-      <c r="F235" s="1" t="s">
-        <v>1072</v>
+      <c r="F235" s="2" t="s">
+        <v>611</v>
       </c>
       <c r="G235" s="2"/>
       <c r="H235" s="2"/>
@@ -8650,20 +8654,20 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
-        <v>609</v>
+        <v>1067</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="C236" s="6" t="s">
-        <v>760</v>
+        <v>255</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>256</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>980</v>
+        <v>155</v>
       </c>
       <c r="E236" s="2"/>
-      <c r="F236" s="2" t="s">
-        <v>611</v>
+      <c r="F236" s="1" t="s">
+        <v>659</v>
       </c>
       <c r="G236" s="2"/>
       <c r="H236" s="2"/>
@@ -8671,20 +8675,20 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B237" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>256</v>
+        <v>508</v>
+      </c>
+      <c r="B237" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>634</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E237" s="2"/>
       <c r="F237" s="1" t="s">
-        <v>659</v>
+        <v>1054</v>
       </c>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
@@ -8692,41 +8696,39 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="B238" s="7" t="s">
-        <v>633</v>
-      </c>
-      <c r="C238" s="4" t="s">
-        <v>634</v>
+        <v>164</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>938</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E238" s="2"/>
-      <c r="F238" s="1" t="s">
-        <v>1054</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F238" s="2"/>
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
       <c r="I238" s="2"/>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A239" s="2" t="s">
-        <v>164</v>
+        <v>1074</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>937</v>
+        <v>966</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>938</v>
+        <v>967</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>1073</v>
-      </c>
+        <v>1071</v>
+      </c>
+      <c r="E239" s="2"/>
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
       <c r="H239" s="2"/>
@@ -8734,16 +8736,16 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
-        <v>1074</v>
+        <v>566</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>966</v>
+        <v>948</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>967</v>
+        <v>949</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>1071</v>
+        <v>569</v>
       </c>
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
@@ -8756,10 +8758,10 @@
         <v>566</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>948</v>
+        <v>890</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>949</v>
+        <v>891</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>569</v>
@@ -8775,10 +8777,10 @@
         <v>566</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>890</v>
+        <v>869</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>891</v>
+        <v>870</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>569</v>
@@ -8791,40 +8793,42 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" s="2" t="s">
-        <v>566</v>
+        <v>436</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>869</v>
+        <v>956</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>870</v>
+        <v>957</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>569</v>
+        <v>1071</v>
       </c>
       <c r="E243" s="2"/>
-      <c r="F243" s="2"/>
+      <c r="F243" s="1" t="s">
+        <v>439</v>
+      </c>
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
       <c r="I243" s="2"/>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" s="2" t="s">
-        <v>436</v>
+        <v>164</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E244" s="2"/>
-      <c r="F244" s="1" t="s">
-        <v>439</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F244" s="2"/>
       <c r="G244" s="2"/>
       <c r="H244" s="2"/>
       <c r="I244" s="2"/>
@@ -8834,10 +8838,10 @@
         <v>164</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>167</v>
@@ -8855,17 +8859,15 @@
         <v>164</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>968</v>
+        <v>928</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>969</v>
+        <v>929</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E246" s="2" t="s">
-        <v>1081</v>
-      </c>
+      <c r="E246" s="2"/>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
@@ -8876,10 +8878,10 @@
         <v>164</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>928</v>
+        <v>1086</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>167</v>
@@ -8889,25 +8891,6 @@
       <c r="G247" s="2"/>
       <c r="H247" s="2"/>
       <c r="I247" s="2"/>
-    </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A248" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>925</v>
-      </c>
-      <c r="D248" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E248" s="2"/>
-      <c r="F248" s="2"/>
-      <c r="G248" s="2"/>
-      <c r="H248" s="2"/>
-      <c r="I248" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -8916,84 +8899,84 @@
     <hyperlink ref="G8" r:id="rId2" xr:uid="{6B85D203-378C-EF4D-91B9-119DC026F3E8}"/>
     <hyperlink ref="H15" r:id="rId3" xr:uid="{BE271FBA-E7D3-1B4E-997A-B46C6FFF8A28}"/>
     <hyperlink ref="F16" r:id="rId4" xr:uid="{5EB059E4-1518-A54E-9011-16B3A6B9249F}"/>
-    <hyperlink ref="F39" r:id="rId5" xr:uid="{105DCE1E-6854-7246-82CC-3EFB481EAB4D}"/>
-    <hyperlink ref="F42" r:id="rId6" xr:uid="{3980170F-D1DF-FA43-A8D4-D1538E3F0248}"/>
-    <hyperlink ref="F43" r:id="rId7" xr:uid="{0B398506-EA14-9B4B-9846-856DF287B1BB}"/>
-    <hyperlink ref="F72" r:id="rId8" xr:uid="{FA465637-D96C-B049-94D5-2375320F8BF1}"/>
-    <hyperlink ref="F73" r:id="rId9" xr:uid="{45935F14-C3A2-EE48-B7C3-F6BE5EA27761}"/>
-    <hyperlink ref="F80" r:id="rId10" xr:uid="{B9F4B4B2-DD08-5D46-A5FD-F3D2C58B8D1B}"/>
-    <hyperlink ref="F82" r:id="rId11" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{6D40418B-C8FB-5C40-BCC1-54177EE04362}"/>
-    <hyperlink ref="F84" r:id="rId12" xr:uid="{59708C19-515B-C64A-9CC2-C7737CF9101D}"/>
-    <hyperlink ref="F85" r:id="rId13" xr:uid="{C0E661FF-2471-C444-AFA1-E67B91403C67}"/>
-    <hyperlink ref="F86" r:id="rId14" xr:uid="{5F782FC3-7ADE-F949-87F7-C500516CC61C}"/>
-    <hyperlink ref="F89" r:id="rId15" xr:uid="{9220AFC0-F027-8E47-8C5D-81035610A2D8}"/>
-    <hyperlink ref="F90" r:id="rId16" xr:uid="{6A8F6FC6-D4F9-3D40-B805-43F28743296D}"/>
-    <hyperlink ref="F91" r:id="rId17" xr:uid="{A0E7FE6C-9675-EA4D-B484-E708DFBABF93}"/>
-    <hyperlink ref="F92" r:id="rId18" xr:uid="{4855D83A-F4D3-D24E-B84F-EC0FF461E655}"/>
-    <hyperlink ref="F94" r:id="rId19" xr:uid="{4E8DDFA3-FE78-CB45-894D-141462FDA895}"/>
-    <hyperlink ref="F95" r:id="rId20" xr:uid="{689BFAAA-8F0E-0C4E-9C22-B29ED77EAF21}"/>
-    <hyperlink ref="F96" r:id="rId21" xr:uid="{B03E1714-A0E5-6840-87E4-626033744D9D}"/>
-    <hyperlink ref="F97" r:id="rId22" xr:uid="{C001EC90-D588-914D-B4CE-EA8F9524F001}"/>
-    <hyperlink ref="F98" r:id="rId23" xr:uid="{51E81B59-495F-1A4B-8DCD-4F0FB0F5F740}"/>
-    <hyperlink ref="F101" r:id="rId24" xr:uid="{69F44087-21F1-444B-BC92-BEDDCB6BAF31}"/>
-    <hyperlink ref="F102" r:id="rId25" xr:uid="{A1C0FEE7-104A-0146-BC92-B8097B6C3EEF}"/>
-    <hyperlink ref="F103" r:id="rId26" xr:uid="{6FE89437-B508-0B4C-AAD7-E2D46D4CD3D9}"/>
-    <hyperlink ref="F104" r:id="rId27" xr:uid="{189A0DB8-012A-384E-98A2-04DE2084D5D3}"/>
-    <hyperlink ref="F105" r:id="rId28" xr:uid="{0635A1BB-B6B3-CB4E-A7A2-351FCE023FE7}"/>
-    <hyperlink ref="F106" r:id="rId29" xr:uid="{A0B6605F-B37F-434A-8AEA-F0CB46055E22}"/>
-    <hyperlink ref="F115" r:id="rId30" xr:uid="{2EF8DF20-0EF7-4840-AC38-29C64AF5C186}"/>
-    <hyperlink ref="F118" r:id="rId31" xr:uid="{A0262EA2-DC6E-884F-80C7-303FD637A859}"/>
-    <hyperlink ref="F119" r:id="rId32" xr:uid="{049853C1-729D-9C4B-949D-FEBAE26B26D5}"/>
-    <hyperlink ref="F120" r:id="rId33" xr:uid="{59BE7560-AEC1-B64A-8B50-03D6A552F07B}"/>
-    <hyperlink ref="F121" r:id="rId34" xr:uid="{C0F51B2A-45E7-6D41-8232-DA7205EB12FB}"/>
-    <hyperlink ref="F122" r:id="rId35" xr:uid="{BF651D05-F02D-E948-B8A9-22260259738B}"/>
-    <hyperlink ref="F123" r:id="rId36" xr:uid="{DB9E6789-F281-994D-9D56-47AA19BB7556}"/>
-    <hyperlink ref="F124" r:id="rId37" xr:uid="{96A190E9-3569-5144-80C1-CEA7D46BEFDB}"/>
-    <hyperlink ref="F125" r:id="rId38" xr:uid="{F764D9D3-F1DB-5749-B1B9-5315EE113BA4}"/>
-    <hyperlink ref="F126" r:id="rId39" xr:uid="{4694032A-E86D-6145-B19F-5FE9D178BB31}"/>
-    <hyperlink ref="F132" r:id="rId40" xr:uid="{59C34E12-49FD-B942-941E-33BE339D3439}"/>
-    <hyperlink ref="F139" r:id="rId41" xr:uid="{FD8D5E73-41AD-8046-955C-15233A75A9DC}"/>
-    <hyperlink ref="F140" r:id="rId42" xr:uid="{3385E6D0-CBA5-A042-99FF-FBFBE2F24306}"/>
-    <hyperlink ref="F144" r:id="rId43" xr:uid="{63F018E8-0392-E24B-B1A6-89ED2C52F00B}"/>
-    <hyperlink ref="F145" r:id="rId44" xr:uid="{08A2D2CE-A6C4-FC45-8AE2-17B323D018A6}"/>
-    <hyperlink ref="F146" r:id="rId45" xr:uid="{17BB58AA-7748-F247-A3AA-ECA5F25C4258}"/>
-    <hyperlink ref="G147" r:id="rId46" xr:uid="{628E2625-F1D2-DC45-BB00-92D5029F1D08}"/>
-    <hyperlink ref="F148" r:id="rId47" xr:uid="{6CFE1148-9296-3643-90DE-DFAEB57BC570}"/>
-    <hyperlink ref="F149" r:id="rId48" xr:uid="{D54D40F4-8961-3348-BF74-74736CCB022E}"/>
-    <hyperlink ref="F150" r:id="rId49" xr:uid="{6848736E-2B5C-9E4D-9EAF-AD5565B47669}"/>
-    <hyperlink ref="F151" r:id="rId50" xr:uid="{D84EB54A-6097-D648-92A5-5F3BAFF86CEA}"/>
-    <hyperlink ref="F152" r:id="rId51" xr:uid="{FD4E266A-815E-BC4A-861C-189DB85BA33A}"/>
-    <hyperlink ref="F153" r:id="rId52" xr:uid="{A2A0EA72-886A-9748-BE4C-C9C26D9DAD7C}"/>
-    <hyperlink ref="F154" r:id="rId53" xr:uid="{BE24F46F-AFE5-A14D-8ECE-2632A5ADE785}"/>
-    <hyperlink ref="F155" r:id="rId54" xr:uid="{854A2A4C-C908-FB43-85DD-352E51E1CAAD}"/>
-    <hyperlink ref="F156" r:id="rId55" xr:uid="{44BD2531-CDA8-F846-AD24-E2918F203277}"/>
-    <hyperlink ref="F157" r:id="rId56" xr:uid="{27F84449-7FAE-2549-97FD-33B7C531AE93}"/>
-    <hyperlink ref="F158" r:id="rId57" xr:uid="{7866B05B-87CA-094D-B73F-0A39A87FECAC}"/>
-    <hyperlink ref="F162" r:id="rId58" xr:uid="{FC0E72F2-F249-0240-B20D-8C5D0CA7C643}"/>
-    <hyperlink ref="F163" r:id="rId59" xr:uid="{0B9FA73B-9B8D-1643-8DEF-416E2B692694}"/>
-    <hyperlink ref="F165" r:id="rId60" xr:uid="{E45AB9BA-6376-DE4C-A3FA-32BA6546F516}"/>
-    <hyperlink ref="G165" r:id="rId61" xr:uid="{64FC7EE6-2E66-3748-976A-BE443F559B9C}"/>
-    <hyperlink ref="H165" r:id="rId62" xr:uid="{321D0DB5-E98D-CF41-A801-E8B7BFF09756}"/>
-    <hyperlink ref="I165" r:id="rId63" xr:uid="{FBA7510A-B20B-1F4E-B5B5-196E1A54C85F}"/>
-    <hyperlink ref="G166" r:id="rId64" xr:uid="{A6CF9215-BFC1-5043-A4EA-EF18123960B9}"/>
-    <hyperlink ref="F181" r:id="rId65" xr:uid="{17CCB66F-91D5-5E42-8770-FEA1371E346A}"/>
-    <hyperlink ref="F194" r:id="rId66" xr:uid="{1861960A-55A4-0249-B9DC-774FEFF441E2}"/>
-    <hyperlink ref="F197" r:id="rId67" xr:uid="{7B579B5A-985A-7D4D-BBC4-1401A261A7BC}"/>
-    <hyperlink ref="G197" r:id="rId68" xr:uid="{743AEE0D-D8B7-9146-A9A6-32FB9591B58D}"/>
-    <hyperlink ref="H197" r:id="rId69" xr:uid="{579AFDDA-539F-B541-B791-E62167568FDC}"/>
-    <hyperlink ref="I197" r:id="rId70" xr:uid="{2711D5EB-3959-ED49-BBAE-F4FC4BAFBC57}"/>
-    <hyperlink ref="F204" r:id="rId71" xr:uid="{09E204B8-2078-204B-9825-CBD106A65014}"/>
-    <hyperlink ref="G204" r:id="rId72" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view" xr:uid="{BB66E76C-2D49-F845-995B-32E33B962EBA}"/>
-    <hyperlink ref="F223" r:id="rId73" xr:uid="{99EF46DF-D91D-874B-9D6E-8FCBE58F05C7}"/>
-    <hyperlink ref="F224" r:id="rId74" xr:uid="{980A4C4E-9C30-7146-9332-598508B6B67F}"/>
-    <hyperlink ref="F225" r:id="rId75" xr:uid="{1D2CA386-3A8B-3247-938F-440847E13D23}"/>
-    <hyperlink ref="F226" r:id="rId76" xr:uid="{15A4F16A-31C9-1948-A6EE-B321367E4D03}"/>
-    <hyperlink ref="F227" r:id="rId77" xr:uid="{2D745C0F-6406-C948-9BDB-1EF51C0CF6A7}"/>
-    <hyperlink ref="F232" r:id="rId78" xr:uid="{E638AB9A-C220-984B-B7C5-1F942C99283B}"/>
-    <hyperlink ref="F235" r:id="rId79" xr:uid="{DDFC1201-2B33-9346-B27C-EFA753D505D9}"/>
-    <hyperlink ref="F237" r:id="rId80" xr:uid="{98FAF202-06A9-3543-AD0A-305D677787E0}"/>
-    <hyperlink ref="F238" r:id="rId81" xr:uid="{A584D741-8D46-B349-A945-AB1D2EB0F2E7}"/>
-    <hyperlink ref="F244" r:id="rId82" xr:uid="{49E513AF-3F9C-A943-BE28-188CC71E9067}"/>
+    <hyperlink ref="F38" r:id="rId5" xr:uid="{105DCE1E-6854-7246-82CC-3EFB481EAB4D}"/>
+    <hyperlink ref="F41" r:id="rId6" xr:uid="{3980170F-D1DF-FA43-A8D4-D1538E3F0248}"/>
+    <hyperlink ref="F42" r:id="rId7" xr:uid="{0B398506-EA14-9B4B-9846-856DF287B1BB}"/>
+    <hyperlink ref="F71" r:id="rId8" xr:uid="{FA465637-D96C-B049-94D5-2375320F8BF1}"/>
+    <hyperlink ref="F72" r:id="rId9" xr:uid="{45935F14-C3A2-EE48-B7C3-F6BE5EA27761}"/>
+    <hyperlink ref="F79" r:id="rId10" xr:uid="{B9F4B4B2-DD08-5D46-A5FD-F3D2C58B8D1B}"/>
+    <hyperlink ref="F81" r:id="rId11" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{6D40418B-C8FB-5C40-BCC1-54177EE04362}"/>
+    <hyperlink ref="F83" r:id="rId12" xr:uid="{59708C19-515B-C64A-9CC2-C7737CF9101D}"/>
+    <hyperlink ref="F84" r:id="rId13" xr:uid="{C0E661FF-2471-C444-AFA1-E67B91403C67}"/>
+    <hyperlink ref="F85" r:id="rId14" xr:uid="{5F782FC3-7ADE-F949-87F7-C500516CC61C}"/>
+    <hyperlink ref="F88" r:id="rId15" xr:uid="{9220AFC0-F027-8E47-8C5D-81035610A2D8}"/>
+    <hyperlink ref="F89" r:id="rId16" xr:uid="{6A8F6FC6-D4F9-3D40-B805-43F28743296D}"/>
+    <hyperlink ref="F90" r:id="rId17" xr:uid="{A0E7FE6C-9675-EA4D-B484-E708DFBABF93}"/>
+    <hyperlink ref="F91" r:id="rId18" xr:uid="{4855D83A-F4D3-D24E-B84F-EC0FF461E655}"/>
+    <hyperlink ref="F93" r:id="rId19" xr:uid="{4E8DDFA3-FE78-CB45-894D-141462FDA895}"/>
+    <hyperlink ref="F94" r:id="rId20" xr:uid="{689BFAAA-8F0E-0C4E-9C22-B29ED77EAF21}"/>
+    <hyperlink ref="F95" r:id="rId21" xr:uid="{B03E1714-A0E5-6840-87E4-626033744D9D}"/>
+    <hyperlink ref="F96" r:id="rId22" xr:uid="{C001EC90-D588-914D-B4CE-EA8F9524F001}"/>
+    <hyperlink ref="F97" r:id="rId23" xr:uid="{51E81B59-495F-1A4B-8DCD-4F0FB0F5F740}"/>
+    <hyperlink ref="F100" r:id="rId24" xr:uid="{69F44087-21F1-444B-BC92-BEDDCB6BAF31}"/>
+    <hyperlink ref="F101" r:id="rId25" xr:uid="{A1C0FEE7-104A-0146-BC92-B8097B6C3EEF}"/>
+    <hyperlink ref="F102" r:id="rId26" xr:uid="{6FE89437-B508-0B4C-AAD7-E2D46D4CD3D9}"/>
+    <hyperlink ref="F103" r:id="rId27" xr:uid="{189A0DB8-012A-384E-98A2-04DE2084D5D3}"/>
+    <hyperlink ref="F104" r:id="rId28" xr:uid="{0635A1BB-B6B3-CB4E-A7A2-351FCE023FE7}"/>
+    <hyperlink ref="F105" r:id="rId29" xr:uid="{A0B6605F-B37F-434A-8AEA-F0CB46055E22}"/>
+    <hyperlink ref="F114" r:id="rId30" xr:uid="{2EF8DF20-0EF7-4840-AC38-29C64AF5C186}"/>
+    <hyperlink ref="F117" r:id="rId31" xr:uid="{A0262EA2-DC6E-884F-80C7-303FD637A859}"/>
+    <hyperlink ref="F118" r:id="rId32" xr:uid="{049853C1-729D-9C4B-949D-FEBAE26B26D5}"/>
+    <hyperlink ref="F119" r:id="rId33" xr:uid="{59BE7560-AEC1-B64A-8B50-03D6A552F07B}"/>
+    <hyperlink ref="F120" r:id="rId34" xr:uid="{C0F51B2A-45E7-6D41-8232-DA7205EB12FB}"/>
+    <hyperlink ref="F121" r:id="rId35" xr:uid="{BF651D05-F02D-E948-B8A9-22260259738B}"/>
+    <hyperlink ref="F122" r:id="rId36" xr:uid="{DB9E6789-F281-994D-9D56-47AA19BB7556}"/>
+    <hyperlink ref="F123" r:id="rId37" xr:uid="{96A190E9-3569-5144-80C1-CEA7D46BEFDB}"/>
+    <hyperlink ref="F124" r:id="rId38" xr:uid="{F764D9D3-F1DB-5749-B1B9-5315EE113BA4}"/>
+    <hyperlink ref="F125" r:id="rId39" xr:uid="{4694032A-E86D-6145-B19F-5FE9D178BB31}"/>
+    <hyperlink ref="F131" r:id="rId40" xr:uid="{59C34E12-49FD-B942-941E-33BE339D3439}"/>
+    <hyperlink ref="F138" r:id="rId41" xr:uid="{FD8D5E73-41AD-8046-955C-15233A75A9DC}"/>
+    <hyperlink ref="F139" r:id="rId42" xr:uid="{3385E6D0-CBA5-A042-99FF-FBFBE2F24306}"/>
+    <hyperlink ref="F143" r:id="rId43" xr:uid="{63F018E8-0392-E24B-B1A6-89ED2C52F00B}"/>
+    <hyperlink ref="F144" r:id="rId44" xr:uid="{08A2D2CE-A6C4-FC45-8AE2-17B323D018A6}"/>
+    <hyperlink ref="F145" r:id="rId45" xr:uid="{17BB58AA-7748-F247-A3AA-ECA5F25C4258}"/>
+    <hyperlink ref="G146" r:id="rId46" xr:uid="{628E2625-F1D2-DC45-BB00-92D5029F1D08}"/>
+    <hyperlink ref="F147" r:id="rId47" xr:uid="{6CFE1148-9296-3643-90DE-DFAEB57BC570}"/>
+    <hyperlink ref="F148" r:id="rId48" xr:uid="{D54D40F4-8961-3348-BF74-74736CCB022E}"/>
+    <hyperlink ref="F149" r:id="rId49" xr:uid="{6848736E-2B5C-9E4D-9EAF-AD5565B47669}"/>
+    <hyperlink ref="F150" r:id="rId50" xr:uid="{D84EB54A-6097-D648-92A5-5F3BAFF86CEA}"/>
+    <hyperlink ref="F151" r:id="rId51" xr:uid="{FD4E266A-815E-BC4A-861C-189DB85BA33A}"/>
+    <hyperlink ref="F152" r:id="rId52" xr:uid="{A2A0EA72-886A-9748-BE4C-C9C26D9DAD7C}"/>
+    <hyperlink ref="F153" r:id="rId53" xr:uid="{BE24F46F-AFE5-A14D-8ECE-2632A5ADE785}"/>
+    <hyperlink ref="F154" r:id="rId54" xr:uid="{854A2A4C-C908-FB43-85DD-352E51E1CAAD}"/>
+    <hyperlink ref="F155" r:id="rId55" xr:uid="{44BD2531-CDA8-F846-AD24-E2918F203277}"/>
+    <hyperlink ref="F156" r:id="rId56" xr:uid="{27F84449-7FAE-2549-97FD-33B7C531AE93}"/>
+    <hyperlink ref="F157" r:id="rId57" xr:uid="{7866B05B-87CA-094D-B73F-0A39A87FECAC}"/>
+    <hyperlink ref="F161" r:id="rId58" xr:uid="{FC0E72F2-F249-0240-B20D-8C5D0CA7C643}"/>
+    <hyperlink ref="F162" r:id="rId59" xr:uid="{0B9FA73B-9B8D-1643-8DEF-416E2B692694}"/>
+    <hyperlink ref="F164" r:id="rId60" xr:uid="{E45AB9BA-6376-DE4C-A3FA-32BA6546F516}"/>
+    <hyperlink ref="G164" r:id="rId61" xr:uid="{64FC7EE6-2E66-3748-976A-BE443F559B9C}"/>
+    <hyperlink ref="H164" r:id="rId62" xr:uid="{321D0DB5-E98D-CF41-A801-E8B7BFF09756}"/>
+    <hyperlink ref="I164" r:id="rId63" xr:uid="{FBA7510A-B20B-1F4E-B5B5-196E1A54C85F}"/>
+    <hyperlink ref="G165" r:id="rId64" xr:uid="{A6CF9215-BFC1-5043-A4EA-EF18123960B9}"/>
+    <hyperlink ref="F180" r:id="rId65" xr:uid="{17CCB66F-91D5-5E42-8770-FEA1371E346A}"/>
+    <hyperlink ref="F193" r:id="rId66" xr:uid="{1861960A-55A4-0249-B9DC-774FEFF441E2}"/>
+    <hyperlink ref="F196" r:id="rId67" xr:uid="{7B579B5A-985A-7D4D-BBC4-1401A261A7BC}"/>
+    <hyperlink ref="G196" r:id="rId68" xr:uid="{743AEE0D-D8B7-9146-A9A6-32FB9591B58D}"/>
+    <hyperlink ref="H196" r:id="rId69" xr:uid="{579AFDDA-539F-B541-B791-E62167568FDC}"/>
+    <hyperlink ref="I196" r:id="rId70" xr:uid="{2711D5EB-3959-ED49-BBAE-F4FC4BAFBC57}"/>
+    <hyperlink ref="F203" r:id="rId71" xr:uid="{09E204B8-2078-204B-9825-CBD106A65014}"/>
+    <hyperlink ref="G203" r:id="rId72" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view" xr:uid="{BB66E76C-2D49-F845-995B-32E33B962EBA}"/>
+    <hyperlink ref="F222" r:id="rId73" xr:uid="{99EF46DF-D91D-874B-9D6E-8FCBE58F05C7}"/>
+    <hyperlink ref="F223" r:id="rId74" xr:uid="{980A4C4E-9C30-7146-9332-598508B6B67F}"/>
+    <hyperlink ref="F224" r:id="rId75" xr:uid="{1D2CA386-3A8B-3247-938F-440847E13D23}"/>
+    <hyperlink ref="F225" r:id="rId76" xr:uid="{15A4F16A-31C9-1948-A6EE-B321367E4D03}"/>
+    <hyperlink ref="F226" r:id="rId77" xr:uid="{2D745C0F-6406-C948-9BDB-1EF51C0CF6A7}"/>
+    <hyperlink ref="F231" r:id="rId78" xr:uid="{E638AB9A-C220-984B-B7C5-1F942C99283B}"/>
+    <hyperlink ref="F234" r:id="rId79" xr:uid="{DDFC1201-2B33-9346-B27C-EFA753D505D9}"/>
+    <hyperlink ref="F236" r:id="rId80" xr:uid="{98FAF202-06A9-3543-AD0A-305D677787E0}"/>
+    <hyperlink ref="F237" r:id="rId81" xr:uid="{A584D741-8D46-B349-A945-AB1D2EB0F2E7}"/>
+    <hyperlink ref="F243" r:id="rId82" xr:uid="{49E513AF-3F9C-A943-BE28-188CC71E9067}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B884D47-DDE6-ED4F-B7B6-612342DB9BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E1CB4A-156F-E14A-B79A-3576F01411BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36940" yWindow="-540" windowWidth="33380" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
+    <workbookView xWindow="-33000" yWindow="500" windowWidth="33380" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
   <sheets>
     <sheet name="xlsx" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3066" uniqueCount="1087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3056" uniqueCount="1090">
   <si>
     <t>Household Name</t>
   </si>
@@ -3299,6 +3299,15 @@
   </si>
   <si>
     <t xml:space="preserve">E9 </t>
+  </si>
+  <si>
+    <t>1/2 Sold</t>
+  </si>
+  <si>
+    <t>Possible hold for rob singh</t>
+  </si>
+  <si>
+    <t>Lyn Hall &amp; Fiona Mackin-Jha</t>
   </si>
 </sst>
 </file>
@@ -3375,18 +3384,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3402,7 +3405,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3410,8 +3413,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -3749,13 +3750,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7894B4-148E-174D-AE8B-E6DE441B89B0}">
-  <dimension ref="A1:I247"/>
+  <dimension ref="A1:I251"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="23.5" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
@@ -4797,20 +4793,20 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -4818,20 +4814,20 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -4839,20 +4835,22 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E51" s="2"/>
+      <c r="E51" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="F51" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
@@ -4860,22 +4858,20 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>205</v>
-      </c>
+      <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
@@ -4883,20 +4879,20 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -4904,20 +4900,20 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
@@ -4925,20 +4921,20 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>216</v>
+        <v>674</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>217</v>
+        <v>712</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
@@ -4946,20 +4942,20 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>674</v>
+        <v>224</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>712</v>
+        <v>225</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
@@ -4967,20 +4963,20 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>225</v>
+        <v>1033</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
@@ -4988,20 +4984,20 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1033</v>
+        <v>233</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
@@ -5009,59 +5005,41 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="E59" s="2"/>
-      <c r="F59" s="2" t="s">
-        <v>234</v>
+      <c r="F59" s="3" t="s">
+        <v>657</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A60" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>155</v>
-      </c>
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
       <c r="E60" s="2"/>
-      <c r="F60" s="3" t="s">
-        <v>657</v>
-      </c>
+      <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A61" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>155</v>
-      </c>
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
@@ -5070,79 +5048,81 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
+      <c r="F62" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E63" s="2"/>
-      <c r="F63" s="2" t="s">
-        <v>247</v>
-      </c>
+      <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
+      <c r="F64" s="3" t="s">
+        <v>658</v>
+      </c>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="E65" s="2"/>
-      <c r="F65" s="3" t="s">
-        <v>658</v>
+      <c r="F65" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
@@ -5153,17 +5133,17 @@
         <v>257</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
@@ -5171,20 +5151,20 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
@@ -5192,20 +5172,20 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
@@ -5213,20 +5193,20 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
@@ -5234,20 +5214,20 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E70" s="2"/>
-      <c r="F70" s="2" t="s">
-        <v>275</v>
+      <c r="F70" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
@@ -5258,17 +5238,17 @@
         <v>276</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="1" t="s">
-        <v>279</v>
+        <v>983</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
@@ -5276,20 +5256,20 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E72" s="2"/>
-      <c r="F72" s="1" t="s">
-        <v>983</v>
+      <c r="F72" s="2" t="s">
+        <v>285</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
@@ -5297,20 +5277,22 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E73" s="2"/>
+      <c r="E73" s="2" t="s">
+        <v>289</v>
+      </c>
       <c r="F73" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
@@ -5318,22 +5300,20 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>289</v>
-      </c>
+      <c r="E74" s="2"/>
       <c r="F74" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
@@ -5341,20 +5321,20 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
@@ -5362,20 +5342,20 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="E76" s="2"/>
-      <c r="F76" s="2" t="s">
-        <v>298</v>
+      <c r="F76" s="3" t="s">
+        <v>660</v>
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -5383,100 +5363,100 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>299</v>
+        <v>164</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="E77" s="2"/>
-      <c r="F77" s="3" t="s">
-        <v>660</v>
-      </c>
+      <c r="F77" s="3"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>164</v>
+        <v>1034</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>167</v>
+        <v>12</v>
       </c>
       <c r="E78" s="2"/>
-      <c r="F78" s="3"/>
+      <c r="F78" s="1" t="s">
+        <v>996</v>
+      </c>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>1034</v>
+        <v>164</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>12</v>
+        <v>167</v>
       </c>
       <c r="E79" s="2"/>
-      <c r="F79" s="1" t="s">
-        <v>996</v>
-      </c>
+      <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>164</v>
+        <v>311</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>167</v>
+        <v>12</v>
       </c>
       <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
+      <c r="F80" s="1" t="s">
+        <v>1035</v>
+      </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E81" s="2"/>
-      <c r="F81" s="1" t="s">
-        <v>1035</v>
+      <c r="F81" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
@@ -5484,20 +5464,20 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E82" s="2"/>
-      <c r="F82" s="3" t="s">
-        <v>314</v>
+      <c r="F82" s="1" t="s">
+        <v>321</v>
       </c>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
@@ -5508,17 +5488,17 @@
         <v>318</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="1" t="s">
-        <v>321</v>
+        <v>984</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -5526,64 +5506,64 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="1" t="s">
-        <v>984</v>
-      </c>
-      <c r="G84" s="2"/>
+        <v>985</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>327</v>
+      </c>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E85" s="2"/>
-      <c r="F85" s="1" t="s">
-        <v>985</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>327</v>
-      </c>
+      <c r="F85" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G85" s="2"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -5591,20 +5571,20 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E87" s="2"/>
-      <c r="F87" s="2" t="s">
-        <v>335</v>
+      <c r="F87" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
@@ -5615,17 +5595,17 @@
         <v>343</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="1" t="s">
-        <v>338</v>
+        <v>986</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -5636,17 +5616,17 @@
         <v>343</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -5654,20 +5634,20 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>343</v>
+        <v>988</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="1" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -5675,20 +5655,20 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E91" s="2"/>
-      <c r="F91" s="1" t="s">
-        <v>989</v>
+      <c r="F91" s="5" t="s">
+        <v>338</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -5696,20 +5676,20 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E92" s="2"/>
-      <c r="F92" s="5" t="s">
-        <v>338</v>
+      <c r="F92" s="1" t="s">
+        <v>992</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -5717,20 +5697,20 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>991</v>
+        <v>350</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="1" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -5738,20 +5718,20 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>351</v>
+        <v>220</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>352</v>
+        <v>221</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="1" t="s">
-        <v>993</v>
+        <v>355</v>
       </c>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -5762,17 +5742,17 @@
         <v>354</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>220</v>
+        <v>356</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>221</v>
+        <v>357</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="1" t="s">
-        <v>355</v>
+        <v>994</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -5783,17 +5763,17 @@
         <v>354</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -5801,20 +5781,20 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E97" s="2"/>
-      <c r="F97" s="1" t="s">
-        <v>995</v>
+      <c r="F97" s="2" t="s">
+        <v>363</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
@@ -5822,20 +5802,20 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>360</v>
+        <v>305</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2" t="s">
-        <v>363</v>
+        <v>308</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
@@ -5843,20 +5823,20 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>305</v>
+        <v>364</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E99" s="2"/>
-      <c r="F99" s="2" t="s">
-        <v>308</v>
+      <c r="F99" s="1" t="s">
+        <v>997</v>
       </c>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
@@ -5867,17 +5847,17 @@
         <v>364</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="1" t="s">
-        <v>997</v>
+        <v>367</v>
       </c>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
@@ -5885,20 +5865,20 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="1" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
@@ -5909,17 +5889,17 @@
         <v>372</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="1" t="s">
-        <v>375</v>
+        <v>998</v>
       </c>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
@@ -5927,20 +5907,20 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="1" t="s">
-        <v>998</v>
+        <v>381</v>
       </c>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -5951,17 +5931,17 @@
         <v>378</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="1" t="s">
-        <v>381</v>
+        <v>999</v>
       </c>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -5969,20 +5949,20 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="E105" s="2"/>
-      <c r="F105" s="1" t="s">
-        <v>999</v>
+      <c r="F105" s="3" t="s">
+        <v>662</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -5990,20 +5970,20 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E106" s="2"/>
-      <c r="F106" s="3" t="s">
-        <v>662</v>
+      <c r="F106" s="5" t="s">
+        <v>390</v>
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -6011,20 +5991,20 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E107" s="2"/>
-      <c r="F107" s="5" t="s">
-        <v>390</v>
+      <c r="F107" s="3" t="s">
+        <v>663</v>
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
@@ -6032,20 +6012,20 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="3" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
@@ -6056,10 +6036,10 @@
         <v>396</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>155</v>
@@ -6074,21 +6054,19 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="E110" s="2"/>
-      <c r="F110" s="3" t="s">
-        <v>664</v>
-      </c>
+      <c r="F110" s="2"/>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
       <c r="I110" s="2"/>
@@ -6098,10 +6076,10 @@
         <v>401</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>12</v>
@@ -6117,10 +6095,10 @@
         <v>401</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>12</v>
@@ -6133,39 +6111,41 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
-        <v>401</v>
+        <v>1036</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E113" s="2"/>
-      <c r="F113" s="2"/>
+      <c r="F113" s="1" t="s">
+        <v>1051</v>
+      </c>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>1036</v>
+        <v>410</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E114" s="2"/>
-      <c r="F114" s="1" t="s">
-        <v>1051</v>
+      <c r="F114" s="2" t="s">
+        <v>413</v>
       </c>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
@@ -6176,17 +6156,17 @@
         <v>410</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
@@ -6194,20 +6174,20 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E116" s="2"/>
-      <c r="F116" s="2" t="s">
-        <v>416</v>
+      <c r="F116" s="1" t="s">
+        <v>675</v>
       </c>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
@@ -6218,10 +6198,10 @@
         <v>417</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>12</v>
@@ -6239,10 +6219,10 @@
         <v>417</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>12</v>
@@ -6257,20 +6237,20 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="1" t="s">
-        <v>675</v>
+        <v>427</v>
       </c>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
@@ -6281,17 +6261,17 @@
         <v>424</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="1" t="s">
-        <v>427</v>
+        <v>1000</v>
       </c>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
@@ -6302,17 +6282,17 @@
         <v>424</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
@@ -6323,17 +6303,17 @@
         <v>424</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
@@ -6344,17 +6324,17 @@
         <v>424</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="1" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
@@ -6362,20 +6342,20 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
-        <v>424</v>
+        <v>1077</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="1" t="s">
-        <v>1003</v>
+        <v>1078</v>
       </c>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
@@ -6383,20 +6363,20 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>1077</v>
+        <v>440</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E125" s="2"/>
-      <c r="F125" s="1" t="s">
-        <v>1078</v>
+      <c r="F125" s="2" t="s">
+        <v>443</v>
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
@@ -6404,20 +6384,20 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
@@ -6428,17 +6408,17 @@
         <v>447</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
@@ -6446,20 +6426,22 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E128" s="2"/>
+      <c r="E128" s="2" t="s">
+        <v>1037</v>
+      </c>
       <c r="F128" s="2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
@@ -6467,22 +6449,22 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F129" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>665</v>
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
@@ -6490,22 +6472,20 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E130" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="F130" s="3" t="s">
-        <v>665</v>
+      <c r="E130" s="2"/>
+      <c r="F130" s="1" t="s">
+        <v>676</v>
       </c>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
@@ -6513,20 +6493,22 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E131" s="2"/>
-      <c r="F131" s="1" t="s">
-        <v>676</v>
+      <c r="E131" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>465</v>
       </c>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
@@ -6534,22 +6516,20 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E132" s="2" t="s">
-        <v>458</v>
-      </c>
+      <c r="E132" s="2"/>
       <c r="F132" s="2" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
@@ -6557,20 +6537,20 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
@@ -6578,20 +6558,22 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E134" s="2"/>
+      <c r="E134" s="2" t="s">
+        <v>1038</v>
+      </c>
       <c r="F134" s="2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
@@ -6599,22 +6581,20 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E135" s="2" t="s">
-        <v>1038</v>
-      </c>
+      <c r="E135" s="2"/>
       <c r="F135" s="2" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
@@ -6622,20 +6602,20 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
@@ -6643,20 +6623,20 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E137" s="2"/>
-      <c r="F137" s="2" t="s">
-        <v>485</v>
+      <c r="F137" s="1" t="s">
+        <v>493</v>
       </c>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
@@ -6664,20 +6644,22 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
-        <v>490</v>
+        <v>1079</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E138" s="2"/>
+      <c r="E138" s="2" t="s">
+        <v>1080</v>
+      </c>
       <c r="F138" s="1" t="s">
-        <v>493</v>
+        <v>666</v>
       </c>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
@@ -6685,22 +6667,20 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
-        <v>1079</v>
+        <v>17</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E139" s="2" t="s">
-        <v>1080</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>666</v>
+      <c r="E139" s="2"/>
+      <c r="F139" s="3" t="s">
+        <v>667</v>
       </c>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
@@ -6711,10 +6691,10 @@
         <v>17</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>12</v>
@@ -6732,10 +6712,10 @@
         <v>17</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>12</v>
@@ -6750,20 +6730,22 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
-        <v>17</v>
+        <v>500</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E142" s="2"/>
-      <c r="F142" s="3" t="s">
-        <v>667</v>
+      <c r="E142" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>503</v>
       </c>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
@@ -6774,10 +6756,10 @@
         <v>500</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>12</v>
@@ -6786,7 +6768,7 @@
         <v>1039</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>503</v>
+        <v>1004</v>
       </c>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
@@ -6797,10 +6779,10 @@
         <v>500</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>12</v>
@@ -6809,7 +6791,7 @@
         <v>1039</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
@@ -6817,66 +6799,64 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
-        <v>500</v>
+        <v>1046</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E145" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>1005</v>
-      </c>
-      <c r="G145" s="2"/>
+      <c r="E145" s="2"/>
+      <c r="F145" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>1052</v>
+      </c>
       <c r="H145" s="2"/>
       <c r="I145" s="2"/>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>1046</v>
+        <v>350</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E146" s="2"/>
-      <c r="F146" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>1052</v>
-      </c>
+      <c r="F146" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G146" s="2"/>
       <c r="H146" s="2"/>
       <c r="I146" s="2"/>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>350</v>
+        <v>516</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="1" t="s">
-        <v>353</v>
+        <v>519</v>
       </c>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
@@ -6887,17 +6867,17 @@
         <v>516</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="1" t="s">
-        <v>519</v>
+        <v>1006</v>
       </c>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
@@ -6908,17 +6888,17 @@
         <v>516</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
@@ -6926,20 +6906,20 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
@@ -6950,17 +6930,17 @@
         <v>524</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
@@ -6971,17 +6951,17 @@
         <v>524</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" s="1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
@@ -6989,20 +6969,20 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
-        <v>524</v>
+        <v>372</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
@@ -7010,20 +6990,20 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
-        <v>372</v>
+        <v>533</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" s="1" t="s">
-        <v>1011</v>
+        <v>538</v>
       </c>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
@@ -7034,17 +7014,17 @@
         <v>533</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" s="1" t="s">
-        <v>538</v>
+        <v>1012</v>
       </c>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
@@ -7055,17 +7035,17 @@
         <v>533</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
@@ -7073,20 +7053,20 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E157" s="2"/>
-      <c r="F157" s="1" t="s">
-        <v>1013</v>
+      <c r="F157" s="2" t="s">
+        <v>544</v>
       </c>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
@@ -7094,20 +7074,20 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" s="2" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
@@ -7115,20 +7095,22 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E159" s="2"/>
+      <c r="E159" s="2" t="s">
+        <v>552</v>
+      </c>
       <c r="F159" s="2" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
@@ -7136,22 +7118,22 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
-        <v>549</v>
+        <v>1014</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="F160" s="2" t="s">
-        <v>553</v>
+        <v>1015</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>1016</v>
       </c>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
@@ -7159,22 +7141,22 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
@@ -7182,22 +7164,20 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
-        <v>1017</v>
+        <v>558</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>556</v>
+        <v>388</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>557</v>
+        <v>389</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E162" s="2" t="s">
-        <v>1018</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>1019</v>
+      <c r="E162" s="2"/>
+      <c r="F162" s="2" t="s">
+        <v>561</v>
       </c>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
@@ -7205,92 +7185,90 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
-        <v>558</v>
+        <v>1020</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>388</v>
+        <v>559</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>389</v>
+        <v>560</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>12</v>
+        <v>980</v>
       </c>
       <c r="E163" s="2"/>
-      <c r="F163" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="G163" s="2"/>
-      <c r="H163" s="2"/>
-      <c r="I163" s="2"/>
+      <c r="F163" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H163" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>1024</v>
+      </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
-        <v>1020</v>
+        <v>562</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>560</v>
+        <v>677</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>980</v>
+        <v>12</v>
       </c>
       <c r="E164" s="2"/>
-      <c r="F164" s="1" t="s">
-        <v>1021</v>
+      <c r="F164" s="3" t="s">
+        <v>668</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>1022</v>
-      </c>
-      <c r="H164" s="1" t="s">
-        <v>1023</v>
-      </c>
-      <c r="I164" s="1" t="s">
-        <v>1024</v>
-      </c>
+        <v>673</v>
+      </c>
+      <c r="H164" s="2"/>
+      <c r="I164" s="2"/>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>673</v>
-      </c>
+        <v>669</v>
+      </c>
+      <c r="G165" s="2"/>
       <c r="H165" s="2"/>
       <c r="I165" s="2"/>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>678</v>
+        <v>568</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>155</v>
+        <v>569</v>
       </c>
       <c r="E166" s="2"/>
-      <c r="F166" s="3" t="s">
-        <v>669</v>
-      </c>
+      <c r="F166" s="2"/>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
       <c r="I166" s="2"/>
@@ -7300,10 +7278,10 @@
         <v>566</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>569</v>
@@ -7319,10 +7297,10 @@
         <v>566</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>569</v>
@@ -7338,10 +7316,10 @@
         <v>566</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>569</v>
@@ -7357,10 +7335,10 @@
         <v>566</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>569</v>
@@ -7376,10 +7354,10 @@
         <v>566</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>569</v>
@@ -7395,10 +7373,10 @@
         <v>566</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>569</v>
@@ -7414,10 +7392,10 @@
         <v>566</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>569</v>
@@ -7433,10 +7411,10 @@
         <v>566</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>569</v>
@@ -7452,10 +7430,10 @@
         <v>566</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>569</v>
@@ -7471,10 +7449,10 @@
         <v>566</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>569</v>
@@ -7490,10 +7468,10 @@
         <v>566</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>569</v>
@@ -7509,10 +7487,10 @@
         <v>566</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>569</v>
@@ -7525,53 +7503,53 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
-        <v>566</v>
+        <v>1082</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>569</v>
+        <v>12</v>
       </c>
       <c r="E179" s="2"/>
-      <c r="F179" s="2"/>
+      <c r="F179" s="1" t="s">
+        <v>1083</v>
+      </c>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
       <c r="I179" s="2"/>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
-        <v>1082</v>
+        <v>1087</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>12</v>
+        <v>569</v>
       </c>
       <c r="E180" s="2"/>
-      <c r="F180" s="1" t="s">
-        <v>1083</v>
-      </c>
+      <c r="F180" s="2"/>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
       <c r="I180" s="2"/>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A181" s="8">
-        <v>46024</v>
+      <c r="A181" s="2" t="s">
+        <v>566</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>597</v>
+        <v>680</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>569</v>
@@ -7587,10 +7565,10 @@
         <v>566</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>569</v>
@@ -7606,10 +7584,10 @@
         <v>566</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>569</v>
@@ -7625,10 +7603,10 @@
         <v>566</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>569</v>
@@ -7644,10 +7622,10 @@
         <v>566</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>569</v>
@@ -7663,10 +7641,10 @@
         <v>566</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>569</v>
@@ -7682,10 +7660,10 @@
         <v>566</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>569</v>
@@ -7701,10 +7679,10 @@
         <v>566</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>569</v>
@@ -7720,10 +7698,10 @@
         <v>566</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>569</v>
@@ -7739,10 +7717,10 @@
         <v>566</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>569</v>
@@ -7758,10 +7736,10 @@
         <v>566</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>569</v>
@@ -7774,128 +7752,128 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
-        <v>566</v>
+        <v>1059</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>608</v>
+        <v>757</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>690</v>
+        <v>758</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="E192" s="2"/>
-      <c r="F192" s="2"/>
+        <v>1060</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>1062</v>
+      </c>
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
       <c r="I192" s="2"/>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" s="2" t="s">
-        <v>1059</v>
+        <v>164</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>757</v>
+        <v>613</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>758</v>
+        <v>692</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>1060</v>
-      </c>
-      <c r="E193" s="2" t="s">
-        <v>1061</v>
-      </c>
-      <c r="F193" s="1" t="s">
-        <v>1062</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="E193" s="2"/>
+      <c r="F193" s="3"/>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
       <c r="I193" s="2"/>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
-        <v>164</v>
+        <v>614</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="E194" s="2"/>
-      <c r="F194" s="3"/>
+      <c r="F194" s="3" t="s">
+        <v>671</v>
+      </c>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
       <c r="I194" s="2"/>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
-        <v>614</v>
+        <v>1020</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>155</v>
+        <v>980</v>
       </c>
       <c r="E195" s="2"/>
-      <c r="F195" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="G195" s="2"/>
-      <c r="H195" s="2"/>
-      <c r="I195" s="2"/>
+      <c r="F195" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H195" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="I195" s="1" t="s">
+        <v>1028</v>
+      </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
-        <v>1020</v>
+        <v>164</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>980</v>
+        <v>167</v>
       </c>
       <c r="E196" s="2"/>
-      <c r="F196" s="1" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G196" s="1" t="s">
-        <v>1026</v>
-      </c>
-      <c r="H196" s="1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="I196" s="1" t="s">
-        <v>1028</v>
-      </c>
+      <c r="F196" s="2"/>
+      <c r="G196" s="2"/>
+      <c r="H196" s="2"/>
+      <c r="I196" s="2"/>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
         <v>164</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E197" s="2"/>
-      <c r="F197" s="2"/>
+      <c r="F197" s="3"/>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
       <c r="I197" s="2"/>
@@ -7905,16 +7883,16 @@
         <v>164</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E198" s="2"/>
-      <c r="F198" s="3"/>
+      <c r="F198" s="2"/>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
       <c r="I198" s="2"/>
@@ -7924,10 +7902,10 @@
         <v>164</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>697</v>
+        <v>622</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>167</v>
@@ -7940,18 +7918,18 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
-        <v>164</v>
+        <v>1059</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>698</v>
+        <v>624</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E200" s="2"/>
+      <c r="E200" s="7"/>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
@@ -7959,37 +7937,43 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
-        <v>164</v>
+        <v>1063</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E201" s="2"/>
-      <c r="F201" s="2"/>
-      <c r="G201" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G201" s="1" t="s">
+        <v>1065</v>
+      </c>
       <c r="H201" s="2"/>
       <c r="I201" s="2"/>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
-        <v>1059</v>
+        <v>164</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E202" s="9"/>
+      <c r="E202" s="2"/>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
@@ -7997,26 +7981,20 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
-        <v>1063</v>
+        <v>164</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E203" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="F203" s="1" t="s">
-        <v>1066</v>
-      </c>
-      <c r="G203" s="1" t="s">
-        <v>1065</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="E203" s="2"/>
+      <c r="F203" s="2"/>
+      <c r="G203" s="2"/>
       <c r="H203" s="2"/>
       <c r="I203" s="2"/>
     </row>
@@ -8025,10 +8003,10 @@
         <v>164</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>167</v>
@@ -8044,10 +8022,10 @@
         <v>164</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>167</v>
@@ -8063,10 +8041,10 @@
         <v>164</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>167</v>
@@ -8079,16 +8057,16 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B207" s="7" t="s">
-        <v>633</v>
+        <v>639</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>640</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>167</v>
+        <v>639</v>
       </c>
       <c r="E207" s="2"/>
       <c r="F207" s="2"/>
@@ -8098,16 +8076,16 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
-        <v>164</v>
+        <v>639</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>167</v>
+        <v>639</v>
       </c>
       <c r="E208" s="2"/>
       <c r="F208" s="2"/>
@@ -8117,16 +8095,16 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209" s="2" t="s">
-        <v>164</v>
+        <v>639</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>167</v>
+        <v>639</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" s="2"/>
@@ -8139,10 +8117,10 @@
         <v>639</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>639</v>
@@ -8155,16 +8133,16 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
-        <v>639</v>
+        <v>566</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>639</v>
+        <v>569</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" s="2"/>
@@ -8174,16 +8152,16 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
-        <v>639</v>
+        <v>566</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>639</v>
+        <v>569</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" s="2"/>
@@ -8193,16 +8171,16 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A213" s="2" t="s">
-        <v>639</v>
+        <v>566</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>639</v>
+        <v>569</v>
       </c>
       <c r="E213" s="2"/>
       <c r="F213" s="2"/>
@@ -8215,10 +8193,10 @@
         <v>566</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>648</v>
+        <v>699</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>649</v>
+        <v>713</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>569</v>
@@ -8234,10 +8212,10 @@
         <v>566</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>650</v>
+        <v>701</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>651</v>
+        <v>715</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>569</v>
@@ -8253,10 +8231,10 @@
         <v>566</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>652</v>
+        <v>702</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>653</v>
+        <v>867</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>569</v>
@@ -8269,203 +8247,209 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
-        <v>566</v>
+        <v>1029</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>713</v>
+        <v>930</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>569</v>
+        <v>980</v>
       </c>
       <c r="E217" s="2"/>
-      <c r="F217" s="2"/>
+      <c r="F217" s="1" t="s">
+        <v>1030</v>
+      </c>
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
       <c r="I217" s="2"/>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="B218" s="7" t="s">
-        <v>700</v>
+        <v>979</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>705</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>714</v>
+        <v>936</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="E218" s="2"/>
-      <c r="F218" s="2"/>
+        <v>980</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>982</v>
+      </c>
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
       <c r="I218" s="2"/>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
-        <v>566</v>
+        <v>1044</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>715</v>
+        <v>939</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="E219" s="2"/>
-      <c r="F219" s="2"/>
+        <v>980</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>1053</v>
+      </c>
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
       <c r="I219" s="2"/>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
-        <v>566</v>
+        <v>1040</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>867</v>
+        <v>732</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>569</v>
+        <v>980</v>
       </c>
       <c r="E220" s="2"/>
-      <c r="F220" s="2"/>
+      <c r="F220" s="1" t="s">
+        <v>1043</v>
+      </c>
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
       <c r="I220" s="2"/>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="B221" s="7" t="s">
-        <v>703</v>
+        <v>1068</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>710</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>569</v>
       </c>
       <c r="E221" s="2"/>
-      <c r="F221" s="2"/>
+      <c r="F221" s="1" t="s">
+        <v>1069</v>
+      </c>
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
       <c r="I221" s="2"/>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
-        <v>1029</v>
+        <v>566</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>930</v>
+        <v>866</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>980</v>
+        <v>569</v>
       </c>
       <c r="E222" s="2"/>
-      <c r="F222" s="1" t="s">
-        <v>1030</v>
-      </c>
+      <c r="F222" s="2"/>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
       <c r="I222" s="2"/>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" s="2" t="s">
-        <v>979</v>
+        <v>566</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>936</v>
+        <v>873</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>980</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>981</v>
-      </c>
-      <c r="F223" s="1" t="s">
-        <v>982</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="E223" s="2"/>
+      <c r="F223" s="2"/>
       <c r="G223" s="2"/>
       <c r="H223" s="2"/>
       <c r="I223" s="2"/>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
-        <v>1044</v>
+        <v>566</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>939</v>
+        <v>714</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>980</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="F224" s="1" t="s">
-        <v>1053</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="E224" s="2"/>
+      <c r="F224" s="2"/>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
       <c r="I224" s="2"/>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" s="2" t="s">
-        <v>1040</v>
+        <v>1084</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>707</v>
+        <v>864</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>732</v>
+        <v>865</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>980</v>
-      </c>
-      <c r="E225" s="2"/>
-      <c r="F225" s="1" t="s">
-        <v>1043</v>
-      </c>
+        <v>1071</v>
+      </c>
+      <c r="E225" s="8" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F225" s="2"/>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
       <c r="I225" s="2"/>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
-        <v>1068</v>
+        <v>1041</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>710</v>
+        <v>833</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>868</v>
+        <v>834</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="E226" s="2"/>
+        <v>980</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>1042</v>
+      </c>
       <c r="F226" s="1" t="s">
-        <v>1069</v>
+        <v>390</v>
       </c>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
@@ -8475,11 +8459,11 @@
       <c r="A227" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="B227" s="7" t="s">
-        <v>703</v>
+      <c r="B227" s="2" t="s">
+        <v>878</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>866</v>
+        <v>879</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>569</v>
@@ -8495,10 +8479,10 @@
         <v>566</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>711</v>
+        <v>922</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>873</v>
+        <v>923</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>569</v>
@@ -8511,62 +8495,62 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="B229" s="7" t="s">
-        <v>700</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>714</v>
+        <v>1070</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C229" s="4" t="s">
+        <v>510</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>569</v>
+        <v>1071</v>
       </c>
       <c r="E229" s="2"/>
-      <c r="F229" s="2"/>
+      <c r="F229" s="1" t="s">
+        <v>1072</v>
+      </c>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
       <c r="I229" s="2"/>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" s="2" t="s">
-        <v>1084</v>
+        <v>609</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>864</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>865</v>
+        <v>759</v>
+      </c>
+      <c r="C230" s="6" t="s">
+        <v>760</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E230" s="10" t="s">
-        <v>1085</v>
-      </c>
-      <c r="F230" s="2"/>
+        <v>980</v>
+      </c>
+      <c r="E230" s="2"/>
+      <c r="F230" s="2" t="s">
+        <v>611</v>
+      </c>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
       <c r="I230" s="2"/>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" s="2" t="s">
-        <v>1041</v>
+        <v>1067</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>833</v>
+        <v>255</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>834</v>
+        <v>256</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>980</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>1042</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="E231" s="2"/>
       <c r="F231" s="1" t="s">
-        <v>390</v>
+        <v>659</v>
       </c>
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
@@ -8574,37 +8558,41 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
-        <v>566</v>
+        <v>508</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>878</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>879</v>
+        <v>633</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>634</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>569</v>
+        <v>155</v>
       </c>
       <c r="E232" s="2"/>
-      <c r="F232" s="2"/>
+      <c r="F232" s="1" t="s">
+        <v>1054</v>
+      </c>
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
       <c r="I232" s="2"/>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" s="2" t="s">
-        <v>566</v>
+        <v>164</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>922</v>
+        <v>937</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>923</v>
+        <v>938</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="E233" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>1073</v>
+      </c>
       <c r="F233" s="2"/>
       <c r="G233" s="2"/>
       <c r="H233" s="2"/>
@@ -8612,123 +8600,117 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" s="2" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="C234" s="4" t="s">
-        <v>510</v>
+        <v>966</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>967</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>1071</v>
       </c>
       <c r="E234" s="2"/>
-      <c r="F234" s="1" t="s">
-        <v>1072</v>
-      </c>
+      <c r="F234" s="2"/>
       <c r="G234" s="2"/>
       <c r="H234" s="2"/>
       <c r="I234" s="2"/>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="2" t="s">
-        <v>609</v>
+        <v>566</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="C235" s="6" t="s">
-        <v>760</v>
+        <v>948</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>949</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>980</v>
+        <v>569</v>
       </c>
       <c r="E235" s="2"/>
-      <c r="F235" s="2" t="s">
-        <v>611</v>
-      </c>
+      <c r="F235" s="2"/>
       <c r="G235" s="2"/>
       <c r="H235" s="2"/>
       <c r="I235" s="2"/>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
-        <v>1067</v>
+        <v>566</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>255</v>
+        <v>890</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>256</v>
+        <v>891</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>155</v>
+        <v>569</v>
       </c>
       <c r="E236" s="2"/>
-      <c r="F236" s="1" t="s">
-        <v>659</v>
-      </c>
+      <c r="F236" s="2"/>
       <c r="G236" s="2"/>
       <c r="H236" s="2"/>
       <c r="I236" s="2"/>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="B237" s="7" t="s">
-        <v>633</v>
-      </c>
-      <c r="C237" s="4" t="s">
-        <v>634</v>
+        <v>566</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>870</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>155</v>
+        <v>569</v>
       </c>
       <c r="E237" s="2"/>
-      <c r="F237" s="1" t="s">
-        <v>1054</v>
-      </c>
+      <c r="F237" s="2"/>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
       <c r="I237" s="2"/>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
-        <v>164</v>
+        <v>436</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>937</v>
+        <v>956</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>938</v>
+        <v>957</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E238" s="2" t="s">
-        <v>1073</v>
-      </c>
-      <c r="F238" s="2"/>
+        <v>1071</v>
+      </c>
+      <c r="E238" s="2"/>
+      <c r="F238" s="1" t="s">
+        <v>439</v>
+      </c>
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
       <c r="I238" s="2"/>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A239" s="2" t="s">
-        <v>1074</v>
+        <v>164</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E239" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>1081</v>
+      </c>
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
       <c r="H239" s="2"/>
@@ -8736,18 +8718,20 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
-        <v>566</v>
+        <v>164</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>948</v>
+        <v>968</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>949</v>
+        <v>969</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="E240" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>1081</v>
+      </c>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
       <c r="H240" s="2"/>
@@ -8755,16 +8739,16 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A241" s="2" t="s">
-        <v>566</v>
+        <v>164</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>890</v>
+        <v>928</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>891</v>
+        <v>929</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>569</v>
+        <v>167</v>
       </c>
       <c r="E241" s="2"/>
       <c r="F241" s="2"/>
@@ -8774,16 +8758,16 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" s="2" t="s">
-        <v>566</v>
+        <v>164</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>869</v>
+        <v>1086</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>870</v>
+        <v>925</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>569</v>
+        <v>167</v>
       </c>
       <c r="E242" s="2"/>
       <c r="F242" s="2"/>
@@ -8793,41 +8777,39 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" s="2" t="s">
-        <v>436</v>
+        <v>1059</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>956</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>957</v>
+        <v>191</v>
+      </c>
+      <c r="C243" t="s">
+        <v>192</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E243" s="2"/>
-      <c r="F243" s="1" t="s">
-        <v>439</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F243" s="2"/>
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
       <c r="I243" s="2"/>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" s="2" t="s">
-        <v>164</v>
+        <v>238</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>964</v>
-      </c>
-      <c r="C244" s="2" t="s">
-        <v>965</v>
+        <v>739</v>
+      </c>
+      <c r="C244" t="s">
+        <v>740</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E244" s="2" t="s">
-        <v>1081</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="E244" s="2"/>
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
       <c r="H244" s="2"/>
@@ -8835,20 +8817,18 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" s="2" t="s">
-        <v>164</v>
+        <v>241</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>968</v>
+        <v>620</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>969</v>
+        <v>698</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E245" s="2" t="s">
-        <v>1081</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="E245" s="2"/>
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
       <c r="H245" s="2"/>
@@ -8856,127 +8836,165 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A246" s="2" t="s">
-        <v>164</v>
+        <v>1089</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>928</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>929</v>
+        <v>723</v>
+      </c>
+      <c r="C246" t="s">
+        <v>724</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>167</v>
+        <v>12</v>
       </c>
       <c r="E246" s="2"/>
-      <c r="F246" s="2"/>
+      <c r="F246" s="2" t="s">
+        <v>193</v>
+      </c>
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
       <c r="I246" s="2"/>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A247" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>925</v>
-      </c>
-      <c r="D247" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="A247" s="2"/>
+      <c r="B247" s="2"/>
+      <c r="C247" s="2"/>
+      <c r="D247" s="2"/>
       <c r="E247" s="2"/>
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
       <c r="H247" s="2"/>
       <c r="I247" s="2"/>
     </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A248" s="2"/>
+      <c r="B248" s="2"/>
+      <c r="C248" s="2"/>
+      <c r="D248" s="2"/>
+      <c r="E248" s="2"/>
+      <c r="F248" s="2"/>
+      <c r="G248" s="2"/>
+      <c r="H248" s="2"/>
+      <c r="I248" s="2"/>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A249" s="2"/>
+      <c r="B249" s="2"/>
+      <c r="C249" s="2"/>
+      <c r="D249" s="2"/>
+      <c r="E249" s="2"/>
+      <c r="F249" s="2"/>
+      <c r="G249" s="2"/>
+      <c r="H249" s="2"/>
+      <c r="I249" s="2"/>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A250" s="2"/>
+      <c r="B250" s="2"/>
+      <c r="C250" s="2"/>
+      <c r="D250" s="2"/>
+      <c r="E250" s="2"/>
+      <c r="F250" s="2"/>
+      <c r="G250" s="2"/>
+      <c r="H250" s="2"/>
+      <c r="I250" s="2"/>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A251" s="2"/>
+      <c r="B251" s="2"/>
+      <c r="C251" s="2"/>
+      <c r="D251" s="2"/>
+      <c r="E251" s="2"/>
+      <c r="F251" s="2"/>
+      <c r="G251" s="2"/>
+      <c r="H251" s="2"/>
+      <c r="I251" s="2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F5" r:id="rId1" xr:uid="{C9E8B679-DCEF-3E42-ABCB-BFEBF50167F9}"/>
-    <hyperlink ref="G8" r:id="rId2" xr:uid="{6B85D203-378C-EF4D-91B9-119DC026F3E8}"/>
-    <hyperlink ref="H15" r:id="rId3" xr:uid="{BE271FBA-E7D3-1B4E-997A-B46C6FFF8A28}"/>
-    <hyperlink ref="F16" r:id="rId4" xr:uid="{5EB059E4-1518-A54E-9011-16B3A6B9249F}"/>
-    <hyperlink ref="F38" r:id="rId5" xr:uid="{105DCE1E-6854-7246-82CC-3EFB481EAB4D}"/>
-    <hyperlink ref="F41" r:id="rId6" xr:uid="{3980170F-D1DF-FA43-A8D4-D1538E3F0248}"/>
-    <hyperlink ref="F42" r:id="rId7" xr:uid="{0B398506-EA14-9B4B-9846-856DF287B1BB}"/>
-    <hyperlink ref="F71" r:id="rId8" xr:uid="{FA465637-D96C-B049-94D5-2375320F8BF1}"/>
-    <hyperlink ref="F72" r:id="rId9" xr:uid="{45935F14-C3A2-EE48-B7C3-F6BE5EA27761}"/>
-    <hyperlink ref="F79" r:id="rId10" xr:uid="{B9F4B4B2-DD08-5D46-A5FD-F3D2C58B8D1B}"/>
-    <hyperlink ref="F81" r:id="rId11" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{6D40418B-C8FB-5C40-BCC1-54177EE04362}"/>
-    <hyperlink ref="F83" r:id="rId12" xr:uid="{59708C19-515B-C64A-9CC2-C7737CF9101D}"/>
-    <hyperlink ref="F84" r:id="rId13" xr:uid="{C0E661FF-2471-C444-AFA1-E67B91403C67}"/>
-    <hyperlink ref="F85" r:id="rId14" xr:uid="{5F782FC3-7ADE-F949-87F7-C500516CC61C}"/>
-    <hyperlink ref="F88" r:id="rId15" xr:uid="{9220AFC0-F027-8E47-8C5D-81035610A2D8}"/>
-    <hyperlink ref="F89" r:id="rId16" xr:uid="{6A8F6FC6-D4F9-3D40-B805-43F28743296D}"/>
-    <hyperlink ref="F90" r:id="rId17" xr:uid="{A0E7FE6C-9675-EA4D-B484-E708DFBABF93}"/>
-    <hyperlink ref="F91" r:id="rId18" xr:uid="{4855D83A-F4D3-D24E-B84F-EC0FF461E655}"/>
-    <hyperlink ref="F93" r:id="rId19" xr:uid="{4E8DDFA3-FE78-CB45-894D-141462FDA895}"/>
-    <hyperlink ref="F94" r:id="rId20" xr:uid="{689BFAAA-8F0E-0C4E-9C22-B29ED77EAF21}"/>
-    <hyperlink ref="F95" r:id="rId21" xr:uid="{B03E1714-A0E5-6840-87E4-626033744D9D}"/>
-    <hyperlink ref="F96" r:id="rId22" xr:uid="{C001EC90-D588-914D-B4CE-EA8F9524F001}"/>
-    <hyperlink ref="F97" r:id="rId23" xr:uid="{51E81B59-495F-1A4B-8DCD-4F0FB0F5F740}"/>
-    <hyperlink ref="F100" r:id="rId24" xr:uid="{69F44087-21F1-444B-BC92-BEDDCB6BAF31}"/>
-    <hyperlink ref="F101" r:id="rId25" xr:uid="{A1C0FEE7-104A-0146-BC92-B8097B6C3EEF}"/>
-    <hyperlink ref="F102" r:id="rId26" xr:uid="{6FE89437-B508-0B4C-AAD7-E2D46D4CD3D9}"/>
-    <hyperlink ref="F103" r:id="rId27" xr:uid="{189A0DB8-012A-384E-98A2-04DE2084D5D3}"/>
-    <hyperlink ref="F104" r:id="rId28" xr:uid="{0635A1BB-B6B3-CB4E-A7A2-351FCE023FE7}"/>
-    <hyperlink ref="F105" r:id="rId29" xr:uid="{A0B6605F-B37F-434A-8AEA-F0CB46055E22}"/>
-    <hyperlink ref="F114" r:id="rId30" xr:uid="{2EF8DF20-0EF7-4840-AC38-29C64AF5C186}"/>
-    <hyperlink ref="F117" r:id="rId31" xr:uid="{A0262EA2-DC6E-884F-80C7-303FD637A859}"/>
-    <hyperlink ref="F118" r:id="rId32" xr:uid="{049853C1-729D-9C4B-949D-FEBAE26B26D5}"/>
-    <hyperlink ref="F119" r:id="rId33" xr:uid="{59BE7560-AEC1-B64A-8B50-03D6A552F07B}"/>
-    <hyperlink ref="F120" r:id="rId34" xr:uid="{C0F51B2A-45E7-6D41-8232-DA7205EB12FB}"/>
-    <hyperlink ref="F121" r:id="rId35" xr:uid="{BF651D05-F02D-E948-B8A9-22260259738B}"/>
-    <hyperlink ref="F122" r:id="rId36" xr:uid="{DB9E6789-F281-994D-9D56-47AA19BB7556}"/>
-    <hyperlink ref="F123" r:id="rId37" xr:uid="{96A190E9-3569-5144-80C1-CEA7D46BEFDB}"/>
-    <hyperlink ref="F124" r:id="rId38" xr:uid="{F764D9D3-F1DB-5749-B1B9-5315EE113BA4}"/>
-    <hyperlink ref="F125" r:id="rId39" xr:uid="{4694032A-E86D-6145-B19F-5FE9D178BB31}"/>
-    <hyperlink ref="F131" r:id="rId40" xr:uid="{59C34E12-49FD-B942-941E-33BE339D3439}"/>
-    <hyperlink ref="F138" r:id="rId41" xr:uid="{FD8D5E73-41AD-8046-955C-15233A75A9DC}"/>
-    <hyperlink ref="F139" r:id="rId42" xr:uid="{3385E6D0-CBA5-A042-99FF-FBFBE2F24306}"/>
-    <hyperlink ref="F143" r:id="rId43" xr:uid="{63F018E8-0392-E24B-B1A6-89ED2C52F00B}"/>
-    <hyperlink ref="F144" r:id="rId44" xr:uid="{08A2D2CE-A6C4-FC45-8AE2-17B323D018A6}"/>
-    <hyperlink ref="F145" r:id="rId45" xr:uid="{17BB58AA-7748-F247-A3AA-ECA5F25C4258}"/>
-    <hyperlink ref="G146" r:id="rId46" xr:uid="{628E2625-F1D2-DC45-BB00-92D5029F1D08}"/>
-    <hyperlink ref="F147" r:id="rId47" xr:uid="{6CFE1148-9296-3643-90DE-DFAEB57BC570}"/>
-    <hyperlink ref="F148" r:id="rId48" xr:uid="{D54D40F4-8961-3348-BF74-74736CCB022E}"/>
-    <hyperlink ref="F149" r:id="rId49" xr:uid="{6848736E-2B5C-9E4D-9EAF-AD5565B47669}"/>
-    <hyperlink ref="F150" r:id="rId50" xr:uid="{D84EB54A-6097-D648-92A5-5F3BAFF86CEA}"/>
-    <hyperlink ref="F151" r:id="rId51" xr:uid="{FD4E266A-815E-BC4A-861C-189DB85BA33A}"/>
-    <hyperlink ref="F152" r:id="rId52" xr:uid="{A2A0EA72-886A-9748-BE4C-C9C26D9DAD7C}"/>
-    <hyperlink ref="F153" r:id="rId53" xr:uid="{BE24F46F-AFE5-A14D-8ECE-2632A5ADE785}"/>
-    <hyperlink ref="F154" r:id="rId54" xr:uid="{854A2A4C-C908-FB43-85DD-352E51E1CAAD}"/>
-    <hyperlink ref="F155" r:id="rId55" xr:uid="{44BD2531-CDA8-F846-AD24-E2918F203277}"/>
-    <hyperlink ref="F156" r:id="rId56" xr:uid="{27F84449-7FAE-2549-97FD-33B7C531AE93}"/>
-    <hyperlink ref="F157" r:id="rId57" xr:uid="{7866B05B-87CA-094D-B73F-0A39A87FECAC}"/>
-    <hyperlink ref="F161" r:id="rId58" xr:uid="{FC0E72F2-F249-0240-B20D-8C5D0CA7C643}"/>
-    <hyperlink ref="F162" r:id="rId59" xr:uid="{0B9FA73B-9B8D-1643-8DEF-416E2B692694}"/>
-    <hyperlink ref="F164" r:id="rId60" xr:uid="{E45AB9BA-6376-DE4C-A3FA-32BA6546F516}"/>
-    <hyperlink ref="G164" r:id="rId61" xr:uid="{64FC7EE6-2E66-3748-976A-BE443F559B9C}"/>
-    <hyperlink ref="H164" r:id="rId62" xr:uid="{321D0DB5-E98D-CF41-A801-E8B7BFF09756}"/>
-    <hyperlink ref="I164" r:id="rId63" xr:uid="{FBA7510A-B20B-1F4E-B5B5-196E1A54C85F}"/>
-    <hyperlink ref="G165" r:id="rId64" xr:uid="{A6CF9215-BFC1-5043-A4EA-EF18123960B9}"/>
-    <hyperlink ref="F180" r:id="rId65" xr:uid="{17CCB66F-91D5-5E42-8770-FEA1371E346A}"/>
-    <hyperlink ref="F193" r:id="rId66" xr:uid="{1861960A-55A4-0249-B9DC-774FEFF441E2}"/>
-    <hyperlink ref="F196" r:id="rId67" xr:uid="{7B579B5A-985A-7D4D-BBC4-1401A261A7BC}"/>
-    <hyperlink ref="G196" r:id="rId68" xr:uid="{743AEE0D-D8B7-9146-A9A6-32FB9591B58D}"/>
-    <hyperlink ref="H196" r:id="rId69" xr:uid="{579AFDDA-539F-B541-B791-E62167568FDC}"/>
-    <hyperlink ref="I196" r:id="rId70" xr:uid="{2711D5EB-3959-ED49-BBAE-F4FC4BAFBC57}"/>
-    <hyperlink ref="F203" r:id="rId71" xr:uid="{09E204B8-2078-204B-9825-CBD106A65014}"/>
-    <hyperlink ref="G203" r:id="rId72" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view" xr:uid="{BB66E76C-2D49-F845-995B-32E33B962EBA}"/>
-    <hyperlink ref="F222" r:id="rId73" xr:uid="{99EF46DF-D91D-874B-9D6E-8FCBE58F05C7}"/>
-    <hyperlink ref="F223" r:id="rId74" xr:uid="{980A4C4E-9C30-7146-9332-598508B6B67F}"/>
-    <hyperlink ref="F224" r:id="rId75" xr:uid="{1D2CA386-3A8B-3247-938F-440847E13D23}"/>
-    <hyperlink ref="F225" r:id="rId76" xr:uid="{15A4F16A-31C9-1948-A6EE-B321367E4D03}"/>
-    <hyperlink ref="F226" r:id="rId77" xr:uid="{2D745C0F-6406-C948-9BDB-1EF51C0CF6A7}"/>
-    <hyperlink ref="F231" r:id="rId78" xr:uid="{E638AB9A-C220-984B-B7C5-1F942C99283B}"/>
-    <hyperlink ref="F234" r:id="rId79" xr:uid="{DDFC1201-2B33-9346-B27C-EFA753D505D9}"/>
-    <hyperlink ref="F236" r:id="rId80" xr:uid="{98FAF202-06A9-3543-AD0A-305D677787E0}"/>
-    <hyperlink ref="F237" r:id="rId81" xr:uid="{A584D741-8D46-B349-A945-AB1D2EB0F2E7}"/>
-    <hyperlink ref="F243" r:id="rId82" xr:uid="{49E513AF-3F9C-A943-BE28-188CC71E9067}"/>
+    <hyperlink ref="F5" r:id="rId1" xr:uid="{365E14E2-46BF-EE43-8255-1A41C64D4BD8}"/>
+    <hyperlink ref="G8" r:id="rId2" xr:uid="{C00986B7-D60E-8242-A439-4AD2D7C99FE5}"/>
+    <hyperlink ref="H15" r:id="rId3" xr:uid="{AA118D60-3EB4-4C4E-BCE6-D9D613D57451}"/>
+    <hyperlink ref="F16" r:id="rId4" xr:uid="{24D0F3F1-3A92-C64F-9317-A5CE8CA710C0}"/>
+    <hyperlink ref="F38" r:id="rId5" xr:uid="{002A6746-936A-AA4B-85F5-09305E7FED4C}"/>
+    <hyperlink ref="F41" r:id="rId6" xr:uid="{0C3A800C-A485-1447-997C-4F2DC9BAF6A5}"/>
+    <hyperlink ref="F42" r:id="rId7" xr:uid="{A46AF372-2FA6-D949-BDEB-99736455BC80}"/>
+    <hyperlink ref="F70" r:id="rId8" xr:uid="{9DDD3B2A-3478-544D-9D8C-9E091D01FD51}"/>
+    <hyperlink ref="F71" r:id="rId9" xr:uid="{75CA6F8E-0F89-604D-8B46-451DD3AC9EBC}"/>
+    <hyperlink ref="F78" r:id="rId10" xr:uid="{068078B3-3A0A-0341-8EAC-E9C6CC9C682E}"/>
+    <hyperlink ref="F80" r:id="rId11" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{958536D5-1068-B449-99B8-AE0D58CEAE3D}"/>
+    <hyperlink ref="F82" r:id="rId12" xr:uid="{1EAA4A5C-08DF-BB4E-BFD3-FC1206894A7D}"/>
+    <hyperlink ref="F83" r:id="rId13" xr:uid="{0FA84AB4-ECAB-454D-8A83-859E39579ADC}"/>
+    <hyperlink ref="F84" r:id="rId14" xr:uid="{11C20F6F-F1FF-244B-B0A7-DF4959E602BE}"/>
+    <hyperlink ref="F87" r:id="rId15" xr:uid="{E7B587D4-4728-9D45-94DD-83558B5026D0}"/>
+    <hyperlink ref="F88" r:id="rId16" xr:uid="{AE60B534-BE92-7E46-9132-CBAC9E040BFF}"/>
+    <hyperlink ref="F89" r:id="rId17" xr:uid="{5FBA3AF4-B685-AE42-9619-3E2BBA333B68}"/>
+    <hyperlink ref="F90" r:id="rId18" xr:uid="{1900EFEE-F2C8-7647-B4D4-A691B74FAE44}"/>
+    <hyperlink ref="F92" r:id="rId19" xr:uid="{E677E8B4-DB49-4F45-A987-CFDE15EFCBF0}"/>
+    <hyperlink ref="F93" r:id="rId20" xr:uid="{26D61E98-16AA-BB40-A9D1-349A46C16E57}"/>
+    <hyperlink ref="F94" r:id="rId21" xr:uid="{83C2EBE7-741A-0C42-B84E-FDA35BEE6AC5}"/>
+    <hyperlink ref="F95" r:id="rId22" xr:uid="{E60B8E58-1835-154D-AEC4-6488B9F59648}"/>
+    <hyperlink ref="F96" r:id="rId23" xr:uid="{1AD9F727-C0D8-644C-B509-A9BB1943A484}"/>
+    <hyperlink ref="F99" r:id="rId24" xr:uid="{0EDF44C1-AE60-7F44-8BCC-BEDC99793959}"/>
+    <hyperlink ref="F100" r:id="rId25" xr:uid="{C3C9CF5A-CF14-3C42-BD04-2F4DDAB41B6B}"/>
+    <hyperlink ref="F101" r:id="rId26" xr:uid="{4E49AE8A-BDDD-D54B-9B2B-8AEEFA6AFF1D}"/>
+    <hyperlink ref="F102" r:id="rId27" xr:uid="{59F6491A-79AE-2C49-BA22-5B81953E00F1}"/>
+    <hyperlink ref="F103" r:id="rId28" xr:uid="{E6A352B4-8E62-2A40-B70D-809A497139E0}"/>
+    <hyperlink ref="F104" r:id="rId29" xr:uid="{E0F2773F-59ED-AF46-9488-0AD4F5D729B2}"/>
+    <hyperlink ref="F113" r:id="rId30" xr:uid="{7AE036DC-5BDC-0447-A091-463757BC075D}"/>
+    <hyperlink ref="F116" r:id="rId31" xr:uid="{44B3F9FB-EDA4-1943-8890-E4AB0D4C618B}"/>
+    <hyperlink ref="F117" r:id="rId32" xr:uid="{D68B6B01-96FC-1D4B-A024-E54C43D6387E}"/>
+    <hyperlink ref="F118" r:id="rId33" xr:uid="{1C1E2B85-F635-EC46-B5F2-6F223D70B0B5}"/>
+    <hyperlink ref="F119" r:id="rId34" xr:uid="{9AE04842-FA97-1245-A036-E2A51214D0C3}"/>
+    <hyperlink ref="F120" r:id="rId35" xr:uid="{5D9A71EA-E9C0-7047-96F4-73F825B145FA}"/>
+    <hyperlink ref="F121" r:id="rId36" xr:uid="{0819190A-10FB-B140-89AD-98EF17E07919}"/>
+    <hyperlink ref="F122" r:id="rId37" xr:uid="{2551EB7F-1078-4646-A2E3-BA8243A5E4F6}"/>
+    <hyperlink ref="F123" r:id="rId38" xr:uid="{FFC3D432-97A6-6842-803C-93127657067D}"/>
+    <hyperlink ref="F124" r:id="rId39" xr:uid="{CE4EAEF3-CC7E-7A4A-8C2B-4EFA5FE22B99}"/>
+    <hyperlink ref="F130" r:id="rId40" xr:uid="{6E7234BC-DA20-EC40-839C-C7EA17D0810C}"/>
+    <hyperlink ref="F137" r:id="rId41" xr:uid="{58D40D66-E3D5-2243-9656-28CB720E98C5}"/>
+    <hyperlink ref="F138" r:id="rId42" xr:uid="{6C286B71-E66F-BE4C-89A8-B046EF084C00}"/>
+    <hyperlink ref="F142" r:id="rId43" xr:uid="{253D52A2-031F-DA45-819B-46B7BAA5434E}"/>
+    <hyperlink ref="F143" r:id="rId44" xr:uid="{ABCB2B19-87D3-C643-ABBC-23A6804324BE}"/>
+    <hyperlink ref="F144" r:id="rId45" xr:uid="{3261D6EB-5BBD-FF4B-A5C7-9FB44A9A2DA0}"/>
+    <hyperlink ref="G145" r:id="rId46" xr:uid="{B90128EA-2BC4-F84D-ADEE-C8BC7C157A9E}"/>
+    <hyperlink ref="F146" r:id="rId47" xr:uid="{C9F18949-C76C-6D44-BDBC-7D8818C467A8}"/>
+    <hyperlink ref="F147" r:id="rId48" xr:uid="{482421D5-A456-B540-98B9-A26868C9EC6B}"/>
+    <hyperlink ref="F148" r:id="rId49" xr:uid="{73BEEEC2-5536-654B-A9A9-B7290D6A4B9E}"/>
+    <hyperlink ref="F149" r:id="rId50" xr:uid="{ECF955C5-AC97-534C-A545-BC5127A9A787}"/>
+    <hyperlink ref="F150" r:id="rId51" xr:uid="{6C6B598D-AC83-5647-A25D-B1D4747D708A}"/>
+    <hyperlink ref="F151" r:id="rId52" xr:uid="{243F3C2A-D93A-E040-B9D6-0F77F868DAB9}"/>
+    <hyperlink ref="F152" r:id="rId53" xr:uid="{FD6D777A-ACDA-0940-9CB0-6DD97A0267E8}"/>
+    <hyperlink ref="F153" r:id="rId54" xr:uid="{5B7B865D-4B45-8C47-B797-25C2AB9B65B2}"/>
+    <hyperlink ref="F154" r:id="rId55" xr:uid="{005163E9-FD73-C94A-B56B-E1128FEF1D4D}"/>
+    <hyperlink ref="F155" r:id="rId56" xr:uid="{C7804621-58D2-A544-A3AA-9C1B9BE0253D}"/>
+    <hyperlink ref="F156" r:id="rId57" xr:uid="{A1E9D0FC-0174-8F4F-9D3B-7030555E4CD0}"/>
+    <hyperlink ref="F160" r:id="rId58" xr:uid="{FFCA4ECB-54E4-9C48-B2B7-DC1EFA557DB8}"/>
+    <hyperlink ref="F161" r:id="rId59" xr:uid="{885304DB-91C9-0545-8442-468157D3D3F9}"/>
+    <hyperlink ref="F163" r:id="rId60" xr:uid="{9BEB4F9C-72FB-E246-9709-0B90A12A1149}"/>
+    <hyperlink ref="G163" r:id="rId61" xr:uid="{EA3DE2D0-1EE8-9F47-AC60-4FE94CEEE017}"/>
+    <hyperlink ref="H163" r:id="rId62" xr:uid="{6A5D971B-7F30-594E-907E-2C3B56DBFBE6}"/>
+    <hyperlink ref="I163" r:id="rId63" xr:uid="{131E9C03-9DC8-F940-B271-186967D9EAAD}"/>
+    <hyperlink ref="G164" r:id="rId64" xr:uid="{B0C1326A-32E9-2544-90F4-C53B1AB01532}"/>
+    <hyperlink ref="F179" r:id="rId65" xr:uid="{270080D6-F880-FC43-877D-DFE8E6C048AE}"/>
+    <hyperlink ref="F192" r:id="rId66" xr:uid="{F17F5626-9D3B-D646-851C-325EA8071273}"/>
+    <hyperlink ref="F195" r:id="rId67" xr:uid="{27CE6421-E365-E647-A8FA-3D16837C4E9D}"/>
+    <hyperlink ref="G195" r:id="rId68" xr:uid="{53803EFA-EDFB-4A4F-B5CE-197EF8A0D2C7}"/>
+    <hyperlink ref="H195" r:id="rId69" xr:uid="{CCCB1E16-CA4B-1343-9621-88D20B749C09}"/>
+    <hyperlink ref="I195" r:id="rId70" xr:uid="{BEDCC2C1-1DE5-FD45-B51F-D92F62FB02A0}"/>
+    <hyperlink ref="F201" r:id="rId71" xr:uid="{22631BD7-8E2B-C146-A50C-84FF17A31237}"/>
+    <hyperlink ref="G201" r:id="rId72" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view" xr:uid="{4BA355E3-F03B-4644-AD1B-D52D1FC3B6CC}"/>
+    <hyperlink ref="F217" r:id="rId73" xr:uid="{ED2338F2-2D8B-FC4A-BEC7-FF8984973651}"/>
+    <hyperlink ref="F218" r:id="rId74" xr:uid="{9DCF66F3-9B62-674E-ADE8-7F370C0B35E5}"/>
+    <hyperlink ref="F219" r:id="rId75" xr:uid="{F45E203B-8CD9-A24E-8449-C1CCAE0DB7AE}"/>
+    <hyperlink ref="F220" r:id="rId76" xr:uid="{178595B4-9A2A-C045-AC61-3A83F6820F53}"/>
+    <hyperlink ref="F221" r:id="rId77" xr:uid="{9A0E30A7-3EAC-484F-A7A6-F55F26A59A1A}"/>
+    <hyperlink ref="F226" r:id="rId78" xr:uid="{43C1F347-3FE1-5142-B8C9-7E3993CE6A93}"/>
+    <hyperlink ref="F229" r:id="rId79" xr:uid="{B2489A93-A07F-5649-99D1-D9B801EC486C}"/>
+    <hyperlink ref="F231" r:id="rId80" xr:uid="{0BEC8478-06FB-C142-ABC2-3403AE8BACC5}"/>
+    <hyperlink ref="F232" r:id="rId81" xr:uid="{903EF81C-44A5-0541-9A8C-84B5E650DD33}"/>
+    <hyperlink ref="F238" r:id="rId82" xr:uid="{A93CD870-B22F-6544-969A-1A104E4DCC04}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E1CB4A-156F-E14A-B79A-3576F01411BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2A39A6-1DA3-D049-B460-C117A71609B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33000" yWindow="500" windowWidth="33380" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
+    <workbookView xWindow="960" yWindow="760" windowWidth="33380" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
   <sheets>
     <sheet name="xlsx" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3056" uniqueCount="1090">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3041" uniqueCount="1090">
   <si>
     <t>Household Name</t>
   </si>
@@ -6240,10 +6240,11 @@
         <v>424</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>426</v>
+        <v>902</v>
+      </c>
+      <c r="C119" s="2" t="str">
+        <f>VLOOKUP(B119,Sheet1!A:B,2,FALSE)</f>
+        <v>x=71.88, y=92.39</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>12</v>
@@ -6261,10 +6262,11 @@
         <v>424</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>429</v>
+        <v>898</v>
+      </c>
+      <c r="C120" s="2" t="str">
+        <f>VLOOKUP(B120,Sheet1!A:B,2,FALSE)</f>
+        <v>x=70.26, y=92.24</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>12</v>
@@ -6282,10 +6284,11 @@
         <v>424</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>431</v>
+        <v>886</v>
+      </c>
+      <c r="C121" s="2" t="str">
+        <f>VLOOKUP(B121,Sheet1!A:B,2,FALSE)</f>
+        <v>x=71.95, y=89.51</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>12</v>
@@ -6303,10 +6306,11 @@
         <v>424</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>433</v>
+        <v>913</v>
+      </c>
+      <c r="C122" s="2" t="str">
+        <f>VLOOKUP(B122,Sheet1!A:B,2,FALSE)</f>
+        <v>x=70.30, y=95.47</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>12</v>
@@ -6324,10 +6328,11 @@
         <v>424</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>435</v>
+        <v>917</v>
+      </c>
+      <c r="C123" s="2" t="str">
+        <f>VLOOKUP(B123,Sheet1!A:B,2,FALSE)</f>
+        <v>x=71.92, y=95.40</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>12</v>
@@ -6670,10 +6675,11 @@
         <v>17</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>495</v>
+        <v>825</v>
+      </c>
+      <c r="C139" s="2" t="str">
+        <f>VLOOKUP(B139,Sheet1!A:B,2,FALSE)</f>
+        <v>x=22.98, y=60.34</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>12</v>
@@ -6691,10 +6697,11 @@
         <v>17</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>497</v>
+        <v>829</v>
+      </c>
+      <c r="C140" s="2" t="str">
+        <f>VLOOKUP(B140,Sheet1!A:B,2,FALSE)</f>
+        <v>x=21.40, y=60.27</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>12</v>
@@ -6712,10 +6719,11 @@
         <v>17</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>499</v>
+        <v>838</v>
+      </c>
+      <c r="C141" s="2" t="str">
+        <f>VLOOKUP(B141,Sheet1!A:B,2,FALSE)</f>
+        <v>x=22.98, y=63.15</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>12</v>
@@ -6733,10 +6741,11 @@
         <v>500</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>502</v>
+        <v>871</v>
+      </c>
+      <c r="C142" s="2" t="str">
+        <f>VLOOKUP(B142,Sheet1!A:B,2,FALSE)</f>
+        <v>x=21.40, y=86.14</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>12</v>
@@ -6756,10 +6765,11 @@
         <v>500</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>505</v>
+        <v>884</v>
+      </c>
+      <c r="C143" s="2" t="str">
+        <f>VLOOKUP(B143,Sheet1!A:B,2,FALSE)</f>
+        <v>x=21.37, y=89.01</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>12</v>
@@ -6779,10 +6789,11 @@
         <v>500</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>507</v>
+        <v>900</v>
+      </c>
+      <c r="C144" s="2" t="str">
+        <f>VLOOKUP(B144,Sheet1!A:B,2,FALSE)</f>
+        <v>x=21.26, y=92.24</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>12</v>
@@ -8022,10 +8033,10 @@
         <v>164</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>167</v>
@@ -8038,16 +8049,16 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
-        <v>164</v>
+        <v>639</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>167</v>
+        <v>639</v>
       </c>
       <c r="E206" s="2"/>
       <c r="F206" s="2"/>
@@ -8060,10 +8071,10 @@
         <v>639</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>639</v>
@@ -8079,10 +8090,10 @@
         <v>639</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>639</v>
@@ -8098,10 +8109,10 @@
         <v>639</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>639</v>
@@ -8114,16 +8125,16 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
-        <v>639</v>
+        <v>566</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>639</v>
+        <v>569</v>
       </c>
       <c r="E210" s="2"/>
       <c r="F210" s="2"/>
@@ -8136,10 +8147,10 @@
         <v>566</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>569</v>
@@ -8155,10 +8166,10 @@
         <v>566</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>569</v>
@@ -8174,10 +8185,10 @@
         <v>566</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>652</v>
+        <v>699</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>653</v>
+        <v>713</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>569</v>
@@ -8193,10 +8204,10 @@
         <v>566</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>569</v>
@@ -8212,10 +8223,10 @@
         <v>566</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>715</v>
+        <v>867</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>569</v>
@@ -8228,39 +8239,43 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
-        <v>566</v>
+        <v>1029</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>867</v>
+        <v>930</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>569</v>
+        <v>980</v>
       </c>
       <c r="E216" s="2"/>
-      <c r="F216" s="2"/>
+      <c r="F216" s="1" t="s">
+        <v>1030</v>
+      </c>
       <c r="G216" s="2"/>
       <c r="H216" s="2"/>
       <c r="I216" s="2"/>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
-        <v>1029</v>
+        <v>979</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="E217" s="2"/>
+      <c r="E217" s="2" t="s">
+        <v>981</v>
+      </c>
       <c r="F217" s="1" t="s">
-        <v>1030</v>
+        <v>982</v>
       </c>
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
@@ -8268,22 +8283,22 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
-        <v>979</v>
+        <v>1044</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>980</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>981</v>
+        <v>1045</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>982</v>
+        <v>1053</v>
       </c>
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
@@ -8291,22 +8306,20 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>939</v>
+        <v>732</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="E219" s="2" t="s">
-        <v>1045</v>
-      </c>
+      <c r="E219" s="2"/>
       <c r="F219" s="1" t="s">
-        <v>1053</v>
+        <v>1043</v>
       </c>
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
@@ -8314,20 +8327,20 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
-        <v>1040</v>
+        <v>1068</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>732</v>
+        <v>868</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>980</v>
+        <v>569</v>
       </c>
       <c r="E220" s="2"/>
       <c r="F220" s="1" t="s">
-        <v>1043</v>
+        <v>1069</v>
       </c>
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
@@ -8335,21 +8348,19 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" s="2" t="s">
-        <v>1068</v>
+        <v>566</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>569</v>
       </c>
       <c r="E221" s="2"/>
-      <c r="F221" s="1" t="s">
-        <v>1069</v>
-      </c>
+      <c r="F221" s="2"/>
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
       <c r="I221" s="2"/>
@@ -8359,10 +8370,10 @@
         <v>566</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>569</v>
@@ -8378,10 +8389,10 @@
         <v>566</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>873</v>
+        <v>714</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>569</v>
@@ -8394,18 +8405,20 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
-        <v>566</v>
+        <v>1084</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>700</v>
+        <v>864</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>714</v>
+        <v>865</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="E224" s="2"/>
+        <v>1071</v>
+      </c>
+      <c r="E224" s="8" t="s">
+        <v>1085</v>
+      </c>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
@@ -8413,44 +8426,42 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" s="2" t="s">
-        <v>1084</v>
+        <v>1041</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>864</v>
+        <v>833</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>865</v>
+        <v>834</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E225" s="8" t="s">
-        <v>1085</v>
-      </c>
-      <c r="F225" s="2"/>
+        <v>980</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F225" s="1" t="s">
+        <v>390</v>
+      </c>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
       <c r="I225" s="2"/>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
-        <v>1041</v>
+        <v>566</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>833</v>
+        <v>878</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>834</v>
+        <v>879</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>980</v>
-      </c>
-      <c r="E226" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F226" s="1" t="s">
-        <v>390</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="E226" s="2"/>
+      <c r="F226" s="2"/>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
       <c r="I226" s="2"/>
@@ -8460,10 +8471,10 @@
         <v>566</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>878</v>
+        <v>922</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>879</v>
+        <v>923</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>569</v>
@@ -8476,39 +8487,41 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
-        <v>566</v>
+        <v>1070</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>922</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>923</v>
+        <v>509</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>510</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>569</v>
+        <v>1071</v>
       </c>
       <c r="E228" s="2"/>
-      <c r="F228" s="2"/>
+      <c r="F228" s="1" t="s">
+        <v>1072</v>
+      </c>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
       <c r="I228" s="2"/>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229" s="2" t="s">
-        <v>1070</v>
+        <v>609</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="C229" s="4" t="s">
-        <v>510</v>
+        <v>759</v>
+      </c>
+      <c r="C229" s="6" t="s">
+        <v>760</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>1071</v>
+        <v>980</v>
       </c>
       <c r="E229" s="2"/>
-      <c r="F229" s="1" t="s">
-        <v>1072</v>
+      <c r="F229" s="2" t="s">
+        <v>611</v>
       </c>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
@@ -8516,20 +8529,20 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" s="2" t="s">
-        <v>609</v>
+        <v>1067</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="C230" s="6" t="s">
-        <v>760</v>
+        <v>255</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>256</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>980</v>
+        <v>155</v>
       </c>
       <c r="E230" s="2"/>
-      <c r="F230" s="2" t="s">
-        <v>611</v>
+      <c r="F230" s="1" t="s">
+        <v>659</v>
       </c>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
@@ -8537,20 +8550,20 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" s="2" t="s">
-        <v>1067</v>
+        <v>508</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>256</v>
+        <v>633</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>634</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E231" s="2"/>
       <c r="F231" s="1" t="s">
-        <v>659</v>
+        <v>1054</v>
       </c>
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
@@ -8558,41 +8571,39 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
-        <v>508</v>
+        <v>164</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="C232" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>636</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E232" s="2"/>
-      <c r="F232" s="1" t="s">
-        <v>1054</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F232" s="2"/>
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
       <c r="I232" s="2"/>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" s="2" t="s">
-        <v>164</v>
+        <v>1074</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>937</v>
+        <v>966</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>938</v>
+        <v>967</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E233" s="2" t="s">
-        <v>1073</v>
-      </c>
+        <v>1071</v>
+      </c>
+      <c r="E233" s="2"/>
       <c r="F233" s="2"/>
       <c r="G233" s="2"/>
       <c r="H233" s="2"/>
@@ -8600,16 +8611,16 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" s="2" t="s">
-        <v>1074</v>
+        <v>566</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>966</v>
+        <v>948</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>967</v>
+        <v>949</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>1071</v>
+        <v>569</v>
       </c>
       <c r="E234" s="2"/>
       <c r="F234" s="2"/>
@@ -8622,10 +8633,10 @@
         <v>566</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>948</v>
+        <v>890</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>949</v>
+        <v>891</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>569</v>
@@ -8641,10 +8652,10 @@
         <v>566</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>890</v>
+        <v>869</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>891</v>
+        <v>870</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>569</v>
@@ -8657,40 +8668,42 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
-        <v>566</v>
+        <v>436</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>869</v>
+        <v>956</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>870</v>
+        <v>957</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>569</v>
+        <v>1071</v>
       </c>
       <c r="E237" s="2"/>
-      <c r="F237" s="2"/>
+      <c r="F237" s="1" t="s">
+        <v>439</v>
+      </c>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
       <c r="I237" s="2"/>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
-        <v>436</v>
+        <v>164</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E238" s="2"/>
-      <c r="F238" s="1" t="s">
-        <v>439</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F238" s="2"/>
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
       <c r="I238" s="2"/>
@@ -8700,10 +8713,10 @@
         <v>164</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>167</v>
@@ -8721,17 +8734,15 @@
         <v>164</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>968</v>
+        <v>928</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>969</v>
+        <v>929</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E240" s="2" t="s">
-        <v>1081</v>
-      </c>
+      <c r="E240" s="2"/>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
       <c r="H240" s="2"/>
@@ -8742,10 +8753,10 @@
         <v>164</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>928</v>
+        <v>1086</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>167</v>
@@ -8758,18 +8769,20 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" s="2" t="s">
-        <v>164</v>
+        <v>1059</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>1086</v>
+        <v>191</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>925</v>
+        <v>192</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E242" s="2"/>
+      <c r="E242" s="2" t="s">
+        <v>1088</v>
+      </c>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
@@ -8777,20 +8790,18 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" s="2" t="s">
-        <v>1059</v>
+        <v>238</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C243" t="s">
-        <v>192</v>
+        <v>739</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>740</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E243" s="2" t="s">
-        <v>1088</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="E243" s="2"/>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
@@ -8798,13 +8809,13 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="C244" t="s">
-        <v>740</v>
+        <v>620</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>698</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>155</v>
@@ -8817,40 +8828,32 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" s="2" t="s">
-        <v>241</v>
+        <v>1089</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>620</v>
+        <v>723</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>698</v>
+        <v>724</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="E245" s="2"/>
-      <c r="F245" s="2"/>
+      <c r="F245" s="2" t="s">
+        <v>193</v>
+      </c>
       <c r="G245" s="2"/>
       <c r="H245" s="2"/>
       <c r="I245" s="2"/>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A246" s="2" t="s">
-        <v>1089</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="C246" t="s">
-        <v>724</v>
-      </c>
-      <c r="D246" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="A246" s="2"/>
+      <c r="B246" s="2"/>
+      <c r="C246" s="2"/>
+      <c r="D246" s="2"/>
       <c r="E246" s="2"/>
-      <c r="F246" s="2" t="s">
-        <v>193</v>
-      </c>
+      <c r="F246" s="2"/>
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
       <c r="I246" s="2"/>
@@ -8913,88 +8916,88 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F5" r:id="rId1" xr:uid="{365E14E2-46BF-EE43-8255-1A41C64D4BD8}"/>
-    <hyperlink ref="G8" r:id="rId2" xr:uid="{C00986B7-D60E-8242-A439-4AD2D7C99FE5}"/>
-    <hyperlink ref="H15" r:id="rId3" xr:uid="{AA118D60-3EB4-4C4E-BCE6-D9D613D57451}"/>
-    <hyperlink ref="F16" r:id="rId4" xr:uid="{24D0F3F1-3A92-C64F-9317-A5CE8CA710C0}"/>
-    <hyperlink ref="F38" r:id="rId5" xr:uid="{002A6746-936A-AA4B-85F5-09305E7FED4C}"/>
-    <hyperlink ref="F41" r:id="rId6" xr:uid="{0C3A800C-A485-1447-997C-4F2DC9BAF6A5}"/>
-    <hyperlink ref="F42" r:id="rId7" xr:uid="{A46AF372-2FA6-D949-BDEB-99736455BC80}"/>
-    <hyperlink ref="F70" r:id="rId8" xr:uid="{9DDD3B2A-3478-544D-9D8C-9E091D01FD51}"/>
-    <hyperlink ref="F71" r:id="rId9" xr:uid="{75CA6F8E-0F89-604D-8B46-451DD3AC9EBC}"/>
-    <hyperlink ref="F78" r:id="rId10" xr:uid="{068078B3-3A0A-0341-8EAC-E9C6CC9C682E}"/>
-    <hyperlink ref="F80" r:id="rId11" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{958536D5-1068-B449-99B8-AE0D58CEAE3D}"/>
-    <hyperlink ref="F82" r:id="rId12" xr:uid="{1EAA4A5C-08DF-BB4E-BFD3-FC1206894A7D}"/>
-    <hyperlink ref="F83" r:id="rId13" xr:uid="{0FA84AB4-ECAB-454D-8A83-859E39579ADC}"/>
-    <hyperlink ref="F84" r:id="rId14" xr:uid="{11C20F6F-F1FF-244B-B0A7-DF4959E602BE}"/>
-    <hyperlink ref="F87" r:id="rId15" xr:uid="{E7B587D4-4728-9D45-94DD-83558B5026D0}"/>
-    <hyperlink ref="F88" r:id="rId16" xr:uid="{AE60B534-BE92-7E46-9132-CBAC9E040BFF}"/>
-    <hyperlink ref="F89" r:id="rId17" xr:uid="{5FBA3AF4-B685-AE42-9619-3E2BBA333B68}"/>
-    <hyperlink ref="F90" r:id="rId18" xr:uid="{1900EFEE-F2C8-7647-B4D4-A691B74FAE44}"/>
-    <hyperlink ref="F92" r:id="rId19" xr:uid="{E677E8B4-DB49-4F45-A987-CFDE15EFCBF0}"/>
-    <hyperlink ref="F93" r:id="rId20" xr:uid="{26D61E98-16AA-BB40-A9D1-349A46C16E57}"/>
-    <hyperlink ref="F94" r:id="rId21" xr:uid="{83C2EBE7-741A-0C42-B84E-FDA35BEE6AC5}"/>
-    <hyperlink ref="F95" r:id="rId22" xr:uid="{E60B8E58-1835-154D-AEC4-6488B9F59648}"/>
-    <hyperlink ref="F96" r:id="rId23" xr:uid="{1AD9F727-C0D8-644C-B509-A9BB1943A484}"/>
-    <hyperlink ref="F99" r:id="rId24" xr:uid="{0EDF44C1-AE60-7F44-8BCC-BEDC99793959}"/>
-    <hyperlink ref="F100" r:id="rId25" xr:uid="{C3C9CF5A-CF14-3C42-BD04-2F4DDAB41B6B}"/>
-    <hyperlink ref="F101" r:id="rId26" xr:uid="{4E49AE8A-BDDD-D54B-9B2B-8AEEFA6AFF1D}"/>
-    <hyperlink ref="F102" r:id="rId27" xr:uid="{59F6491A-79AE-2C49-BA22-5B81953E00F1}"/>
-    <hyperlink ref="F103" r:id="rId28" xr:uid="{E6A352B4-8E62-2A40-B70D-809A497139E0}"/>
-    <hyperlink ref="F104" r:id="rId29" xr:uid="{E0F2773F-59ED-AF46-9488-0AD4F5D729B2}"/>
-    <hyperlink ref="F113" r:id="rId30" xr:uid="{7AE036DC-5BDC-0447-A091-463757BC075D}"/>
-    <hyperlink ref="F116" r:id="rId31" xr:uid="{44B3F9FB-EDA4-1943-8890-E4AB0D4C618B}"/>
-    <hyperlink ref="F117" r:id="rId32" xr:uid="{D68B6B01-96FC-1D4B-A024-E54C43D6387E}"/>
-    <hyperlink ref="F118" r:id="rId33" xr:uid="{1C1E2B85-F635-EC46-B5F2-6F223D70B0B5}"/>
-    <hyperlink ref="F119" r:id="rId34" xr:uid="{9AE04842-FA97-1245-A036-E2A51214D0C3}"/>
-    <hyperlink ref="F120" r:id="rId35" xr:uid="{5D9A71EA-E9C0-7047-96F4-73F825B145FA}"/>
-    <hyperlink ref="F121" r:id="rId36" xr:uid="{0819190A-10FB-B140-89AD-98EF17E07919}"/>
-    <hyperlink ref="F122" r:id="rId37" xr:uid="{2551EB7F-1078-4646-A2E3-BA8243A5E4F6}"/>
-    <hyperlink ref="F123" r:id="rId38" xr:uid="{FFC3D432-97A6-6842-803C-93127657067D}"/>
-    <hyperlink ref="F124" r:id="rId39" xr:uid="{CE4EAEF3-CC7E-7A4A-8C2B-4EFA5FE22B99}"/>
-    <hyperlink ref="F130" r:id="rId40" xr:uid="{6E7234BC-DA20-EC40-839C-C7EA17D0810C}"/>
-    <hyperlink ref="F137" r:id="rId41" xr:uid="{58D40D66-E3D5-2243-9656-28CB720E98C5}"/>
-    <hyperlink ref="F138" r:id="rId42" xr:uid="{6C286B71-E66F-BE4C-89A8-B046EF084C00}"/>
-    <hyperlink ref="F142" r:id="rId43" xr:uid="{253D52A2-031F-DA45-819B-46B7BAA5434E}"/>
-    <hyperlink ref="F143" r:id="rId44" xr:uid="{ABCB2B19-87D3-C643-ABBC-23A6804324BE}"/>
-    <hyperlink ref="F144" r:id="rId45" xr:uid="{3261D6EB-5BBD-FF4B-A5C7-9FB44A9A2DA0}"/>
-    <hyperlink ref="G145" r:id="rId46" xr:uid="{B90128EA-2BC4-F84D-ADEE-C8BC7C157A9E}"/>
-    <hyperlink ref="F146" r:id="rId47" xr:uid="{C9F18949-C76C-6D44-BDBC-7D8818C467A8}"/>
-    <hyperlink ref="F147" r:id="rId48" xr:uid="{482421D5-A456-B540-98B9-A26868C9EC6B}"/>
-    <hyperlink ref="F148" r:id="rId49" xr:uid="{73BEEEC2-5536-654B-A9A9-B7290D6A4B9E}"/>
-    <hyperlink ref="F149" r:id="rId50" xr:uid="{ECF955C5-AC97-534C-A545-BC5127A9A787}"/>
-    <hyperlink ref="F150" r:id="rId51" xr:uid="{6C6B598D-AC83-5647-A25D-B1D4747D708A}"/>
-    <hyperlink ref="F151" r:id="rId52" xr:uid="{243F3C2A-D93A-E040-B9D6-0F77F868DAB9}"/>
-    <hyperlink ref="F152" r:id="rId53" xr:uid="{FD6D777A-ACDA-0940-9CB0-6DD97A0267E8}"/>
-    <hyperlink ref="F153" r:id="rId54" xr:uid="{5B7B865D-4B45-8C47-B797-25C2AB9B65B2}"/>
-    <hyperlink ref="F154" r:id="rId55" xr:uid="{005163E9-FD73-C94A-B56B-E1128FEF1D4D}"/>
-    <hyperlink ref="F155" r:id="rId56" xr:uid="{C7804621-58D2-A544-A3AA-9C1B9BE0253D}"/>
-    <hyperlink ref="F156" r:id="rId57" xr:uid="{A1E9D0FC-0174-8F4F-9D3B-7030555E4CD0}"/>
-    <hyperlink ref="F160" r:id="rId58" xr:uid="{FFCA4ECB-54E4-9C48-B2B7-DC1EFA557DB8}"/>
-    <hyperlink ref="F161" r:id="rId59" xr:uid="{885304DB-91C9-0545-8442-468157D3D3F9}"/>
-    <hyperlink ref="F163" r:id="rId60" xr:uid="{9BEB4F9C-72FB-E246-9709-0B90A12A1149}"/>
-    <hyperlink ref="G163" r:id="rId61" xr:uid="{EA3DE2D0-1EE8-9F47-AC60-4FE94CEEE017}"/>
-    <hyperlink ref="H163" r:id="rId62" xr:uid="{6A5D971B-7F30-594E-907E-2C3B56DBFBE6}"/>
-    <hyperlink ref="I163" r:id="rId63" xr:uid="{131E9C03-9DC8-F940-B271-186967D9EAAD}"/>
-    <hyperlink ref="G164" r:id="rId64" xr:uid="{B0C1326A-32E9-2544-90F4-C53B1AB01532}"/>
-    <hyperlink ref="F179" r:id="rId65" xr:uid="{270080D6-F880-FC43-877D-DFE8E6C048AE}"/>
-    <hyperlink ref="F192" r:id="rId66" xr:uid="{F17F5626-9D3B-D646-851C-325EA8071273}"/>
-    <hyperlink ref="F195" r:id="rId67" xr:uid="{27CE6421-E365-E647-A8FA-3D16837C4E9D}"/>
-    <hyperlink ref="G195" r:id="rId68" xr:uid="{53803EFA-EDFB-4A4F-B5CE-197EF8A0D2C7}"/>
-    <hyperlink ref="H195" r:id="rId69" xr:uid="{CCCB1E16-CA4B-1343-9621-88D20B749C09}"/>
-    <hyperlink ref="I195" r:id="rId70" xr:uid="{BEDCC2C1-1DE5-FD45-B51F-D92F62FB02A0}"/>
-    <hyperlink ref="F201" r:id="rId71" xr:uid="{22631BD7-8E2B-C146-A50C-84FF17A31237}"/>
-    <hyperlink ref="G201" r:id="rId72" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view" xr:uid="{4BA355E3-F03B-4644-AD1B-D52D1FC3B6CC}"/>
-    <hyperlink ref="F217" r:id="rId73" xr:uid="{ED2338F2-2D8B-FC4A-BEC7-FF8984973651}"/>
-    <hyperlink ref="F218" r:id="rId74" xr:uid="{9DCF66F3-9B62-674E-ADE8-7F370C0B35E5}"/>
-    <hyperlink ref="F219" r:id="rId75" xr:uid="{F45E203B-8CD9-A24E-8449-C1CCAE0DB7AE}"/>
-    <hyperlink ref="F220" r:id="rId76" xr:uid="{178595B4-9A2A-C045-AC61-3A83F6820F53}"/>
-    <hyperlink ref="F221" r:id="rId77" xr:uid="{9A0E30A7-3EAC-484F-A7A6-F55F26A59A1A}"/>
-    <hyperlink ref="F226" r:id="rId78" xr:uid="{43C1F347-3FE1-5142-B8C9-7E3993CE6A93}"/>
-    <hyperlink ref="F229" r:id="rId79" xr:uid="{B2489A93-A07F-5649-99D1-D9B801EC486C}"/>
-    <hyperlink ref="F231" r:id="rId80" xr:uid="{0BEC8478-06FB-C142-ABC2-3403AE8BACC5}"/>
-    <hyperlink ref="F232" r:id="rId81" xr:uid="{903EF81C-44A5-0541-9A8C-84B5E650DD33}"/>
-    <hyperlink ref="F238" r:id="rId82" xr:uid="{A93CD870-B22F-6544-969A-1A104E4DCC04}"/>
+    <hyperlink ref="F5" r:id="rId1" xr:uid="{0AB045F2-E56A-044E-8D8D-E1DC5FE1CBC5}"/>
+    <hyperlink ref="G8" r:id="rId2" xr:uid="{87D3A3EE-2B88-164F-9F09-914B3D68A2F5}"/>
+    <hyperlink ref="H15" r:id="rId3" xr:uid="{D07FDE6D-4A0B-BE4B-B53A-E6E8DEE42DDD}"/>
+    <hyperlink ref="F16" r:id="rId4" xr:uid="{FE7CC572-22A6-4340-8584-4F7354393190}"/>
+    <hyperlink ref="F38" r:id="rId5" xr:uid="{168C388A-10A6-7B45-88F0-5501064E4A32}"/>
+    <hyperlink ref="F41" r:id="rId6" xr:uid="{CD6C81A6-2A1F-3E43-8127-E9D09EF07A16}"/>
+    <hyperlink ref="F42" r:id="rId7" xr:uid="{414F1078-BD93-754B-9FB5-B8BA8272669C}"/>
+    <hyperlink ref="F70" r:id="rId8" xr:uid="{78B8557C-336E-FB43-8F93-178A6394F6D8}"/>
+    <hyperlink ref="F71" r:id="rId9" xr:uid="{08083AAA-8163-B547-A19C-82359E9E0EA1}"/>
+    <hyperlink ref="F78" r:id="rId10" xr:uid="{9C65A6EB-4F7C-144D-8681-F06CCFCD6276}"/>
+    <hyperlink ref="F80" r:id="rId11" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{6D193310-F7ED-CA4D-B525-49E03318CCEB}"/>
+    <hyperlink ref="F82" r:id="rId12" xr:uid="{E02027AE-0260-6943-806D-5DA84D6A9A6B}"/>
+    <hyperlink ref="F83" r:id="rId13" xr:uid="{66A0F6E2-A05C-434A-94BF-4AC25C50AB85}"/>
+    <hyperlink ref="F84" r:id="rId14" xr:uid="{626A1202-2BDC-3140-9251-F45543CB09F2}"/>
+    <hyperlink ref="F87" r:id="rId15" xr:uid="{4908BC65-5278-0A45-A258-0131DEC55723}"/>
+    <hyperlink ref="F88" r:id="rId16" xr:uid="{A144B8FA-8019-D04E-87DC-29D48C393D69}"/>
+    <hyperlink ref="F89" r:id="rId17" xr:uid="{95EFE1FA-5C24-784E-AD1E-93EE2A63A546}"/>
+    <hyperlink ref="F90" r:id="rId18" xr:uid="{32A158D9-4B87-824B-AB61-6B12B6E98CFD}"/>
+    <hyperlink ref="F92" r:id="rId19" xr:uid="{8A94F32D-F2B1-EC4B-9D66-BACFA262E0EE}"/>
+    <hyperlink ref="F93" r:id="rId20" xr:uid="{E2235D0B-C2E9-B14E-B617-80E2CEDB49C7}"/>
+    <hyperlink ref="F94" r:id="rId21" xr:uid="{110622C5-51D8-894E-8932-F7A4172B56A6}"/>
+    <hyperlink ref="F95" r:id="rId22" xr:uid="{3149F5C7-2C10-DE49-BDC6-1B6B266FA059}"/>
+    <hyperlink ref="F96" r:id="rId23" xr:uid="{59005E10-2BAC-2F4A-9009-8AD7AC70BAD3}"/>
+    <hyperlink ref="F99" r:id="rId24" xr:uid="{CED6A443-E9E6-3E49-956D-EA12DF5B3DEA}"/>
+    <hyperlink ref="F100" r:id="rId25" xr:uid="{465A66B8-1577-C440-9067-FCA4FE22A2D1}"/>
+    <hyperlink ref="F101" r:id="rId26" xr:uid="{44412521-835F-5946-8EA5-9C32CF609109}"/>
+    <hyperlink ref="F102" r:id="rId27" xr:uid="{4F2231EF-F1D8-3C4A-97A3-320866366335}"/>
+    <hyperlink ref="F103" r:id="rId28" xr:uid="{CB891C5B-59C7-C94C-A888-3B106A5F0FDD}"/>
+    <hyperlink ref="F104" r:id="rId29" xr:uid="{84BCCEFD-A2BD-5549-AAFB-AF2B71AD0E85}"/>
+    <hyperlink ref="F113" r:id="rId30" xr:uid="{98FF0402-AA33-CB43-A884-587A68E9E6EA}"/>
+    <hyperlink ref="F116" r:id="rId31" xr:uid="{8CB896B6-9987-F441-82FF-D9532D9277EE}"/>
+    <hyperlink ref="F117" r:id="rId32" xr:uid="{04B0F952-6CF0-D24F-81B8-4B7C7A840919}"/>
+    <hyperlink ref="F118" r:id="rId33" xr:uid="{262503F7-8E84-4C44-A3CA-6D67FFADEC47}"/>
+    <hyperlink ref="F119" r:id="rId34" xr:uid="{0E788439-B8E6-D74F-9121-E617A5B4CB19}"/>
+    <hyperlink ref="F120" r:id="rId35" xr:uid="{061CF9A0-E4D7-0742-97C2-2B310400FD94}"/>
+    <hyperlink ref="F121" r:id="rId36" xr:uid="{C35ACC96-CC79-D549-BD7E-FC3DC89A01F4}"/>
+    <hyperlink ref="F122" r:id="rId37" xr:uid="{0B91CAB4-80C2-104B-A7F0-969B8C4D19F7}"/>
+    <hyperlink ref="F123" r:id="rId38" xr:uid="{2213CD68-DDBA-414D-A2B1-1CBD7AC43159}"/>
+    <hyperlink ref="F124" r:id="rId39" xr:uid="{AC33011D-B4A2-814E-8A54-8217460DA167}"/>
+    <hyperlink ref="F130" r:id="rId40" xr:uid="{BE406C0A-EDEA-C540-AE3A-3D08C7866906}"/>
+    <hyperlink ref="F137" r:id="rId41" xr:uid="{C236FA99-B8A0-C949-80D8-87C30BC816F9}"/>
+    <hyperlink ref="F138" r:id="rId42" xr:uid="{936D69B2-227B-F64C-83BB-54831B957916}"/>
+    <hyperlink ref="F142" r:id="rId43" xr:uid="{67193E24-3154-B849-BAC4-4DE584B753EE}"/>
+    <hyperlink ref="F143" r:id="rId44" xr:uid="{D838C8D7-C233-C849-A504-91875C4C6C06}"/>
+    <hyperlink ref="F144" r:id="rId45" xr:uid="{08AD25E3-FBA4-A84B-8DB7-49E184BF07F4}"/>
+    <hyperlink ref="G145" r:id="rId46" xr:uid="{BBC09AD5-E30B-5845-96B8-24B56919451D}"/>
+    <hyperlink ref="F146" r:id="rId47" xr:uid="{6033E2AE-2775-C242-A1BD-06E5D0B32F47}"/>
+    <hyperlink ref="F147" r:id="rId48" xr:uid="{83C253AE-AD19-D840-BEB4-77B57FFBAEC5}"/>
+    <hyperlink ref="F148" r:id="rId49" xr:uid="{B98D88B0-ED4A-D141-8CEF-3AF727B6202A}"/>
+    <hyperlink ref="F149" r:id="rId50" xr:uid="{E92226CF-CF7B-3544-82D5-95B9D4568A5C}"/>
+    <hyperlink ref="F150" r:id="rId51" xr:uid="{194AD442-153B-E64F-A42D-FB69D762D7EB}"/>
+    <hyperlink ref="F151" r:id="rId52" xr:uid="{A0261D30-E806-EC4C-B4CF-434E2AA6C765}"/>
+    <hyperlink ref="F152" r:id="rId53" xr:uid="{3BDC04C2-63A3-D64B-B5A2-15575CD44E80}"/>
+    <hyperlink ref="F153" r:id="rId54" xr:uid="{00673863-5562-734E-B66F-08A640D1F06A}"/>
+    <hyperlink ref="F154" r:id="rId55" xr:uid="{38D8ED80-6FA2-A84E-89D8-98FBE8677406}"/>
+    <hyperlink ref="F155" r:id="rId56" xr:uid="{02EE18E2-91EB-094C-ABD6-CC8A1C6EFF3F}"/>
+    <hyperlink ref="F156" r:id="rId57" xr:uid="{F83721EF-F230-CF47-A7C1-DA0B70194F8B}"/>
+    <hyperlink ref="F160" r:id="rId58" xr:uid="{76413504-563E-154D-9341-AACB82EA608C}"/>
+    <hyperlink ref="F161" r:id="rId59" xr:uid="{D5C34AB8-3A21-D940-ADE7-FBD29BD395A3}"/>
+    <hyperlink ref="F163" r:id="rId60" xr:uid="{7D3AE0E2-8EBC-0D46-8C30-CCAA88C6442D}"/>
+    <hyperlink ref="G163" r:id="rId61" xr:uid="{51B84387-074B-C04A-8122-6D5F8B4EA1DF}"/>
+    <hyperlink ref="H163" r:id="rId62" xr:uid="{C6B004D3-A3E4-7445-8137-C823C10C49E4}"/>
+    <hyperlink ref="I163" r:id="rId63" xr:uid="{DFAFEBEF-3651-5744-8E60-AF2BD507B56E}"/>
+    <hyperlink ref="G164" r:id="rId64" xr:uid="{5672884D-678D-EB4A-873D-999056730B60}"/>
+    <hyperlink ref="F179" r:id="rId65" xr:uid="{94888A3F-AB69-2B4A-8AA2-83F2013B6986}"/>
+    <hyperlink ref="F192" r:id="rId66" xr:uid="{91EFF99C-DD4D-974C-89E7-7C13B8C3715C}"/>
+    <hyperlink ref="F195" r:id="rId67" xr:uid="{82E1A65F-3788-B740-B0C0-7D6537F54DC5}"/>
+    <hyperlink ref="G195" r:id="rId68" xr:uid="{BDE5270C-DB9F-B449-A56A-9DCAA370299E}"/>
+    <hyperlink ref="H195" r:id="rId69" xr:uid="{43413F0D-FA79-2E42-ABEA-D6BE8BB4683F}"/>
+    <hyperlink ref="I195" r:id="rId70" xr:uid="{9596B637-1826-F941-9C9B-3E68FBB88766}"/>
+    <hyperlink ref="F201" r:id="rId71" xr:uid="{957992F9-EF91-A34D-95E9-0355221FE468}"/>
+    <hyperlink ref="G201" r:id="rId72" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view" xr:uid="{B876CD8F-2B91-3C49-930C-B2E931DACAF9}"/>
+    <hyperlink ref="F216" r:id="rId73" xr:uid="{EFBDE15E-8786-C04C-9FF6-19864A6F4E88}"/>
+    <hyperlink ref="F217" r:id="rId74" xr:uid="{A25ECB1A-B28F-5049-B565-9F44D1D40A06}"/>
+    <hyperlink ref="F218" r:id="rId75" xr:uid="{6FF4D85A-2AAC-8646-9F1C-11C2F3B44FA7}"/>
+    <hyperlink ref="F219" r:id="rId76" xr:uid="{7AE5391E-F68D-4848-AB27-60D4CD022691}"/>
+    <hyperlink ref="F220" r:id="rId77" xr:uid="{468DCB47-1F18-AC44-BD19-8E7FB2AA7E74}"/>
+    <hyperlink ref="F225" r:id="rId78" xr:uid="{45EE4087-CC84-5A47-82A9-FE188D8A5010}"/>
+    <hyperlink ref="F228" r:id="rId79" xr:uid="{8093CE5E-9FFE-3146-9CDE-7E6BA25BAB91}"/>
+    <hyperlink ref="F230" r:id="rId80" xr:uid="{991F94F6-A6FB-884C-99E0-2EE4530B0BDE}"/>
+    <hyperlink ref="F231" r:id="rId81" xr:uid="{B8F3BCD4-4823-A347-937C-5C72F3B4EC16}"/>
+    <hyperlink ref="F237" r:id="rId82" xr:uid="{8D72700C-0EA2-AE42-B43D-C95D0639BE88}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2A39A6-1DA3-D049-B460-C117A71609B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6080CEF-337D-094E-AEF0-8F0BD7824E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="960" yWindow="760" windowWidth="33380" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3041" uniqueCount="1090">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3040" uniqueCount="1090">
   <si>
     <t>Household Name</t>
   </si>
@@ -3259,9 +3259,6 @@
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000w8AGvYAM/view</t>
   </si>
   <si>
-    <t>Potential table for Manchester Grand Hyatt</t>
-  </si>
-  <si>
     <t>Larry Paulson</t>
   </si>
   <si>
@@ -3308,6 +3305,9 @@
   </si>
   <si>
     <t>Lyn Hall &amp; Fiona Mackin-Jha</t>
+  </si>
+  <si>
+    <t>Manchester Grand Hyatt</t>
   </si>
 </sst>
 </file>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -4638,7 +4638,7 @@
         <v>1032</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -6347,7 +6347,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>437</v>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
@@ -6649,7 +6649,7 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>491</v>
@@ -6661,7 +6661,7 @@
         <v>12</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>666</v>
@@ -7514,7 +7514,7 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>594</v>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="E179" s="2"/>
       <c r="F179" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
@@ -7535,7 +7535,7 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>596</v>
@@ -8405,7 +8405,7 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>864</v>
@@ -8417,7 +8417,7 @@
         <v>1071</v>
       </c>
       <c r="E224" s="8" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
@@ -8571,7 +8571,7 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
-        <v>164</v>
+        <v>1089</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>635</v>
@@ -8580,11 +8580,9 @@
         <v>636</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E232" s="2" t="s">
-        <v>1073</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="E232" s="2"/>
       <c r="F232" s="2"/>
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
@@ -8592,7 +8590,7 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>966</v>
@@ -8701,7 +8699,7 @@
         <v>167</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
@@ -8722,7 +8720,7 @@
         <v>167</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
@@ -8753,7 +8751,7 @@
         <v>164</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>925</v>
@@ -8781,7 +8779,7 @@
         <v>167</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
@@ -8828,7 +8826,7 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>723</v>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6080CEF-337D-094E-AEF0-8F0BD7824E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD6D450-5493-2946-90F7-15D36F01585F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="960" yWindow="760" windowWidth="33380" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3040" uniqueCount="1090">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3043" uniqueCount="1090">
   <si>
     <t>Household Name</t>
   </si>
@@ -6677,9 +6677,8 @@
       <c r="B139" s="2" t="s">
         <v>825</v>
       </c>
-      <c r="C139" s="2" t="str">
-        <f>VLOOKUP(B139,Sheet1!A:B,2,FALSE)</f>
-        <v>x=22.98, y=60.34</v>
+      <c r="C139" s="2" t="s">
+        <v>850</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>12</v>
@@ -6699,9 +6698,8 @@
       <c r="B140" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="C140" s="2" t="str">
-        <f>VLOOKUP(B140,Sheet1!A:B,2,FALSE)</f>
-        <v>x=21.40, y=60.27</v>
+      <c r="C140" s="2" t="s">
+        <v>854</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>12</v>
@@ -6721,9 +6719,8 @@
       <c r="B141" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="C141" s="2" t="str">
-        <f>VLOOKUP(B141,Sheet1!A:B,2,FALSE)</f>
-        <v>x=22.98, y=63.15</v>
+      <c r="C141" s="2" t="s">
+        <v>839</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>12</v>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD6D450-5493-2946-90F7-15D36F01585F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034347D6-DFF2-6D43-8C1C-FC2B8FCCC671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="760" windowWidth="33380" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="33340" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
   <sheets>
     <sheet name="xlsx" sheetId="1" r:id="rId1"/>
@@ -4041,10 +4041,10 @@
         <v>54</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>55</v>
+        <v>717</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>56</v>
+        <v>718</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>12</v>
@@ -4131,10 +4131,10 @@
         <v>73</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
+      </c>
+      <c r="C18" t="s">
+        <v>71</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>12</v>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034347D6-DFF2-6D43-8C1C-FC2B8FCCC671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96912650-C7DA-2940-B7D5-D2400E1799A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33340" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -4152,10 +4152,10 @@
         <v>77</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>12</v>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96912650-C7DA-2940-B7D5-D2400E1799A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FED8E6C-06A9-9D40-8362-35C2B78724CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33340" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3043" uniqueCount="1090">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3061" uniqueCount="1098">
   <si>
     <t>Household Name</t>
   </si>
@@ -3308,13 +3308,37 @@
   </si>
   <si>
     <t>Manchester Grand Hyatt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curebound Inventory </t>
+  </si>
+  <si>
+    <t>Rady Kids Sponsored by Smith</t>
+  </si>
+  <si>
+    <t>Stephanie Smith Donating to cancer fighters</t>
+  </si>
+  <si>
+    <t>Tammy &amp; Larry Hershfeild</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000y36ZPYAY/view</t>
+  </si>
+  <si>
+    <t>Jessica Doshay &amp; Sarah Towner</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000x2HfWYAU/view</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000y6U47YAE/view</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3383,6 +3407,12 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3405,7 +3435,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3415,6 +3445,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3750,7 +3781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7894B4-148E-174D-AE8B-E6DE441B89B0}">
-  <dimension ref="A1:I251"/>
+  <dimension ref="A1:I252"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -4133,7 +4164,7 @@
       <c r="B18" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D18" s="2" t="s">
@@ -4154,7 +4185,7 @@
       <c r="B19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D19" s="2" t="s">
@@ -6092,16 +6123,14 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>401</v>
+        <v>164</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>407</v>
-      </c>
+      <c r="C112" s="2"/>
       <c r="D112" s="2" t="s">
-        <v>12</v>
+        <v>1090</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
@@ -6242,9 +6271,8 @@
       <c r="B119" s="2" t="s">
         <v>902</v>
       </c>
-      <c r="C119" s="2" t="str">
-        <f>VLOOKUP(B119,Sheet1!A:B,2,FALSE)</f>
-        <v>x=71.88, y=92.39</v>
+      <c r="C119" s="2" t="s">
+        <v>903</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>12</v>
@@ -6264,9 +6292,8 @@
       <c r="B120" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="C120" s="2" t="str">
-        <f>VLOOKUP(B120,Sheet1!A:B,2,FALSE)</f>
-        <v>x=70.26, y=92.24</v>
+      <c r="C120" s="2" t="s">
+        <v>899</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>12</v>
@@ -6286,9 +6313,8 @@
       <c r="B121" s="2" t="s">
         <v>886</v>
       </c>
-      <c r="C121" s="2" t="str">
-        <f>VLOOKUP(B121,Sheet1!A:B,2,FALSE)</f>
-        <v>x=71.95, y=89.51</v>
+      <c r="C121" s="2" t="s">
+        <v>887</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>12</v>
@@ -6308,9 +6334,8 @@
       <c r="B122" s="2" t="s">
         <v>913</v>
       </c>
-      <c r="C122" s="2" t="str">
-        <f>VLOOKUP(B122,Sheet1!A:B,2,FALSE)</f>
-        <v>x=70.30, y=95.47</v>
+      <c r="C122" s="2" t="s">
+        <v>914</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>12</v>
@@ -6330,9 +6355,8 @@
       <c r="B123" s="2" t="s">
         <v>917</v>
       </c>
-      <c r="C123" s="2" t="str">
-        <f>VLOOKUP(B123,Sheet1!A:B,2,FALSE)</f>
-        <v>x=71.92, y=95.40</v>
+      <c r="C123" s="2" t="s">
+        <v>918</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>12</v>
@@ -6675,7 +6699,7 @@
         <v>17</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>825</v>
+        <v>849</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>850</v>
@@ -6696,7 +6720,7 @@
         <v>17</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>829</v>
+        <v>853</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>854</v>
@@ -6740,9 +6764,8 @@
       <c r="B142" s="2" t="s">
         <v>871</v>
       </c>
-      <c r="C142" s="2" t="str">
-        <f>VLOOKUP(B142,Sheet1!A:B,2,FALSE)</f>
-        <v>x=21.40, y=86.14</v>
+      <c r="C142" s="2" t="s">
+        <v>872</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>12</v>
@@ -6764,9 +6787,8 @@
       <c r="B143" s="2" t="s">
         <v>884</v>
       </c>
-      <c r="C143" s="2" t="str">
-        <f>VLOOKUP(B143,Sheet1!A:B,2,FALSE)</f>
-        <v>x=21.37, y=89.01</v>
+      <c r="C143" s="2" t="s">
+        <v>885</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>12</v>
@@ -6788,9 +6810,8 @@
       <c r="B144" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="C144" s="2" t="str">
-        <f>VLOOKUP(B144,Sheet1!A:B,2,FALSE)</f>
-        <v>x=21.26, y=92.24</v>
+      <c r="C144" s="2" t="s">
+        <v>901</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>12</v>
@@ -8280,19 +8301,17 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
-        <v>1044</v>
+        <v>1091</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="C218" s="2" t="s">
-        <v>939</v>
-      </c>
+      <c r="C218" s="2"/>
       <c r="D218" s="2" t="s">
         <v>980</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>1045</v>
+        <v>1092</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>1053</v>
@@ -8843,21 +8862,35 @@
       <c r="I245" s="2"/>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A246" s="2"/>
-      <c r="B246" s="2"/>
+      <c r="A246" s="9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>876</v>
+      </c>
       <c r="C246" s="2"/>
-      <c r="D246" s="2"/>
+      <c r="D246" s="2" t="s">
+        <v>1071</v>
+      </c>
       <c r="E246" s="2"/>
-      <c r="F246" s="2"/>
+      <c r="F246" s="1" t="s">
+        <v>1094</v>
+      </c>
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
       <c r="I246" s="2"/>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A247" s="2"/>
-      <c r="B247" s="2"/>
+      <c r="A247" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>937</v>
+      </c>
       <c r="C247" s="2"/>
-      <c r="D247" s="2"/>
+      <c r="D247" s="2" t="s">
+        <v>167</v>
+      </c>
       <c r="E247" s="2"/>
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
@@ -8865,13 +8898,23 @@
       <c r="I247" s="2"/>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A248" s="2"/>
-      <c r="B248" s="2"/>
+      <c r="A248" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>496</v>
+      </c>
       <c r="C248" s="2"/>
-      <c r="D248" s="2"/>
+      <c r="D248" s="2" t="s">
+        <v>980</v>
+      </c>
       <c r="E248" s="2"/>
-      <c r="F248" s="2"/>
-      <c r="G248" s="2"/>
+      <c r="F248" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G248" s="1" t="s">
+        <v>1097</v>
+      </c>
       <c r="H248" s="2"/>
       <c r="I248" s="2"/>
     </row>
@@ -8881,8 +8924,8 @@
       <c r="C249" s="2"/>
       <c r="D249" s="2"/>
       <c r="E249" s="2"/>
-      <c r="F249" s="2"/>
-      <c r="G249" s="2"/>
+      <c r="F249" s="3"/>
+      <c r="G249" s="3"/>
       <c r="H249" s="2"/>
       <c r="I249" s="2"/>
     </row>
@@ -8908,91 +8951,105 @@
       <c r="H251" s="2"/>
       <c r="I251" s="2"/>
     </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A252" s="2"/>
+      <c r="B252" s="2"/>
+      <c r="C252" s="2"/>
+      <c r="D252" s="2"/>
+      <c r="E252" s="2"/>
+      <c r="F252" s="2"/>
+      <c r="G252" s="2"/>
+      <c r="H252" s="2"/>
+      <c r="I252" s="2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F5" r:id="rId1" xr:uid="{0AB045F2-E56A-044E-8D8D-E1DC5FE1CBC5}"/>
-    <hyperlink ref="G8" r:id="rId2" xr:uid="{87D3A3EE-2B88-164F-9F09-914B3D68A2F5}"/>
-    <hyperlink ref="H15" r:id="rId3" xr:uid="{D07FDE6D-4A0B-BE4B-B53A-E6E8DEE42DDD}"/>
-    <hyperlink ref="F16" r:id="rId4" xr:uid="{FE7CC572-22A6-4340-8584-4F7354393190}"/>
-    <hyperlink ref="F38" r:id="rId5" xr:uid="{168C388A-10A6-7B45-88F0-5501064E4A32}"/>
-    <hyperlink ref="F41" r:id="rId6" xr:uid="{CD6C81A6-2A1F-3E43-8127-E9D09EF07A16}"/>
-    <hyperlink ref="F42" r:id="rId7" xr:uid="{414F1078-BD93-754B-9FB5-B8BA8272669C}"/>
-    <hyperlink ref="F70" r:id="rId8" xr:uid="{78B8557C-336E-FB43-8F93-178A6394F6D8}"/>
-    <hyperlink ref="F71" r:id="rId9" xr:uid="{08083AAA-8163-B547-A19C-82359E9E0EA1}"/>
-    <hyperlink ref="F78" r:id="rId10" xr:uid="{9C65A6EB-4F7C-144D-8681-F06CCFCD6276}"/>
-    <hyperlink ref="F80" r:id="rId11" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{6D193310-F7ED-CA4D-B525-49E03318CCEB}"/>
-    <hyperlink ref="F82" r:id="rId12" xr:uid="{E02027AE-0260-6943-806D-5DA84D6A9A6B}"/>
-    <hyperlink ref="F83" r:id="rId13" xr:uid="{66A0F6E2-A05C-434A-94BF-4AC25C50AB85}"/>
-    <hyperlink ref="F84" r:id="rId14" xr:uid="{626A1202-2BDC-3140-9251-F45543CB09F2}"/>
-    <hyperlink ref="F87" r:id="rId15" xr:uid="{4908BC65-5278-0A45-A258-0131DEC55723}"/>
-    <hyperlink ref="F88" r:id="rId16" xr:uid="{A144B8FA-8019-D04E-87DC-29D48C393D69}"/>
-    <hyperlink ref="F89" r:id="rId17" xr:uid="{95EFE1FA-5C24-784E-AD1E-93EE2A63A546}"/>
-    <hyperlink ref="F90" r:id="rId18" xr:uid="{32A158D9-4B87-824B-AB61-6B12B6E98CFD}"/>
-    <hyperlink ref="F92" r:id="rId19" xr:uid="{8A94F32D-F2B1-EC4B-9D66-BACFA262E0EE}"/>
-    <hyperlink ref="F93" r:id="rId20" xr:uid="{E2235D0B-C2E9-B14E-B617-80E2CEDB49C7}"/>
-    <hyperlink ref="F94" r:id="rId21" xr:uid="{110622C5-51D8-894E-8932-F7A4172B56A6}"/>
-    <hyperlink ref="F95" r:id="rId22" xr:uid="{3149F5C7-2C10-DE49-BDC6-1B6B266FA059}"/>
-    <hyperlink ref="F96" r:id="rId23" xr:uid="{59005E10-2BAC-2F4A-9009-8AD7AC70BAD3}"/>
-    <hyperlink ref="F99" r:id="rId24" xr:uid="{CED6A443-E9E6-3E49-956D-EA12DF5B3DEA}"/>
-    <hyperlink ref="F100" r:id="rId25" xr:uid="{465A66B8-1577-C440-9067-FCA4FE22A2D1}"/>
-    <hyperlink ref="F101" r:id="rId26" xr:uid="{44412521-835F-5946-8EA5-9C32CF609109}"/>
-    <hyperlink ref="F102" r:id="rId27" xr:uid="{4F2231EF-F1D8-3C4A-97A3-320866366335}"/>
-    <hyperlink ref="F103" r:id="rId28" xr:uid="{CB891C5B-59C7-C94C-A888-3B106A5F0FDD}"/>
-    <hyperlink ref="F104" r:id="rId29" xr:uid="{84BCCEFD-A2BD-5549-AAFB-AF2B71AD0E85}"/>
-    <hyperlink ref="F113" r:id="rId30" xr:uid="{98FF0402-AA33-CB43-A884-587A68E9E6EA}"/>
-    <hyperlink ref="F116" r:id="rId31" xr:uid="{8CB896B6-9987-F441-82FF-D9532D9277EE}"/>
-    <hyperlink ref="F117" r:id="rId32" xr:uid="{04B0F952-6CF0-D24F-81B8-4B7C7A840919}"/>
-    <hyperlink ref="F118" r:id="rId33" xr:uid="{262503F7-8E84-4C44-A3CA-6D67FFADEC47}"/>
-    <hyperlink ref="F119" r:id="rId34" xr:uid="{0E788439-B8E6-D74F-9121-E617A5B4CB19}"/>
-    <hyperlink ref="F120" r:id="rId35" xr:uid="{061CF9A0-E4D7-0742-97C2-2B310400FD94}"/>
-    <hyperlink ref="F121" r:id="rId36" xr:uid="{C35ACC96-CC79-D549-BD7E-FC3DC89A01F4}"/>
-    <hyperlink ref="F122" r:id="rId37" xr:uid="{0B91CAB4-80C2-104B-A7F0-969B8C4D19F7}"/>
-    <hyperlink ref="F123" r:id="rId38" xr:uid="{2213CD68-DDBA-414D-A2B1-1CBD7AC43159}"/>
-    <hyperlink ref="F124" r:id="rId39" xr:uid="{AC33011D-B4A2-814E-8A54-8217460DA167}"/>
-    <hyperlink ref="F130" r:id="rId40" xr:uid="{BE406C0A-EDEA-C540-AE3A-3D08C7866906}"/>
-    <hyperlink ref="F137" r:id="rId41" xr:uid="{C236FA99-B8A0-C949-80D8-87C30BC816F9}"/>
-    <hyperlink ref="F138" r:id="rId42" xr:uid="{936D69B2-227B-F64C-83BB-54831B957916}"/>
-    <hyperlink ref="F142" r:id="rId43" xr:uid="{67193E24-3154-B849-BAC4-4DE584B753EE}"/>
-    <hyperlink ref="F143" r:id="rId44" xr:uid="{D838C8D7-C233-C849-A504-91875C4C6C06}"/>
-    <hyperlink ref="F144" r:id="rId45" xr:uid="{08AD25E3-FBA4-A84B-8DB7-49E184BF07F4}"/>
-    <hyperlink ref="G145" r:id="rId46" xr:uid="{BBC09AD5-E30B-5845-96B8-24B56919451D}"/>
-    <hyperlink ref="F146" r:id="rId47" xr:uid="{6033E2AE-2775-C242-A1BD-06E5D0B32F47}"/>
-    <hyperlink ref="F147" r:id="rId48" xr:uid="{83C253AE-AD19-D840-BEB4-77B57FFBAEC5}"/>
-    <hyperlink ref="F148" r:id="rId49" xr:uid="{B98D88B0-ED4A-D141-8CEF-3AF727B6202A}"/>
-    <hyperlink ref="F149" r:id="rId50" xr:uid="{E92226CF-CF7B-3544-82D5-95B9D4568A5C}"/>
-    <hyperlink ref="F150" r:id="rId51" xr:uid="{194AD442-153B-E64F-A42D-FB69D762D7EB}"/>
-    <hyperlink ref="F151" r:id="rId52" xr:uid="{A0261D30-E806-EC4C-B4CF-434E2AA6C765}"/>
-    <hyperlink ref="F152" r:id="rId53" xr:uid="{3BDC04C2-63A3-D64B-B5A2-15575CD44E80}"/>
-    <hyperlink ref="F153" r:id="rId54" xr:uid="{00673863-5562-734E-B66F-08A640D1F06A}"/>
-    <hyperlink ref="F154" r:id="rId55" xr:uid="{38D8ED80-6FA2-A84E-89D8-98FBE8677406}"/>
-    <hyperlink ref="F155" r:id="rId56" xr:uid="{02EE18E2-91EB-094C-ABD6-CC8A1C6EFF3F}"/>
-    <hyperlink ref="F156" r:id="rId57" xr:uid="{F83721EF-F230-CF47-A7C1-DA0B70194F8B}"/>
-    <hyperlink ref="F160" r:id="rId58" xr:uid="{76413504-563E-154D-9341-AACB82EA608C}"/>
-    <hyperlink ref="F161" r:id="rId59" xr:uid="{D5C34AB8-3A21-D940-ADE7-FBD29BD395A3}"/>
-    <hyperlink ref="F163" r:id="rId60" xr:uid="{7D3AE0E2-8EBC-0D46-8C30-CCAA88C6442D}"/>
-    <hyperlink ref="G163" r:id="rId61" xr:uid="{51B84387-074B-C04A-8122-6D5F8B4EA1DF}"/>
-    <hyperlink ref="H163" r:id="rId62" xr:uid="{C6B004D3-A3E4-7445-8137-C823C10C49E4}"/>
-    <hyperlink ref="I163" r:id="rId63" xr:uid="{DFAFEBEF-3651-5744-8E60-AF2BD507B56E}"/>
-    <hyperlink ref="G164" r:id="rId64" xr:uid="{5672884D-678D-EB4A-873D-999056730B60}"/>
-    <hyperlink ref="F179" r:id="rId65" xr:uid="{94888A3F-AB69-2B4A-8AA2-83F2013B6986}"/>
-    <hyperlink ref="F192" r:id="rId66" xr:uid="{91EFF99C-DD4D-974C-89E7-7C13B8C3715C}"/>
-    <hyperlink ref="F195" r:id="rId67" xr:uid="{82E1A65F-3788-B740-B0C0-7D6537F54DC5}"/>
-    <hyperlink ref="G195" r:id="rId68" xr:uid="{BDE5270C-DB9F-B449-A56A-9DCAA370299E}"/>
-    <hyperlink ref="H195" r:id="rId69" xr:uid="{43413F0D-FA79-2E42-ABEA-D6BE8BB4683F}"/>
-    <hyperlink ref="I195" r:id="rId70" xr:uid="{9596B637-1826-F941-9C9B-3E68FBB88766}"/>
-    <hyperlink ref="F201" r:id="rId71" xr:uid="{957992F9-EF91-A34D-95E9-0355221FE468}"/>
-    <hyperlink ref="G201" r:id="rId72" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view" xr:uid="{B876CD8F-2B91-3C49-930C-B2E931DACAF9}"/>
-    <hyperlink ref="F216" r:id="rId73" xr:uid="{EFBDE15E-8786-C04C-9FF6-19864A6F4E88}"/>
-    <hyperlink ref="F217" r:id="rId74" xr:uid="{A25ECB1A-B28F-5049-B565-9F44D1D40A06}"/>
-    <hyperlink ref="F218" r:id="rId75" xr:uid="{6FF4D85A-2AAC-8646-9F1C-11C2F3B44FA7}"/>
-    <hyperlink ref="F219" r:id="rId76" xr:uid="{7AE5391E-F68D-4848-AB27-60D4CD022691}"/>
-    <hyperlink ref="F220" r:id="rId77" xr:uid="{468DCB47-1F18-AC44-BD19-8E7FB2AA7E74}"/>
-    <hyperlink ref="F225" r:id="rId78" xr:uid="{45EE4087-CC84-5A47-82A9-FE188D8A5010}"/>
-    <hyperlink ref="F228" r:id="rId79" xr:uid="{8093CE5E-9FFE-3146-9CDE-7E6BA25BAB91}"/>
-    <hyperlink ref="F230" r:id="rId80" xr:uid="{991F94F6-A6FB-884C-99E0-2EE4530B0BDE}"/>
-    <hyperlink ref="F231" r:id="rId81" xr:uid="{B8F3BCD4-4823-A347-937C-5C72F3B4EC16}"/>
-    <hyperlink ref="F237" r:id="rId82" xr:uid="{8D72700C-0EA2-AE42-B43D-C95D0639BE88}"/>
+    <hyperlink ref="F5" r:id="rId1" xr:uid="{F837FE5B-009A-5E41-9919-715441AB0B1B}"/>
+    <hyperlink ref="G8" r:id="rId2" xr:uid="{A2E18574-7376-2D40-8622-EDDAC22418BA}"/>
+    <hyperlink ref="H15" r:id="rId3" xr:uid="{DE4DE499-C679-604C-AE6B-6B4D29D7C72F}"/>
+    <hyperlink ref="F16" r:id="rId4" xr:uid="{39D989A0-960F-074F-AC7D-11234243380B}"/>
+    <hyperlink ref="F38" r:id="rId5" xr:uid="{5E9C148C-AA79-1348-BCAC-FF7A1B7E74BF}"/>
+    <hyperlink ref="F41" r:id="rId6" xr:uid="{05A44978-D8E4-A244-8634-37AC1F1EB44C}"/>
+    <hyperlink ref="F42" r:id="rId7" xr:uid="{85B2974F-6824-6646-A292-8088C3ED1F69}"/>
+    <hyperlink ref="F70" r:id="rId8" xr:uid="{15A56521-14D7-9C41-AE6B-B476AE95BAAF}"/>
+    <hyperlink ref="F71" r:id="rId9" xr:uid="{9FA4EF41-0568-8645-8290-6DA9EAEABC36}"/>
+    <hyperlink ref="F78" r:id="rId10" xr:uid="{3EFF470B-0E94-214E-9443-E56AF17B121D}"/>
+    <hyperlink ref="F80" r:id="rId11" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{773FA8DE-2CC1-D945-9BA2-0AE1A31BC0E5}"/>
+    <hyperlink ref="F82" r:id="rId12" xr:uid="{FDB4BAB4-4A2A-AB45-8003-F395E02A7E62}"/>
+    <hyperlink ref="F83" r:id="rId13" xr:uid="{B59AAE8D-EA4E-8E46-BE1A-C8BDFB868748}"/>
+    <hyperlink ref="F84" r:id="rId14" xr:uid="{A3AC6792-7A06-904E-BC68-28F1DFF4075C}"/>
+    <hyperlink ref="F87" r:id="rId15" xr:uid="{56D0C844-74E6-7B4E-BBBB-462262C59A4E}"/>
+    <hyperlink ref="F88" r:id="rId16" xr:uid="{898CB5D7-DD4D-9440-BA59-4A64FF58061C}"/>
+    <hyperlink ref="F89" r:id="rId17" xr:uid="{31A17526-DE37-2B4C-98F8-A495DD8180BD}"/>
+    <hyperlink ref="F90" r:id="rId18" xr:uid="{51ECBB3A-79DE-7E41-9F2E-DBAEC891F74E}"/>
+    <hyperlink ref="F92" r:id="rId19" xr:uid="{71112AC6-CCBB-0349-ADF0-26B28C505F92}"/>
+    <hyperlink ref="F93" r:id="rId20" xr:uid="{83050CD8-ACBB-C64D-A443-B3A651F78132}"/>
+    <hyperlink ref="F94" r:id="rId21" xr:uid="{7ABB4F7F-F5E1-4441-8A70-8EE0325F6388}"/>
+    <hyperlink ref="F95" r:id="rId22" xr:uid="{2BECA3B4-A66A-DF4A-830B-B955578096F2}"/>
+    <hyperlink ref="F96" r:id="rId23" xr:uid="{FF0F0EB6-2E08-914B-B9FB-207F968038A7}"/>
+    <hyperlink ref="F99" r:id="rId24" xr:uid="{9717E59D-F205-8D4F-B3C1-3C0C1EF31108}"/>
+    <hyperlink ref="F100" r:id="rId25" xr:uid="{175DECD6-A8CF-8642-B6FE-CC0ECD3B4008}"/>
+    <hyperlink ref="F101" r:id="rId26" xr:uid="{6EC0E300-2055-0A49-864F-A4BA9C951517}"/>
+    <hyperlink ref="F102" r:id="rId27" xr:uid="{D1FF52B5-11E6-894C-8439-E8396B2A0B8A}"/>
+    <hyperlink ref="F103" r:id="rId28" xr:uid="{E0A67A88-07E4-DA44-A496-C32C764BEC62}"/>
+    <hyperlink ref="F104" r:id="rId29" xr:uid="{D725CEB7-BA74-4A4A-9121-47834676D8D2}"/>
+    <hyperlink ref="F113" r:id="rId30" xr:uid="{E672434A-25B7-0540-B1CD-140E91A14A5E}"/>
+    <hyperlink ref="F116" r:id="rId31" xr:uid="{46B62753-D89F-9940-AFB7-B4E4C83483E7}"/>
+    <hyperlink ref="F117" r:id="rId32" xr:uid="{F44A915A-9F9E-A14E-861B-4A0C9CC63348}"/>
+    <hyperlink ref="F118" r:id="rId33" xr:uid="{96C9F518-E770-434A-8663-5452F83CFD76}"/>
+    <hyperlink ref="F119" r:id="rId34" xr:uid="{7739C151-C132-0E4F-B8AE-E8367AAD6246}"/>
+    <hyperlink ref="F120" r:id="rId35" xr:uid="{1C83882E-8E5E-8345-BB7D-BB239ED3F784}"/>
+    <hyperlink ref="F121" r:id="rId36" xr:uid="{B2DA782D-8FD6-2541-BD05-A3C5843309E8}"/>
+    <hyperlink ref="F122" r:id="rId37" xr:uid="{ED3713D6-AD8E-B74A-8B98-3FEAA5003D75}"/>
+    <hyperlink ref="F123" r:id="rId38" xr:uid="{AEFE7C89-EC2A-A64F-A376-F292A548B8A4}"/>
+    <hyperlink ref="F124" r:id="rId39" xr:uid="{40437B6C-075B-6B4A-96BB-00BBF9D5EA40}"/>
+    <hyperlink ref="F130" r:id="rId40" xr:uid="{8E249B0C-4F6E-E14B-AD33-37C462E07AB0}"/>
+    <hyperlink ref="F137" r:id="rId41" xr:uid="{92B686E9-53CB-6549-8410-223F42D560CF}"/>
+    <hyperlink ref="F138" r:id="rId42" xr:uid="{9FBAB0F7-2225-1C44-9ACB-AD8A5F38CF10}"/>
+    <hyperlink ref="F142" r:id="rId43" xr:uid="{4327DB2B-149E-794F-A688-F5DED78F0A35}"/>
+    <hyperlink ref="F143" r:id="rId44" xr:uid="{50950B48-933C-204C-B4E5-41530AE555C9}"/>
+    <hyperlink ref="F144" r:id="rId45" xr:uid="{C33B52B5-9369-B344-B561-5340ECF445B8}"/>
+    <hyperlink ref="G145" r:id="rId46" xr:uid="{E02F97B6-41E0-6C47-B25D-59827C7DDB5F}"/>
+    <hyperlink ref="F146" r:id="rId47" xr:uid="{BCC9DAF4-2099-4D49-83A0-E491CF9009D4}"/>
+    <hyperlink ref="F147" r:id="rId48" xr:uid="{AFEACF1A-4527-6C41-852C-E65593625063}"/>
+    <hyperlink ref="F148" r:id="rId49" xr:uid="{E0A02364-027D-614F-BE1C-BD2731740E92}"/>
+    <hyperlink ref="F149" r:id="rId50" xr:uid="{3D6010C5-732A-4A4F-8703-EA585857FBEE}"/>
+    <hyperlink ref="F150" r:id="rId51" xr:uid="{F2EA3ADA-3A32-564E-8B15-98D059C308AC}"/>
+    <hyperlink ref="F151" r:id="rId52" xr:uid="{3486E020-2764-B84F-BA5A-27FB95FD2FAB}"/>
+    <hyperlink ref="F152" r:id="rId53" xr:uid="{C90D3824-FF88-6749-AA2E-1F783F598F2C}"/>
+    <hyperlink ref="F153" r:id="rId54" xr:uid="{0426AAFD-540B-5948-9623-32FDF41938DF}"/>
+    <hyperlink ref="F154" r:id="rId55" xr:uid="{4493A058-62F9-F747-9A2B-29CC2BC59FB1}"/>
+    <hyperlink ref="F155" r:id="rId56" xr:uid="{846F46B7-F73C-3542-A61D-FF7F60BF6E14}"/>
+    <hyperlink ref="F156" r:id="rId57" xr:uid="{F31E650C-5BB8-A842-B84A-757E43799774}"/>
+    <hyperlink ref="F160" r:id="rId58" xr:uid="{8785D4BD-0511-E84F-85F8-89061424CF07}"/>
+    <hyperlink ref="F161" r:id="rId59" xr:uid="{8174EE50-8065-834F-A8C9-D4CE3A8460FA}"/>
+    <hyperlink ref="F163" r:id="rId60" xr:uid="{CE794BAF-C7D1-EF4F-8E53-6B690380C297}"/>
+    <hyperlink ref="G163" r:id="rId61" xr:uid="{F3C24748-D246-B149-B3D6-2F558BC0A567}"/>
+    <hyperlink ref="H163" r:id="rId62" xr:uid="{3C2E15EE-D3BB-4E49-BFE1-9EE756E91621}"/>
+    <hyperlink ref="I163" r:id="rId63" xr:uid="{7CB05144-529A-4047-8600-6111EEA6B7F7}"/>
+    <hyperlink ref="G164" r:id="rId64" xr:uid="{E8286BB1-E3CC-0640-AC8F-B3C6066A5BDF}"/>
+    <hyperlink ref="F179" r:id="rId65" xr:uid="{D0BC1777-F31F-EB4E-91C5-6F9D918C63D1}"/>
+    <hyperlink ref="F192" r:id="rId66" xr:uid="{5D7A5891-ED27-2E45-A8F1-515302EF5C38}"/>
+    <hyperlink ref="F195" r:id="rId67" xr:uid="{CA5D1208-7C0A-C94E-90EE-749B2A5E1C05}"/>
+    <hyperlink ref="G195" r:id="rId68" xr:uid="{6479AE3D-0DC2-864C-8EE2-69D641BD80D4}"/>
+    <hyperlink ref="H195" r:id="rId69" xr:uid="{D7FA6D55-F268-EF4C-9BDC-694DBB9482E1}"/>
+    <hyperlink ref="I195" r:id="rId70" xr:uid="{C7074EC1-0FCB-3142-B7F7-F363A2E939B0}"/>
+    <hyperlink ref="F201" r:id="rId71" xr:uid="{F07CAA80-6FEB-9648-BFA4-69643BD1D2F2}"/>
+    <hyperlink ref="G201" r:id="rId72" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view" xr:uid="{27561D3E-E871-E348-9E3C-FCBE6BD2795D}"/>
+    <hyperlink ref="F216" r:id="rId73" xr:uid="{10CC2030-CFF7-AE48-8AC5-EFD3D795D7E4}"/>
+    <hyperlink ref="F217" r:id="rId74" xr:uid="{690867F5-8276-2346-8750-5A99A33F8BE3}"/>
+    <hyperlink ref="F218" r:id="rId75" xr:uid="{8D355359-2FC3-194B-825B-A421B209BB36}"/>
+    <hyperlink ref="F219" r:id="rId76" xr:uid="{0050D335-4F31-EB47-B470-1FD4F1867014}"/>
+    <hyperlink ref="F220" r:id="rId77" xr:uid="{60D3CEF3-D8EF-B84E-87A0-8BB2DCA3A1A7}"/>
+    <hyperlink ref="F225" r:id="rId78" xr:uid="{83220FA6-4F43-F246-A5E2-2D92CF0B88DF}"/>
+    <hyperlink ref="F228" r:id="rId79" xr:uid="{112F8051-E56D-E246-B326-AFA003D587DA}"/>
+    <hyperlink ref="F230" r:id="rId80" xr:uid="{4512F17F-DA68-524A-8326-8748C7BD9D63}"/>
+    <hyperlink ref="F231" r:id="rId81" xr:uid="{B1DA24A1-59F3-BE4C-9622-4E8DAD10017E}"/>
+    <hyperlink ref="F237" r:id="rId82" xr:uid="{6CDA9222-D464-8B4A-8535-E61CA8D6100F}"/>
+    <hyperlink ref="F246" r:id="rId83" xr:uid="{9573DE5D-3A50-2C4C-BD6C-D51F5E47AD48}"/>
+    <hyperlink ref="F248" r:id="rId84" xr:uid="{EB5AA941-4105-D746-9C12-9E3AA1AEC845}"/>
+    <hyperlink ref="G248" r:id="rId85" xr:uid="{18144297-1CD9-6E43-BCB4-CB02CC0EB017}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FED8E6C-06A9-9D40-8362-35C2B78724CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39482839-6E81-804A-B8CE-9D6D4D6DBEA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33340" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3061" uniqueCount="1098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3064" uniqueCount="1098">
   <si>
     <t>Household Name</t>
   </si>
@@ -8868,7 +8868,9 @@
       <c r="B246" s="2" t="s">
         <v>876</v>
       </c>
-      <c r="C246" s="2"/>
+      <c r="C246" s="2" t="s">
+        <v>877</v>
+      </c>
       <c r="D246" s="2" t="s">
         <v>1071</v>
       </c>
@@ -8887,7 +8889,9 @@
       <c r="B247" s="2" t="s">
         <v>937</v>
       </c>
-      <c r="C247" s="2"/>
+      <c r="C247" s="2" t="s">
+        <v>938</v>
+      </c>
       <c r="D247" s="2" t="s">
         <v>167</v>
       </c>
@@ -8904,7 +8908,9 @@
       <c r="B248" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="C248" s="2"/>
+      <c r="C248" s="2" t="s">
+        <v>497</v>
+      </c>
       <c r="D248" s="2" t="s">
         <v>980</v>
       </c>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39482839-6E81-804A-B8CE-9D6D4D6DBEA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1753E485-CB15-6B4A-81A2-FA0F8C7FE18A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33340" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3064" uniqueCount="1098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3066" uniqueCount="1098">
   <si>
     <t>Household Name</t>
   </si>
@@ -6128,7 +6128,9 @@
       <c r="B112" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C112" s="2"/>
+      <c r="C112" s="2" t="s">
+        <v>407</v>
+      </c>
       <c r="D112" s="2" t="s">
         <v>1090</v>
       </c>
@@ -8306,7 +8308,9 @@
       <c r="B218" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="C218" s="2"/>
+      <c r="C218" s="2" t="s">
+        <v>939</v>
+      </c>
       <c r="D218" s="2" t="s">
         <v>980</v>
       </c>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1753E485-CB15-6B4A-81A2-FA0F8C7FE18A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30702C2-3999-3C4E-A039-CB2E6F252050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33340" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3066" uniqueCount="1098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3061" uniqueCount="1098">
   <si>
     <t>Household Name</t>
   </si>
@@ -8710,17 +8710,15 @@
         <v>164</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E238" s="2" t="s">
-        <v>1080</v>
-      </c>
+      <c r="E238" s="2"/>
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
@@ -8731,11 +8729,9 @@
         <v>164</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>968</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>969</v>
-      </c>
+        <v>928</v>
+      </c>
+      <c r="C239" s="2"/>
       <c r="D239" s="2" t="s">
         <v>167</v>
       </c>
@@ -8752,10 +8748,10 @@
         <v>164</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>928</v>
+        <v>1085</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>167</v>
@@ -8768,18 +8764,20 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A241" s="2" t="s">
-        <v>164</v>
+        <v>1059</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>1085</v>
+        <v>191</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>925</v>
+        <v>192</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E241" s="2"/>
+      <c r="E241" s="2" t="s">
+        <v>1087</v>
+      </c>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
       <c r="H241" s="2"/>
@@ -8787,20 +8785,18 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" s="2" t="s">
-        <v>1059</v>
+        <v>238</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>191</v>
+        <v>739</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>192</v>
+        <v>740</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E242" s="2" t="s">
-        <v>1087</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="E242" s="2"/>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
@@ -8808,13 +8804,13 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>739</v>
+        <v>620</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>740</v>
+        <v>698</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>155</v>
@@ -8827,104 +8823,98 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" s="2" t="s">
-        <v>241</v>
+        <v>1088</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>620</v>
+        <v>723</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>698</v>
+        <v>724</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="E244" s="2"/>
-      <c r="F244" s="2"/>
+      <c r="F244" s="2" t="s">
+        <v>193</v>
+      </c>
       <c r="G244" s="2"/>
       <c r="H244" s="2"/>
       <c r="I244" s="2"/>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A245" s="2" t="s">
-        <v>1088</v>
+      <c r="A245" s="9" t="s">
+        <v>1093</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>723</v>
+        <v>876</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>724</v>
+        <v>877</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>12</v>
+        <v>1071</v>
       </c>
       <c r="E245" s="2"/>
-      <c r="F245" s="2" t="s">
-        <v>193</v>
+      <c r="F245" s="1" t="s">
+        <v>1094</v>
       </c>
       <c r="G245" s="2"/>
       <c r="H245" s="2"/>
       <c r="I245" s="2"/>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A246" s="9" t="s">
-        <v>1093</v>
+      <c r="A246" s="2" t="s">
+        <v>1059</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>876</v>
+        <v>937</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>877</v>
+        <v>938</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E246" s="2"/>
-      <c r="F246" s="1" t="s">
-        <v>1094</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F246" s="2"/>
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
       <c r="I246" s="2"/>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" s="2" t="s">
-        <v>1059</v>
+        <v>1095</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>937</v>
+        <v>964</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>938</v>
+        <v>965</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>167</v>
+        <v>980</v>
       </c>
       <c r="E247" s="2"/>
-      <c r="F247" s="2"/>
-      <c r="G247" s="2"/>
+      <c r="F247" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G247" s="1" t="s">
+        <v>1097</v>
+      </c>
       <c r="H247" s="2"/>
       <c r="I247" s="2"/>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A248" s="2" t="s">
-        <v>1095</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="D248" s="2" t="s">
-        <v>980</v>
-      </c>
+      <c r="A248" s="2"/>
+      <c r="B248" s="2"/>
+      <c r="C248" s="2"/>
+      <c r="D248" s="2"/>
       <c r="E248" s="2"/>
-      <c r="F248" s="1" t="s">
-        <v>1096</v>
-      </c>
-      <c r="G248" s="1" t="s">
-        <v>1097</v>
-      </c>
+      <c r="F248" s="3"/>
+      <c r="G248" s="3"/>
       <c r="H248" s="2"/>
       <c r="I248" s="2"/>
     </row>
@@ -8934,8 +8924,8 @@
       <c r="C249" s="2"/>
       <c r="D249" s="2"/>
       <c r="E249" s="2"/>
-      <c r="F249" s="3"/>
-      <c r="G249" s="3"/>
+      <c r="F249" s="2"/>
+      <c r="G249" s="2"/>
       <c r="H249" s="2"/>
       <c r="I249" s="2"/>
     </row>
@@ -8975,91 +8965,91 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F5" r:id="rId1" xr:uid="{F837FE5B-009A-5E41-9919-715441AB0B1B}"/>
-    <hyperlink ref="G8" r:id="rId2" xr:uid="{A2E18574-7376-2D40-8622-EDDAC22418BA}"/>
-    <hyperlink ref="H15" r:id="rId3" xr:uid="{DE4DE499-C679-604C-AE6B-6B4D29D7C72F}"/>
-    <hyperlink ref="F16" r:id="rId4" xr:uid="{39D989A0-960F-074F-AC7D-11234243380B}"/>
-    <hyperlink ref="F38" r:id="rId5" xr:uid="{5E9C148C-AA79-1348-BCAC-FF7A1B7E74BF}"/>
-    <hyperlink ref="F41" r:id="rId6" xr:uid="{05A44978-D8E4-A244-8634-37AC1F1EB44C}"/>
-    <hyperlink ref="F42" r:id="rId7" xr:uid="{85B2974F-6824-6646-A292-8088C3ED1F69}"/>
-    <hyperlink ref="F70" r:id="rId8" xr:uid="{15A56521-14D7-9C41-AE6B-B476AE95BAAF}"/>
-    <hyperlink ref="F71" r:id="rId9" xr:uid="{9FA4EF41-0568-8645-8290-6DA9EAEABC36}"/>
-    <hyperlink ref="F78" r:id="rId10" xr:uid="{3EFF470B-0E94-214E-9443-E56AF17B121D}"/>
-    <hyperlink ref="F80" r:id="rId11" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{773FA8DE-2CC1-D945-9BA2-0AE1A31BC0E5}"/>
-    <hyperlink ref="F82" r:id="rId12" xr:uid="{FDB4BAB4-4A2A-AB45-8003-F395E02A7E62}"/>
-    <hyperlink ref="F83" r:id="rId13" xr:uid="{B59AAE8D-EA4E-8E46-BE1A-C8BDFB868748}"/>
-    <hyperlink ref="F84" r:id="rId14" xr:uid="{A3AC6792-7A06-904E-BC68-28F1DFF4075C}"/>
-    <hyperlink ref="F87" r:id="rId15" xr:uid="{56D0C844-74E6-7B4E-BBBB-462262C59A4E}"/>
-    <hyperlink ref="F88" r:id="rId16" xr:uid="{898CB5D7-DD4D-9440-BA59-4A64FF58061C}"/>
-    <hyperlink ref="F89" r:id="rId17" xr:uid="{31A17526-DE37-2B4C-98F8-A495DD8180BD}"/>
-    <hyperlink ref="F90" r:id="rId18" xr:uid="{51ECBB3A-79DE-7E41-9F2E-DBAEC891F74E}"/>
-    <hyperlink ref="F92" r:id="rId19" xr:uid="{71112AC6-CCBB-0349-ADF0-26B28C505F92}"/>
-    <hyperlink ref="F93" r:id="rId20" xr:uid="{83050CD8-ACBB-C64D-A443-B3A651F78132}"/>
-    <hyperlink ref="F94" r:id="rId21" xr:uid="{7ABB4F7F-F5E1-4441-8A70-8EE0325F6388}"/>
-    <hyperlink ref="F95" r:id="rId22" xr:uid="{2BECA3B4-A66A-DF4A-830B-B955578096F2}"/>
-    <hyperlink ref="F96" r:id="rId23" xr:uid="{FF0F0EB6-2E08-914B-B9FB-207F968038A7}"/>
-    <hyperlink ref="F99" r:id="rId24" xr:uid="{9717E59D-F205-8D4F-B3C1-3C0C1EF31108}"/>
-    <hyperlink ref="F100" r:id="rId25" xr:uid="{175DECD6-A8CF-8642-B6FE-CC0ECD3B4008}"/>
-    <hyperlink ref="F101" r:id="rId26" xr:uid="{6EC0E300-2055-0A49-864F-A4BA9C951517}"/>
-    <hyperlink ref="F102" r:id="rId27" xr:uid="{D1FF52B5-11E6-894C-8439-E8396B2A0B8A}"/>
-    <hyperlink ref="F103" r:id="rId28" xr:uid="{E0A67A88-07E4-DA44-A496-C32C764BEC62}"/>
-    <hyperlink ref="F104" r:id="rId29" xr:uid="{D725CEB7-BA74-4A4A-9121-47834676D8D2}"/>
-    <hyperlink ref="F113" r:id="rId30" xr:uid="{E672434A-25B7-0540-B1CD-140E91A14A5E}"/>
-    <hyperlink ref="F116" r:id="rId31" xr:uid="{46B62753-D89F-9940-AFB7-B4E4C83483E7}"/>
-    <hyperlink ref="F117" r:id="rId32" xr:uid="{F44A915A-9F9E-A14E-861B-4A0C9CC63348}"/>
-    <hyperlink ref="F118" r:id="rId33" xr:uid="{96C9F518-E770-434A-8663-5452F83CFD76}"/>
-    <hyperlink ref="F119" r:id="rId34" xr:uid="{7739C151-C132-0E4F-B8AE-E8367AAD6246}"/>
-    <hyperlink ref="F120" r:id="rId35" xr:uid="{1C83882E-8E5E-8345-BB7D-BB239ED3F784}"/>
-    <hyperlink ref="F121" r:id="rId36" xr:uid="{B2DA782D-8FD6-2541-BD05-A3C5843309E8}"/>
-    <hyperlink ref="F122" r:id="rId37" xr:uid="{ED3713D6-AD8E-B74A-8B98-3FEAA5003D75}"/>
-    <hyperlink ref="F123" r:id="rId38" xr:uid="{AEFE7C89-EC2A-A64F-A376-F292A548B8A4}"/>
-    <hyperlink ref="F124" r:id="rId39" xr:uid="{40437B6C-075B-6B4A-96BB-00BBF9D5EA40}"/>
-    <hyperlink ref="F130" r:id="rId40" xr:uid="{8E249B0C-4F6E-E14B-AD33-37C462E07AB0}"/>
-    <hyperlink ref="F137" r:id="rId41" xr:uid="{92B686E9-53CB-6549-8410-223F42D560CF}"/>
-    <hyperlink ref="F138" r:id="rId42" xr:uid="{9FBAB0F7-2225-1C44-9ACB-AD8A5F38CF10}"/>
-    <hyperlink ref="F142" r:id="rId43" xr:uid="{4327DB2B-149E-794F-A688-F5DED78F0A35}"/>
-    <hyperlink ref="F143" r:id="rId44" xr:uid="{50950B48-933C-204C-B4E5-41530AE555C9}"/>
-    <hyperlink ref="F144" r:id="rId45" xr:uid="{C33B52B5-9369-B344-B561-5340ECF445B8}"/>
-    <hyperlink ref="G145" r:id="rId46" xr:uid="{E02F97B6-41E0-6C47-B25D-59827C7DDB5F}"/>
-    <hyperlink ref="F146" r:id="rId47" xr:uid="{BCC9DAF4-2099-4D49-83A0-E491CF9009D4}"/>
-    <hyperlink ref="F147" r:id="rId48" xr:uid="{AFEACF1A-4527-6C41-852C-E65593625063}"/>
-    <hyperlink ref="F148" r:id="rId49" xr:uid="{E0A02364-027D-614F-BE1C-BD2731740E92}"/>
-    <hyperlink ref="F149" r:id="rId50" xr:uid="{3D6010C5-732A-4A4F-8703-EA585857FBEE}"/>
-    <hyperlink ref="F150" r:id="rId51" xr:uid="{F2EA3ADA-3A32-564E-8B15-98D059C308AC}"/>
-    <hyperlink ref="F151" r:id="rId52" xr:uid="{3486E020-2764-B84F-BA5A-27FB95FD2FAB}"/>
-    <hyperlink ref="F152" r:id="rId53" xr:uid="{C90D3824-FF88-6749-AA2E-1F783F598F2C}"/>
-    <hyperlink ref="F153" r:id="rId54" xr:uid="{0426AAFD-540B-5948-9623-32FDF41938DF}"/>
-    <hyperlink ref="F154" r:id="rId55" xr:uid="{4493A058-62F9-F747-9A2B-29CC2BC59FB1}"/>
-    <hyperlink ref="F155" r:id="rId56" xr:uid="{846F46B7-F73C-3542-A61D-FF7F60BF6E14}"/>
-    <hyperlink ref="F156" r:id="rId57" xr:uid="{F31E650C-5BB8-A842-B84A-757E43799774}"/>
-    <hyperlink ref="F160" r:id="rId58" xr:uid="{8785D4BD-0511-E84F-85F8-89061424CF07}"/>
-    <hyperlink ref="F161" r:id="rId59" xr:uid="{8174EE50-8065-834F-A8C9-D4CE3A8460FA}"/>
-    <hyperlink ref="F163" r:id="rId60" xr:uid="{CE794BAF-C7D1-EF4F-8E53-6B690380C297}"/>
-    <hyperlink ref="G163" r:id="rId61" xr:uid="{F3C24748-D246-B149-B3D6-2F558BC0A567}"/>
-    <hyperlink ref="H163" r:id="rId62" xr:uid="{3C2E15EE-D3BB-4E49-BFE1-9EE756E91621}"/>
-    <hyperlink ref="I163" r:id="rId63" xr:uid="{7CB05144-529A-4047-8600-6111EEA6B7F7}"/>
-    <hyperlink ref="G164" r:id="rId64" xr:uid="{E8286BB1-E3CC-0640-AC8F-B3C6066A5BDF}"/>
-    <hyperlink ref="F179" r:id="rId65" xr:uid="{D0BC1777-F31F-EB4E-91C5-6F9D918C63D1}"/>
-    <hyperlink ref="F192" r:id="rId66" xr:uid="{5D7A5891-ED27-2E45-A8F1-515302EF5C38}"/>
-    <hyperlink ref="F195" r:id="rId67" xr:uid="{CA5D1208-7C0A-C94E-90EE-749B2A5E1C05}"/>
-    <hyperlink ref="G195" r:id="rId68" xr:uid="{6479AE3D-0DC2-864C-8EE2-69D641BD80D4}"/>
-    <hyperlink ref="H195" r:id="rId69" xr:uid="{D7FA6D55-F268-EF4C-9BDC-694DBB9482E1}"/>
-    <hyperlink ref="I195" r:id="rId70" xr:uid="{C7074EC1-0FCB-3142-B7F7-F363A2E939B0}"/>
-    <hyperlink ref="F201" r:id="rId71" xr:uid="{F07CAA80-6FEB-9648-BFA4-69643BD1D2F2}"/>
-    <hyperlink ref="G201" r:id="rId72" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view" xr:uid="{27561D3E-E871-E348-9E3C-FCBE6BD2795D}"/>
-    <hyperlink ref="F216" r:id="rId73" xr:uid="{10CC2030-CFF7-AE48-8AC5-EFD3D795D7E4}"/>
-    <hyperlink ref="F217" r:id="rId74" xr:uid="{690867F5-8276-2346-8750-5A99A33F8BE3}"/>
-    <hyperlink ref="F218" r:id="rId75" xr:uid="{8D355359-2FC3-194B-825B-A421B209BB36}"/>
-    <hyperlink ref="F219" r:id="rId76" xr:uid="{0050D335-4F31-EB47-B470-1FD4F1867014}"/>
-    <hyperlink ref="F220" r:id="rId77" xr:uid="{60D3CEF3-D8EF-B84E-87A0-8BB2DCA3A1A7}"/>
-    <hyperlink ref="F225" r:id="rId78" xr:uid="{83220FA6-4F43-F246-A5E2-2D92CF0B88DF}"/>
-    <hyperlink ref="F228" r:id="rId79" xr:uid="{112F8051-E56D-E246-B326-AFA003D587DA}"/>
-    <hyperlink ref="F230" r:id="rId80" xr:uid="{4512F17F-DA68-524A-8326-8748C7BD9D63}"/>
-    <hyperlink ref="F231" r:id="rId81" xr:uid="{B1DA24A1-59F3-BE4C-9622-4E8DAD10017E}"/>
-    <hyperlink ref="F237" r:id="rId82" xr:uid="{6CDA9222-D464-8B4A-8535-E61CA8D6100F}"/>
-    <hyperlink ref="F246" r:id="rId83" xr:uid="{9573DE5D-3A50-2C4C-BD6C-D51F5E47AD48}"/>
-    <hyperlink ref="F248" r:id="rId84" xr:uid="{EB5AA941-4105-D746-9C12-9E3AA1AEC845}"/>
-    <hyperlink ref="G248" r:id="rId85" xr:uid="{18144297-1CD9-6E43-BCB4-CB02CC0EB017}"/>
+    <hyperlink ref="F5" r:id="rId1" xr:uid="{7D678CA7-FFC9-0642-BF6D-831A84FF2E86}"/>
+    <hyperlink ref="G8" r:id="rId2" xr:uid="{7EF37452-FB75-D645-AB06-83FC58895D99}"/>
+    <hyperlink ref="H15" r:id="rId3" xr:uid="{2663EC30-05C9-E946-AF07-8ABC091E7803}"/>
+    <hyperlink ref="F16" r:id="rId4" xr:uid="{DDC573EA-A7FD-A14D-A1F7-15A4732FB1FC}"/>
+    <hyperlink ref="F38" r:id="rId5" xr:uid="{E4987B93-0B6A-D046-A082-D2A436115363}"/>
+    <hyperlink ref="F41" r:id="rId6" xr:uid="{D66CF4F0-D6F1-1D45-8934-FDC71E9CFB77}"/>
+    <hyperlink ref="F42" r:id="rId7" xr:uid="{603418C6-0D27-2044-9D8B-B30A91669918}"/>
+    <hyperlink ref="F70" r:id="rId8" xr:uid="{AD5D6B79-C341-6441-BC79-B3754C38F4B4}"/>
+    <hyperlink ref="F71" r:id="rId9" xr:uid="{D7CA26E6-E9E1-764F-993F-7F4DC437F814}"/>
+    <hyperlink ref="F78" r:id="rId10" xr:uid="{3EB1B0D7-9BC0-E249-BFA7-07A145D6E419}"/>
+    <hyperlink ref="F80" r:id="rId11" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000qd93vYAA/view" xr:uid="{919A363A-2704-0941-9089-B68C847B68C8}"/>
+    <hyperlink ref="F82" r:id="rId12" xr:uid="{68DB40B7-B938-3340-B142-531875047CDF}"/>
+    <hyperlink ref="F83" r:id="rId13" xr:uid="{BBD58185-D491-774F-8870-E3762604ABD4}"/>
+    <hyperlink ref="F84" r:id="rId14" xr:uid="{D0631E7A-04D6-BD43-AC53-1AFF97C28471}"/>
+    <hyperlink ref="F87" r:id="rId15" xr:uid="{C1CA280A-6657-064E-A602-696A1E43F5FB}"/>
+    <hyperlink ref="F88" r:id="rId16" xr:uid="{15C8F6C5-D6EE-7E4D-88AB-7B246E1F663A}"/>
+    <hyperlink ref="F89" r:id="rId17" xr:uid="{3FB59042-0AE6-B945-AE8C-3666C7F04FCB}"/>
+    <hyperlink ref="F90" r:id="rId18" xr:uid="{344BB635-211E-3B40-9C10-563BE8C4AD99}"/>
+    <hyperlink ref="F92" r:id="rId19" xr:uid="{07BEB721-AB66-9442-A88D-47FC0FA39934}"/>
+    <hyperlink ref="F93" r:id="rId20" xr:uid="{64DCDAED-B639-7D41-8A47-81F0FEAFB3AB}"/>
+    <hyperlink ref="F94" r:id="rId21" xr:uid="{7B8746F9-5FDF-D241-9280-21CC6B74B8D2}"/>
+    <hyperlink ref="F95" r:id="rId22" xr:uid="{989F26C7-18F7-854C-968E-3C6DF0273708}"/>
+    <hyperlink ref="F96" r:id="rId23" xr:uid="{AC2B3B23-C09F-324B-B41F-D49EDAD01EC0}"/>
+    <hyperlink ref="F99" r:id="rId24" xr:uid="{298077C7-46EE-894F-AEC0-A805F20C6F35}"/>
+    <hyperlink ref="F100" r:id="rId25" xr:uid="{EA69D60D-02F3-EF48-B25E-8D55B17B3AB7}"/>
+    <hyperlink ref="F101" r:id="rId26" xr:uid="{8329693E-7EF9-7540-9D02-24F3A9C3ABB0}"/>
+    <hyperlink ref="F102" r:id="rId27" xr:uid="{5CE9C0D3-85FA-1747-A807-8BC50A1E5D38}"/>
+    <hyperlink ref="F103" r:id="rId28" xr:uid="{A0207670-7677-FB49-B611-1F487030BFB9}"/>
+    <hyperlink ref="F104" r:id="rId29" xr:uid="{1B1C35DF-C39C-4849-B3E0-2F5085185D1A}"/>
+    <hyperlink ref="F113" r:id="rId30" xr:uid="{21FD626A-D483-3B4E-A3B9-55C0AE5B417D}"/>
+    <hyperlink ref="F116" r:id="rId31" xr:uid="{D7D373B9-3622-514F-ACAD-D10850F67FEE}"/>
+    <hyperlink ref="F117" r:id="rId32" xr:uid="{ADA19048-4D4E-CE48-90EA-27354F82A0F8}"/>
+    <hyperlink ref="F118" r:id="rId33" xr:uid="{1EED59C2-A203-EA4F-9FF5-E787E416AF1F}"/>
+    <hyperlink ref="F119" r:id="rId34" xr:uid="{D8608A12-2296-BF4D-B432-99076F4ED1D0}"/>
+    <hyperlink ref="F120" r:id="rId35" xr:uid="{F2095FF9-459F-E349-98C9-2433741B0A07}"/>
+    <hyperlink ref="F121" r:id="rId36" xr:uid="{DCD408F2-D36D-7E44-B47E-74CEE71D2B61}"/>
+    <hyperlink ref="F122" r:id="rId37" xr:uid="{BEB9D810-C29F-EA47-A193-260E1DE43381}"/>
+    <hyperlink ref="F123" r:id="rId38" xr:uid="{55A16C94-BAA0-454C-B6CB-D30EB6D84ECC}"/>
+    <hyperlink ref="F124" r:id="rId39" xr:uid="{B70AE80F-F68C-BF4F-BA50-236E75C01E9A}"/>
+    <hyperlink ref="F130" r:id="rId40" xr:uid="{86E778C1-DDB9-0244-B4A8-6C40EEB05FC6}"/>
+    <hyperlink ref="F137" r:id="rId41" xr:uid="{78DEE783-B4DA-A741-A236-2C123381F446}"/>
+    <hyperlink ref="F138" r:id="rId42" xr:uid="{9DAD4803-FAE5-9349-93BA-0DA77365C8D6}"/>
+    <hyperlink ref="F142" r:id="rId43" xr:uid="{2025D596-CA79-A54C-8CCE-5D1573A94244}"/>
+    <hyperlink ref="F143" r:id="rId44" xr:uid="{4537A4C3-A490-AF4E-A446-1D71F0264BD6}"/>
+    <hyperlink ref="F144" r:id="rId45" xr:uid="{3D722801-BCA6-EE41-9368-F836370AC859}"/>
+    <hyperlink ref="G145" r:id="rId46" xr:uid="{A37F4900-84EB-4C4C-A378-BFA136963C42}"/>
+    <hyperlink ref="F146" r:id="rId47" xr:uid="{1914ADB3-2C18-FB4D-A895-E1E9C86DF058}"/>
+    <hyperlink ref="F147" r:id="rId48" xr:uid="{B186780C-E555-F540-A2E9-2FF47C37DA3D}"/>
+    <hyperlink ref="F148" r:id="rId49" xr:uid="{3C388B94-901C-FF4A-B6FC-14682105EE33}"/>
+    <hyperlink ref="F149" r:id="rId50" xr:uid="{EB91C546-0C1B-1D4B-AC1F-054C1A5AE178}"/>
+    <hyperlink ref="F150" r:id="rId51" xr:uid="{AC121ED8-9400-C443-8A30-369C6AB5D99A}"/>
+    <hyperlink ref="F151" r:id="rId52" xr:uid="{41C85CE4-6609-E943-A50F-D6975E90C654}"/>
+    <hyperlink ref="F152" r:id="rId53" xr:uid="{8394185F-C678-1F4A-B133-70C0B788C2ED}"/>
+    <hyperlink ref="F153" r:id="rId54" xr:uid="{1FDA7E8E-D1D0-8E49-9685-E98B9240311E}"/>
+    <hyperlink ref="F154" r:id="rId55" xr:uid="{41F02B6B-67A7-4F4B-AC6F-DF2FF7052623}"/>
+    <hyperlink ref="F155" r:id="rId56" xr:uid="{9273A798-E328-C348-936E-D3027E97899B}"/>
+    <hyperlink ref="F156" r:id="rId57" xr:uid="{C53A3F8A-4C57-AC46-899F-F5022A0D266B}"/>
+    <hyperlink ref="F160" r:id="rId58" xr:uid="{ADD438AF-FF7B-164F-B68E-B283AB5919A4}"/>
+    <hyperlink ref="F161" r:id="rId59" xr:uid="{A2C81EE3-1817-CF4F-AEAF-DF18E08335CF}"/>
+    <hyperlink ref="F163" r:id="rId60" xr:uid="{4FF42EFE-E839-1540-AA5A-021C2830645B}"/>
+    <hyperlink ref="G163" r:id="rId61" xr:uid="{E24E6E3A-F8DA-8544-A42B-31D64BD9F463}"/>
+    <hyperlink ref="H163" r:id="rId62" xr:uid="{B18B973E-C27C-B649-A0BD-97FEB64C35AC}"/>
+    <hyperlink ref="I163" r:id="rId63" xr:uid="{C54CB6B8-9E5C-2C45-925E-029E9E1844E8}"/>
+    <hyperlink ref="G164" r:id="rId64" xr:uid="{339763E2-D6BC-BE4E-BB60-736FE734C446}"/>
+    <hyperlink ref="F179" r:id="rId65" xr:uid="{1CA817FA-A7EB-3C4C-A96A-980499C334C0}"/>
+    <hyperlink ref="F192" r:id="rId66" xr:uid="{2F7AEC53-8C89-104B-A726-D5FB261833B3}"/>
+    <hyperlink ref="F195" r:id="rId67" xr:uid="{2A1B1B2D-D1A3-6944-88B0-6BC0E9DDB274}"/>
+    <hyperlink ref="G195" r:id="rId68" xr:uid="{8356A44E-3881-9B47-8A1C-220A732E3757}"/>
+    <hyperlink ref="H195" r:id="rId69" xr:uid="{77E3D0A9-FC48-BC40-957C-E93C50F3264E}"/>
+    <hyperlink ref="I195" r:id="rId70" xr:uid="{1994BD9B-5F6D-9D42-BBA3-E8502C3E41C5}"/>
+    <hyperlink ref="F201" r:id="rId71" xr:uid="{D3028D58-7789-834D-94E9-20E983CADC76}"/>
+    <hyperlink ref="G201" r:id="rId72" display="https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vZf98YAC/view" xr:uid="{0A541AC7-127D-7D48-A33F-97D34805C79F}"/>
+    <hyperlink ref="F216" r:id="rId73" xr:uid="{729754EC-8ED3-684D-9C04-30DB7E4A3D79}"/>
+    <hyperlink ref="F217" r:id="rId74" xr:uid="{43AAD8EC-4CD2-1E44-98E0-B8FCADE20A82}"/>
+    <hyperlink ref="F218" r:id="rId75" xr:uid="{6B5495F3-4FEC-2E44-A6D3-E5A1743A34DF}"/>
+    <hyperlink ref="F219" r:id="rId76" xr:uid="{89FA7EC9-BC01-5C48-A4A8-6D78744A673B}"/>
+    <hyperlink ref="F220" r:id="rId77" xr:uid="{70721A96-AACE-D946-A980-11DF667EFC29}"/>
+    <hyperlink ref="F225" r:id="rId78" xr:uid="{A52E33EE-3295-F84C-8908-8849084D4A76}"/>
+    <hyperlink ref="F228" r:id="rId79" xr:uid="{84301D3F-B7E0-0C4B-86D3-9A5432C80B0A}"/>
+    <hyperlink ref="F230" r:id="rId80" xr:uid="{19188191-9A18-E64B-A09A-6495C306CBDA}"/>
+    <hyperlink ref="F231" r:id="rId81" xr:uid="{5C5669F8-316E-D641-90D5-9D9DFB694979}"/>
+    <hyperlink ref="F237" r:id="rId82" xr:uid="{54C665A4-B8F4-3445-9ED1-E4A1B23BCE7E}"/>
+    <hyperlink ref="F245" r:id="rId83" xr:uid="{3041AEDF-D7CA-5040-ACB2-1A9CA316A35F}"/>
+    <hyperlink ref="F247" r:id="rId84" xr:uid="{FFC8A283-67C9-9543-840E-7262B41C4D46}"/>
+    <hyperlink ref="G247" r:id="rId85" xr:uid="{6F58BB39-7CE6-3940-A0BD-7EF768D61B66}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30702C2-3999-3C4E-A039-CB2E6F252050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCFB56D7-BFB7-3045-9378-2509741E37A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33340" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3061" uniqueCount="1098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3066" uniqueCount="1100">
   <si>
     <t>Household Name</t>
   </si>
@@ -3332,6 +3332,12 @@
   </si>
   <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000y6U47YAE/view</t>
+  </si>
+  <si>
+    <t>Lauren Shawver</t>
+  </si>
+  <si>
+    <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000y20uDYAQ/view</t>
   </si>
 </sst>
 </file>
@@ -8908,12 +8914,22 @@
       <c r="I247" s="2"/>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A248" s="2"/>
-      <c r="B248" s="2"/>
-      <c r="C248" s="2"/>
-      <c r="D248" s="2"/>
+      <c r="A248" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>1071</v>
+      </c>
       <c r="E248" s="2"/>
-      <c r="F248" s="3"/>
+      <c r="F248" s="1" t="s">
+        <v>1099</v>
+      </c>
       <c r="G248" s="3"/>
       <c r="H248" s="2"/>
       <c r="I248" s="2"/>
@@ -9050,6 +9066,7 @@
     <hyperlink ref="F245" r:id="rId83" xr:uid="{3041AEDF-D7CA-5040-ACB2-1A9CA316A35F}"/>
     <hyperlink ref="F247" r:id="rId84" xr:uid="{FFC8A283-67C9-9543-840E-7262B41C4D46}"/>
     <hyperlink ref="G247" r:id="rId85" xr:uid="{6F58BB39-7CE6-3940-A0BD-7EF768D61B66}"/>
+    <hyperlink ref="F248" r:id="rId86" xr:uid="{D4250793-AE22-D94D-80E0-4409E278BB60}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCFB56D7-BFB7-3045-9378-2509741E37A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72434A5-00E9-164E-A153-504BC810FD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33340" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3066" uniqueCount="1100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3067" uniqueCount="1100">
   <si>
     <t>Household Name</t>
   </si>
@@ -8737,7 +8737,9 @@
       <c r="B239" s="2" t="s">
         <v>928</v>
       </c>
-      <c r="C239" s="2"/>
+      <c r="C239" s="2" t="s">
+        <v>929</v>
+      </c>
       <c r="D239" s="2" t="s">
         <v>167</v>
       </c>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72434A5-00E9-164E-A153-504BC810FD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF08B247-8AB9-EF43-8BBC-D79253D97843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33340" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3067" uniqueCount="1100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3067" uniqueCount="1101">
   <si>
     <t>Household Name</t>
   </si>
@@ -3338,6 +3338,9 @@
   </si>
   <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000y20uDYAQ/view</t>
+  </si>
+  <si>
+    <t>HOLD- Tammy</t>
   </si>
 </sst>
 </file>
@@ -4872,7 +4875,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>202</v>
+        <v>1100</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>203</v>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF08B247-8AB9-EF43-8BBC-D79253D97843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8EF06C3-474F-0648-9832-68C01B99DA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33340" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -3310,9 +3310,6 @@
     <t>Manchester Grand Hyatt</t>
   </si>
   <si>
-    <t xml:space="preserve">Curebound Inventory </t>
-  </si>
-  <si>
     <t>Rady Kids Sponsored by Smith</t>
   </si>
   <si>
@@ -3341,6 +3338,9 @@
   </si>
   <si>
     <t>HOLD- Tammy</t>
+  </si>
+  <si>
+    <t>Garretts Popcorn</t>
   </si>
 </sst>
 </file>
@@ -4875,7 +4875,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>203</v>
@@ -6132,7 +6132,7 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>164</v>
+        <v>1100</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>406</v>
@@ -6141,7 +6141,7 @@
         <v>407</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>1090</v>
+        <v>155</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
@@ -8312,7 +8312,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>706</v>
@@ -8324,7 +8324,7 @@
         <v>980</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>1053</v>
@@ -8855,7 +8855,7 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" s="9" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>876</v>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="E245" s="2"/>
       <c r="F245" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G245" s="2"/>
       <c r="H245" s="2"/>
@@ -8897,7 +8897,7 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" s="2" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>964</v>
@@ -8910,17 +8910,17 @@
       </c>
       <c r="E247" s="2"/>
       <c r="F247" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G247" s="1" t="s">
         <v>1096</v>
-      </c>
-      <c r="G247" s="1" t="s">
-        <v>1097</v>
       </c>
       <c r="H247" s="2"/>
       <c r="I247" s="2"/>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A248" s="2" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>721</v>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="E248" s="2"/>
       <c r="F248" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G248" s="3"/>
       <c r="H248" s="2"/>

--- a/Pinktabletrackerlocal.xlsx
+++ b/Pinktabletrackerlocal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8EF06C3-474F-0648-9832-68C01B99DA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E48F038A-4764-6943-B875-02389ACE480B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33340" windowHeight="21100" xr2:uid="{FD50FAA3-49BA-8240-9E13-4B4D6922A4C0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3067" uniqueCount="1101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2829" uniqueCount="1085">
   <si>
     <t>Household Name</t>
   </si>
@@ -3214,12 +3214,6 @@
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uKciSYAS/view</t>
   </si>
   <si>
-    <t>HOLD - Trott</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CB </t>
-  </si>
-  <si>
     <t>Curebound Hold</t>
   </si>
   <si>
@@ -3229,9 +3223,6 @@
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000vTNtIYAW/view</t>
   </si>
   <si>
-    <t>Casa Dragones &amp; BRAND</t>
-  </si>
-  <si>
     <t>2 tickets each</t>
   </si>
   <si>
@@ -3241,106 +3232,67 @@
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uCpUlYAK/view</t>
   </si>
   <si>
-    <t>Chopard</t>
-  </si>
-  <si>
-    <t>Half Jennifer Ledfors/Half Sold Online</t>
-  </si>
-  <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000w7PJfYAM/view</t>
   </si>
   <si>
-    <t>Chuck Reiter</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sold Offline </t>
   </si>
   <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000w8AGvYAM/view</t>
   </si>
   <si>
-    <t>Larry Paulson</t>
-  </si>
-  <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000wYVO9YAO/view</t>
   </si>
   <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000wYVw1YAG/view</t>
   </si>
   <si>
-    <t>Ommid Asbaghi</t>
-  </si>
-  <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000wXRHlYAO/view</t>
   </si>
   <si>
-    <t>Kathy Stumm</t>
-  </si>
-  <si>
     <t>four way split</t>
   </si>
   <si>
     <t xml:space="preserve">potential table for Ommid's friend </t>
   </si>
   <si>
-    <t xml:space="preserve"> 1/2 Maryellen Aviano 1/2 Online</t>
-  </si>
-  <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000uutEVYAY/view</t>
   </si>
   <si>
-    <t>1/2 Eileen Zismer 1/2 CB</t>
-  </si>
-  <si>
     <t>1/2 Eileen Zismer &amp; 1/2 CB inventory</t>
   </si>
   <si>
     <t xml:space="preserve">E9 </t>
   </si>
   <si>
-    <t>1/2 Sold</t>
-  </si>
-  <si>
     <t>Possible hold for rob singh</t>
   </si>
   <si>
-    <t>Lyn Hall &amp; Fiona Mackin-Jha</t>
-  </si>
-  <si>
-    <t>Manchester Grand Hyatt</t>
-  </si>
-  <si>
-    <t>Rady Kids Sponsored by Smith</t>
-  </si>
-  <si>
     <t>Stephanie Smith Donating to cancer fighters</t>
   </si>
   <si>
-    <t>Tammy &amp; Larry Hershfeild</t>
-  </si>
-  <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000y36ZPYAY/view</t>
   </si>
   <si>
-    <t>Jessica Doshay &amp; Sarah Towner</t>
-  </si>
-  <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000x2HfWYAU/view</t>
   </si>
   <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000y6U47YAE/view</t>
   </si>
   <si>
-    <t>Lauren Shawver</t>
-  </si>
-  <si>
     <t>https://curebound.lightning.force.com/lightning/r/Opportunity/006QU00000y20uDYAQ/view</t>
   </si>
   <si>
-    <t>HOLD- Tammy</t>
-  </si>
-  <si>
-    <t>Garretts Popcorn</t>
+    <t>tammy finding a friend for this table</t>
+  </si>
+  <si>
+    <t>Daigle Concert 2026 Tickets | Opportunity | Salesforce</t>
+  </si>
+  <si>
+    <t>Near Cat Jamieson</t>
+  </si>
+  <si>
+    <t>Ortiguerra Concert 2026 Tickets | Opportunity | Salesforce</t>
   </si>
 </sst>
 </file>
@@ -3417,18 +3369,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="12"/>
-      <color rgb="FF242424"/>
+      <color rgb="FF9C0006"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3444,7 +3404,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3454,7 +3414,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3790,1281 +3752,1102 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7894B4-148E-174D-AE8B-E6DE441B89B0}">
-  <dimension ref="A1:I252"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>975</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="1" t="s">
-        <v>1074</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>1031</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1031</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>976</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>1047</v>
       </c>
+      <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>977</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
         <v>41</v>
       </c>
+      <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2" t="s">
         <v>49</v>
       </c>
+      <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>54</v>
+        <v>717</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2" t="s">
         <v>57</v>
       </c>
+      <c r="F1